--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbbe609a94fe6405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Rd9ffae5f9e08499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R5281c784f09c4ac1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Ra88293b40c3647bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R486f71848f1d4fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R8e0656c55bf34d82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Red754b3f4e034903"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R99b1a9c2e2584d78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R03a020807e4c4926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R82cadf81c1fe46c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R1bb771829ec04e1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="Rcea8f5695dda49d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Re49b14150b8b4fda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R74900d517ef64b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R7a333a2784b7412a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="Rbf30424629834973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R56f9982514ec4c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R52ab312bf27f43ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rfe9c7bbfcb3e4cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R4ae80a3db4ac48e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rd6336210097e425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Ra8ef5ec2e43646e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R9bbdac122ee443a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R23d983b4e0b54559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R87e16378cec04e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Rcdd268ce4c2e44a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rfe5d0e44ed5744c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R3f6c0464f8ca4e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R1e3dd2b250ac45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R821ecf18f1d84721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Re9aa046ae6e144a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Raa88f68917964720"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R5e9b3d1fed294da5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Re06998f4bed2431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R1c322b1a273146f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R9c5895f5b71d407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R2c199b36166f4ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R1ed7fc4d538c4bce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Redeac162ebee46b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="Rd5683193bee24f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R47221c194dbc4565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R56e91dae03db40cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R6b712a79253b4aa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R16da6693456342a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R839f10c154824757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R21e1a3d00c3b4fc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R9451357a51134cbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="R859e328057004a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R80f0cdbfee934eca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R0a82bb8127134445"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Ra4f2147d959741cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R4bd1322932774738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rc16da02fedbd474b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Rb1bb4276559242ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Raf0bfe3f87b64467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R7166dd472ac14dd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Re5f45c15dbd24c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R5c39db710e6c4020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R2d2d44852a834fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R594b761480e547bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rccaa6c3739ab4d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R3da6f002791b4da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R53434dee85974d61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R811d5e952e86496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R1137bd330331448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R24fe666cb85f4a7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R25283bf47a754fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rc91414faee36438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Re9ff0c04f09641c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="Rc27ed19f114f430e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Re129f1cbb9904d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rbe55f94bbad54bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R5499cef0e3f34d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="Rdd1f17b2cb30447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R923b51ac0595453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Rf62e835aadc647d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rdf48a97b2ae148b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R7c58b57d949a4ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rd12114bcffd94601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rf6eb86bd258d4596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rb8ca52395bd34c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R42dc08fe01ad4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R2f791a86bea747a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R25f6899593e44230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R2627ba994766437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R8209352158df40a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R8dd65bdd0cd84139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Raf1c3ff93da0451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R0f40aef933c14f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R90feb16396af48c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R551da609cef746cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R0fcc51ad90a5453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rf7245d1c83844a9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rd1e09b7f635e48ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R6171d3d61e864a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R9530e900431c407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R8445655acc534906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R0c7d5c727fc641b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Raa5c2c4fa6674e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R230e483b87e74047"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R1ff023cfe0924178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R13ebd64926b84e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R52389870c8024969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rffee81e084c34d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R19773a28afd04520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R2862f88e3dc34d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R5aa81de6bf5a4f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R5693377c424a467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R5f6c0f75bb9e4c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rafb0645ceffe4d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rfc5b57c03fe240bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R9aeb6de9abdc4eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R0af15f49ea724801"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Rb938ba0233104cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rb2932757ae824c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R2c590a6204d44fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Raae9fa6d54984c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R19798d42e55b4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R0c8b60a5550749d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rd0431f8af02b4055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R7f4f575efdca4c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rff01e373444f4e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rf404238e04de469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R7dfd9445dc784c39"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2310,9 +2310,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -2381,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R746a0e22665c455e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R33dc2c58b3e24603"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2704,15 +2702,15 @@
       </x:c>
       <x:c r="B5" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$222,"MVP")</x:f>
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.009433962264150943</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2805,7 +2803,7 @@
       </x:c>
       <x:c r="G8" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F8)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3974,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77cd311e3024246"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra941cc7dbd444fa7"/>
 </x:worksheet>
 </file>
 
@@ -10687,19 +10685,46 @@
       <x:c r="M11" s="32" t="n"/>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
-      <x:c r="A12" s="32" t="n"/>
-      <x:c r="B12" s="32" t="n"/>
-      <x:c r="C12" s="32" t="n"/>
-      <x:c r="D12" s="32" t="n"/>
-      <x:c r="E12" s="32" t="n"/>
-      <x:c r="F12" s="32" t="n"/>
-      <x:c r="G12" s="32" t="n"/>
-      <x:c r="H12" s="32" t="n"/>
-      <x:c r="I12" s="376" t="n"/>
-      <x:c r="J12" s="32" t="n"/>
-      <x:c r="K12" s="32" t="n"/>
-      <x:c r="L12" s="32" t="n"/>
-      <x:c r="M12" s="32" t="n"/>
+      <x:c r="A12" s="32" t="str">
+        <x:v>R-001</x:v>
+      </x:c>
+      <x:c r="B12" s="32" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C12" s="32" t="str">
+        <x:v>Foundation</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="str">
+        <x:v>Platform monorepo bootstrap</x:v>
+      </x:c>
+      <x:c r="E12" s="32" t="str">
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+      </x:c>
+      <x:c r="F12" s="32" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G12" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H12" s="32" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I12" s="376" t="n">
+        <x:f>IF(H12="Done",1,IF(H12="In Progress",0.5,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L12" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 8a12c4489e078072bfef689c3bfbf5e8042b993c</x:v>
+      </x:c>
+      <x:c r="M12" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="inlineStr">
@@ -21166,7 +21191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb9b5b7e13c748d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R308e65523c8a432d"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R53434dee85974d61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R811d5e952e86496d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R1137bd330331448f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R24fe666cb85f4a7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R25283bf47a754fcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rc91414faee36438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Re9ff0c04f09641c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="Rc27ed19f114f430e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Re129f1cbb9904d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rbe55f94bbad54bdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R5499cef0e3f34d2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="Rdd1f17b2cb30447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R923b51ac0595453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Rf62e835aadc647d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rdf48a97b2ae148b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R7c58b57d949a4ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rd12114bcffd94601"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rf6eb86bd258d4596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rb8ca52395bd34c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R42dc08fe01ad4ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R2f791a86bea747a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R25f6899593e44230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R2627ba994766437a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R8209352158df40a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R8dd65bdd0cd84139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Raf1c3ff93da0451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R0f40aef933c14f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R90feb16396af48c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R551da609cef746cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R0fcc51ad90a5453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rf7245d1c83844a9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rd1e09b7f635e48ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R6171d3d61e864a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R9530e900431c407e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R8445655acc534906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R0c7d5c727fc641b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Raa5c2c4fa6674e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R230e483b87e74047"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R1ff023cfe0924178"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R13ebd64926b84e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R52389870c8024969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rffee81e084c34d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R19773a28afd04520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R2862f88e3dc34d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R5aa81de6bf5a4f5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R5693377c424a467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R5f6c0f75bb9e4c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rafb0645ceffe4d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rfc5b57c03fe240bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R9aeb6de9abdc4eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R0af15f49ea724801"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Rb938ba0233104cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rb2932757ae824c10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R2c590a6204d44fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Raae9fa6d54984c0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R19798d42e55b4536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R0c8b60a5550749d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rd0431f8af02b4055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R7f4f575efdca4c12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rff01e373444f4e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rf404238e04de469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R7dfd9445dc784c39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcce5a4271fdd419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R873991dd74de4312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R2b4b18eb72474075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Ree55d45e30354faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rd2cc8fce176d4fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rd7b95eb9440640e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R64f12543ff7c4d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R5d6665c006d94d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R5841bf770ad4473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R391a0c040616469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Rca93e63580834734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R00d3a828e7dc42d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rec2790c465f14dfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R6caab6076d9040f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R2ba545387a2e40f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R99e977f6e4d8475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R08bf5749087244a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Re01a644b94834c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Ra82be8d8d1ed4e01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R5bb75f4bac5b45d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R7ffe4c646fe2492c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R4cad4b62f2bb4760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R67c8cd945d9341ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R8613b7e33dea4624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Reffb609e029c4c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R486aa7ae100545a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R9557c25d386844ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R0f483e93beaa48bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Rdc731b3d155a401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Rb3c968e776c943ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rb1dada1a743a4e5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R405b08135a694214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R893c054fd75a48af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R2f0052978a1d4240"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Re328dc2fb7564d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R80b79a23ff0247e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rf7e068e013324921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R0960dad9b5214e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rcf10b90fb6b84791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R4225c18de0134965"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R0e2918abad244cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rf55fc6aa82e64253"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R12186a36ce9045d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R690d1cba378444ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R5c94faac583d414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R45eaf74270a6410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R69ebcad7e3994a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rbdd1d8e9f13c44b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rbbb70bf6e3a541a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rd223f13db0fb41fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Rb302da5ddc5e4414"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R9f49acb8c40c4fa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rde2bcba4d86c497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R69a0cba04f0240dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Ra8c6771fcab04b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Rda3adcc18fcf4e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rabf3efc9a1ff4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rdbf6625df3dc4767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R96be7971c4124993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R3e1062837bed4356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rf85a4aca30c34e30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R43213853d3fa49ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R33dc2c58b3e24603"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf1ee6919bce44265"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra941cc7dbd444fa7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe35812a2fe64fbb"/>
 </x:worksheet>
 </file>
 
@@ -10720,7 +10720,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 8a12c4489e078072bfef689c3bfbf5e8042b993c</x:v>
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
         <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
@@ -21191,7 +21191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R308e65523c8a432d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R138fe27d356948a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcce5a4271fdd419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R873991dd74de4312"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R2b4b18eb72474075"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Ree55d45e30354faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rd2cc8fce176d4fc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rd7b95eb9440640e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R64f12543ff7c4d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R5d6665c006d94d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R5841bf770ad4473e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R391a0c040616469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Rca93e63580834734"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R00d3a828e7dc42d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rec2790c465f14dfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R6caab6076d9040f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R2ba545387a2e40f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R99e977f6e4d8475f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R08bf5749087244a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Re01a644b94834c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Ra82be8d8d1ed4e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R5bb75f4bac5b45d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R7ffe4c646fe2492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R4cad4b62f2bb4760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R67c8cd945d9341ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R8613b7e33dea4624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Reffb609e029c4c5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R486aa7ae100545a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R9557c25d386844ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R0f483e93beaa48bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Rdc731b3d155a401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Rb3c968e776c943ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rb1dada1a743a4e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R405b08135a694214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R893c054fd75a48af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R2f0052978a1d4240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Re328dc2fb7564d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R80b79a23ff0247e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rf7e068e013324921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R0960dad9b5214e24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rcf10b90fb6b84791"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R4225c18de0134965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R0e2918abad244cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rf55fc6aa82e64253"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R12186a36ce9045d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R690d1cba378444ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R5c94faac583d414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R45eaf74270a6410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R69ebcad7e3994a5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rbdd1d8e9f13c44b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rbbb70bf6e3a541a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rd223f13db0fb41fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Rb302da5ddc5e4414"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R9f49acb8c40c4fa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rde2bcba4d86c497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R69a0cba04f0240dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Ra8c6771fcab04b14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Rda3adcc18fcf4e92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rabf3efc9a1ff4d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rdbf6625df3dc4767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R96be7971c4124993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R3e1062837bed4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rf85a4aca30c34e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R43213853d3fa49ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R055dc900bf2241c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Ra031a499505a4af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Racc121a9012349c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Rf24acdf53d5640f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rc953ee98501742dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R23d0eac6df534487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R262c1aefed3346b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R7c39edeabce34a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rf7e4511bd0d34750"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rae53df53fb2e4b62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Rbe94df90b5aa4fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="Rcd4c8e4069fb4194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rc421fbcf855c40bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R4b5d18a925ee44dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R6c51546179bb4080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R22b524276f274abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R4ef8fa1b37534d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R2e813f8cde7b40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="R6e8830cb46154bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R000709e30b324215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R32ee06ef527748c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rb37354c0d353430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R997fa43272c74878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Rd1b0a06f73744779"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Raffa046de9a74d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R34fd07f56a09401e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rd4be4754cbf14140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Ra698f838b3c44a41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R316da57ee7644c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R424e2f8462ae4378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Ref7493ba32574737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R1b5b1b8ebe354f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rc845f6c0c26a4a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rdf97651bb4644c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Rf3da740d1a5649a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R6002af1f50ac4998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R23e0bcb00b714400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Rf1bbcc12089c4400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R12b282c398c843ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R432209197d504cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rddaae48048f74a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rdeeb8b5438414bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="Rd7e878b7f33c4506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="Rb3bf180fb85f4a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R41d0fc2312a64676"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R32def2ff70a84778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Rc2576c8541c94bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rff5b9ff7047041e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rd05cf17ea27e4644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R6ec1e6f264814db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Rb32cb386a2264d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R79d884b815464368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R6c08667853464a8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R2269e45d1a884ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R37e001332890456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Re71c31b28a014bee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Red3f4c4fc7e14e28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R2892f2cde1cb4d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R828a973a1be34cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R0cb5167682514729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R9f7ce3147da74f7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R8441a1c28a894bd8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf1ee6919bce44265"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc435c82eb18c4027"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2702,7 +2702,7 @@
       </x:c>
       <x:c r="B5" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$222,"MVP")</x:f>
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
@@ -2710,7 +2710,7 @@
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.009433962264150943</x:v>
+        <x:v>0.009345794392523364</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F6)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe35812a2fe64fbb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d8b9323a55a45ff"/>
 </x:worksheet>
 </file>
 
@@ -10670,19 +10670,46 @@
       <x:c r="M10" s="32" t="n"/>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
-      <x:c r="A11" s="32" t="n"/>
-      <x:c r="B11" s="32" t="n"/>
-      <x:c r="C11" s="32" t="n"/>
-      <x:c r="D11" s="32" t="n"/>
-      <x:c r="E11" s="32" t="n"/>
-      <x:c r="F11" s="32" t="n"/>
-      <x:c r="G11" s="32" t="n"/>
-      <x:c r="H11" s="32" t="n"/>
-      <x:c r="I11" s="376" t="n"/>
-      <x:c r="J11" s="32" t="n"/>
-      <x:c r="K11" s="32" t="n"/>
-      <x:c r="L11" s="32" t="n"/>
-      <x:c r="M11" s="32" t="n"/>
+      <x:c r="A11" s="32" t="str">
+        <x:v>R-002</x:v>
+      </x:c>
+      <x:c r="B11" s="32" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C11" s="32" t="str">
+        <x:v>Data</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="str">
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+      </x:c>
+      <x:c r="E11" s="32" t="str">
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+      </x:c>
+      <x:c r="F11" s="32" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G11" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H11" s="32" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="I11" s="376" t="n">
+        <x:f>IF(H11="Done",1,IF(H11="In Progress",0.5,0))</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="J11" s="32" t="str">
+        <x:v>R-001</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L11" s="32" t="str">
+        <x:v>task contract recorded; static Compose and migration checks pass</x:v>
+      </x:c>
+      <x:c r="M11" s="32" t="str">
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
@@ -21191,7 +21218,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R138fe27d356948a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcedfc23c096340a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R055dc900bf2241c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Ra031a499505a4af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Racc121a9012349c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Rf24acdf53d5640f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rc953ee98501742dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R23d0eac6df534487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R262c1aefed3346b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R7c39edeabce34a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rf7e4511bd0d34750"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rae53df53fb2e4b62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Rbe94df90b5aa4fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="Rcd4c8e4069fb4194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rc421fbcf855c40bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R4b5d18a925ee44dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R6c51546179bb4080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R22b524276f274abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R4ef8fa1b37534d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R2e813f8cde7b40d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="R6e8830cb46154bf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R000709e30b324215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R32ee06ef527748c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rb37354c0d353430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R997fa43272c74878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Rd1b0a06f73744779"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Raffa046de9a74d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R34fd07f56a09401e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rd4be4754cbf14140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Ra698f838b3c44a41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R316da57ee7644c98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R424e2f8462ae4378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Ref7493ba32574737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R1b5b1b8ebe354f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rc845f6c0c26a4a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rdf97651bb4644c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Rf3da740d1a5649a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R6002af1f50ac4998"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R23e0bcb00b714400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Rf1bbcc12089c4400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R12b282c398c843ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R432209197d504cfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rddaae48048f74a9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rdeeb8b5438414bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="Rd7e878b7f33c4506"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="Rb3bf180fb85f4a45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R41d0fc2312a64676"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R32def2ff70a84778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Rc2576c8541c94bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rff5b9ff7047041e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rd05cf17ea27e4644"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R6ec1e6f264814db0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Rb32cb386a2264d78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R79d884b815464368"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R6c08667853464a8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R2269e45d1a884ab9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R37e001332890456d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Re71c31b28a014bee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Red3f4c4fc7e14e28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R2892f2cde1cb4d81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R828a973a1be34cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R0cb5167682514729"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R9f7ce3147da74f7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R8441a1c28a894bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R30dfdbe8a4214586"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R6dd41cb6189e4b92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rbf48f50fcaac4fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Ra85df556ebf94f4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R7fc125ec1fcd4d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R689da3e4b9094b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R850485b156c84206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R4cc16544f20c4b29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R4dc22b7c7c6444af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R62bf6f9031294e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Ra6f563bdafd44ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R5f10c292c36e4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rc25e933c46374d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R0828258b76844c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R0cf53487725d4b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R6f802ce7454b43eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rec6bf71fb99744d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R6895a9537831455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rbeb580ff773d400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R6fe18c14d8b64232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rcc6bb55f08a04baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rd41e25fa45eb4e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="Rb963ed8edc634ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R08769eed11c44e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rfb172b85f0b34f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Rfa4d88d47a504366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R18a1c0d254f94fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Rc29e70a6a9454333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R7aca78547cd84097"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R8608465f29334255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rbfcc86ad20d64ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R61ceca7a3a874a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R28a520315385444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R0244a1f44de34a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R254bde6a66284d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Ra798b0e058104f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rc73c81ef8cd047c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R81e1357580554d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rff75b2da3a7f4160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R4f2a7d62c167415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rdf96649e006c4689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Re1da4396c79e4c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R0ddbc8d377cc4023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R2976ceeb57ca4b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="Rcf6d3a9f2a4f4b69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="Rf78a8dbd791944d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R19641641136a4dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rac192eb5abaa4c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rf905d382e27f4014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rb0247ad453a24341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R712f047b5b32411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Ra8f29b6cf15f4834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R38dc9e50aac34516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Rdbea0b634cfd43e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R09317ba2a26c43cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Ra931e516b884493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Ra08ba73841a74cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R7ec8db2d04b74fd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R7db43b5a5641498e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R7fb527def27f4f61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R79bdb25758404d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R4ba89d80aef74606"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc435c82eb18c4027"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e6d6ae1f3a04092"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2706,11 +2706,11 @@
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.009345794392523364</x:v>
+        <x:v>0.018691588785046728</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F6)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2803,7 +2803,7 @@
       </x:c>
       <x:c r="G8" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F8)</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d8b9323a55a45ff"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1281b347a9d84fb2"/>
 </x:worksheet>
 </file>
 
@@ -10692,11 +10692,11 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H11" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I11" s="376" t="n">
         <x:f>IF(H11="Done",1,IF(H11="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
         <x:v>R-001</x:v>
@@ -10705,7 +10705,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>task contract recorded; static Compose and migration checks pass</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
         <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
@@ -21218,7 +21218,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcedfc23c096340a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R658fa812d75c4342"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R30dfdbe8a4214586"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R6dd41cb6189e4b92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rbf48f50fcaac4fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Ra85df556ebf94f4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R7fc125ec1fcd4d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R689da3e4b9094b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R850485b156c84206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R4cc16544f20c4b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R4dc22b7c7c6444af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R62bf6f9031294e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Ra6f563bdafd44ec3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R5f10c292c36e4dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rc25e933c46374d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R0828258b76844c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R0cf53487725d4b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R6f802ce7454b43eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rec6bf71fb99744d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R6895a9537831455e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rbeb580ff773d400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R6fe18c14d8b64232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rcc6bb55f08a04baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rd41e25fa45eb4e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="Rb963ed8edc634ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R08769eed11c44e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rfb172b85f0b34f04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Rfa4d88d47a504366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R18a1c0d254f94fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Rc29e70a6a9454333"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R7aca78547cd84097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R8608465f29334255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rbfcc86ad20d64ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R61ceca7a3a874a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R28a520315385444f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R0244a1f44de34a5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R254bde6a66284d41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Ra798b0e058104f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rc73c81ef8cd047c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R81e1357580554d18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rff75b2da3a7f4160"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R4f2a7d62c167415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rdf96649e006c4689"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Re1da4396c79e4c9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R0ddbc8d377cc4023"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R2976ceeb57ca4b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="Rcf6d3a9f2a4f4b69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="Rf78a8dbd791944d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R19641641136a4dfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rac192eb5abaa4c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rf905d382e27f4014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rb0247ad453a24341"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R712f047b5b32411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Ra8f29b6cf15f4834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R38dc9e50aac34516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Rdbea0b634cfd43e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R09317ba2a26c43cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Ra931e516b884493a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Ra08ba73841a74cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R7ec8db2d04b74fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R7db43b5a5641498e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R7fb527def27f4f61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R79bdb25758404d6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R4ba89d80aef74606"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R00d7f0a73cdf45ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Re0202e6fcad941e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R7b70692b89404357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Rf4c6d44c25594c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rb342a0bf540748cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R7a737c0e45d34555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R24fe5548064d4c41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R44e7375bbad245be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R78f01624e0e44a09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rc3a7aab8c00b4532"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R83a2a836b535473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R2589996fc76d4b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R2bc7c8c834664593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Ra9730933a1b846f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rd4403e296e024055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R472f54521621486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R8c22e830b0f348f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R04e83f3e37ae46bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="R194b62c715e744af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R6e907ebfbed84f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rddd74835f85d4509"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R4d2d2429a2e74e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="Radefe041470246a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Ra9c69dc89df84f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R95aa3bb8b3a743f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Rda1b821fc4dc4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R04377a60c5d44424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R37588fbc27304fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R44271d7c04d241aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R90b07ede2dca4ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R8b3343dbcff548b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rca8824d877014da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rb1e066dadbc1470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rd747f63dafe64618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R0c836f4f212c4dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R36bd44e5fe17490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R3e86a50313c84742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Re01fe66c50ab4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rd50c265820004029"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R243381d39d8b43fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rb3ed12f7c3da4dbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rf6c313ff76884794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R5d94ba99ef304488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R62180abd8cfc4222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R6b3544e4ab6e4f30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R538e66e9adf24efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R4e798b72d83b4704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="R98b425bd4af24233"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R3eb03668fe734ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R6591e613a2cb4c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Raa6db372f38142a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Ra402f6c81f584542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Ra05fc1aa689b49a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R96f7272ba3a24fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R69dd3172312a45fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R2d19f12323dd474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R7ce6120509624fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rd9a2385e5ffc4118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="Rfea6e29156754801"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R1b60c1475e6846f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rfca6dd5e58d2488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R45af6a41d7104827"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e6d6ae1f3a04092"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R13cddeb11a084527"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2702,7 +2702,7 @@
       </x:c>
       <x:c r="B5" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$222,"MVP")</x:f>
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
@@ -2710,7 +2710,7 @@
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.018691588785046728</x:v>
+        <x:v>0.018518518518518517</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F6)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1281b347a9d84fb2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dae25eb44e74dc4"/>
 </x:worksheet>
 </file>
 
@@ -10655,19 +10655,46 @@
       <x:c r="M9" s="32" t="n"/>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
-      <x:c r="A10" s="32" t="n"/>
-      <x:c r="B10" s="32" t="n"/>
-      <x:c r="C10" s="32" t="n"/>
-      <x:c r="D10" s="32" t="n"/>
-      <x:c r="E10" s="32" t="n"/>
-      <x:c r="F10" s="32" t="n"/>
-      <x:c r="G10" s="32" t="n"/>
-      <x:c r="H10" s="32" t="n"/>
-      <x:c r="I10" s="376" t="n"/>
-      <x:c r="J10" s="32" t="n"/>
-      <x:c r="K10" s="32" t="n"/>
-      <x:c r="L10" s="32" t="n"/>
-      <x:c r="M10" s="32" t="n"/>
+      <x:c r="A10" s="32" t="str">
+        <x:v>R-003</x:v>
+      </x:c>
+      <x:c r="B10" s="32" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C10" s="32" t="str">
+        <x:v>Models</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="str">
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+      </x:c>
+      <x:c r="E10" s="32" t="str">
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+      </x:c>
+      <x:c r="F10" s="32" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G10" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H10" s="32" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="I10" s="376" t="n">
+        <x:f>IF(H10="Done",1,IF(H10="In Progress",0.5,0))</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="J10" s="32" t="str">
+        <x:v>R-002</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L10" s="32" t="str">
+        <x:v>task contract recorded; existing local models discovered</x:v>
+      </x:c>
+      <x:c r="M10" s="32" t="str">
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
@@ -21218,7 +21245,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R658fa812d75c4342"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e492d900a2a440d"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R00d7f0a73cdf45ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Re0202e6fcad941e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R7b70692b89404357"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Rf4c6d44c25594c1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rb342a0bf540748cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R7a737c0e45d34555"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R24fe5548064d4c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R44e7375bbad245be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R78f01624e0e44a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rc3a7aab8c00b4532"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R83a2a836b535473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R2589996fc76d4b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R2bc7c8c834664593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Ra9730933a1b846f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rd4403e296e024055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R472f54521621486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R8c22e830b0f348f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R04e83f3e37ae46bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="R194b62c715e744af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R6e907ebfbed84f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rddd74835f85d4509"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R4d2d2429a2e74e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="Radefe041470246a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Ra9c69dc89df84f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R95aa3bb8b3a743f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Rda1b821fc4dc4c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R04377a60c5d44424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R37588fbc27304fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R44271d7c04d241aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R90b07ede2dca4ca0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R8b3343dbcff548b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rca8824d877014da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rb1e066dadbc1470f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rd747f63dafe64618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R0c836f4f212c4dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R36bd44e5fe17490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R3e86a50313c84742"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Re01fe66c50ab4c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rd50c265820004029"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R243381d39d8b43fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rb3ed12f7c3da4dbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rf6c313ff76884794"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R5d94ba99ef304488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R62180abd8cfc4222"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R6b3544e4ab6e4f30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R538e66e9adf24efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R4e798b72d83b4704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="R98b425bd4af24233"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R3eb03668fe734ecd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R6591e613a2cb4c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Raa6db372f38142a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Ra402f6c81f584542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Ra05fc1aa689b49a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R96f7272ba3a24fc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R69dd3172312a45fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R2d19f12323dd474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R7ce6120509624fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rd9a2385e5ffc4118"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="Rfea6e29156754801"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R1b60c1475e6846f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rfca6dd5e58d2488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R45af6a41d7104827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reb09c50866a4468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R7840e42548674cad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R9069d6e5481849d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R3c542c3193b94325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R2eb1dff453ed4a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R62e555690fc542be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Ra2d0c23a2f304d5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R730012f6360a43a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Re7e6b3f16d2d440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R5377cc5b07324889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R9b8857cbb2334cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R0afa09499cd34be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R159eea6fa51e452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R30df471c68524bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Re70996f2e50c4645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R5d375f470d9b4d2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rf1124f7814154b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R89a5f63759934c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Ra41f755ee044498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R72d1f2dfdde94d13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R270b5ffb660242f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rc2a1cb3189734183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R34979fe55fc74a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R42df6e56253e4b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rfe04e657137f43a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Re9d515345bf640bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R3f260f61bd5241ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R74a4fd70205442e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R899744d06c88468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Rfc4ef13310d24b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R822e84e6b7cf4a27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rbee77dbe4c7d4723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R5f85690d9665476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R4daaf45726794e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R6afe2279321740f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Rb052c1579dd848d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rccce0e7fe5f44386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Rbed796f6c7a34ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Re2e534ba97634b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R9e857ad26fc74191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Re1dc9713f1f74161"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R39ea44b2d3754a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R7b45cb3435fd47d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R8f33ac9219e94bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R18fd06a2f5f54a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R2d84666f629f424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Rd154960bc7494c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="R7c4abb49f1e24ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R63b2009c5509487c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R5046c29838cf4cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R14a8ee372b0445fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R61b4c286f0d14e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rca8dccedfc6b47c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R12239c58f8004104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R49eaede7d7d04645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Rb001f705c49e4437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R14553b24b76d4d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R811d3acb194841d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="Rce208b14e94b4831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R152813ae02224dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rce52d7cf754742c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R20cfcd4158a54dc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R13cddeb11a084527"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re23275222e1e45e8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2706,11 +2706,11 @@
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.018518518518518517</x:v>
+        <x:v>0.027777777777777776</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F6)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2803,7 +2803,7 @@
       </x:c>
       <x:c r="G8" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F8)</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dae25eb44e74dc4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8872284e5de04766"/>
 </x:worksheet>
 </file>
 
@@ -10677,11 +10677,11 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H10" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I10" s="376" t="n">
         <x:f>IF(H10="Done",1,IF(H10="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
         <x:v>R-002</x:v>
@@ -10690,7 +10690,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>task contract recorded; existing local models discovered</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
         <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
@@ -21245,7 +21245,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e492d900a2a440d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87b80298bf6640dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reb09c50866a4468a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R7840e42548674cad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R9069d6e5481849d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R3c542c3193b94325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R2eb1dff453ed4a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R62e555690fc542be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Ra2d0c23a2f304d5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R730012f6360a43a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Re7e6b3f16d2d440e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R5377cc5b07324889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R9b8857cbb2334cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R0afa09499cd34be8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R159eea6fa51e452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R30df471c68524bed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Re70996f2e50c4645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R5d375f470d9b4d2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rf1124f7814154b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R89a5f63759934c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Ra41f755ee044498f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R72d1f2dfdde94d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R270b5ffb660242f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rc2a1cb3189734183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R34979fe55fc74a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R42df6e56253e4b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rfe04e657137f43a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Re9d515345bf640bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R3f260f61bd5241ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R74a4fd70205442e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R899744d06c88468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Rfc4ef13310d24b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R822e84e6b7cf4a27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rbee77dbe4c7d4723"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R5f85690d9665476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R4daaf45726794e2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R6afe2279321740f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Rb052c1579dd848d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rccce0e7fe5f44386"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Rbed796f6c7a34ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Re2e534ba97634b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R9e857ad26fc74191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Re1dc9713f1f74161"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R39ea44b2d3754a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R7b45cb3435fd47d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R8f33ac9219e94bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R18fd06a2f5f54a0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R2d84666f629f424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Rd154960bc7494c73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="R7c4abb49f1e24ee7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R63b2009c5509487c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R5046c29838cf4cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R14a8ee372b0445fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R61b4c286f0d14e65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rca8dccedfc6b47c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R12239c58f8004104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R49eaede7d7d04645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Rb001f705c49e4437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R14553b24b76d4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R811d3acb194841d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="Rce208b14e94b4831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R152813ae02224dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rce52d7cf754742c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R20cfcd4158a54dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb4ccc713052b4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R540b9f24d02d40cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rcb178b95a2164083"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R3de5e31164044f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R858ca87e1835447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R0d4de921ce974731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R651975375e484c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R490aff20e8aa456e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R783299526cc64bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R71116ae298c34bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R3ca67558595440c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R2c978254ba0f4b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R09abb08cc8244bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Ra491fb970b734e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R0b8e92946a2049eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R34da357b6e344890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rab3cf2fd81454526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rc87f03b3cbf64bb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rd42782c91d354a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="Rd53696d979fc4bb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R87b2d2b1c5914afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R18d90eaead514ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R995bc5141b8c4503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R81ce74a7a7344da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rb3d3a767a03b487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R39993b8f63014bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R15fbc9e1d9a5407b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R9051549eb5824e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R0960439038004bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Re747810f50d844fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rfc6174ea7edd4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R60d44a89af704a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rcd2c30fb3ac04584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rde1b59a000664582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R5af3faa1abe94c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R81bdff4576be4426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R9278920f2c514faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R41f12cfbd222427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R383388c0f16d4475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="Ra60a4641af924349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rae542ac6cc9843d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R93e4d227b1074e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="Rd1d7688c78714798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R6532fc594fcc4170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R98a7bdd6a6c94000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R31ed06484c784ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Rdc8e807f31e54c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rb9603baae9274404"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R9b3d7dbb6e3647fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rc2c31f286438446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R39ec5f09bae043a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Rddc11a1a5ba14b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R5d323f184b8b46ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Ra4882b061e3a45e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R622e70d707c44a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Re1f73e99dd084150"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rb69ede4989964d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rbf159f1f0dda45cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R093045188c134686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rb726a4e450a64ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R36dbced7b4554b9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="Rfc5ddd21faea4623"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re23275222e1e45e8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38439dbd57b74c0e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2702,7 +2702,7 @@
       </x:c>
       <x:c r="B5" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$222,"MVP")</x:f>
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
@@ -2710,7 +2710,7 @@
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.027777777777777776</x:v>
+        <x:v>0.027522935779816515</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F6)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8872284e5de04766"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bbb6eb3f804405f"/>
 </x:worksheet>
 </file>
 
@@ -10640,19 +10640,46 @@
       </x:c>
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
-      <x:c r="A9" s="32" t="n"/>
-      <x:c r="B9" s="32" t="n"/>
-      <x:c r="C9" s="32" t="n"/>
-      <x:c r="D9" s="32" t="n"/>
-      <x:c r="E9" s="32" t="n"/>
-      <x:c r="F9" s="32" t="n"/>
-      <x:c r="G9" s="32" t="n"/>
-      <x:c r="H9" s="32" t="n"/>
-      <x:c r="I9" s="376" t="n"/>
-      <x:c r="J9" s="32" t="n"/>
-      <x:c r="K9" s="32" t="n"/>
-      <x:c r="L9" s="32" t="n"/>
-      <x:c r="M9" s="32" t="n"/>
+      <x:c r="A9" s="32" t="str">
+        <x:v>R-004</x:v>
+      </x:c>
+      <x:c r="B9" s="32" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C9" s="32" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="str">
+        <x:v>Go control-plane foundation</x:v>
+      </x:c>
+      <x:c r="E9" s="32" t="str">
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+      </x:c>
+      <x:c r="F9" s="32" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G9" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="H9" s="32" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="I9" s="376" t="n">
+        <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="J9" s="32" t="str">
+        <x:v>R-003</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L9" s="32" t="str">
+        <x:v>local Ollama design review completed; implementation pending</x:v>
+      </x:c>
+      <x:c r="M9" s="32" t="str">
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
@@ -21245,7 +21272,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87b80298bf6640dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4f620f4fdce4784"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb4ccc713052b4c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R540b9f24d02d40cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rcb178b95a2164083"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R3de5e31164044f2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R858ca87e1835447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R0d4de921ce974731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R651975375e484c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R490aff20e8aa456e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R783299526cc64bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R71116ae298c34bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R3ca67558595440c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R2c978254ba0f4b5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R09abb08cc8244bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Ra491fb970b734e36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R0b8e92946a2049eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R34da357b6e344890"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rab3cf2fd81454526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rc87f03b3cbf64bb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rd42782c91d354a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="Rd53696d979fc4bb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R87b2d2b1c5914afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R18d90eaead514ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R995bc5141b8c4503"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R81ce74a7a7344da6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rb3d3a767a03b487b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R39993b8f63014bde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R15fbc9e1d9a5407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R9051549eb5824e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R0960439038004bfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Re747810f50d844fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rfc6174ea7edd4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R60d44a89af704a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rcd2c30fb3ac04584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rde1b59a000664582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R5af3faa1abe94c16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R81bdff4576be4426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R9278920f2c514faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R41f12cfbd222427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R383388c0f16d4475"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="Ra60a4641af924349"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Rae542ac6cc9843d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R93e4d227b1074e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="Rd1d7688c78714798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R6532fc594fcc4170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R98a7bdd6a6c94000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R31ed06484c784ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Rdc8e807f31e54c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rb9603baae9274404"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R9b3d7dbb6e3647fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rc2c31f286438446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R39ec5f09bae043a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Rddc11a1a5ba14b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R5d323f184b8b46ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Ra4882b061e3a45e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R622e70d707c44a8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Re1f73e99dd084150"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rb69ede4989964d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rbf159f1f0dda45cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R093045188c134686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rb726a4e450a64ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R36dbced7b4554b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="Rfc5ddd21faea4623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc85171383c054e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R612b52ccde644f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R4250bca6c9f743ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Reb2be2181f7d405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R586d117199014e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Ra661b0fffea84c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R2abef9f7cdc74880"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R2361a2127f904c06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rb5df949e707a4ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R6ab5076f2b7e4577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Re4d84e69d4ae4897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="Rb94c9e7a22b94e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R5582ca5198dc40ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="Ra1d66c352d2c4ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R652032e6c1d04b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="Rbae9157fb8884b81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R6580bfe76e3c49be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rb8b15d49279842ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rde93abb13fd14252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="Rd39641b674f94789"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rb13320e7ff744ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R56f12e6076a3435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="Re8368796553d4247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R517910fcd8a244e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R983a36d0299a41fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Ra86dee9d2a9c4db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R7f08bc7885be46f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Ra71650951cec4ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Rf32cfc2b2eea4d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R7f8458654b194dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R0d22e3d0a2f6473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="Rb2d3774d14cf4931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="Rdf2a80acbbba4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="Rf55d32b2b7c64f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R24aeae4dfd104fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R68c08163658941be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Rf640f49bf9bc4a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R67835ae307b046a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rcec0af4665df49a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="Rac96ddb1c3d94a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R562d1b5a8efa441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R347a383d93314a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R01d6d3b14fc9480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R4c755ee167324704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R7fa5d0f607a84931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R894a58b01f394cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R1bebb3142e394bd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rb5b3c5e13fa547cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Rc87df91e40724d78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R7564129f8b4f4417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R097a31f299684ca0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R05025e72dbb04d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R4f95d019df3a4be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R3b68fb968a7f4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Rbc097d41c0de4697"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R1133ea33851e4337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rb7d7817ab6114cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rf5b1a44ab41e4322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="Rcf6192531f554001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rcc0c47f576bb4816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Rf2bdb7dea1ce47f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R26b3945183de4664"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38439dbd57b74c0e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc6066a337ef949c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2706,11 +2706,11 @@
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$222,"MVP",Phase_Roadmap!$H$4:$H$222,"Done")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.027522935779816515</x:v>
+        <x:v>0.03669724770642202</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F6)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2803,7 +2803,7 @@
       </x:c>
       <x:c r="G8" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$222,F8)</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bbb6eb3f804405f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb869ef5424934a2d"/>
 </x:worksheet>
 </file>
 
@@ -10662,11 +10662,11 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-003</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>local Ollama design review completed; implementation pending</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
@@ -21272,7 +21272,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4f620f4fdce4784"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0812535af8224cf1"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6fe0c7394c2c4173"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R9b457d3552314bfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="R015f6ec2e3c74bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="Rea1af2c3ec59434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R7e40d7acfe784656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rcec0e5433a9a43ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R97993079f57c429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R0f6b282dc07f4a1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rdd8cd7e913504c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="Rc09b4f24f86945bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Rddd1a66f9c794d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R9738735dd5734ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Rd2edf97a36a943f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R768bc226d7374259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rf5bb56bdd83d4e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R2cf1c7874db0410e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Re57128e0544e432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rd21cf4452f7b4753"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="R8ae30d5887754efc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R12e6fdc17b6e4dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rf60ee456d0344472"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R996bd6ff43cc4431"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R733ec763525b480f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R27c2e4e333854918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R7d5528ead5af45ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="Ra4db8b920d9c4be4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R9a407171a56f4ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Ra7a6df0c03304818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Rabb03fe1e98045be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R62ef2f30528b45af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R5800f3eee6c94928"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R89a203449b404e61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R8c7fd9786ca048b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R0fd40b2a82474d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Re7ec11da982b421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Racb0941bda684ca4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R8071c4831e684dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Rcf1bc7ac9c344d01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rb0974ce6637d4b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R22c5f79788a84fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R9fff97bc4e7842f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R78862bc09e724e17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R67c6f399987f49d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="Rf6092c8ff00c4ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="Rd7acda311c13443c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R683a50368b7c447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Re679b01840ad4f10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Re0f5c2f114574f6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R1ee02a1700d34c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R53c08a0f65434ffb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R1f6f19e685254a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R8a17b96582574383"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Rff43df5536974dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R8a565355e6914c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Ra907ed9fc52a4b0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Rbab94cf73e0e487c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Ra7e5ebb528184871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R6be7179bc7f54d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="Rc690be9ebbb7472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R70fec2bf13a6481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="Re6e6b83a921c452b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R48be471dda0a46c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R845be9d295304bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R78f3e3fb4fae496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rac180c866b1e4178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R9e6c2e37dd5f4342"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R7dea24a35661401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rb5aab34033b14156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Rd3789afc68334614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="Rc06b768a4abd4183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rd37ccd6295e54869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R7a939b5a9aab4971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Ra9f689786cac4c66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R27131bf574d44400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R4eab6978bb12416a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R292eaa4bbb084c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R7d1342d4728c4810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R85202e8c1b3545ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rf6f1735b9554478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rcd6e018c51324fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rc514a667ea004f60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R3ea8419881b74f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R7d4bd20a0b354f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R88f40b52c2ec49c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R5135d552a9e24778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Rb73f4e4716584916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rb97a9680e13c4a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R7b87c226d9734229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rdbe50d512a044841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R2cd5303c50144c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R45ffcdbb8103409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Rd4ae7394511648e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R730be16c44794e5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R010a0c65e87a4e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R287fa46d3c274fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R42bbf45020c5475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R11e939439af8409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Raa078d47216f46d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Re4b4d1c3d670450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R9bb01f58ef814582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R01e6340136484ba6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R1ef0bcd213bb40f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Ra769e92b63ea4306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R837b49f6b7d94d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R432535d648ce49f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="Rc9ba1133362748b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R75754a19c29b4b5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R667dc0b877714b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Re524e032e9b24fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Racd97e2a22584194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R8dd7bec5c9e44c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rd954de2f302c440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R07b910a7caf04230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R4859bd9e08b0451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R122039b701d84cb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R8d94b2cc539c44ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R20342883c68f4bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R75dd23d8e20f4133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rd0d8562bfeb74c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rc033f566ebc94e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R865d24e726f14025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R0835cc25f7e94356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R495180a7bd574d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="Rd074d9d6cb06487b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe84f9b5d6194868"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04b45655343f4593"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2706,11 +2706,11 @@
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$223,"MVP",Phase_Roadmap!$H$4:$H$223,"Done")</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.03636363636363636</x:v>
+        <x:v>0.045454545454545456</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F6)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2803,7 +2803,7 @@
       </x:c>
       <x:c r="G8" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F8)</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7561346f29c413a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270cde4f50234b36"/>
 </x:worksheet>
 </file>
 
@@ -10662,11 +10662,11 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-004</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Task contract recorded; two local review attempts returned no capturable text; implementation pending; cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
@@ -17998,7 +17998,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2d0e3b741654a19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fdf58ba6b6400d"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R845be9d295304bde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R78f3e3fb4fae496f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rac180c866b1e4178"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R9e6c2e37dd5f4342"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R7dea24a35661401d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rb5aab34033b14156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Rd3789afc68334614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="Rc06b768a4abd4183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rd37ccd6295e54869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R7a939b5a9aab4971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Ra9f689786cac4c66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R27131bf574d44400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="R4eab6978bb12416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R292eaa4bbb084c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R7d1342d4728c4810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="R85202e8c1b3545ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rf6f1735b9554478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rcd6e018c51324fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rc514a667ea004f60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R3ea8419881b74f35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R7d4bd20a0b354f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="R88f40b52c2ec49c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R5135d552a9e24778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Rb73f4e4716584916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rb97a9680e13c4a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R7b87c226d9734229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rdbe50d512a044841"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R2cd5303c50144c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="R45ffcdbb8103409c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="Rd4ae7394511648e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="R730be16c44794e5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R010a0c65e87a4e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R287fa46d3c274fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R42bbf45020c5475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R11e939439af8409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="Raa078d47216f46d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Re4b4d1c3d670450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R9bb01f58ef814582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R01e6340136484ba6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R1ef0bcd213bb40f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="Ra769e92b63ea4306"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="R837b49f6b7d94d28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R432535d648ce49f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="Rc9ba1133362748b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R75754a19c29b4b5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R667dc0b877714b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Re524e032e9b24fcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Racd97e2a22584194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R8dd7bec5c9e44c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="Rd954de2f302c440e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R07b910a7caf04230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R4859bd9e08b0451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="R122039b701d84cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R8d94b2cc539c44ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R20342883c68f4bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R75dd23d8e20f4133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rd0d8562bfeb74c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="Rc033f566ebc94e1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R865d24e726f14025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R0835cc25f7e94356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R495180a7bd574d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="Rd074d9d6cb06487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8f03f928e9ba40d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Rb92228bb2ea645ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Re535e91e3cc34259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R822174bfda8745fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R2ac6ab7ab81b4289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R1ad22d7cf2f34458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Rfa6fde6cb7a145f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R5df1b92fc1164dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R6aeab484d2e74963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R4aad5bc894b34909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Radec3e9ebc604ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R19d4c8ad021840c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Ra624480c3972480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R4098bcc395dc405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R21c1fc4892994710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="Re1f0f06e306e4d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R7c391ea780614ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rf28ebb8ed52d4334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rd79a85621a8a4dab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R1f38e2b48a9a413e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rb1775eb2cec34d2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Re518c3dc672c48a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R69a3d106ec8e46ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Raa6fab16bf9f4fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rc3a3a2877e5b40c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R4478a8d596dd4182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rb07c64ae7c6a4e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Rbf3491ad6f584b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Ra8a68b8657ea4804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R5d29fd2913c94199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Re516337aabee4920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R3a312b29ccd445e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R5b394eee0f5c449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R4ac34d5fa4f24ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Rb3cb9f5d12b347bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R93cd1352d2dc4490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Re46d1d63834b4f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Red5789bbba1a4ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rc0ddc73b071d44ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R0782e6079c7a478c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R55cd8a9925994ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rce8d44d0bad54f63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R58f1f2aebcdd4e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R11f13a1b1233489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R5d4c79a934d042af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="Rc6e3d3915aa54d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Ra07966c5bdb14e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rcb3a6401d85d4d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R96afb7f00bb64d97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R1218e8c40c8d406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R59bcf14944f54e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R47c937dbff8248cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Raf27715a6ae349b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Reb29ca4326794f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Rfad5282bea2b484c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R75e8c81fa61f4f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R82cf9543823848b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R96e00af2a7cf49ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R7420459d16464482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rc9d477b006074375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R5f6238433f4c46b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R57eae45e4b4c4542"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04b45655343f4593"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d7e437deed84762"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2701,16 +2701,16 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$223,"MVP")</x:f>
-        <x:v>110</x:v>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"MVP")</x:f>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$223,"MVP",Phase_Roadmap!$H$4:$H$223,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"MVP",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.045454545454545456</x:v>
+        <x:v>0.04504504504504504</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$223,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$223,"MID",Phase_Roadmap!$H$4:$H$223,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"MID",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,8 +2746,8 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F6)</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F6)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$223,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$223,"ADVANCED",Phase_Roadmap!$H$4:$H$223,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"ADVANCED",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$223,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$223,"PRODUCTION",Phase_Roadmap!$H$4:$H$223,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"PRODUCTION",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F8)</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$223,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270cde4f50234b36"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dad15da017348e8"/>
 </x:worksheet>
 </file>
 
@@ -10641,7 +10641,7 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10650,10 +10650,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
@@ -10662,40 +10662,40 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Task contract recorded; baseline task verify passed; local_calls=1 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C10" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
@@ -10711,33 +10711,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C11" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
@@ -10753,33 +10753,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
@@ -10795,33 +10795,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
@@ -10837,53 +10837,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G14" s="32"/>
+      <x:c r="G14" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H14" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I14" s="376" t="n">
         <x:f>IF(H14="Done",1,IF(H14="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="32"/>
-      <x:c r="K14" s="32"/>
-      <x:c r="L14" s="32"/>
-      <x:c r="M14" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K14" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L14" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M14" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10892,10 +10902,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
@@ -10915,7 +10925,7 @@
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10924,10 +10934,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
@@ -10947,7 +10957,7 @@
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10956,10 +10966,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
@@ -10979,7 +10989,7 @@
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10988,10 +10998,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
@@ -11011,7 +11021,7 @@
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11020,10 +11030,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
@@ -11043,19 +11053,19 @@
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C20" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
@@ -11075,7 +11085,7 @@
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11084,10 +11094,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11107,19 +11117,19 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C22" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11139,7 +11149,7 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11148,10 +11158,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11171,19 +11181,19 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C24" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11203,19 +11213,19 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C25" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11235,7 +11245,7 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11244,10 +11254,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11267,19 +11277,19 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C27" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11299,7 +11309,7 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11308,10 +11318,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11331,7 +11341,7 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11340,10 +11350,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11363,19 +11373,19 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C30" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11395,7 +11405,7 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11404,10 +11414,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11427,7 +11437,7 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11436,10 +11446,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11459,7 +11469,7 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11468,10 +11478,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11491,7 +11501,7 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11500,10 +11510,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11523,19 +11533,19 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C35" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11555,7 +11565,7 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11564,10 +11574,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11587,19 +11597,19 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C37" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11619,7 +11629,7 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11628,10 +11638,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11651,19 +11661,19 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C39" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11683,19 +11693,19 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C40" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11715,19 +11725,19 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C41" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11747,7 +11757,7 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11756,10 +11766,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11779,7 +11789,7 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11788,10 +11798,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11811,7 +11821,7 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11820,10 +11830,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11843,19 +11853,19 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C45" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11875,7 +11885,7 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11884,10 +11894,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11907,19 +11917,19 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C47" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11939,7 +11949,7 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11948,10 +11958,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -11971,19 +11981,19 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C49" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12003,7 +12013,7 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12012,10 +12022,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12035,7 +12045,7 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12044,10 +12054,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12067,19 +12077,19 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C52" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12099,7 +12109,7 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12108,10 +12118,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12131,7 +12141,7 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12140,10 +12150,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12163,19 +12173,19 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C55" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12195,22 +12205,22 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C56" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G56" s="32"/>
       <x:c r="H56" s="32" t="str">
@@ -12227,7 +12237,7 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
         <x:v>MID</x:v>
@@ -12236,10 +12246,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
         <x:v>P1</x:v>
@@ -12259,19 +12269,19 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C58" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
         <x:v>P1</x:v>
@@ -12291,19 +12301,19 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C59" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
         <x:v>P1</x:v>
@@ -12323,7 +12333,7 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
         <x:v>MID</x:v>
@@ -12332,10 +12342,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
         <x:v>P1</x:v>
@@ -12355,19 +12365,19 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C61" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
         <x:v>P1</x:v>
@@ -12387,19 +12397,19 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C62" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
         <x:v>P1</x:v>
@@ -12419,19 +12429,19 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C63" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12451,7 +12461,7 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
@@ -12460,10 +12470,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12483,19 +12493,19 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C65" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12515,7 +12525,7 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
@@ -12524,10 +12534,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12547,7 +12557,7 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
@@ -12556,10 +12566,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12579,19 +12589,19 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C68" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12611,7 +12621,7 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
@@ -12620,10 +12630,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12643,19 +12653,19 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C70" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12675,19 +12685,19 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C71" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12707,19 +12717,19 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C72" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12739,19 +12749,19 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C73" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12771,7 +12781,7 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
@@ -12780,10 +12790,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12803,7 +12813,7 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
@@ -12812,10 +12822,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12835,19 +12845,19 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C76" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12867,7 +12877,7 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
@@ -12876,10 +12886,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12899,19 +12909,19 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C78" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12931,19 +12941,19 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C79" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -12963,19 +12973,19 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C80" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -12995,22 +13005,22 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C81" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G81" s="32"/>
       <x:c r="H81" s="32" t="str">
@@ -13027,7 +13037,7 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13036,13 +13046,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G82" s="32"/>
       <x:c r="H82" s="32" t="str">
@@ -13059,22 +13069,22 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C83" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G83" s="32"/>
       <x:c r="H83" s="32" t="str">
@@ -13091,7 +13101,7 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13100,10 +13110,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
         <x:v>P2</x:v>
@@ -13123,19 +13133,19 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C85" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
         <x:v>P2</x:v>
@@ -13155,19 +13165,19 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C86" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
         <x:v>P2</x:v>
@@ -13187,19 +13197,19 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C87" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
         <x:v>P2</x:v>
@@ -13219,7 +13229,7 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13228,10 +13238,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
         <x:v>P2</x:v>
@@ -13251,19 +13261,19 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C89" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
         <x:v>P2</x:v>
@@ -13283,7 +13293,7 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13292,10 +13302,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13315,7 +13325,7 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13324,10 +13334,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13347,19 +13357,19 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C92" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13379,7 +13389,7 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13388,10 +13398,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13411,19 +13421,19 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C94" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13443,19 +13453,19 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C95" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13475,7 +13485,7 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13484,10 +13494,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13507,19 +13517,19 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-093</x:v>
+        <x:v>R-092</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C97" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Quality trend analytics</x:v>
+        <x:v>Spot/preemptible optimization</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
+        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13539,22 +13549,22 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-094</x:v>
+        <x:v>R-093</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C98" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>SLO/SLA framework</x:v>
+        <x:v>Quality trend analytics</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
+        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G98" s="32"/>
       <x:c r="H98" s="32" t="str">
@@ -13571,7 +13581,7 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-095</x:v>
+        <x:v>R-094</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13580,10 +13590,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>HA control plane</x:v>
+        <x:v>SLO/SLA framework</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
+        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
         <x:v>P0</x:v>
@@ -13603,7 +13613,7 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-096</x:v>
+        <x:v>R-095</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13612,10 +13622,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>Backup + restore drills</x:v>
+        <x:v>HA control plane</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Automated backups plus regularly tested restoration.</x:v>
+        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
         <x:v>P0</x:v>
@@ -13635,7 +13645,7 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-097</x:v>
+        <x:v>R-096</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13644,10 +13654,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>Disaster recovery</x:v>
+        <x:v>Backup + restore drills</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Document and exercise regional recovery procedures.</x:v>
+        <x:v>Automated backups plus regularly tested restoration.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
         <x:v>P0</x:v>
@@ -13667,19 +13677,19 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-098</x:v>
+        <x:v>R-097</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C102" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>Independent penetration test</x:v>
+        <x:v>Disaster recovery</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>External security assessment before broad enterprise launch.</x:v>
+        <x:v>Document and exercise regional recovery procedures.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
         <x:v>P0</x:v>
@@ -13699,7 +13709,7 @@
     </x:row>
     <x:row r="103" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A103" s="32" t="str">
-        <x:v>R-099</x:v>
+        <x:v>R-098</x:v>
       </x:c>
       <x:c r="B103" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13708,10 +13718,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D103" s="32" t="str">
-        <x:v>SOC 2 readiness controls</x:v>
+        <x:v>Independent penetration test</x:v>
       </x:c>
       <x:c r="E103" s="32" t="str">
-        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
+        <x:v>External security assessment before broad enterprise launch.</x:v>
       </x:c>
       <x:c r="F103" s="32" t="str">
         <x:v>P0</x:v>
@@ -13731,7 +13741,7 @@
     </x:row>
     <x:row r="104" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A104" s="32" t="str">
-        <x:v>R-100</x:v>
+        <x:v>R-099</x:v>
       </x:c>
       <x:c r="B104" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13740,10 +13750,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D104" s="32" t="str">
-        <x:v>Tenant isolation validation</x:v>
+        <x:v>SOC 2 readiness controls</x:v>
       </x:c>
       <x:c r="E104" s="32" t="str">
-        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
+        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
       </x:c>
       <x:c r="F104" s="32" t="str">
         <x:v>P0</x:v>
@@ -13763,7 +13773,7 @@
     </x:row>
     <x:row r="105" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A105" s="32" t="str">
-        <x:v>R-101</x:v>
+        <x:v>R-100</x:v>
       </x:c>
       <x:c r="B105" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13772,10 +13782,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D105" s="32" t="str">
-        <x:v>Signing-key hardening</x:v>
+        <x:v>Tenant isolation validation</x:v>
       </x:c>
       <x:c r="E105" s="32" t="str">
-        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
+        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
       </x:c>
       <x:c r="F105" s="32" t="str">
         <x:v>P0</x:v>
@@ -13795,19 +13805,19 @@
     </x:row>
     <x:row r="106" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A106" s="32" t="str">
-        <x:v>R-102</x:v>
+        <x:v>R-101</x:v>
       </x:c>
       <x:c r="B106" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C106" s="32" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D106" s="32" t="str">
-        <x:v>24x7 incident process</x:v>
+        <x:v>Signing-key hardening</x:v>
       </x:c>
       <x:c r="E106" s="32" t="str">
-        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
+        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
       </x:c>
       <x:c r="F106" s="32" t="str">
         <x:v>P0</x:v>
@@ -13827,7 +13837,7 @@
     </x:row>
     <x:row r="107" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A107" s="32" t="str">
-        <x:v>R-103</x:v>
+        <x:v>R-102</x:v>
       </x:c>
       <x:c r="B107" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13836,10 +13846,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>Capacity/load tests</x:v>
+        <x:v>24x7 incident process</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
-        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
+        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
       </x:c>
       <x:c r="F107" s="32" t="str">
         <x:v>P0</x:v>
@@ -13859,7 +13869,7 @@
     </x:row>
     <x:row r="108" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A108" s="32" t="str">
-        <x:v>R-104</x:v>
+        <x:v>R-103</x:v>
       </x:c>
       <x:c r="B108" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13868,10 +13878,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>Cost guardrails</x:v>
+        <x:v>Capacity/load tests</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
-        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
+        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
       </x:c>
       <x:c r="F108" s="32" t="str">
         <x:v>P0</x:v>
@@ -13891,19 +13901,19 @@
     </x:row>
     <x:row r="109" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A109" s="32" t="str">
-        <x:v>R-105</x:v>
+        <x:v>R-104</x:v>
       </x:c>
       <x:c r="B109" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C109" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>Release qualification suite</x:v>
+        <x:v>Cost guardrails</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
-        <x:v>Full regression across supported stack versions before platform releases.</x:v>
+        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
       </x:c>
       <x:c r="F109" s="32" t="str">
         <x:v>P0</x:v>
@@ -13923,7 +13933,7 @@
     </x:row>
     <x:row r="110" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A110" s="32" t="str">
-        <x:v>R-106</x:v>
+        <x:v>R-105</x:v>
       </x:c>
       <x:c r="B110" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13932,10 +13942,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>Canary platform releases</x:v>
+        <x:v>Release qualification suite</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
-        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
+        <x:v>Full regression across supported stack versions before platform releases.</x:v>
       </x:c>
       <x:c r="F110" s="32" t="str">
         <x:v>P0</x:v>
@@ -13955,19 +13965,19 @@
     </x:row>
     <x:row r="111" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A111" s="32" t="str">
-        <x:v>R-107</x:v>
+        <x:v>R-106</x:v>
       </x:c>
       <x:c r="B111" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C111" s="32" t="str">
-        <x:v>Support</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>Support tooling</x:v>
+        <x:v>Canary platform releases</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
-        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
+        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
       </x:c>
       <x:c r="F111" s="32" t="str">
         <x:v>P0</x:v>
@@ -13987,19 +13997,19 @@
     </x:row>
     <x:row r="112" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A112" s="32" t="str">
-        <x:v>R-108</x:v>
+        <x:v>R-107</x:v>
       </x:c>
       <x:c r="B112" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C112" s="32" t="str">
-        <x:v>Legal/Privacy</x:v>
+        <x:v>Support</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Privacy + retention controls</x:v>
+        <x:v>Support tooling</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
         <x:v>P0</x:v>
@@ -14019,19 +14029,19 @@
     </x:row>
     <x:row r="113" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A113" s="32" t="str">
-        <x:v>R-109</x:v>
+        <x:v>R-108</x:v>
       </x:c>
       <x:c r="B113" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C113" s="32" t="str">
-        <x:v>Business</x:v>
+        <x:v>Legal/Privacy</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Plan entitlements</x:v>
+        <x:v>Privacy + retention controls</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
+        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
         <x:v>P0</x:v>
@@ -14051,7 +14061,7 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="43" t="str">
-        <x:v>R-110</x:v>
+        <x:v>R-109</x:v>
       </x:c>
       <x:c r="B114" s="43" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14060,10 +14070,10 @@
         <x:v>Business</x:v>
       </x:c>
       <x:c r="D114" s="43" t="str">
-        <x:v>Unit economics dashboard</x:v>
+        <x:v>Plan entitlements</x:v>
       </x:c>
       <x:c r="E114" s="43" t="str">
-        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
+        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
       </x:c>
       <x:c r="F114" s="43" t="str">
         <x:v>P0</x:v>
@@ -14083,19 +14093,19 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="42" t="str">
-        <x:v>R-111</x:v>
+        <x:v>R-110</x:v>
       </x:c>
       <x:c r="B115" s="42" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C115" s="42" t="str">
-        <x:v>Framework Strategy</x:v>
+        <x:v>Business</x:v>
       </x:c>
       <x:c r="D115" s="42" t="str">
-        <x:v>Cross-platform Mobile Agent</x:v>
+        <x:v>Unit economics dashboard</x:v>
       </x:c>
       <x:c r="E115" s="42" t="str">
-        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
+        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
       </x:c>
       <x:c r="F115" s="42" t="str">
         <x:v>P0</x:v>
@@ -14108,16 +14118,14 @@
         <x:f>IF(H115="Done",1,IF(H115="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J115" s="42" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
+      <x:c r="J115" s="42"/>
       <x:c r="K115" s="42"/>
       <x:c r="L115" s="42"/>
       <x:c r="M115" s="42"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="43" t="str">
-        <x:v>R-112</x:v>
+        <x:v>R-111</x:v>
       </x:c>
       <x:c r="B116" s="43" t="str">
         <x:v>MVP</x:v>
@@ -14126,10 +14134,10 @@
         <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D116" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
+        <x:v>Cross-platform Mobile Agent</x:v>
       </x:c>
       <x:c r="E116" s="43" t="str">
-        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
+        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
       </x:c>
       <x:c r="F116" s="43" t="str">
         <x:v>P0</x:v>
@@ -14143,7 +14151,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J116" s="43" t="str">
-        <x:v>Requirement specification step</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K116" s="43"/>
       <x:c r="L116" s="43"/>
@@ -14151,7 +14159,7 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="42" t="str">
-        <x:v>R-113</x:v>
+        <x:v>R-112</x:v>
       </x:c>
       <x:c r="B117" s="42" t="str">
         <x:v>MVP</x:v>
@@ -14160,10 +14168,10 @@
         <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D117" s="42" t="str">
-        <x:v>Auto / Recommended project mode</x:v>
+        <x:v>Framework recommendation engine</x:v>
       </x:c>
       <x:c r="E117" s="42" t="str">
-        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
+        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
       </x:c>
       <x:c r="F117" s="42" t="str">
         <x:v>P0</x:v>
@@ -14177,7 +14185,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J117" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
+        <x:v>Requirement specification step</x:v>
       </x:c>
       <x:c r="K117" s="42"/>
       <x:c r="L117" s="42"/>
@@ -14185,7 +14193,7 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="43" t="str">
-        <x:v>R-114</x:v>
+        <x:v>R-113</x:v>
       </x:c>
       <x:c r="B118" s="43" t="str">
         <x:v>MVP</x:v>
@@ -14194,13 +14202,13 @@
         <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D118" s="43" t="str">
-        <x:v>Manual framework override</x:v>
+        <x:v>Auto / Recommended project mode</x:v>
       </x:c>
       <x:c r="E118" s="43" t="str">
-        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
+        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
       </x:c>
       <x:c r="F118" s="43" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G118" s="43"/>
       <x:c r="H118" s="43" t="str">
@@ -14219,22 +14227,22 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="42" t="str">
-        <x:v>R-115</x:v>
+        <x:v>R-114</x:v>
       </x:c>
       <x:c r="B119" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C119" s="42" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D119" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
+        <x:v>Manual framework override</x:v>
       </x:c>
       <x:c r="E119" s="42" t="str">
-        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
+        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
       </x:c>
       <x:c r="F119" s="42" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G119" s="42"/>
       <x:c r="H119" s="42" t="str">
@@ -14245,7 +14253,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J119" s="42" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>Framework recommendation engine</x:v>
       </x:c>
       <x:c r="K119" s="42"/>
       <x:c r="L119" s="42"/>
@@ -14253,7 +14261,7 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="43" t="str">
-        <x:v>R-116</x:v>
+        <x:v>R-115</x:v>
       </x:c>
       <x:c r="B120" s="43" t="str">
         <x:v>MVP</x:v>
@@ -14262,10 +14270,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D120" s="43" t="str">
-        <x:v>Shared-code policy</x:v>
+        <x:v>Framework adapter contract</x:v>
       </x:c>
       <x:c r="E120" s="43" t="str">
-        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
+        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
       </x:c>
       <x:c r="F120" s="43" t="str">
         <x:v>P0</x:v>
@@ -14279,7 +14287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J120" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K120" s="43"/>
       <x:c r="L120" s="43"/>
@@ -14287,19 +14295,19 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="42" t="str">
-        <x:v>R-117</x:v>
+        <x:v>R-116</x:v>
       </x:c>
       <x:c r="B121" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C121" s="42" t="str">
-        <x:v>Web/Admin</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D121" s="42" t="str">
-        <x:v>Next.js web + admin default</x:v>
+        <x:v>Shared-code policy</x:v>
       </x:c>
       <x:c r="E121" s="42" t="str">
-        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
+        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
       </x:c>
       <x:c r="F121" s="42" t="str">
         <x:v>P0</x:v>
@@ -14313,7 +14321,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J121" s="42" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Framework adapter contract</x:v>
       </x:c>
       <x:c r="K121" s="42"/>
       <x:c r="L121" s="42"/>
@@ -14321,22 +14329,22 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="43" t="str">
-        <x:v>R-118</x:v>
+        <x:v>R-117</x:v>
       </x:c>
       <x:c r="B122" s="43" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C122" s="43" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
       <x:c r="D122" s="43" t="str">
-        <x:v>Flutter Web optional profile</x:v>
+        <x:v>Next.js web + admin default</x:v>
       </x:c>
       <x:c r="E122" s="43" t="str">
-        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
+        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
       </x:c>
       <x:c r="F122" s="43" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G122" s="43"/>
       <x:c r="H122" s="43" t="str">
@@ -14347,7 +14355,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J122" s="43" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="K122" s="43"/>
       <x:c r="L122" s="43"/>
@@ -14355,7 +14363,7 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="42" t="str">
-        <x:v>R-119</x:v>
+        <x:v>R-118</x:v>
       </x:c>
       <x:c r="B123" s="42" t="str">
         <x:v>MID</x:v>
@@ -14364,10 +14372,10 @@
         <x:v>Web/Admin</x:v>
       </x:c>
       <x:c r="D123" s="42" t="str">
-        <x:v>React Native Web optional profile</x:v>
+        <x:v>Flutter Web optional profile</x:v>
       </x:c>
       <x:c r="E123" s="42" t="str">
-        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
+        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
       </x:c>
       <x:c r="F123" s="42" t="str">
         <x:v>P1</x:v>
@@ -14381,7 +14389,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J123" s="42" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="K123" s="42"/>
       <x:c r="L123" s="42"/>
@@ -14389,22 +14397,22 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="43" t="str">
-        <x:v>R-120</x:v>
+        <x:v>R-119</x:v>
       </x:c>
       <x:c r="B124" s="43" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C124" s="43" t="str">
-        <x:v>Framework Strategy</x:v>
+        <x:v>Web/Admin</x:v>
       </x:c>
       <x:c r="D124" s="43" t="str">
-        <x:v>Native recommendation profile</x:v>
+        <x:v>React Native Web optional profile</x:v>
       </x:c>
       <x:c r="E124" s="43" t="str">
-        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
+        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
       </x:c>
       <x:c r="F124" s="43" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G124" s="43"/>
       <x:c r="H124" s="43" t="str">
@@ -14415,7 +14423,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J124" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="K124" s="43"/>
       <x:c r="L124" s="43"/>
@@ -14423,19 +14431,19 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="42" t="str">
-        <x:v>R-121</x:v>
+        <x:v>R-120</x:v>
       </x:c>
       <x:c r="B125" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C125" s="42" t="str">
-        <x:v>Git/Repository</x:v>
+        <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D125" s="42" t="str">
-        <x:v>Platform modular monorepo</x:v>
+        <x:v>Native recommendation profile</x:v>
       </x:c>
       <x:c r="E125" s="42" t="str">
-        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
+        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
       </x:c>
       <x:c r="F125" s="42" t="str">
         <x:v>P0</x:v>
@@ -14449,7 +14457,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J125" s="42" t="str">
-        <x:v>Project + workspace model</x:v>
+        <x:v>Framework recommendation engine</x:v>
       </x:c>
       <x:c r="K125" s="42"/>
       <x:c r="L125" s="42"/>
@@ -14457,7 +14465,7 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="43" t="str">
-        <x:v>R-122</x:v>
+        <x:v>R-121</x:v>
       </x:c>
       <x:c r="B126" s="43" t="str">
         <x:v>MVP</x:v>
@@ -14466,10 +14474,10 @@
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D126" s="43" t="str">
-        <x:v>One Git repo per customer project</x:v>
+        <x:v>Platform modular monorepo</x:v>
       </x:c>
       <x:c r="E126" s="43" t="str">
-        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
+        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
       </x:c>
       <x:c r="F126" s="43" t="str">
         <x:v>P0</x:v>
@@ -14491,7 +14499,7 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="42" t="str">
-        <x:v>R-123</x:v>
+        <x:v>R-122</x:v>
       </x:c>
       <x:c r="B127" s="42" t="str">
         <x:v>MVP</x:v>
@@ -14500,10 +14508,10 @@
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D127" s="42" t="str">
-        <x:v>Customer project monorepo default</x:v>
+        <x:v>One Git repo per customer project</x:v>
       </x:c>
       <x:c r="E127" s="42" t="str">
-        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
+        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
       </x:c>
       <x:c r="F127" s="42" t="str">
         <x:v>P0</x:v>
@@ -14517,7 +14525,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J127" s="42" t="str">
-        <x:v>One Git repo per customer project</x:v>
+        <x:v>Project + workspace model</x:v>
       </x:c>
       <x:c r="K127" s="42"/>
       <x:c r="L127" s="42"/>
@@ -14525,7 +14533,7 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="43" t="str">
-        <x:v>R-124</x:v>
+        <x:v>R-123</x:v>
       </x:c>
       <x:c r="B128" s="43" t="str">
         <x:v>MVP</x:v>
@@ -14534,13 +14542,13 @@
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D128" s="43" t="str">
-        <x:v>Repository naming convention</x:v>
+        <x:v>Customer project monorepo default</x:v>
       </x:c>
       <x:c r="E128" s="43" t="str">
-        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
+        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
       </x:c>
       <x:c r="F128" s="43" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G128" s="43"/>
       <x:c r="H128" s="43" t="str">
@@ -14559,7 +14567,7 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="42" t="str">
-        <x:v>R-125</x:v>
+        <x:v>R-124</x:v>
       </x:c>
       <x:c r="B129" s="42" t="str">
         <x:v>MVP</x:v>
@@ -14568,13 +14576,13 @@
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D129" s="42" t="str">
-        <x:v>Branch + PR naming convention</x:v>
+        <x:v>Repository naming convention</x:v>
       </x:c>
       <x:c r="E129" s="42" t="str">
-        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
+        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
       </x:c>
       <x:c r="F129" s="42" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G129" s="42"/>
       <x:c r="H129" s="42" t="str">
@@ -14585,7 +14593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J129" s="42" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>One Git repo per customer project</x:v>
       </x:c>
       <x:c r="K129" s="42"/>
       <x:c r="L129" s="42"/>
@@ -14593,19 +14601,19 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="43" t="str">
-        <x:v>R-126</x:v>
+        <x:v>R-125</x:v>
       </x:c>
       <x:c r="B130" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C130" s="43" t="str">
-        <x:v>Product Foundation</x:v>
+        <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D130" s="43" t="str">
-        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
+        <x:v>Branch + PR naming convention</x:v>
       </x:c>
       <x:c r="E130" s="43" t="str">
-        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
+        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
       </x:c>
       <x:c r="F130" s="43" t="str">
         <x:v>P0</x:v>
@@ -14619,7 +14627,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J130" s="43" t="str">
-        <x:v>Project + workspace model</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="K130" s="43"/>
       <x:c r="L130" s="43"/>
@@ -14627,19 +14635,19 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="42" t="str">
-        <x:v>R-127</x:v>
+        <x:v>R-126</x:v>
       </x:c>
       <x:c r="B131" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C131" s="42" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Product Foundation</x:v>
       </x:c>
       <x:c r="D131" s="42" t="str">
-        <x:v>Shared contracts package</x:v>
+        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
       </x:c>
       <x:c r="E131" s="42" t="str">
-        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
+        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
       </x:c>
       <x:c r="F131" s="42" t="str">
         <x:v>P0</x:v>
@@ -14653,7 +14661,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J131" s="42" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>Project + workspace model</x:v>
       </x:c>
       <x:c r="K131" s="42"/>
       <x:c r="L131" s="42"/>
@@ -14661,22 +14669,22 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="43" t="str">
-        <x:v>R-128</x:v>
+        <x:v>R-127</x:v>
       </x:c>
       <x:c r="B132" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C132" s="43" t="str">
-        <x:v>Git/Repository</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D132" s="43" t="str">
-        <x:v>Cross-language monorepo orchestration</x:v>
+        <x:v>Shared contracts package</x:v>
       </x:c>
       <x:c r="E132" s="43" t="str">
-        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
+        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
       </x:c>
       <x:c r="F132" s="43" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G132" s="43"/>
       <x:c r="H132" s="43" t="str">
@@ -14687,7 +14695,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J132" s="43" t="str">
-        <x:v>Platform modular monorepo</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K132" s="43"/>
       <x:c r="L132" s="43"/>
@@ -14695,19 +14703,19 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="42" t="str">
-        <x:v>R-129</x:v>
+        <x:v>R-128</x:v>
       </x:c>
       <x:c r="B133" s="42" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C133" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D133" s="42" t="str">
-        <x:v>Repository split decision policy</x:v>
+        <x:v>Cross-language monorepo orchestration</x:v>
       </x:c>
       <x:c r="E133" s="42" t="str">
-        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
+        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
       </x:c>
       <x:c r="F133" s="42" t="str">
         <x:v>P1</x:v>
@@ -14721,7 +14729,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J133" s="42" t="str">
-        <x:v>Customer project monorepo default</x:v>
+        <x:v>Platform modular monorepo</x:v>
       </x:c>
       <x:c r="K133" s="42"/>
       <x:c r="L133" s="42"/>
@@ -14729,22 +14737,22 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="43" t="str">
-        <x:v>R-130</x:v>
+        <x:v>R-129</x:v>
       </x:c>
       <x:c r="B134" s="43" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C134" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D134" s="43" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
+        <x:v>Repository split decision policy</x:v>
       </x:c>
       <x:c r="E134" s="43" t="str">
-        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
+        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
       </x:c>
       <x:c r="F134" s="43" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G134" s="43"/>
       <x:c r="H134" s="43" t="str">
@@ -14755,7 +14763,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J134" s="43" t="str">
-        <x:v>Repository split decision policy</x:v>
+        <x:v>Customer project monorepo default</x:v>
       </x:c>
       <x:c r="K134" s="43"/>
       <x:c r="L134" s="43"/>
@@ -14763,22 +14771,22 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="42" t="str">
-        <x:v>R-131</x:v>
+        <x:v>R-130</x:v>
       </x:c>
       <x:c r="B135" s="42" t="str">
-        <x:v>MID</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C135" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D135" s="42" t="str">
-        <x:v>CODEOWNERS + protected paths</x:v>
+        <x:v>Enterprise multi-repo support</x:v>
       </x:c>
       <x:c r="E135" s="42" t="str">
-        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
+        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
       </x:c>
       <x:c r="F135" s="42" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G135" s="42"/>
       <x:c r="H135" s="42" t="str">
@@ -14789,7 +14797,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J135" s="42" t="str">
-        <x:v>Branch + PR naming convention</x:v>
+        <x:v>Repository split decision policy</x:v>
       </x:c>
       <x:c r="K135" s="42"/>
       <x:c r="L135" s="42"/>
@@ -14797,22 +14805,22 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="43" t="str">
-        <x:v>R-132</x:v>
+        <x:v>R-131</x:v>
       </x:c>
       <x:c r="B136" s="43" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C136" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D136" s="43" t="str">
-        <x:v>Framework-specific repo templates</x:v>
+        <x:v>CODEOWNERS + protected paths</x:v>
       </x:c>
       <x:c r="E136" s="43" t="str">
-        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
+        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
       </x:c>
       <x:c r="F136" s="43" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G136" s="43"/>
       <x:c r="H136" s="43" t="str">
@@ -14823,7 +14831,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J136" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
+        <x:v>Branch + PR naming convention</x:v>
       </x:c>
       <x:c r="K136" s="43"/>
       <x:c r="L136" s="43"/>
@@ -14831,19 +14839,19 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="42" t="str">
-        <x:v>R-133</x:v>
+        <x:v>R-132</x:v>
       </x:c>
       <x:c r="B137" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C137" s="42" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D137" s="42" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
+        <x:v>Framework-specific repo templates</x:v>
       </x:c>
       <x:c r="E137" s="42" t="str">
-        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
+        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
       </x:c>
       <x:c r="F137" s="42" t="str">
         <x:v>P0</x:v>
@@ -14857,7 +14865,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J137" s="42" t="str">
-        <x:v>Customer project monorepo default</x:v>
+        <x:v>Framework adapter contract</x:v>
       </x:c>
       <x:c r="K137" s="42"/>
       <x:c r="L137" s="42"/>
@@ -14865,22 +14873,22 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="66" t="str">
-        <x:v>R-134</x:v>
+        <x:v>R-133</x:v>
       </x:c>
       <x:c r="B138" s="66" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C138" s="66" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D138" s="66" t="str">
-        <x:v>Repository/build health metrics</x:v>
+        <x:v>Atomic cross-platform change set</x:v>
       </x:c>
       <x:c r="E138" s="66" t="str">
-        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
+        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
       </x:c>
       <x:c r="F138" s="66" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G138" s="66"/>
       <x:c r="H138" s="66" t="str">
@@ -14891,7 +14899,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J138" s="66" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Customer project monorepo default</x:v>
       </x:c>
       <x:c r="K138" s="66"/>
       <x:c r="L138" s="66"/>
@@ -14899,22 +14907,22 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="65" t="str">
-        <x:v>R-135</x:v>
+        <x:v>R-134</x:v>
       </x:c>
       <x:c r="B139" s="65" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C139" s="65" t="str">
-        <x:v>Framework Strategy</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D139" s="65" t="str">
-        <x:v>Stack selection wizard</x:v>
+        <x:v>Repository/build health metrics</x:v>
       </x:c>
       <x:c r="E139" s="65" t="str">
-        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
+        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
       </x:c>
       <x:c r="F139" s="65" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G139" s="65"/>
       <x:c r="H139" s="65" t="str">
@@ -14925,17 +14933,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J139" s="65" t="str">
-        <x:v>Framework recommendation engine</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="K139" s="65"/>
       <x:c r="L139" s="65"/>
-      <x:c r="M139" s="65" t="str">
-        <x:v>V3</x:v>
-      </x:c>
+      <x:c r="M139" s="65"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="66" t="str">
-        <x:v>R-136</x:v>
+        <x:v>R-135</x:v>
       </x:c>
       <x:c r="B140" s="66" t="str">
         <x:v>MVP</x:v>
@@ -14944,10 +14950,10 @@
         <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D140" s="66" t="str">
-        <x:v>Recommendation score model</x:v>
+        <x:v>Stack selection wizard</x:v>
       </x:c>
       <x:c r="E140" s="66" t="str">
-        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
+        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
       </x:c>
       <x:c r="F140" s="66" t="str">
         <x:v>P0</x:v>
@@ -14961,29 +14967,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J140" s="66" t="str">
-        <x:v>Stack selection wizard</x:v>
+        <x:v>Framework recommendation engine</x:v>
       </x:c>
       <x:c r="K140" s="66"/>
       <x:c r="L140" s="66"/>
       <x:c r="M140" s="66" t="str">
-        <x:v>Do not choose by industry label alone.</x:v>
+        <x:v>V3</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="65" t="str">
-        <x:v>R-137</x:v>
+        <x:v>R-136</x:v>
       </x:c>
       <x:c r="B141" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C141" s="65" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D141" s="65" t="str">
-        <x:v>Code sharing policy</x:v>
+        <x:v>Recommendation score model</x:v>
       </x:c>
       <x:c r="E141" s="65" t="str">
-        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
+        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
       </x:c>
       <x:c r="F141" s="65" t="str">
         <x:v>P0</x:v>
@@ -14997,17 +15003,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J141" s="65" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>Stack selection wizard</x:v>
       </x:c>
       <x:c r="K141" s="65"/>
       <x:c r="L141" s="65"/>
       <x:c r="M141" s="65" t="str">
-        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
+        <x:v>Do not choose by industry label alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="66" t="str">
-        <x:v>R-138</x:v>
+        <x:v>R-137</x:v>
       </x:c>
       <x:c r="B142" s="66" t="str">
         <x:v>MVP</x:v>
@@ -15016,10 +15022,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D142" s="66" t="str">
-        <x:v>Canonical generated project root</x:v>
+        <x:v>Code sharing policy</x:v>
       </x:c>
       <x:c r="E142" s="66" t="str">
-        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
+        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
       </x:c>
       <x:c r="F142" s="66" t="str">
         <x:v>P0</x:v>
@@ -15033,32 +15039,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J142" s="66" t="str">
-        <x:v>Customer project monorepo default</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K142" s="66"/>
       <x:c r="L142" s="66"/>
       <x:c r="M142" s="66" t="str">
-        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
+        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="65" t="str">
-        <x:v>R-139</x:v>
+        <x:v>R-138</x:v>
       </x:c>
       <x:c r="B143" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C143" s="65" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D143" s="65" t="str">
-        <x:v>Root task commands</x:v>
+        <x:v>Canonical generated project root</x:v>
       </x:c>
       <x:c r="E143" s="65" t="str">
-        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
+        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
       </x:c>
       <x:c r="F143" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G143" s="65"/>
       <x:c r="H143" s="65" t="str">
@@ -15069,32 +15075,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J143" s="65" t="str">
-        <x:v>Canonical generated project root</x:v>
+        <x:v>Customer project monorepo default</x:v>
       </x:c>
       <x:c r="K143" s="65"/>
       <x:c r="L143" s="65"/>
       <x:c r="M143" s="65" t="str">
-        <x:v>Framework-independent agent commands.</x:v>
+        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="66" t="str">
-        <x:v>R-140</x:v>
+        <x:v>R-139</x:v>
       </x:c>
       <x:c r="B144" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C144" s="66" t="str">
-        <x:v>Templates</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D144" s="66" t="str">
-        <x:v>Flutter lean template</x:v>
+        <x:v>Root task commands</x:v>
       </x:c>
       <x:c r="E144" s="66" t="str">
-        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
+        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
       </x:c>
       <x:c r="F144" s="66" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G144" s="66"/>
       <x:c r="H144" s="66" t="str">
@@ -15105,32 +15111,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J144" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
+        <x:v>Canonical generated project root</x:v>
       </x:c>
       <x:c r="K144" s="66"/>
       <x:c r="L144" s="66"/>
       <x:c r="M144" s="66" t="str">
-        <x:v>Stable target.</x:v>
+        <x:v>Framework-independent agent commands.</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="65" t="str">
-        <x:v>R-141</x:v>
+        <x:v>R-140</x:v>
       </x:c>
       <x:c r="B145" s="65" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C145" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D145" s="65" t="str">
-        <x:v>Flutter scaled template</x:v>
+        <x:v>Flutter lean template</x:v>
       </x:c>
       <x:c r="E145" s="65" t="str">
-        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
+        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
       </x:c>
       <x:c r="F145" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G145" s="65"/>
       <x:c r="H145" s="65" t="str">
@@ -15141,32 +15147,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J145" s="65" t="str">
-        <x:v>Flutter lean template</x:v>
+        <x:v>Framework-specific repo templates</x:v>
       </x:c>
       <x:c r="K145" s="65"/>
       <x:c r="L145" s="65"/>
       <x:c r="M145" s="65" t="str">
-        <x:v>Use only when complexity warrants.</x:v>
+        <x:v>Stable target.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="66" t="str">
-        <x:v>R-142</x:v>
+        <x:v>R-141</x:v>
       </x:c>
       <x:c r="B146" s="66" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C146" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D146" s="66" t="str">
-        <x:v>React Native TypeScript template</x:v>
+        <x:v>Flutter scaled template</x:v>
       </x:c>
       <x:c r="E146" s="66" t="str">
-        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
+        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
       </x:c>
       <x:c r="F146" s="66" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G146" s="66"/>
       <x:c r="H146" s="66" t="str">
@@ -15177,17 +15183,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J146" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
+        <x:v>Flutter lean template</x:v>
       </x:c>
       <x:c r="K146" s="66"/>
       <x:c r="L146" s="66"/>
       <x:c r="M146" s="66" t="str">
-        <x:v>Expo profile when capabilities fit.</x:v>
+        <x:v>Use only when complexity warrants.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="65" t="str">
-        <x:v>R-143</x:v>
+        <x:v>R-142</x:v>
       </x:c>
       <x:c r="B147" s="65" t="str">
         <x:v>MVP</x:v>
@@ -15196,13 +15202,13 @@
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D147" s="65" t="str">
-        <x:v>React Native shared TS packages</x:v>
+        <x:v>React Native TypeScript template</x:v>
       </x:c>
       <x:c r="E147" s="65" t="str">
-        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
+        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
       </x:c>
       <x:c r="F147" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G147" s="65"/>
       <x:c r="H147" s="65" t="str">
@@ -15213,17 +15219,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J147" s="65" t="str">
-        <x:v>Shared contracts package</x:v>
+        <x:v>Framework-specific repo templates</x:v>
       </x:c>
       <x:c r="K147" s="65"/>
       <x:c r="L147" s="65"/>
       <x:c r="M147" s="65" t="str">
-        <x:v>Do not share UI blindly.</x:v>
+        <x:v>Expo profile when capabilities fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="66" t="str">
-        <x:v>R-144</x:v>
+        <x:v>R-143</x:v>
       </x:c>
       <x:c r="B148" s="66" t="str">
         <x:v>MVP</x:v>
@@ -15232,13 +15238,13 @@
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D148" s="66" t="str">
-        <x:v>Native Android lean template</x:v>
+        <x:v>React Native shared TS packages</x:v>
       </x:c>
       <x:c r="E148" s="66" t="str">
-        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
+        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
       </x:c>
       <x:c r="F148" s="66" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G148" s="66"/>
       <x:c r="H148" s="66" t="str">
@@ -15249,32 +15255,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J148" s="66" t="str">
-        <x:v>Native Android Agent</x:v>
+        <x:v>Shared contracts package</x:v>
       </x:c>
       <x:c r="K148" s="66"/>
       <x:c r="L148" s="66"/>
       <x:c r="M148" s="66" t="str">
-        <x:v>Native selectable beta.</x:v>
+        <x:v>Do not share UI blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="65" t="str">
-        <x:v>R-145</x:v>
+        <x:v>R-144</x:v>
       </x:c>
       <x:c r="B149" s="65" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C149" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D149" s="65" t="str">
-        <x:v>Native Android scaled modules</x:v>
+        <x:v>Native Android lean template</x:v>
       </x:c>
       <x:c r="E149" s="65" t="str">
-        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
+        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
       </x:c>
       <x:c r="F149" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G149" s="65"/>
       <x:c r="H149" s="65" t="str">
@@ -15285,32 +15291,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J149" s="65" t="str">
-        <x:v>Native Android lean template</x:v>
+        <x:v>Native Android Agent</x:v>
       </x:c>
       <x:c r="K149" s="65"/>
       <x:c r="L149" s="65"/>
       <x:c r="M149" s="65" t="str">
-        <x:v>Experienced team structure.</x:v>
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="66" t="str">
-        <x:v>R-146</x:v>
+        <x:v>R-145</x:v>
       </x:c>
       <x:c r="B150" s="66" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C150" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D150" s="66" t="str">
-        <x:v>Native iOS lean template</x:v>
+        <x:v>Native Android scaled modules</x:v>
       </x:c>
       <x:c r="E150" s="66" t="str">
-        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
+        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
       </x:c>
       <x:c r="F150" s="66" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G150" s="66"/>
       <x:c r="H150" s="66" t="str">
@@ -15321,32 +15327,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J150" s="66" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Native Android lean template</x:v>
       </x:c>
       <x:c r="K150" s="66"/>
       <x:c r="L150" s="66"/>
       <x:c r="M150" s="66" t="str">
-        <x:v>Native selectable beta.</x:v>
+        <x:v>Experienced team structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="65" t="str">
-        <x:v>R-147</x:v>
+        <x:v>R-146</x:v>
       </x:c>
       <x:c r="B151" s="65" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C151" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D151" s="65" t="str">
-        <x:v>Native iOS scaled Swift Packages</x:v>
+        <x:v>Native iOS lean template</x:v>
       </x:c>
       <x:c r="E151" s="65" t="str">
-        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
+        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
       </x:c>
       <x:c r="F151" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G151" s="65"/>
       <x:c r="H151" s="65" t="str">
@@ -15357,32 +15363,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J151" s="65" t="str">
-        <x:v>Native iOS lean template</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="K151" s="65"/>
       <x:c r="L151" s="65"/>
       <x:c r="M151" s="65" t="str">
-        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="66" t="str">
-        <x:v>R-148</x:v>
+        <x:v>R-147</x:v>
       </x:c>
       <x:c r="B152" s="66" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C152" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D152" s="66" t="str">
-        <x:v>Next.js public web template</x:v>
+        <x:v>Native iOS scaled Swift Packages</x:v>
       </x:c>
       <x:c r="E152" s="66" t="str">
-        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
+        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
       </x:c>
       <x:c r="F152" s="66" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G152" s="66"/>
       <x:c r="H152" s="66" t="str">
@@ -15393,17 +15399,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J152" s="66" t="str">
-        <x:v>Next.js web + admin default</x:v>
+        <x:v>Native iOS lean template</x:v>
       </x:c>
       <x:c r="K152" s="66"/>
       <x:c r="L152" s="66"/>
       <x:c r="M152" s="66" t="str">
-        <x:v>Web optimized independently.</x:v>
+        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="65" t="str">
-        <x:v>R-149</x:v>
+        <x:v>R-148</x:v>
       </x:c>
       <x:c r="B153" s="65" t="str">
         <x:v>MVP</x:v>
@@ -15412,10 +15418,10 @@
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D153" s="65" t="str">
-        <x:v>Next.js admin template</x:v>
+        <x:v>Next.js public web template</x:v>
       </x:c>
       <x:c r="E153" s="65" t="str">
-        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
+        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
       </x:c>
       <x:c r="F153" s="65" t="str">
         <x:v>P0</x:v>
@@ -15434,12 +15440,12 @@
       <x:c r="K153" s="65"/>
       <x:c r="L153" s="65"/>
       <x:c r="M153" s="65" t="str">
-        <x:v>Never force admin onto Flutter/RN Web.</x:v>
+        <x:v>Web optimized independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="66" t="str">
-        <x:v>R-150</x:v>
+        <x:v>R-149</x:v>
       </x:c>
       <x:c r="B154" s="66" t="str">
         <x:v>MVP</x:v>
@@ -15448,10 +15454,10 @@
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D154" s="66" t="str">
-        <x:v>Go backend standard template</x:v>
+        <x:v>Next.js admin template</x:v>
       </x:c>
       <x:c r="E154" s="66" t="str">
-        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
+        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
       </x:c>
       <x:c r="F154" s="66" t="str">
         <x:v>P0</x:v>
@@ -15465,17 +15471,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J154" s="66" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Next.js web + admin default</x:v>
       </x:c>
       <x:c r="K154" s="66"/>
       <x:c r="L154" s="66"/>
       <x:c r="M154" s="66" t="str">
-        <x:v>Default backend profile.</x:v>
+        <x:v>Never force admin onto Flutter/RN Web.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="65" t="str">
-        <x:v>R-151</x:v>
+        <x:v>R-150</x:v>
       </x:c>
       <x:c r="B155" s="65" t="str">
         <x:v>MVP</x:v>
@@ -15484,10 +15490,10 @@
         <x:v>Templates</x:v>
       </x:c>
       <x:c r="D155" s="65" t="str">
-        <x:v>Python backend standard template</x:v>
+        <x:v>Go backend standard template</x:v>
       </x:c>
       <x:c r="E155" s="65" t="str">
-        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
+        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
       </x:c>
       <x:c r="F155" s="65" t="str">
         <x:v>P0</x:v>
@@ -15506,24 +15512,24 @@
       <x:c r="K155" s="65"/>
       <x:c r="L155" s="65"/>
       <x:c r="M155" s="65" t="str">
-        <x:v>Alternative default backend profile.</x:v>
+        <x:v>Default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="66" t="str">
-        <x:v>R-152</x:v>
+        <x:v>R-151</x:v>
       </x:c>
       <x:c r="B156" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C156" s="66" t="str">
-        <x:v>Contracts</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D156" s="66" t="str">
-        <x:v>Generated client matrix</x:v>
+        <x:v>Python backend standard template</x:v>
       </x:c>
       <x:c r="E156" s="66" t="str">
-        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
+        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
       </x:c>
       <x:c r="F156" s="66" t="str">
         <x:v>P0</x:v>
@@ -15537,29 +15543,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J156" s="66" t="str">
-        <x:v>Shared contracts package</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="K156" s="66"/>
       <x:c r="L156" s="66"/>
       <x:c r="M156" s="66" t="str">
-        <x:v>Contract-first consistency.</x:v>
+        <x:v>Alternative default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="65" t="str">
-        <x:v>R-153</x:v>
+        <x:v>R-152</x:v>
       </x:c>
       <x:c r="B157" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C157" s="65" t="str">
-        <x:v>Templates</x:v>
+        <x:v>Contracts</x:v>
       </x:c>
       <x:c r="D157" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
+        <x:v>Generated client matrix</x:v>
       </x:c>
       <x:c r="E157" s="65" t="str">
-        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
+        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
       </x:c>
       <x:c r="F157" s="65" t="str">
         <x:v>P0</x:v>
@@ -15573,29 +15579,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J157" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
+        <x:v>Shared contracts package</x:v>
       </x:c>
       <x:c r="K157" s="65"/>
       <x:c r="L157" s="65"/>
       <x:c r="M157" s="65" t="str">
-        <x:v>Stable/Beta/Experimental visible to user.</x:v>
+        <x:v>Contract-first consistency.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="66" t="str">
-        <x:v>R-154</x:v>
+        <x:v>R-153</x:v>
       </x:c>
       <x:c r="B158" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C158" s="66" t="str">
-        <x:v>Dependencies</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D158" s="66" t="str">
-        <x:v>Approved dependency catalog</x:v>
+        <x:v>Template manifest + maturity</x:v>
       </x:c>
       <x:c r="E158" s="66" t="str">
-        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
+        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
       </x:c>
       <x:c r="F158" s="66" t="str">
         <x:v>P0</x:v>
@@ -15609,29 +15615,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J158" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
+        <x:v>Framework-specific repo templates</x:v>
       </x:c>
       <x:c r="K158" s="66"/>
       <x:c r="L158" s="66"/>
       <x:c r="M158" s="66" t="str">
-        <x:v>Prevents dependency explosion.</x:v>
+        <x:v>Stable/Beta/Experimental visible to user.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="65" t="str">
-        <x:v>R-155</x:v>
+        <x:v>R-154</x:v>
       </x:c>
       <x:c r="B159" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C159" s="65" t="str">
-        <x:v>Platform Architecture</x:v>
+        <x:v>Dependencies</x:v>
       </x:c>
       <x:c r="D159" s="65" t="str">
-        <x:v>Go control plane modular monolith</x:v>
+        <x:v>Approved dependency catalog</x:v>
       </x:c>
       <x:c r="E159" s="65" t="str">
-        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
+        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
       </x:c>
       <x:c r="F159" s="65" t="str">
         <x:v>P0</x:v>
@@ -15645,17 +15651,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J159" s="65" t="str">
-        <x:v>Platform modular monorepo</x:v>
+        <x:v>Template manifest + maturity</x:v>
       </x:c>
       <x:c r="K159" s="65"/>
       <x:c r="L159" s="65"/>
       <x:c r="M159" s="65" t="str">
-        <x:v>Avoid premature microservices.</x:v>
+        <x:v>Prevents dependency explosion.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="66" t="str">
-        <x:v>R-156</x:v>
+        <x:v>R-155</x:v>
       </x:c>
       <x:c r="B160" s="66" t="str">
         <x:v>MVP</x:v>
@@ -15664,10 +15670,10 @@
         <x:v>Platform Architecture</x:v>
       </x:c>
       <x:c r="D160" s="66" t="str">
-        <x:v>Python agent engine boundary</x:v>
+        <x:v>Go control plane modular monolith</x:v>
       </x:c>
       <x:c r="E160" s="66" t="str">
-        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
+        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
       </x:c>
       <x:c r="F160" s="66" t="str">
         <x:v>P0</x:v>
@@ -15681,17 +15687,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J160" s="66" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Platform modular monorepo</x:v>
       </x:c>
       <x:c r="K160" s="66"/>
       <x:c r="L160" s="66"/>
       <x:c r="M160" s="66" t="str">
-        <x:v>Different ecosystem/iteration cadence.</x:v>
+        <x:v>Avoid premature microservices.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="65" t="str">
-        <x:v>R-157</x:v>
+        <x:v>R-156</x:v>
       </x:c>
       <x:c r="B161" s="65" t="str">
         <x:v>MVP</x:v>
@@ -15700,10 +15706,10 @@
         <x:v>Platform Architecture</x:v>
       </x:c>
       <x:c r="D161" s="65" t="str">
-        <x:v>Runner manager boundary</x:v>
+        <x:v>Python agent engine boundary</x:v>
       </x:c>
       <x:c r="E161" s="65" t="str">
-        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
+        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
       </x:c>
       <x:c r="F161" s="65" t="str">
         <x:v>P0</x:v>
@@ -15717,29 +15723,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J161" s="65" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="K161" s="65"/>
       <x:c r="L161" s="65"/>
       <x:c r="M161" s="65" t="str">
-        <x:v>Central execution control.</x:v>
+        <x:v>Different ecosystem/iteration cadence.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="66" t="str">
-        <x:v>R-158</x:v>
+        <x:v>R-157</x:v>
       </x:c>
       <x:c r="B162" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C162" s="66" t="str">
-        <x:v>CI/CD</x:v>
+        <x:v>Platform Architecture</x:v>
       </x:c>
       <x:c r="D162" s="66" t="str">
-        <x:v>Unified PR pipeline</x:v>
+        <x:v>Runner manager boundary</x:v>
       </x:c>
       <x:c r="E162" s="66" t="str">
-        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
+        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
       </x:c>
       <x:c r="F162" s="66" t="str">
         <x:v>P0</x:v>
@@ -15753,17 +15759,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J162" s="66" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K162" s="66"/>
       <x:c r="L162" s="66"/>
       <x:c r="M162" s="66" t="str">
-        <x:v>Real iOS compile uses macOS.</x:v>
+        <x:v>Central execution control.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="65" t="str">
-        <x:v>R-159</x:v>
+        <x:v>R-158</x:v>
       </x:c>
       <x:c r="B163" s="65" t="str">
         <x:v>MVP</x:v>
@@ -15772,13 +15778,13 @@
         <x:v>CI/CD</x:v>
       </x:c>
       <x:c r="D163" s="65" t="str">
-        <x:v>Immutable build promotion</x:v>
+        <x:v>Unified PR pipeline</x:v>
       </x:c>
       <x:c r="E163" s="65" t="str">
-        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
+        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
       </x:c>
       <x:c r="F163" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G163" s="65"/>
       <x:c r="H163" s="65" t="str">
@@ -15789,29 +15795,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J163" s="65" t="str">
-        <x:v>Deployment Agent</x:v>
+        <x:v>Atomic cross-platform change set</x:v>
       </x:c>
       <x:c r="K163" s="65"/>
       <x:c r="L163" s="65"/>
       <x:c r="M163" s="65" t="str">
-        <x:v>Reduces preview/production mismatch.</x:v>
+        <x:v>Real iOS compile uses macOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="66" t="str">
-        <x:v>R-160</x:v>
+        <x:v>R-159</x:v>
       </x:c>
       <x:c r="B164" s="66" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C164" s="66" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>CI/CD</x:v>
       </x:c>
       <x:c r="D164" s="66" t="str">
-        <x:v>Framework upgrade workflow</x:v>
+        <x:v>Immutable build promotion</x:v>
       </x:c>
       <x:c r="E164" s="66" t="str">
-        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
+        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
       </x:c>
       <x:c r="F164" s="66" t="str">
         <x:v>P1</x:v>
@@ -15825,27 +15831,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J164" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
+        <x:v>Deployment Agent</x:v>
       </x:c>
       <x:c r="K164" s="66"/>
       <x:c r="L164" s="66"/>
-      <x:c r="M164" s="66"/>
+      <x:c r="M164" s="66" t="str">
+        <x:v>Reduces preview/production mismatch.</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="65" t="str">
-        <x:v>R-161</x:v>
+        <x:v>R-160</x:v>
       </x:c>
       <x:c r="B165" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C165" s="65" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D165" s="65" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="E165" s="65" t="str">
-        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
+        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
       </x:c>
       <x:c r="F165" s="65" t="str">
         <x:v>P1</x:v>
@@ -15859,17 +15867,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J165" s="65" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Template manifest + maturity</x:v>
       </x:c>
       <x:c r="K165" s="65"/>
       <x:c r="L165" s="65"/>
-      <x:c r="M165" s="65" t="str">
-        <x:v>Reduces cloud Mac cost.</x:v>
-      </x:c>
+      <x:c r="M165" s="65"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="66" t="str">
-        <x:v>R-162</x:v>
+        <x:v>R-161</x:v>
       </x:c>
       <x:c r="B166" s="66" t="str">
         <x:v>MID</x:v>
@@ -15878,10 +15884,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D166" s="66" t="str">
-        <x:v>Interactive cloud simulator metering</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="E166" s="66" t="str">
-        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
+        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
       </x:c>
       <x:c r="F166" s="66" t="str">
         <x:v>P1</x:v>
@@ -15895,29 +15901,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J166" s="66" t="str">
-        <x:v>Real iOS Simulator</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="K166" s="66"/>
       <x:c r="L166" s="66"/>
       <x:c r="M166" s="66" t="str">
-        <x:v>Separate verification build cost from interactive session cost.</x:v>
+        <x:v>Reduces cloud Mac cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="65" t="str">
-        <x:v>R-163</x:v>
+        <x:v>R-162</x:v>
       </x:c>
       <x:c r="B167" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C167" s="65" t="str">
-        <x:v>Framework Strategy</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D167" s="65" t="str">
-        <x:v>Native module adapter path</x:v>
+        <x:v>Interactive cloud simulator metering</x:v>
       </x:c>
       <x:c r="E167" s="65" t="str">
-        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
+        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
       </x:c>
       <x:c r="F167" s="65" t="str">
         <x:v>P1</x:v>
@@ -15931,29 +15937,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J167" s="65" t="str">
-        <x:v>Framework adapter contract</x:v>
+        <x:v>Real iOS Simulator</x:v>
       </x:c>
       <x:c r="K167" s="65"/>
       <x:c r="L167" s="65"/>
       <x:c r="M167" s="65" t="str">
-        <x:v>Measure before rewrite.</x:v>
+        <x:v>Separate verification build cost from interactive session cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="66" t="str">
-        <x:v>R-164</x:v>
+        <x:v>R-163</x:v>
       </x:c>
       <x:c r="B168" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C168" s="66" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Framework Strategy</x:v>
       </x:c>
       <x:c r="D168" s="66" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Native module adapter path</x:v>
       </x:c>
       <x:c r="E168" s="66" t="str">
-        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
+        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
       </x:c>
       <x:c r="F168" s="66" t="str">
         <x:v>P1</x:v>
@@ -15967,29 +15973,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J168" s="66" t="str">
-        <x:v>Repository/build health metrics</x:v>
+        <x:v>Framework adapter contract</x:v>
       </x:c>
       <x:c r="K168" s="66"/>
       <x:c r="L168" s="66"/>
       <x:c r="M168" s="66" t="str">
-        <x:v>Use data to trigger architecture review.</x:v>
+        <x:v>Measure before rewrite.</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="65" t="str">
-        <x:v>R-165</x:v>
+        <x:v>R-164</x:v>
       </x:c>
       <x:c r="B169" s="65" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C169" s="65" t="str">
-        <x:v>Migration</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D169" s="65" t="str">
-        <x:v>Cross-platform to native migration engine</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="E169" s="65" t="str">
-        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
+        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
       </x:c>
       <x:c r="F169" s="65" t="str">
         <x:v>P1</x:v>
@@ -16003,32 +16009,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J169" s="65" t="str">
-        <x:v>Native module adapter path</x:v>
+        <x:v>Repository/build health metrics</x:v>
       </x:c>
       <x:c r="K169" s="65"/>
       <x:c r="L169" s="65"/>
       <x:c r="M169" s="65" t="str">
-        <x:v>Prevents framework lock-in.</x:v>
+        <x:v>Use data to trigger architecture review.</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="66" t="str">
-        <x:v>R-166</x:v>
+        <x:v>R-165</x:v>
       </x:c>
       <x:c r="B170" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C170" s="66" t="str">
-        <x:v>Git/Repository</x:v>
+        <x:v>Migration</x:v>
       </x:c>
       <x:c r="D170" s="66" t="str">
-        <x:v>Cross-repo task coordinator</x:v>
+        <x:v>Cross-platform to native migration engine</x:v>
       </x:c>
       <x:c r="E170" s="66" t="str">
-        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
+        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
       </x:c>
       <x:c r="F170" s="66" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G170" s="66"/>
       <x:c r="H170" s="66" t="str">
@@ -16039,27 +16045,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J170" s="66" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
+        <x:v>Native module adapter path</x:v>
       </x:c>
       <x:c r="K170" s="66"/>
       <x:c r="L170" s="66"/>
-      <x:c r="M170" s="66"/>
+      <x:c r="M170" s="66" t="str">
+        <x:v>Prevents framework lock-in.</x:v>
+      </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="65" t="str">
-        <x:v>R-167</x:v>
+        <x:v>R-166</x:v>
       </x:c>
       <x:c r="B171" s="65" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C171" s="65" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Git/Repository</x:v>
       </x:c>
       <x:c r="D171" s="65" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Cross-repo task coordinator</x:v>
       </x:c>
       <x:c r="E171" s="65" t="str">
-        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
+        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
       </x:c>
       <x:c r="F171" s="65" t="str">
         <x:v>P2</x:v>
@@ -16073,7 +16081,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J171" s="65" t="str">
-        <x:v>Enterprise workload isolation</x:v>
+        <x:v>Enterprise multi-repo support</x:v>
       </x:c>
       <x:c r="K171" s="65"/>
       <x:c r="L171" s="65"/>
@@ -16081,19 +16089,19 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="66" t="str">
-        <x:v>R-168</x:v>
+        <x:v>R-167</x:v>
       </x:c>
       <x:c r="B172" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C172" s="66" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D172" s="66" t="str">
-        <x:v>Physical device cloud integration</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="E172" s="66" t="str">
-        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
+        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
       </x:c>
       <x:c r="F172" s="66" t="str">
         <x:v>P2</x:v>
@@ -16107,7 +16115,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J172" s="66" t="str">
-        <x:v>Real iOS Simulator</x:v>
+        <x:v>Enterprise workload isolation</x:v>
       </x:c>
       <x:c r="K172" s="66"/>
       <x:c r="L172" s="66"/>
@@ -16115,22 +16123,22 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="65" t="str">
-        <x:v>R-169</x:v>
+        <x:v>R-168</x:v>
       </x:c>
       <x:c r="B173" s="65" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C173" s="65" t="str">
-        <x:v>Templates</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D173" s="65" t="str">
-        <x:v>Template support lifecycle</x:v>
+        <x:v>Physical device cloud integration</x:v>
       </x:c>
       <x:c r="E173" s="65" t="str">
-        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
+        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
       </x:c>
       <x:c r="F173" s="65" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G173" s="65"/>
       <x:c r="H173" s="65" t="str">
@@ -16141,7 +16149,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J173" s="65" t="str">
-        <x:v>Framework upgrade workflow</x:v>
+        <x:v>Real iOS Simulator</x:v>
       </x:c>
       <x:c r="K173" s="65"/>
       <x:c r="L173" s="65"/>
@@ -16149,22 +16157,22 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="127" t="str">
-        <x:v>R-170</x:v>
+        <x:v>R-169</x:v>
       </x:c>
       <x:c r="B174" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C174" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D174" s="127" t="str">
-        <x:v>Framework/toolchain production SLO</x:v>
+        <x:v>Template support lifecycle</x:v>
       </x:c>
       <x:c r="E174" s="127" t="str">
-        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
+        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
       </x:c>
       <x:c r="F174" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G174" s="127"/>
       <x:c r="H174" s="127" t="str">
@@ -16175,29 +16183,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J174" s="127" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="K174" s="127"/>
       <x:c r="L174" s="127"/>
-      <x:c r="M174" s="127" t="str">
-        <x:v>Production readiness is measured, not assumed.</x:v>
-      </x:c>
+      <x:c r="M174" s="127"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="127" t="str">
-        <x:v>R-171</x:v>
+        <x:v>R-170</x:v>
       </x:c>
       <x:c r="B175" s="127" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C175" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D175" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Framework/toolchain production SLO</x:v>
       </x:c>
       <x:c r="E175" s="127" t="str">
-        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
+        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
       </x:c>
       <x:c r="F175" s="127" t="str">
         <x:v>P0</x:v>
@@ -16211,17 +16217,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J175" s="127" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="K175" s="127"/>
       <x:c r="L175" s="127"/>
       <x:c r="M175" s="127" t="str">
-        <x:v>No agent-to-vendor SDK coupling.</x:v>
+        <x:v>Production readiness is measured, not assumed.</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="127" t="str">
-        <x:v>R-172</x:v>
+        <x:v>R-171</x:v>
       </x:c>
       <x:c r="B176" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16230,10 +16236,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D176" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="E176" s="127" t="str">
-        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
+        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
       </x:c>
       <x:c r="F176" s="127" t="str">
         <x:v>P0</x:v>
@@ -16247,17 +16253,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J176" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K176" s="127"/>
       <x:c r="L176" s="127"/>
       <x:c r="M176" s="127" t="str">
-        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
+        <x:v>No agent-to-vendor SDK coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="127" t="str">
-        <x:v>R-173</x:v>
+        <x:v>R-172</x:v>
       </x:c>
       <x:c r="B177" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16266,10 +16272,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D177" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="E177" s="127" t="str">
-        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
+        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
       </x:c>
       <x:c r="F177" s="127" t="str">
         <x:v>P0</x:v>
@@ -16288,12 +16294,12 @@
       <x:c r="K177" s="127"/>
       <x:c r="L177" s="127"/>
       <x:c r="M177" s="127" t="str">
-        <x:v>Cheapest safe runtime wins.</x:v>
+        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="127" t="str">
-        <x:v>R-174</x:v>
+        <x:v>R-173</x:v>
       </x:c>
       <x:c r="B178" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16302,13 +16308,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D178" s="127" t="str">
-        <x:v>Browser runtime PoC</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="E178" s="127" t="str">
-        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
+        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
       </x:c>
       <x:c r="F178" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G178" s="127"/>
       <x:c r="H178" s="127" t="str">
@@ -16319,17 +16325,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K178" s="127"/>
       <x:c r="L178" s="127"/>
       <x:c r="M178" s="127" t="str">
-        <x:v>Not universal sandbox.</x:v>
+        <x:v>Cheapest safe runtime wins.</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="127" t="str">
-        <x:v>R-175</x:v>
+        <x:v>R-174</x:v>
       </x:c>
       <x:c r="B179" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16338,13 +16344,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D179" s="127" t="str">
-        <x:v>Runtime quotas and metering</x:v>
+        <x:v>Browser runtime PoC</x:v>
       </x:c>
       <x:c r="E179" s="127" t="str">
-        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
+        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
       </x:c>
       <x:c r="F179" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G179" s="127"/>
       <x:c r="H179" s="127" t="str">
@@ -16355,29 +16361,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="K179" s="127"/>
       <x:c r="L179" s="127"/>
       <x:c r="M179" s="127" t="str">
-        <x:v>Required for cost and abuse control.</x:v>
+        <x:v>Not universal sandbox.</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="127" t="str">
-        <x:v>R-176</x:v>
+        <x:v>R-175</x:v>
       </x:c>
       <x:c r="B180" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C180" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D180" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Runtime quotas and metering</x:v>
       </x:c>
       <x:c r="E180" s="127" t="str">
-        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
+        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
       </x:c>
       <x:c r="F180" s="127" t="str">
         <x:v>P0</x:v>
@@ -16391,17 +16397,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="127" t="str">
-        <x:v>Supervisor / orchestrator</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K180" s="127"/>
       <x:c r="L180" s="127"/>
       <x:c r="M180" s="127" t="str">
-        <x:v>Platform-owned state schema.</x:v>
+        <x:v>Required for cost and abuse control.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="127" t="str">
-        <x:v>R-177</x:v>
+        <x:v>R-176</x:v>
       </x:c>
       <x:c r="B181" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16410,10 +16416,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D181" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="E181" s="127" t="str">
-        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
+        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
       </x:c>
       <x:c r="F181" s="127" t="str">
         <x:v>P0</x:v>
@@ -16427,17 +16433,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Supervisor / orchestrator</x:v>
       </x:c>
       <x:c r="K181" s="127"/>
       <x:c r="L181" s="127"/>
       <x:c r="M181" s="127" t="str">
-        <x:v>No full restart by default.</x:v>
+        <x:v>Platform-owned state schema.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="127" t="str">
-        <x:v>R-178</x:v>
+        <x:v>R-177</x:v>
       </x:c>
       <x:c r="B182" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16446,10 +16452,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D182" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="E182" s="127" t="str">
-        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
+        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
       </x:c>
       <x:c r="F182" s="127" t="str">
         <x:v>P0</x:v>
@@ -16463,29 +16469,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K182" s="127"/>
       <x:c r="L182" s="127"/>
       <x:c r="M182" s="127" t="str">
-        <x:v>Prevent duplicate side effects.</x:v>
+        <x:v>No full restart by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="127" t="str">
-        <x:v>R-179</x:v>
+        <x:v>R-178</x:v>
       </x:c>
       <x:c r="B183" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C183" s="127" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D183" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="E183" s="127" t="str">
-        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
+        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
       </x:c>
       <x:c r="F183" s="127" t="str">
         <x:v>P0</x:v>
@@ -16499,29 +16505,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K183" s="127"/>
       <x:c r="L183" s="127"/>
       <x:c r="M183" s="127" t="str">
-        <x:v>Supports replay, audit and debugging.</x:v>
+        <x:v>Prevent duplicate side effects.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="127" t="str">
-        <x:v>R-180</x:v>
+        <x:v>R-179</x:v>
       </x:c>
       <x:c r="B184" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C184" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D184" s="127" t="str">
-        <x:v>Orchestrator Adapter</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="E184" s="127" t="str">
-        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
+        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
       </x:c>
       <x:c r="F184" s="127" t="str">
         <x:v>P0</x:v>
@@ -16540,24 +16546,24 @@
       <x:c r="K184" s="127"/>
       <x:c r="L184" s="127"/>
       <x:c r="M184" s="127" t="str">
-        <x:v>LangGraph may be first implementation.</x:v>
+        <x:v>Supports replay, audit and debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="127" t="str">
-        <x:v>R-181</x:v>
+        <x:v>R-180</x:v>
       </x:c>
       <x:c r="B185" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C185" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D185" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Orchestrator Adapter</x:v>
       </x:c>
       <x:c r="E185" s="127" t="str">
-        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
+        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
       </x:c>
       <x:c r="F185" s="127" t="str">
         <x:v>P0</x:v>
@@ -16571,17 +16577,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K185" s="127"/>
       <x:c r="L185" s="127"/>
       <x:c r="M185" s="127" t="str">
-        <x:v>Frontend never parses provider-specific streams.</x:v>
+        <x:v>LangGraph may be first implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="127" t="str">
-        <x:v>R-182</x:v>
+        <x:v>R-181</x:v>
       </x:c>
       <x:c r="B186" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16590,10 +16596,10 @@
         <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D186" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="E186" s="127" t="str">
-        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
+        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
       </x:c>
       <x:c r="F186" s="127" t="str">
         <x:v>P0</x:v>
@@ -16607,29 +16613,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K186" s="127"/>
       <x:c r="L186" s="127"/>
       <x:c r="M186" s="127" t="str">
-        <x:v>SSE allowed for simple one-way streams.</x:v>
+        <x:v>Frontend never parses provider-specific streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="127" t="str">
-        <x:v>R-183</x:v>
+        <x:v>R-182</x:v>
       </x:c>
       <x:c r="B187" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C187" s="127" t="str">
-        <x:v>Approvals</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D187" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="E187" s="127" t="str">
-        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
+        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
       </x:c>
       <x:c r="F187" s="127" t="str">
         <x:v>P0</x:v>
@@ -16643,17 +16649,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="K187" s="127"/>
       <x:c r="L187" s="127"/>
       <x:c r="M187" s="127" t="str">
-        <x:v>Approval based on risk.</x:v>
+        <x:v>SSE allowed for simple one-way streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="127" t="str">
-        <x:v>R-184</x:v>
+        <x:v>R-183</x:v>
       </x:c>
       <x:c r="B188" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16662,10 +16668,10 @@
         <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D188" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="E188" s="127" t="str">
-        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
+        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
       </x:c>
       <x:c r="F188" s="127" t="str">
         <x:v>P0</x:v>
@@ -16679,29 +16685,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K188" s="127"/>
       <x:c r="L188" s="127"/>
       <x:c r="M188" s="127" t="str">
-        <x:v>Production/destructive actions auditable.</x:v>
+        <x:v>Approval based on risk.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="127" t="str">
-        <x:v>R-185</x:v>
+        <x:v>R-184</x:v>
       </x:c>
       <x:c r="B189" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C189" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D189" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="E189" s="127" t="str">
-        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
+        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
       </x:c>
       <x:c r="F189" s="127" t="str">
         <x:v>P0</x:v>
@@ -16715,17 +16721,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="K189" s="127"/>
       <x:c r="L189" s="127"/>
       <x:c r="M189" s="127" t="str">
-        <x:v>Deny by default.</x:v>
+        <x:v>Production/destructive actions auditable.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="127" t="str">
-        <x:v>R-186</x:v>
+        <x:v>R-185</x:v>
       </x:c>
       <x:c r="B190" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16734,13 +16740,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D190" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="E190" s="127" t="str">
-        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
+        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
       </x:c>
       <x:c r="F190" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G190" s="127"/>
       <x:c r="H190" s="127" t="str">
@@ -16751,17 +16757,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K190" s="127"/>
       <x:c r="L190" s="127"/>
       <x:c r="M190" s="127" t="str">
-        <x:v>No arbitrary agent-to-MCP connections.</x:v>
+        <x:v>Deny by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="127" t="str">
-        <x:v>R-187</x:v>
+        <x:v>R-186</x:v>
       </x:c>
       <x:c r="B191" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16770,13 +16776,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D191" s="127" t="str">
-        <x:v>Tool secret broker</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="E191" s="127" t="str">
-        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
+        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
       </x:c>
       <x:c r="F191" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G191" s="127"/>
       <x:c r="H191" s="127" t="str">
@@ -16792,27 +16798,27 @@
       <x:c r="K191" s="127"/>
       <x:c r="L191" s="127"/>
       <x:c r="M191" s="127" t="str">
-        <x:v>Audit every secret grant.</x:v>
+        <x:v>No arbitrary agent-to-MCP connections.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="127" t="str">
-        <x:v>R-188</x:v>
+        <x:v>R-187</x:v>
       </x:c>
       <x:c r="B192" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C192" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D192" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Tool secret broker</x:v>
       </x:c>
       <x:c r="E192" s="127" t="str">
-        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
+        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
       </x:c>
       <x:c r="F192" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G192" s="127"/>
       <x:c r="H192" s="127" t="str">
@@ -16823,32 +16829,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="127" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="K192" s="127"/>
       <x:c r="L192" s="127"/>
       <x:c r="M192" s="127" t="str">
-        <x:v>Not platform core.</x:v>
+        <x:v>Audit every secret grant.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="127" t="str">
-        <x:v>R-189</x:v>
+        <x:v>R-188</x:v>
       </x:c>
       <x:c r="B193" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C193" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D193" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="E193" s="127" t="str">
-        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
+        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
       </x:c>
       <x:c r="F193" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G193" s="127"/>
       <x:c r="H193" s="127" t="str">
@@ -16859,29 +16865,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="127" t="str">
-        <x:v>Architecture decision records</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K193" s="127"/>
       <x:c r="L193" s="127"/>
       <x:c r="M193" s="127" t="str">
-        <x:v>References inform; benchmarks decide.</x:v>
+        <x:v>Not platform core.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="127" t="str">
-        <x:v>R-190</x:v>
+        <x:v>R-189</x:v>
       </x:c>
       <x:c r="B194" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C194" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D194" s="127" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="E194" s="127" t="str">
-        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
+        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
       </x:c>
       <x:c r="F194" s="127" t="str">
         <x:v>P0</x:v>
@@ -16895,32 +16901,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Architecture decision records</x:v>
       </x:c>
       <x:c r="K194" s="127"/>
       <x:c r="L194" s="127"/>
       <x:c r="M194" s="127" t="str">
-        <x:v>Architectural learning != code copying.</x:v>
+        <x:v>References inform; benchmarks decide.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="127" t="str">
-        <x:v>R-191</x:v>
+        <x:v>R-190</x:v>
       </x:c>
       <x:c r="B195" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C195" s="127" t="str">
-        <x:v>Team</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D195" s="127" t="str">
-        <x:v>Shared engineering glossary</x:v>
+        <x:v>Open-source license review</x:v>
       </x:c>
       <x:c r="E195" s="127" t="str">
-        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
+        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
       </x:c>
       <x:c r="F195" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G195" s="127"/>
       <x:c r="H195" s="127" t="str">
@@ -16930,31 +16936,33 @@
         <x:f>IF(H195="Done",1,IF(H195="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J195" s="127"/>
+      <x:c r="J195" s="127" t="str">
+        <x:v>Build-vs-Buy benchmark process</x:v>
+      </x:c>
       <x:c r="K195" s="127"/>
       <x:c r="L195" s="127"/>
       <x:c r="M195" s="127" t="str">
-        <x:v>Use in docs and AI prompts.</x:v>
+        <x:v>Architectural learning != code copying.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="127" t="str">
-        <x:v>R-192</x:v>
+        <x:v>R-191</x:v>
       </x:c>
       <x:c r="B196" s="127" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C196" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Team</x:v>
       </x:c>
       <x:c r="D196" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Shared engineering glossary</x:v>
       </x:c>
       <x:c r="E196" s="127" t="str">
-        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
+        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
       </x:c>
       <x:c r="F196" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G196" s="127"/>
       <x:c r="H196" s="127" t="str">
@@ -16964,30 +16972,28 @@
         <x:f>IF(H196="Done",1,IF(H196="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J196" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
-      </x:c>
+      <x:c r="J196" s="127"/>
       <x:c r="K196" s="127"/>
       <x:c r="L196" s="127"/>
       <x:c r="M196" s="127" t="str">
-        <x:v>Marketplace later.</x:v>
+        <x:v>Use in docs and AI prompts.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="127" t="str">
-        <x:v>R-193</x:v>
+        <x:v>R-192</x:v>
       </x:c>
       <x:c r="B197" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C197" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D197" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="E197" s="127" t="str">
-        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
+        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
       </x:c>
       <x:c r="F197" s="127" t="str">
         <x:v>P1</x:v>
@@ -17001,17 +17007,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J197" s="127" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K197" s="127"/>
       <x:c r="L197" s="127"/>
       <x:c r="M197" s="127" t="str">
-        <x:v>Extends local mode beyond Mac.</x:v>
+        <x:v>Marketplace later.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="127" t="str">
-        <x:v>R-194</x:v>
+        <x:v>R-193</x:v>
       </x:c>
       <x:c r="B198" s="127" t="str">
         <x:v>MID</x:v>
@@ -17020,10 +17026,10 @@
         <x:v>Execution</x:v>
       </x:c>
       <x:c r="D198" s="127" t="str">
-        <x:v>Hybrid BYOK/local mode</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="E198" s="127" t="str">
-        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
+        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
       </x:c>
       <x:c r="F198" s="127" t="str">
         <x:v>P1</x:v>
@@ -17037,29 +17043,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J198" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="K198" s="127"/>
       <x:c r="L198" s="127"/>
       <x:c r="M198" s="127" t="str">
-        <x:v>Privacy + cost option.</x:v>
+        <x:v>Extends local mode beyond Mac.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="127" t="str">
-        <x:v>R-195</x:v>
+        <x:v>R-194</x:v>
       </x:c>
       <x:c r="B199" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C199" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D199" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Hybrid BYOK/local mode</x:v>
       </x:c>
       <x:c r="E199" s="127" t="str">
-        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
+        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
       </x:c>
       <x:c r="F199" s="127" t="str">
         <x:v>P1</x:v>
@@ -17073,17 +17079,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J199" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K199" s="127"/>
       <x:c r="L199" s="127"/>
       <x:c r="M199" s="127" t="str">
-        <x:v>Validate portability/failover.</x:v>
+        <x:v>Privacy + cost option.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="127" t="str">
-        <x:v>R-196</x:v>
+        <x:v>R-195</x:v>
       </x:c>
       <x:c r="B200" s="127" t="str">
         <x:v>MID</x:v>
@@ -17092,13 +17098,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D200" s="127" t="str">
-        <x:v>Sandbox snapshots and warm pools</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="E200" s="127" t="str">
-        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
+        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
       </x:c>
       <x:c r="F200" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G200" s="127"/>
       <x:c r="H200" s="127" t="str">
@@ -17109,32 +17115,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K200" s="127"/>
       <x:c r="L200" s="127"/>
       <x:c r="M200" s="127" t="str">
-        <x:v>Do not optimize blindly.</x:v>
+        <x:v>Validate portability/failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="127" t="str">
-        <x:v>R-197</x:v>
+        <x:v>R-196</x:v>
       </x:c>
       <x:c r="B201" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C201" s="127" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D201" s="127" t="str">
-        <x:v>Agent time-travel debugging</x:v>
+        <x:v>Sandbox snapshots and warm pools</x:v>
       </x:c>
       <x:c r="E201" s="127" t="str">
-        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
+        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
       </x:c>
       <x:c r="F201" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G201" s="127"/>
       <x:c r="H201" s="127" t="str">
@@ -17145,32 +17151,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K201" s="127"/>
       <x:c r="L201" s="127"/>
       <x:c r="M201" s="127" t="str">
-        <x:v>Operator and developer debugging.</x:v>
+        <x:v>Do not optimize blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="127" t="str">
-        <x:v>R-198</x:v>
+        <x:v>R-197</x:v>
       </x:c>
       <x:c r="B202" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C202" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D202" s="127" t="str">
-        <x:v>Tool marketplace verification</x:v>
+        <x:v>Agent time-travel debugging</x:v>
       </x:c>
       <x:c r="E202" s="127" t="str">
-        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
+        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
       </x:c>
       <x:c r="F202" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G202" s="127"/>
       <x:c r="H202" s="127" t="str">
@@ -17181,32 +17187,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K202" s="127"/>
       <x:c r="L202" s="127"/>
       <x:c r="M202" s="127" t="str">
-        <x:v>Verified badge is evidence-based.</x:v>
+        <x:v>Operator and developer debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="127" t="str">
-        <x:v>R-199</x:v>
+        <x:v>R-198</x:v>
       </x:c>
       <x:c r="B203" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C203" s="127" t="str">
-        <x:v>Routing</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D203" s="127" t="str">
-        <x:v>Runtime provider cost-latency routing</x:v>
+        <x:v>Tool marketplace verification</x:v>
       </x:c>
       <x:c r="E203" s="127" t="str">
-        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
+        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
       </x:c>
       <x:c r="F203" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G203" s="127"/>
       <x:c r="H203" s="127" t="str">
@@ -17217,32 +17223,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K203" s="127"/>
       <x:c r="L203" s="127"/>
       <x:c r="M203" s="127" t="str">
-        <x:v>Policy can override cheapest route.</x:v>
+        <x:v>Verified badge is evidence-based.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="127" t="str">
-        <x:v>R-200</x:v>
+        <x:v>R-199</x:v>
       </x:c>
       <x:c r="B204" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C204" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="D204" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Runtime provider cost-latency routing</x:v>
       </x:c>
       <x:c r="E204" s="127" t="str">
-        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
+        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
       </x:c>
       <x:c r="F204" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G204" s="127"/>
       <x:c r="H204" s="127" t="str">
@@ -17253,29 +17259,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K204" s="127"/>
       <x:c r="L204" s="127"/>
       <x:c r="M204" s="127" t="str">
-        <x:v>Keep portability via IR/contracts.</x:v>
+        <x:v>Policy can override cheapest route.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="127" t="str">
-        <x:v>R-201</x:v>
+        <x:v>R-200</x:v>
       </x:c>
       <x:c r="B205" s="127" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C205" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D205" s="127" t="str">
-        <x:v>Customer private MCP servers</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="E205" s="127" t="str">
-        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
+        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
       </x:c>
       <x:c r="F205" s="127" t="str">
         <x:v>P2</x:v>
@@ -17289,32 +17295,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="K205" s="127"/>
       <x:c r="L205" s="127"/>
       <x:c r="M205" s="127" t="str">
-        <x:v>Enterprise feature.</x:v>
+        <x:v>Keep portability via IR/contracts.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="127" t="str">
-        <x:v>R-202</x:v>
+        <x:v>R-201</x:v>
       </x:c>
       <x:c r="B206" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C206" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D206" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>Customer private MCP servers</x:v>
       </x:c>
       <x:c r="E206" s="127" t="str">
-        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
+        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
       </x:c>
       <x:c r="F206" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G206" s="127"/>
       <x:c r="H206" s="127" t="str">
@@ -17325,32 +17331,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="127" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K206" s="127"/>
       <x:c r="L206" s="127"/>
       <x:c r="M206" s="127" t="str">
-        <x:v>Central policy + audit remain.</x:v>
+        <x:v>Enterprise feature.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="127" t="str">
-        <x:v>R-203</x:v>
+        <x:v>R-202</x:v>
       </x:c>
       <x:c r="B207" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C207" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D207" s="127" t="str">
-        <x:v>Cross-region runtime scheduler</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="E207" s="127" t="str">
-        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
+        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
       </x:c>
       <x:c r="F207" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G207" s="127"/>
       <x:c r="H207" s="127" t="str">
@@ -17361,17 +17367,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="K207" s="127"/>
       <x:c r="L207" s="127"/>
       <x:c r="M207" s="127" t="str">
-        <x:v>Enterprise scale.</x:v>
+        <x:v>Central policy + audit remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="127" t="str">
-        <x:v>R-204</x:v>
+        <x:v>R-203</x:v>
       </x:c>
       <x:c r="B208" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17380,10 +17386,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D208" s="127" t="str">
-        <x:v>Hardened microVM runner fleet</x:v>
+        <x:v>Cross-region runtime scheduler</x:v>
       </x:c>
       <x:c r="E208" s="127" t="str">
-        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
+        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
       </x:c>
       <x:c r="F208" s="127" t="str">
         <x:v>P2</x:v>
@@ -17397,32 +17403,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="127" t="str">
-        <x:v>Provider cost-latency routing</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="K208" s="127"/>
       <x:c r="L208" s="127"/>
       <x:c r="M208" s="127" t="str">
-        <x:v>Do not build before benchmark.</x:v>
+        <x:v>Enterprise scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="127" t="str">
-        <x:v>R-205</x:v>
+        <x:v>R-204</x:v>
       </x:c>
       <x:c r="B209" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C209" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D209" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>Hardened microVM runner fleet</x:v>
       </x:c>
       <x:c r="E209" s="127" t="str">
-        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
+        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
       </x:c>
       <x:c r="F209" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G209" s="127"/>
       <x:c r="H209" s="127" t="str">
@@ -17433,29 +17439,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Provider cost-latency routing</x:v>
       </x:c>
       <x:c r="K209" s="127"/>
       <x:c r="L209" s="127"/>
       <x:c r="M209" s="127" t="str">
-        <x:v>Checkpoint-aware failover.</x:v>
+        <x:v>Do not build before benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="127" t="str">
-        <x:v>R-206</x:v>
+        <x:v>R-205</x:v>
       </x:c>
       <x:c r="B210" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C210" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D210" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="E210" s="127" t="str">
-        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
+        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
       </x:c>
       <x:c r="F210" s="127" t="str">
         <x:v>P1</x:v>
@@ -17469,17 +17475,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K210" s="127"/>
       <x:c r="L210" s="127"/>
       <x:c r="M210" s="127" t="str">
-        <x:v>Enterprise override support.</x:v>
+        <x:v>Checkpoint-aware failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="127" t="str">
-        <x:v>R-207</x:v>
+        <x:v>R-206</x:v>
       </x:c>
       <x:c r="B211" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17488,13 +17494,13 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D211" s="127" t="str">
-        <x:v>Two-person critical approval</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="E211" s="127" t="str">
-        <x:v>Optional dual approval for L4 actions.</x:v>
+        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
       </x:c>
       <x:c r="F211" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G211" s="127"/>
       <x:c r="H211" s="127" t="str">
@@ -17505,29 +17511,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K211" s="127"/>
       <x:c r="L211" s="127"/>
       <x:c r="M211" s="127" t="str">
-        <x:v>High-risk enterprise.</x:v>
+        <x:v>Enterprise override support.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="127" t="str">
-        <x:v>R-208</x:v>
+        <x:v>R-207</x:v>
       </x:c>
       <x:c r="B212" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C212" s="127" t="str">
-        <x:v>Models</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D212" s="127" t="str">
-        <x:v>Customer private model endpoints</x:v>
+        <x:v>Two-person critical approval</x:v>
       </x:c>
       <x:c r="E212" s="127" t="str">
-        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
+        <x:v>Optional dual approval for L4 actions.</x:v>
       </x:c>
       <x:c r="F212" s="127" t="str">
         <x:v>P2</x:v>
@@ -17541,29 +17547,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="127" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="K212" s="127"/>
       <x:c r="L212" s="127"/>
       <x:c r="M212" s="127" t="str">
-        <x:v>No direct client-to-model coupling.</x:v>
+        <x:v>High-risk enterprise.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="127" t="str">
-        <x:v>R-209</x:v>
+        <x:v>R-208</x:v>
       </x:c>
       <x:c r="B213" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C213" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D213" s="127" t="str">
-        <x:v>Automated provider benchmark suite</x:v>
+        <x:v>Customer private model endpoints</x:v>
       </x:c>
       <x:c r="E213" s="127" t="str">
-        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
+        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
       </x:c>
       <x:c r="F213" s="127" t="str">
         <x:v>P2</x:v>
@@ -17577,32 +17583,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="K213" s="127"/>
       <x:c r="L213" s="127"/>
       <x:c r="M213" s="127" t="str">
-        <x:v>Feeds routing/ADR reviews.</x:v>
+        <x:v>No direct client-to-model coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="127" t="str">
-        <x:v>R-210</x:v>
+        <x:v>R-209</x:v>
       </x:c>
       <x:c r="B214" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C214" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D214" s="127" t="str">
-        <x:v>Crash-resume production test</x:v>
+        <x:v>Automated provider benchmark suite</x:v>
       </x:c>
       <x:c r="E214" s="127" t="str">
-        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
+        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
       </x:c>
       <x:c r="F214" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G214" s="127"/>
       <x:c r="H214" s="127" t="str">
@@ -17613,17 +17619,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="K214" s="127"/>
       <x:c r="L214" s="127"/>
       <x:c r="M214" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Feeds routing/ADR reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="127" t="str">
-        <x:v>R-211</x:v>
+        <x:v>R-210</x:v>
       </x:c>
       <x:c r="B215" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17632,10 +17638,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D215" s="127" t="str">
-        <x:v>Duplicate side-effect prevention test</x:v>
+        <x:v>Crash-resume production test</x:v>
       </x:c>
       <x:c r="E215" s="127" t="str">
-        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
+        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
       </x:c>
       <x:c r="F215" s="127" t="str">
         <x:v>P0</x:v>
@@ -17649,7 +17655,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K215" s="127"/>
       <x:c r="L215" s="127"/>
@@ -17659,19 +17665,19 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="127" t="str">
-        <x:v>R-212</x:v>
+        <x:v>R-211</x:v>
       </x:c>
       <x:c r="B216" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C216" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D216" s="127" t="str">
-        <x:v>WebSocket replay correctness SLO</x:v>
+        <x:v>Duplicate side-effect prevention test</x:v>
       </x:c>
       <x:c r="E216" s="127" t="str">
-        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
+        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
       </x:c>
       <x:c r="F216" s="127" t="str">
         <x:v>P0</x:v>
@@ -17685,7 +17691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K216" s="127"/>
       <x:c r="L216" s="127"/>
@@ -17695,19 +17701,19 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="127" t="str">
-        <x:v>R-213</x:v>
+        <x:v>R-212</x:v>
       </x:c>
       <x:c r="B217" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C217" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D217" s="127" t="str">
-        <x:v>MCP isolation and prompt-injection test</x:v>
+        <x:v>WebSocket replay correctness SLO</x:v>
       </x:c>
       <x:c r="E217" s="127" t="str">
-        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
+        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
       </x:c>
       <x:c r="F217" s="127" t="str">
         <x:v>P0</x:v>
@@ -17721,7 +17727,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="K217" s="127"/>
       <x:c r="L217" s="127"/>
@@ -17731,7 +17737,7 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="127" t="str">
-        <x:v>R-214</x:v>
+        <x:v>R-213</x:v>
       </x:c>
       <x:c r="B218" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17740,10 +17746,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D218" s="127" t="str">
-        <x:v>Sandbox tenant isolation test</x:v>
+        <x:v>MCP isolation and prompt-injection test</x:v>
       </x:c>
       <x:c r="E218" s="127" t="str">
-        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
+        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
       </x:c>
       <x:c r="F218" s="127" t="str">
         <x:v>P0</x:v>
@@ -17757,7 +17763,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K218" s="127"/>
       <x:c r="L218" s="127"/>
@@ -17767,19 +17773,19 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="127" t="str">
-        <x:v>R-215</x:v>
+        <x:v>R-214</x:v>
       </x:c>
       <x:c r="B219" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C219" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D219" s="127" t="str">
-        <x:v>Runtime provider outage failover</x:v>
+        <x:v>Sandbox tenant isolation test</x:v>
       </x:c>
       <x:c r="E219" s="127" t="str">
-        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
+        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
       </x:c>
       <x:c r="F219" s="127" t="str">
         <x:v>P0</x:v>
@@ -17793,7 +17799,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K219" s="127"/>
       <x:c r="L219" s="127"/>
@@ -17803,19 +17809,19 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="127" t="str">
-        <x:v>R-216</x:v>
+        <x:v>R-215</x:v>
       </x:c>
       <x:c r="B220" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C220" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D220" s="127" t="str">
-        <x:v>Approval auditability test</x:v>
+        <x:v>Runtime provider outage failover</x:v>
       </x:c>
       <x:c r="E220" s="127" t="str">
-        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
+        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
       </x:c>
       <x:c r="F220" s="127" t="str">
         <x:v>P0</x:v>
@@ -17829,7 +17835,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="K220" s="127"/>
       <x:c r="L220" s="127"/>
@@ -17839,22 +17845,22 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="127" t="str">
-        <x:v>R-217</x:v>
+        <x:v>R-216</x:v>
       </x:c>
       <x:c r="B221" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C221" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D221" s="127" t="str">
-        <x:v>BaaS to custom migration test</x:v>
+        <x:v>Approval auditability test</x:v>
       </x:c>
       <x:c r="E221" s="127" t="str">
-        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
       </x:c>
       <x:c r="F221" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G221" s="127"/>
       <x:c r="H221" s="127" t="str">
@@ -17865,32 +17871,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K221" s="127"/>
       <x:c r="L221" s="127"/>
       <x:c r="M221" s="127" t="str">
-        <x:v>Avoid backend lock-in.</x:v>
+        <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="127" t="str">
-        <x:v>R-218</x:v>
+        <x:v>R-217</x:v>
       </x:c>
       <x:c r="B222" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C222" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D222" s="127" t="str">
-        <x:v>Local Agent security lifecycle</x:v>
+        <x:v>BaaS to custom migration test</x:v>
       </x:c>
       <x:c r="E222" s="127" t="str">
-        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
+        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
       </x:c>
       <x:c r="F222" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G222" s="127"/>
       <x:c r="H222" s="127" t="str">
@@ -17901,29 +17907,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="K222" s="127"/>
       <x:c r="L222" s="127"/>
       <x:c r="M222" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Avoid backend lock-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" t="str">
-        <x:v>R-219</x:v>
+        <x:v>R-218</x:v>
       </x:c>
       <x:c r="B223" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C223" t="str">
-        <x:v>Compliance</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D223" t="str">
-        <x:v>OSS license and SBOM gate</x:v>
+        <x:v>Local Agent security lifecycle</x:v>
       </x:c>
       <x:c r="E223" t="str">
-        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
       </x:c>
       <x:c r="F223" t="str">
         <x:v>P0</x:v>
@@ -17937,11 +17943,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K223"/>
       <x:c r="L223"/>
       <x:c r="M223" t="str">
+        <x:v>Production gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" t="str">
+        <x:v>R-219</x:v>
+      </x:c>
+      <x:c r="B224" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>Compliance</x:v>
+      </x:c>
+      <x:c r="D224" t="str">
+        <x:v>OSS license and SBOM gate</x:v>
+      </x:c>
+      <x:c r="E224" t="str">
+        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+      </x:c>
+      <x:c r="F224" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G224"/>
+      <x:c r="H224" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="I224" t="n">
+        <x:f>IF(H224="Done",1,IF(H224="In Progress",0.5,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J224" t="str">
+        <x:v>Open-source license review</x:v>
+      </x:c>
+      <x:c r="K224"/>
+      <x:c r="L224"/>
+      <x:c r="M224" t="str">
         <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
@@ -17998,7 +18040,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fdf58ba6b6400d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f3baf1db734685"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2,68 +2,68 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8f03f928e9ba40d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="Rb92228bb2ea645ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Re535e91e3cc34259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R822174bfda8745fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="R2ac6ab7ab81b4289"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="R1ad22d7cf2f34458"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="Rfa6fde6cb7a145f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="R5df1b92fc1164dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="R6aeab484d2e74963"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R4aad5bc894b34909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="Radec3e9ebc604ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R19d4c8ad021840c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Ra624480c3972480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R4098bcc395dc405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="R21c1fc4892994710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="Re1f0f06e306e4d38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="R7c391ea780614ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="Rf28ebb8ed52d4334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rd79a85621a8a4dab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R1f38e2b48a9a413e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="Rb1775eb2cec34d2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Re518c3dc672c48a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="R69a3d106ec8e46ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="Raa6fab16bf9f4fa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="Rc3a3a2877e5b40c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R4478a8d596dd4182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="Rb07c64ae7c6a4e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="Rbf3491ad6f584b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Ra8a68b8657ea4804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R5d29fd2913c94199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Re516337aabee4920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R3a312b29ccd445e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R5b394eee0f5c449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R4ac34d5fa4f24ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="Rb3cb9f5d12b347bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R93cd1352d2dc4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="Re46d1d63834b4f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="Red5789bbba1a4ddb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="Rc0ddc73b071d44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R0782e6079c7a478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R55cd8a9925994ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Rce8d44d0bad54f63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R58f1f2aebcdd4e63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="R11f13a1b1233489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="R5d4c79a934d042af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="Rc6e3d3915aa54d38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="Ra07966c5bdb14e3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rcb3a6401d85d4d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="R96afb7f00bb64d97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R1218e8c40c8d406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="R59bcf14944f54e24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="R47c937dbff8248cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Raf27715a6ae349b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="Reb29ca4326794f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="Rfad5282bea2b484c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="R75e8c81fa61f4f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="R82cf9543823848b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R96e00af2a7cf49ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R7420459d16464482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="Rc9d477b006074375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R5f6238433f4c46b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="R57eae45e4b4c4542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdd47f631d76f4f1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase_Roadmap" sheetId="2" r:id="R6659c2c1e684476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_UI_Tabs" sheetId="3" r:id="Rade5cf8d8b8c40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Architecture" sheetId="4" r:id="R47fcccdd55294144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Application_IR" sheetId="5" r:id="Rf8da5ff482cc4570"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change_Impact" sheetId="6" r:id="Rf36c0fc8972b4284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Build_Matrix" sheetId="7" r:id="R594a4884eff04ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testing_Quality" sheetId="8" r:id="Re8e7364a3dc6418e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security" sheetId="9" r:id="Rbee1c0d403664a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="10" r:id="R7b8fd3bf4f8e4bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Costs" sheetId="11" r:id="R8a4be8acf5da489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analytics_KPIs" sheetId="12" r:id="R676b5de3731c4b00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks_Competitor" sheetId="13" r:id="Ra7a7067d28594475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production_Gates" sheetId="14" r:id="R87598fa7c6e64ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="15" r:id="Rc514f98e78b54a12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Selection" sheetId="16" r:id="Re98f4d4cdb144b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework_Decision" sheetId="17" r:id="Rc1c9ae362a1a49b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repo_Architecture" sheetId="18" r:id="R2f31ab4a8b554852"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Structure" sheetId="19" r:id="Rd0da59769fe948a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack_Profiles" sheetId="20" r:id="R8d34430268224808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Code_Sharing" sheetId="21" r:id="R5eeefb5b179942b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform_Architecture" sheetId="22" r:id="Rb59729cc4aae4f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Git_Standards" sheetId="23" r:id="Rfc1d30cc496a45a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flutter_Template" sheetId="24" r:id="R58a6840c83394cbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactNative_Template" sheetId="25" r:id="R66783a4fe9744e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Android_Template" sheetId="26" r:id="R17ffc502c10a483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="iOS_Template" sheetId="27" r:id="R85a624b83eeb4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web_Template" sheetId="28" r:id="R97bc7939659947aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin_Template" sheetId="29" r:id="Ra3f48405b225477c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Templates" sheetId="30" r:id="R85dfdb6f1c874061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CI_CD" sheetId="31" r:id="Rd61ad5399f3b459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration_Paths" sheetId="32" r:id="R55e3ca6af5384808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template_Governance" sheetId="33" r:id="R38946782d4c241a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Study" sheetId="34" r:id="R46d33a3983954ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime_Tiers" sheetId="35" r:id="R2cd8c72b11ba4411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Durable_Agent_Runtime" sheetId="36" r:id="R20c487f1de5d4250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCP_Tool_Registry" sheetId="37" r:id="R7fb0b2ed173a48c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HITL_Approvals" sheetId="38" r:id="R4a6ecba061314228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution_Modes" sheetId="39" r:id="R5e44dd48774f43f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backend_Profiles" sheetId="40" r:id="R3dbfa3e7b92c4d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent_Streaming" sheetId="41" r:id="R8d8418c37f9b4cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture_Research" sheetId="42" r:id="Re2cc9d491322436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Glossary" sheetId="43" r:id="R05eb3f6114764ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand_Naming" sheetId="44" r:id="Rcbd0d9f7a92c4017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preview_Verification" sheetId="45" r:id="Re36649bff8de4dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Device_QR_Delivery" sheetId="46" r:id="R8f62d288f1304c23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Context_Engine" sheetId="47" r:id="R510921099b754637"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Memory" sheetId="48" r:id="Rd09153d947344a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LLM_Cost_Optimization" sheetId="49" r:id="Re2cb193628414591"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Database_Strategy" sheetId="50" r:id="R6aaeb7f342b64683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incident_Bug_Flow" sheetId="51" r:id="Rf7672bb4f89e4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor_Matrix" sheetId="52" r:id="Rf828f2bc51d74e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client_Handover" sheetId="53" r:id="Ra528ed05e55447c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publishing_Release" sheetId="54" r:id="R1883f721a0504c22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="55" r:id="R43bfe94ed6c34fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider_Interfaces" sheetId="56" r:id="Rf02ce2f567904d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supply_Chain" sheetId="57" r:id="Rb8e4e43a80c14f67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RND_Gap_Audit" sheetId="58" r:id="R3d1103fab0c74f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Local_LLM_Providers" sheetId="59" r:id="R9370d9fb8c90421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_Developer_Handoff" sheetId="60" r:id="R9422248acb1f4058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment_Matrix" sheetId="61" r:id="R006ff08d348c4e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Capability_Registry" sheetId="62" r:id="Rce44d0fcf7c74d18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2379,7 +2379,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d7e437deed84762"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6eca6997bd0b46f2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2706,11 +2706,11 @@
       </x:c>
       <x:c r="C5" s="32" t="n">
         <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"MVP",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
         <x:f>IF(B5=0,0,C5/B5)</x:f>
-        <x:v>0.04504504504504504</x:v>
+        <x:v>0.05405405405405406</x:v>
       </x:c>
       <x:c r="F5" s="32" t="inlineStr">
         <x:is>
@@ -2747,7 +2747,7 @@
       </x:c>
       <x:c r="G6" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F6)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2803,7 +2803,7 @@
       </x:c>
       <x:c r="G8" s="32" t="n">
         <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F8)</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3972,7 +3972,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dad15da017348e8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fb82ea71d4f4f7b"/>
 </x:worksheet>
 </file>
 
@@ -10662,11 +10662,11 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-005</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Task contract recorded; baseline task verify passed; local_calls=1 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
@@ -18040,7 +18040,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f3baf1db734685"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8d3181bed244ca5"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2389,7 +2389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M113" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -2701,11 +2701,11 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"MVP")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"MVP")</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"MVP",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"MVP",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"MID",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"MID",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,7 +2746,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F6)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"ADVANCED",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"ADVANCED",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$224,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$224,"PRODUCTION",Phase_Roadmap!$H$4:$H$224,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"PRODUCTION",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F8)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$224,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -10641,7 +10641,7 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10650,40 +10650,40 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Loopback Ollama provider adapter</x:v>
+        <x:v>Balanced Model Gateway router</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
+        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G9" s="32" t="str">
-        <x:v>Codex</x:v>
+        <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
+        <x:v>Implementation in progress on ai/R-007-balanced-model-gateway; deterministic Balanced router and 14 offline gateway tests added; local_calls=0, cloud_calls=0.</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10692,10 +10692,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
@@ -10711,33 +10711,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C11" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
@@ -10753,33 +10753,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
@@ -10795,33 +10795,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
@@ -10837,33 +10837,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
@@ -10879,53 +10879,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K14" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L14" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M14" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C15" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G15" s="32"/>
+      <x:c r="G15" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H15" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I15" s="376" t="n">
         <x:f>IF(H15="Done",1,IF(H15="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="32"/>
-      <x:c r="K15" s="32"/>
-      <x:c r="L15" s="32"/>
-      <x:c r="M15" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K15" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L15" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M15" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10934,10 +10944,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
@@ -10957,7 +10967,7 @@
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10966,10 +10976,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
@@ -10989,7 +10999,7 @@
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10998,10 +11008,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
@@ -11021,7 +11031,7 @@
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11030,10 +11040,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
@@ -11053,7 +11063,7 @@
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11062,10 +11072,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
@@ -11085,19 +11095,19 @@
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C21" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11117,7 +11127,7 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11126,10 +11136,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11149,19 +11159,19 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C23" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11181,7 +11191,7 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11190,10 +11200,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11213,19 +11223,19 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C25" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11245,19 +11255,19 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C26" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11277,7 +11287,7 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11286,10 +11296,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11309,19 +11319,19 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C28" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11341,7 +11351,7 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11350,10 +11360,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11373,7 +11383,7 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11382,10 +11392,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11405,19 +11415,19 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C31" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11437,7 +11447,7 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11446,10 +11456,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11469,7 +11479,7 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11478,10 +11488,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11501,7 +11511,7 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11510,10 +11520,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11533,7 +11543,7 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11542,10 +11552,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11565,19 +11575,19 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C36" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11597,7 +11607,7 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11606,10 +11616,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11629,19 +11639,19 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C38" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11661,7 +11671,7 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11670,10 +11680,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11693,19 +11703,19 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C40" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11725,19 +11735,19 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C41" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11757,19 +11767,19 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C42" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11789,7 +11799,7 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11798,10 +11808,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11821,7 +11831,7 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11830,10 +11840,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11853,7 +11863,7 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11862,10 +11872,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11885,19 +11895,19 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C46" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11917,7 +11927,7 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11926,10 +11936,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11949,19 +11959,19 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C48" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -11981,7 +11991,7 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11990,10 +12000,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12013,19 +12023,19 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C50" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12045,7 +12055,7 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12054,10 +12064,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12077,7 +12087,7 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12086,10 +12096,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12109,19 +12119,19 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C53" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12141,7 +12151,7 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12150,10 +12160,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12173,7 +12183,7 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12182,10 +12192,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12205,19 +12215,19 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C56" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
         <x:v>P0</x:v>
@@ -12237,22 +12247,22 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C57" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G57" s="32"/>
       <x:c r="H57" s="32" t="str">
@@ -12269,7 +12279,7 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
         <x:v>MID</x:v>
@@ -12278,10 +12288,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
         <x:v>P1</x:v>
@@ -12301,19 +12311,19 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C59" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
         <x:v>P1</x:v>
@@ -12333,19 +12343,19 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C60" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
         <x:v>P1</x:v>
@@ -12365,7 +12375,7 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
         <x:v>MID</x:v>
@@ -12374,10 +12384,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
         <x:v>P1</x:v>
@@ -12397,19 +12407,19 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C62" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
         <x:v>P1</x:v>
@@ -12429,19 +12439,19 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C63" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12461,19 +12471,19 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C64" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12493,7 +12503,7 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
@@ -12502,10 +12512,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12525,19 +12535,19 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C66" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12557,7 +12567,7 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
@@ -12566,10 +12576,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12589,7 +12599,7 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
@@ -12598,10 +12608,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12621,19 +12631,19 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C69" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12653,7 +12663,7 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
@@ -12662,10 +12672,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12685,19 +12695,19 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C71" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12717,19 +12727,19 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C72" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12749,19 +12759,19 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C73" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12781,19 +12791,19 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C74" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12813,7 +12823,7 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
@@ -12822,10 +12832,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12845,7 +12855,7 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
@@ -12854,10 +12864,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12877,19 +12887,19 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C77" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12909,7 +12919,7 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
@@ -12918,10 +12928,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12941,19 +12951,19 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C79" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -12973,19 +12983,19 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C80" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -13005,19 +13015,19 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C81" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
         <x:v>P1</x:v>
@@ -13037,22 +13047,22 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C82" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G82" s="32"/>
       <x:c r="H82" s="32" t="str">
@@ -13069,7 +13079,7 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13078,13 +13088,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G83" s="32"/>
       <x:c r="H83" s="32" t="str">
@@ -13101,22 +13111,22 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C84" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G84" s="32"/>
       <x:c r="H84" s="32" t="str">
@@ -13133,7 +13143,7 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13142,10 +13152,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
         <x:v>P2</x:v>
@@ -13165,19 +13175,19 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C86" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
         <x:v>P2</x:v>
@@ -13197,19 +13207,19 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C87" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
         <x:v>P2</x:v>
@@ -13229,19 +13239,19 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C88" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
         <x:v>P2</x:v>
@@ -13261,7 +13271,7 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13270,10 +13280,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
         <x:v>P2</x:v>
@@ -13293,19 +13303,19 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C90" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13325,7 +13335,7 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13334,10 +13344,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13357,7 +13367,7 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13366,10 +13376,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13389,19 +13399,19 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C93" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13421,7 +13431,7 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13430,10 +13440,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13453,19 +13463,19 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C95" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13485,19 +13495,19 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C96" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13517,7 +13527,7 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13526,10 +13536,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13549,19 +13559,19 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-093</x:v>
+        <x:v>R-092</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C98" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Quality trend analytics</x:v>
+        <x:v>Spot/preemptible optimization</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
+        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
         <x:v>P2</x:v>
@@ -13581,22 +13591,22 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-094</x:v>
+        <x:v>R-093</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C99" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>SLO/SLA framework</x:v>
+        <x:v>Quality trend analytics</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
+        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G99" s="32"/>
       <x:c r="H99" s="32" t="str">
@@ -13613,7 +13623,7 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-095</x:v>
+        <x:v>R-094</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13622,10 +13632,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>HA control plane</x:v>
+        <x:v>SLO/SLA framework</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
+        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
         <x:v>P0</x:v>
@@ -13645,7 +13655,7 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-096</x:v>
+        <x:v>R-095</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13654,10 +13664,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>Backup + restore drills</x:v>
+        <x:v>HA control plane</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Automated backups plus regularly tested restoration.</x:v>
+        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
         <x:v>P0</x:v>
@@ -13677,7 +13687,7 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-097</x:v>
+        <x:v>R-096</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13686,10 +13696,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>Disaster recovery</x:v>
+        <x:v>Backup + restore drills</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>Document and exercise regional recovery procedures.</x:v>
+        <x:v>Automated backups plus regularly tested restoration.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
         <x:v>P0</x:v>
@@ -13709,19 +13719,19 @@
     </x:row>
     <x:row r="103" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A103" s="32" t="str">
-        <x:v>R-098</x:v>
+        <x:v>R-097</x:v>
       </x:c>
       <x:c r="B103" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C103" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D103" s="32" t="str">
-        <x:v>Independent penetration test</x:v>
+        <x:v>Disaster recovery</x:v>
       </x:c>
       <x:c r="E103" s="32" t="str">
-        <x:v>External security assessment before broad enterprise launch.</x:v>
+        <x:v>Document and exercise regional recovery procedures.</x:v>
       </x:c>
       <x:c r="F103" s="32" t="str">
         <x:v>P0</x:v>
@@ -13741,7 +13751,7 @@
     </x:row>
     <x:row r="104" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A104" s="32" t="str">
-        <x:v>R-099</x:v>
+        <x:v>R-098</x:v>
       </x:c>
       <x:c r="B104" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13750,10 +13760,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D104" s="32" t="str">
-        <x:v>SOC 2 readiness controls</x:v>
+        <x:v>Independent penetration test</x:v>
       </x:c>
       <x:c r="E104" s="32" t="str">
-        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
+        <x:v>External security assessment before broad enterprise launch.</x:v>
       </x:c>
       <x:c r="F104" s="32" t="str">
         <x:v>P0</x:v>
@@ -13773,7 +13783,7 @@
     </x:row>
     <x:row r="105" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A105" s="32" t="str">
-        <x:v>R-100</x:v>
+        <x:v>R-099</x:v>
       </x:c>
       <x:c r="B105" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13782,10 +13792,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D105" s="32" t="str">
-        <x:v>Tenant isolation validation</x:v>
+        <x:v>SOC 2 readiness controls</x:v>
       </x:c>
       <x:c r="E105" s="32" t="str">
-        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
+        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
       </x:c>
       <x:c r="F105" s="32" t="str">
         <x:v>P0</x:v>
@@ -13805,7 +13815,7 @@
     </x:row>
     <x:row r="106" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A106" s="32" t="str">
-        <x:v>R-101</x:v>
+        <x:v>R-100</x:v>
       </x:c>
       <x:c r="B106" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13814,10 +13824,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D106" s="32" t="str">
-        <x:v>Signing-key hardening</x:v>
+        <x:v>Tenant isolation validation</x:v>
       </x:c>
       <x:c r="E106" s="32" t="str">
-        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
+        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
       </x:c>
       <x:c r="F106" s="32" t="str">
         <x:v>P0</x:v>
@@ -13837,19 +13847,19 @@
     </x:row>
     <x:row r="107" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A107" s="32" t="str">
-        <x:v>R-102</x:v>
+        <x:v>R-101</x:v>
       </x:c>
       <x:c r="B107" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C107" s="32" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>24x7 incident process</x:v>
+        <x:v>Signing-key hardening</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
-        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
+        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
       </x:c>
       <x:c r="F107" s="32" t="str">
         <x:v>P0</x:v>
@@ -13869,7 +13879,7 @@
     </x:row>
     <x:row r="108" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A108" s="32" t="str">
-        <x:v>R-103</x:v>
+        <x:v>R-102</x:v>
       </x:c>
       <x:c r="B108" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13878,10 +13888,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>Capacity/load tests</x:v>
+        <x:v>24x7 incident process</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
-        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
+        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
       </x:c>
       <x:c r="F108" s="32" t="str">
         <x:v>P0</x:v>
@@ -13901,7 +13911,7 @@
     </x:row>
     <x:row r="109" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A109" s="32" t="str">
-        <x:v>R-104</x:v>
+        <x:v>R-103</x:v>
       </x:c>
       <x:c r="B109" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13910,10 +13920,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>Cost guardrails</x:v>
+        <x:v>Capacity/load tests</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
-        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
+        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
       </x:c>
       <x:c r="F109" s="32" t="str">
         <x:v>P0</x:v>
@@ -13933,19 +13943,19 @@
     </x:row>
     <x:row r="110" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A110" s="32" t="str">
-        <x:v>R-105</x:v>
+        <x:v>R-104</x:v>
       </x:c>
       <x:c r="B110" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C110" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>Release qualification suite</x:v>
+        <x:v>Cost guardrails</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
-        <x:v>Full regression across supported stack versions before platform releases.</x:v>
+        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
       </x:c>
       <x:c r="F110" s="32" t="str">
         <x:v>P0</x:v>
@@ -13965,7 +13975,7 @@
     </x:row>
     <x:row r="111" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A111" s="32" t="str">
-        <x:v>R-106</x:v>
+        <x:v>R-105</x:v>
       </x:c>
       <x:c r="B111" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13974,10 +13984,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>Canary platform releases</x:v>
+        <x:v>Release qualification suite</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
-        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
+        <x:v>Full regression across supported stack versions before platform releases.</x:v>
       </x:c>
       <x:c r="F111" s="32" t="str">
         <x:v>P0</x:v>
@@ -13997,19 +14007,19 @@
     </x:row>
     <x:row r="112" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A112" s="32" t="str">
-        <x:v>R-107</x:v>
+        <x:v>R-106</x:v>
       </x:c>
       <x:c r="B112" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C112" s="32" t="str">
-        <x:v>Support</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Support tooling</x:v>
+        <x:v>Canary platform releases</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
+        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
         <x:v>P0</x:v>
@@ -14029,19 +14039,19 @@
     </x:row>
     <x:row r="113" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A113" s="32" t="str">
-        <x:v>R-108</x:v>
+        <x:v>R-107</x:v>
       </x:c>
       <x:c r="B113" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C113" s="32" t="str">
-        <x:v>Legal/Privacy</x:v>
+        <x:v>Support</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Privacy + retention controls</x:v>
+        <x:v>Support tooling</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
         <x:v>P0</x:v>
@@ -14059,2154 +14069,2152 @@
       <x:c r="L113" s="32"/>
       <x:c r="M113" s="32"/>
     </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="43" t="str">
-        <x:v>R-109</x:v>
-      </x:c>
-      <x:c r="B114" s="43" t="str">
+    <x:row r="114" s="40" customFormat="1" ht="34" customHeight="1">
+      <x:c r="A114" s="32" t="str">
+        <x:v>R-108</x:v>
+      </x:c>
+      <x:c r="B114" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C114" s="43" t="str">
-        <x:v>Business</x:v>
-      </x:c>
-      <x:c r="D114" s="43" t="str">
-        <x:v>Plan entitlements</x:v>
-      </x:c>
-      <x:c r="E114" s="43" t="str">
-        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
-      </x:c>
-      <x:c r="F114" s="43" t="str">
+      <x:c r="C114" s="32" t="str">
+        <x:v>Legal/Privacy</x:v>
+      </x:c>
+      <x:c r="D114" s="32" t="str">
+        <x:v>Privacy + retention controls</x:v>
+      </x:c>
+      <x:c r="E114" s="32" t="str">
+        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+      </x:c>
+      <x:c r="F114" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G114" s="43"/>
-      <x:c r="H114" s="43" t="str">
+      <x:c r="G114" s="32"/>
+      <x:c r="H114" s="32" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I114" s="386" t="n">
+      <x:c r="I114" s="376" t="n">
         <x:f>IF(H114="Done",1,IF(H114="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J114" s="43"/>
-      <x:c r="K114" s="43"/>
-      <x:c r="L114" s="43"/>
-      <x:c r="M114" s="43"/>
+      <x:c r="J114" s="32"/>
+      <x:c r="K114" s="32"/>
+      <x:c r="L114" s="32"/>
+      <x:c r="M114" s="32"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="42" t="str">
-        <x:v>R-110</x:v>
-      </x:c>
-      <x:c r="B115" s="42" t="str">
+      <x:c r="A115" s="43" t="str">
+        <x:v>R-109</x:v>
+      </x:c>
+      <x:c r="B115" s="43" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C115" s="42" t="str">
+      <x:c r="C115" s="43" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="D115" s="42" t="str">
-        <x:v>Unit economics dashboard</x:v>
-      </x:c>
-      <x:c r="E115" s="42" t="str">
-        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
-      </x:c>
-      <x:c r="F115" s="42" t="str">
+      <x:c r="D115" s="43" t="str">
+        <x:v>Plan entitlements</x:v>
+      </x:c>
+      <x:c r="E115" s="43" t="str">
+        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
+      </x:c>
+      <x:c r="F115" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G115" s="42"/>
-      <x:c r="H115" s="42" t="str">
+      <x:c r="G115" s="43"/>
+      <x:c r="H115" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I115" s="387" t="n">
+      <x:c r="I115" s="386" t="n">
         <x:f>IF(H115="Done",1,IF(H115="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J115" s="42"/>
-      <x:c r="K115" s="42"/>
-      <x:c r="L115" s="42"/>
-      <x:c r="M115" s="42"/>
+      <x:c r="J115" s="43"/>
+      <x:c r="K115" s="43"/>
+      <x:c r="L115" s="43"/>
+      <x:c r="M115" s="43"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="43" t="str">
-        <x:v>R-111</x:v>
-      </x:c>
-      <x:c r="B116" s="43" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C116" s="43" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D116" s="43" t="str">
-        <x:v>Cross-platform Mobile Agent</x:v>
-      </x:c>
-      <x:c r="E116" s="43" t="str">
-        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
-      </x:c>
-      <x:c r="F116" s="43" t="str">
+      <x:c r="A116" s="42" t="str">
+        <x:v>R-110</x:v>
+      </x:c>
+      <x:c r="B116" s="42" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C116" s="42" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="D116" s="42" t="str">
+        <x:v>Unit economics dashboard</x:v>
+      </x:c>
+      <x:c r="E116" s="42" t="str">
+        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
+      </x:c>
+      <x:c r="F116" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G116" s="43"/>
-      <x:c r="H116" s="43" t="str">
+      <x:c r="G116" s="42"/>
+      <x:c r="H116" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I116" s="386" t="n">
+      <x:c r="I116" s="387" t="n">
         <x:f>IF(H116="Done",1,IF(H116="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J116" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K116" s="43"/>
-      <x:c r="L116" s="43"/>
-      <x:c r="M116" s="43"/>
+      <x:c r="J116" s="42"/>
+      <x:c r="K116" s="42"/>
+      <x:c r="L116" s="42"/>
+      <x:c r="M116" s="42"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="42" t="str">
-        <x:v>R-112</x:v>
-      </x:c>
-      <x:c r="B117" s="42" t="str">
+      <x:c r="A117" s="43" t="str">
+        <x:v>R-111</x:v>
+      </x:c>
+      <x:c r="B117" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C117" s="42" t="str">
+      <x:c r="C117" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D117" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="E117" s="42" t="str">
-        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
-      </x:c>
-      <x:c r="F117" s="42" t="str">
+      <x:c r="D117" s="43" t="str">
+        <x:v>Cross-platform Mobile Agent</x:v>
+      </x:c>
+      <x:c r="E117" s="43" t="str">
+        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
+      </x:c>
+      <x:c r="F117" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G117" s="42"/>
-      <x:c r="H117" s="42" t="str">
+      <x:c r="G117" s="43"/>
+      <x:c r="H117" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I117" s="387" t="n">
+      <x:c r="I117" s="386" t="n">
         <x:f>IF(H117="Done",1,IF(H117="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J117" s="42" t="str">
-        <x:v>Requirement specification step</x:v>
-      </x:c>
-      <x:c r="K117" s="42"/>
-      <x:c r="L117" s="42"/>
-      <x:c r="M117" s="42"/>
+      <x:c r="J117" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K117" s="43"/>
+      <x:c r="L117" s="43"/>
+      <x:c r="M117" s="43"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="43" t="str">
-        <x:v>R-113</x:v>
-      </x:c>
-      <x:c r="B118" s="43" t="str">
+      <x:c r="A118" s="42" t="str">
+        <x:v>R-112</x:v>
+      </x:c>
+      <x:c r="B118" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C118" s="43" t="str">
+      <x:c r="C118" s="42" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D118" s="43" t="str">
-        <x:v>Auto / Recommended project mode</x:v>
-      </x:c>
-      <x:c r="E118" s="43" t="str">
-        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
-      </x:c>
-      <x:c r="F118" s="43" t="str">
+      <x:c r="D118" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="E118" s="42" t="str">
+        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
+      </x:c>
+      <x:c r="F118" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G118" s="43"/>
-      <x:c r="H118" s="43" t="str">
+      <x:c r="G118" s="42"/>
+      <x:c r="H118" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I118" s="386" t="n">
+      <x:c r="I118" s="387" t="n">
         <x:f>IF(H118="Done",1,IF(H118="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J118" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K118" s="43"/>
-      <x:c r="L118" s="43"/>
-      <x:c r="M118" s="43"/>
+      <x:c r="J118" s="42" t="str">
+        <x:v>Requirement specification step</x:v>
+      </x:c>
+      <x:c r="K118" s="42"/>
+      <x:c r="L118" s="42"/>
+      <x:c r="M118" s="42"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="42" t="str">
-        <x:v>R-114</x:v>
-      </x:c>
-      <x:c r="B119" s="42" t="str">
+      <x:c r="A119" s="43" t="str">
+        <x:v>R-113</x:v>
+      </x:c>
+      <x:c r="B119" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C119" s="42" t="str">
+      <x:c r="C119" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D119" s="42" t="str">
-        <x:v>Manual framework override</x:v>
-      </x:c>
-      <x:c r="E119" s="42" t="str">
-        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
-      </x:c>
-      <x:c r="F119" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G119" s="42"/>
-      <x:c r="H119" s="42" t="str">
+      <x:c r="D119" s="43" t="str">
+        <x:v>Auto / Recommended project mode</x:v>
+      </x:c>
+      <x:c r="E119" s="43" t="str">
+        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
+      </x:c>
+      <x:c r="F119" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G119" s="43"/>
+      <x:c r="H119" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I119" s="387" t="n">
+      <x:c r="I119" s="386" t="n">
         <x:f>IF(H119="Done",1,IF(H119="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J119" s="42" t="str">
+      <x:c r="J119" s="43" t="str">
         <x:v>Framework recommendation engine</x:v>
       </x:c>
-      <x:c r="K119" s="42"/>
-      <x:c r="L119" s="42"/>
-      <x:c r="M119" s="42"/>
+      <x:c r="K119" s="43"/>
+      <x:c r="L119" s="43"/>
+      <x:c r="M119" s="43"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="43" t="str">
-        <x:v>R-115</x:v>
-      </x:c>
-      <x:c r="B120" s="43" t="str">
+      <x:c r="A120" s="42" t="str">
+        <x:v>R-114</x:v>
+      </x:c>
+      <x:c r="B120" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C120" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D120" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="E120" s="43" t="str">
-        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
-      </x:c>
-      <x:c r="F120" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G120" s="43"/>
-      <x:c r="H120" s="43" t="str">
+      <x:c r="C120" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D120" s="42" t="str">
+        <x:v>Manual framework override</x:v>
+      </x:c>
+      <x:c r="E120" s="42" t="str">
+        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
+      </x:c>
+      <x:c r="F120" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G120" s="42"/>
+      <x:c r="H120" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I120" s="386" t="n">
+      <x:c r="I120" s="387" t="n">
         <x:f>IF(H120="Done",1,IF(H120="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K120" s="43"/>
-      <x:c r="L120" s="43"/>
-      <x:c r="M120" s="43"/>
+      <x:c r="J120" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K120" s="42"/>
+      <x:c r="L120" s="42"/>
+      <x:c r="M120" s="42"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="42" t="str">
-        <x:v>R-116</x:v>
-      </x:c>
-      <x:c r="B121" s="42" t="str">
+      <x:c r="A121" s="43" t="str">
+        <x:v>R-115</x:v>
+      </x:c>
+      <x:c r="B121" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C121" s="42" t="str">
+      <x:c r="C121" s="43" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D121" s="42" t="str">
-        <x:v>Shared-code policy</x:v>
-      </x:c>
-      <x:c r="E121" s="42" t="str">
-        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
-      </x:c>
-      <x:c r="F121" s="42" t="str">
+      <x:c r="D121" s="43" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="E121" s="43" t="str">
+        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
+      </x:c>
+      <x:c r="F121" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G121" s="42"/>
-      <x:c r="H121" s="42" t="str">
+      <x:c r="G121" s="43"/>
+      <x:c r="H121" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I121" s="387" t="n">
+      <x:c r="I121" s="386" t="n">
         <x:f>IF(H121="Done",1,IF(H121="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K121" s="42"/>
-      <x:c r="L121" s="42"/>
-      <x:c r="M121" s="42"/>
+      <x:c r="J121" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K121" s="43"/>
+      <x:c r="L121" s="43"/>
+      <x:c r="M121" s="43"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="43" t="str">
-        <x:v>R-117</x:v>
-      </x:c>
-      <x:c r="B122" s="43" t="str">
+      <x:c r="A122" s="42" t="str">
+        <x:v>R-116</x:v>
+      </x:c>
+      <x:c r="B122" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C122" s="43" t="str">
-        <x:v>Web/Admin</x:v>
-      </x:c>
-      <x:c r="D122" s="43" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="E122" s="43" t="str">
-        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
-      </x:c>
-      <x:c r="F122" s="43" t="str">
+      <x:c r="C122" s="42" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D122" s="42" t="str">
+        <x:v>Shared-code policy</x:v>
+      </x:c>
+      <x:c r="E122" s="42" t="str">
+        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
+      </x:c>
+      <x:c r="F122" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G122" s="43"/>
-      <x:c r="H122" s="43" t="str">
+      <x:c r="G122" s="42"/>
+      <x:c r="H122" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I122" s="386" t="n">
+      <x:c r="I122" s="387" t="n">
         <x:f>IF(H122="Done",1,IF(H122="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="43" t="str">
-        <x:v>Web/Admin Agent</x:v>
-      </x:c>
-      <x:c r="K122" s="43"/>
-      <x:c r="L122" s="43"/>
-      <x:c r="M122" s="43"/>
+      <x:c r="J122" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K122" s="42"/>
+      <x:c r="L122" s="42"/>
+      <x:c r="M122" s="42"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="42" t="str">
-        <x:v>R-118</x:v>
-      </x:c>
-      <x:c r="B123" s="42" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C123" s="42" t="str">
+      <x:c r="A123" s="43" t="str">
+        <x:v>R-117</x:v>
+      </x:c>
+      <x:c r="B123" s="43" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C123" s="43" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D123" s="42" t="str">
-        <x:v>Flutter Web optional profile</x:v>
-      </x:c>
-      <x:c r="E123" s="42" t="str">
-        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
-      </x:c>
-      <x:c r="F123" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G123" s="42"/>
-      <x:c r="H123" s="42" t="str">
+      <x:c r="D123" s="43" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="E123" s="43" t="str">
+        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
+      </x:c>
+      <x:c r="F123" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G123" s="43"/>
+      <x:c r="H123" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I123" s="387" t="n">
+      <x:c r="I123" s="386" t="n">
         <x:f>IF(H123="Done",1,IF(H123="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J123" s="42" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
-      </x:c>
-      <x:c r="K123" s="42"/>
-      <x:c r="L123" s="42"/>
-      <x:c r="M123" s="42"/>
+      <x:c r="J123" s="43" t="str">
+        <x:v>Web/Admin Agent</x:v>
+      </x:c>
+      <x:c r="K123" s="43"/>
+      <x:c r="L123" s="43"/>
+      <x:c r="M123" s="43"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="43" t="str">
-        <x:v>R-119</x:v>
-      </x:c>
-      <x:c r="B124" s="43" t="str">
+      <x:c r="A124" s="42" t="str">
+        <x:v>R-118</x:v>
+      </x:c>
+      <x:c r="B124" s="42" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C124" s="43" t="str">
+      <x:c r="C124" s="42" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D124" s="43" t="str">
-        <x:v>React Native Web optional profile</x:v>
-      </x:c>
-      <x:c r="E124" s="43" t="str">
-        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
-      </x:c>
-      <x:c r="F124" s="43" t="str">
+      <x:c r="D124" s="42" t="str">
+        <x:v>Flutter Web optional profile</x:v>
+      </x:c>
+      <x:c r="E124" s="42" t="str">
+        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
+      </x:c>
+      <x:c r="F124" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G124" s="43"/>
-      <x:c r="H124" s="43" t="str">
+      <x:c r="G124" s="42"/>
+      <x:c r="H124" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I124" s="386" t="n">
+      <x:c r="I124" s="387" t="n">
         <x:f>IF(H124="Done",1,IF(H124="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="43" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
-      </x:c>
-      <x:c r="K124" s="43"/>
-      <x:c r="L124" s="43"/>
-      <x:c r="M124" s="43"/>
+      <x:c r="J124" s="42" t="str">
+        <x:v>Flutter target (GA baseline)</x:v>
+      </x:c>
+      <x:c r="K124" s="42"/>
+      <x:c r="L124" s="42"/>
+      <x:c r="M124" s="42"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="42" t="str">
-        <x:v>R-120</x:v>
-      </x:c>
-      <x:c r="B125" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C125" s="42" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D125" s="42" t="str">
-        <x:v>Native recommendation profile</x:v>
-      </x:c>
-      <x:c r="E125" s="42" t="str">
-        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
-      </x:c>
-      <x:c r="F125" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G125" s="42"/>
-      <x:c r="H125" s="42" t="str">
+      <x:c r="A125" s="43" t="str">
+        <x:v>R-119</x:v>
+      </x:c>
+      <x:c r="B125" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C125" s="43" t="str">
+        <x:v>Web/Admin</x:v>
+      </x:c>
+      <x:c r="D125" s="43" t="str">
+        <x:v>React Native Web optional profile</x:v>
+      </x:c>
+      <x:c r="E125" s="43" t="str">
+        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
+      </x:c>
+      <x:c r="F125" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G125" s="43"/>
+      <x:c r="H125" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I125" s="387" t="n">
+      <x:c r="I125" s="386" t="n">
         <x:f>IF(H125="Done",1,IF(H125="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J125" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K125" s="42"/>
-      <x:c r="L125" s="42"/>
-      <x:c r="M125" s="42"/>
+      <x:c r="J125" s="43" t="str">
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
+      </x:c>
+      <x:c r="K125" s="43"/>
+      <x:c r="L125" s="43"/>
+      <x:c r="M125" s="43"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="43" t="str">
-        <x:v>R-121</x:v>
-      </x:c>
-      <x:c r="B126" s="43" t="str">
+      <x:c r="A126" s="42" t="str">
+        <x:v>R-120</x:v>
+      </x:c>
+      <x:c r="B126" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C126" s="43" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D126" s="43" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="E126" s="43" t="str">
-        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
-      </x:c>
-      <x:c r="F126" s="43" t="str">
+      <x:c r="C126" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D126" s="42" t="str">
+        <x:v>Native recommendation profile</x:v>
+      </x:c>
+      <x:c r="E126" s="42" t="str">
+        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
+      </x:c>
+      <x:c r="F126" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G126" s="43"/>
-      <x:c r="H126" s="43" t="str">
+      <x:c r="G126" s="42"/>
+      <x:c r="H126" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I126" s="386" t="n">
+      <x:c r="I126" s="387" t="n">
         <x:f>IF(H126="Done",1,IF(H126="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="43" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K126" s="43"/>
-      <x:c r="L126" s="43"/>
-      <x:c r="M126" s="43"/>
+      <x:c r="J126" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K126" s="42"/>
+      <x:c r="L126" s="42"/>
+      <x:c r="M126" s="42"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="42" t="str">
-        <x:v>R-122</x:v>
-      </x:c>
-      <x:c r="B127" s="42" t="str">
+      <x:c r="A127" s="43" t="str">
+        <x:v>R-121</x:v>
+      </x:c>
+      <x:c r="B127" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C127" s="42" t="str">
+      <x:c r="C127" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D127" s="42" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="E127" s="42" t="str">
-        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
-      </x:c>
-      <x:c r="F127" s="42" t="str">
+      <x:c r="D127" s="43" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="E127" s="43" t="str">
+        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
+      </x:c>
+      <x:c r="F127" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G127" s="42"/>
-      <x:c r="H127" s="42" t="str">
+      <x:c r="G127" s="43"/>
+      <x:c r="H127" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I127" s="387" t="n">
+      <x:c r="I127" s="386" t="n">
         <x:f>IF(H127="Done",1,IF(H127="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J127" s="42" t="str">
+      <x:c r="J127" s="43" t="str">
         <x:v>Project + workspace model</x:v>
       </x:c>
-      <x:c r="K127" s="42"/>
-      <x:c r="L127" s="42"/>
-      <x:c r="M127" s="42"/>
+      <x:c r="K127" s="43"/>
+      <x:c r="L127" s="43"/>
+      <x:c r="M127" s="43"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="43" t="str">
-        <x:v>R-123</x:v>
-      </x:c>
-      <x:c r="B128" s="43" t="str">
+      <x:c r="A128" s="42" t="str">
+        <x:v>R-122</x:v>
+      </x:c>
+      <x:c r="B128" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C128" s="43" t="str">
+      <x:c r="C128" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D128" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="E128" s="43" t="str">
-        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
-      </x:c>
-      <x:c r="F128" s="43" t="str">
+      <x:c r="D128" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="E128" s="42" t="str">
+        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
+      </x:c>
+      <x:c r="F128" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G128" s="43"/>
-      <x:c r="H128" s="43" t="str">
+      <x:c r="G128" s="42"/>
+      <x:c r="H128" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I128" s="386" t="n">
+      <x:c r="I128" s="387" t="n">
         <x:f>IF(H128="Done",1,IF(H128="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="43" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="K128" s="43"/>
-      <x:c r="L128" s="43"/>
-      <x:c r="M128" s="43"/>
+      <x:c r="J128" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K128" s="42"/>
+      <x:c r="L128" s="42"/>
+      <x:c r="M128" s="42"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="42" t="str">
-        <x:v>R-124</x:v>
-      </x:c>
-      <x:c r="B129" s="42" t="str">
+      <x:c r="A129" s="43" t="str">
+        <x:v>R-123</x:v>
+      </x:c>
+      <x:c r="B129" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C129" s="42" t="str">
+      <x:c r="C129" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D129" s="42" t="str">
-        <x:v>Repository naming convention</x:v>
-      </x:c>
-      <x:c r="E129" s="42" t="str">
-        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
-      </x:c>
-      <x:c r="F129" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G129" s="42"/>
-      <x:c r="H129" s="42" t="str">
+      <x:c r="D129" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="E129" s="43" t="str">
+        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
+      </x:c>
+      <x:c r="F129" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G129" s="43"/>
+      <x:c r="H129" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I129" s="387" t="n">
+      <x:c r="I129" s="386" t="n">
         <x:f>IF(H129="Done",1,IF(H129="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J129" s="42" t="str">
+      <x:c r="J129" s="43" t="str">
         <x:v>One Git repo per customer project</x:v>
       </x:c>
-      <x:c r="K129" s="42"/>
-      <x:c r="L129" s="42"/>
-      <x:c r="M129" s="42"/>
+      <x:c r="K129" s="43"/>
+      <x:c r="L129" s="43"/>
+      <x:c r="M129" s="43"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="43" t="str">
-        <x:v>R-125</x:v>
-      </x:c>
-      <x:c r="B130" s="43" t="str">
+      <x:c r="A130" s="42" t="str">
+        <x:v>R-124</x:v>
+      </x:c>
+      <x:c r="B130" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C130" s="43" t="str">
+      <x:c r="C130" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D130" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="E130" s="43" t="str">
-        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
-      </x:c>
-      <x:c r="F130" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G130" s="43"/>
-      <x:c r="H130" s="43" t="str">
+      <x:c r="D130" s="42" t="str">
+        <x:v>Repository naming convention</x:v>
+      </x:c>
+      <x:c r="E130" s="42" t="str">
+        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
+      </x:c>
+      <x:c r="F130" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G130" s="42"/>
+      <x:c r="H130" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I130" s="386" t="n">
+      <x:c r="I130" s="387" t="n">
         <x:f>IF(H130="Done",1,IF(H130="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J130" s="43" t="str">
-        <x:v>Branch per task</x:v>
-      </x:c>
-      <x:c r="K130" s="43"/>
-      <x:c r="L130" s="43"/>
-      <x:c r="M130" s="43"/>
+      <x:c r="J130" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="K130" s="42"/>
+      <x:c r="L130" s="42"/>
+      <x:c r="M130" s="42"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="42" t="str">
-        <x:v>R-126</x:v>
-      </x:c>
-      <x:c r="B131" s="42" t="str">
+      <x:c r="A131" s="43" t="str">
+        <x:v>R-125</x:v>
+      </x:c>
+      <x:c r="B131" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C131" s="42" t="str">
-        <x:v>Product Foundation</x:v>
-      </x:c>
-      <x:c r="D131" s="42" t="str">
-        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
-      </x:c>
-      <x:c r="E131" s="42" t="str">
-        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
-      </x:c>
-      <x:c r="F131" s="42" t="str">
+      <x:c r="C131" s="43" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D131" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="E131" s="43" t="str">
+        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
+      </x:c>
+      <x:c r="F131" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G131" s="42"/>
-      <x:c r="H131" s="42" t="str">
+      <x:c r="G131" s="43"/>
+      <x:c r="H131" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I131" s="387" t="n">
+      <x:c r="I131" s="386" t="n">
         <x:f>IF(H131="Done",1,IF(H131="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J131" s="42" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K131" s="42"/>
-      <x:c r="L131" s="42"/>
-      <x:c r="M131" s="42"/>
+      <x:c r="J131" s="43" t="str">
+        <x:v>Branch per task</x:v>
+      </x:c>
+      <x:c r="K131" s="43"/>
+      <x:c r="L131" s="43"/>
+      <x:c r="M131" s="43"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="43" t="str">
-        <x:v>R-127</x:v>
-      </x:c>
-      <x:c r="B132" s="43" t="str">
+      <x:c r="A132" s="42" t="str">
+        <x:v>R-126</x:v>
+      </x:c>
+      <x:c r="B132" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C132" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D132" s="43" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="E132" s="43" t="str">
-        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
-      </x:c>
-      <x:c r="F132" s="43" t="str">
+      <x:c r="C132" s="42" t="str">
+        <x:v>Product Foundation</x:v>
+      </x:c>
+      <x:c r="D132" s="42" t="str">
+        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
+      </x:c>
+      <x:c r="E132" s="42" t="str">
+        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
+      </x:c>
+      <x:c r="F132" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G132" s="43"/>
-      <x:c r="H132" s="43" t="str">
+      <x:c r="G132" s="42"/>
+      <x:c r="H132" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I132" s="386" t="n">
+      <x:c r="I132" s="387" t="n">
         <x:f>IF(H132="Done",1,IF(H132="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J132" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K132" s="43"/>
-      <x:c r="L132" s="43"/>
-      <x:c r="M132" s="43"/>
+      <x:c r="J132" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K132" s="42"/>
+      <x:c r="L132" s="42"/>
+      <x:c r="M132" s="42"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="42" t="str">
-        <x:v>R-128</x:v>
-      </x:c>
-      <x:c r="B133" s="42" t="str">
+      <x:c r="A133" s="43" t="str">
+        <x:v>R-127</x:v>
+      </x:c>
+      <x:c r="B133" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C133" s="42" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D133" s="42" t="str">
-        <x:v>Cross-language monorepo orchestration</x:v>
-      </x:c>
-      <x:c r="E133" s="42" t="str">
-        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
-      </x:c>
-      <x:c r="F133" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G133" s="42"/>
-      <x:c r="H133" s="42" t="str">
+      <x:c r="C133" s="43" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D133" s="43" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="E133" s="43" t="str">
+        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
+      </x:c>
+      <x:c r="F133" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G133" s="43"/>
+      <x:c r="H133" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I133" s="387" t="n">
+      <x:c r="I133" s="386" t="n">
         <x:f>IF(H133="Done",1,IF(H133="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J133" s="42" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K133" s="42"/>
-      <x:c r="L133" s="42"/>
-      <x:c r="M133" s="42"/>
+      <x:c r="J133" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K133" s="43"/>
+      <x:c r="L133" s="43"/>
+      <x:c r="M133" s="43"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="43" t="str">
-        <x:v>R-129</x:v>
-      </x:c>
-      <x:c r="B134" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C134" s="43" t="str">
+      <x:c r="A134" s="42" t="str">
+        <x:v>R-128</x:v>
+      </x:c>
+      <x:c r="B134" s="42" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C134" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D134" s="43" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="E134" s="43" t="str">
-        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
-      </x:c>
-      <x:c r="F134" s="43" t="str">
+      <x:c r="D134" s="42" t="str">
+        <x:v>Cross-language monorepo orchestration</x:v>
+      </x:c>
+      <x:c r="E134" s="42" t="str">
+        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
+      </x:c>
+      <x:c r="F134" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G134" s="43"/>
-      <x:c r="H134" s="43" t="str">
+      <x:c r="G134" s="42"/>
+      <x:c r="H134" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I134" s="386" t="n">
+      <x:c r="I134" s="387" t="n">
         <x:f>IF(H134="Done",1,IF(H134="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J134" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K134" s="43"/>
-      <x:c r="L134" s="43"/>
-      <x:c r="M134" s="43"/>
+      <x:c r="J134" s="42" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K134" s="42"/>
+      <x:c r="L134" s="42"/>
+      <x:c r="M134" s="42"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="42" t="str">
-        <x:v>R-130</x:v>
-      </x:c>
-      <x:c r="B135" s="42" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C135" s="42" t="str">
+      <x:c r="A135" s="43" t="str">
+        <x:v>R-129</x:v>
+      </x:c>
+      <x:c r="B135" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C135" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D135" s="42" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="E135" s="42" t="str">
-        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
-      </x:c>
-      <x:c r="F135" s="42" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G135" s="42"/>
-      <x:c r="H135" s="42" t="str">
+      <x:c r="D135" s="43" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="E135" s="43" t="str">
+        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
+      </x:c>
+      <x:c r="F135" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G135" s="43"/>
+      <x:c r="H135" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I135" s="387" t="n">
+      <x:c r="I135" s="386" t="n">
         <x:f>IF(H135="Done",1,IF(H135="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J135" s="42" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="K135" s="42"/>
-      <x:c r="L135" s="42"/>
-      <x:c r="M135" s="42"/>
+      <x:c r="J135" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K135" s="43"/>
+      <x:c r="L135" s="43"/>
+      <x:c r="M135" s="43"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="43" t="str">
-        <x:v>R-131</x:v>
-      </x:c>
-      <x:c r="B136" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C136" s="43" t="str">
+      <x:c r="A136" s="42" t="str">
+        <x:v>R-130</x:v>
+      </x:c>
+      <x:c r="B136" s="42" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C136" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D136" s="43" t="str">
-        <x:v>CODEOWNERS + protected paths</x:v>
-      </x:c>
-      <x:c r="E136" s="43" t="str">
-        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
-      </x:c>
-      <x:c r="F136" s="43" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G136" s="43"/>
-      <x:c r="H136" s="43" t="str">
+      <x:c r="D136" s="42" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="E136" s="42" t="str">
+        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
+      </x:c>
+      <x:c r="F136" s="42" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G136" s="42"/>
+      <x:c r="H136" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I136" s="386" t="n">
+      <x:c r="I136" s="387" t="n">
         <x:f>IF(H136="Done",1,IF(H136="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J136" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="K136" s="43"/>
-      <x:c r="L136" s="43"/>
-      <x:c r="M136" s="43"/>
+      <x:c r="J136" s="42" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="K136" s="42"/>
+      <x:c r="L136" s="42"/>
+      <x:c r="M136" s="42"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="42" t="str">
-        <x:v>R-132</x:v>
-      </x:c>
-      <x:c r="B137" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C137" s="42" t="str">
+      <x:c r="A137" s="43" t="str">
+        <x:v>R-131</x:v>
+      </x:c>
+      <x:c r="B137" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C137" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D137" s="42" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="E137" s="42" t="str">
-        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
-      </x:c>
-      <x:c r="F137" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G137" s="42"/>
-      <x:c r="H137" s="42" t="str">
+      <x:c r="D137" s="43" t="str">
+        <x:v>CODEOWNERS + protected paths</x:v>
+      </x:c>
+      <x:c r="E137" s="43" t="str">
+        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
+      </x:c>
+      <x:c r="F137" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G137" s="43"/>
+      <x:c r="H137" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I137" s="387" t="n">
+      <x:c r="I137" s="386" t="n">
         <x:f>IF(H137="Done",1,IF(H137="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J137" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K137" s="42"/>
-      <x:c r="L137" s="42"/>
-      <x:c r="M137" s="42"/>
+      <x:c r="J137" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="K137" s="43"/>
+      <x:c r="L137" s="43"/>
+      <x:c r="M137" s="43"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="66" t="str">
-        <x:v>R-133</x:v>
-      </x:c>
-      <x:c r="B138" s="66" t="str">
+      <x:c r="A138" s="42" t="str">
+        <x:v>R-132</x:v>
+      </x:c>
+      <x:c r="B138" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C138" s="66" t="str">
-        <x:v>Change Safety</x:v>
-      </x:c>
-      <x:c r="D138" s="66" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="E138" s="66" t="str">
-        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
-      </x:c>
-      <x:c r="F138" s="66" t="str">
+      <x:c r="C138" s="42" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D138" s="42" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="E138" s="42" t="str">
+        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
+      </x:c>
+      <x:c r="F138" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G138" s="66"/>
-      <x:c r="H138" s="66" t="str">
+      <x:c r="G138" s="42"/>
+      <x:c r="H138" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I138" s="388" t="n">
+      <x:c r="I138" s="387" t="n">
         <x:f>IF(H138="Done",1,IF(H138="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J138" s="66" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K138" s="66"/>
-      <x:c r="L138" s="66"/>
-      <x:c r="M138" s="66"/>
+      <x:c r="J138" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K138" s="42"/>
+      <x:c r="L138" s="42"/>
+      <x:c r="M138" s="42"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="65" t="str">
-        <x:v>R-134</x:v>
-      </x:c>
-      <x:c r="B139" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C139" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D139" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="E139" s="65" t="str">
-        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
-      </x:c>
-      <x:c r="F139" s="65" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G139" s="65"/>
-      <x:c r="H139" s="65" t="str">
+      <x:c r="A139" s="66" t="str">
+        <x:v>R-133</x:v>
+      </x:c>
+      <x:c r="B139" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C139" s="66" t="str">
+        <x:v>Change Safety</x:v>
+      </x:c>
+      <x:c r="D139" s="66" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="E139" s="66" t="str">
+        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
+      </x:c>
+      <x:c r="F139" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G139" s="66"/>
+      <x:c r="H139" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I139" s="389" t="n">
+      <x:c r="I139" s="388" t="n">
         <x:f>IF(H139="Done",1,IF(H139="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J139" s="65" t="str">
-        <x:v>Build artifact caching</x:v>
-      </x:c>
-      <x:c r="K139" s="65"/>
-      <x:c r="L139" s="65"/>
-      <x:c r="M139" s="65"/>
+      <x:c r="J139" s="66" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K139" s="66"/>
+      <x:c r="L139" s="66"/>
+      <x:c r="M139" s="66"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="66" t="str">
-        <x:v>R-135</x:v>
-      </x:c>
-      <x:c r="B140" s="66" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C140" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D140" s="66" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="E140" s="66" t="str">
-        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
-      </x:c>
-      <x:c r="F140" s="66" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G140" s="66"/>
-      <x:c r="H140" s="66" t="str">
+      <x:c r="A140" s="65" t="str">
+        <x:v>R-134</x:v>
+      </x:c>
+      <x:c r="B140" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C140" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D140" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="E140" s="65" t="str">
+        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
+      </x:c>
+      <x:c r="F140" s="65" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G140" s="65"/>
+      <x:c r="H140" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I140" s="388" t="n">
+      <x:c r="I140" s="389" t="n">
         <x:f>IF(H140="Done",1,IF(H140="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J140" s="66" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K140" s="66"/>
-      <x:c r="L140" s="66"/>
-      <x:c r="M140" s="66" t="str">
-        <x:v>V3</x:v>
-      </x:c>
+      <x:c r="J140" s="65" t="str">
+        <x:v>Build artifact caching</x:v>
+      </x:c>
+      <x:c r="K140" s="65"/>
+      <x:c r="L140" s="65"/>
+      <x:c r="M140" s="65"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="65" t="str">
-        <x:v>R-136</x:v>
-      </x:c>
-      <x:c r="B141" s="65" t="str">
+      <x:c r="A141" s="66" t="str">
+        <x:v>R-135</x:v>
+      </x:c>
+      <x:c r="B141" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C141" s="65" t="str">
+      <x:c r="C141" s="66" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D141" s="65" t="str">
-        <x:v>Recommendation score model</x:v>
-      </x:c>
-      <x:c r="E141" s="65" t="str">
-        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
-      </x:c>
-      <x:c r="F141" s="65" t="str">
+      <x:c r="D141" s="66" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="E141" s="66" t="str">
+        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
+      </x:c>
+      <x:c r="F141" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G141" s="65"/>
-      <x:c r="H141" s="65" t="str">
+      <x:c r="G141" s="66"/>
+      <x:c r="H141" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I141" s="389" t="n">
+      <x:c r="I141" s="388" t="n">
         <x:f>IF(H141="Done",1,IF(H141="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J141" s="65" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="K141" s="65"/>
-      <x:c r="L141" s="65"/>
-      <x:c r="M141" s="65" t="str">
-        <x:v>Do not choose by industry label alone.</x:v>
+      <x:c r="J141" s="66" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K141" s="66"/>
+      <x:c r="L141" s="66"/>
+      <x:c r="M141" s="66" t="str">
+        <x:v>V3</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="66" t="str">
-        <x:v>R-137</x:v>
-      </x:c>
-      <x:c r="B142" s="66" t="str">
+      <x:c r="A142" s="65" t="str">
+        <x:v>R-136</x:v>
+      </x:c>
+      <x:c r="B142" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C142" s="66" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D142" s="66" t="str">
-        <x:v>Code sharing policy</x:v>
-      </x:c>
-      <x:c r="E142" s="66" t="str">
-        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
-      </x:c>
-      <x:c r="F142" s="66" t="str">
+      <x:c r="C142" s="65" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D142" s="65" t="str">
+        <x:v>Recommendation score model</x:v>
+      </x:c>
+      <x:c r="E142" s="65" t="str">
+        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
+      </x:c>
+      <x:c r="F142" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G142" s="66"/>
-      <x:c r="H142" s="66" t="str">
+      <x:c r="G142" s="65"/>
+      <x:c r="H142" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I142" s="388" t="n">
+      <x:c r="I142" s="389" t="n">
         <x:f>IF(H142="Done",1,IF(H142="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J142" s="66" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K142" s="66"/>
-      <x:c r="L142" s="66"/>
-      <x:c r="M142" s="66" t="str">
-        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
+      <x:c r="J142" s="65" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="K142" s="65"/>
+      <x:c r="L142" s="65"/>
+      <x:c r="M142" s="65" t="str">
+        <x:v>Do not choose by industry label alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="65" t="str">
-        <x:v>R-138</x:v>
-      </x:c>
-      <x:c r="B143" s="65" t="str">
+      <x:c r="A143" s="66" t="str">
+        <x:v>R-137</x:v>
+      </x:c>
+      <x:c r="B143" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C143" s="65" t="str">
+      <x:c r="C143" s="66" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D143" s="65" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="E143" s="65" t="str">
-        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
-      </x:c>
-      <x:c r="F143" s="65" t="str">
+      <x:c r="D143" s="66" t="str">
+        <x:v>Code sharing policy</x:v>
+      </x:c>
+      <x:c r="E143" s="66" t="str">
+        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
+      </x:c>
+      <x:c r="F143" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G143" s="65"/>
-      <x:c r="H143" s="65" t="str">
+      <x:c r="G143" s="66"/>
+      <x:c r="H143" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I143" s="389" t="n">
+      <x:c r="I143" s="388" t="n">
         <x:f>IF(H143="Done",1,IF(H143="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J143" s="65" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K143" s="65"/>
-      <x:c r="L143" s="65"/>
-      <x:c r="M143" s="65" t="str">
-        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
+      <x:c r="J143" s="66" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K143" s="66"/>
+      <x:c r="L143" s="66"/>
+      <x:c r="M143" s="66" t="str">
+        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="66" t="str">
-        <x:v>R-139</x:v>
-      </x:c>
-      <x:c r="B144" s="66" t="str">
+      <x:c r="A144" s="65" t="str">
+        <x:v>R-138</x:v>
+      </x:c>
+      <x:c r="B144" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C144" s="66" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D144" s="66" t="str">
-        <x:v>Root task commands</x:v>
-      </x:c>
-      <x:c r="E144" s="66" t="str">
-        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
-      </x:c>
-      <x:c r="F144" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G144" s="66"/>
-      <x:c r="H144" s="66" t="str">
+      <x:c r="C144" s="65" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D144" s="65" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="E144" s="65" t="str">
+        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
+      </x:c>
+      <x:c r="F144" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G144" s="65"/>
+      <x:c r="H144" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I144" s="388" t="n">
+      <x:c r="I144" s="389" t="n">
         <x:f>IF(H144="Done",1,IF(H144="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J144" s="66" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="K144" s="66"/>
-      <x:c r="L144" s="66"/>
-      <x:c r="M144" s="66" t="str">
-        <x:v>Framework-independent agent commands.</x:v>
+      <x:c r="J144" s="65" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K144" s="65"/>
+      <x:c r="L144" s="65"/>
+      <x:c r="M144" s="65" t="str">
+        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="65" t="str">
-        <x:v>R-140</x:v>
-      </x:c>
-      <x:c r="B145" s="65" t="str">
+      <x:c r="A145" s="66" t="str">
+        <x:v>R-139</x:v>
+      </x:c>
+      <x:c r="B145" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C145" s="65" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D145" s="65" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="E145" s="65" t="str">
-        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
-      </x:c>
-      <x:c r="F145" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G145" s="65"/>
-      <x:c r="H145" s="65" t="str">
+      <x:c r="C145" s="66" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D145" s="66" t="str">
+        <x:v>Root task commands</x:v>
+      </x:c>
+      <x:c r="E145" s="66" t="str">
+        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
+      </x:c>
+      <x:c r="F145" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G145" s="66"/>
+      <x:c r="H145" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I145" s="389" t="n">
+      <x:c r="I145" s="388" t="n">
         <x:f>IF(H145="Done",1,IF(H145="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K145" s="65"/>
-      <x:c r="L145" s="65"/>
-      <x:c r="M145" s="65" t="str">
-        <x:v>Stable target.</x:v>
+      <x:c r="J145" s="66" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="K145" s="66"/>
+      <x:c r="L145" s="66"/>
+      <x:c r="M145" s="66" t="str">
+        <x:v>Framework-independent agent commands.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="66" t="str">
-        <x:v>R-141</x:v>
-      </x:c>
-      <x:c r="B146" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C146" s="66" t="str">
+      <x:c r="A146" s="65" t="str">
+        <x:v>R-140</x:v>
+      </x:c>
+      <x:c r="B146" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C146" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D146" s="66" t="str">
-        <x:v>Flutter scaled template</x:v>
-      </x:c>
-      <x:c r="E146" s="66" t="str">
-        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
-      </x:c>
-      <x:c r="F146" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G146" s="66"/>
-      <x:c r="H146" s="66" t="str">
+      <x:c r="D146" s="65" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="E146" s="65" t="str">
+        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
+      </x:c>
+      <x:c r="F146" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G146" s="65"/>
+      <x:c r="H146" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I146" s="388" t="n">
+      <x:c r="I146" s="389" t="n">
         <x:f>IF(H146="Done",1,IF(H146="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="66" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="K146" s="66"/>
-      <x:c r="L146" s="66"/>
-      <x:c r="M146" s="66" t="str">
-        <x:v>Use only when complexity warrants.</x:v>
+      <x:c r="J146" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K146" s="65"/>
+      <x:c r="L146" s="65"/>
+      <x:c r="M146" s="65" t="str">
+        <x:v>Stable target.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="65" t="str">
-        <x:v>R-142</x:v>
-      </x:c>
-      <x:c r="B147" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C147" s="65" t="str">
+      <x:c r="A147" s="66" t="str">
+        <x:v>R-141</x:v>
+      </x:c>
+      <x:c r="B147" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C147" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D147" s="65" t="str">
-        <x:v>React Native TypeScript template</x:v>
-      </x:c>
-      <x:c r="E147" s="65" t="str">
-        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
-      </x:c>
-      <x:c r="F147" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G147" s="65"/>
-      <x:c r="H147" s="65" t="str">
+      <x:c r="D147" s="66" t="str">
+        <x:v>Flutter scaled template</x:v>
+      </x:c>
+      <x:c r="E147" s="66" t="str">
+        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
+      </x:c>
+      <x:c r="F147" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G147" s="66"/>
+      <x:c r="H147" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I147" s="389" t="n">
+      <x:c r="I147" s="388" t="n">
         <x:f>IF(H147="Done",1,IF(H147="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K147" s="65"/>
-      <x:c r="L147" s="65"/>
-      <x:c r="M147" s="65" t="str">
-        <x:v>Expo profile when capabilities fit.</x:v>
+      <x:c r="J147" s="66" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="K147" s="66"/>
+      <x:c r="L147" s="66"/>
+      <x:c r="M147" s="66" t="str">
+        <x:v>Use only when complexity warrants.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="66" t="str">
-        <x:v>R-143</x:v>
-      </x:c>
-      <x:c r="B148" s="66" t="str">
+      <x:c r="A148" s="65" t="str">
+        <x:v>R-142</x:v>
+      </x:c>
+      <x:c r="B148" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C148" s="66" t="str">
+      <x:c r="C148" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D148" s="66" t="str">
-        <x:v>React Native shared TS packages</x:v>
-      </x:c>
-      <x:c r="E148" s="66" t="str">
-        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
-      </x:c>
-      <x:c r="F148" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G148" s="66"/>
-      <x:c r="H148" s="66" t="str">
+      <x:c r="D148" s="65" t="str">
+        <x:v>React Native TypeScript template</x:v>
+      </x:c>
+      <x:c r="E148" s="65" t="str">
+        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
+      </x:c>
+      <x:c r="F148" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G148" s="65"/>
+      <x:c r="H148" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I148" s="388" t="n">
+      <x:c r="I148" s="389" t="n">
         <x:f>IF(H148="Done",1,IF(H148="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J148" s="66" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K148" s="66"/>
-      <x:c r="L148" s="66"/>
-      <x:c r="M148" s="66" t="str">
-        <x:v>Do not share UI blindly.</x:v>
+      <x:c r="J148" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K148" s="65"/>
+      <x:c r="L148" s="65"/>
+      <x:c r="M148" s="65" t="str">
+        <x:v>Expo profile when capabilities fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="65" t="str">
-        <x:v>R-144</x:v>
-      </x:c>
-      <x:c r="B149" s="65" t="str">
+      <x:c r="A149" s="66" t="str">
+        <x:v>R-143</x:v>
+      </x:c>
+      <x:c r="B149" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C149" s="65" t="str">
+      <x:c r="C149" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D149" s="65" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="E149" s="65" t="str">
-        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
-      </x:c>
-      <x:c r="F149" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G149" s="65"/>
-      <x:c r="H149" s="65" t="str">
+      <x:c r="D149" s="66" t="str">
+        <x:v>React Native shared TS packages</x:v>
+      </x:c>
+      <x:c r="E149" s="66" t="str">
+        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
+      </x:c>
+      <x:c r="F149" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G149" s="66"/>
+      <x:c r="H149" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I149" s="389" t="n">
+      <x:c r="I149" s="388" t="n">
         <x:f>IF(H149="Done",1,IF(H149="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J149" s="65" t="str">
-        <x:v>Native Android Agent</x:v>
-      </x:c>
-      <x:c r="K149" s="65"/>
-      <x:c r="L149" s="65"/>
-      <x:c r="M149" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J149" s="66" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K149" s="66"/>
+      <x:c r="L149" s="66"/>
+      <x:c r="M149" s="66" t="str">
+        <x:v>Do not share UI blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="66" t="str">
-        <x:v>R-145</x:v>
-      </x:c>
-      <x:c r="B150" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C150" s="66" t="str">
+      <x:c r="A150" s="65" t="str">
+        <x:v>R-144</x:v>
+      </x:c>
+      <x:c r="B150" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C150" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D150" s="66" t="str">
-        <x:v>Native Android scaled modules</x:v>
-      </x:c>
-      <x:c r="E150" s="66" t="str">
-        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
-      </x:c>
-      <x:c r="F150" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G150" s="66"/>
-      <x:c r="H150" s="66" t="str">
+      <x:c r="D150" s="65" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="E150" s="65" t="str">
+        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
+      </x:c>
+      <x:c r="F150" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G150" s="65"/>
+      <x:c r="H150" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I150" s="388" t="n">
+      <x:c r="I150" s="389" t="n">
         <x:f>IF(H150="Done",1,IF(H150="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="66" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="K150" s="66"/>
-      <x:c r="L150" s="66"/>
-      <x:c r="M150" s="66" t="str">
-        <x:v>Experienced team structure.</x:v>
+      <x:c r="J150" s="65" t="str">
+        <x:v>Native Android Agent</x:v>
+      </x:c>
+      <x:c r="K150" s="65"/>
+      <x:c r="L150" s="65"/>
+      <x:c r="M150" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="65" t="str">
-        <x:v>R-146</x:v>
-      </x:c>
-      <x:c r="B151" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C151" s="65" t="str">
+      <x:c r="A151" s="66" t="str">
+        <x:v>R-145</x:v>
+      </x:c>
+      <x:c r="B151" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C151" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D151" s="65" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="E151" s="65" t="str">
-        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
-      </x:c>
-      <x:c r="F151" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G151" s="65"/>
-      <x:c r="H151" s="65" t="str">
+      <x:c r="D151" s="66" t="str">
+        <x:v>Native Android scaled modules</x:v>
+      </x:c>
+      <x:c r="E151" s="66" t="str">
+        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
+      </x:c>
+      <x:c r="F151" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G151" s="66"/>
+      <x:c r="H151" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I151" s="389" t="n">
+      <x:c r="I151" s="388" t="n">
         <x:f>IF(H151="Done",1,IF(H151="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J151" s="65" t="str">
-        <x:v>Native iOS Agent</x:v>
-      </x:c>
-      <x:c r="K151" s="65"/>
-      <x:c r="L151" s="65"/>
-      <x:c r="M151" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J151" s="66" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="K151" s="66"/>
+      <x:c r="L151" s="66"/>
+      <x:c r="M151" s="66" t="str">
+        <x:v>Experienced team structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="66" t="str">
-        <x:v>R-147</x:v>
-      </x:c>
-      <x:c r="B152" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C152" s="66" t="str">
+      <x:c r="A152" s="65" t="str">
+        <x:v>R-146</x:v>
+      </x:c>
+      <x:c r="B152" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C152" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D152" s="66" t="str">
-        <x:v>Native iOS scaled Swift Packages</x:v>
-      </x:c>
-      <x:c r="E152" s="66" t="str">
-        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
-      </x:c>
-      <x:c r="F152" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G152" s="66"/>
-      <x:c r="H152" s="66" t="str">
+      <x:c r="D152" s="65" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="E152" s="65" t="str">
+        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
+      </x:c>
+      <x:c r="F152" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G152" s="65"/>
+      <x:c r="H152" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I152" s="388" t="n">
+      <x:c r="I152" s="389" t="n">
         <x:f>IF(H152="Done",1,IF(H152="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J152" s="66" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="K152" s="66"/>
-      <x:c r="L152" s="66"/>
-      <x:c r="M152" s="66" t="str">
-        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
+      <x:c r="J152" s="65" t="str">
+        <x:v>Native iOS Agent</x:v>
+      </x:c>
+      <x:c r="K152" s="65"/>
+      <x:c r="L152" s="65"/>
+      <x:c r="M152" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="65" t="str">
-        <x:v>R-148</x:v>
-      </x:c>
-      <x:c r="B153" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C153" s="65" t="str">
+      <x:c r="A153" s="66" t="str">
+        <x:v>R-147</x:v>
+      </x:c>
+      <x:c r="B153" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C153" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D153" s="65" t="str">
-        <x:v>Next.js public web template</x:v>
-      </x:c>
-      <x:c r="E153" s="65" t="str">
-        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
-      </x:c>
-      <x:c r="F153" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G153" s="65"/>
-      <x:c r="H153" s="65" t="str">
+      <x:c r="D153" s="66" t="str">
+        <x:v>Native iOS scaled Swift Packages</x:v>
+      </x:c>
+      <x:c r="E153" s="66" t="str">
+        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
+      </x:c>
+      <x:c r="F153" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G153" s="66"/>
+      <x:c r="H153" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I153" s="389" t="n">
+      <x:c r="I153" s="388" t="n">
         <x:f>IF(H153="Done",1,IF(H153="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J153" s="65" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="K153" s="65"/>
-      <x:c r="L153" s="65"/>
-      <x:c r="M153" s="65" t="str">
-        <x:v>Web optimized independently.</x:v>
+      <x:c r="J153" s="66" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="K153" s="66"/>
+      <x:c r="L153" s="66"/>
+      <x:c r="M153" s="66" t="str">
+        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="66" t="str">
-        <x:v>R-149</x:v>
-      </x:c>
-      <x:c r="B154" s="66" t="str">
+      <x:c r="A154" s="65" t="str">
+        <x:v>R-148</x:v>
+      </x:c>
+      <x:c r="B154" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C154" s="66" t="str">
+      <x:c r="C154" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D154" s="66" t="str">
-        <x:v>Next.js admin template</x:v>
-      </x:c>
-      <x:c r="E154" s="66" t="str">
-        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
-      </x:c>
-      <x:c r="F154" s="66" t="str">
+      <x:c r="D154" s="65" t="str">
+        <x:v>Next.js public web template</x:v>
+      </x:c>
+      <x:c r="E154" s="65" t="str">
+        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
+      </x:c>
+      <x:c r="F154" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G154" s="66"/>
-      <x:c r="H154" s="66" t="str">
+      <x:c r="G154" s="65"/>
+      <x:c r="H154" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I154" s="388" t="n">
+      <x:c r="I154" s="389" t="n">
         <x:f>IF(H154="Done",1,IF(H154="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="66" t="str">
+      <x:c r="J154" s="65" t="str">
         <x:v>Next.js web + admin default</x:v>
       </x:c>
-      <x:c r="K154" s="66"/>
-      <x:c r="L154" s="66"/>
-      <x:c r="M154" s="66" t="str">
-        <x:v>Never force admin onto Flutter/RN Web.</x:v>
+      <x:c r="K154" s="65"/>
+      <x:c r="L154" s="65"/>
+      <x:c r="M154" s="65" t="str">
+        <x:v>Web optimized independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="65" t="str">
-        <x:v>R-150</x:v>
-      </x:c>
-      <x:c r="B155" s="65" t="str">
+      <x:c r="A155" s="66" t="str">
+        <x:v>R-149</x:v>
+      </x:c>
+      <x:c r="B155" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C155" s="65" t="str">
+      <x:c r="C155" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D155" s="65" t="str">
-        <x:v>Go backend standard template</x:v>
-      </x:c>
-      <x:c r="E155" s="65" t="str">
-        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
-      </x:c>
-      <x:c r="F155" s="65" t="str">
+      <x:c r="D155" s="66" t="str">
+        <x:v>Next.js admin template</x:v>
+      </x:c>
+      <x:c r="E155" s="66" t="str">
+        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
+      </x:c>
+      <x:c r="F155" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G155" s="65"/>
-      <x:c r="H155" s="65" t="str">
+      <x:c r="G155" s="66"/>
+      <x:c r="H155" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I155" s="389" t="n">
+      <x:c r="I155" s="388" t="n">
         <x:f>IF(H155="Done",1,IF(H155="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J155" s="65" t="str">
-        <x:v>Backend Agent</x:v>
-      </x:c>
-      <x:c r="K155" s="65"/>
-      <x:c r="L155" s="65"/>
-      <x:c r="M155" s="65" t="str">
-        <x:v>Default backend profile.</x:v>
+      <x:c r="J155" s="66" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="K155" s="66"/>
+      <x:c r="L155" s="66"/>
+      <x:c r="M155" s="66" t="str">
+        <x:v>Never force admin onto Flutter/RN Web.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="66" t="str">
-        <x:v>R-151</x:v>
-      </x:c>
-      <x:c r="B156" s="66" t="str">
+      <x:c r="A156" s="65" t="str">
+        <x:v>R-150</x:v>
+      </x:c>
+      <x:c r="B156" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C156" s="66" t="str">
+      <x:c r="C156" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D156" s="66" t="str">
-        <x:v>Python backend standard template</x:v>
-      </x:c>
-      <x:c r="E156" s="66" t="str">
-        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
-      </x:c>
-      <x:c r="F156" s="66" t="str">
+      <x:c r="D156" s="65" t="str">
+        <x:v>Go backend standard template</x:v>
+      </x:c>
+      <x:c r="E156" s="65" t="str">
+        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
+      </x:c>
+      <x:c r="F156" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G156" s="66"/>
-      <x:c r="H156" s="66" t="str">
+      <x:c r="G156" s="65"/>
+      <x:c r="H156" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I156" s="388" t="n">
+      <x:c r="I156" s="389" t="n">
         <x:f>IF(H156="Done",1,IF(H156="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J156" s="66" t="str">
+      <x:c r="J156" s="65" t="str">
         <x:v>Backend Agent</x:v>
       </x:c>
-      <x:c r="K156" s="66"/>
-      <x:c r="L156" s="66"/>
-      <x:c r="M156" s="66" t="str">
-        <x:v>Alternative default backend profile.</x:v>
+      <x:c r="K156" s="65"/>
+      <x:c r="L156" s="65"/>
+      <x:c r="M156" s="65" t="str">
+        <x:v>Default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="65" t="str">
-        <x:v>R-152</x:v>
-      </x:c>
-      <x:c r="B157" s="65" t="str">
+      <x:c r="A157" s="66" t="str">
+        <x:v>R-151</x:v>
+      </x:c>
+      <x:c r="B157" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C157" s="65" t="str">
-        <x:v>Contracts</x:v>
-      </x:c>
-      <x:c r="D157" s="65" t="str">
-        <x:v>Generated client matrix</x:v>
-      </x:c>
-      <x:c r="E157" s="65" t="str">
-        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
-      </x:c>
-      <x:c r="F157" s="65" t="str">
+      <x:c r="C157" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D157" s="66" t="str">
+        <x:v>Python backend standard template</x:v>
+      </x:c>
+      <x:c r="E157" s="66" t="str">
+        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
+      </x:c>
+      <x:c r="F157" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G157" s="65"/>
-      <x:c r="H157" s="65" t="str">
+      <x:c r="G157" s="66"/>
+      <x:c r="H157" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I157" s="389" t="n">
+      <x:c r="I157" s="388" t="n">
         <x:f>IF(H157="Done",1,IF(H157="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J157" s="65" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K157" s="65"/>
-      <x:c r="L157" s="65"/>
-      <x:c r="M157" s="65" t="str">
-        <x:v>Contract-first consistency.</x:v>
+      <x:c r="J157" s="66" t="str">
+        <x:v>Backend Agent</x:v>
+      </x:c>
+      <x:c r="K157" s="66"/>
+      <x:c r="L157" s="66"/>
+      <x:c r="M157" s="66" t="str">
+        <x:v>Alternative default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="66" t="str">
-        <x:v>R-153</x:v>
-      </x:c>
-      <x:c r="B158" s="66" t="str">
+      <x:c r="A158" s="65" t="str">
+        <x:v>R-152</x:v>
+      </x:c>
+      <x:c r="B158" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C158" s="66" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D158" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="E158" s="66" t="str">
-        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
-      </x:c>
-      <x:c r="F158" s="66" t="str">
+      <x:c r="C158" s="65" t="str">
+        <x:v>Contracts</x:v>
+      </x:c>
+      <x:c r="D158" s="65" t="str">
+        <x:v>Generated client matrix</x:v>
+      </x:c>
+      <x:c r="E158" s="65" t="str">
+        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
+      </x:c>
+      <x:c r="F158" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G158" s="66"/>
-      <x:c r="H158" s="66" t="str">
+      <x:c r="G158" s="65"/>
+      <x:c r="H158" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I158" s="388" t="n">
+      <x:c r="I158" s="389" t="n">
         <x:f>IF(H158="Done",1,IF(H158="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K158" s="66"/>
-      <x:c r="L158" s="66"/>
-      <x:c r="M158" s="66" t="str">
-        <x:v>Stable/Beta/Experimental visible to user.</x:v>
+      <x:c r="J158" s="65" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K158" s="65"/>
+      <x:c r="L158" s="65"/>
+      <x:c r="M158" s="65" t="str">
+        <x:v>Contract-first consistency.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="65" t="str">
-        <x:v>R-154</x:v>
-      </x:c>
-      <x:c r="B159" s="65" t="str">
+      <x:c r="A159" s="66" t="str">
+        <x:v>R-153</x:v>
+      </x:c>
+      <x:c r="B159" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C159" s="65" t="str">
-        <x:v>Dependencies</x:v>
-      </x:c>
-      <x:c r="D159" s="65" t="str">
-        <x:v>Approved dependency catalog</x:v>
-      </x:c>
-      <x:c r="E159" s="65" t="str">
-        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
-      </x:c>
-      <x:c r="F159" s="65" t="str">
+      <x:c r="C159" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D159" s="66" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="E159" s="66" t="str">
+        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
+      </x:c>
+      <x:c r="F159" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G159" s="65"/>
-      <x:c r="H159" s="65" t="str">
+      <x:c r="G159" s="66"/>
+      <x:c r="H159" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I159" s="389" t="n">
+      <x:c r="I159" s="388" t="n">
         <x:f>IF(H159="Done",1,IF(H159="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K159" s="65"/>
-      <x:c r="L159" s="65"/>
-      <x:c r="M159" s="65" t="str">
-        <x:v>Prevents dependency explosion.</x:v>
+      <x:c r="J159" s="66" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K159" s="66"/>
+      <x:c r="L159" s="66"/>
+      <x:c r="M159" s="66" t="str">
+        <x:v>Stable/Beta/Experimental visible to user.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="66" t="str">
-        <x:v>R-155</x:v>
-      </x:c>
-      <x:c r="B160" s="66" t="str">
+      <x:c r="A160" s="65" t="str">
+        <x:v>R-154</x:v>
+      </x:c>
+      <x:c r="B160" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C160" s="66" t="str">
-        <x:v>Platform Architecture</x:v>
-      </x:c>
-      <x:c r="D160" s="66" t="str">
-        <x:v>Go control plane modular monolith</x:v>
-      </x:c>
-      <x:c r="E160" s="66" t="str">
-        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
-      </x:c>
-      <x:c r="F160" s="66" t="str">
+      <x:c r="C160" s="65" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D160" s="65" t="str">
+        <x:v>Approved dependency catalog</x:v>
+      </x:c>
+      <x:c r="E160" s="65" t="str">
+        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
+      </x:c>
+      <x:c r="F160" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G160" s="66"/>
-      <x:c r="H160" s="66" t="str">
+      <x:c r="G160" s="65"/>
+      <x:c r="H160" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I160" s="388" t="n">
+      <x:c r="I160" s="389" t="n">
         <x:f>IF(H160="Done",1,IF(H160="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="66" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K160" s="66"/>
-      <x:c r="L160" s="66"/>
-      <x:c r="M160" s="66" t="str">
-        <x:v>Avoid premature microservices.</x:v>
+      <x:c r="J160" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K160" s="65"/>
+      <x:c r="L160" s="65"/>
+      <x:c r="M160" s="65" t="str">
+        <x:v>Prevents dependency explosion.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="65" t="str">
-        <x:v>R-156</x:v>
-      </x:c>
-      <x:c r="B161" s="65" t="str">
+      <x:c r="A161" s="66" t="str">
+        <x:v>R-155</x:v>
+      </x:c>
+      <x:c r="B161" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C161" s="65" t="str">
+      <x:c r="C161" s="66" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D161" s="65" t="str">
-        <x:v>Python agent engine boundary</x:v>
-      </x:c>
-      <x:c r="E161" s="65" t="str">
-        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
-      </x:c>
-      <x:c r="F161" s="65" t="str">
+      <x:c r="D161" s="66" t="str">
+        <x:v>Go control plane modular monolith</x:v>
+      </x:c>
+      <x:c r="E161" s="66" t="str">
+        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
+      </x:c>
+      <x:c r="F161" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G161" s="65"/>
-      <x:c r="H161" s="65" t="str">
+      <x:c r="G161" s="66"/>
+      <x:c r="H161" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I161" s="389" t="n">
+      <x:c r="I161" s="388" t="n">
         <x:f>IF(H161="Done",1,IF(H161="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J161" s="65" t="str">
-        <x:v>Model gateway</x:v>
-      </x:c>
-      <x:c r="K161" s="65"/>
-      <x:c r="L161" s="65"/>
-      <x:c r="M161" s="65" t="str">
-        <x:v>Different ecosystem/iteration cadence.</x:v>
+      <x:c r="J161" s="66" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K161" s="66"/>
+      <x:c r="L161" s="66"/>
+      <x:c r="M161" s="66" t="str">
+        <x:v>Avoid premature microservices.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="66" t="str">
-        <x:v>R-157</x:v>
-      </x:c>
-      <x:c r="B162" s="66" t="str">
+      <x:c r="A162" s="65" t="str">
+        <x:v>R-156</x:v>
+      </x:c>
+      <x:c r="B162" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C162" s="66" t="str">
+      <x:c r="C162" s="65" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D162" s="66" t="str">
-        <x:v>Runner manager boundary</x:v>
-      </x:c>
-      <x:c r="E162" s="66" t="str">
-        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
-      </x:c>
-      <x:c r="F162" s="66" t="str">
+      <x:c r="D162" s="65" t="str">
+        <x:v>Python agent engine boundary</x:v>
+      </x:c>
+      <x:c r="E162" s="65" t="str">
+        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
+      </x:c>
+      <x:c r="F162" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G162" s="66"/>
-      <x:c r="H162" s="66" t="str">
+      <x:c r="G162" s="65"/>
+      <x:c r="H162" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I162" s="388" t="n">
+      <x:c r="I162" s="389" t="n">
         <x:f>IF(H162="Done",1,IF(H162="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J162" s="66" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
-      </x:c>
-      <x:c r="K162" s="66"/>
-      <x:c r="L162" s="66"/>
-      <x:c r="M162" s="66" t="str">
-        <x:v>Central execution control.</x:v>
+      <x:c r="J162" s="65" t="str">
+        <x:v>Model gateway</x:v>
+      </x:c>
+      <x:c r="K162" s="65"/>
+      <x:c r="L162" s="65"/>
+      <x:c r="M162" s="65" t="str">
+        <x:v>Different ecosystem/iteration cadence.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="65" t="str">
-        <x:v>R-158</x:v>
-      </x:c>
-      <x:c r="B163" s="65" t="str">
+      <x:c r="A163" s="66" t="str">
+        <x:v>R-157</x:v>
+      </x:c>
+      <x:c r="B163" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C163" s="65" t="str">
-        <x:v>CI/CD</x:v>
-      </x:c>
-      <x:c r="D163" s="65" t="str">
-        <x:v>Unified PR pipeline</x:v>
-      </x:c>
-      <x:c r="E163" s="65" t="str">
-        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
-      </x:c>
-      <x:c r="F163" s="65" t="str">
+      <x:c r="C163" s="66" t="str">
+        <x:v>Platform Architecture</x:v>
+      </x:c>
+      <x:c r="D163" s="66" t="str">
+        <x:v>Runner manager boundary</x:v>
+      </x:c>
+      <x:c r="E163" s="66" t="str">
+        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
+      </x:c>
+      <x:c r="F163" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G163" s="65"/>
-      <x:c r="H163" s="65" t="str">
+      <x:c r="G163" s="66"/>
+      <x:c r="H163" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I163" s="389" t="n">
+      <x:c r="I163" s="388" t="n">
         <x:f>IF(H163="Done",1,IF(H163="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J163" s="65" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="K163" s="65"/>
-      <x:c r="L163" s="65"/>
-      <x:c r="M163" s="65" t="str">
-        <x:v>Real iOS compile uses macOS.</x:v>
+      <x:c r="J163" s="66" t="str">
+        <x:v>Ephemeral Linux sandbox</x:v>
+      </x:c>
+      <x:c r="K163" s="66"/>
+      <x:c r="L163" s="66"/>
+      <x:c r="M163" s="66" t="str">
+        <x:v>Central execution control.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="66" t="str">
-        <x:v>R-159</x:v>
-      </x:c>
-      <x:c r="B164" s="66" t="str">
+      <x:c r="A164" s="65" t="str">
+        <x:v>R-158</x:v>
+      </x:c>
+      <x:c r="B164" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C164" s="66" t="str">
+      <x:c r="C164" s="65" t="str">
         <x:v>CI/CD</x:v>
       </x:c>
-      <x:c r="D164" s="66" t="str">
-        <x:v>Immutable build promotion</x:v>
-      </x:c>
-      <x:c r="E164" s="66" t="str">
-        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
-      </x:c>
-      <x:c r="F164" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G164" s="66"/>
-      <x:c r="H164" s="66" t="str">
+      <x:c r="D164" s="65" t="str">
+        <x:v>Unified PR pipeline</x:v>
+      </x:c>
+      <x:c r="E164" s="65" t="str">
+        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
+      </x:c>
+      <x:c r="F164" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G164" s="65"/>
+      <x:c r="H164" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I164" s="388" t="n">
+      <x:c r="I164" s="389" t="n">
         <x:f>IF(H164="Done",1,IF(H164="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J164" s="66" t="str">
-        <x:v>Deployment Agent</x:v>
-      </x:c>
-      <x:c r="K164" s="66"/>
-      <x:c r="L164" s="66"/>
-      <x:c r="M164" s="66" t="str">
-        <x:v>Reduces preview/production mismatch.</x:v>
+      <x:c r="J164" s="65" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="K164" s="65"/>
+      <x:c r="L164" s="65"/>
+      <x:c r="M164" s="65" t="str">
+        <x:v>Real iOS compile uses macOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="65" t="str">
-        <x:v>R-160</x:v>
-      </x:c>
-      <x:c r="B165" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C165" s="65" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D165" s="65" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="E165" s="65" t="str">
-        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
-      </x:c>
-      <x:c r="F165" s="65" t="str">
+      <x:c r="A165" s="66" t="str">
+        <x:v>R-159</x:v>
+      </x:c>
+      <x:c r="B165" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C165" s="66" t="str">
+        <x:v>CI/CD</x:v>
+      </x:c>
+      <x:c r="D165" s="66" t="str">
+        <x:v>Immutable build promotion</x:v>
+      </x:c>
+      <x:c r="E165" s="66" t="str">
+        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
+      </x:c>
+      <x:c r="F165" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G165" s="65"/>
-      <x:c r="H165" s="65" t="str">
+      <x:c r="G165" s="66"/>
+      <x:c r="H165" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I165" s="389" t="n">
+      <x:c r="I165" s="388" t="n">
         <x:f>IF(H165="Done",1,IF(H165="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J165" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K165" s="65"/>
-      <x:c r="L165" s="65"/>
-      <x:c r="M165" s="65"/>
+      <x:c r="J165" s="66" t="str">
+        <x:v>Deployment Agent</x:v>
+      </x:c>
+      <x:c r="K165" s="66"/>
+      <x:c r="L165" s="66"/>
+      <x:c r="M165" s="66" t="str">
+        <x:v>Reduces preview/production mismatch.</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="66" t="str">
-        <x:v>R-161</x:v>
-      </x:c>
-      <x:c r="B166" s="66" t="str">
+      <x:c r="A166" s="65" t="str">
+        <x:v>R-160</x:v>
+      </x:c>
+      <x:c r="B166" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C166" s="66" t="str">
-        <x:v>Preview</x:v>
-      </x:c>
-      <x:c r="D166" s="66" t="str">
-        <x:v>Local Mac Agent productized</x:v>
-      </x:c>
-      <x:c r="E166" s="66" t="str">
-        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
-      </x:c>
-      <x:c r="F166" s="66" t="str">
+      <x:c r="C166" s="65" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D166" s="65" t="str">
+        <x:v>Framework upgrade workflow</x:v>
+      </x:c>
+      <x:c r="E166" s="65" t="str">
+        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
+      </x:c>
+      <x:c r="F166" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G166" s="66"/>
-      <x:c r="H166" s="66" t="str">
+      <x:c r="G166" s="65"/>
+      <x:c r="H166" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I166" s="388" t="n">
+      <x:c r="I166" s="389" t="n">
         <x:f>IF(H166="Done",1,IF(H166="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J166" s="66" t="str">
-        <x:v>Local Mac Agent</x:v>
-      </x:c>
-      <x:c r="K166" s="66"/>
-      <x:c r="L166" s="66"/>
-      <x:c r="M166" s="66" t="str">
-        <x:v>Reduces cloud Mac cost.</x:v>
-      </x:c>
+      <x:c r="J166" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K166" s="65"/>
+      <x:c r="L166" s="65"/>
+      <x:c r="M166" s="65"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="65" t="str">
-        <x:v>R-162</x:v>
-      </x:c>
-      <x:c r="B167" s="65" t="str">
+      <x:c r="A167" s="66" t="str">
+        <x:v>R-161</x:v>
+      </x:c>
+      <x:c r="B167" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C167" s="65" t="str">
+      <x:c r="C167" s="66" t="str">
         <x:v>Preview</x:v>
       </x:c>
-      <x:c r="D167" s="65" t="str">
-        <x:v>Interactive cloud simulator metering</x:v>
-      </x:c>
-      <x:c r="E167" s="65" t="str">
-        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
-      </x:c>
-      <x:c r="F167" s="65" t="str">
+      <x:c r="D167" s="66" t="str">
+        <x:v>Local Mac Agent productized</x:v>
+      </x:c>
+      <x:c r="E167" s="66" t="str">
+        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
+      </x:c>
+      <x:c r="F167" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G167" s="65"/>
-      <x:c r="H167" s="65" t="str">
+      <x:c r="G167" s="66"/>
+      <x:c r="H167" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I167" s="389" t="n">
+      <x:c r="I167" s="388" t="n">
         <x:f>IF(H167="Done",1,IF(H167="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J167" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K167" s="65"/>
-      <x:c r="L167" s="65"/>
-      <x:c r="M167" s="65" t="str">
-        <x:v>Separate verification build cost from interactive session cost.</x:v>
+      <x:c r="J167" s="66" t="str">
+        <x:v>Local Mac Agent</x:v>
+      </x:c>
+      <x:c r="K167" s="66"/>
+      <x:c r="L167" s="66"/>
+      <x:c r="M167" s="66" t="str">
+        <x:v>Reduces cloud Mac cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="66" t="str">
-        <x:v>R-163</x:v>
-      </x:c>
-      <x:c r="B168" s="66" t="str">
+      <x:c r="A168" s="65" t="str">
+        <x:v>R-162</x:v>
+      </x:c>
+      <x:c r="B168" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C168" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D168" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="E168" s="66" t="str">
-        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
-      </x:c>
-      <x:c r="F168" s="66" t="str">
+      <x:c r="C168" s="65" t="str">
+        <x:v>Preview</x:v>
+      </x:c>
+      <x:c r="D168" s="65" t="str">
+        <x:v>Interactive cloud simulator metering</x:v>
+      </x:c>
+      <x:c r="E168" s="65" t="str">
+        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
+      </x:c>
+      <x:c r="F168" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G168" s="66"/>
-      <x:c r="H168" s="66" t="str">
+      <x:c r="G168" s="65"/>
+      <x:c r="H168" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I168" s="388" t="n">
+      <x:c r="I168" s="389" t="n">
         <x:f>IF(H168="Done",1,IF(H168="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J168" s="66" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K168" s="66"/>
-      <x:c r="L168" s="66"/>
-      <x:c r="M168" s="66" t="str">
-        <x:v>Measure before rewrite.</x:v>
+      <x:c r="J168" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K168" s="65"/>
+      <x:c r="L168" s="65"/>
+      <x:c r="M168" s="65" t="str">
+        <x:v>Separate verification build cost from interactive session cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="65" t="str">
-        <x:v>R-164</x:v>
-      </x:c>
-      <x:c r="B169" s="65" t="str">
+      <x:c r="A169" s="66" t="str">
+        <x:v>R-163</x:v>
+      </x:c>
+      <x:c r="B169" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C169" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D169" s="65" t="str">
-        <x:v>Template/repo health dashboard</x:v>
-      </x:c>
-      <x:c r="E169" s="65" t="str">
-        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
-      </x:c>
-      <x:c r="F169" s="65" t="str">
+      <x:c r="C169" s="66" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D169" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="E169" s="66" t="str">
+        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
+      </x:c>
+      <x:c r="F169" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G169" s="65"/>
-      <x:c r="H169" s="65" t="str">
+      <x:c r="G169" s="66"/>
+      <x:c r="H169" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I169" s="389" t="n">
+      <x:c r="I169" s="388" t="n">
         <x:f>IF(H169="Done",1,IF(H169="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J169" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="K169" s="65"/>
-      <x:c r="L169" s="65"/>
-      <x:c r="M169" s="65" t="str">
-        <x:v>Use data to trigger architecture review.</x:v>
+      <x:c r="J169" s="66" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K169" s="66"/>
+      <x:c r="L169" s="66"/>
+      <x:c r="M169" s="66" t="str">
+        <x:v>Measure before rewrite.</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="66" t="str">
-        <x:v>R-165</x:v>
-      </x:c>
-      <x:c r="B170" s="66" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C170" s="66" t="str">
-        <x:v>Migration</x:v>
-      </x:c>
-      <x:c r="D170" s="66" t="str">
-        <x:v>Cross-platform to native migration engine</x:v>
-      </x:c>
-      <x:c r="E170" s="66" t="str">
-        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
-      </x:c>
-      <x:c r="F170" s="66" t="str">
+      <x:c r="A170" s="65" t="str">
+        <x:v>R-164</x:v>
+      </x:c>
+      <x:c r="B170" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C170" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D170" s="65" t="str">
+        <x:v>Template/repo health dashboard</x:v>
+      </x:c>
+      <x:c r="E170" s="65" t="str">
+        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
+      </x:c>
+      <x:c r="F170" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G170" s="66"/>
-      <x:c r="H170" s="66" t="str">
+      <x:c r="G170" s="65"/>
+      <x:c r="H170" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I170" s="388" t="n">
+      <x:c r="I170" s="389" t="n">
         <x:f>IF(H170="Done",1,IF(H170="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J170" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="K170" s="66"/>
-      <x:c r="L170" s="66"/>
-      <x:c r="M170" s="66" t="str">
-        <x:v>Prevents framework lock-in.</x:v>
+      <x:c r="J170" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="K170" s="65"/>
+      <x:c r="L170" s="65"/>
+      <x:c r="M170" s="65" t="str">
+        <x:v>Use data to trigger architecture review.</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="65" t="str">
-        <x:v>R-166</x:v>
-      </x:c>
-      <x:c r="B171" s="65" t="str">
+      <x:c r="A171" s="66" t="str">
+        <x:v>R-165</x:v>
+      </x:c>
+      <x:c r="B171" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C171" s="65" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D171" s="65" t="str">
-        <x:v>Cross-repo task coordinator</x:v>
-      </x:c>
-      <x:c r="E171" s="65" t="str">
-        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
-      </x:c>
-      <x:c r="F171" s="65" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G171" s="65"/>
-      <x:c r="H171" s="65" t="str">
+      <x:c r="C171" s="66" t="str">
+        <x:v>Migration</x:v>
+      </x:c>
+      <x:c r="D171" s="66" t="str">
+        <x:v>Cross-platform to native migration engine</x:v>
+      </x:c>
+      <x:c r="E171" s="66" t="str">
+        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
+      </x:c>
+      <x:c r="F171" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G171" s="66"/>
+      <x:c r="H171" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I171" s="389" t="n">
+      <x:c r="I171" s="388" t="n">
         <x:f>IF(H171="Done",1,IF(H171="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J171" s="65" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="K171" s="65"/>
-      <x:c r="L171" s="65"/>
-      <x:c r="M171" s="65"/>
+      <x:c r="J171" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="K171" s="66"/>
+      <x:c r="L171" s="66"/>
+      <x:c r="M171" s="66" t="str">
+        <x:v>Prevents framework lock-in.</x:v>
+      </x:c>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="66" t="str">
-        <x:v>R-167</x:v>
-      </x:c>
-      <x:c r="B172" s="66" t="str">
+      <x:c r="A172" s="65" t="str">
+        <x:v>R-166</x:v>
+      </x:c>
+      <x:c r="B172" s="65" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C172" s="66" t="str">
-        <x:v>Infrastructure</x:v>
-      </x:c>
-      <x:c r="D172" s="66" t="str">
-        <x:v>BYOC / private runners</x:v>
-      </x:c>
-      <x:c r="E172" s="66" t="str">
-        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
-      </x:c>
-      <x:c r="F172" s="66" t="str">
+      <x:c r="C172" s="65" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D172" s="65" t="str">
+        <x:v>Cross-repo task coordinator</x:v>
+      </x:c>
+      <x:c r="E172" s="65" t="str">
+        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
+      </x:c>
+      <x:c r="F172" s="65" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G172" s="66"/>
-      <x:c r="H172" s="66" t="str">
+      <x:c r="G172" s="65"/>
+      <x:c r="H172" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I172" s="388" t="n">
+      <x:c r="I172" s="389" t="n">
         <x:f>IF(H172="Done",1,IF(H172="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J172" s="66" t="str">
-        <x:v>Enterprise workload isolation</x:v>
-      </x:c>
-      <x:c r="K172" s="66"/>
-      <x:c r="L172" s="66"/>
-      <x:c r="M172" s="66"/>
+      <x:c r="J172" s="65" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="K172" s="65"/>
+      <x:c r="L172" s="65"/>
+      <x:c r="M172" s="65"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="65" t="str">
-        <x:v>R-168</x:v>
-      </x:c>
-      <x:c r="B173" s="65" t="str">
+      <x:c r="A173" s="66" t="str">
+        <x:v>R-167</x:v>
+      </x:c>
+      <x:c r="B173" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C173" s="65" t="str">
-        <x:v>Testing</x:v>
-      </x:c>
-      <x:c r="D173" s="65" t="str">
-        <x:v>Physical device cloud integration</x:v>
-      </x:c>
-      <x:c r="E173" s="65" t="str">
-        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
-      </x:c>
-      <x:c r="F173" s="65" t="str">
+      <x:c r="C173" s="66" t="str">
+        <x:v>Infrastructure</x:v>
+      </x:c>
+      <x:c r="D173" s="66" t="str">
+        <x:v>BYOC / private runners</x:v>
+      </x:c>
+      <x:c r="E173" s="66" t="str">
+        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
+      </x:c>
+      <x:c r="F173" s="66" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G173" s="65"/>
-      <x:c r="H173" s="65" t="str">
+      <x:c r="G173" s="66"/>
+      <x:c r="H173" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I173" s="389" t="n">
+      <x:c r="I173" s="388" t="n">
         <x:f>IF(H173="Done",1,IF(H173="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J173" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K173" s="65"/>
-      <x:c r="L173" s="65"/>
-      <x:c r="M173" s="65"/>
+      <x:c r="J173" s="66" t="str">
+        <x:v>Enterprise workload isolation</x:v>
+      </x:c>
+      <x:c r="K173" s="66"/>
+      <x:c r="L173" s="66"/>
+      <x:c r="M173" s="66"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="127" t="str">
-        <x:v>R-169</x:v>
-      </x:c>
-      <x:c r="B174" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
-      </x:c>
-      <x:c r="C174" s="127" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D174" s="127" t="str">
-        <x:v>Template support lifecycle</x:v>
-      </x:c>
-      <x:c r="E174" s="127" t="str">
-        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
-      </x:c>
-      <x:c r="F174" s="127" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G174" s="127"/>
-      <x:c r="H174" s="127" t="str">
+      <x:c r="A174" s="65" t="str">
+        <x:v>R-168</x:v>
+      </x:c>
+      <x:c r="B174" s="65" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C174" s="65" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="D174" s="65" t="str">
+        <x:v>Physical device cloud integration</x:v>
+      </x:c>
+      <x:c r="E174" s="65" t="str">
+        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
+      </x:c>
+      <x:c r="F174" s="65" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G174" s="65"/>
+      <x:c r="H174" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I174" s="390" t="n">
+      <x:c r="I174" s="389" t="n">
         <x:f>IF(H174="Done",1,IF(H174="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J174" s="127" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="K174" s="127"/>
-      <x:c r="L174" s="127"/>
-      <x:c r="M174" s="127"/>
+      <x:c r="J174" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K174" s="65"/>
+      <x:c r="L174" s="65"/>
+      <x:c r="M174" s="65"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="127" t="str">
-        <x:v>R-170</x:v>
+        <x:v>R-169</x:v>
       </x:c>
       <x:c r="B175" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C175" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D175" s="127" t="str">
-        <x:v>Framework/toolchain production SLO</x:v>
+        <x:v>Template support lifecycle</x:v>
       </x:c>
       <x:c r="E175" s="127" t="str">
-        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
+        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
       </x:c>
       <x:c r="F175" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G175" s="127"/>
       <x:c r="H175" s="127" t="str">
@@ -16217,29 +16225,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J175" s="127" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="K175" s="127"/>
       <x:c r="L175" s="127"/>
-      <x:c r="M175" s="127" t="str">
-        <x:v>Production readiness is measured, not assumed.</x:v>
-      </x:c>
+      <x:c r="M175" s="127"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="127" t="str">
-        <x:v>R-171</x:v>
+        <x:v>R-170</x:v>
       </x:c>
       <x:c r="B176" s="127" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C176" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D176" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Framework/toolchain production SLO</x:v>
       </x:c>
       <x:c r="E176" s="127" t="str">
-        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
+        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
       </x:c>
       <x:c r="F176" s="127" t="str">
         <x:v>P0</x:v>
@@ -16253,17 +16259,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J176" s="127" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="K176" s="127"/>
       <x:c r="L176" s="127"/>
       <x:c r="M176" s="127" t="str">
-        <x:v>No agent-to-vendor SDK coupling.</x:v>
+        <x:v>Production readiness is measured, not assumed.</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="127" t="str">
-        <x:v>R-172</x:v>
+        <x:v>R-171</x:v>
       </x:c>
       <x:c r="B177" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16272,10 +16278,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D177" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="E177" s="127" t="str">
-        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
+        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
       </x:c>
       <x:c r="F177" s="127" t="str">
         <x:v>P0</x:v>
@@ -16289,17 +16295,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K177" s="127"/>
       <x:c r="L177" s="127"/>
       <x:c r="M177" s="127" t="str">
-        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
+        <x:v>No agent-to-vendor SDK coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="127" t="str">
-        <x:v>R-173</x:v>
+        <x:v>R-172</x:v>
       </x:c>
       <x:c r="B178" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16308,10 +16314,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D178" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="E178" s="127" t="str">
-        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
+        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
       </x:c>
       <x:c r="F178" s="127" t="str">
         <x:v>P0</x:v>
@@ -16330,12 +16336,12 @@
       <x:c r="K178" s="127"/>
       <x:c r="L178" s="127"/>
       <x:c r="M178" s="127" t="str">
-        <x:v>Cheapest safe runtime wins.</x:v>
+        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="127" t="str">
-        <x:v>R-174</x:v>
+        <x:v>R-173</x:v>
       </x:c>
       <x:c r="B179" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16344,13 +16350,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D179" s="127" t="str">
-        <x:v>Browser runtime PoC</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="E179" s="127" t="str">
-        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
+        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
       </x:c>
       <x:c r="F179" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G179" s="127"/>
       <x:c r="H179" s="127" t="str">
@@ -16361,17 +16367,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K179" s="127"/>
       <x:c r="L179" s="127"/>
       <x:c r="M179" s="127" t="str">
-        <x:v>Not universal sandbox.</x:v>
+        <x:v>Cheapest safe runtime wins.</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="127" t="str">
-        <x:v>R-175</x:v>
+        <x:v>R-174</x:v>
       </x:c>
       <x:c r="B180" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16380,13 +16386,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D180" s="127" t="str">
-        <x:v>Runtime quotas and metering</x:v>
+        <x:v>Browser runtime PoC</x:v>
       </x:c>
       <x:c r="E180" s="127" t="str">
-        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
+        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
       </x:c>
       <x:c r="F180" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G180" s="127"/>
       <x:c r="H180" s="127" t="str">
@@ -16397,29 +16403,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="K180" s="127"/>
       <x:c r="L180" s="127"/>
       <x:c r="M180" s="127" t="str">
-        <x:v>Required for cost and abuse control.</x:v>
+        <x:v>Not universal sandbox.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="127" t="str">
-        <x:v>R-176</x:v>
+        <x:v>R-175</x:v>
       </x:c>
       <x:c r="B181" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C181" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D181" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Runtime quotas and metering</x:v>
       </x:c>
       <x:c r="E181" s="127" t="str">
-        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
+        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
       </x:c>
       <x:c r="F181" s="127" t="str">
         <x:v>P0</x:v>
@@ -16433,17 +16439,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="127" t="str">
-        <x:v>Supervisor / orchestrator</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K181" s="127"/>
       <x:c r="L181" s="127"/>
       <x:c r="M181" s="127" t="str">
-        <x:v>Platform-owned state schema.</x:v>
+        <x:v>Required for cost and abuse control.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="127" t="str">
-        <x:v>R-177</x:v>
+        <x:v>R-176</x:v>
       </x:c>
       <x:c r="B182" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16452,10 +16458,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D182" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="E182" s="127" t="str">
-        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
+        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
       </x:c>
       <x:c r="F182" s="127" t="str">
         <x:v>P0</x:v>
@@ -16469,17 +16475,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Supervisor / orchestrator</x:v>
       </x:c>
       <x:c r="K182" s="127"/>
       <x:c r="L182" s="127"/>
       <x:c r="M182" s="127" t="str">
-        <x:v>No full restart by default.</x:v>
+        <x:v>Platform-owned state schema.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="127" t="str">
-        <x:v>R-178</x:v>
+        <x:v>R-177</x:v>
       </x:c>
       <x:c r="B183" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16488,10 +16494,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D183" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="E183" s="127" t="str">
-        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
+        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
       </x:c>
       <x:c r="F183" s="127" t="str">
         <x:v>P0</x:v>
@@ -16505,29 +16511,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K183" s="127"/>
       <x:c r="L183" s="127"/>
       <x:c r="M183" s="127" t="str">
-        <x:v>Prevent duplicate side effects.</x:v>
+        <x:v>No full restart by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="127" t="str">
-        <x:v>R-179</x:v>
+        <x:v>R-178</x:v>
       </x:c>
       <x:c r="B184" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C184" s="127" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D184" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="E184" s="127" t="str">
-        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
+        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
       </x:c>
       <x:c r="F184" s="127" t="str">
         <x:v>P0</x:v>
@@ -16541,29 +16547,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K184" s="127"/>
       <x:c r="L184" s="127"/>
       <x:c r="M184" s="127" t="str">
-        <x:v>Supports replay, audit and debugging.</x:v>
+        <x:v>Prevent duplicate side effects.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="127" t="str">
-        <x:v>R-180</x:v>
+        <x:v>R-179</x:v>
       </x:c>
       <x:c r="B185" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C185" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D185" s="127" t="str">
-        <x:v>Orchestrator Adapter</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="E185" s="127" t="str">
-        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
+        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
       </x:c>
       <x:c r="F185" s="127" t="str">
         <x:v>P0</x:v>
@@ -16582,24 +16588,24 @@
       <x:c r="K185" s="127"/>
       <x:c r="L185" s="127"/>
       <x:c r="M185" s="127" t="str">
-        <x:v>LangGraph may be first implementation.</x:v>
+        <x:v>Supports replay, audit and debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="127" t="str">
-        <x:v>R-181</x:v>
+        <x:v>R-180</x:v>
       </x:c>
       <x:c r="B186" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C186" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D186" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Orchestrator Adapter</x:v>
       </x:c>
       <x:c r="E186" s="127" t="str">
-        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
+        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
       </x:c>
       <x:c r="F186" s="127" t="str">
         <x:v>P0</x:v>
@@ -16613,17 +16619,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K186" s="127"/>
       <x:c r="L186" s="127"/>
       <x:c r="M186" s="127" t="str">
-        <x:v>Frontend never parses provider-specific streams.</x:v>
+        <x:v>LangGraph may be first implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="127" t="str">
-        <x:v>R-182</x:v>
+        <x:v>R-181</x:v>
       </x:c>
       <x:c r="B187" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16632,10 +16638,10 @@
         <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D187" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="E187" s="127" t="str">
-        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
+        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
       </x:c>
       <x:c r="F187" s="127" t="str">
         <x:v>P0</x:v>
@@ -16649,29 +16655,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K187" s="127"/>
       <x:c r="L187" s="127"/>
       <x:c r="M187" s="127" t="str">
-        <x:v>SSE allowed for simple one-way streams.</x:v>
+        <x:v>Frontend never parses provider-specific streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="127" t="str">
-        <x:v>R-183</x:v>
+        <x:v>R-182</x:v>
       </x:c>
       <x:c r="B188" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C188" s="127" t="str">
-        <x:v>Approvals</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D188" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="E188" s="127" t="str">
-        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
+        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
       </x:c>
       <x:c r="F188" s="127" t="str">
         <x:v>P0</x:v>
@@ -16685,17 +16691,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="K188" s="127"/>
       <x:c r="L188" s="127"/>
       <x:c r="M188" s="127" t="str">
-        <x:v>Approval based on risk.</x:v>
+        <x:v>SSE allowed for simple one-way streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="127" t="str">
-        <x:v>R-184</x:v>
+        <x:v>R-183</x:v>
       </x:c>
       <x:c r="B189" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16704,10 +16710,10 @@
         <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D189" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="E189" s="127" t="str">
-        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
+        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
       </x:c>
       <x:c r="F189" s="127" t="str">
         <x:v>P0</x:v>
@@ -16721,29 +16727,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K189" s="127"/>
       <x:c r="L189" s="127"/>
       <x:c r="M189" s="127" t="str">
-        <x:v>Production/destructive actions auditable.</x:v>
+        <x:v>Approval based on risk.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="127" t="str">
-        <x:v>R-185</x:v>
+        <x:v>R-184</x:v>
       </x:c>
       <x:c r="B190" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C190" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D190" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="E190" s="127" t="str">
-        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
+        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
       </x:c>
       <x:c r="F190" s="127" t="str">
         <x:v>P0</x:v>
@@ -16757,17 +16763,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="K190" s="127"/>
       <x:c r="L190" s="127"/>
       <x:c r="M190" s="127" t="str">
-        <x:v>Deny by default.</x:v>
+        <x:v>Production/destructive actions auditable.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="127" t="str">
-        <x:v>R-186</x:v>
+        <x:v>R-185</x:v>
       </x:c>
       <x:c r="B191" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16776,13 +16782,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D191" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="E191" s="127" t="str">
-        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
+        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
       </x:c>
       <x:c r="F191" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G191" s="127"/>
       <x:c r="H191" s="127" t="str">
@@ -16793,17 +16799,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K191" s="127"/>
       <x:c r="L191" s="127"/>
       <x:c r="M191" s="127" t="str">
-        <x:v>No arbitrary agent-to-MCP connections.</x:v>
+        <x:v>Deny by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="127" t="str">
-        <x:v>R-187</x:v>
+        <x:v>R-186</x:v>
       </x:c>
       <x:c r="B192" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16812,13 +16818,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D192" s="127" t="str">
-        <x:v>Tool secret broker</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="E192" s="127" t="str">
-        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
+        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
       </x:c>
       <x:c r="F192" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G192" s="127"/>
       <x:c r="H192" s="127" t="str">
@@ -16834,27 +16840,27 @@
       <x:c r="K192" s="127"/>
       <x:c r="L192" s="127"/>
       <x:c r="M192" s="127" t="str">
-        <x:v>Audit every secret grant.</x:v>
+        <x:v>No arbitrary agent-to-MCP connections.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="127" t="str">
-        <x:v>R-188</x:v>
+        <x:v>R-187</x:v>
       </x:c>
       <x:c r="B193" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C193" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D193" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Tool secret broker</x:v>
       </x:c>
       <x:c r="E193" s="127" t="str">
-        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
+        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
       </x:c>
       <x:c r="F193" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G193" s="127"/>
       <x:c r="H193" s="127" t="str">
@@ -16865,32 +16871,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="127" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="K193" s="127"/>
       <x:c r="L193" s="127"/>
       <x:c r="M193" s="127" t="str">
-        <x:v>Not platform core.</x:v>
+        <x:v>Audit every secret grant.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="127" t="str">
-        <x:v>R-189</x:v>
+        <x:v>R-188</x:v>
       </x:c>
       <x:c r="B194" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C194" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D194" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="E194" s="127" t="str">
-        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
+        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
       </x:c>
       <x:c r="F194" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G194" s="127"/>
       <x:c r="H194" s="127" t="str">
@@ -16901,29 +16907,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="127" t="str">
-        <x:v>Architecture decision records</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K194" s="127"/>
       <x:c r="L194" s="127"/>
       <x:c r="M194" s="127" t="str">
-        <x:v>References inform; benchmarks decide.</x:v>
+        <x:v>Not platform core.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="127" t="str">
-        <x:v>R-190</x:v>
+        <x:v>R-189</x:v>
       </x:c>
       <x:c r="B195" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C195" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D195" s="127" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="E195" s="127" t="str">
-        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
+        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
       </x:c>
       <x:c r="F195" s="127" t="str">
         <x:v>P0</x:v>
@@ -16937,32 +16943,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J195" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Architecture decision records</x:v>
       </x:c>
       <x:c r="K195" s="127"/>
       <x:c r="L195" s="127"/>
       <x:c r="M195" s="127" t="str">
-        <x:v>Architectural learning != code copying.</x:v>
+        <x:v>References inform; benchmarks decide.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="127" t="str">
-        <x:v>R-191</x:v>
+        <x:v>R-190</x:v>
       </x:c>
       <x:c r="B196" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C196" s="127" t="str">
-        <x:v>Team</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D196" s="127" t="str">
-        <x:v>Shared engineering glossary</x:v>
+        <x:v>Open-source license review</x:v>
       </x:c>
       <x:c r="E196" s="127" t="str">
-        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
+        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
       </x:c>
       <x:c r="F196" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G196" s="127"/>
       <x:c r="H196" s="127" t="str">
@@ -16972,31 +16978,33 @@
         <x:f>IF(H196="Done",1,IF(H196="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J196" s="127"/>
+      <x:c r="J196" s="127" t="str">
+        <x:v>Build-vs-Buy benchmark process</x:v>
+      </x:c>
       <x:c r="K196" s="127"/>
       <x:c r="L196" s="127"/>
       <x:c r="M196" s="127" t="str">
-        <x:v>Use in docs and AI prompts.</x:v>
+        <x:v>Architectural learning != code copying.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="127" t="str">
-        <x:v>R-192</x:v>
+        <x:v>R-191</x:v>
       </x:c>
       <x:c r="B197" s="127" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C197" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Team</x:v>
       </x:c>
       <x:c r="D197" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Shared engineering glossary</x:v>
       </x:c>
       <x:c r="E197" s="127" t="str">
-        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
+        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
       </x:c>
       <x:c r="F197" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G197" s="127"/>
       <x:c r="H197" s="127" t="str">
@@ -17006,30 +17014,28 @@
         <x:f>IF(H197="Done",1,IF(H197="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J197" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
-      </x:c>
+      <x:c r="J197" s="127"/>
       <x:c r="K197" s="127"/>
       <x:c r="L197" s="127"/>
       <x:c r="M197" s="127" t="str">
-        <x:v>Marketplace later.</x:v>
+        <x:v>Use in docs and AI prompts.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="127" t="str">
-        <x:v>R-193</x:v>
+        <x:v>R-192</x:v>
       </x:c>
       <x:c r="B198" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C198" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D198" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="E198" s="127" t="str">
-        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
+        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
       </x:c>
       <x:c r="F198" s="127" t="str">
         <x:v>P1</x:v>
@@ -17043,17 +17049,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J198" s="127" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K198" s="127"/>
       <x:c r="L198" s="127"/>
       <x:c r="M198" s="127" t="str">
-        <x:v>Extends local mode beyond Mac.</x:v>
+        <x:v>Marketplace later.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="127" t="str">
-        <x:v>R-194</x:v>
+        <x:v>R-193</x:v>
       </x:c>
       <x:c r="B199" s="127" t="str">
         <x:v>MID</x:v>
@@ -17062,10 +17068,10 @@
         <x:v>Execution</x:v>
       </x:c>
       <x:c r="D199" s="127" t="str">
-        <x:v>Hybrid BYOK/local mode</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="E199" s="127" t="str">
-        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
+        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
       </x:c>
       <x:c r="F199" s="127" t="str">
         <x:v>P1</x:v>
@@ -17079,29 +17085,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J199" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="K199" s="127"/>
       <x:c r="L199" s="127"/>
       <x:c r="M199" s="127" t="str">
-        <x:v>Privacy + cost option.</x:v>
+        <x:v>Extends local mode beyond Mac.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="127" t="str">
-        <x:v>R-195</x:v>
+        <x:v>R-194</x:v>
       </x:c>
       <x:c r="B200" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C200" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D200" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Hybrid BYOK/local mode</x:v>
       </x:c>
       <x:c r="E200" s="127" t="str">
-        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
+        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
       </x:c>
       <x:c r="F200" s="127" t="str">
         <x:v>P1</x:v>
@@ -17115,17 +17121,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K200" s="127"/>
       <x:c r="L200" s="127"/>
       <x:c r="M200" s="127" t="str">
-        <x:v>Validate portability/failover.</x:v>
+        <x:v>Privacy + cost option.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="127" t="str">
-        <x:v>R-196</x:v>
+        <x:v>R-195</x:v>
       </x:c>
       <x:c r="B201" s="127" t="str">
         <x:v>MID</x:v>
@@ -17134,13 +17140,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D201" s="127" t="str">
-        <x:v>Sandbox snapshots and warm pools</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="E201" s="127" t="str">
-        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
+        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
       </x:c>
       <x:c r="F201" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G201" s="127"/>
       <x:c r="H201" s="127" t="str">
@@ -17151,32 +17157,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K201" s="127"/>
       <x:c r="L201" s="127"/>
       <x:c r="M201" s="127" t="str">
-        <x:v>Do not optimize blindly.</x:v>
+        <x:v>Validate portability/failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="127" t="str">
-        <x:v>R-197</x:v>
+        <x:v>R-196</x:v>
       </x:c>
       <x:c r="B202" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C202" s="127" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D202" s="127" t="str">
-        <x:v>Agent time-travel debugging</x:v>
+        <x:v>Sandbox snapshots and warm pools</x:v>
       </x:c>
       <x:c r="E202" s="127" t="str">
-        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
+        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
       </x:c>
       <x:c r="F202" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G202" s="127"/>
       <x:c r="H202" s="127" t="str">
@@ -17187,32 +17193,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K202" s="127"/>
       <x:c r="L202" s="127"/>
       <x:c r="M202" s="127" t="str">
-        <x:v>Operator and developer debugging.</x:v>
+        <x:v>Do not optimize blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="127" t="str">
-        <x:v>R-198</x:v>
+        <x:v>R-197</x:v>
       </x:c>
       <x:c r="B203" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C203" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D203" s="127" t="str">
-        <x:v>Tool marketplace verification</x:v>
+        <x:v>Agent time-travel debugging</x:v>
       </x:c>
       <x:c r="E203" s="127" t="str">
-        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
+        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
       </x:c>
       <x:c r="F203" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G203" s="127"/>
       <x:c r="H203" s="127" t="str">
@@ -17223,32 +17229,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K203" s="127"/>
       <x:c r="L203" s="127"/>
       <x:c r="M203" s="127" t="str">
-        <x:v>Verified badge is evidence-based.</x:v>
+        <x:v>Operator and developer debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="127" t="str">
-        <x:v>R-199</x:v>
+        <x:v>R-198</x:v>
       </x:c>
       <x:c r="B204" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C204" s="127" t="str">
-        <x:v>Routing</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D204" s="127" t="str">
-        <x:v>Runtime provider cost-latency routing</x:v>
+        <x:v>Tool marketplace verification</x:v>
       </x:c>
       <x:c r="E204" s="127" t="str">
-        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
+        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
       </x:c>
       <x:c r="F204" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G204" s="127"/>
       <x:c r="H204" s="127" t="str">
@@ -17259,32 +17265,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K204" s="127"/>
       <x:c r="L204" s="127"/>
       <x:c r="M204" s="127" t="str">
-        <x:v>Policy can override cheapest route.</x:v>
+        <x:v>Verified badge is evidence-based.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="127" t="str">
-        <x:v>R-200</x:v>
+        <x:v>R-199</x:v>
       </x:c>
       <x:c r="B205" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C205" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="D205" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Runtime provider cost-latency routing</x:v>
       </x:c>
       <x:c r="E205" s="127" t="str">
-        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
+        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
       </x:c>
       <x:c r="F205" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G205" s="127"/>
       <x:c r="H205" s="127" t="str">
@@ -17295,29 +17301,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K205" s="127"/>
       <x:c r="L205" s="127"/>
       <x:c r="M205" s="127" t="str">
-        <x:v>Keep portability via IR/contracts.</x:v>
+        <x:v>Policy can override cheapest route.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="127" t="str">
-        <x:v>R-201</x:v>
+        <x:v>R-200</x:v>
       </x:c>
       <x:c r="B206" s="127" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C206" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D206" s="127" t="str">
-        <x:v>Customer private MCP servers</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="E206" s="127" t="str">
-        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
+        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
       </x:c>
       <x:c r="F206" s="127" t="str">
         <x:v>P2</x:v>
@@ -17331,32 +17337,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="K206" s="127"/>
       <x:c r="L206" s="127"/>
       <x:c r="M206" s="127" t="str">
-        <x:v>Enterprise feature.</x:v>
+        <x:v>Keep portability via IR/contracts.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="127" t="str">
-        <x:v>R-202</x:v>
+        <x:v>R-201</x:v>
       </x:c>
       <x:c r="B207" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C207" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D207" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>Customer private MCP servers</x:v>
       </x:c>
       <x:c r="E207" s="127" t="str">
-        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
+        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
       </x:c>
       <x:c r="F207" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G207" s="127"/>
       <x:c r="H207" s="127" t="str">
@@ -17367,32 +17373,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="127" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K207" s="127"/>
       <x:c r="L207" s="127"/>
       <x:c r="M207" s="127" t="str">
-        <x:v>Central policy + audit remain.</x:v>
+        <x:v>Enterprise feature.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="127" t="str">
-        <x:v>R-203</x:v>
+        <x:v>R-202</x:v>
       </x:c>
       <x:c r="B208" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C208" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D208" s="127" t="str">
-        <x:v>Cross-region runtime scheduler</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="E208" s="127" t="str">
-        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
+        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
       </x:c>
       <x:c r="F208" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G208" s="127"/>
       <x:c r="H208" s="127" t="str">
@@ -17403,17 +17409,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="K208" s="127"/>
       <x:c r="L208" s="127"/>
       <x:c r="M208" s="127" t="str">
-        <x:v>Enterprise scale.</x:v>
+        <x:v>Central policy + audit remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="127" t="str">
-        <x:v>R-204</x:v>
+        <x:v>R-203</x:v>
       </x:c>
       <x:c r="B209" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17422,10 +17428,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D209" s="127" t="str">
-        <x:v>Hardened microVM runner fleet</x:v>
+        <x:v>Cross-region runtime scheduler</x:v>
       </x:c>
       <x:c r="E209" s="127" t="str">
-        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
+        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
       </x:c>
       <x:c r="F209" s="127" t="str">
         <x:v>P2</x:v>
@@ -17439,32 +17445,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="127" t="str">
-        <x:v>Provider cost-latency routing</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="K209" s="127"/>
       <x:c r="L209" s="127"/>
       <x:c r="M209" s="127" t="str">
-        <x:v>Do not build before benchmark.</x:v>
+        <x:v>Enterprise scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="127" t="str">
-        <x:v>R-205</x:v>
+        <x:v>R-204</x:v>
       </x:c>
       <x:c r="B210" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C210" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D210" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>Hardened microVM runner fleet</x:v>
       </x:c>
       <x:c r="E210" s="127" t="str">
-        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
+        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
       </x:c>
       <x:c r="F210" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G210" s="127"/>
       <x:c r="H210" s="127" t="str">
@@ -17475,29 +17481,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Provider cost-latency routing</x:v>
       </x:c>
       <x:c r="K210" s="127"/>
       <x:c r="L210" s="127"/>
       <x:c r="M210" s="127" t="str">
-        <x:v>Checkpoint-aware failover.</x:v>
+        <x:v>Do not build before benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="127" t="str">
-        <x:v>R-206</x:v>
+        <x:v>R-205</x:v>
       </x:c>
       <x:c r="B211" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C211" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D211" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="E211" s="127" t="str">
-        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
+        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
       </x:c>
       <x:c r="F211" s="127" t="str">
         <x:v>P1</x:v>
@@ -17511,17 +17517,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K211" s="127"/>
       <x:c r="L211" s="127"/>
       <x:c r="M211" s="127" t="str">
-        <x:v>Enterprise override support.</x:v>
+        <x:v>Checkpoint-aware failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="127" t="str">
-        <x:v>R-207</x:v>
+        <x:v>R-206</x:v>
       </x:c>
       <x:c r="B212" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17530,13 +17536,13 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D212" s="127" t="str">
-        <x:v>Two-person critical approval</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="E212" s="127" t="str">
-        <x:v>Optional dual approval for L4 actions.</x:v>
+        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
       </x:c>
       <x:c r="F212" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G212" s="127"/>
       <x:c r="H212" s="127" t="str">
@@ -17547,29 +17553,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K212" s="127"/>
       <x:c r="L212" s="127"/>
       <x:c r="M212" s="127" t="str">
-        <x:v>High-risk enterprise.</x:v>
+        <x:v>Enterprise override support.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="127" t="str">
-        <x:v>R-208</x:v>
+        <x:v>R-207</x:v>
       </x:c>
       <x:c r="B213" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C213" s="127" t="str">
-        <x:v>Models</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D213" s="127" t="str">
-        <x:v>Customer private model endpoints</x:v>
+        <x:v>Two-person critical approval</x:v>
       </x:c>
       <x:c r="E213" s="127" t="str">
-        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
+        <x:v>Optional dual approval for L4 actions.</x:v>
       </x:c>
       <x:c r="F213" s="127" t="str">
         <x:v>P2</x:v>
@@ -17583,29 +17589,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="127" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="K213" s="127"/>
       <x:c r="L213" s="127"/>
       <x:c r="M213" s="127" t="str">
-        <x:v>No direct client-to-model coupling.</x:v>
+        <x:v>High-risk enterprise.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="127" t="str">
-        <x:v>R-209</x:v>
+        <x:v>R-208</x:v>
       </x:c>
       <x:c r="B214" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C214" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D214" s="127" t="str">
-        <x:v>Automated provider benchmark suite</x:v>
+        <x:v>Customer private model endpoints</x:v>
       </x:c>
       <x:c r="E214" s="127" t="str">
-        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
+        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
       </x:c>
       <x:c r="F214" s="127" t="str">
         <x:v>P2</x:v>
@@ -17619,32 +17625,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="K214" s="127"/>
       <x:c r="L214" s="127"/>
       <x:c r="M214" s="127" t="str">
-        <x:v>Feeds routing/ADR reviews.</x:v>
+        <x:v>No direct client-to-model coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="127" t="str">
-        <x:v>R-210</x:v>
+        <x:v>R-209</x:v>
       </x:c>
       <x:c r="B215" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C215" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D215" s="127" t="str">
-        <x:v>Crash-resume production test</x:v>
+        <x:v>Automated provider benchmark suite</x:v>
       </x:c>
       <x:c r="E215" s="127" t="str">
-        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
+        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
       </x:c>
       <x:c r="F215" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G215" s="127"/>
       <x:c r="H215" s="127" t="str">
@@ -17655,17 +17661,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="K215" s="127"/>
       <x:c r="L215" s="127"/>
       <x:c r="M215" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Feeds routing/ADR reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="127" t="str">
-        <x:v>R-211</x:v>
+        <x:v>R-210</x:v>
       </x:c>
       <x:c r="B216" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17674,10 +17680,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D216" s="127" t="str">
-        <x:v>Duplicate side-effect prevention test</x:v>
+        <x:v>Crash-resume production test</x:v>
       </x:c>
       <x:c r="E216" s="127" t="str">
-        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
+        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
       </x:c>
       <x:c r="F216" s="127" t="str">
         <x:v>P0</x:v>
@@ -17691,7 +17697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K216" s="127"/>
       <x:c r="L216" s="127"/>
@@ -17701,19 +17707,19 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="127" t="str">
-        <x:v>R-212</x:v>
+        <x:v>R-211</x:v>
       </x:c>
       <x:c r="B217" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C217" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D217" s="127" t="str">
-        <x:v>WebSocket replay correctness SLO</x:v>
+        <x:v>Duplicate side-effect prevention test</x:v>
       </x:c>
       <x:c r="E217" s="127" t="str">
-        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
+        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
       </x:c>
       <x:c r="F217" s="127" t="str">
         <x:v>P0</x:v>
@@ -17727,7 +17733,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K217" s="127"/>
       <x:c r="L217" s="127"/>
@@ -17737,19 +17743,19 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="127" t="str">
-        <x:v>R-213</x:v>
+        <x:v>R-212</x:v>
       </x:c>
       <x:c r="B218" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C218" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D218" s="127" t="str">
-        <x:v>MCP isolation and prompt-injection test</x:v>
+        <x:v>WebSocket replay correctness SLO</x:v>
       </x:c>
       <x:c r="E218" s="127" t="str">
-        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
+        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
       </x:c>
       <x:c r="F218" s="127" t="str">
         <x:v>P0</x:v>
@@ -17763,7 +17769,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="K218" s="127"/>
       <x:c r="L218" s="127"/>
@@ -17773,7 +17779,7 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="127" t="str">
-        <x:v>R-214</x:v>
+        <x:v>R-213</x:v>
       </x:c>
       <x:c r="B219" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17782,10 +17788,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D219" s="127" t="str">
-        <x:v>Sandbox tenant isolation test</x:v>
+        <x:v>MCP isolation and prompt-injection test</x:v>
       </x:c>
       <x:c r="E219" s="127" t="str">
-        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
+        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
       </x:c>
       <x:c r="F219" s="127" t="str">
         <x:v>P0</x:v>
@@ -17799,7 +17805,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K219" s="127"/>
       <x:c r="L219" s="127"/>
@@ -17809,19 +17815,19 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="127" t="str">
-        <x:v>R-215</x:v>
+        <x:v>R-214</x:v>
       </x:c>
       <x:c r="B220" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C220" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D220" s="127" t="str">
-        <x:v>Runtime provider outage failover</x:v>
+        <x:v>Sandbox tenant isolation test</x:v>
       </x:c>
       <x:c r="E220" s="127" t="str">
-        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
+        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
       </x:c>
       <x:c r="F220" s="127" t="str">
         <x:v>P0</x:v>
@@ -17835,7 +17841,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K220" s="127"/>
       <x:c r="L220" s="127"/>
@@ -17845,19 +17851,19 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="127" t="str">
-        <x:v>R-216</x:v>
+        <x:v>R-215</x:v>
       </x:c>
       <x:c r="B221" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C221" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D221" s="127" t="str">
-        <x:v>Approval auditability test</x:v>
+        <x:v>Runtime provider outage failover</x:v>
       </x:c>
       <x:c r="E221" s="127" t="str">
-        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
+        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
       </x:c>
       <x:c r="F221" s="127" t="str">
         <x:v>P0</x:v>
@@ -17871,7 +17877,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="K221" s="127"/>
       <x:c r="L221" s="127"/>
@@ -17881,22 +17887,22 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="127" t="str">
-        <x:v>R-217</x:v>
+        <x:v>R-216</x:v>
       </x:c>
       <x:c r="B222" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C222" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D222" s="127" t="str">
-        <x:v>BaaS to custom migration test</x:v>
+        <x:v>Approval auditability test</x:v>
       </x:c>
       <x:c r="E222" s="127" t="str">
-        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
       </x:c>
       <x:c r="F222" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G222" s="127"/>
       <x:c r="H222" s="127" t="str">
@@ -17907,65 +17913,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K222" s="127"/>
       <x:c r="L222" s="127"/>
       <x:c r="M222" s="127" t="str">
-        <x:v>Avoid backend lock-in.</x:v>
+        <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
-      <x:c r="A223" t="str">
-        <x:v>R-218</x:v>
-      </x:c>
-      <x:c r="B223" t="str">
+      <x:c r="A223" s="127" t="str">
+        <x:v>R-217</x:v>
+      </x:c>
+      <x:c r="B223" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C223" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="D223" t="str">
-        <x:v>Local Agent security lifecycle</x:v>
-      </x:c>
-      <x:c r="E223" t="str">
-        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
-      </x:c>
-      <x:c r="F223" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G223"/>
-      <x:c r="H223" t="str">
+      <x:c r="C223" s="127" t="str">
+        <x:v>Backend Strategy</x:v>
+      </x:c>
+      <x:c r="D223" s="127" t="str">
+        <x:v>BaaS to custom migration test</x:v>
+      </x:c>
+      <x:c r="E223" s="127" t="str">
+        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+      </x:c>
+      <x:c r="F223" s="127" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G223" s="127"/>
+      <x:c r="H223" s="127" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I223" t="n">
+      <x:c r="I223" s="390" t="n">
         <x:f>IF(H223="Done",1,IF(H223="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J223" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
-      </x:c>
-      <x:c r="K223"/>
-      <x:c r="L223"/>
-      <x:c r="M223" t="str">
-        <x:v>Production gate.</x:v>
+      <x:c r="J223" s="127" t="str">
+        <x:v>BaaS provider expansion</x:v>
+      </x:c>
+      <x:c r="K223" s="127"/>
+      <x:c r="L223" s="127"/>
+      <x:c r="M223" s="127" t="str">
+        <x:v>Avoid backend lock-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" t="str">
-        <x:v>R-219</x:v>
+        <x:v>R-218</x:v>
       </x:c>
       <x:c r="B224" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C224" t="str">
-        <x:v>Compliance</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D224" t="str">
-        <x:v>OSS license and SBOM gate</x:v>
+        <x:v>Local Agent security lifecycle</x:v>
       </x:c>
       <x:c r="E224" t="str">
-        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
       </x:c>
       <x:c r="F224" t="str">
         <x:v>P0</x:v>
@@ -17979,11 +17985,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K224"/>
       <x:c r="L224"/>
       <x:c r="M224" t="str">
+        <x:v>Production gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" t="str">
+        <x:v>R-219</x:v>
+      </x:c>
+      <x:c r="B225" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>Compliance</x:v>
+      </x:c>
+      <x:c r="D225" t="str">
+        <x:v>OSS license and SBOM gate</x:v>
+      </x:c>
+      <x:c r="E225" t="str">
+        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+      </x:c>
+      <x:c r="F225" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G225"/>
+      <x:c r="H225" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="I225" t="n">
+        <x:f>IF(H225="Done",1,IF(H225="In Progress",0.5,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J225" t="str">
+        <x:v>Open-source license review</x:v>
+      </x:c>
+      <x:c r="K225"/>
+      <x:c r="L225"/>
+      <x:c r="M225" t="str">
         <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
@@ -17992,7 +18034,7 @@
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H4:H113">
+  <x:conditionalFormatting sqref="H4:H114">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>H4="Done"</x:formula>
     </x:cfRule>
@@ -18007,34 +18049,34 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="10">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B113">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B114">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F113">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F114">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H113">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H114">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B114:B137">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B115:B138">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F114:F137">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F115:F138">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H114:H137">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H115:H138">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F138:F173">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F139:F174">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H138:H173">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H139:H174">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H222">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H223">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F222">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F223">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -10662,11 +10662,11 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-006</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation in progress on ai/R-007-balanced-model-gateway; deterministic Balanced router and 14 offline gateway tests added; local_calls=0, cloud_calls=0.</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); deterministic routing, local_calls=0, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); deterministic routing, local_calls=0, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2389,7 +2389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M114" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M115" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -2701,11 +2701,11 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"MVP")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"MVP")</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"MVP",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"MVP",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"MID",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"MID",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,7 +2746,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F6)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"ADVANCED",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"ADVANCED",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$225,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$225,"PRODUCTION",Phase_Roadmap!$H$4:$H$225,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"PRODUCTION",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F8)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$225,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -10641,7 +10641,7 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10650,10 +10650,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Balanced Model Gateway router</x:v>
+        <x:v>Cloud API-key provider adapters</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
+        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
@@ -10662,28 +10662,28 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation in progress on ai/R-008-cloud-provider-adapters; multi-provider cloud adapters + env bootstrap + offline tests added; no cloud key set, cloud_calls=0.</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
+        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10692,16 +10692,16 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>Loopback Ollama provider adapter</x:v>
+        <x:v>Balanced Model Gateway router</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
+        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G10" s="32" t="str">
-        <x:v>Codex</x:v>
+        <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H10" s="32" t="str">
         <x:v>Done</x:v>
@@ -10711,21 +10711,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10734,10 +10734,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
@@ -10753,33 +10753,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C12" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
@@ -10795,33 +10795,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
@@ -10837,33 +10837,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
@@ -10879,33 +10879,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K14" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L14" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M14" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C15" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
@@ -10921,53 +10921,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K15" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L15" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M15" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C16" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G16" s="32"/>
+      <x:c r="G16" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H16" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I16" s="376" t="n">
         <x:f>IF(H16="Done",1,IF(H16="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="32"/>
-      <x:c r="K16" s="32"/>
-      <x:c r="L16" s="32"/>
-      <x:c r="M16" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K16" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L16" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M16" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10976,10 +10986,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
@@ -10999,7 +11009,7 @@
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11008,10 +11018,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
@@ -11031,7 +11041,7 @@
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11040,10 +11050,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
@@ -11063,7 +11073,7 @@
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11072,10 +11082,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
@@ -11095,7 +11105,7 @@
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11104,10 +11114,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11127,19 +11137,19 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C22" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11159,7 +11169,7 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11168,10 +11178,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11191,19 +11201,19 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C24" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11223,7 +11233,7 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11232,10 +11242,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11255,19 +11265,19 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C26" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11287,19 +11297,19 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C27" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11319,7 +11329,7 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11328,10 +11338,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11351,19 +11361,19 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C29" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11383,7 +11393,7 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11392,10 +11402,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11415,7 +11425,7 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11424,10 +11434,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11447,19 +11457,19 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C32" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11479,7 +11489,7 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11488,10 +11498,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11511,7 +11521,7 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11520,10 +11530,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11543,7 +11553,7 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11552,10 +11562,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11575,7 +11585,7 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11584,10 +11594,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11607,19 +11617,19 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C37" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11639,7 +11649,7 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11648,10 +11658,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11671,19 +11681,19 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C39" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11703,7 +11713,7 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11712,10 +11722,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11735,19 +11745,19 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C41" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11767,19 +11777,19 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C42" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11799,19 +11809,19 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C43" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11831,7 +11841,7 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11840,10 +11850,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11863,7 +11873,7 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11872,10 +11882,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11895,7 +11905,7 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11904,10 +11914,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11927,19 +11937,19 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C47" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11959,7 +11969,7 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11968,10 +11978,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -11991,19 +12001,19 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C49" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12023,7 +12033,7 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12032,10 +12042,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12055,19 +12065,19 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C51" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12087,7 +12097,7 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12096,10 +12106,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12119,7 +12129,7 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12128,10 +12138,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12151,19 +12161,19 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C54" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12183,7 +12193,7 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12192,10 +12202,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12215,7 +12225,7 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12224,10 +12234,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
         <x:v>P0</x:v>
@@ -12247,19 +12257,19 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C57" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
         <x:v>P0</x:v>
@@ -12279,22 +12289,22 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C58" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G58" s="32"/>
       <x:c r="H58" s="32" t="str">
@@ -12311,7 +12321,7 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
         <x:v>MID</x:v>
@@ -12320,10 +12330,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
         <x:v>P1</x:v>
@@ -12343,19 +12353,19 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C60" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
         <x:v>P1</x:v>
@@ -12375,19 +12385,19 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C61" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
         <x:v>P1</x:v>
@@ -12407,7 +12417,7 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
         <x:v>MID</x:v>
@@ -12416,10 +12426,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
         <x:v>P1</x:v>
@@ -12439,19 +12449,19 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C63" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12471,19 +12481,19 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C64" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12503,19 +12513,19 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C65" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12535,7 +12545,7 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
@@ -12544,10 +12554,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12567,19 +12577,19 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C67" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12599,7 +12609,7 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
@@ -12608,10 +12618,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12631,7 +12641,7 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
@@ -12640,10 +12650,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12663,19 +12673,19 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C70" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12695,7 +12705,7 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
@@ -12704,10 +12714,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12727,19 +12737,19 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C72" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12759,19 +12769,19 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C73" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12791,19 +12801,19 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C74" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12823,19 +12833,19 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C75" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12855,7 +12865,7 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
@@ -12864,10 +12874,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12887,7 +12897,7 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
@@ -12896,10 +12906,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12919,19 +12929,19 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C78" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12951,7 +12961,7 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
@@ -12960,10 +12970,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -12983,19 +12993,19 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C80" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -13015,19 +13025,19 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C81" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
         <x:v>P1</x:v>
@@ -13047,19 +13057,19 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C82" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
         <x:v>P1</x:v>
@@ -13079,22 +13089,22 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C83" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G83" s="32"/>
       <x:c r="H83" s="32" t="str">
@@ -13111,7 +13121,7 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13120,13 +13130,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G84" s="32"/>
       <x:c r="H84" s="32" t="str">
@@ -13143,22 +13153,22 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C85" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G85" s="32"/>
       <x:c r="H85" s="32" t="str">
@@ -13175,7 +13185,7 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13184,10 +13194,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
         <x:v>P2</x:v>
@@ -13207,19 +13217,19 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C87" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
         <x:v>P2</x:v>
@@ -13239,19 +13249,19 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C88" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
         <x:v>P2</x:v>
@@ -13271,19 +13281,19 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C89" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
         <x:v>P2</x:v>
@@ -13303,7 +13313,7 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13312,10 +13322,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13335,19 +13345,19 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C91" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13367,7 +13377,7 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13376,10 +13386,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13399,7 +13409,7 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13408,10 +13418,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13431,19 +13441,19 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C94" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13463,7 +13473,7 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13472,10 +13482,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13495,19 +13505,19 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C96" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13527,19 +13537,19 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C97" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13559,7 +13569,7 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13568,10 +13578,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
         <x:v>P2</x:v>
@@ -13591,19 +13601,19 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-093</x:v>
+        <x:v>R-092</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C99" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>Quality trend analytics</x:v>
+        <x:v>Spot/preemptible optimization</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
+        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
         <x:v>P2</x:v>
@@ -13623,22 +13633,22 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-094</x:v>
+        <x:v>R-093</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C100" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>SLO/SLA framework</x:v>
+        <x:v>Quality trend analytics</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
+        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G100" s="32"/>
       <x:c r="H100" s="32" t="str">
@@ -13655,7 +13665,7 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-095</x:v>
+        <x:v>R-094</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13664,10 +13674,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>HA control plane</x:v>
+        <x:v>SLO/SLA framework</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
+        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
         <x:v>P0</x:v>
@@ -13687,7 +13697,7 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-096</x:v>
+        <x:v>R-095</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13696,10 +13706,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>Backup + restore drills</x:v>
+        <x:v>HA control plane</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>Automated backups plus regularly tested restoration.</x:v>
+        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
         <x:v>P0</x:v>
@@ -13719,7 +13729,7 @@
     </x:row>
     <x:row r="103" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A103" s="32" t="str">
-        <x:v>R-097</x:v>
+        <x:v>R-096</x:v>
       </x:c>
       <x:c r="B103" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13728,10 +13738,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D103" s="32" t="str">
-        <x:v>Disaster recovery</x:v>
+        <x:v>Backup + restore drills</x:v>
       </x:c>
       <x:c r="E103" s="32" t="str">
-        <x:v>Document and exercise regional recovery procedures.</x:v>
+        <x:v>Automated backups plus regularly tested restoration.</x:v>
       </x:c>
       <x:c r="F103" s="32" t="str">
         <x:v>P0</x:v>
@@ -13751,19 +13761,19 @@
     </x:row>
     <x:row r="104" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A104" s="32" t="str">
-        <x:v>R-098</x:v>
+        <x:v>R-097</x:v>
       </x:c>
       <x:c r="B104" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C104" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D104" s="32" t="str">
-        <x:v>Independent penetration test</x:v>
+        <x:v>Disaster recovery</x:v>
       </x:c>
       <x:c r="E104" s="32" t="str">
-        <x:v>External security assessment before broad enterprise launch.</x:v>
+        <x:v>Document and exercise regional recovery procedures.</x:v>
       </x:c>
       <x:c r="F104" s="32" t="str">
         <x:v>P0</x:v>
@@ -13783,7 +13793,7 @@
     </x:row>
     <x:row r="105" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A105" s="32" t="str">
-        <x:v>R-099</x:v>
+        <x:v>R-098</x:v>
       </x:c>
       <x:c r="B105" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13792,10 +13802,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D105" s="32" t="str">
-        <x:v>SOC 2 readiness controls</x:v>
+        <x:v>Independent penetration test</x:v>
       </x:c>
       <x:c r="E105" s="32" t="str">
-        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
+        <x:v>External security assessment before broad enterprise launch.</x:v>
       </x:c>
       <x:c r="F105" s="32" t="str">
         <x:v>P0</x:v>
@@ -13815,7 +13825,7 @@
     </x:row>
     <x:row r="106" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A106" s="32" t="str">
-        <x:v>R-100</x:v>
+        <x:v>R-099</x:v>
       </x:c>
       <x:c r="B106" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13824,10 +13834,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D106" s="32" t="str">
-        <x:v>Tenant isolation validation</x:v>
+        <x:v>SOC 2 readiness controls</x:v>
       </x:c>
       <x:c r="E106" s="32" t="str">
-        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
+        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
       </x:c>
       <x:c r="F106" s="32" t="str">
         <x:v>P0</x:v>
@@ -13847,7 +13857,7 @@
     </x:row>
     <x:row r="107" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A107" s="32" t="str">
-        <x:v>R-101</x:v>
+        <x:v>R-100</x:v>
       </x:c>
       <x:c r="B107" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13856,10 +13866,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>Signing-key hardening</x:v>
+        <x:v>Tenant isolation validation</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
-        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
+        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
       </x:c>
       <x:c r="F107" s="32" t="str">
         <x:v>P0</x:v>
@@ -13879,19 +13889,19 @@
     </x:row>
     <x:row r="108" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A108" s="32" t="str">
-        <x:v>R-102</x:v>
+        <x:v>R-101</x:v>
       </x:c>
       <x:c r="B108" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C108" s="32" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>24x7 incident process</x:v>
+        <x:v>Signing-key hardening</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
-        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
+        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
       </x:c>
       <x:c r="F108" s="32" t="str">
         <x:v>P0</x:v>
@@ -13911,7 +13921,7 @@
     </x:row>
     <x:row r="109" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A109" s="32" t="str">
-        <x:v>R-103</x:v>
+        <x:v>R-102</x:v>
       </x:c>
       <x:c r="B109" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13920,10 +13930,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>Capacity/load tests</x:v>
+        <x:v>24x7 incident process</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
-        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
+        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
       </x:c>
       <x:c r="F109" s="32" t="str">
         <x:v>P0</x:v>
@@ -13943,7 +13953,7 @@
     </x:row>
     <x:row r="110" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A110" s="32" t="str">
-        <x:v>R-104</x:v>
+        <x:v>R-103</x:v>
       </x:c>
       <x:c r="B110" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13952,10 +13962,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>Cost guardrails</x:v>
+        <x:v>Capacity/load tests</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
-        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
+        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
       </x:c>
       <x:c r="F110" s="32" t="str">
         <x:v>P0</x:v>
@@ -13975,19 +13985,19 @@
     </x:row>
     <x:row r="111" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A111" s="32" t="str">
-        <x:v>R-105</x:v>
+        <x:v>R-104</x:v>
       </x:c>
       <x:c r="B111" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C111" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>Release qualification suite</x:v>
+        <x:v>Cost guardrails</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
-        <x:v>Full regression across supported stack versions before platform releases.</x:v>
+        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
       </x:c>
       <x:c r="F111" s="32" t="str">
         <x:v>P0</x:v>
@@ -14007,7 +14017,7 @@
     </x:row>
     <x:row r="112" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A112" s="32" t="str">
-        <x:v>R-106</x:v>
+        <x:v>R-105</x:v>
       </x:c>
       <x:c r="B112" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14016,10 +14026,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Canary platform releases</x:v>
+        <x:v>Release qualification suite</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
+        <x:v>Full regression across supported stack versions before platform releases.</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
         <x:v>P0</x:v>
@@ -14039,19 +14049,19 @@
     </x:row>
     <x:row r="113" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A113" s="32" t="str">
-        <x:v>R-107</x:v>
+        <x:v>R-106</x:v>
       </x:c>
       <x:c r="B113" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C113" s="32" t="str">
-        <x:v>Support</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Support tooling</x:v>
+        <x:v>Canary platform releases</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
+        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
         <x:v>P0</x:v>
@@ -14071,19 +14081,19 @@
     </x:row>
     <x:row r="114" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A114" s="32" t="str">
-        <x:v>R-108</x:v>
+        <x:v>R-107</x:v>
       </x:c>
       <x:c r="B114" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C114" s="32" t="str">
-        <x:v>Legal/Privacy</x:v>
+        <x:v>Support</x:v>
       </x:c>
       <x:c r="D114" s="32" t="str">
-        <x:v>Privacy + retention controls</x:v>
+        <x:v>Support tooling</x:v>
       </x:c>
       <x:c r="E114" s="32" t="str">
-        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
       </x:c>
       <x:c r="F114" s="32" t="str">
         <x:v>P0</x:v>
@@ -14101,2154 +14111,2152 @@
       <x:c r="L114" s="32"/>
       <x:c r="M114" s="32"/>
     </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="43" t="str">
-        <x:v>R-109</x:v>
-      </x:c>
-      <x:c r="B115" s="43" t="str">
+    <x:row r="115" s="40" customFormat="1" ht="34" customHeight="1">
+      <x:c r="A115" s="32" t="str">
+        <x:v>R-108</x:v>
+      </x:c>
+      <x:c r="B115" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C115" s="43" t="str">
-        <x:v>Business</x:v>
-      </x:c>
-      <x:c r="D115" s="43" t="str">
-        <x:v>Plan entitlements</x:v>
-      </x:c>
-      <x:c r="E115" s="43" t="str">
-        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
-      </x:c>
-      <x:c r="F115" s="43" t="str">
+      <x:c r="C115" s="32" t="str">
+        <x:v>Legal/Privacy</x:v>
+      </x:c>
+      <x:c r="D115" s="32" t="str">
+        <x:v>Privacy + retention controls</x:v>
+      </x:c>
+      <x:c r="E115" s="32" t="str">
+        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+      </x:c>
+      <x:c r="F115" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G115" s="43"/>
-      <x:c r="H115" s="43" t="str">
+      <x:c r="G115" s="32"/>
+      <x:c r="H115" s="32" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I115" s="386" t="n">
+      <x:c r="I115" s="376" t="n">
         <x:f>IF(H115="Done",1,IF(H115="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J115" s="43"/>
-      <x:c r="K115" s="43"/>
-      <x:c r="L115" s="43"/>
-      <x:c r="M115" s="43"/>
+      <x:c r="J115" s="32"/>
+      <x:c r="K115" s="32"/>
+      <x:c r="L115" s="32"/>
+      <x:c r="M115" s="32"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="42" t="str">
-        <x:v>R-110</x:v>
-      </x:c>
-      <x:c r="B116" s="42" t="str">
+      <x:c r="A116" s="43" t="str">
+        <x:v>R-109</x:v>
+      </x:c>
+      <x:c r="B116" s="43" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C116" s="42" t="str">
+      <x:c r="C116" s="43" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="D116" s="42" t="str">
-        <x:v>Unit economics dashboard</x:v>
-      </x:c>
-      <x:c r="E116" s="42" t="str">
-        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
-      </x:c>
-      <x:c r="F116" s="42" t="str">
+      <x:c r="D116" s="43" t="str">
+        <x:v>Plan entitlements</x:v>
+      </x:c>
+      <x:c r="E116" s="43" t="str">
+        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
+      </x:c>
+      <x:c r="F116" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G116" s="42"/>
-      <x:c r="H116" s="42" t="str">
+      <x:c r="G116" s="43"/>
+      <x:c r="H116" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I116" s="387" t="n">
+      <x:c r="I116" s="386" t="n">
         <x:f>IF(H116="Done",1,IF(H116="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J116" s="42"/>
-      <x:c r="K116" s="42"/>
-      <x:c r="L116" s="42"/>
-      <x:c r="M116" s="42"/>
+      <x:c r="J116" s="43"/>
+      <x:c r="K116" s="43"/>
+      <x:c r="L116" s="43"/>
+      <x:c r="M116" s="43"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="43" t="str">
-        <x:v>R-111</x:v>
-      </x:c>
-      <x:c r="B117" s="43" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C117" s="43" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D117" s="43" t="str">
-        <x:v>Cross-platform Mobile Agent</x:v>
-      </x:c>
-      <x:c r="E117" s="43" t="str">
-        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
-      </x:c>
-      <x:c r="F117" s="43" t="str">
+      <x:c r="A117" s="42" t="str">
+        <x:v>R-110</x:v>
+      </x:c>
+      <x:c r="B117" s="42" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C117" s="42" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="D117" s="42" t="str">
+        <x:v>Unit economics dashboard</x:v>
+      </x:c>
+      <x:c r="E117" s="42" t="str">
+        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
+      </x:c>
+      <x:c r="F117" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G117" s="43"/>
-      <x:c r="H117" s="43" t="str">
+      <x:c r="G117" s="42"/>
+      <x:c r="H117" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I117" s="386" t="n">
+      <x:c r="I117" s="387" t="n">
         <x:f>IF(H117="Done",1,IF(H117="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J117" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K117" s="43"/>
-      <x:c r="L117" s="43"/>
-      <x:c r="M117" s="43"/>
+      <x:c r="J117" s="42"/>
+      <x:c r="K117" s="42"/>
+      <x:c r="L117" s="42"/>
+      <x:c r="M117" s="42"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="42" t="str">
-        <x:v>R-112</x:v>
-      </x:c>
-      <x:c r="B118" s="42" t="str">
+      <x:c r="A118" s="43" t="str">
+        <x:v>R-111</x:v>
+      </x:c>
+      <x:c r="B118" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C118" s="42" t="str">
+      <x:c r="C118" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D118" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="E118" s="42" t="str">
-        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
-      </x:c>
-      <x:c r="F118" s="42" t="str">
+      <x:c r="D118" s="43" t="str">
+        <x:v>Cross-platform Mobile Agent</x:v>
+      </x:c>
+      <x:c r="E118" s="43" t="str">
+        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
+      </x:c>
+      <x:c r="F118" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G118" s="42"/>
-      <x:c r="H118" s="42" t="str">
+      <x:c r="G118" s="43"/>
+      <x:c r="H118" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I118" s="387" t="n">
+      <x:c r="I118" s="386" t="n">
         <x:f>IF(H118="Done",1,IF(H118="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J118" s="42" t="str">
-        <x:v>Requirement specification step</x:v>
-      </x:c>
-      <x:c r="K118" s="42"/>
-      <x:c r="L118" s="42"/>
-      <x:c r="M118" s="42"/>
+      <x:c r="J118" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K118" s="43"/>
+      <x:c r="L118" s="43"/>
+      <x:c r="M118" s="43"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="43" t="str">
-        <x:v>R-113</x:v>
-      </x:c>
-      <x:c r="B119" s="43" t="str">
+      <x:c r="A119" s="42" t="str">
+        <x:v>R-112</x:v>
+      </x:c>
+      <x:c r="B119" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C119" s="43" t="str">
+      <x:c r="C119" s="42" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D119" s="43" t="str">
-        <x:v>Auto / Recommended project mode</x:v>
-      </x:c>
-      <x:c r="E119" s="43" t="str">
-        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
-      </x:c>
-      <x:c r="F119" s="43" t="str">
+      <x:c r="D119" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="E119" s="42" t="str">
+        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
+      </x:c>
+      <x:c r="F119" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G119" s="43"/>
-      <x:c r="H119" s="43" t="str">
+      <x:c r="G119" s="42"/>
+      <x:c r="H119" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I119" s="386" t="n">
+      <x:c r="I119" s="387" t="n">
         <x:f>IF(H119="Done",1,IF(H119="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J119" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K119" s="43"/>
-      <x:c r="L119" s="43"/>
-      <x:c r="M119" s="43"/>
+      <x:c r="J119" s="42" t="str">
+        <x:v>Requirement specification step</x:v>
+      </x:c>
+      <x:c r="K119" s="42"/>
+      <x:c r="L119" s="42"/>
+      <x:c r="M119" s="42"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="42" t="str">
-        <x:v>R-114</x:v>
-      </x:c>
-      <x:c r="B120" s="42" t="str">
+      <x:c r="A120" s="43" t="str">
+        <x:v>R-113</x:v>
+      </x:c>
+      <x:c r="B120" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C120" s="42" t="str">
+      <x:c r="C120" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D120" s="42" t="str">
-        <x:v>Manual framework override</x:v>
-      </x:c>
-      <x:c r="E120" s="42" t="str">
-        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
-      </x:c>
-      <x:c r="F120" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G120" s="42"/>
-      <x:c r="H120" s="42" t="str">
+      <x:c r="D120" s="43" t="str">
+        <x:v>Auto / Recommended project mode</x:v>
+      </x:c>
+      <x:c r="E120" s="43" t="str">
+        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
+      </x:c>
+      <x:c r="F120" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G120" s="43"/>
+      <x:c r="H120" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I120" s="387" t="n">
+      <x:c r="I120" s="386" t="n">
         <x:f>IF(H120="Done",1,IF(H120="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="42" t="str">
+      <x:c r="J120" s="43" t="str">
         <x:v>Framework recommendation engine</x:v>
       </x:c>
-      <x:c r="K120" s="42"/>
-      <x:c r="L120" s="42"/>
-      <x:c r="M120" s="42"/>
+      <x:c r="K120" s="43"/>
+      <x:c r="L120" s="43"/>
+      <x:c r="M120" s="43"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="43" t="str">
-        <x:v>R-115</x:v>
-      </x:c>
-      <x:c r="B121" s="43" t="str">
+      <x:c r="A121" s="42" t="str">
+        <x:v>R-114</x:v>
+      </x:c>
+      <x:c r="B121" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C121" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D121" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="E121" s="43" t="str">
-        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
-      </x:c>
-      <x:c r="F121" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G121" s="43"/>
-      <x:c r="H121" s="43" t="str">
+      <x:c r="C121" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D121" s="42" t="str">
+        <x:v>Manual framework override</x:v>
+      </x:c>
+      <x:c r="E121" s="42" t="str">
+        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
+      </x:c>
+      <x:c r="F121" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G121" s="42"/>
+      <x:c r="H121" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I121" s="386" t="n">
+      <x:c r="I121" s="387" t="n">
         <x:f>IF(H121="Done",1,IF(H121="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K121" s="43"/>
-      <x:c r="L121" s="43"/>
-      <x:c r="M121" s="43"/>
+      <x:c r="J121" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K121" s="42"/>
+      <x:c r="L121" s="42"/>
+      <x:c r="M121" s="42"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="42" t="str">
-        <x:v>R-116</x:v>
-      </x:c>
-      <x:c r="B122" s="42" t="str">
+      <x:c r="A122" s="43" t="str">
+        <x:v>R-115</x:v>
+      </x:c>
+      <x:c r="B122" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C122" s="42" t="str">
+      <x:c r="C122" s="43" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D122" s="42" t="str">
-        <x:v>Shared-code policy</x:v>
-      </x:c>
-      <x:c r="E122" s="42" t="str">
-        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
-      </x:c>
-      <x:c r="F122" s="42" t="str">
+      <x:c r="D122" s="43" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="E122" s="43" t="str">
+        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
+      </x:c>
+      <x:c r="F122" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G122" s="42"/>
-      <x:c r="H122" s="42" t="str">
+      <x:c r="G122" s="43"/>
+      <x:c r="H122" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I122" s="387" t="n">
+      <x:c r="I122" s="386" t="n">
         <x:f>IF(H122="Done",1,IF(H122="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K122" s="42"/>
-      <x:c r="L122" s="42"/>
-      <x:c r="M122" s="42"/>
+      <x:c r="J122" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K122" s="43"/>
+      <x:c r="L122" s="43"/>
+      <x:c r="M122" s="43"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="43" t="str">
-        <x:v>R-117</x:v>
-      </x:c>
-      <x:c r="B123" s="43" t="str">
+      <x:c r="A123" s="42" t="str">
+        <x:v>R-116</x:v>
+      </x:c>
+      <x:c r="B123" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C123" s="43" t="str">
-        <x:v>Web/Admin</x:v>
-      </x:c>
-      <x:c r="D123" s="43" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="E123" s="43" t="str">
-        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
-      </x:c>
-      <x:c r="F123" s="43" t="str">
+      <x:c r="C123" s="42" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D123" s="42" t="str">
+        <x:v>Shared-code policy</x:v>
+      </x:c>
+      <x:c r="E123" s="42" t="str">
+        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
+      </x:c>
+      <x:c r="F123" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G123" s="43"/>
-      <x:c r="H123" s="43" t="str">
+      <x:c r="G123" s="42"/>
+      <x:c r="H123" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I123" s="386" t="n">
+      <x:c r="I123" s="387" t="n">
         <x:f>IF(H123="Done",1,IF(H123="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J123" s="43" t="str">
-        <x:v>Web/Admin Agent</x:v>
-      </x:c>
-      <x:c r="K123" s="43"/>
-      <x:c r="L123" s="43"/>
-      <x:c r="M123" s="43"/>
+      <x:c r="J123" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K123" s="42"/>
+      <x:c r="L123" s="42"/>
+      <x:c r="M123" s="42"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="42" t="str">
-        <x:v>R-118</x:v>
-      </x:c>
-      <x:c r="B124" s="42" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C124" s="42" t="str">
+      <x:c r="A124" s="43" t="str">
+        <x:v>R-117</x:v>
+      </x:c>
+      <x:c r="B124" s="43" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C124" s="43" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D124" s="42" t="str">
-        <x:v>Flutter Web optional profile</x:v>
-      </x:c>
-      <x:c r="E124" s="42" t="str">
-        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
-      </x:c>
-      <x:c r="F124" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G124" s="42"/>
-      <x:c r="H124" s="42" t="str">
+      <x:c r="D124" s="43" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="E124" s="43" t="str">
+        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
+      </x:c>
+      <x:c r="F124" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G124" s="43"/>
+      <x:c r="H124" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I124" s="387" t="n">
+      <x:c r="I124" s="386" t="n">
         <x:f>IF(H124="Done",1,IF(H124="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="42" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
-      </x:c>
-      <x:c r="K124" s="42"/>
-      <x:c r="L124" s="42"/>
-      <x:c r="M124" s="42"/>
+      <x:c r="J124" s="43" t="str">
+        <x:v>Web/Admin Agent</x:v>
+      </x:c>
+      <x:c r="K124" s="43"/>
+      <x:c r="L124" s="43"/>
+      <x:c r="M124" s="43"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="43" t="str">
-        <x:v>R-119</x:v>
-      </x:c>
-      <x:c r="B125" s="43" t="str">
+      <x:c r="A125" s="42" t="str">
+        <x:v>R-118</x:v>
+      </x:c>
+      <x:c r="B125" s="42" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C125" s="43" t="str">
+      <x:c r="C125" s="42" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D125" s="43" t="str">
-        <x:v>React Native Web optional profile</x:v>
-      </x:c>
-      <x:c r="E125" s="43" t="str">
-        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
-      </x:c>
-      <x:c r="F125" s="43" t="str">
+      <x:c r="D125" s="42" t="str">
+        <x:v>Flutter Web optional profile</x:v>
+      </x:c>
+      <x:c r="E125" s="42" t="str">
+        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
+      </x:c>
+      <x:c r="F125" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G125" s="43"/>
-      <x:c r="H125" s="43" t="str">
+      <x:c r="G125" s="42"/>
+      <x:c r="H125" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I125" s="386" t="n">
+      <x:c r="I125" s="387" t="n">
         <x:f>IF(H125="Done",1,IF(H125="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J125" s="43" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
-      </x:c>
-      <x:c r="K125" s="43"/>
-      <x:c r="L125" s="43"/>
-      <x:c r="M125" s="43"/>
+      <x:c r="J125" s="42" t="str">
+        <x:v>Flutter target (GA baseline)</x:v>
+      </x:c>
+      <x:c r="K125" s="42"/>
+      <x:c r="L125" s="42"/>
+      <x:c r="M125" s="42"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="42" t="str">
-        <x:v>R-120</x:v>
-      </x:c>
-      <x:c r="B126" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C126" s="42" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D126" s="42" t="str">
-        <x:v>Native recommendation profile</x:v>
-      </x:c>
-      <x:c r="E126" s="42" t="str">
-        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
-      </x:c>
-      <x:c r="F126" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G126" s="42"/>
-      <x:c r="H126" s="42" t="str">
+      <x:c r="A126" s="43" t="str">
+        <x:v>R-119</x:v>
+      </x:c>
+      <x:c r="B126" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C126" s="43" t="str">
+        <x:v>Web/Admin</x:v>
+      </x:c>
+      <x:c r="D126" s="43" t="str">
+        <x:v>React Native Web optional profile</x:v>
+      </x:c>
+      <x:c r="E126" s="43" t="str">
+        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
+      </x:c>
+      <x:c r="F126" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G126" s="43"/>
+      <x:c r="H126" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I126" s="387" t="n">
+      <x:c r="I126" s="386" t="n">
         <x:f>IF(H126="Done",1,IF(H126="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K126" s="42"/>
-      <x:c r="L126" s="42"/>
-      <x:c r="M126" s="42"/>
+      <x:c r="J126" s="43" t="str">
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
+      </x:c>
+      <x:c r="K126" s="43"/>
+      <x:c r="L126" s="43"/>
+      <x:c r="M126" s="43"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="43" t="str">
-        <x:v>R-121</x:v>
-      </x:c>
-      <x:c r="B127" s="43" t="str">
+      <x:c r="A127" s="42" t="str">
+        <x:v>R-120</x:v>
+      </x:c>
+      <x:c r="B127" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C127" s="43" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D127" s="43" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="E127" s="43" t="str">
-        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
-      </x:c>
-      <x:c r="F127" s="43" t="str">
+      <x:c r="C127" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D127" s="42" t="str">
+        <x:v>Native recommendation profile</x:v>
+      </x:c>
+      <x:c r="E127" s="42" t="str">
+        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
+      </x:c>
+      <x:c r="F127" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G127" s="43"/>
-      <x:c r="H127" s="43" t="str">
+      <x:c r="G127" s="42"/>
+      <x:c r="H127" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I127" s="386" t="n">
+      <x:c r="I127" s="387" t="n">
         <x:f>IF(H127="Done",1,IF(H127="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J127" s="43" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K127" s="43"/>
-      <x:c r="L127" s="43"/>
-      <x:c r="M127" s="43"/>
+      <x:c r="J127" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K127" s="42"/>
+      <x:c r="L127" s="42"/>
+      <x:c r="M127" s="42"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="42" t="str">
-        <x:v>R-122</x:v>
-      </x:c>
-      <x:c r="B128" s="42" t="str">
+      <x:c r="A128" s="43" t="str">
+        <x:v>R-121</x:v>
+      </x:c>
+      <x:c r="B128" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C128" s="42" t="str">
+      <x:c r="C128" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D128" s="42" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="E128" s="42" t="str">
-        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
-      </x:c>
-      <x:c r="F128" s="42" t="str">
+      <x:c r="D128" s="43" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="E128" s="43" t="str">
+        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
+      </x:c>
+      <x:c r="F128" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G128" s="42"/>
-      <x:c r="H128" s="42" t="str">
+      <x:c r="G128" s="43"/>
+      <x:c r="H128" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I128" s="387" t="n">
+      <x:c r="I128" s="386" t="n">
         <x:f>IF(H128="Done",1,IF(H128="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="42" t="str">
+      <x:c r="J128" s="43" t="str">
         <x:v>Project + workspace model</x:v>
       </x:c>
-      <x:c r="K128" s="42"/>
-      <x:c r="L128" s="42"/>
-      <x:c r="M128" s="42"/>
+      <x:c r="K128" s="43"/>
+      <x:c r="L128" s="43"/>
+      <x:c r="M128" s="43"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="43" t="str">
-        <x:v>R-123</x:v>
-      </x:c>
-      <x:c r="B129" s="43" t="str">
+      <x:c r="A129" s="42" t="str">
+        <x:v>R-122</x:v>
+      </x:c>
+      <x:c r="B129" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C129" s="43" t="str">
+      <x:c r="C129" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D129" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="E129" s="43" t="str">
-        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
-      </x:c>
-      <x:c r="F129" s="43" t="str">
+      <x:c r="D129" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="E129" s="42" t="str">
+        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
+      </x:c>
+      <x:c r="F129" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G129" s="43"/>
-      <x:c r="H129" s="43" t="str">
+      <x:c r="G129" s="42"/>
+      <x:c r="H129" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I129" s="386" t="n">
+      <x:c r="I129" s="387" t="n">
         <x:f>IF(H129="Done",1,IF(H129="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J129" s="43" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="K129" s="43"/>
-      <x:c r="L129" s="43"/>
-      <x:c r="M129" s="43"/>
+      <x:c r="J129" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K129" s="42"/>
+      <x:c r="L129" s="42"/>
+      <x:c r="M129" s="42"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="42" t="str">
-        <x:v>R-124</x:v>
-      </x:c>
-      <x:c r="B130" s="42" t="str">
+      <x:c r="A130" s="43" t="str">
+        <x:v>R-123</x:v>
+      </x:c>
+      <x:c r="B130" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C130" s="42" t="str">
+      <x:c r="C130" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D130" s="42" t="str">
-        <x:v>Repository naming convention</x:v>
-      </x:c>
-      <x:c r="E130" s="42" t="str">
-        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
-      </x:c>
-      <x:c r="F130" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G130" s="42"/>
-      <x:c r="H130" s="42" t="str">
+      <x:c r="D130" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="E130" s="43" t="str">
+        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
+      </x:c>
+      <x:c r="F130" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G130" s="43"/>
+      <x:c r="H130" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I130" s="387" t="n">
+      <x:c r="I130" s="386" t="n">
         <x:f>IF(H130="Done",1,IF(H130="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J130" s="42" t="str">
+      <x:c r="J130" s="43" t="str">
         <x:v>One Git repo per customer project</x:v>
       </x:c>
-      <x:c r="K130" s="42"/>
-      <x:c r="L130" s="42"/>
-      <x:c r="M130" s="42"/>
+      <x:c r="K130" s="43"/>
+      <x:c r="L130" s="43"/>
+      <x:c r="M130" s="43"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="43" t="str">
-        <x:v>R-125</x:v>
-      </x:c>
-      <x:c r="B131" s="43" t="str">
+      <x:c r="A131" s="42" t="str">
+        <x:v>R-124</x:v>
+      </x:c>
+      <x:c r="B131" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C131" s="43" t="str">
+      <x:c r="C131" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D131" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="E131" s="43" t="str">
-        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
-      </x:c>
-      <x:c r="F131" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G131" s="43"/>
-      <x:c r="H131" s="43" t="str">
+      <x:c r="D131" s="42" t="str">
+        <x:v>Repository naming convention</x:v>
+      </x:c>
+      <x:c r="E131" s="42" t="str">
+        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
+      </x:c>
+      <x:c r="F131" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G131" s="42"/>
+      <x:c r="H131" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I131" s="386" t="n">
+      <x:c r="I131" s="387" t="n">
         <x:f>IF(H131="Done",1,IF(H131="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J131" s="43" t="str">
-        <x:v>Branch per task</x:v>
-      </x:c>
-      <x:c r="K131" s="43"/>
-      <x:c r="L131" s="43"/>
-      <x:c r="M131" s="43"/>
+      <x:c r="J131" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="K131" s="42"/>
+      <x:c r="L131" s="42"/>
+      <x:c r="M131" s="42"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="42" t="str">
-        <x:v>R-126</x:v>
-      </x:c>
-      <x:c r="B132" s="42" t="str">
+      <x:c r="A132" s="43" t="str">
+        <x:v>R-125</x:v>
+      </x:c>
+      <x:c r="B132" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C132" s="42" t="str">
-        <x:v>Product Foundation</x:v>
-      </x:c>
-      <x:c r="D132" s="42" t="str">
-        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
-      </x:c>
-      <x:c r="E132" s="42" t="str">
-        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
-      </x:c>
-      <x:c r="F132" s="42" t="str">
+      <x:c r="C132" s="43" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D132" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="E132" s="43" t="str">
+        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
+      </x:c>
+      <x:c r="F132" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G132" s="42"/>
-      <x:c r="H132" s="42" t="str">
+      <x:c r="G132" s="43"/>
+      <x:c r="H132" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I132" s="387" t="n">
+      <x:c r="I132" s="386" t="n">
         <x:f>IF(H132="Done",1,IF(H132="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J132" s="42" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K132" s="42"/>
-      <x:c r="L132" s="42"/>
-      <x:c r="M132" s="42"/>
+      <x:c r="J132" s="43" t="str">
+        <x:v>Branch per task</x:v>
+      </x:c>
+      <x:c r="K132" s="43"/>
+      <x:c r="L132" s="43"/>
+      <x:c r="M132" s="43"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="43" t="str">
-        <x:v>R-127</x:v>
-      </x:c>
-      <x:c r="B133" s="43" t="str">
+      <x:c r="A133" s="42" t="str">
+        <x:v>R-126</x:v>
+      </x:c>
+      <x:c r="B133" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C133" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D133" s="43" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="E133" s="43" t="str">
-        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
-      </x:c>
-      <x:c r="F133" s="43" t="str">
+      <x:c r="C133" s="42" t="str">
+        <x:v>Product Foundation</x:v>
+      </x:c>
+      <x:c r="D133" s="42" t="str">
+        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
+      </x:c>
+      <x:c r="E133" s="42" t="str">
+        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
+      </x:c>
+      <x:c r="F133" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G133" s="43"/>
-      <x:c r="H133" s="43" t="str">
+      <x:c r="G133" s="42"/>
+      <x:c r="H133" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I133" s="386" t="n">
+      <x:c r="I133" s="387" t="n">
         <x:f>IF(H133="Done",1,IF(H133="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J133" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K133" s="43"/>
-      <x:c r="L133" s="43"/>
-      <x:c r="M133" s="43"/>
+      <x:c r="J133" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K133" s="42"/>
+      <x:c r="L133" s="42"/>
+      <x:c r="M133" s="42"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="42" t="str">
-        <x:v>R-128</x:v>
-      </x:c>
-      <x:c r="B134" s="42" t="str">
+      <x:c r="A134" s="43" t="str">
+        <x:v>R-127</x:v>
+      </x:c>
+      <x:c r="B134" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C134" s="42" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D134" s="42" t="str">
-        <x:v>Cross-language monorepo orchestration</x:v>
-      </x:c>
-      <x:c r="E134" s="42" t="str">
-        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
-      </x:c>
-      <x:c r="F134" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G134" s="42"/>
-      <x:c r="H134" s="42" t="str">
+      <x:c r="C134" s="43" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D134" s="43" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="E134" s="43" t="str">
+        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
+      </x:c>
+      <x:c r="F134" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G134" s="43"/>
+      <x:c r="H134" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I134" s="387" t="n">
+      <x:c r="I134" s="386" t="n">
         <x:f>IF(H134="Done",1,IF(H134="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J134" s="42" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K134" s="42"/>
-      <x:c r="L134" s="42"/>
-      <x:c r="M134" s="42"/>
+      <x:c r="J134" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K134" s="43"/>
+      <x:c r="L134" s="43"/>
+      <x:c r="M134" s="43"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="43" t="str">
-        <x:v>R-129</x:v>
-      </x:c>
-      <x:c r="B135" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C135" s="43" t="str">
+      <x:c r="A135" s="42" t="str">
+        <x:v>R-128</x:v>
+      </x:c>
+      <x:c r="B135" s="42" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C135" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D135" s="43" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="E135" s="43" t="str">
-        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
-      </x:c>
-      <x:c r="F135" s="43" t="str">
+      <x:c r="D135" s="42" t="str">
+        <x:v>Cross-language monorepo orchestration</x:v>
+      </x:c>
+      <x:c r="E135" s="42" t="str">
+        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
+      </x:c>
+      <x:c r="F135" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G135" s="43"/>
-      <x:c r="H135" s="43" t="str">
+      <x:c r="G135" s="42"/>
+      <x:c r="H135" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I135" s="386" t="n">
+      <x:c r="I135" s="387" t="n">
         <x:f>IF(H135="Done",1,IF(H135="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J135" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K135" s="43"/>
-      <x:c r="L135" s="43"/>
-      <x:c r="M135" s="43"/>
+      <x:c r="J135" s="42" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K135" s="42"/>
+      <x:c r="L135" s="42"/>
+      <x:c r="M135" s="42"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="42" t="str">
-        <x:v>R-130</x:v>
-      </x:c>
-      <x:c r="B136" s="42" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C136" s="42" t="str">
+      <x:c r="A136" s="43" t="str">
+        <x:v>R-129</x:v>
+      </x:c>
+      <x:c r="B136" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C136" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D136" s="42" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="E136" s="42" t="str">
-        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
-      </x:c>
-      <x:c r="F136" s="42" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G136" s="42"/>
-      <x:c r="H136" s="42" t="str">
+      <x:c r="D136" s="43" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="E136" s="43" t="str">
+        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
+      </x:c>
+      <x:c r="F136" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G136" s="43"/>
+      <x:c r="H136" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I136" s="387" t="n">
+      <x:c r="I136" s="386" t="n">
         <x:f>IF(H136="Done",1,IF(H136="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J136" s="42" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="K136" s="42"/>
-      <x:c r="L136" s="42"/>
-      <x:c r="M136" s="42"/>
+      <x:c r="J136" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K136" s="43"/>
+      <x:c r="L136" s="43"/>
+      <x:c r="M136" s="43"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="43" t="str">
-        <x:v>R-131</x:v>
-      </x:c>
-      <x:c r="B137" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C137" s="43" t="str">
+      <x:c r="A137" s="42" t="str">
+        <x:v>R-130</x:v>
+      </x:c>
+      <x:c r="B137" s="42" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C137" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D137" s="43" t="str">
-        <x:v>CODEOWNERS + protected paths</x:v>
-      </x:c>
-      <x:c r="E137" s="43" t="str">
-        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
-      </x:c>
-      <x:c r="F137" s="43" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G137" s="43"/>
-      <x:c r="H137" s="43" t="str">
+      <x:c r="D137" s="42" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="E137" s="42" t="str">
+        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
+      </x:c>
+      <x:c r="F137" s="42" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G137" s="42"/>
+      <x:c r="H137" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I137" s="386" t="n">
+      <x:c r="I137" s="387" t="n">
         <x:f>IF(H137="Done",1,IF(H137="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J137" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="K137" s="43"/>
-      <x:c r="L137" s="43"/>
-      <x:c r="M137" s="43"/>
+      <x:c r="J137" s="42" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="K137" s="42"/>
+      <x:c r="L137" s="42"/>
+      <x:c r="M137" s="42"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="42" t="str">
-        <x:v>R-132</x:v>
-      </x:c>
-      <x:c r="B138" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C138" s="42" t="str">
+      <x:c r="A138" s="43" t="str">
+        <x:v>R-131</x:v>
+      </x:c>
+      <x:c r="B138" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C138" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D138" s="42" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="E138" s="42" t="str">
-        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
-      </x:c>
-      <x:c r="F138" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G138" s="42"/>
-      <x:c r="H138" s="42" t="str">
+      <x:c r="D138" s="43" t="str">
+        <x:v>CODEOWNERS + protected paths</x:v>
+      </x:c>
+      <x:c r="E138" s="43" t="str">
+        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
+      </x:c>
+      <x:c r="F138" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G138" s="43"/>
+      <x:c r="H138" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I138" s="387" t="n">
+      <x:c r="I138" s="386" t="n">
         <x:f>IF(H138="Done",1,IF(H138="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J138" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K138" s="42"/>
-      <x:c r="L138" s="42"/>
-      <x:c r="M138" s="42"/>
+      <x:c r="J138" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="K138" s="43"/>
+      <x:c r="L138" s="43"/>
+      <x:c r="M138" s="43"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="66" t="str">
-        <x:v>R-133</x:v>
-      </x:c>
-      <x:c r="B139" s="66" t="str">
+      <x:c r="A139" s="42" t="str">
+        <x:v>R-132</x:v>
+      </x:c>
+      <x:c r="B139" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C139" s="66" t="str">
-        <x:v>Change Safety</x:v>
-      </x:c>
-      <x:c r="D139" s="66" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="E139" s="66" t="str">
-        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
-      </x:c>
-      <x:c r="F139" s="66" t="str">
+      <x:c r="C139" s="42" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D139" s="42" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="E139" s="42" t="str">
+        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
+      </x:c>
+      <x:c r="F139" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G139" s="66"/>
-      <x:c r="H139" s="66" t="str">
+      <x:c r="G139" s="42"/>
+      <x:c r="H139" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I139" s="388" t="n">
+      <x:c r="I139" s="387" t="n">
         <x:f>IF(H139="Done",1,IF(H139="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J139" s="66" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K139" s="66"/>
-      <x:c r="L139" s="66"/>
-      <x:c r="M139" s="66"/>
+      <x:c r="J139" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K139" s="42"/>
+      <x:c r="L139" s="42"/>
+      <x:c r="M139" s="42"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="65" t="str">
-        <x:v>R-134</x:v>
-      </x:c>
-      <x:c r="B140" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C140" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D140" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="E140" s="65" t="str">
-        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
-      </x:c>
-      <x:c r="F140" s="65" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G140" s="65"/>
-      <x:c r="H140" s="65" t="str">
+      <x:c r="A140" s="66" t="str">
+        <x:v>R-133</x:v>
+      </x:c>
+      <x:c r="B140" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C140" s="66" t="str">
+        <x:v>Change Safety</x:v>
+      </x:c>
+      <x:c r="D140" s="66" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="E140" s="66" t="str">
+        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
+      </x:c>
+      <x:c r="F140" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G140" s="66"/>
+      <x:c r="H140" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I140" s="389" t="n">
+      <x:c r="I140" s="388" t="n">
         <x:f>IF(H140="Done",1,IF(H140="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J140" s="65" t="str">
-        <x:v>Build artifact caching</x:v>
-      </x:c>
-      <x:c r="K140" s="65"/>
-      <x:c r="L140" s="65"/>
-      <x:c r="M140" s="65"/>
+      <x:c r="J140" s="66" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K140" s="66"/>
+      <x:c r="L140" s="66"/>
+      <x:c r="M140" s="66"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="66" t="str">
-        <x:v>R-135</x:v>
-      </x:c>
-      <x:c r="B141" s="66" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C141" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D141" s="66" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="E141" s="66" t="str">
-        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
-      </x:c>
-      <x:c r="F141" s="66" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G141" s="66"/>
-      <x:c r="H141" s="66" t="str">
+      <x:c r="A141" s="65" t="str">
+        <x:v>R-134</x:v>
+      </x:c>
+      <x:c r="B141" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C141" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D141" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="E141" s="65" t="str">
+        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
+      </x:c>
+      <x:c r="F141" s="65" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G141" s="65"/>
+      <x:c r="H141" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I141" s="388" t="n">
+      <x:c r="I141" s="389" t="n">
         <x:f>IF(H141="Done",1,IF(H141="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J141" s="66" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K141" s="66"/>
-      <x:c r="L141" s="66"/>
-      <x:c r="M141" s="66" t="str">
-        <x:v>V3</x:v>
-      </x:c>
+      <x:c r="J141" s="65" t="str">
+        <x:v>Build artifact caching</x:v>
+      </x:c>
+      <x:c r="K141" s="65"/>
+      <x:c r="L141" s="65"/>
+      <x:c r="M141" s="65"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="65" t="str">
-        <x:v>R-136</x:v>
-      </x:c>
-      <x:c r="B142" s="65" t="str">
+      <x:c r="A142" s="66" t="str">
+        <x:v>R-135</x:v>
+      </x:c>
+      <x:c r="B142" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C142" s="65" t="str">
+      <x:c r="C142" s="66" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D142" s="65" t="str">
-        <x:v>Recommendation score model</x:v>
-      </x:c>
-      <x:c r="E142" s="65" t="str">
-        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
-      </x:c>
-      <x:c r="F142" s="65" t="str">
+      <x:c r="D142" s="66" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="E142" s="66" t="str">
+        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
+      </x:c>
+      <x:c r="F142" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G142" s="65"/>
-      <x:c r="H142" s="65" t="str">
+      <x:c r="G142" s="66"/>
+      <x:c r="H142" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I142" s="389" t="n">
+      <x:c r="I142" s="388" t="n">
         <x:f>IF(H142="Done",1,IF(H142="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J142" s="65" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="K142" s="65"/>
-      <x:c r="L142" s="65"/>
-      <x:c r="M142" s="65" t="str">
-        <x:v>Do not choose by industry label alone.</x:v>
+      <x:c r="J142" s="66" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K142" s="66"/>
+      <x:c r="L142" s="66"/>
+      <x:c r="M142" s="66" t="str">
+        <x:v>V3</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="66" t="str">
-        <x:v>R-137</x:v>
-      </x:c>
-      <x:c r="B143" s="66" t="str">
+      <x:c r="A143" s="65" t="str">
+        <x:v>R-136</x:v>
+      </x:c>
+      <x:c r="B143" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C143" s="66" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D143" s="66" t="str">
-        <x:v>Code sharing policy</x:v>
-      </x:c>
-      <x:c r="E143" s="66" t="str">
-        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
-      </x:c>
-      <x:c r="F143" s="66" t="str">
+      <x:c r="C143" s="65" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D143" s="65" t="str">
+        <x:v>Recommendation score model</x:v>
+      </x:c>
+      <x:c r="E143" s="65" t="str">
+        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
+      </x:c>
+      <x:c r="F143" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G143" s="66"/>
-      <x:c r="H143" s="66" t="str">
+      <x:c r="G143" s="65"/>
+      <x:c r="H143" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I143" s="388" t="n">
+      <x:c r="I143" s="389" t="n">
         <x:f>IF(H143="Done",1,IF(H143="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J143" s="66" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K143" s="66"/>
-      <x:c r="L143" s="66"/>
-      <x:c r="M143" s="66" t="str">
-        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
+      <x:c r="J143" s="65" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="K143" s="65"/>
+      <x:c r="L143" s="65"/>
+      <x:c r="M143" s="65" t="str">
+        <x:v>Do not choose by industry label alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="65" t="str">
-        <x:v>R-138</x:v>
-      </x:c>
-      <x:c r="B144" s="65" t="str">
+      <x:c r="A144" s="66" t="str">
+        <x:v>R-137</x:v>
+      </x:c>
+      <x:c r="B144" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C144" s="65" t="str">
+      <x:c r="C144" s="66" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D144" s="65" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="E144" s="65" t="str">
-        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
-      </x:c>
-      <x:c r="F144" s="65" t="str">
+      <x:c r="D144" s="66" t="str">
+        <x:v>Code sharing policy</x:v>
+      </x:c>
+      <x:c r="E144" s="66" t="str">
+        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
+      </x:c>
+      <x:c r="F144" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G144" s="65"/>
-      <x:c r="H144" s="65" t="str">
+      <x:c r="G144" s="66"/>
+      <x:c r="H144" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I144" s="389" t="n">
+      <x:c r="I144" s="388" t="n">
         <x:f>IF(H144="Done",1,IF(H144="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J144" s="65" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K144" s="65"/>
-      <x:c r="L144" s="65"/>
-      <x:c r="M144" s="65" t="str">
-        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
+      <x:c r="J144" s="66" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K144" s="66"/>
+      <x:c r="L144" s="66"/>
+      <x:c r="M144" s="66" t="str">
+        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="66" t="str">
-        <x:v>R-139</x:v>
-      </x:c>
-      <x:c r="B145" s="66" t="str">
+      <x:c r="A145" s="65" t="str">
+        <x:v>R-138</x:v>
+      </x:c>
+      <x:c r="B145" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C145" s="66" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D145" s="66" t="str">
-        <x:v>Root task commands</x:v>
-      </x:c>
-      <x:c r="E145" s="66" t="str">
-        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
-      </x:c>
-      <x:c r="F145" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G145" s="66"/>
-      <x:c r="H145" s="66" t="str">
+      <x:c r="C145" s="65" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D145" s="65" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="E145" s="65" t="str">
+        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
+      </x:c>
+      <x:c r="F145" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G145" s="65"/>
+      <x:c r="H145" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I145" s="388" t="n">
+      <x:c r="I145" s="389" t="n">
         <x:f>IF(H145="Done",1,IF(H145="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="66" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="K145" s="66"/>
-      <x:c r="L145" s="66"/>
-      <x:c r="M145" s="66" t="str">
-        <x:v>Framework-independent agent commands.</x:v>
+      <x:c r="J145" s="65" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K145" s="65"/>
+      <x:c r="L145" s="65"/>
+      <x:c r="M145" s="65" t="str">
+        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="65" t="str">
-        <x:v>R-140</x:v>
-      </x:c>
-      <x:c r="B146" s="65" t="str">
+      <x:c r="A146" s="66" t="str">
+        <x:v>R-139</x:v>
+      </x:c>
+      <x:c r="B146" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C146" s="65" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D146" s="65" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="E146" s="65" t="str">
-        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
-      </x:c>
-      <x:c r="F146" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G146" s="65"/>
-      <x:c r="H146" s="65" t="str">
+      <x:c r="C146" s="66" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D146" s="66" t="str">
+        <x:v>Root task commands</x:v>
+      </x:c>
+      <x:c r="E146" s="66" t="str">
+        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
+      </x:c>
+      <x:c r="F146" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G146" s="66"/>
+      <x:c r="H146" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I146" s="389" t="n">
+      <x:c r="I146" s="388" t="n">
         <x:f>IF(H146="Done",1,IF(H146="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K146" s="65"/>
-      <x:c r="L146" s="65"/>
-      <x:c r="M146" s="65" t="str">
-        <x:v>Stable target.</x:v>
+      <x:c r="J146" s="66" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="K146" s="66"/>
+      <x:c r="L146" s="66"/>
+      <x:c r="M146" s="66" t="str">
+        <x:v>Framework-independent agent commands.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="66" t="str">
-        <x:v>R-141</x:v>
-      </x:c>
-      <x:c r="B147" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C147" s="66" t="str">
+      <x:c r="A147" s="65" t="str">
+        <x:v>R-140</x:v>
+      </x:c>
+      <x:c r="B147" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C147" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D147" s="66" t="str">
-        <x:v>Flutter scaled template</x:v>
-      </x:c>
-      <x:c r="E147" s="66" t="str">
-        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
-      </x:c>
-      <x:c r="F147" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G147" s="66"/>
-      <x:c r="H147" s="66" t="str">
+      <x:c r="D147" s="65" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="E147" s="65" t="str">
+        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
+      </x:c>
+      <x:c r="F147" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G147" s="65"/>
+      <x:c r="H147" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I147" s="388" t="n">
+      <x:c r="I147" s="389" t="n">
         <x:f>IF(H147="Done",1,IF(H147="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="66" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="K147" s="66"/>
-      <x:c r="L147" s="66"/>
-      <x:c r="M147" s="66" t="str">
-        <x:v>Use only when complexity warrants.</x:v>
+      <x:c r="J147" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K147" s="65"/>
+      <x:c r="L147" s="65"/>
+      <x:c r="M147" s="65" t="str">
+        <x:v>Stable target.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="65" t="str">
-        <x:v>R-142</x:v>
-      </x:c>
-      <x:c r="B148" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C148" s="65" t="str">
+      <x:c r="A148" s="66" t="str">
+        <x:v>R-141</x:v>
+      </x:c>
+      <x:c r="B148" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C148" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D148" s="65" t="str">
-        <x:v>React Native TypeScript template</x:v>
-      </x:c>
-      <x:c r="E148" s="65" t="str">
-        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
-      </x:c>
-      <x:c r="F148" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G148" s="65"/>
-      <x:c r="H148" s="65" t="str">
+      <x:c r="D148" s="66" t="str">
+        <x:v>Flutter scaled template</x:v>
+      </x:c>
+      <x:c r="E148" s="66" t="str">
+        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
+      </x:c>
+      <x:c r="F148" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G148" s="66"/>
+      <x:c r="H148" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I148" s="389" t="n">
+      <x:c r="I148" s="388" t="n">
         <x:f>IF(H148="Done",1,IF(H148="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J148" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K148" s="65"/>
-      <x:c r="L148" s="65"/>
-      <x:c r="M148" s="65" t="str">
-        <x:v>Expo profile when capabilities fit.</x:v>
+      <x:c r="J148" s="66" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="K148" s="66"/>
+      <x:c r="L148" s="66"/>
+      <x:c r="M148" s="66" t="str">
+        <x:v>Use only when complexity warrants.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="66" t="str">
-        <x:v>R-143</x:v>
-      </x:c>
-      <x:c r="B149" s="66" t="str">
+      <x:c r="A149" s="65" t="str">
+        <x:v>R-142</x:v>
+      </x:c>
+      <x:c r="B149" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C149" s="66" t="str">
+      <x:c r="C149" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D149" s="66" t="str">
-        <x:v>React Native shared TS packages</x:v>
-      </x:c>
-      <x:c r="E149" s="66" t="str">
-        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
-      </x:c>
-      <x:c r="F149" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G149" s="66"/>
-      <x:c r="H149" s="66" t="str">
+      <x:c r="D149" s="65" t="str">
+        <x:v>React Native TypeScript template</x:v>
+      </x:c>
+      <x:c r="E149" s="65" t="str">
+        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
+      </x:c>
+      <x:c r="F149" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G149" s="65"/>
+      <x:c r="H149" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I149" s="388" t="n">
+      <x:c r="I149" s="389" t="n">
         <x:f>IF(H149="Done",1,IF(H149="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J149" s="66" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K149" s="66"/>
-      <x:c r="L149" s="66"/>
-      <x:c r="M149" s="66" t="str">
-        <x:v>Do not share UI blindly.</x:v>
+      <x:c r="J149" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K149" s="65"/>
+      <x:c r="L149" s="65"/>
+      <x:c r="M149" s="65" t="str">
+        <x:v>Expo profile when capabilities fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="65" t="str">
-        <x:v>R-144</x:v>
-      </x:c>
-      <x:c r="B150" s="65" t="str">
+      <x:c r="A150" s="66" t="str">
+        <x:v>R-143</x:v>
+      </x:c>
+      <x:c r="B150" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C150" s="65" t="str">
+      <x:c r="C150" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D150" s="65" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="E150" s="65" t="str">
-        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
-      </x:c>
-      <x:c r="F150" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G150" s="65"/>
-      <x:c r="H150" s="65" t="str">
+      <x:c r="D150" s="66" t="str">
+        <x:v>React Native shared TS packages</x:v>
+      </x:c>
+      <x:c r="E150" s="66" t="str">
+        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
+      </x:c>
+      <x:c r="F150" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G150" s="66"/>
+      <x:c r="H150" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I150" s="389" t="n">
+      <x:c r="I150" s="388" t="n">
         <x:f>IF(H150="Done",1,IF(H150="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="65" t="str">
-        <x:v>Native Android Agent</x:v>
-      </x:c>
-      <x:c r="K150" s="65"/>
-      <x:c r="L150" s="65"/>
-      <x:c r="M150" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J150" s="66" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K150" s="66"/>
+      <x:c r="L150" s="66"/>
+      <x:c r="M150" s="66" t="str">
+        <x:v>Do not share UI blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="66" t="str">
-        <x:v>R-145</x:v>
-      </x:c>
-      <x:c r="B151" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C151" s="66" t="str">
+      <x:c r="A151" s="65" t="str">
+        <x:v>R-144</x:v>
+      </x:c>
+      <x:c r="B151" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C151" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D151" s="66" t="str">
-        <x:v>Native Android scaled modules</x:v>
-      </x:c>
-      <x:c r="E151" s="66" t="str">
-        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
-      </x:c>
-      <x:c r="F151" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G151" s="66"/>
-      <x:c r="H151" s="66" t="str">
+      <x:c r="D151" s="65" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="E151" s="65" t="str">
+        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
+      </x:c>
+      <x:c r="F151" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G151" s="65"/>
+      <x:c r="H151" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I151" s="388" t="n">
+      <x:c r="I151" s="389" t="n">
         <x:f>IF(H151="Done",1,IF(H151="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J151" s="66" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="K151" s="66"/>
-      <x:c r="L151" s="66"/>
-      <x:c r="M151" s="66" t="str">
-        <x:v>Experienced team structure.</x:v>
+      <x:c r="J151" s="65" t="str">
+        <x:v>Native Android Agent</x:v>
+      </x:c>
+      <x:c r="K151" s="65"/>
+      <x:c r="L151" s="65"/>
+      <x:c r="M151" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="65" t="str">
-        <x:v>R-146</x:v>
-      </x:c>
-      <x:c r="B152" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C152" s="65" t="str">
+      <x:c r="A152" s="66" t="str">
+        <x:v>R-145</x:v>
+      </x:c>
+      <x:c r="B152" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C152" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D152" s="65" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="E152" s="65" t="str">
-        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
-      </x:c>
-      <x:c r="F152" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G152" s="65"/>
-      <x:c r="H152" s="65" t="str">
+      <x:c r="D152" s="66" t="str">
+        <x:v>Native Android scaled modules</x:v>
+      </x:c>
+      <x:c r="E152" s="66" t="str">
+        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
+      </x:c>
+      <x:c r="F152" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G152" s="66"/>
+      <x:c r="H152" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I152" s="389" t="n">
+      <x:c r="I152" s="388" t="n">
         <x:f>IF(H152="Done",1,IF(H152="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J152" s="65" t="str">
-        <x:v>Native iOS Agent</x:v>
-      </x:c>
-      <x:c r="K152" s="65"/>
-      <x:c r="L152" s="65"/>
-      <x:c r="M152" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J152" s="66" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="K152" s="66"/>
+      <x:c r="L152" s="66"/>
+      <x:c r="M152" s="66" t="str">
+        <x:v>Experienced team structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="66" t="str">
-        <x:v>R-147</x:v>
-      </x:c>
-      <x:c r="B153" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C153" s="66" t="str">
+      <x:c r="A153" s="65" t="str">
+        <x:v>R-146</x:v>
+      </x:c>
+      <x:c r="B153" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C153" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D153" s="66" t="str">
-        <x:v>Native iOS scaled Swift Packages</x:v>
-      </x:c>
-      <x:c r="E153" s="66" t="str">
-        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
-      </x:c>
-      <x:c r="F153" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G153" s="66"/>
-      <x:c r="H153" s="66" t="str">
+      <x:c r="D153" s="65" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="E153" s="65" t="str">
+        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
+      </x:c>
+      <x:c r="F153" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G153" s="65"/>
+      <x:c r="H153" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I153" s="388" t="n">
+      <x:c r="I153" s="389" t="n">
         <x:f>IF(H153="Done",1,IF(H153="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J153" s="66" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="K153" s="66"/>
-      <x:c r="L153" s="66"/>
-      <x:c r="M153" s="66" t="str">
-        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
+      <x:c r="J153" s="65" t="str">
+        <x:v>Native iOS Agent</x:v>
+      </x:c>
+      <x:c r="K153" s="65"/>
+      <x:c r="L153" s="65"/>
+      <x:c r="M153" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="65" t="str">
-        <x:v>R-148</x:v>
-      </x:c>
-      <x:c r="B154" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C154" s="65" t="str">
+      <x:c r="A154" s="66" t="str">
+        <x:v>R-147</x:v>
+      </x:c>
+      <x:c r="B154" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C154" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D154" s="65" t="str">
-        <x:v>Next.js public web template</x:v>
-      </x:c>
-      <x:c r="E154" s="65" t="str">
-        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
-      </x:c>
-      <x:c r="F154" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G154" s="65"/>
-      <x:c r="H154" s="65" t="str">
+      <x:c r="D154" s="66" t="str">
+        <x:v>Native iOS scaled Swift Packages</x:v>
+      </x:c>
+      <x:c r="E154" s="66" t="str">
+        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
+      </x:c>
+      <x:c r="F154" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G154" s="66"/>
+      <x:c r="H154" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I154" s="389" t="n">
+      <x:c r="I154" s="388" t="n">
         <x:f>IF(H154="Done",1,IF(H154="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="65" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="K154" s="65"/>
-      <x:c r="L154" s="65"/>
-      <x:c r="M154" s="65" t="str">
-        <x:v>Web optimized independently.</x:v>
+      <x:c r="J154" s="66" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="K154" s="66"/>
+      <x:c r="L154" s="66"/>
+      <x:c r="M154" s="66" t="str">
+        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="66" t="str">
-        <x:v>R-149</x:v>
-      </x:c>
-      <x:c r="B155" s="66" t="str">
+      <x:c r="A155" s="65" t="str">
+        <x:v>R-148</x:v>
+      </x:c>
+      <x:c r="B155" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C155" s="66" t="str">
+      <x:c r="C155" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D155" s="66" t="str">
-        <x:v>Next.js admin template</x:v>
-      </x:c>
-      <x:c r="E155" s="66" t="str">
-        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
-      </x:c>
-      <x:c r="F155" s="66" t="str">
+      <x:c r="D155" s="65" t="str">
+        <x:v>Next.js public web template</x:v>
+      </x:c>
+      <x:c r="E155" s="65" t="str">
+        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
+      </x:c>
+      <x:c r="F155" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G155" s="66"/>
-      <x:c r="H155" s="66" t="str">
+      <x:c r="G155" s="65"/>
+      <x:c r="H155" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I155" s="388" t="n">
+      <x:c r="I155" s="389" t="n">
         <x:f>IF(H155="Done",1,IF(H155="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J155" s="66" t="str">
+      <x:c r="J155" s="65" t="str">
         <x:v>Next.js web + admin default</x:v>
       </x:c>
-      <x:c r="K155" s="66"/>
-      <x:c r="L155" s="66"/>
-      <x:c r="M155" s="66" t="str">
-        <x:v>Never force admin onto Flutter/RN Web.</x:v>
+      <x:c r="K155" s="65"/>
+      <x:c r="L155" s="65"/>
+      <x:c r="M155" s="65" t="str">
+        <x:v>Web optimized independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="65" t="str">
-        <x:v>R-150</x:v>
-      </x:c>
-      <x:c r="B156" s="65" t="str">
+      <x:c r="A156" s="66" t="str">
+        <x:v>R-149</x:v>
+      </x:c>
+      <x:c r="B156" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C156" s="65" t="str">
+      <x:c r="C156" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D156" s="65" t="str">
-        <x:v>Go backend standard template</x:v>
-      </x:c>
-      <x:c r="E156" s="65" t="str">
-        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
-      </x:c>
-      <x:c r="F156" s="65" t="str">
+      <x:c r="D156" s="66" t="str">
+        <x:v>Next.js admin template</x:v>
+      </x:c>
+      <x:c r="E156" s="66" t="str">
+        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
+      </x:c>
+      <x:c r="F156" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G156" s="65"/>
-      <x:c r="H156" s="65" t="str">
+      <x:c r="G156" s="66"/>
+      <x:c r="H156" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I156" s="389" t="n">
+      <x:c r="I156" s="388" t="n">
         <x:f>IF(H156="Done",1,IF(H156="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J156" s="65" t="str">
-        <x:v>Backend Agent</x:v>
-      </x:c>
-      <x:c r="K156" s="65"/>
-      <x:c r="L156" s="65"/>
-      <x:c r="M156" s="65" t="str">
-        <x:v>Default backend profile.</x:v>
+      <x:c r="J156" s="66" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="K156" s="66"/>
+      <x:c r="L156" s="66"/>
+      <x:c r="M156" s="66" t="str">
+        <x:v>Never force admin onto Flutter/RN Web.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="66" t="str">
-        <x:v>R-151</x:v>
-      </x:c>
-      <x:c r="B157" s="66" t="str">
+      <x:c r="A157" s="65" t="str">
+        <x:v>R-150</x:v>
+      </x:c>
+      <x:c r="B157" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C157" s="66" t="str">
+      <x:c r="C157" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D157" s="66" t="str">
-        <x:v>Python backend standard template</x:v>
-      </x:c>
-      <x:c r="E157" s="66" t="str">
-        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
-      </x:c>
-      <x:c r="F157" s="66" t="str">
+      <x:c r="D157" s="65" t="str">
+        <x:v>Go backend standard template</x:v>
+      </x:c>
+      <x:c r="E157" s="65" t="str">
+        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
+      </x:c>
+      <x:c r="F157" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G157" s="66"/>
-      <x:c r="H157" s="66" t="str">
+      <x:c r="G157" s="65"/>
+      <x:c r="H157" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I157" s="388" t="n">
+      <x:c r="I157" s="389" t="n">
         <x:f>IF(H157="Done",1,IF(H157="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J157" s="66" t="str">
+      <x:c r="J157" s="65" t="str">
         <x:v>Backend Agent</x:v>
       </x:c>
-      <x:c r="K157" s="66"/>
-      <x:c r="L157" s="66"/>
-      <x:c r="M157" s="66" t="str">
-        <x:v>Alternative default backend profile.</x:v>
+      <x:c r="K157" s="65"/>
+      <x:c r="L157" s="65"/>
+      <x:c r="M157" s="65" t="str">
+        <x:v>Default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="65" t="str">
-        <x:v>R-152</x:v>
-      </x:c>
-      <x:c r="B158" s="65" t="str">
+      <x:c r="A158" s="66" t="str">
+        <x:v>R-151</x:v>
+      </x:c>
+      <x:c r="B158" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C158" s="65" t="str">
-        <x:v>Contracts</x:v>
-      </x:c>
-      <x:c r="D158" s="65" t="str">
-        <x:v>Generated client matrix</x:v>
-      </x:c>
-      <x:c r="E158" s="65" t="str">
-        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
-      </x:c>
-      <x:c r="F158" s="65" t="str">
+      <x:c r="C158" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D158" s="66" t="str">
+        <x:v>Python backend standard template</x:v>
+      </x:c>
+      <x:c r="E158" s="66" t="str">
+        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
+      </x:c>
+      <x:c r="F158" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G158" s="65"/>
-      <x:c r="H158" s="65" t="str">
+      <x:c r="G158" s="66"/>
+      <x:c r="H158" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I158" s="389" t="n">
+      <x:c r="I158" s="388" t="n">
         <x:f>IF(H158="Done",1,IF(H158="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="65" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K158" s="65"/>
-      <x:c r="L158" s="65"/>
-      <x:c r="M158" s="65" t="str">
-        <x:v>Contract-first consistency.</x:v>
+      <x:c r="J158" s="66" t="str">
+        <x:v>Backend Agent</x:v>
+      </x:c>
+      <x:c r="K158" s="66"/>
+      <x:c r="L158" s="66"/>
+      <x:c r="M158" s="66" t="str">
+        <x:v>Alternative default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="66" t="str">
-        <x:v>R-153</x:v>
-      </x:c>
-      <x:c r="B159" s="66" t="str">
+      <x:c r="A159" s="65" t="str">
+        <x:v>R-152</x:v>
+      </x:c>
+      <x:c r="B159" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C159" s="66" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D159" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="E159" s="66" t="str">
-        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
-      </x:c>
-      <x:c r="F159" s="66" t="str">
+      <x:c r="C159" s="65" t="str">
+        <x:v>Contracts</x:v>
+      </x:c>
+      <x:c r="D159" s="65" t="str">
+        <x:v>Generated client matrix</x:v>
+      </x:c>
+      <x:c r="E159" s="65" t="str">
+        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
+      </x:c>
+      <x:c r="F159" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G159" s="66"/>
-      <x:c r="H159" s="66" t="str">
+      <x:c r="G159" s="65"/>
+      <x:c r="H159" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I159" s="388" t="n">
+      <x:c r="I159" s="389" t="n">
         <x:f>IF(H159="Done",1,IF(H159="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K159" s="66"/>
-      <x:c r="L159" s="66"/>
-      <x:c r="M159" s="66" t="str">
-        <x:v>Stable/Beta/Experimental visible to user.</x:v>
+      <x:c r="J159" s="65" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K159" s="65"/>
+      <x:c r="L159" s="65"/>
+      <x:c r="M159" s="65" t="str">
+        <x:v>Contract-first consistency.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="65" t="str">
-        <x:v>R-154</x:v>
-      </x:c>
-      <x:c r="B160" s="65" t="str">
+      <x:c r="A160" s="66" t="str">
+        <x:v>R-153</x:v>
+      </x:c>
+      <x:c r="B160" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C160" s="65" t="str">
-        <x:v>Dependencies</x:v>
-      </x:c>
-      <x:c r="D160" s="65" t="str">
-        <x:v>Approved dependency catalog</x:v>
-      </x:c>
-      <x:c r="E160" s="65" t="str">
-        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
-      </x:c>
-      <x:c r="F160" s="65" t="str">
+      <x:c r="C160" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D160" s="66" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="E160" s="66" t="str">
+        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
+      </x:c>
+      <x:c r="F160" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G160" s="65"/>
-      <x:c r="H160" s="65" t="str">
+      <x:c r="G160" s="66"/>
+      <x:c r="H160" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I160" s="389" t="n">
+      <x:c r="I160" s="388" t="n">
         <x:f>IF(H160="Done",1,IF(H160="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K160" s="65"/>
-      <x:c r="L160" s="65"/>
-      <x:c r="M160" s="65" t="str">
-        <x:v>Prevents dependency explosion.</x:v>
+      <x:c r="J160" s="66" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K160" s="66"/>
+      <x:c r="L160" s="66"/>
+      <x:c r="M160" s="66" t="str">
+        <x:v>Stable/Beta/Experimental visible to user.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="66" t="str">
-        <x:v>R-155</x:v>
-      </x:c>
-      <x:c r="B161" s="66" t="str">
+      <x:c r="A161" s="65" t="str">
+        <x:v>R-154</x:v>
+      </x:c>
+      <x:c r="B161" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C161" s="66" t="str">
-        <x:v>Platform Architecture</x:v>
-      </x:c>
-      <x:c r="D161" s="66" t="str">
-        <x:v>Go control plane modular monolith</x:v>
-      </x:c>
-      <x:c r="E161" s="66" t="str">
-        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
-      </x:c>
-      <x:c r="F161" s="66" t="str">
+      <x:c r="C161" s="65" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D161" s="65" t="str">
+        <x:v>Approved dependency catalog</x:v>
+      </x:c>
+      <x:c r="E161" s="65" t="str">
+        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
+      </x:c>
+      <x:c r="F161" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G161" s="66"/>
-      <x:c r="H161" s="66" t="str">
+      <x:c r="G161" s="65"/>
+      <x:c r="H161" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I161" s="388" t="n">
+      <x:c r="I161" s="389" t="n">
         <x:f>IF(H161="Done",1,IF(H161="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J161" s="66" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K161" s="66"/>
-      <x:c r="L161" s="66"/>
-      <x:c r="M161" s="66" t="str">
-        <x:v>Avoid premature microservices.</x:v>
+      <x:c r="J161" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K161" s="65"/>
+      <x:c r="L161" s="65"/>
+      <x:c r="M161" s="65" t="str">
+        <x:v>Prevents dependency explosion.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="65" t="str">
-        <x:v>R-156</x:v>
-      </x:c>
-      <x:c r="B162" s="65" t="str">
+      <x:c r="A162" s="66" t="str">
+        <x:v>R-155</x:v>
+      </x:c>
+      <x:c r="B162" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C162" s="65" t="str">
+      <x:c r="C162" s="66" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D162" s="65" t="str">
-        <x:v>Python agent engine boundary</x:v>
-      </x:c>
-      <x:c r="E162" s="65" t="str">
-        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
-      </x:c>
-      <x:c r="F162" s="65" t="str">
+      <x:c r="D162" s="66" t="str">
+        <x:v>Go control plane modular monolith</x:v>
+      </x:c>
+      <x:c r="E162" s="66" t="str">
+        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
+      </x:c>
+      <x:c r="F162" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G162" s="65"/>
-      <x:c r="H162" s="65" t="str">
+      <x:c r="G162" s="66"/>
+      <x:c r="H162" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I162" s="389" t="n">
+      <x:c r="I162" s="388" t="n">
         <x:f>IF(H162="Done",1,IF(H162="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J162" s="65" t="str">
-        <x:v>Model gateway</x:v>
-      </x:c>
-      <x:c r="K162" s="65"/>
-      <x:c r="L162" s="65"/>
-      <x:c r="M162" s="65" t="str">
-        <x:v>Different ecosystem/iteration cadence.</x:v>
+      <x:c r="J162" s="66" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K162" s="66"/>
+      <x:c r="L162" s="66"/>
+      <x:c r="M162" s="66" t="str">
+        <x:v>Avoid premature microservices.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="66" t="str">
-        <x:v>R-157</x:v>
-      </x:c>
-      <x:c r="B163" s="66" t="str">
+      <x:c r="A163" s="65" t="str">
+        <x:v>R-156</x:v>
+      </x:c>
+      <x:c r="B163" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C163" s="66" t="str">
+      <x:c r="C163" s="65" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D163" s="66" t="str">
-        <x:v>Runner manager boundary</x:v>
-      </x:c>
-      <x:c r="E163" s="66" t="str">
-        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
-      </x:c>
-      <x:c r="F163" s="66" t="str">
+      <x:c r="D163" s="65" t="str">
+        <x:v>Python agent engine boundary</x:v>
+      </x:c>
+      <x:c r="E163" s="65" t="str">
+        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
+      </x:c>
+      <x:c r="F163" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G163" s="66"/>
-      <x:c r="H163" s="66" t="str">
+      <x:c r="G163" s="65"/>
+      <x:c r="H163" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I163" s="388" t="n">
+      <x:c r="I163" s="389" t="n">
         <x:f>IF(H163="Done",1,IF(H163="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J163" s="66" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
-      </x:c>
-      <x:c r="K163" s="66"/>
-      <x:c r="L163" s="66"/>
-      <x:c r="M163" s="66" t="str">
-        <x:v>Central execution control.</x:v>
+      <x:c r="J163" s="65" t="str">
+        <x:v>Model gateway</x:v>
+      </x:c>
+      <x:c r="K163" s="65"/>
+      <x:c r="L163" s="65"/>
+      <x:c r="M163" s="65" t="str">
+        <x:v>Different ecosystem/iteration cadence.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="65" t="str">
-        <x:v>R-158</x:v>
-      </x:c>
-      <x:c r="B164" s="65" t="str">
+      <x:c r="A164" s="66" t="str">
+        <x:v>R-157</x:v>
+      </x:c>
+      <x:c r="B164" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C164" s="65" t="str">
-        <x:v>CI/CD</x:v>
-      </x:c>
-      <x:c r="D164" s="65" t="str">
-        <x:v>Unified PR pipeline</x:v>
-      </x:c>
-      <x:c r="E164" s="65" t="str">
-        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
-      </x:c>
-      <x:c r="F164" s="65" t="str">
+      <x:c r="C164" s="66" t="str">
+        <x:v>Platform Architecture</x:v>
+      </x:c>
+      <x:c r="D164" s="66" t="str">
+        <x:v>Runner manager boundary</x:v>
+      </x:c>
+      <x:c r="E164" s="66" t="str">
+        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
+      </x:c>
+      <x:c r="F164" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G164" s="65"/>
-      <x:c r="H164" s="65" t="str">
+      <x:c r="G164" s="66"/>
+      <x:c r="H164" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I164" s="389" t="n">
+      <x:c r="I164" s="388" t="n">
         <x:f>IF(H164="Done",1,IF(H164="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J164" s="65" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="K164" s="65"/>
-      <x:c r="L164" s="65"/>
-      <x:c r="M164" s="65" t="str">
-        <x:v>Real iOS compile uses macOS.</x:v>
+      <x:c r="J164" s="66" t="str">
+        <x:v>Ephemeral Linux sandbox</x:v>
+      </x:c>
+      <x:c r="K164" s="66"/>
+      <x:c r="L164" s="66"/>
+      <x:c r="M164" s="66" t="str">
+        <x:v>Central execution control.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="66" t="str">
-        <x:v>R-159</x:v>
-      </x:c>
-      <x:c r="B165" s="66" t="str">
+      <x:c r="A165" s="65" t="str">
+        <x:v>R-158</x:v>
+      </x:c>
+      <x:c r="B165" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C165" s="66" t="str">
+      <x:c r="C165" s="65" t="str">
         <x:v>CI/CD</x:v>
       </x:c>
-      <x:c r="D165" s="66" t="str">
-        <x:v>Immutable build promotion</x:v>
-      </x:c>
-      <x:c r="E165" s="66" t="str">
-        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
-      </x:c>
-      <x:c r="F165" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G165" s="66"/>
-      <x:c r="H165" s="66" t="str">
+      <x:c r="D165" s="65" t="str">
+        <x:v>Unified PR pipeline</x:v>
+      </x:c>
+      <x:c r="E165" s="65" t="str">
+        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
+      </x:c>
+      <x:c r="F165" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G165" s="65"/>
+      <x:c r="H165" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I165" s="388" t="n">
+      <x:c r="I165" s="389" t="n">
         <x:f>IF(H165="Done",1,IF(H165="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J165" s="66" t="str">
-        <x:v>Deployment Agent</x:v>
-      </x:c>
-      <x:c r="K165" s="66"/>
-      <x:c r="L165" s="66"/>
-      <x:c r="M165" s="66" t="str">
-        <x:v>Reduces preview/production mismatch.</x:v>
+      <x:c r="J165" s="65" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="K165" s="65"/>
+      <x:c r="L165" s="65"/>
+      <x:c r="M165" s="65" t="str">
+        <x:v>Real iOS compile uses macOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="65" t="str">
-        <x:v>R-160</x:v>
-      </x:c>
-      <x:c r="B166" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C166" s="65" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D166" s="65" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="E166" s="65" t="str">
-        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
-      </x:c>
-      <x:c r="F166" s="65" t="str">
+      <x:c r="A166" s="66" t="str">
+        <x:v>R-159</x:v>
+      </x:c>
+      <x:c r="B166" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C166" s="66" t="str">
+        <x:v>CI/CD</x:v>
+      </x:c>
+      <x:c r="D166" s="66" t="str">
+        <x:v>Immutable build promotion</x:v>
+      </x:c>
+      <x:c r="E166" s="66" t="str">
+        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
+      </x:c>
+      <x:c r="F166" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G166" s="65"/>
-      <x:c r="H166" s="65" t="str">
+      <x:c r="G166" s="66"/>
+      <x:c r="H166" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I166" s="389" t="n">
+      <x:c r="I166" s="388" t="n">
         <x:f>IF(H166="Done",1,IF(H166="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J166" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K166" s="65"/>
-      <x:c r="L166" s="65"/>
-      <x:c r="M166" s="65"/>
+      <x:c r="J166" s="66" t="str">
+        <x:v>Deployment Agent</x:v>
+      </x:c>
+      <x:c r="K166" s="66"/>
+      <x:c r="L166" s="66"/>
+      <x:c r="M166" s="66" t="str">
+        <x:v>Reduces preview/production mismatch.</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="66" t="str">
-        <x:v>R-161</x:v>
-      </x:c>
-      <x:c r="B167" s="66" t="str">
+      <x:c r="A167" s="65" t="str">
+        <x:v>R-160</x:v>
+      </x:c>
+      <x:c r="B167" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C167" s="66" t="str">
-        <x:v>Preview</x:v>
-      </x:c>
-      <x:c r="D167" s="66" t="str">
-        <x:v>Local Mac Agent productized</x:v>
-      </x:c>
-      <x:c r="E167" s="66" t="str">
-        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
-      </x:c>
-      <x:c r="F167" s="66" t="str">
+      <x:c r="C167" s="65" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D167" s="65" t="str">
+        <x:v>Framework upgrade workflow</x:v>
+      </x:c>
+      <x:c r="E167" s="65" t="str">
+        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
+      </x:c>
+      <x:c r="F167" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G167" s="66"/>
-      <x:c r="H167" s="66" t="str">
+      <x:c r="G167" s="65"/>
+      <x:c r="H167" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I167" s="388" t="n">
+      <x:c r="I167" s="389" t="n">
         <x:f>IF(H167="Done",1,IF(H167="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J167" s="66" t="str">
-        <x:v>Local Mac Agent</x:v>
-      </x:c>
-      <x:c r="K167" s="66"/>
-      <x:c r="L167" s="66"/>
-      <x:c r="M167" s="66" t="str">
-        <x:v>Reduces cloud Mac cost.</x:v>
-      </x:c>
+      <x:c r="J167" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K167" s="65"/>
+      <x:c r="L167" s="65"/>
+      <x:c r="M167" s="65"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="65" t="str">
-        <x:v>R-162</x:v>
-      </x:c>
-      <x:c r="B168" s="65" t="str">
+      <x:c r="A168" s="66" t="str">
+        <x:v>R-161</x:v>
+      </x:c>
+      <x:c r="B168" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C168" s="65" t="str">
+      <x:c r="C168" s="66" t="str">
         <x:v>Preview</x:v>
       </x:c>
-      <x:c r="D168" s="65" t="str">
-        <x:v>Interactive cloud simulator metering</x:v>
-      </x:c>
-      <x:c r="E168" s="65" t="str">
-        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
-      </x:c>
-      <x:c r="F168" s="65" t="str">
+      <x:c r="D168" s="66" t="str">
+        <x:v>Local Mac Agent productized</x:v>
+      </x:c>
+      <x:c r="E168" s="66" t="str">
+        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
+      </x:c>
+      <x:c r="F168" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G168" s="65"/>
-      <x:c r="H168" s="65" t="str">
+      <x:c r="G168" s="66"/>
+      <x:c r="H168" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I168" s="389" t="n">
+      <x:c r="I168" s="388" t="n">
         <x:f>IF(H168="Done",1,IF(H168="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J168" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K168" s="65"/>
-      <x:c r="L168" s="65"/>
-      <x:c r="M168" s="65" t="str">
-        <x:v>Separate verification build cost from interactive session cost.</x:v>
+      <x:c r="J168" s="66" t="str">
+        <x:v>Local Mac Agent</x:v>
+      </x:c>
+      <x:c r="K168" s="66"/>
+      <x:c r="L168" s="66"/>
+      <x:c r="M168" s="66" t="str">
+        <x:v>Reduces cloud Mac cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="66" t="str">
-        <x:v>R-163</x:v>
-      </x:c>
-      <x:c r="B169" s="66" t="str">
+      <x:c r="A169" s="65" t="str">
+        <x:v>R-162</x:v>
+      </x:c>
+      <x:c r="B169" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C169" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D169" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="E169" s="66" t="str">
-        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
-      </x:c>
-      <x:c r="F169" s="66" t="str">
+      <x:c r="C169" s="65" t="str">
+        <x:v>Preview</x:v>
+      </x:c>
+      <x:c r="D169" s="65" t="str">
+        <x:v>Interactive cloud simulator metering</x:v>
+      </x:c>
+      <x:c r="E169" s="65" t="str">
+        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
+      </x:c>
+      <x:c r="F169" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G169" s="66"/>
-      <x:c r="H169" s="66" t="str">
+      <x:c r="G169" s="65"/>
+      <x:c r="H169" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I169" s="388" t="n">
+      <x:c r="I169" s="389" t="n">
         <x:f>IF(H169="Done",1,IF(H169="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J169" s="66" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K169" s="66"/>
-      <x:c r="L169" s="66"/>
-      <x:c r="M169" s="66" t="str">
-        <x:v>Measure before rewrite.</x:v>
+      <x:c r="J169" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K169" s="65"/>
+      <x:c r="L169" s="65"/>
+      <x:c r="M169" s="65" t="str">
+        <x:v>Separate verification build cost from interactive session cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="65" t="str">
-        <x:v>R-164</x:v>
-      </x:c>
-      <x:c r="B170" s="65" t="str">
+      <x:c r="A170" s="66" t="str">
+        <x:v>R-163</x:v>
+      </x:c>
+      <x:c r="B170" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C170" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D170" s="65" t="str">
-        <x:v>Template/repo health dashboard</x:v>
-      </x:c>
-      <x:c r="E170" s="65" t="str">
-        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
-      </x:c>
-      <x:c r="F170" s="65" t="str">
+      <x:c r="C170" s="66" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D170" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="E170" s="66" t="str">
+        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
+      </x:c>
+      <x:c r="F170" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G170" s="65"/>
-      <x:c r="H170" s="65" t="str">
+      <x:c r="G170" s="66"/>
+      <x:c r="H170" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I170" s="389" t="n">
+      <x:c r="I170" s="388" t="n">
         <x:f>IF(H170="Done",1,IF(H170="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J170" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="K170" s="65"/>
-      <x:c r="L170" s="65"/>
-      <x:c r="M170" s="65" t="str">
-        <x:v>Use data to trigger architecture review.</x:v>
+      <x:c r="J170" s="66" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K170" s="66"/>
+      <x:c r="L170" s="66"/>
+      <x:c r="M170" s="66" t="str">
+        <x:v>Measure before rewrite.</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="66" t="str">
-        <x:v>R-165</x:v>
-      </x:c>
-      <x:c r="B171" s="66" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C171" s="66" t="str">
-        <x:v>Migration</x:v>
-      </x:c>
-      <x:c r="D171" s="66" t="str">
-        <x:v>Cross-platform to native migration engine</x:v>
-      </x:c>
-      <x:c r="E171" s="66" t="str">
-        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
-      </x:c>
-      <x:c r="F171" s="66" t="str">
+      <x:c r="A171" s="65" t="str">
+        <x:v>R-164</x:v>
+      </x:c>
+      <x:c r="B171" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C171" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D171" s="65" t="str">
+        <x:v>Template/repo health dashboard</x:v>
+      </x:c>
+      <x:c r="E171" s="65" t="str">
+        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
+      </x:c>
+      <x:c r="F171" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G171" s="66"/>
-      <x:c r="H171" s="66" t="str">
+      <x:c r="G171" s="65"/>
+      <x:c r="H171" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I171" s="388" t="n">
+      <x:c r="I171" s="389" t="n">
         <x:f>IF(H171="Done",1,IF(H171="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J171" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="K171" s="66"/>
-      <x:c r="L171" s="66"/>
-      <x:c r="M171" s="66" t="str">
-        <x:v>Prevents framework lock-in.</x:v>
+      <x:c r="J171" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="K171" s="65"/>
+      <x:c r="L171" s="65"/>
+      <x:c r="M171" s="65" t="str">
+        <x:v>Use data to trigger architecture review.</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="65" t="str">
-        <x:v>R-166</x:v>
-      </x:c>
-      <x:c r="B172" s="65" t="str">
+      <x:c r="A172" s="66" t="str">
+        <x:v>R-165</x:v>
+      </x:c>
+      <x:c r="B172" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C172" s="65" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D172" s="65" t="str">
-        <x:v>Cross-repo task coordinator</x:v>
-      </x:c>
-      <x:c r="E172" s="65" t="str">
-        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
-      </x:c>
-      <x:c r="F172" s="65" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G172" s="65"/>
-      <x:c r="H172" s="65" t="str">
+      <x:c r="C172" s="66" t="str">
+        <x:v>Migration</x:v>
+      </x:c>
+      <x:c r="D172" s="66" t="str">
+        <x:v>Cross-platform to native migration engine</x:v>
+      </x:c>
+      <x:c r="E172" s="66" t="str">
+        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
+      </x:c>
+      <x:c r="F172" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G172" s="66"/>
+      <x:c r="H172" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I172" s="389" t="n">
+      <x:c r="I172" s="388" t="n">
         <x:f>IF(H172="Done",1,IF(H172="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J172" s="65" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="K172" s="65"/>
-      <x:c r="L172" s="65"/>
-      <x:c r="M172" s="65"/>
+      <x:c r="J172" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="K172" s="66"/>
+      <x:c r="L172" s="66"/>
+      <x:c r="M172" s="66" t="str">
+        <x:v>Prevents framework lock-in.</x:v>
+      </x:c>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="66" t="str">
-        <x:v>R-167</x:v>
-      </x:c>
-      <x:c r="B173" s="66" t="str">
+      <x:c r="A173" s="65" t="str">
+        <x:v>R-166</x:v>
+      </x:c>
+      <x:c r="B173" s="65" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C173" s="66" t="str">
-        <x:v>Infrastructure</x:v>
-      </x:c>
-      <x:c r="D173" s="66" t="str">
-        <x:v>BYOC / private runners</x:v>
-      </x:c>
-      <x:c r="E173" s="66" t="str">
-        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
-      </x:c>
-      <x:c r="F173" s="66" t="str">
+      <x:c r="C173" s="65" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D173" s="65" t="str">
+        <x:v>Cross-repo task coordinator</x:v>
+      </x:c>
+      <x:c r="E173" s="65" t="str">
+        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
+      </x:c>
+      <x:c r="F173" s="65" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G173" s="66"/>
-      <x:c r="H173" s="66" t="str">
+      <x:c r="G173" s="65"/>
+      <x:c r="H173" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I173" s="388" t="n">
+      <x:c r="I173" s="389" t="n">
         <x:f>IF(H173="Done",1,IF(H173="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J173" s="66" t="str">
-        <x:v>Enterprise workload isolation</x:v>
-      </x:c>
-      <x:c r="K173" s="66"/>
-      <x:c r="L173" s="66"/>
-      <x:c r="M173" s="66"/>
+      <x:c r="J173" s="65" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="K173" s="65"/>
+      <x:c r="L173" s="65"/>
+      <x:c r="M173" s="65"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="65" t="str">
-        <x:v>R-168</x:v>
-      </x:c>
-      <x:c r="B174" s="65" t="str">
+      <x:c r="A174" s="66" t="str">
+        <x:v>R-167</x:v>
+      </x:c>
+      <x:c r="B174" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C174" s="65" t="str">
-        <x:v>Testing</x:v>
-      </x:c>
-      <x:c r="D174" s="65" t="str">
-        <x:v>Physical device cloud integration</x:v>
-      </x:c>
-      <x:c r="E174" s="65" t="str">
-        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
-      </x:c>
-      <x:c r="F174" s="65" t="str">
+      <x:c r="C174" s="66" t="str">
+        <x:v>Infrastructure</x:v>
+      </x:c>
+      <x:c r="D174" s="66" t="str">
+        <x:v>BYOC / private runners</x:v>
+      </x:c>
+      <x:c r="E174" s="66" t="str">
+        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
+      </x:c>
+      <x:c r="F174" s="66" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G174" s="65"/>
-      <x:c r="H174" s="65" t="str">
+      <x:c r="G174" s="66"/>
+      <x:c r="H174" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I174" s="389" t="n">
+      <x:c r="I174" s="388" t="n">
         <x:f>IF(H174="Done",1,IF(H174="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J174" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K174" s="65"/>
-      <x:c r="L174" s="65"/>
-      <x:c r="M174" s="65"/>
+      <x:c r="J174" s="66" t="str">
+        <x:v>Enterprise workload isolation</x:v>
+      </x:c>
+      <x:c r="K174" s="66"/>
+      <x:c r="L174" s="66"/>
+      <x:c r="M174" s="66"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="127" t="str">
-        <x:v>R-169</x:v>
-      </x:c>
-      <x:c r="B175" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
-      </x:c>
-      <x:c r="C175" s="127" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D175" s="127" t="str">
-        <x:v>Template support lifecycle</x:v>
-      </x:c>
-      <x:c r="E175" s="127" t="str">
-        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
-      </x:c>
-      <x:c r="F175" s="127" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G175" s="127"/>
-      <x:c r="H175" s="127" t="str">
+      <x:c r="A175" s="65" t="str">
+        <x:v>R-168</x:v>
+      </x:c>
+      <x:c r="B175" s="65" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C175" s="65" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="D175" s="65" t="str">
+        <x:v>Physical device cloud integration</x:v>
+      </x:c>
+      <x:c r="E175" s="65" t="str">
+        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
+      </x:c>
+      <x:c r="F175" s="65" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G175" s="65"/>
+      <x:c r="H175" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I175" s="390" t="n">
+      <x:c r="I175" s="389" t="n">
         <x:f>IF(H175="Done",1,IF(H175="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J175" s="127" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="K175" s="127"/>
-      <x:c r="L175" s="127"/>
-      <x:c r="M175" s="127"/>
+      <x:c r="J175" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K175" s="65"/>
+      <x:c r="L175" s="65"/>
+      <x:c r="M175" s="65"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="127" t="str">
-        <x:v>R-170</x:v>
+        <x:v>R-169</x:v>
       </x:c>
       <x:c r="B176" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C176" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D176" s="127" t="str">
-        <x:v>Framework/toolchain production SLO</x:v>
+        <x:v>Template support lifecycle</x:v>
       </x:c>
       <x:c r="E176" s="127" t="str">
-        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
+        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
       </x:c>
       <x:c r="F176" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G176" s="127"/>
       <x:c r="H176" s="127" t="str">
@@ -16259,29 +16267,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J176" s="127" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="K176" s="127"/>
       <x:c r="L176" s="127"/>
-      <x:c r="M176" s="127" t="str">
-        <x:v>Production readiness is measured, not assumed.</x:v>
-      </x:c>
+      <x:c r="M176" s="127"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="127" t="str">
-        <x:v>R-171</x:v>
+        <x:v>R-170</x:v>
       </x:c>
       <x:c r="B177" s="127" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C177" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D177" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Framework/toolchain production SLO</x:v>
       </x:c>
       <x:c r="E177" s="127" t="str">
-        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
+        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
       </x:c>
       <x:c r="F177" s="127" t="str">
         <x:v>P0</x:v>
@@ -16295,17 +16301,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="127" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="K177" s="127"/>
       <x:c r="L177" s="127"/>
       <x:c r="M177" s="127" t="str">
-        <x:v>No agent-to-vendor SDK coupling.</x:v>
+        <x:v>Production readiness is measured, not assumed.</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="127" t="str">
-        <x:v>R-172</x:v>
+        <x:v>R-171</x:v>
       </x:c>
       <x:c r="B178" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16314,10 +16320,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D178" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="E178" s="127" t="str">
-        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
+        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
       </x:c>
       <x:c r="F178" s="127" t="str">
         <x:v>P0</x:v>
@@ -16331,17 +16337,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K178" s="127"/>
       <x:c r="L178" s="127"/>
       <x:c r="M178" s="127" t="str">
-        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
+        <x:v>No agent-to-vendor SDK coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="127" t="str">
-        <x:v>R-173</x:v>
+        <x:v>R-172</x:v>
       </x:c>
       <x:c r="B179" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16350,10 +16356,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D179" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="E179" s="127" t="str">
-        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
+        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
       </x:c>
       <x:c r="F179" s="127" t="str">
         <x:v>P0</x:v>
@@ -16372,12 +16378,12 @@
       <x:c r="K179" s="127"/>
       <x:c r="L179" s="127"/>
       <x:c r="M179" s="127" t="str">
-        <x:v>Cheapest safe runtime wins.</x:v>
+        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="127" t="str">
-        <x:v>R-174</x:v>
+        <x:v>R-173</x:v>
       </x:c>
       <x:c r="B180" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16386,13 +16392,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D180" s="127" t="str">
-        <x:v>Browser runtime PoC</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="E180" s="127" t="str">
-        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
+        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
       </x:c>
       <x:c r="F180" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G180" s="127"/>
       <x:c r="H180" s="127" t="str">
@@ -16403,17 +16409,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K180" s="127"/>
       <x:c r="L180" s="127"/>
       <x:c r="M180" s="127" t="str">
-        <x:v>Not universal sandbox.</x:v>
+        <x:v>Cheapest safe runtime wins.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="127" t="str">
-        <x:v>R-175</x:v>
+        <x:v>R-174</x:v>
       </x:c>
       <x:c r="B181" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16422,13 +16428,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D181" s="127" t="str">
-        <x:v>Runtime quotas and metering</x:v>
+        <x:v>Browser runtime PoC</x:v>
       </x:c>
       <x:c r="E181" s="127" t="str">
-        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
+        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
       </x:c>
       <x:c r="F181" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G181" s="127"/>
       <x:c r="H181" s="127" t="str">
@@ -16439,29 +16445,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="K181" s="127"/>
       <x:c r="L181" s="127"/>
       <x:c r="M181" s="127" t="str">
-        <x:v>Required for cost and abuse control.</x:v>
+        <x:v>Not universal sandbox.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="127" t="str">
-        <x:v>R-176</x:v>
+        <x:v>R-175</x:v>
       </x:c>
       <x:c r="B182" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C182" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D182" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Runtime quotas and metering</x:v>
       </x:c>
       <x:c r="E182" s="127" t="str">
-        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
+        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
       </x:c>
       <x:c r="F182" s="127" t="str">
         <x:v>P0</x:v>
@@ -16475,17 +16481,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="127" t="str">
-        <x:v>Supervisor / orchestrator</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K182" s="127"/>
       <x:c r="L182" s="127"/>
       <x:c r="M182" s="127" t="str">
-        <x:v>Platform-owned state schema.</x:v>
+        <x:v>Required for cost and abuse control.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="127" t="str">
-        <x:v>R-177</x:v>
+        <x:v>R-176</x:v>
       </x:c>
       <x:c r="B183" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16494,10 +16500,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D183" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="E183" s="127" t="str">
-        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
+        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
       </x:c>
       <x:c r="F183" s="127" t="str">
         <x:v>P0</x:v>
@@ -16511,17 +16517,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Supervisor / orchestrator</x:v>
       </x:c>
       <x:c r="K183" s="127"/>
       <x:c r="L183" s="127"/>
       <x:c r="M183" s="127" t="str">
-        <x:v>No full restart by default.</x:v>
+        <x:v>Platform-owned state schema.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="127" t="str">
-        <x:v>R-178</x:v>
+        <x:v>R-177</x:v>
       </x:c>
       <x:c r="B184" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16530,10 +16536,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D184" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="E184" s="127" t="str">
-        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
+        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
       </x:c>
       <x:c r="F184" s="127" t="str">
         <x:v>P0</x:v>
@@ -16547,29 +16553,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K184" s="127"/>
       <x:c r="L184" s="127"/>
       <x:c r="M184" s="127" t="str">
-        <x:v>Prevent duplicate side effects.</x:v>
+        <x:v>No full restart by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="127" t="str">
-        <x:v>R-179</x:v>
+        <x:v>R-178</x:v>
       </x:c>
       <x:c r="B185" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C185" s="127" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D185" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="E185" s="127" t="str">
-        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
+        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
       </x:c>
       <x:c r="F185" s="127" t="str">
         <x:v>P0</x:v>
@@ -16583,29 +16589,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K185" s="127"/>
       <x:c r="L185" s="127"/>
       <x:c r="M185" s="127" t="str">
-        <x:v>Supports replay, audit and debugging.</x:v>
+        <x:v>Prevent duplicate side effects.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="127" t="str">
-        <x:v>R-180</x:v>
+        <x:v>R-179</x:v>
       </x:c>
       <x:c r="B186" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C186" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D186" s="127" t="str">
-        <x:v>Orchestrator Adapter</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="E186" s="127" t="str">
-        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
+        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
       </x:c>
       <x:c r="F186" s="127" t="str">
         <x:v>P0</x:v>
@@ -16624,24 +16630,24 @@
       <x:c r="K186" s="127"/>
       <x:c r="L186" s="127"/>
       <x:c r="M186" s="127" t="str">
-        <x:v>LangGraph may be first implementation.</x:v>
+        <x:v>Supports replay, audit and debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="127" t="str">
-        <x:v>R-181</x:v>
+        <x:v>R-180</x:v>
       </x:c>
       <x:c r="B187" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C187" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D187" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Orchestrator Adapter</x:v>
       </x:c>
       <x:c r="E187" s="127" t="str">
-        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
+        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
       </x:c>
       <x:c r="F187" s="127" t="str">
         <x:v>P0</x:v>
@@ -16655,17 +16661,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K187" s="127"/>
       <x:c r="L187" s="127"/>
       <x:c r="M187" s="127" t="str">
-        <x:v>Frontend never parses provider-specific streams.</x:v>
+        <x:v>LangGraph may be first implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="127" t="str">
-        <x:v>R-182</x:v>
+        <x:v>R-181</x:v>
       </x:c>
       <x:c r="B188" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16674,10 +16680,10 @@
         <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D188" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="E188" s="127" t="str">
-        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
+        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
       </x:c>
       <x:c r="F188" s="127" t="str">
         <x:v>P0</x:v>
@@ -16691,29 +16697,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K188" s="127"/>
       <x:c r="L188" s="127"/>
       <x:c r="M188" s="127" t="str">
-        <x:v>SSE allowed for simple one-way streams.</x:v>
+        <x:v>Frontend never parses provider-specific streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="127" t="str">
-        <x:v>R-183</x:v>
+        <x:v>R-182</x:v>
       </x:c>
       <x:c r="B189" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C189" s="127" t="str">
-        <x:v>Approvals</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D189" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="E189" s="127" t="str">
-        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
+        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
       </x:c>
       <x:c r="F189" s="127" t="str">
         <x:v>P0</x:v>
@@ -16727,17 +16733,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="K189" s="127"/>
       <x:c r="L189" s="127"/>
       <x:c r="M189" s="127" t="str">
-        <x:v>Approval based on risk.</x:v>
+        <x:v>SSE allowed for simple one-way streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="127" t="str">
-        <x:v>R-184</x:v>
+        <x:v>R-183</x:v>
       </x:c>
       <x:c r="B190" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16746,10 +16752,10 @@
         <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D190" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="E190" s="127" t="str">
-        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
+        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
       </x:c>
       <x:c r="F190" s="127" t="str">
         <x:v>P0</x:v>
@@ -16763,29 +16769,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K190" s="127"/>
       <x:c r="L190" s="127"/>
       <x:c r="M190" s="127" t="str">
-        <x:v>Production/destructive actions auditable.</x:v>
+        <x:v>Approval based on risk.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="127" t="str">
-        <x:v>R-185</x:v>
+        <x:v>R-184</x:v>
       </x:c>
       <x:c r="B191" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C191" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D191" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="E191" s="127" t="str">
-        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
+        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
       </x:c>
       <x:c r="F191" s="127" t="str">
         <x:v>P0</x:v>
@@ -16799,17 +16805,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="K191" s="127"/>
       <x:c r="L191" s="127"/>
       <x:c r="M191" s="127" t="str">
-        <x:v>Deny by default.</x:v>
+        <x:v>Production/destructive actions auditable.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="127" t="str">
-        <x:v>R-186</x:v>
+        <x:v>R-185</x:v>
       </x:c>
       <x:c r="B192" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16818,13 +16824,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D192" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="E192" s="127" t="str">
-        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
+        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
       </x:c>
       <x:c r="F192" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G192" s="127"/>
       <x:c r="H192" s="127" t="str">
@@ -16835,17 +16841,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K192" s="127"/>
       <x:c r="L192" s="127"/>
       <x:c r="M192" s="127" t="str">
-        <x:v>No arbitrary agent-to-MCP connections.</x:v>
+        <x:v>Deny by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="127" t="str">
-        <x:v>R-187</x:v>
+        <x:v>R-186</x:v>
       </x:c>
       <x:c r="B193" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16854,13 +16860,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D193" s="127" t="str">
-        <x:v>Tool secret broker</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="E193" s="127" t="str">
-        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
+        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
       </x:c>
       <x:c r="F193" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G193" s="127"/>
       <x:c r="H193" s="127" t="str">
@@ -16876,27 +16882,27 @@
       <x:c r="K193" s="127"/>
       <x:c r="L193" s="127"/>
       <x:c r="M193" s="127" t="str">
-        <x:v>Audit every secret grant.</x:v>
+        <x:v>No arbitrary agent-to-MCP connections.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="127" t="str">
-        <x:v>R-188</x:v>
+        <x:v>R-187</x:v>
       </x:c>
       <x:c r="B194" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C194" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D194" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Tool secret broker</x:v>
       </x:c>
       <x:c r="E194" s="127" t="str">
-        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
+        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
       </x:c>
       <x:c r="F194" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G194" s="127"/>
       <x:c r="H194" s="127" t="str">
@@ -16907,32 +16913,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="127" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="K194" s="127"/>
       <x:c r="L194" s="127"/>
       <x:c r="M194" s="127" t="str">
-        <x:v>Not platform core.</x:v>
+        <x:v>Audit every secret grant.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="127" t="str">
-        <x:v>R-189</x:v>
+        <x:v>R-188</x:v>
       </x:c>
       <x:c r="B195" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C195" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D195" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="E195" s="127" t="str">
-        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
+        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
       </x:c>
       <x:c r="F195" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G195" s="127"/>
       <x:c r="H195" s="127" t="str">
@@ -16943,29 +16949,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J195" s="127" t="str">
-        <x:v>Architecture decision records</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K195" s="127"/>
       <x:c r="L195" s="127"/>
       <x:c r="M195" s="127" t="str">
-        <x:v>References inform; benchmarks decide.</x:v>
+        <x:v>Not platform core.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="127" t="str">
-        <x:v>R-190</x:v>
+        <x:v>R-189</x:v>
       </x:c>
       <x:c r="B196" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C196" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D196" s="127" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="E196" s="127" t="str">
-        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
+        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
       </x:c>
       <x:c r="F196" s="127" t="str">
         <x:v>P0</x:v>
@@ -16979,32 +16985,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J196" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Architecture decision records</x:v>
       </x:c>
       <x:c r="K196" s="127"/>
       <x:c r="L196" s="127"/>
       <x:c r="M196" s="127" t="str">
-        <x:v>Architectural learning != code copying.</x:v>
+        <x:v>References inform; benchmarks decide.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="127" t="str">
-        <x:v>R-191</x:v>
+        <x:v>R-190</x:v>
       </x:c>
       <x:c r="B197" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C197" s="127" t="str">
-        <x:v>Team</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D197" s="127" t="str">
-        <x:v>Shared engineering glossary</x:v>
+        <x:v>Open-source license review</x:v>
       </x:c>
       <x:c r="E197" s="127" t="str">
-        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
+        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
       </x:c>
       <x:c r="F197" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G197" s="127"/>
       <x:c r="H197" s="127" t="str">
@@ -17014,31 +17020,33 @@
         <x:f>IF(H197="Done",1,IF(H197="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J197" s="127"/>
+      <x:c r="J197" s="127" t="str">
+        <x:v>Build-vs-Buy benchmark process</x:v>
+      </x:c>
       <x:c r="K197" s="127"/>
       <x:c r="L197" s="127"/>
       <x:c r="M197" s="127" t="str">
-        <x:v>Use in docs and AI prompts.</x:v>
+        <x:v>Architectural learning != code copying.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="127" t="str">
-        <x:v>R-192</x:v>
+        <x:v>R-191</x:v>
       </x:c>
       <x:c r="B198" s="127" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C198" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Team</x:v>
       </x:c>
       <x:c r="D198" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Shared engineering glossary</x:v>
       </x:c>
       <x:c r="E198" s="127" t="str">
-        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
+        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
       </x:c>
       <x:c r="F198" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G198" s="127"/>
       <x:c r="H198" s="127" t="str">
@@ -17048,30 +17056,28 @@
         <x:f>IF(H198="Done",1,IF(H198="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J198" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
-      </x:c>
+      <x:c r="J198" s="127"/>
       <x:c r="K198" s="127"/>
       <x:c r="L198" s="127"/>
       <x:c r="M198" s="127" t="str">
-        <x:v>Marketplace later.</x:v>
+        <x:v>Use in docs and AI prompts.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="127" t="str">
-        <x:v>R-193</x:v>
+        <x:v>R-192</x:v>
       </x:c>
       <x:c r="B199" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C199" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D199" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="E199" s="127" t="str">
-        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
+        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
       </x:c>
       <x:c r="F199" s="127" t="str">
         <x:v>P1</x:v>
@@ -17085,17 +17091,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J199" s="127" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K199" s="127"/>
       <x:c r="L199" s="127"/>
       <x:c r="M199" s="127" t="str">
-        <x:v>Extends local mode beyond Mac.</x:v>
+        <x:v>Marketplace later.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="127" t="str">
-        <x:v>R-194</x:v>
+        <x:v>R-193</x:v>
       </x:c>
       <x:c r="B200" s="127" t="str">
         <x:v>MID</x:v>
@@ -17104,10 +17110,10 @@
         <x:v>Execution</x:v>
       </x:c>
       <x:c r="D200" s="127" t="str">
-        <x:v>Hybrid BYOK/local mode</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="E200" s="127" t="str">
-        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
+        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
       </x:c>
       <x:c r="F200" s="127" t="str">
         <x:v>P1</x:v>
@@ -17121,29 +17127,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="K200" s="127"/>
       <x:c r="L200" s="127"/>
       <x:c r="M200" s="127" t="str">
-        <x:v>Privacy + cost option.</x:v>
+        <x:v>Extends local mode beyond Mac.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="127" t="str">
-        <x:v>R-195</x:v>
+        <x:v>R-194</x:v>
       </x:c>
       <x:c r="B201" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C201" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D201" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Hybrid BYOK/local mode</x:v>
       </x:c>
       <x:c r="E201" s="127" t="str">
-        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
+        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
       </x:c>
       <x:c r="F201" s="127" t="str">
         <x:v>P1</x:v>
@@ -17157,17 +17163,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K201" s="127"/>
       <x:c r="L201" s="127"/>
       <x:c r="M201" s="127" t="str">
-        <x:v>Validate portability/failover.</x:v>
+        <x:v>Privacy + cost option.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="127" t="str">
-        <x:v>R-196</x:v>
+        <x:v>R-195</x:v>
       </x:c>
       <x:c r="B202" s="127" t="str">
         <x:v>MID</x:v>
@@ -17176,13 +17182,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D202" s="127" t="str">
-        <x:v>Sandbox snapshots and warm pools</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="E202" s="127" t="str">
-        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
+        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
       </x:c>
       <x:c r="F202" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G202" s="127"/>
       <x:c r="H202" s="127" t="str">
@@ -17193,32 +17199,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K202" s="127"/>
       <x:c r="L202" s="127"/>
       <x:c r="M202" s="127" t="str">
-        <x:v>Do not optimize blindly.</x:v>
+        <x:v>Validate portability/failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="127" t="str">
-        <x:v>R-197</x:v>
+        <x:v>R-196</x:v>
       </x:c>
       <x:c r="B203" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C203" s="127" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D203" s="127" t="str">
-        <x:v>Agent time-travel debugging</x:v>
+        <x:v>Sandbox snapshots and warm pools</x:v>
       </x:c>
       <x:c r="E203" s="127" t="str">
-        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
+        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
       </x:c>
       <x:c r="F203" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G203" s="127"/>
       <x:c r="H203" s="127" t="str">
@@ -17229,32 +17235,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K203" s="127"/>
       <x:c r="L203" s="127"/>
       <x:c r="M203" s="127" t="str">
-        <x:v>Operator and developer debugging.</x:v>
+        <x:v>Do not optimize blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="127" t="str">
-        <x:v>R-198</x:v>
+        <x:v>R-197</x:v>
       </x:c>
       <x:c r="B204" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C204" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D204" s="127" t="str">
-        <x:v>Tool marketplace verification</x:v>
+        <x:v>Agent time-travel debugging</x:v>
       </x:c>
       <x:c r="E204" s="127" t="str">
-        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
+        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
       </x:c>
       <x:c r="F204" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G204" s="127"/>
       <x:c r="H204" s="127" t="str">
@@ -17265,32 +17271,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K204" s="127"/>
       <x:c r="L204" s="127"/>
       <x:c r="M204" s="127" t="str">
-        <x:v>Verified badge is evidence-based.</x:v>
+        <x:v>Operator and developer debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="127" t="str">
-        <x:v>R-199</x:v>
+        <x:v>R-198</x:v>
       </x:c>
       <x:c r="B205" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C205" s="127" t="str">
-        <x:v>Routing</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D205" s="127" t="str">
-        <x:v>Runtime provider cost-latency routing</x:v>
+        <x:v>Tool marketplace verification</x:v>
       </x:c>
       <x:c r="E205" s="127" t="str">
-        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
+        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
       </x:c>
       <x:c r="F205" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G205" s="127"/>
       <x:c r="H205" s="127" t="str">
@@ -17301,32 +17307,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K205" s="127"/>
       <x:c r="L205" s="127"/>
       <x:c r="M205" s="127" t="str">
-        <x:v>Policy can override cheapest route.</x:v>
+        <x:v>Verified badge is evidence-based.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="127" t="str">
-        <x:v>R-200</x:v>
+        <x:v>R-199</x:v>
       </x:c>
       <x:c r="B206" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C206" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="D206" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Runtime provider cost-latency routing</x:v>
       </x:c>
       <x:c r="E206" s="127" t="str">
-        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
+        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
       </x:c>
       <x:c r="F206" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G206" s="127"/>
       <x:c r="H206" s="127" t="str">
@@ -17337,29 +17343,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K206" s="127"/>
       <x:c r="L206" s="127"/>
       <x:c r="M206" s="127" t="str">
-        <x:v>Keep portability via IR/contracts.</x:v>
+        <x:v>Policy can override cheapest route.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="127" t="str">
-        <x:v>R-201</x:v>
+        <x:v>R-200</x:v>
       </x:c>
       <x:c r="B207" s="127" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C207" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D207" s="127" t="str">
-        <x:v>Customer private MCP servers</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="E207" s="127" t="str">
-        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
+        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
       </x:c>
       <x:c r="F207" s="127" t="str">
         <x:v>P2</x:v>
@@ -17373,32 +17379,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="K207" s="127"/>
       <x:c r="L207" s="127"/>
       <x:c r="M207" s="127" t="str">
-        <x:v>Enterprise feature.</x:v>
+        <x:v>Keep portability via IR/contracts.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="127" t="str">
-        <x:v>R-202</x:v>
+        <x:v>R-201</x:v>
       </x:c>
       <x:c r="B208" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C208" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D208" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>Customer private MCP servers</x:v>
       </x:c>
       <x:c r="E208" s="127" t="str">
-        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
+        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
       </x:c>
       <x:c r="F208" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G208" s="127"/>
       <x:c r="H208" s="127" t="str">
@@ -17409,32 +17415,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="127" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K208" s="127"/>
       <x:c r="L208" s="127"/>
       <x:c r="M208" s="127" t="str">
-        <x:v>Central policy + audit remain.</x:v>
+        <x:v>Enterprise feature.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="127" t="str">
-        <x:v>R-203</x:v>
+        <x:v>R-202</x:v>
       </x:c>
       <x:c r="B209" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C209" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D209" s="127" t="str">
-        <x:v>Cross-region runtime scheduler</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="E209" s="127" t="str">
-        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
+        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
       </x:c>
       <x:c r="F209" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G209" s="127"/>
       <x:c r="H209" s="127" t="str">
@@ -17445,17 +17451,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="K209" s="127"/>
       <x:c r="L209" s="127"/>
       <x:c r="M209" s="127" t="str">
-        <x:v>Enterprise scale.</x:v>
+        <x:v>Central policy + audit remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="127" t="str">
-        <x:v>R-204</x:v>
+        <x:v>R-203</x:v>
       </x:c>
       <x:c r="B210" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17464,10 +17470,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D210" s="127" t="str">
-        <x:v>Hardened microVM runner fleet</x:v>
+        <x:v>Cross-region runtime scheduler</x:v>
       </x:c>
       <x:c r="E210" s="127" t="str">
-        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
+        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
       </x:c>
       <x:c r="F210" s="127" t="str">
         <x:v>P2</x:v>
@@ -17481,32 +17487,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="127" t="str">
-        <x:v>Provider cost-latency routing</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="K210" s="127"/>
       <x:c r="L210" s="127"/>
       <x:c r="M210" s="127" t="str">
-        <x:v>Do not build before benchmark.</x:v>
+        <x:v>Enterprise scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="127" t="str">
-        <x:v>R-205</x:v>
+        <x:v>R-204</x:v>
       </x:c>
       <x:c r="B211" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C211" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D211" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>Hardened microVM runner fleet</x:v>
       </x:c>
       <x:c r="E211" s="127" t="str">
-        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
+        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
       </x:c>
       <x:c r="F211" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G211" s="127"/>
       <x:c r="H211" s="127" t="str">
@@ -17517,29 +17523,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Provider cost-latency routing</x:v>
       </x:c>
       <x:c r="K211" s="127"/>
       <x:c r="L211" s="127"/>
       <x:c r="M211" s="127" t="str">
-        <x:v>Checkpoint-aware failover.</x:v>
+        <x:v>Do not build before benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="127" t="str">
-        <x:v>R-206</x:v>
+        <x:v>R-205</x:v>
       </x:c>
       <x:c r="B212" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C212" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D212" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="E212" s="127" t="str">
-        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
+        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
       </x:c>
       <x:c r="F212" s="127" t="str">
         <x:v>P1</x:v>
@@ -17553,17 +17559,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K212" s="127"/>
       <x:c r="L212" s="127"/>
       <x:c r="M212" s="127" t="str">
-        <x:v>Enterprise override support.</x:v>
+        <x:v>Checkpoint-aware failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="127" t="str">
-        <x:v>R-207</x:v>
+        <x:v>R-206</x:v>
       </x:c>
       <x:c r="B213" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17572,13 +17578,13 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D213" s="127" t="str">
-        <x:v>Two-person critical approval</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="E213" s="127" t="str">
-        <x:v>Optional dual approval for L4 actions.</x:v>
+        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
       </x:c>
       <x:c r="F213" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G213" s="127"/>
       <x:c r="H213" s="127" t="str">
@@ -17589,29 +17595,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K213" s="127"/>
       <x:c r="L213" s="127"/>
       <x:c r="M213" s="127" t="str">
-        <x:v>High-risk enterprise.</x:v>
+        <x:v>Enterprise override support.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="127" t="str">
-        <x:v>R-208</x:v>
+        <x:v>R-207</x:v>
       </x:c>
       <x:c r="B214" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C214" s="127" t="str">
-        <x:v>Models</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D214" s="127" t="str">
-        <x:v>Customer private model endpoints</x:v>
+        <x:v>Two-person critical approval</x:v>
       </x:c>
       <x:c r="E214" s="127" t="str">
-        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
+        <x:v>Optional dual approval for L4 actions.</x:v>
       </x:c>
       <x:c r="F214" s="127" t="str">
         <x:v>P2</x:v>
@@ -17625,29 +17631,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="127" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="K214" s="127"/>
       <x:c r="L214" s="127"/>
       <x:c r="M214" s="127" t="str">
-        <x:v>No direct client-to-model coupling.</x:v>
+        <x:v>High-risk enterprise.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="127" t="str">
-        <x:v>R-209</x:v>
+        <x:v>R-208</x:v>
       </x:c>
       <x:c r="B215" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C215" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D215" s="127" t="str">
-        <x:v>Automated provider benchmark suite</x:v>
+        <x:v>Customer private model endpoints</x:v>
       </x:c>
       <x:c r="E215" s="127" t="str">
-        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
+        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
       </x:c>
       <x:c r="F215" s="127" t="str">
         <x:v>P2</x:v>
@@ -17661,32 +17667,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="K215" s="127"/>
       <x:c r="L215" s="127"/>
       <x:c r="M215" s="127" t="str">
-        <x:v>Feeds routing/ADR reviews.</x:v>
+        <x:v>No direct client-to-model coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="127" t="str">
-        <x:v>R-210</x:v>
+        <x:v>R-209</x:v>
       </x:c>
       <x:c r="B216" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C216" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D216" s="127" t="str">
-        <x:v>Crash-resume production test</x:v>
+        <x:v>Automated provider benchmark suite</x:v>
       </x:c>
       <x:c r="E216" s="127" t="str">
-        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
+        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
       </x:c>
       <x:c r="F216" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G216" s="127"/>
       <x:c r="H216" s="127" t="str">
@@ -17697,17 +17703,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="K216" s="127"/>
       <x:c r="L216" s="127"/>
       <x:c r="M216" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Feeds routing/ADR reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="127" t="str">
-        <x:v>R-211</x:v>
+        <x:v>R-210</x:v>
       </x:c>
       <x:c r="B217" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17716,10 +17722,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D217" s="127" t="str">
-        <x:v>Duplicate side-effect prevention test</x:v>
+        <x:v>Crash-resume production test</x:v>
       </x:c>
       <x:c r="E217" s="127" t="str">
-        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
+        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
       </x:c>
       <x:c r="F217" s="127" t="str">
         <x:v>P0</x:v>
@@ -17733,7 +17739,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K217" s="127"/>
       <x:c r="L217" s="127"/>
@@ -17743,19 +17749,19 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="127" t="str">
-        <x:v>R-212</x:v>
+        <x:v>R-211</x:v>
       </x:c>
       <x:c r="B218" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C218" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D218" s="127" t="str">
-        <x:v>WebSocket replay correctness SLO</x:v>
+        <x:v>Duplicate side-effect prevention test</x:v>
       </x:c>
       <x:c r="E218" s="127" t="str">
-        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
+        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
       </x:c>
       <x:c r="F218" s="127" t="str">
         <x:v>P0</x:v>
@@ -17769,7 +17775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K218" s="127"/>
       <x:c r="L218" s="127"/>
@@ -17779,19 +17785,19 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="127" t="str">
-        <x:v>R-213</x:v>
+        <x:v>R-212</x:v>
       </x:c>
       <x:c r="B219" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C219" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D219" s="127" t="str">
-        <x:v>MCP isolation and prompt-injection test</x:v>
+        <x:v>WebSocket replay correctness SLO</x:v>
       </x:c>
       <x:c r="E219" s="127" t="str">
-        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
+        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
       </x:c>
       <x:c r="F219" s="127" t="str">
         <x:v>P0</x:v>
@@ -17805,7 +17811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="K219" s="127"/>
       <x:c r="L219" s="127"/>
@@ -17815,7 +17821,7 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="127" t="str">
-        <x:v>R-214</x:v>
+        <x:v>R-213</x:v>
       </x:c>
       <x:c r="B220" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17824,10 +17830,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D220" s="127" t="str">
-        <x:v>Sandbox tenant isolation test</x:v>
+        <x:v>MCP isolation and prompt-injection test</x:v>
       </x:c>
       <x:c r="E220" s="127" t="str">
-        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
+        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
       </x:c>
       <x:c r="F220" s="127" t="str">
         <x:v>P0</x:v>
@@ -17841,7 +17847,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K220" s="127"/>
       <x:c r="L220" s="127"/>
@@ -17851,19 +17857,19 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="127" t="str">
-        <x:v>R-215</x:v>
+        <x:v>R-214</x:v>
       </x:c>
       <x:c r="B221" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C221" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D221" s="127" t="str">
-        <x:v>Runtime provider outage failover</x:v>
+        <x:v>Sandbox tenant isolation test</x:v>
       </x:c>
       <x:c r="E221" s="127" t="str">
-        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
+        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
       </x:c>
       <x:c r="F221" s="127" t="str">
         <x:v>P0</x:v>
@@ -17877,7 +17883,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K221" s="127"/>
       <x:c r="L221" s="127"/>
@@ -17887,19 +17893,19 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="127" t="str">
-        <x:v>R-216</x:v>
+        <x:v>R-215</x:v>
       </x:c>
       <x:c r="B222" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C222" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D222" s="127" t="str">
-        <x:v>Approval auditability test</x:v>
+        <x:v>Runtime provider outage failover</x:v>
       </x:c>
       <x:c r="E222" s="127" t="str">
-        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
+        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
       </x:c>
       <x:c r="F222" s="127" t="str">
         <x:v>P0</x:v>
@@ -17913,7 +17919,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="K222" s="127"/>
       <x:c r="L222" s="127"/>
@@ -17923,22 +17929,22 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="127" t="str">
-        <x:v>R-217</x:v>
+        <x:v>R-216</x:v>
       </x:c>
       <x:c r="B223" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C223" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D223" s="127" t="str">
-        <x:v>BaaS to custom migration test</x:v>
+        <x:v>Approval auditability test</x:v>
       </x:c>
       <x:c r="E223" s="127" t="str">
-        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
       </x:c>
       <x:c r="F223" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G223" s="127"/>
       <x:c r="H223" s="127" t="str">
@@ -17949,65 +17955,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K223" s="127"/>
       <x:c r="L223" s="127"/>
       <x:c r="M223" s="127" t="str">
-        <x:v>Avoid backend lock-in.</x:v>
+        <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" t="str">
-        <x:v>R-218</x:v>
-      </x:c>
-      <x:c r="B224" t="str">
+      <x:c r="A224" s="127" t="str">
+        <x:v>R-217</x:v>
+      </x:c>
+      <x:c r="B224" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C224" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="D224" t="str">
-        <x:v>Local Agent security lifecycle</x:v>
-      </x:c>
-      <x:c r="E224" t="str">
-        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
-      </x:c>
-      <x:c r="F224" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G224"/>
-      <x:c r="H224" t="str">
+      <x:c r="C224" s="127" t="str">
+        <x:v>Backend Strategy</x:v>
+      </x:c>
+      <x:c r="D224" s="127" t="str">
+        <x:v>BaaS to custom migration test</x:v>
+      </x:c>
+      <x:c r="E224" s="127" t="str">
+        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+      </x:c>
+      <x:c r="F224" s="127" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G224" s="127"/>
+      <x:c r="H224" s="127" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I224" t="n">
+      <x:c r="I224" s="390" t="n">
         <x:f>IF(H224="Done",1,IF(H224="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J224" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
-      </x:c>
-      <x:c r="K224"/>
-      <x:c r="L224"/>
-      <x:c r="M224" t="str">
-        <x:v>Production gate.</x:v>
+      <x:c r="J224" s="127" t="str">
+        <x:v>BaaS provider expansion</x:v>
+      </x:c>
+      <x:c r="K224" s="127"/>
+      <x:c r="L224" s="127"/>
+      <x:c r="M224" s="127" t="str">
+        <x:v>Avoid backend lock-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" t="str">
-        <x:v>R-219</x:v>
+        <x:v>R-218</x:v>
       </x:c>
       <x:c r="B225" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C225" t="str">
-        <x:v>Compliance</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D225" t="str">
-        <x:v>OSS license and SBOM gate</x:v>
+        <x:v>Local Agent security lifecycle</x:v>
       </x:c>
       <x:c r="E225" t="str">
-        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
       </x:c>
       <x:c r="F225" t="str">
         <x:v>P0</x:v>
@@ -18021,11 +18027,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K225"/>
       <x:c r="L225"/>
       <x:c r="M225" t="str">
+        <x:v>Production gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" t="str">
+        <x:v>R-219</x:v>
+      </x:c>
+      <x:c r="B226" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C226" t="str">
+        <x:v>Compliance</x:v>
+      </x:c>
+      <x:c r="D226" t="str">
+        <x:v>OSS license and SBOM gate</x:v>
+      </x:c>
+      <x:c r="E226" t="str">
+        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+      </x:c>
+      <x:c r="F226" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G226"/>
+      <x:c r="H226" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="I226" t="n">
+        <x:f>IF(H226="Done",1,IF(H226="In Progress",0.5,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J226" t="str">
+        <x:v>Open-source license review</x:v>
+      </x:c>
+      <x:c r="K226"/>
+      <x:c r="L226"/>
+      <x:c r="M226" t="str">
         <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
@@ -18034,7 +18076,7 @@
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H4:H114">
+  <x:conditionalFormatting sqref="H4:H115">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>H4="Done"</x:formula>
     </x:cfRule>
@@ -18049,34 +18091,34 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="10">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B114">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B115">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F114">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F115">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H114">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H115">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B115:B138">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B116:B139">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F115:F138">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F116:F139">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H115:H138">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H116:H139">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F139:F174">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F140:F175">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H139:H174">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H140:H175">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H223">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H224">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F223">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F224">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -10662,11 +10662,11 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-007</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation in progress on ai/R-008-cloud-provider-adapters; multi-provider cloud adapters + env bootstrap + offline tests added; no cloud key set, cloud_calls=0.</x:v>
+        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2389,7 +2389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M115" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M116" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -2701,11 +2701,11 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"MVP")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"MVP")</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"MVP",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"MVP",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"MID",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"MID",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,7 +2746,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F6)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"ADVANCED",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"ADVANCED",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$226,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$226,"PRODUCTION",Phase_Roadmap!$H$4:$H$226,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"PRODUCTION",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F8)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$226,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -10641,7 +10641,7 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10650,10 +10650,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Cloud API-key provider adapters</x:v>
+        <x:v>Usage and cost accounting</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
+        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
@@ -10662,28 +10662,28 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation in progress on ai/R-009-usage-cost-accounting; usage/cost accounting records, price book, and ledger added; wired into the gateway; offline tests added; local_calls=0, cloud_calls=0.</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10692,10 +10692,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>Balanced Model Gateway router</x:v>
+        <x:v>Cloud API-key provider adapters</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
+        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
@@ -10711,21 +10711,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
+        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10734,16 +10734,16 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>Loopback Ollama provider adapter</x:v>
+        <x:v>Balanced Model Gateway router</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
+        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G11" s="32" t="str">
-        <x:v>Codex</x:v>
+        <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H11" s="32" t="str">
         <x:v>Done</x:v>
@@ -10753,21 +10753,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10776,10 +10776,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
@@ -10795,33 +10795,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C13" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
@@ -10837,33 +10837,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
@@ -10879,33 +10879,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K14" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L14" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M14" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C15" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
@@ -10921,33 +10921,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K15" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L15" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M15" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C16" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
@@ -10963,53 +10963,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J16" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K16" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L16" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M16" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C17" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G17" s="32"/>
+      <x:c r="G17" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H17" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I17" s="376" t="n">
         <x:f>IF(H17="Done",1,IF(H17="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="32"/>
-      <x:c r="K17" s="32"/>
-      <x:c r="L17" s="32"/>
-      <x:c r="M17" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K17" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L17" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M17" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11018,10 +11028,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
@@ -11041,7 +11051,7 @@
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11050,10 +11060,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
@@ -11073,7 +11083,7 @@
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11082,10 +11092,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
@@ -11105,7 +11115,7 @@
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11114,10 +11124,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11137,7 +11147,7 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11146,10 +11156,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11169,19 +11179,19 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C23" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11201,7 +11211,7 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11210,10 +11220,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11233,19 +11243,19 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C25" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11265,7 +11275,7 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11274,10 +11284,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11297,19 +11307,19 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C27" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11329,19 +11339,19 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C28" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11361,7 +11371,7 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11370,10 +11380,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11393,19 +11403,19 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C30" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11425,7 +11435,7 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11434,10 +11444,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11457,7 +11467,7 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11466,10 +11476,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11489,19 +11499,19 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C33" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11521,7 +11531,7 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11530,10 +11540,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11553,7 +11563,7 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11562,10 +11572,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11585,7 +11595,7 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11594,10 +11604,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11617,7 +11627,7 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11626,10 +11636,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11649,19 +11659,19 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C38" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11681,7 +11691,7 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11690,10 +11700,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11713,19 +11723,19 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C40" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11745,7 +11755,7 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11754,10 +11764,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11777,19 +11787,19 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C42" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11809,19 +11819,19 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C43" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11841,19 +11851,19 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C44" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11873,7 +11883,7 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11882,10 +11892,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11905,7 +11915,7 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11914,10 +11924,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11937,7 +11947,7 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11946,10 +11956,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11969,19 +11979,19 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C48" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -12001,7 +12011,7 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12010,10 +12020,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12033,19 +12043,19 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C50" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12065,7 +12075,7 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12074,10 +12084,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12097,19 +12107,19 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C52" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12129,7 +12139,7 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12138,10 +12148,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12161,7 +12171,7 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12170,10 +12180,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12193,19 +12203,19 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C55" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12225,7 +12235,7 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12234,10 +12244,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
         <x:v>P0</x:v>
@@ -12257,7 +12267,7 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12266,10 +12276,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
         <x:v>P0</x:v>
@@ -12289,19 +12299,19 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C58" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
         <x:v>P0</x:v>
@@ -12321,22 +12331,22 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C59" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G59" s="32"/>
       <x:c r="H59" s="32" t="str">
@@ -12353,7 +12363,7 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
         <x:v>MID</x:v>
@@ -12362,10 +12372,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
         <x:v>P1</x:v>
@@ -12385,19 +12395,19 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C61" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
         <x:v>P1</x:v>
@@ -12417,19 +12427,19 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C62" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
         <x:v>P1</x:v>
@@ -12449,7 +12459,7 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
@@ -12458,10 +12468,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12481,19 +12491,19 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C64" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12513,19 +12523,19 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C65" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12545,19 +12555,19 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C66" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12577,7 +12587,7 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
@@ -12586,10 +12596,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12609,19 +12619,19 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C68" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12641,7 +12651,7 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
@@ -12650,10 +12660,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12673,7 +12683,7 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
@@ -12682,10 +12692,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12705,19 +12715,19 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C71" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12737,7 +12747,7 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
@@ -12746,10 +12756,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12769,19 +12779,19 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C73" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12801,19 +12811,19 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C74" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12833,19 +12843,19 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C75" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12865,19 +12875,19 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C76" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12897,7 +12907,7 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
@@ -12906,10 +12916,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12929,7 +12939,7 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
@@ -12938,10 +12948,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12961,19 +12971,19 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C79" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -12993,7 +13003,7 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
@@ -13002,10 +13012,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -13025,19 +13035,19 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C81" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
         <x:v>P1</x:v>
@@ -13057,19 +13067,19 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C82" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
         <x:v>P1</x:v>
@@ -13089,19 +13099,19 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C83" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
         <x:v>P1</x:v>
@@ -13121,22 +13131,22 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C84" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G84" s="32"/>
       <x:c r="H84" s="32" t="str">
@@ -13153,7 +13163,7 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13162,13 +13172,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G85" s="32"/>
       <x:c r="H85" s="32" t="str">
@@ -13185,22 +13195,22 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C86" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G86" s="32"/>
       <x:c r="H86" s="32" t="str">
@@ -13217,7 +13227,7 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13226,10 +13236,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
         <x:v>P2</x:v>
@@ -13249,19 +13259,19 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C88" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
         <x:v>P2</x:v>
@@ -13281,19 +13291,19 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C89" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
         <x:v>P2</x:v>
@@ -13313,19 +13323,19 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C90" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13345,7 +13355,7 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13354,10 +13364,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13377,19 +13387,19 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C92" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13409,7 +13419,7 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13418,10 +13428,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13441,7 +13451,7 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13450,10 +13460,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13473,19 +13483,19 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C95" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13505,7 +13515,7 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13514,10 +13524,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13537,19 +13547,19 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C97" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13569,19 +13579,19 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C98" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
         <x:v>P2</x:v>
@@ -13601,7 +13611,7 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13610,10 +13620,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
         <x:v>P2</x:v>
@@ -13633,19 +13643,19 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-093</x:v>
+        <x:v>R-092</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C100" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>Quality trend analytics</x:v>
+        <x:v>Spot/preemptible optimization</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
+        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
         <x:v>P2</x:v>
@@ -13665,22 +13675,22 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-094</x:v>
+        <x:v>R-093</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C101" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>SLO/SLA framework</x:v>
+        <x:v>Quality trend analytics</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
+        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G101" s="32"/>
       <x:c r="H101" s="32" t="str">
@@ -13697,7 +13707,7 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-095</x:v>
+        <x:v>R-094</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13706,10 +13716,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>HA control plane</x:v>
+        <x:v>SLO/SLA framework</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
+        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
         <x:v>P0</x:v>
@@ -13729,7 +13739,7 @@
     </x:row>
     <x:row r="103" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A103" s="32" t="str">
-        <x:v>R-096</x:v>
+        <x:v>R-095</x:v>
       </x:c>
       <x:c r="B103" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13738,10 +13748,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D103" s="32" t="str">
-        <x:v>Backup + restore drills</x:v>
+        <x:v>HA control plane</x:v>
       </x:c>
       <x:c r="E103" s="32" t="str">
-        <x:v>Automated backups plus regularly tested restoration.</x:v>
+        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
       </x:c>
       <x:c r="F103" s="32" t="str">
         <x:v>P0</x:v>
@@ -13761,7 +13771,7 @@
     </x:row>
     <x:row r="104" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A104" s="32" t="str">
-        <x:v>R-097</x:v>
+        <x:v>R-096</x:v>
       </x:c>
       <x:c r="B104" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13770,10 +13780,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D104" s="32" t="str">
-        <x:v>Disaster recovery</x:v>
+        <x:v>Backup + restore drills</x:v>
       </x:c>
       <x:c r="E104" s="32" t="str">
-        <x:v>Document and exercise regional recovery procedures.</x:v>
+        <x:v>Automated backups plus regularly tested restoration.</x:v>
       </x:c>
       <x:c r="F104" s="32" t="str">
         <x:v>P0</x:v>
@@ -13793,19 +13803,19 @@
     </x:row>
     <x:row r="105" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A105" s="32" t="str">
-        <x:v>R-098</x:v>
+        <x:v>R-097</x:v>
       </x:c>
       <x:c r="B105" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C105" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D105" s="32" t="str">
-        <x:v>Independent penetration test</x:v>
+        <x:v>Disaster recovery</x:v>
       </x:c>
       <x:c r="E105" s="32" t="str">
-        <x:v>External security assessment before broad enterprise launch.</x:v>
+        <x:v>Document and exercise regional recovery procedures.</x:v>
       </x:c>
       <x:c r="F105" s="32" t="str">
         <x:v>P0</x:v>
@@ -13825,7 +13835,7 @@
     </x:row>
     <x:row r="106" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A106" s="32" t="str">
-        <x:v>R-099</x:v>
+        <x:v>R-098</x:v>
       </x:c>
       <x:c r="B106" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13834,10 +13844,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D106" s="32" t="str">
-        <x:v>SOC 2 readiness controls</x:v>
+        <x:v>Independent penetration test</x:v>
       </x:c>
       <x:c r="E106" s="32" t="str">
-        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
+        <x:v>External security assessment before broad enterprise launch.</x:v>
       </x:c>
       <x:c r="F106" s="32" t="str">
         <x:v>P0</x:v>
@@ -13857,7 +13867,7 @@
     </x:row>
     <x:row r="107" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A107" s="32" t="str">
-        <x:v>R-100</x:v>
+        <x:v>R-099</x:v>
       </x:c>
       <x:c r="B107" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13866,10 +13876,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>Tenant isolation validation</x:v>
+        <x:v>SOC 2 readiness controls</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
-        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
+        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
       </x:c>
       <x:c r="F107" s="32" t="str">
         <x:v>P0</x:v>
@@ -13889,7 +13899,7 @@
     </x:row>
     <x:row r="108" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A108" s="32" t="str">
-        <x:v>R-101</x:v>
+        <x:v>R-100</x:v>
       </x:c>
       <x:c r="B108" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13898,10 +13908,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>Signing-key hardening</x:v>
+        <x:v>Tenant isolation validation</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
-        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
+        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
       </x:c>
       <x:c r="F108" s="32" t="str">
         <x:v>P0</x:v>
@@ -13921,19 +13931,19 @@
     </x:row>
     <x:row r="109" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A109" s="32" t="str">
-        <x:v>R-102</x:v>
+        <x:v>R-101</x:v>
       </x:c>
       <x:c r="B109" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C109" s="32" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>24x7 incident process</x:v>
+        <x:v>Signing-key hardening</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
-        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
+        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
       </x:c>
       <x:c r="F109" s="32" t="str">
         <x:v>P0</x:v>
@@ -13953,7 +13963,7 @@
     </x:row>
     <x:row r="110" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A110" s="32" t="str">
-        <x:v>R-103</x:v>
+        <x:v>R-102</x:v>
       </x:c>
       <x:c r="B110" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13962,10 +13972,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>Capacity/load tests</x:v>
+        <x:v>24x7 incident process</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
-        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
+        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
       </x:c>
       <x:c r="F110" s="32" t="str">
         <x:v>P0</x:v>
@@ -13985,7 +13995,7 @@
     </x:row>
     <x:row r="111" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A111" s="32" t="str">
-        <x:v>R-104</x:v>
+        <x:v>R-103</x:v>
       </x:c>
       <x:c r="B111" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13994,10 +14004,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>Cost guardrails</x:v>
+        <x:v>Capacity/load tests</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
-        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
+        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
       </x:c>
       <x:c r="F111" s="32" t="str">
         <x:v>P0</x:v>
@@ -14017,19 +14027,19 @@
     </x:row>
     <x:row r="112" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A112" s="32" t="str">
-        <x:v>R-105</x:v>
+        <x:v>R-104</x:v>
       </x:c>
       <x:c r="B112" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C112" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Release qualification suite</x:v>
+        <x:v>Cost guardrails</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Full regression across supported stack versions before platform releases.</x:v>
+        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
         <x:v>P0</x:v>
@@ -14049,7 +14059,7 @@
     </x:row>
     <x:row r="113" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A113" s="32" t="str">
-        <x:v>R-106</x:v>
+        <x:v>R-105</x:v>
       </x:c>
       <x:c r="B113" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14058,10 +14068,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Canary platform releases</x:v>
+        <x:v>Release qualification suite</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
+        <x:v>Full regression across supported stack versions before platform releases.</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
         <x:v>P0</x:v>
@@ -14081,19 +14091,19 @@
     </x:row>
     <x:row r="114" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A114" s="32" t="str">
-        <x:v>R-107</x:v>
+        <x:v>R-106</x:v>
       </x:c>
       <x:c r="B114" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C114" s="32" t="str">
-        <x:v>Support</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D114" s="32" t="str">
-        <x:v>Support tooling</x:v>
+        <x:v>Canary platform releases</x:v>
       </x:c>
       <x:c r="E114" s="32" t="str">
-        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
+        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
       </x:c>
       <x:c r="F114" s="32" t="str">
         <x:v>P0</x:v>
@@ -14113,19 +14123,19 @@
     </x:row>
     <x:row r="115" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A115" s="32" t="str">
-        <x:v>R-108</x:v>
+        <x:v>R-107</x:v>
       </x:c>
       <x:c r="B115" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C115" s="32" t="str">
-        <x:v>Legal/Privacy</x:v>
+        <x:v>Support</x:v>
       </x:c>
       <x:c r="D115" s="32" t="str">
-        <x:v>Privacy + retention controls</x:v>
+        <x:v>Support tooling</x:v>
       </x:c>
       <x:c r="E115" s="32" t="str">
-        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
       </x:c>
       <x:c r="F115" s="32" t="str">
         <x:v>P0</x:v>
@@ -14143,2154 +14153,2152 @@
       <x:c r="L115" s="32"/>
       <x:c r="M115" s="32"/>
     </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="43" t="str">
-        <x:v>R-109</x:v>
-      </x:c>
-      <x:c r="B116" s="43" t="str">
+    <x:row r="116" s="40" customFormat="1" ht="34" customHeight="1">
+      <x:c r="A116" s="32" t="str">
+        <x:v>R-108</x:v>
+      </x:c>
+      <x:c r="B116" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C116" s="43" t="str">
-        <x:v>Business</x:v>
-      </x:c>
-      <x:c r="D116" s="43" t="str">
-        <x:v>Plan entitlements</x:v>
-      </x:c>
-      <x:c r="E116" s="43" t="str">
-        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
-      </x:c>
-      <x:c r="F116" s="43" t="str">
+      <x:c r="C116" s="32" t="str">
+        <x:v>Legal/Privacy</x:v>
+      </x:c>
+      <x:c r="D116" s="32" t="str">
+        <x:v>Privacy + retention controls</x:v>
+      </x:c>
+      <x:c r="E116" s="32" t="str">
+        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+      </x:c>
+      <x:c r="F116" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G116" s="43"/>
-      <x:c r="H116" s="43" t="str">
+      <x:c r="G116" s="32"/>
+      <x:c r="H116" s="32" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I116" s="386" t="n">
+      <x:c r="I116" s="376" t="n">
         <x:f>IF(H116="Done",1,IF(H116="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J116" s="43"/>
-      <x:c r="K116" s="43"/>
-      <x:c r="L116" s="43"/>
-      <x:c r="M116" s="43"/>
+      <x:c r="J116" s="32"/>
+      <x:c r="K116" s="32"/>
+      <x:c r="L116" s="32"/>
+      <x:c r="M116" s="32"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="42" t="str">
-        <x:v>R-110</x:v>
-      </x:c>
-      <x:c r="B117" s="42" t="str">
+      <x:c r="A117" s="43" t="str">
+        <x:v>R-109</x:v>
+      </x:c>
+      <x:c r="B117" s="43" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C117" s="42" t="str">
+      <x:c r="C117" s="43" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="D117" s="42" t="str">
-        <x:v>Unit economics dashboard</x:v>
-      </x:c>
-      <x:c r="E117" s="42" t="str">
-        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
-      </x:c>
-      <x:c r="F117" s="42" t="str">
+      <x:c r="D117" s="43" t="str">
+        <x:v>Plan entitlements</x:v>
+      </x:c>
+      <x:c r="E117" s="43" t="str">
+        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
+      </x:c>
+      <x:c r="F117" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G117" s="42"/>
-      <x:c r="H117" s="42" t="str">
+      <x:c r="G117" s="43"/>
+      <x:c r="H117" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I117" s="387" t="n">
+      <x:c r="I117" s="386" t="n">
         <x:f>IF(H117="Done",1,IF(H117="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J117" s="42"/>
-      <x:c r="K117" s="42"/>
-      <x:c r="L117" s="42"/>
-      <x:c r="M117" s="42"/>
+      <x:c r="J117" s="43"/>
+      <x:c r="K117" s="43"/>
+      <x:c r="L117" s="43"/>
+      <x:c r="M117" s="43"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="43" t="str">
-        <x:v>R-111</x:v>
-      </x:c>
-      <x:c r="B118" s="43" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C118" s="43" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D118" s="43" t="str">
-        <x:v>Cross-platform Mobile Agent</x:v>
-      </x:c>
-      <x:c r="E118" s="43" t="str">
-        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
-      </x:c>
-      <x:c r="F118" s="43" t="str">
+      <x:c r="A118" s="42" t="str">
+        <x:v>R-110</x:v>
+      </x:c>
+      <x:c r="B118" s="42" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C118" s="42" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="D118" s="42" t="str">
+        <x:v>Unit economics dashboard</x:v>
+      </x:c>
+      <x:c r="E118" s="42" t="str">
+        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
+      </x:c>
+      <x:c r="F118" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G118" s="43"/>
-      <x:c r="H118" s="43" t="str">
+      <x:c r="G118" s="42"/>
+      <x:c r="H118" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I118" s="386" t="n">
+      <x:c r="I118" s="387" t="n">
         <x:f>IF(H118="Done",1,IF(H118="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J118" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K118" s="43"/>
-      <x:c r="L118" s="43"/>
-      <x:c r="M118" s="43"/>
+      <x:c r="J118" s="42"/>
+      <x:c r="K118" s="42"/>
+      <x:c r="L118" s="42"/>
+      <x:c r="M118" s="42"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="42" t="str">
-        <x:v>R-112</x:v>
-      </x:c>
-      <x:c r="B119" s="42" t="str">
+      <x:c r="A119" s="43" t="str">
+        <x:v>R-111</x:v>
+      </x:c>
+      <x:c r="B119" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C119" s="42" t="str">
+      <x:c r="C119" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D119" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="E119" s="42" t="str">
-        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
-      </x:c>
-      <x:c r="F119" s="42" t="str">
+      <x:c r="D119" s="43" t="str">
+        <x:v>Cross-platform Mobile Agent</x:v>
+      </x:c>
+      <x:c r="E119" s="43" t="str">
+        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
+      </x:c>
+      <x:c r="F119" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G119" s="42"/>
-      <x:c r="H119" s="42" t="str">
+      <x:c r="G119" s="43"/>
+      <x:c r="H119" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I119" s="387" t="n">
+      <x:c r="I119" s="386" t="n">
         <x:f>IF(H119="Done",1,IF(H119="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J119" s="42" t="str">
-        <x:v>Requirement specification step</x:v>
-      </x:c>
-      <x:c r="K119" s="42"/>
-      <x:c r="L119" s="42"/>
-      <x:c r="M119" s="42"/>
+      <x:c r="J119" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K119" s="43"/>
+      <x:c r="L119" s="43"/>
+      <x:c r="M119" s="43"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="43" t="str">
-        <x:v>R-113</x:v>
-      </x:c>
-      <x:c r="B120" s="43" t="str">
+      <x:c r="A120" s="42" t="str">
+        <x:v>R-112</x:v>
+      </x:c>
+      <x:c r="B120" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C120" s="43" t="str">
+      <x:c r="C120" s="42" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D120" s="43" t="str">
-        <x:v>Auto / Recommended project mode</x:v>
-      </x:c>
-      <x:c r="E120" s="43" t="str">
-        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
-      </x:c>
-      <x:c r="F120" s="43" t="str">
+      <x:c r="D120" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="E120" s="42" t="str">
+        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
+      </x:c>
+      <x:c r="F120" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G120" s="43"/>
-      <x:c r="H120" s="43" t="str">
+      <x:c r="G120" s="42"/>
+      <x:c r="H120" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I120" s="386" t="n">
+      <x:c r="I120" s="387" t="n">
         <x:f>IF(H120="Done",1,IF(H120="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K120" s="43"/>
-      <x:c r="L120" s="43"/>
-      <x:c r="M120" s="43"/>
+      <x:c r="J120" s="42" t="str">
+        <x:v>Requirement specification step</x:v>
+      </x:c>
+      <x:c r="K120" s="42"/>
+      <x:c r="L120" s="42"/>
+      <x:c r="M120" s="42"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="42" t="str">
-        <x:v>R-114</x:v>
-      </x:c>
-      <x:c r="B121" s="42" t="str">
+      <x:c r="A121" s="43" t="str">
+        <x:v>R-113</x:v>
+      </x:c>
+      <x:c r="B121" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C121" s="42" t="str">
+      <x:c r="C121" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D121" s="42" t="str">
-        <x:v>Manual framework override</x:v>
-      </x:c>
-      <x:c r="E121" s="42" t="str">
-        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
-      </x:c>
-      <x:c r="F121" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G121" s="42"/>
-      <x:c r="H121" s="42" t="str">
+      <x:c r="D121" s="43" t="str">
+        <x:v>Auto / Recommended project mode</x:v>
+      </x:c>
+      <x:c r="E121" s="43" t="str">
+        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
+      </x:c>
+      <x:c r="F121" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G121" s="43"/>
+      <x:c r="H121" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I121" s="387" t="n">
+      <x:c r="I121" s="386" t="n">
         <x:f>IF(H121="Done",1,IF(H121="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="42" t="str">
+      <x:c r="J121" s="43" t="str">
         <x:v>Framework recommendation engine</x:v>
       </x:c>
-      <x:c r="K121" s="42"/>
-      <x:c r="L121" s="42"/>
-      <x:c r="M121" s="42"/>
+      <x:c r="K121" s="43"/>
+      <x:c r="L121" s="43"/>
+      <x:c r="M121" s="43"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="43" t="str">
-        <x:v>R-115</x:v>
-      </x:c>
-      <x:c r="B122" s="43" t="str">
+      <x:c r="A122" s="42" t="str">
+        <x:v>R-114</x:v>
+      </x:c>
+      <x:c r="B122" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C122" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D122" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="E122" s="43" t="str">
-        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
-      </x:c>
-      <x:c r="F122" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G122" s="43"/>
-      <x:c r="H122" s="43" t="str">
+      <x:c r="C122" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D122" s="42" t="str">
+        <x:v>Manual framework override</x:v>
+      </x:c>
+      <x:c r="E122" s="42" t="str">
+        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
+      </x:c>
+      <x:c r="F122" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G122" s="42"/>
+      <x:c r="H122" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I122" s="386" t="n">
+      <x:c r="I122" s="387" t="n">
         <x:f>IF(H122="Done",1,IF(H122="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K122" s="43"/>
-      <x:c r="L122" s="43"/>
-      <x:c r="M122" s="43"/>
+      <x:c r="J122" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K122" s="42"/>
+      <x:c r="L122" s="42"/>
+      <x:c r="M122" s="42"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="42" t="str">
-        <x:v>R-116</x:v>
-      </x:c>
-      <x:c r="B123" s="42" t="str">
+      <x:c r="A123" s="43" t="str">
+        <x:v>R-115</x:v>
+      </x:c>
+      <x:c r="B123" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C123" s="42" t="str">
+      <x:c r="C123" s="43" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D123" s="42" t="str">
-        <x:v>Shared-code policy</x:v>
-      </x:c>
-      <x:c r="E123" s="42" t="str">
-        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
-      </x:c>
-      <x:c r="F123" s="42" t="str">
+      <x:c r="D123" s="43" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="E123" s="43" t="str">
+        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
+      </x:c>
+      <x:c r="F123" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G123" s="42"/>
-      <x:c r="H123" s="42" t="str">
+      <x:c r="G123" s="43"/>
+      <x:c r="H123" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I123" s="387" t="n">
+      <x:c r="I123" s="386" t="n">
         <x:f>IF(H123="Done",1,IF(H123="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J123" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K123" s="42"/>
-      <x:c r="L123" s="42"/>
-      <x:c r="M123" s="42"/>
+      <x:c r="J123" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K123" s="43"/>
+      <x:c r="L123" s="43"/>
+      <x:c r="M123" s="43"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="43" t="str">
-        <x:v>R-117</x:v>
-      </x:c>
-      <x:c r="B124" s="43" t="str">
+      <x:c r="A124" s="42" t="str">
+        <x:v>R-116</x:v>
+      </x:c>
+      <x:c r="B124" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C124" s="43" t="str">
-        <x:v>Web/Admin</x:v>
-      </x:c>
-      <x:c r="D124" s="43" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="E124" s="43" t="str">
-        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
-      </x:c>
-      <x:c r="F124" s="43" t="str">
+      <x:c r="C124" s="42" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D124" s="42" t="str">
+        <x:v>Shared-code policy</x:v>
+      </x:c>
+      <x:c r="E124" s="42" t="str">
+        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
+      </x:c>
+      <x:c r="F124" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G124" s="43"/>
-      <x:c r="H124" s="43" t="str">
+      <x:c r="G124" s="42"/>
+      <x:c r="H124" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I124" s="386" t="n">
+      <x:c r="I124" s="387" t="n">
         <x:f>IF(H124="Done",1,IF(H124="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="43" t="str">
-        <x:v>Web/Admin Agent</x:v>
-      </x:c>
-      <x:c r="K124" s="43"/>
-      <x:c r="L124" s="43"/>
-      <x:c r="M124" s="43"/>
+      <x:c r="J124" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K124" s="42"/>
+      <x:c r="L124" s="42"/>
+      <x:c r="M124" s="42"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="42" t="str">
-        <x:v>R-118</x:v>
-      </x:c>
-      <x:c r="B125" s="42" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C125" s="42" t="str">
+      <x:c r="A125" s="43" t="str">
+        <x:v>R-117</x:v>
+      </x:c>
+      <x:c r="B125" s="43" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C125" s="43" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D125" s="42" t="str">
-        <x:v>Flutter Web optional profile</x:v>
-      </x:c>
-      <x:c r="E125" s="42" t="str">
-        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
-      </x:c>
-      <x:c r="F125" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G125" s="42"/>
-      <x:c r="H125" s="42" t="str">
+      <x:c r="D125" s="43" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="E125" s="43" t="str">
+        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
+      </x:c>
+      <x:c r="F125" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G125" s="43"/>
+      <x:c r="H125" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I125" s="387" t="n">
+      <x:c r="I125" s="386" t="n">
         <x:f>IF(H125="Done",1,IF(H125="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J125" s="42" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
-      </x:c>
-      <x:c r="K125" s="42"/>
-      <x:c r="L125" s="42"/>
-      <x:c r="M125" s="42"/>
+      <x:c r="J125" s="43" t="str">
+        <x:v>Web/Admin Agent</x:v>
+      </x:c>
+      <x:c r="K125" s="43"/>
+      <x:c r="L125" s="43"/>
+      <x:c r="M125" s="43"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="43" t="str">
-        <x:v>R-119</x:v>
-      </x:c>
-      <x:c r="B126" s="43" t="str">
+      <x:c r="A126" s="42" t="str">
+        <x:v>R-118</x:v>
+      </x:c>
+      <x:c r="B126" s="42" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C126" s="43" t="str">
+      <x:c r="C126" s="42" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D126" s="43" t="str">
-        <x:v>React Native Web optional profile</x:v>
-      </x:c>
-      <x:c r="E126" s="43" t="str">
-        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
-      </x:c>
-      <x:c r="F126" s="43" t="str">
+      <x:c r="D126" s="42" t="str">
+        <x:v>Flutter Web optional profile</x:v>
+      </x:c>
+      <x:c r="E126" s="42" t="str">
+        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
+      </x:c>
+      <x:c r="F126" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G126" s="43"/>
-      <x:c r="H126" s="43" t="str">
+      <x:c r="G126" s="42"/>
+      <x:c r="H126" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I126" s="386" t="n">
+      <x:c r="I126" s="387" t="n">
         <x:f>IF(H126="Done",1,IF(H126="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="43" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
-      </x:c>
-      <x:c r="K126" s="43"/>
-      <x:c r="L126" s="43"/>
-      <x:c r="M126" s="43"/>
+      <x:c r="J126" s="42" t="str">
+        <x:v>Flutter target (GA baseline)</x:v>
+      </x:c>
+      <x:c r="K126" s="42"/>
+      <x:c r="L126" s="42"/>
+      <x:c r="M126" s="42"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="42" t="str">
-        <x:v>R-120</x:v>
-      </x:c>
-      <x:c r="B127" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C127" s="42" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D127" s="42" t="str">
-        <x:v>Native recommendation profile</x:v>
-      </x:c>
-      <x:c r="E127" s="42" t="str">
-        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
-      </x:c>
-      <x:c r="F127" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G127" s="42"/>
-      <x:c r="H127" s="42" t="str">
+      <x:c r="A127" s="43" t="str">
+        <x:v>R-119</x:v>
+      </x:c>
+      <x:c r="B127" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C127" s="43" t="str">
+        <x:v>Web/Admin</x:v>
+      </x:c>
+      <x:c r="D127" s="43" t="str">
+        <x:v>React Native Web optional profile</x:v>
+      </x:c>
+      <x:c r="E127" s="43" t="str">
+        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
+      </x:c>
+      <x:c r="F127" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G127" s="43"/>
+      <x:c r="H127" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I127" s="387" t="n">
+      <x:c r="I127" s="386" t="n">
         <x:f>IF(H127="Done",1,IF(H127="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J127" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K127" s="42"/>
-      <x:c r="L127" s="42"/>
-      <x:c r="M127" s="42"/>
+      <x:c r="J127" s="43" t="str">
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
+      </x:c>
+      <x:c r="K127" s="43"/>
+      <x:c r="L127" s="43"/>
+      <x:c r="M127" s="43"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="43" t="str">
-        <x:v>R-121</x:v>
-      </x:c>
-      <x:c r="B128" s="43" t="str">
+      <x:c r="A128" s="42" t="str">
+        <x:v>R-120</x:v>
+      </x:c>
+      <x:c r="B128" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C128" s="43" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D128" s="43" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="E128" s="43" t="str">
-        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
-      </x:c>
-      <x:c r="F128" s="43" t="str">
+      <x:c r="C128" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D128" s="42" t="str">
+        <x:v>Native recommendation profile</x:v>
+      </x:c>
+      <x:c r="E128" s="42" t="str">
+        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
+      </x:c>
+      <x:c r="F128" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G128" s="43"/>
-      <x:c r="H128" s="43" t="str">
+      <x:c r="G128" s="42"/>
+      <x:c r="H128" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I128" s="386" t="n">
+      <x:c r="I128" s="387" t="n">
         <x:f>IF(H128="Done",1,IF(H128="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="43" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K128" s="43"/>
-      <x:c r="L128" s="43"/>
-      <x:c r="M128" s="43"/>
+      <x:c r="J128" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K128" s="42"/>
+      <x:c r="L128" s="42"/>
+      <x:c r="M128" s="42"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="42" t="str">
-        <x:v>R-122</x:v>
-      </x:c>
-      <x:c r="B129" s="42" t="str">
+      <x:c r="A129" s="43" t="str">
+        <x:v>R-121</x:v>
+      </x:c>
+      <x:c r="B129" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C129" s="42" t="str">
+      <x:c r="C129" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D129" s="42" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="E129" s="42" t="str">
-        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
-      </x:c>
-      <x:c r="F129" s="42" t="str">
+      <x:c r="D129" s="43" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="E129" s="43" t="str">
+        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
+      </x:c>
+      <x:c r="F129" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G129" s="42"/>
-      <x:c r="H129" s="42" t="str">
+      <x:c r="G129" s="43"/>
+      <x:c r="H129" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I129" s="387" t="n">
+      <x:c r="I129" s="386" t="n">
         <x:f>IF(H129="Done",1,IF(H129="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J129" s="42" t="str">
+      <x:c r="J129" s="43" t="str">
         <x:v>Project + workspace model</x:v>
       </x:c>
-      <x:c r="K129" s="42"/>
-      <x:c r="L129" s="42"/>
-      <x:c r="M129" s="42"/>
+      <x:c r="K129" s="43"/>
+      <x:c r="L129" s="43"/>
+      <x:c r="M129" s="43"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="43" t="str">
-        <x:v>R-123</x:v>
-      </x:c>
-      <x:c r="B130" s="43" t="str">
+      <x:c r="A130" s="42" t="str">
+        <x:v>R-122</x:v>
+      </x:c>
+      <x:c r="B130" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C130" s="43" t="str">
+      <x:c r="C130" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D130" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="E130" s="43" t="str">
-        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
-      </x:c>
-      <x:c r="F130" s="43" t="str">
+      <x:c r="D130" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="E130" s="42" t="str">
+        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
+      </x:c>
+      <x:c r="F130" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G130" s="43"/>
-      <x:c r="H130" s="43" t="str">
+      <x:c r="G130" s="42"/>
+      <x:c r="H130" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I130" s="386" t="n">
+      <x:c r="I130" s="387" t="n">
         <x:f>IF(H130="Done",1,IF(H130="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J130" s="43" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="K130" s="43"/>
-      <x:c r="L130" s="43"/>
-      <x:c r="M130" s="43"/>
+      <x:c r="J130" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K130" s="42"/>
+      <x:c r="L130" s="42"/>
+      <x:c r="M130" s="42"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="42" t="str">
-        <x:v>R-124</x:v>
-      </x:c>
-      <x:c r="B131" s="42" t="str">
+      <x:c r="A131" s="43" t="str">
+        <x:v>R-123</x:v>
+      </x:c>
+      <x:c r="B131" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C131" s="42" t="str">
+      <x:c r="C131" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D131" s="42" t="str">
-        <x:v>Repository naming convention</x:v>
-      </x:c>
-      <x:c r="E131" s="42" t="str">
-        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
-      </x:c>
-      <x:c r="F131" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G131" s="42"/>
-      <x:c r="H131" s="42" t="str">
+      <x:c r="D131" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="E131" s="43" t="str">
+        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
+      </x:c>
+      <x:c r="F131" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G131" s="43"/>
+      <x:c r="H131" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I131" s="387" t="n">
+      <x:c r="I131" s="386" t="n">
         <x:f>IF(H131="Done",1,IF(H131="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J131" s="42" t="str">
+      <x:c r="J131" s="43" t="str">
         <x:v>One Git repo per customer project</x:v>
       </x:c>
-      <x:c r="K131" s="42"/>
-      <x:c r="L131" s="42"/>
-      <x:c r="M131" s="42"/>
+      <x:c r="K131" s="43"/>
+      <x:c r="L131" s="43"/>
+      <x:c r="M131" s="43"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="43" t="str">
-        <x:v>R-125</x:v>
-      </x:c>
-      <x:c r="B132" s="43" t="str">
+      <x:c r="A132" s="42" t="str">
+        <x:v>R-124</x:v>
+      </x:c>
+      <x:c r="B132" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C132" s="43" t="str">
+      <x:c r="C132" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D132" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="E132" s="43" t="str">
-        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
-      </x:c>
-      <x:c r="F132" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G132" s="43"/>
-      <x:c r="H132" s="43" t="str">
+      <x:c r="D132" s="42" t="str">
+        <x:v>Repository naming convention</x:v>
+      </x:c>
+      <x:c r="E132" s="42" t="str">
+        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
+      </x:c>
+      <x:c r="F132" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G132" s="42"/>
+      <x:c r="H132" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I132" s="386" t="n">
+      <x:c r="I132" s="387" t="n">
         <x:f>IF(H132="Done",1,IF(H132="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J132" s="43" t="str">
-        <x:v>Branch per task</x:v>
-      </x:c>
-      <x:c r="K132" s="43"/>
-      <x:c r="L132" s="43"/>
-      <x:c r="M132" s="43"/>
+      <x:c r="J132" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="K132" s="42"/>
+      <x:c r="L132" s="42"/>
+      <x:c r="M132" s="42"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="42" t="str">
-        <x:v>R-126</x:v>
-      </x:c>
-      <x:c r="B133" s="42" t="str">
+      <x:c r="A133" s="43" t="str">
+        <x:v>R-125</x:v>
+      </x:c>
+      <x:c r="B133" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C133" s="42" t="str">
-        <x:v>Product Foundation</x:v>
-      </x:c>
-      <x:c r="D133" s="42" t="str">
-        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
-      </x:c>
-      <x:c r="E133" s="42" t="str">
-        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
-      </x:c>
-      <x:c r="F133" s="42" t="str">
+      <x:c r="C133" s="43" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D133" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="E133" s="43" t="str">
+        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
+      </x:c>
+      <x:c r="F133" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G133" s="42"/>
-      <x:c r="H133" s="42" t="str">
+      <x:c r="G133" s="43"/>
+      <x:c r="H133" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I133" s="387" t="n">
+      <x:c r="I133" s="386" t="n">
         <x:f>IF(H133="Done",1,IF(H133="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J133" s="42" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K133" s="42"/>
-      <x:c r="L133" s="42"/>
-      <x:c r="M133" s="42"/>
+      <x:c r="J133" s="43" t="str">
+        <x:v>Branch per task</x:v>
+      </x:c>
+      <x:c r="K133" s="43"/>
+      <x:c r="L133" s="43"/>
+      <x:c r="M133" s="43"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="43" t="str">
-        <x:v>R-127</x:v>
-      </x:c>
-      <x:c r="B134" s="43" t="str">
+      <x:c r="A134" s="42" t="str">
+        <x:v>R-126</x:v>
+      </x:c>
+      <x:c r="B134" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C134" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D134" s="43" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="E134" s="43" t="str">
-        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
-      </x:c>
-      <x:c r="F134" s="43" t="str">
+      <x:c r="C134" s="42" t="str">
+        <x:v>Product Foundation</x:v>
+      </x:c>
+      <x:c r="D134" s="42" t="str">
+        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
+      </x:c>
+      <x:c r="E134" s="42" t="str">
+        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
+      </x:c>
+      <x:c r="F134" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G134" s="43"/>
-      <x:c r="H134" s="43" t="str">
+      <x:c r="G134" s="42"/>
+      <x:c r="H134" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I134" s="386" t="n">
+      <x:c r="I134" s="387" t="n">
         <x:f>IF(H134="Done",1,IF(H134="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J134" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K134" s="43"/>
-      <x:c r="L134" s="43"/>
-      <x:c r="M134" s="43"/>
+      <x:c r="J134" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K134" s="42"/>
+      <x:c r="L134" s="42"/>
+      <x:c r="M134" s="42"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="42" t="str">
-        <x:v>R-128</x:v>
-      </x:c>
-      <x:c r="B135" s="42" t="str">
+      <x:c r="A135" s="43" t="str">
+        <x:v>R-127</x:v>
+      </x:c>
+      <x:c r="B135" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C135" s="42" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D135" s="42" t="str">
-        <x:v>Cross-language monorepo orchestration</x:v>
-      </x:c>
-      <x:c r="E135" s="42" t="str">
-        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
-      </x:c>
-      <x:c r="F135" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G135" s="42"/>
-      <x:c r="H135" s="42" t="str">
+      <x:c r="C135" s="43" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D135" s="43" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="E135" s="43" t="str">
+        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
+      </x:c>
+      <x:c r="F135" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G135" s="43"/>
+      <x:c r="H135" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I135" s="387" t="n">
+      <x:c r="I135" s="386" t="n">
         <x:f>IF(H135="Done",1,IF(H135="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J135" s="42" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K135" s="42"/>
-      <x:c r="L135" s="42"/>
-      <x:c r="M135" s="42"/>
+      <x:c r="J135" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K135" s="43"/>
+      <x:c r="L135" s="43"/>
+      <x:c r="M135" s="43"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="43" t="str">
-        <x:v>R-129</x:v>
-      </x:c>
-      <x:c r="B136" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C136" s="43" t="str">
+      <x:c r="A136" s="42" t="str">
+        <x:v>R-128</x:v>
+      </x:c>
+      <x:c r="B136" s="42" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C136" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D136" s="43" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="E136" s="43" t="str">
-        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
-      </x:c>
-      <x:c r="F136" s="43" t="str">
+      <x:c r="D136" s="42" t="str">
+        <x:v>Cross-language monorepo orchestration</x:v>
+      </x:c>
+      <x:c r="E136" s="42" t="str">
+        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
+      </x:c>
+      <x:c r="F136" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G136" s="43"/>
-      <x:c r="H136" s="43" t="str">
+      <x:c r="G136" s="42"/>
+      <x:c r="H136" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I136" s="386" t="n">
+      <x:c r="I136" s="387" t="n">
         <x:f>IF(H136="Done",1,IF(H136="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J136" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K136" s="43"/>
-      <x:c r="L136" s="43"/>
-      <x:c r="M136" s="43"/>
+      <x:c r="J136" s="42" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K136" s="42"/>
+      <x:c r="L136" s="42"/>
+      <x:c r="M136" s="42"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="42" t="str">
-        <x:v>R-130</x:v>
-      </x:c>
-      <x:c r="B137" s="42" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C137" s="42" t="str">
+      <x:c r="A137" s="43" t="str">
+        <x:v>R-129</x:v>
+      </x:c>
+      <x:c r="B137" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C137" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D137" s="42" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="E137" s="42" t="str">
-        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
-      </x:c>
-      <x:c r="F137" s="42" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G137" s="42"/>
-      <x:c r="H137" s="42" t="str">
+      <x:c r="D137" s="43" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="E137" s="43" t="str">
+        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
+      </x:c>
+      <x:c r="F137" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G137" s="43"/>
+      <x:c r="H137" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I137" s="387" t="n">
+      <x:c r="I137" s="386" t="n">
         <x:f>IF(H137="Done",1,IF(H137="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J137" s="42" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="K137" s="42"/>
-      <x:c r="L137" s="42"/>
-      <x:c r="M137" s="42"/>
+      <x:c r="J137" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K137" s="43"/>
+      <x:c r="L137" s="43"/>
+      <x:c r="M137" s="43"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="43" t="str">
-        <x:v>R-131</x:v>
-      </x:c>
-      <x:c r="B138" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C138" s="43" t="str">
+      <x:c r="A138" s="42" t="str">
+        <x:v>R-130</x:v>
+      </x:c>
+      <x:c r="B138" s="42" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C138" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D138" s="43" t="str">
-        <x:v>CODEOWNERS + protected paths</x:v>
-      </x:c>
-      <x:c r="E138" s="43" t="str">
-        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
-      </x:c>
-      <x:c r="F138" s="43" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G138" s="43"/>
-      <x:c r="H138" s="43" t="str">
+      <x:c r="D138" s="42" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="E138" s="42" t="str">
+        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
+      </x:c>
+      <x:c r="F138" s="42" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G138" s="42"/>
+      <x:c r="H138" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I138" s="386" t="n">
+      <x:c r="I138" s="387" t="n">
         <x:f>IF(H138="Done",1,IF(H138="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J138" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="K138" s="43"/>
-      <x:c r="L138" s="43"/>
-      <x:c r="M138" s="43"/>
+      <x:c r="J138" s="42" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="K138" s="42"/>
+      <x:c r="L138" s="42"/>
+      <x:c r="M138" s="42"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="42" t="str">
-        <x:v>R-132</x:v>
-      </x:c>
-      <x:c r="B139" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C139" s="42" t="str">
+      <x:c r="A139" s="43" t="str">
+        <x:v>R-131</x:v>
+      </x:c>
+      <x:c r="B139" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C139" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D139" s="42" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="E139" s="42" t="str">
-        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
-      </x:c>
-      <x:c r="F139" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G139" s="42"/>
-      <x:c r="H139" s="42" t="str">
+      <x:c r="D139" s="43" t="str">
+        <x:v>CODEOWNERS + protected paths</x:v>
+      </x:c>
+      <x:c r="E139" s="43" t="str">
+        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
+      </x:c>
+      <x:c r="F139" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G139" s="43"/>
+      <x:c r="H139" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I139" s="387" t="n">
+      <x:c r="I139" s="386" t="n">
         <x:f>IF(H139="Done",1,IF(H139="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J139" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K139" s="42"/>
-      <x:c r="L139" s="42"/>
-      <x:c r="M139" s="42"/>
+      <x:c r="J139" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="K139" s="43"/>
+      <x:c r="L139" s="43"/>
+      <x:c r="M139" s="43"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="66" t="str">
-        <x:v>R-133</x:v>
-      </x:c>
-      <x:c r="B140" s="66" t="str">
+      <x:c r="A140" s="42" t="str">
+        <x:v>R-132</x:v>
+      </x:c>
+      <x:c r="B140" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C140" s="66" t="str">
-        <x:v>Change Safety</x:v>
-      </x:c>
-      <x:c r="D140" s="66" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="E140" s="66" t="str">
-        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
-      </x:c>
-      <x:c r="F140" s="66" t="str">
+      <x:c r="C140" s="42" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D140" s="42" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="E140" s="42" t="str">
+        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
+      </x:c>
+      <x:c r="F140" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G140" s="66"/>
-      <x:c r="H140" s="66" t="str">
+      <x:c r="G140" s="42"/>
+      <x:c r="H140" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I140" s="388" t="n">
+      <x:c r="I140" s="387" t="n">
         <x:f>IF(H140="Done",1,IF(H140="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J140" s="66" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K140" s="66"/>
-      <x:c r="L140" s="66"/>
-      <x:c r="M140" s="66"/>
+      <x:c r="J140" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K140" s="42"/>
+      <x:c r="L140" s="42"/>
+      <x:c r="M140" s="42"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="65" t="str">
-        <x:v>R-134</x:v>
-      </x:c>
-      <x:c r="B141" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C141" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D141" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="E141" s="65" t="str">
-        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
-      </x:c>
-      <x:c r="F141" s="65" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G141" s="65"/>
-      <x:c r="H141" s="65" t="str">
+      <x:c r="A141" s="66" t="str">
+        <x:v>R-133</x:v>
+      </x:c>
+      <x:c r="B141" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C141" s="66" t="str">
+        <x:v>Change Safety</x:v>
+      </x:c>
+      <x:c r="D141" s="66" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="E141" s="66" t="str">
+        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
+      </x:c>
+      <x:c r="F141" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G141" s="66"/>
+      <x:c r="H141" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I141" s="389" t="n">
+      <x:c r="I141" s="388" t="n">
         <x:f>IF(H141="Done",1,IF(H141="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J141" s="65" t="str">
-        <x:v>Build artifact caching</x:v>
-      </x:c>
-      <x:c r="K141" s="65"/>
-      <x:c r="L141" s="65"/>
-      <x:c r="M141" s="65"/>
+      <x:c r="J141" s="66" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K141" s="66"/>
+      <x:c r="L141" s="66"/>
+      <x:c r="M141" s="66"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="66" t="str">
-        <x:v>R-135</x:v>
-      </x:c>
-      <x:c r="B142" s="66" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C142" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D142" s="66" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="E142" s="66" t="str">
-        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
-      </x:c>
-      <x:c r="F142" s="66" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G142" s="66"/>
-      <x:c r="H142" s="66" t="str">
+      <x:c r="A142" s="65" t="str">
+        <x:v>R-134</x:v>
+      </x:c>
+      <x:c r="B142" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C142" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D142" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="E142" s="65" t="str">
+        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
+      </x:c>
+      <x:c r="F142" s="65" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G142" s="65"/>
+      <x:c r="H142" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I142" s="388" t="n">
+      <x:c r="I142" s="389" t="n">
         <x:f>IF(H142="Done",1,IF(H142="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J142" s="66" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K142" s="66"/>
-      <x:c r="L142" s="66"/>
-      <x:c r="M142" s="66" t="str">
-        <x:v>V3</x:v>
-      </x:c>
+      <x:c r="J142" s="65" t="str">
+        <x:v>Build artifact caching</x:v>
+      </x:c>
+      <x:c r="K142" s="65"/>
+      <x:c r="L142" s="65"/>
+      <x:c r="M142" s="65"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="65" t="str">
-        <x:v>R-136</x:v>
-      </x:c>
-      <x:c r="B143" s="65" t="str">
+      <x:c r="A143" s="66" t="str">
+        <x:v>R-135</x:v>
+      </x:c>
+      <x:c r="B143" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C143" s="65" t="str">
+      <x:c r="C143" s="66" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D143" s="65" t="str">
-        <x:v>Recommendation score model</x:v>
-      </x:c>
-      <x:c r="E143" s="65" t="str">
-        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
-      </x:c>
-      <x:c r="F143" s="65" t="str">
+      <x:c r="D143" s="66" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="E143" s="66" t="str">
+        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
+      </x:c>
+      <x:c r="F143" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G143" s="65"/>
-      <x:c r="H143" s="65" t="str">
+      <x:c r="G143" s="66"/>
+      <x:c r="H143" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I143" s="389" t="n">
+      <x:c r="I143" s="388" t="n">
         <x:f>IF(H143="Done",1,IF(H143="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J143" s="65" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="K143" s="65"/>
-      <x:c r="L143" s="65"/>
-      <x:c r="M143" s="65" t="str">
-        <x:v>Do not choose by industry label alone.</x:v>
+      <x:c r="J143" s="66" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K143" s="66"/>
+      <x:c r="L143" s="66"/>
+      <x:c r="M143" s="66" t="str">
+        <x:v>V3</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="66" t="str">
-        <x:v>R-137</x:v>
-      </x:c>
-      <x:c r="B144" s="66" t="str">
+      <x:c r="A144" s="65" t="str">
+        <x:v>R-136</x:v>
+      </x:c>
+      <x:c r="B144" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C144" s="66" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D144" s="66" t="str">
-        <x:v>Code sharing policy</x:v>
-      </x:c>
-      <x:c r="E144" s="66" t="str">
-        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
-      </x:c>
-      <x:c r="F144" s="66" t="str">
+      <x:c r="C144" s="65" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D144" s="65" t="str">
+        <x:v>Recommendation score model</x:v>
+      </x:c>
+      <x:c r="E144" s="65" t="str">
+        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
+      </x:c>
+      <x:c r="F144" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G144" s="66"/>
-      <x:c r="H144" s="66" t="str">
+      <x:c r="G144" s="65"/>
+      <x:c r="H144" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I144" s="388" t="n">
+      <x:c r="I144" s="389" t="n">
         <x:f>IF(H144="Done",1,IF(H144="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J144" s="66" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K144" s="66"/>
-      <x:c r="L144" s="66"/>
-      <x:c r="M144" s="66" t="str">
-        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
+      <x:c r="J144" s="65" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="K144" s="65"/>
+      <x:c r="L144" s="65"/>
+      <x:c r="M144" s="65" t="str">
+        <x:v>Do not choose by industry label alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="65" t="str">
-        <x:v>R-138</x:v>
-      </x:c>
-      <x:c r="B145" s="65" t="str">
+      <x:c r="A145" s="66" t="str">
+        <x:v>R-137</x:v>
+      </x:c>
+      <x:c r="B145" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C145" s="65" t="str">
+      <x:c r="C145" s="66" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D145" s="65" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="E145" s="65" t="str">
-        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
-      </x:c>
-      <x:c r="F145" s="65" t="str">
+      <x:c r="D145" s="66" t="str">
+        <x:v>Code sharing policy</x:v>
+      </x:c>
+      <x:c r="E145" s="66" t="str">
+        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
+      </x:c>
+      <x:c r="F145" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G145" s="65"/>
-      <x:c r="H145" s="65" t="str">
+      <x:c r="G145" s="66"/>
+      <x:c r="H145" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I145" s="389" t="n">
+      <x:c r="I145" s="388" t="n">
         <x:f>IF(H145="Done",1,IF(H145="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="65" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K145" s="65"/>
-      <x:c r="L145" s="65"/>
-      <x:c r="M145" s="65" t="str">
-        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
+      <x:c r="J145" s="66" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K145" s="66"/>
+      <x:c r="L145" s="66"/>
+      <x:c r="M145" s="66" t="str">
+        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="66" t="str">
-        <x:v>R-139</x:v>
-      </x:c>
-      <x:c r="B146" s="66" t="str">
+      <x:c r="A146" s="65" t="str">
+        <x:v>R-138</x:v>
+      </x:c>
+      <x:c r="B146" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C146" s="66" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D146" s="66" t="str">
-        <x:v>Root task commands</x:v>
-      </x:c>
-      <x:c r="E146" s="66" t="str">
-        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
-      </x:c>
-      <x:c r="F146" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G146" s="66"/>
-      <x:c r="H146" s="66" t="str">
+      <x:c r="C146" s="65" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D146" s="65" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="E146" s="65" t="str">
+        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
+      </x:c>
+      <x:c r="F146" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G146" s="65"/>
+      <x:c r="H146" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I146" s="388" t="n">
+      <x:c r="I146" s="389" t="n">
         <x:f>IF(H146="Done",1,IF(H146="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="66" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="K146" s="66"/>
-      <x:c r="L146" s="66"/>
-      <x:c r="M146" s="66" t="str">
-        <x:v>Framework-independent agent commands.</x:v>
+      <x:c r="J146" s="65" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K146" s="65"/>
+      <x:c r="L146" s="65"/>
+      <x:c r="M146" s="65" t="str">
+        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="65" t="str">
-        <x:v>R-140</x:v>
-      </x:c>
-      <x:c r="B147" s="65" t="str">
+      <x:c r="A147" s="66" t="str">
+        <x:v>R-139</x:v>
+      </x:c>
+      <x:c r="B147" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C147" s="65" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D147" s="65" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="E147" s="65" t="str">
-        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
-      </x:c>
-      <x:c r="F147" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G147" s="65"/>
-      <x:c r="H147" s="65" t="str">
+      <x:c r="C147" s="66" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D147" s="66" t="str">
+        <x:v>Root task commands</x:v>
+      </x:c>
+      <x:c r="E147" s="66" t="str">
+        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
+      </x:c>
+      <x:c r="F147" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G147" s="66"/>
+      <x:c r="H147" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I147" s="389" t="n">
+      <x:c r="I147" s="388" t="n">
         <x:f>IF(H147="Done",1,IF(H147="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K147" s="65"/>
-      <x:c r="L147" s="65"/>
-      <x:c r="M147" s="65" t="str">
-        <x:v>Stable target.</x:v>
+      <x:c r="J147" s="66" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="K147" s="66"/>
+      <x:c r="L147" s="66"/>
+      <x:c r="M147" s="66" t="str">
+        <x:v>Framework-independent agent commands.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="66" t="str">
-        <x:v>R-141</x:v>
-      </x:c>
-      <x:c r="B148" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C148" s="66" t="str">
+      <x:c r="A148" s="65" t="str">
+        <x:v>R-140</x:v>
+      </x:c>
+      <x:c r="B148" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C148" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D148" s="66" t="str">
-        <x:v>Flutter scaled template</x:v>
-      </x:c>
-      <x:c r="E148" s="66" t="str">
-        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
-      </x:c>
-      <x:c r="F148" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G148" s="66"/>
-      <x:c r="H148" s="66" t="str">
+      <x:c r="D148" s="65" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="E148" s="65" t="str">
+        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
+      </x:c>
+      <x:c r="F148" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G148" s="65"/>
+      <x:c r="H148" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I148" s="388" t="n">
+      <x:c r="I148" s="389" t="n">
         <x:f>IF(H148="Done",1,IF(H148="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J148" s="66" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="K148" s="66"/>
-      <x:c r="L148" s="66"/>
-      <x:c r="M148" s="66" t="str">
-        <x:v>Use only when complexity warrants.</x:v>
+      <x:c r="J148" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K148" s="65"/>
+      <x:c r="L148" s="65"/>
+      <x:c r="M148" s="65" t="str">
+        <x:v>Stable target.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="65" t="str">
-        <x:v>R-142</x:v>
-      </x:c>
-      <x:c r="B149" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C149" s="65" t="str">
+      <x:c r="A149" s="66" t="str">
+        <x:v>R-141</x:v>
+      </x:c>
+      <x:c r="B149" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C149" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D149" s="65" t="str">
-        <x:v>React Native TypeScript template</x:v>
-      </x:c>
-      <x:c r="E149" s="65" t="str">
-        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
-      </x:c>
-      <x:c r="F149" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G149" s="65"/>
-      <x:c r="H149" s="65" t="str">
+      <x:c r="D149" s="66" t="str">
+        <x:v>Flutter scaled template</x:v>
+      </x:c>
+      <x:c r="E149" s="66" t="str">
+        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
+      </x:c>
+      <x:c r="F149" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G149" s="66"/>
+      <x:c r="H149" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I149" s="389" t="n">
+      <x:c r="I149" s="388" t="n">
         <x:f>IF(H149="Done",1,IF(H149="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J149" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K149" s="65"/>
-      <x:c r="L149" s="65"/>
-      <x:c r="M149" s="65" t="str">
-        <x:v>Expo profile when capabilities fit.</x:v>
+      <x:c r="J149" s="66" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="K149" s="66"/>
+      <x:c r="L149" s="66"/>
+      <x:c r="M149" s="66" t="str">
+        <x:v>Use only when complexity warrants.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="66" t="str">
-        <x:v>R-143</x:v>
-      </x:c>
-      <x:c r="B150" s="66" t="str">
+      <x:c r="A150" s="65" t="str">
+        <x:v>R-142</x:v>
+      </x:c>
+      <x:c r="B150" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C150" s="66" t="str">
+      <x:c r="C150" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D150" s="66" t="str">
-        <x:v>React Native shared TS packages</x:v>
-      </x:c>
-      <x:c r="E150" s="66" t="str">
-        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
-      </x:c>
-      <x:c r="F150" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G150" s="66"/>
-      <x:c r="H150" s="66" t="str">
+      <x:c r="D150" s="65" t="str">
+        <x:v>React Native TypeScript template</x:v>
+      </x:c>
+      <x:c r="E150" s="65" t="str">
+        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
+      </x:c>
+      <x:c r="F150" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G150" s="65"/>
+      <x:c r="H150" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I150" s="388" t="n">
+      <x:c r="I150" s="389" t="n">
         <x:f>IF(H150="Done",1,IF(H150="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="66" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K150" s="66"/>
-      <x:c r="L150" s="66"/>
-      <x:c r="M150" s="66" t="str">
-        <x:v>Do not share UI blindly.</x:v>
+      <x:c r="J150" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K150" s="65"/>
+      <x:c r="L150" s="65"/>
+      <x:c r="M150" s="65" t="str">
+        <x:v>Expo profile when capabilities fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="65" t="str">
-        <x:v>R-144</x:v>
-      </x:c>
-      <x:c r="B151" s="65" t="str">
+      <x:c r="A151" s="66" t="str">
+        <x:v>R-143</x:v>
+      </x:c>
+      <x:c r="B151" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C151" s="65" t="str">
+      <x:c r="C151" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D151" s="65" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="E151" s="65" t="str">
-        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
-      </x:c>
-      <x:c r="F151" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G151" s="65"/>
-      <x:c r="H151" s="65" t="str">
+      <x:c r="D151" s="66" t="str">
+        <x:v>React Native shared TS packages</x:v>
+      </x:c>
+      <x:c r="E151" s="66" t="str">
+        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
+      </x:c>
+      <x:c r="F151" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G151" s="66"/>
+      <x:c r="H151" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I151" s="389" t="n">
+      <x:c r="I151" s="388" t="n">
         <x:f>IF(H151="Done",1,IF(H151="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J151" s="65" t="str">
-        <x:v>Native Android Agent</x:v>
-      </x:c>
-      <x:c r="K151" s="65"/>
-      <x:c r="L151" s="65"/>
-      <x:c r="M151" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J151" s="66" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K151" s="66"/>
+      <x:c r="L151" s="66"/>
+      <x:c r="M151" s="66" t="str">
+        <x:v>Do not share UI blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="66" t="str">
-        <x:v>R-145</x:v>
-      </x:c>
-      <x:c r="B152" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C152" s="66" t="str">
+      <x:c r="A152" s="65" t="str">
+        <x:v>R-144</x:v>
+      </x:c>
+      <x:c r="B152" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C152" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D152" s="66" t="str">
-        <x:v>Native Android scaled modules</x:v>
-      </x:c>
-      <x:c r="E152" s="66" t="str">
-        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
-      </x:c>
-      <x:c r="F152" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G152" s="66"/>
-      <x:c r="H152" s="66" t="str">
+      <x:c r="D152" s="65" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="E152" s="65" t="str">
+        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
+      </x:c>
+      <x:c r="F152" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G152" s="65"/>
+      <x:c r="H152" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I152" s="388" t="n">
+      <x:c r="I152" s="389" t="n">
         <x:f>IF(H152="Done",1,IF(H152="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J152" s="66" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="K152" s="66"/>
-      <x:c r="L152" s="66"/>
-      <x:c r="M152" s="66" t="str">
-        <x:v>Experienced team structure.</x:v>
+      <x:c r="J152" s="65" t="str">
+        <x:v>Native Android Agent</x:v>
+      </x:c>
+      <x:c r="K152" s="65"/>
+      <x:c r="L152" s="65"/>
+      <x:c r="M152" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="65" t="str">
-        <x:v>R-146</x:v>
-      </x:c>
-      <x:c r="B153" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C153" s="65" t="str">
+      <x:c r="A153" s="66" t="str">
+        <x:v>R-145</x:v>
+      </x:c>
+      <x:c r="B153" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C153" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D153" s="65" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="E153" s="65" t="str">
-        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
-      </x:c>
-      <x:c r="F153" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G153" s="65"/>
-      <x:c r="H153" s="65" t="str">
+      <x:c r="D153" s="66" t="str">
+        <x:v>Native Android scaled modules</x:v>
+      </x:c>
+      <x:c r="E153" s="66" t="str">
+        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
+      </x:c>
+      <x:c r="F153" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G153" s="66"/>
+      <x:c r="H153" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I153" s="389" t="n">
+      <x:c r="I153" s="388" t="n">
         <x:f>IF(H153="Done",1,IF(H153="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J153" s="65" t="str">
-        <x:v>Native iOS Agent</x:v>
-      </x:c>
-      <x:c r="K153" s="65"/>
-      <x:c r="L153" s="65"/>
-      <x:c r="M153" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J153" s="66" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="K153" s="66"/>
+      <x:c r="L153" s="66"/>
+      <x:c r="M153" s="66" t="str">
+        <x:v>Experienced team structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="66" t="str">
-        <x:v>R-147</x:v>
-      </x:c>
-      <x:c r="B154" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C154" s="66" t="str">
+      <x:c r="A154" s="65" t="str">
+        <x:v>R-146</x:v>
+      </x:c>
+      <x:c r="B154" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C154" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D154" s="66" t="str">
-        <x:v>Native iOS scaled Swift Packages</x:v>
-      </x:c>
-      <x:c r="E154" s="66" t="str">
-        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
-      </x:c>
-      <x:c r="F154" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G154" s="66"/>
-      <x:c r="H154" s="66" t="str">
+      <x:c r="D154" s="65" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="E154" s="65" t="str">
+        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
+      </x:c>
+      <x:c r="F154" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G154" s="65"/>
+      <x:c r="H154" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I154" s="388" t="n">
+      <x:c r="I154" s="389" t="n">
         <x:f>IF(H154="Done",1,IF(H154="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="66" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="K154" s="66"/>
-      <x:c r="L154" s="66"/>
-      <x:c r="M154" s="66" t="str">
-        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
+      <x:c r="J154" s="65" t="str">
+        <x:v>Native iOS Agent</x:v>
+      </x:c>
+      <x:c r="K154" s="65"/>
+      <x:c r="L154" s="65"/>
+      <x:c r="M154" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="65" t="str">
-        <x:v>R-148</x:v>
-      </x:c>
-      <x:c r="B155" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C155" s="65" t="str">
+      <x:c r="A155" s="66" t="str">
+        <x:v>R-147</x:v>
+      </x:c>
+      <x:c r="B155" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C155" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D155" s="65" t="str">
-        <x:v>Next.js public web template</x:v>
-      </x:c>
-      <x:c r="E155" s="65" t="str">
-        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
-      </x:c>
-      <x:c r="F155" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G155" s="65"/>
-      <x:c r="H155" s="65" t="str">
+      <x:c r="D155" s="66" t="str">
+        <x:v>Native iOS scaled Swift Packages</x:v>
+      </x:c>
+      <x:c r="E155" s="66" t="str">
+        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
+      </x:c>
+      <x:c r="F155" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G155" s="66"/>
+      <x:c r="H155" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I155" s="389" t="n">
+      <x:c r="I155" s="388" t="n">
         <x:f>IF(H155="Done",1,IF(H155="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J155" s="65" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="K155" s="65"/>
-      <x:c r="L155" s="65"/>
-      <x:c r="M155" s="65" t="str">
-        <x:v>Web optimized independently.</x:v>
+      <x:c r="J155" s="66" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="K155" s="66"/>
+      <x:c r="L155" s="66"/>
+      <x:c r="M155" s="66" t="str">
+        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="66" t="str">
-        <x:v>R-149</x:v>
-      </x:c>
-      <x:c r="B156" s="66" t="str">
+      <x:c r="A156" s="65" t="str">
+        <x:v>R-148</x:v>
+      </x:c>
+      <x:c r="B156" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C156" s="66" t="str">
+      <x:c r="C156" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D156" s="66" t="str">
-        <x:v>Next.js admin template</x:v>
-      </x:c>
-      <x:c r="E156" s="66" t="str">
-        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
-      </x:c>
-      <x:c r="F156" s="66" t="str">
+      <x:c r="D156" s="65" t="str">
+        <x:v>Next.js public web template</x:v>
+      </x:c>
+      <x:c r="E156" s="65" t="str">
+        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
+      </x:c>
+      <x:c r="F156" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G156" s="66"/>
-      <x:c r="H156" s="66" t="str">
+      <x:c r="G156" s="65"/>
+      <x:c r="H156" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I156" s="388" t="n">
+      <x:c r="I156" s="389" t="n">
         <x:f>IF(H156="Done",1,IF(H156="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J156" s="66" t="str">
+      <x:c r="J156" s="65" t="str">
         <x:v>Next.js web + admin default</x:v>
       </x:c>
-      <x:c r="K156" s="66"/>
-      <x:c r="L156" s="66"/>
-      <x:c r="M156" s="66" t="str">
-        <x:v>Never force admin onto Flutter/RN Web.</x:v>
+      <x:c r="K156" s="65"/>
+      <x:c r="L156" s="65"/>
+      <x:c r="M156" s="65" t="str">
+        <x:v>Web optimized independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="65" t="str">
-        <x:v>R-150</x:v>
-      </x:c>
-      <x:c r="B157" s="65" t="str">
+      <x:c r="A157" s="66" t="str">
+        <x:v>R-149</x:v>
+      </x:c>
+      <x:c r="B157" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C157" s="65" t="str">
+      <x:c r="C157" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D157" s="65" t="str">
-        <x:v>Go backend standard template</x:v>
-      </x:c>
-      <x:c r="E157" s="65" t="str">
-        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
-      </x:c>
-      <x:c r="F157" s="65" t="str">
+      <x:c r="D157" s="66" t="str">
+        <x:v>Next.js admin template</x:v>
+      </x:c>
+      <x:c r="E157" s="66" t="str">
+        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
+      </x:c>
+      <x:c r="F157" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G157" s="65"/>
-      <x:c r="H157" s="65" t="str">
+      <x:c r="G157" s="66"/>
+      <x:c r="H157" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I157" s="389" t="n">
+      <x:c r="I157" s="388" t="n">
         <x:f>IF(H157="Done",1,IF(H157="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J157" s="65" t="str">
-        <x:v>Backend Agent</x:v>
-      </x:c>
-      <x:c r="K157" s="65"/>
-      <x:c r="L157" s="65"/>
-      <x:c r="M157" s="65" t="str">
-        <x:v>Default backend profile.</x:v>
+      <x:c r="J157" s="66" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="K157" s="66"/>
+      <x:c r="L157" s="66"/>
+      <x:c r="M157" s="66" t="str">
+        <x:v>Never force admin onto Flutter/RN Web.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="66" t="str">
-        <x:v>R-151</x:v>
-      </x:c>
-      <x:c r="B158" s="66" t="str">
+      <x:c r="A158" s="65" t="str">
+        <x:v>R-150</x:v>
+      </x:c>
+      <x:c r="B158" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C158" s="66" t="str">
+      <x:c r="C158" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D158" s="66" t="str">
-        <x:v>Python backend standard template</x:v>
-      </x:c>
-      <x:c r="E158" s="66" t="str">
-        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
-      </x:c>
-      <x:c r="F158" s="66" t="str">
+      <x:c r="D158" s="65" t="str">
+        <x:v>Go backend standard template</x:v>
+      </x:c>
+      <x:c r="E158" s="65" t="str">
+        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
+      </x:c>
+      <x:c r="F158" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G158" s="66"/>
-      <x:c r="H158" s="66" t="str">
+      <x:c r="G158" s="65"/>
+      <x:c r="H158" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I158" s="388" t="n">
+      <x:c r="I158" s="389" t="n">
         <x:f>IF(H158="Done",1,IF(H158="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="66" t="str">
+      <x:c r="J158" s="65" t="str">
         <x:v>Backend Agent</x:v>
       </x:c>
-      <x:c r="K158" s="66"/>
-      <x:c r="L158" s="66"/>
-      <x:c r="M158" s="66" t="str">
-        <x:v>Alternative default backend profile.</x:v>
+      <x:c r="K158" s="65"/>
+      <x:c r="L158" s="65"/>
+      <x:c r="M158" s="65" t="str">
+        <x:v>Default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="65" t="str">
-        <x:v>R-152</x:v>
-      </x:c>
-      <x:c r="B159" s="65" t="str">
+      <x:c r="A159" s="66" t="str">
+        <x:v>R-151</x:v>
+      </x:c>
+      <x:c r="B159" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C159" s="65" t="str">
-        <x:v>Contracts</x:v>
-      </x:c>
-      <x:c r="D159" s="65" t="str">
-        <x:v>Generated client matrix</x:v>
-      </x:c>
-      <x:c r="E159" s="65" t="str">
-        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
-      </x:c>
-      <x:c r="F159" s="65" t="str">
+      <x:c r="C159" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D159" s="66" t="str">
+        <x:v>Python backend standard template</x:v>
+      </x:c>
+      <x:c r="E159" s="66" t="str">
+        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
+      </x:c>
+      <x:c r="F159" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G159" s="65"/>
-      <x:c r="H159" s="65" t="str">
+      <x:c r="G159" s="66"/>
+      <x:c r="H159" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I159" s="389" t="n">
+      <x:c r="I159" s="388" t="n">
         <x:f>IF(H159="Done",1,IF(H159="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="65" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K159" s="65"/>
-      <x:c r="L159" s="65"/>
-      <x:c r="M159" s="65" t="str">
-        <x:v>Contract-first consistency.</x:v>
+      <x:c r="J159" s="66" t="str">
+        <x:v>Backend Agent</x:v>
+      </x:c>
+      <x:c r="K159" s="66"/>
+      <x:c r="L159" s="66"/>
+      <x:c r="M159" s="66" t="str">
+        <x:v>Alternative default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="66" t="str">
-        <x:v>R-153</x:v>
-      </x:c>
-      <x:c r="B160" s="66" t="str">
+      <x:c r="A160" s="65" t="str">
+        <x:v>R-152</x:v>
+      </x:c>
+      <x:c r="B160" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C160" s="66" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D160" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="E160" s="66" t="str">
-        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
-      </x:c>
-      <x:c r="F160" s="66" t="str">
+      <x:c r="C160" s="65" t="str">
+        <x:v>Contracts</x:v>
+      </x:c>
+      <x:c r="D160" s="65" t="str">
+        <x:v>Generated client matrix</x:v>
+      </x:c>
+      <x:c r="E160" s="65" t="str">
+        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
+      </x:c>
+      <x:c r="F160" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G160" s="66"/>
-      <x:c r="H160" s="66" t="str">
+      <x:c r="G160" s="65"/>
+      <x:c r="H160" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I160" s="388" t="n">
+      <x:c r="I160" s="389" t="n">
         <x:f>IF(H160="Done",1,IF(H160="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K160" s="66"/>
-      <x:c r="L160" s="66"/>
-      <x:c r="M160" s="66" t="str">
-        <x:v>Stable/Beta/Experimental visible to user.</x:v>
+      <x:c r="J160" s="65" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K160" s="65"/>
+      <x:c r="L160" s="65"/>
+      <x:c r="M160" s="65" t="str">
+        <x:v>Contract-first consistency.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="65" t="str">
-        <x:v>R-154</x:v>
-      </x:c>
-      <x:c r="B161" s="65" t="str">
+      <x:c r="A161" s="66" t="str">
+        <x:v>R-153</x:v>
+      </x:c>
+      <x:c r="B161" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C161" s="65" t="str">
-        <x:v>Dependencies</x:v>
-      </x:c>
-      <x:c r="D161" s="65" t="str">
-        <x:v>Approved dependency catalog</x:v>
-      </x:c>
-      <x:c r="E161" s="65" t="str">
-        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
-      </x:c>
-      <x:c r="F161" s="65" t="str">
+      <x:c r="C161" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D161" s="66" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="E161" s="66" t="str">
+        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
+      </x:c>
+      <x:c r="F161" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G161" s="65"/>
-      <x:c r="H161" s="65" t="str">
+      <x:c r="G161" s="66"/>
+      <x:c r="H161" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I161" s="389" t="n">
+      <x:c r="I161" s="388" t="n">
         <x:f>IF(H161="Done",1,IF(H161="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J161" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K161" s="65"/>
-      <x:c r="L161" s="65"/>
-      <x:c r="M161" s="65" t="str">
-        <x:v>Prevents dependency explosion.</x:v>
+      <x:c r="J161" s="66" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K161" s="66"/>
+      <x:c r="L161" s="66"/>
+      <x:c r="M161" s="66" t="str">
+        <x:v>Stable/Beta/Experimental visible to user.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="66" t="str">
-        <x:v>R-155</x:v>
-      </x:c>
-      <x:c r="B162" s="66" t="str">
+      <x:c r="A162" s="65" t="str">
+        <x:v>R-154</x:v>
+      </x:c>
+      <x:c r="B162" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C162" s="66" t="str">
-        <x:v>Platform Architecture</x:v>
-      </x:c>
-      <x:c r="D162" s="66" t="str">
-        <x:v>Go control plane modular monolith</x:v>
-      </x:c>
-      <x:c r="E162" s="66" t="str">
-        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
-      </x:c>
-      <x:c r="F162" s="66" t="str">
+      <x:c r="C162" s="65" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D162" s="65" t="str">
+        <x:v>Approved dependency catalog</x:v>
+      </x:c>
+      <x:c r="E162" s="65" t="str">
+        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
+      </x:c>
+      <x:c r="F162" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G162" s="66"/>
-      <x:c r="H162" s="66" t="str">
+      <x:c r="G162" s="65"/>
+      <x:c r="H162" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I162" s="388" t="n">
+      <x:c r="I162" s="389" t="n">
         <x:f>IF(H162="Done",1,IF(H162="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J162" s="66" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K162" s="66"/>
-      <x:c r="L162" s="66"/>
-      <x:c r="M162" s="66" t="str">
-        <x:v>Avoid premature microservices.</x:v>
+      <x:c r="J162" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K162" s="65"/>
+      <x:c r="L162" s="65"/>
+      <x:c r="M162" s="65" t="str">
+        <x:v>Prevents dependency explosion.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="65" t="str">
-        <x:v>R-156</x:v>
-      </x:c>
-      <x:c r="B163" s="65" t="str">
+      <x:c r="A163" s="66" t="str">
+        <x:v>R-155</x:v>
+      </x:c>
+      <x:c r="B163" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C163" s="65" t="str">
+      <x:c r="C163" s="66" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D163" s="65" t="str">
-        <x:v>Python agent engine boundary</x:v>
-      </x:c>
-      <x:c r="E163" s="65" t="str">
-        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
-      </x:c>
-      <x:c r="F163" s="65" t="str">
+      <x:c r="D163" s="66" t="str">
+        <x:v>Go control plane modular monolith</x:v>
+      </x:c>
+      <x:c r="E163" s="66" t="str">
+        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
+      </x:c>
+      <x:c r="F163" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G163" s="65"/>
-      <x:c r="H163" s="65" t="str">
+      <x:c r="G163" s="66"/>
+      <x:c r="H163" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I163" s="389" t="n">
+      <x:c r="I163" s="388" t="n">
         <x:f>IF(H163="Done",1,IF(H163="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J163" s="65" t="str">
-        <x:v>Model gateway</x:v>
-      </x:c>
-      <x:c r="K163" s="65"/>
-      <x:c r="L163" s="65"/>
-      <x:c r="M163" s="65" t="str">
-        <x:v>Different ecosystem/iteration cadence.</x:v>
+      <x:c r="J163" s="66" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K163" s="66"/>
+      <x:c r="L163" s="66"/>
+      <x:c r="M163" s="66" t="str">
+        <x:v>Avoid premature microservices.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="66" t="str">
-        <x:v>R-157</x:v>
-      </x:c>
-      <x:c r="B164" s="66" t="str">
+      <x:c r="A164" s="65" t="str">
+        <x:v>R-156</x:v>
+      </x:c>
+      <x:c r="B164" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C164" s="66" t="str">
+      <x:c r="C164" s="65" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D164" s="66" t="str">
-        <x:v>Runner manager boundary</x:v>
-      </x:c>
-      <x:c r="E164" s="66" t="str">
-        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
-      </x:c>
-      <x:c r="F164" s="66" t="str">
+      <x:c r="D164" s="65" t="str">
+        <x:v>Python agent engine boundary</x:v>
+      </x:c>
+      <x:c r="E164" s="65" t="str">
+        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
+      </x:c>
+      <x:c r="F164" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G164" s="66"/>
-      <x:c r="H164" s="66" t="str">
+      <x:c r="G164" s="65"/>
+      <x:c r="H164" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I164" s="388" t="n">
+      <x:c r="I164" s="389" t="n">
         <x:f>IF(H164="Done",1,IF(H164="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J164" s="66" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
-      </x:c>
-      <x:c r="K164" s="66"/>
-      <x:c r="L164" s="66"/>
-      <x:c r="M164" s="66" t="str">
-        <x:v>Central execution control.</x:v>
+      <x:c r="J164" s="65" t="str">
+        <x:v>Model gateway</x:v>
+      </x:c>
+      <x:c r="K164" s="65"/>
+      <x:c r="L164" s="65"/>
+      <x:c r="M164" s="65" t="str">
+        <x:v>Different ecosystem/iteration cadence.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="65" t="str">
-        <x:v>R-158</x:v>
-      </x:c>
-      <x:c r="B165" s="65" t="str">
+      <x:c r="A165" s="66" t="str">
+        <x:v>R-157</x:v>
+      </x:c>
+      <x:c r="B165" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C165" s="65" t="str">
-        <x:v>CI/CD</x:v>
-      </x:c>
-      <x:c r="D165" s="65" t="str">
-        <x:v>Unified PR pipeline</x:v>
-      </x:c>
-      <x:c r="E165" s="65" t="str">
-        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
-      </x:c>
-      <x:c r="F165" s="65" t="str">
+      <x:c r="C165" s="66" t="str">
+        <x:v>Platform Architecture</x:v>
+      </x:c>
+      <x:c r="D165" s="66" t="str">
+        <x:v>Runner manager boundary</x:v>
+      </x:c>
+      <x:c r="E165" s="66" t="str">
+        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
+      </x:c>
+      <x:c r="F165" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G165" s="65"/>
-      <x:c r="H165" s="65" t="str">
+      <x:c r="G165" s="66"/>
+      <x:c r="H165" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I165" s="389" t="n">
+      <x:c r="I165" s="388" t="n">
         <x:f>IF(H165="Done",1,IF(H165="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J165" s="65" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="K165" s="65"/>
-      <x:c r="L165" s="65"/>
-      <x:c r="M165" s="65" t="str">
-        <x:v>Real iOS compile uses macOS.</x:v>
+      <x:c r="J165" s="66" t="str">
+        <x:v>Ephemeral Linux sandbox</x:v>
+      </x:c>
+      <x:c r="K165" s="66"/>
+      <x:c r="L165" s="66"/>
+      <x:c r="M165" s="66" t="str">
+        <x:v>Central execution control.</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="66" t="str">
-        <x:v>R-159</x:v>
-      </x:c>
-      <x:c r="B166" s="66" t="str">
+      <x:c r="A166" s="65" t="str">
+        <x:v>R-158</x:v>
+      </x:c>
+      <x:c r="B166" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C166" s="66" t="str">
+      <x:c r="C166" s="65" t="str">
         <x:v>CI/CD</x:v>
       </x:c>
-      <x:c r="D166" s="66" t="str">
-        <x:v>Immutable build promotion</x:v>
-      </x:c>
-      <x:c r="E166" s="66" t="str">
-        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
-      </x:c>
-      <x:c r="F166" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G166" s="66"/>
-      <x:c r="H166" s="66" t="str">
+      <x:c r="D166" s="65" t="str">
+        <x:v>Unified PR pipeline</x:v>
+      </x:c>
+      <x:c r="E166" s="65" t="str">
+        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
+      </x:c>
+      <x:c r="F166" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G166" s="65"/>
+      <x:c r="H166" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I166" s="388" t="n">
+      <x:c r="I166" s="389" t="n">
         <x:f>IF(H166="Done",1,IF(H166="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J166" s="66" t="str">
-        <x:v>Deployment Agent</x:v>
-      </x:c>
-      <x:c r="K166" s="66"/>
-      <x:c r="L166" s="66"/>
-      <x:c r="M166" s="66" t="str">
-        <x:v>Reduces preview/production mismatch.</x:v>
+      <x:c r="J166" s="65" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="K166" s="65"/>
+      <x:c r="L166" s="65"/>
+      <x:c r="M166" s="65" t="str">
+        <x:v>Real iOS compile uses macOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="65" t="str">
-        <x:v>R-160</x:v>
-      </x:c>
-      <x:c r="B167" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C167" s="65" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D167" s="65" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="E167" s="65" t="str">
-        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
-      </x:c>
-      <x:c r="F167" s="65" t="str">
+      <x:c r="A167" s="66" t="str">
+        <x:v>R-159</x:v>
+      </x:c>
+      <x:c r="B167" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C167" s="66" t="str">
+        <x:v>CI/CD</x:v>
+      </x:c>
+      <x:c r="D167" s="66" t="str">
+        <x:v>Immutable build promotion</x:v>
+      </x:c>
+      <x:c r="E167" s="66" t="str">
+        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
+      </x:c>
+      <x:c r="F167" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G167" s="65"/>
-      <x:c r="H167" s="65" t="str">
+      <x:c r="G167" s="66"/>
+      <x:c r="H167" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I167" s="389" t="n">
+      <x:c r="I167" s="388" t="n">
         <x:f>IF(H167="Done",1,IF(H167="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J167" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K167" s="65"/>
-      <x:c r="L167" s="65"/>
-      <x:c r="M167" s="65"/>
+      <x:c r="J167" s="66" t="str">
+        <x:v>Deployment Agent</x:v>
+      </x:c>
+      <x:c r="K167" s="66"/>
+      <x:c r="L167" s="66"/>
+      <x:c r="M167" s="66" t="str">
+        <x:v>Reduces preview/production mismatch.</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="66" t="str">
-        <x:v>R-161</x:v>
-      </x:c>
-      <x:c r="B168" s="66" t="str">
+      <x:c r="A168" s="65" t="str">
+        <x:v>R-160</x:v>
+      </x:c>
+      <x:c r="B168" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C168" s="66" t="str">
-        <x:v>Preview</x:v>
-      </x:c>
-      <x:c r="D168" s="66" t="str">
-        <x:v>Local Mac Agent productized</x:v>
-      </x:c>
-      <x:c r="E168" s="66" t="str">
-        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
-      </x:c>
-      <x:c r="F168" s="66" t="str">
+      <x:c r="C168" s="65" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D168" s="65" t="str">
+        <x:v>Framework upgrade workflow</x:v>
+      </x:c>
+      <x:c r="E168" s="65" t="str">
+        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
+      </x:c>
+      <x:c r="F168" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G168" s="66"/>
-      <x:c r="H168" s="66" t="str">
+      <x:c r="G168" s="65"/>
+      <x:c r="H168" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I168" s="388" t="n">
+      <x:c r="I168" s="389" t="n">
         <x:f>IF(H168="Done",1,IF(H168="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J168" s="66" t="str">
-        <x:v>Local Mac Agent</x:v>
-      </x:c>
-      <x:c r="K168" s="66"/>
-      <x:c r="L168" s="66"/>
-      <x:c r="M168" s="66" t="str">
-        <x:v>Reduces cloud Mac cost.</x:v>
-      </x:c>
+      <x:c r="J168" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K168" s="65"/>
+      <x:c r="L168" s="65"/>
+      <x:c r="M168" s="65"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="65" t="str">
-        <x:v>R-162</x:v>
-      </x:c>
-      <x:c r="B169" s="65" t="str">
+      <x:c r="A169" s="66" t="str">
+        <x:v>R-161</x:v>
+      </x:c>
+      <x:c r="B169" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C169" s="65" t="str">
+      <x:c r="C169" s="66" t="str">
         <x:v>Preview</x:v>
       </x:c>
-      <x:c r="D169" s="65" t="str">
-        <x:v>Interactive cloud simulator metering</x:v>
-      </x:c>
-      <x:c r="E169" s="65" t="str">
-        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
-      </x:c>
-      <x:c r="F169" s="65" t="str">
+      <x:c r="D169" s="66" t="str">
+        <x:v>Local Mac Agent productized</x:v>
+      </x:c>
+      <x:c r="E169" s="66" t="str">
+        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
+      </x:c>
+      <x:c r="F169" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G169" s="65"/>
-      <x:c r="H169" s="65" t="str">
+      <x:c r="G169" s="66"/>
+      <x:c r="H169" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I169" s="389" t="n">
+      <x:c r="I169" s="388" t="n">
         <x:f>IF(H169="Done",1,IF(H169="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J169" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K169" s="65"/>
-      <x:c r="L169" s="65"/>
-      <x:c r="M169" s="65" t="str">
-        <x:v>Separate verification build cost from interactive session cost.</x:v>
+      <x:c r="J169" s="66" t="str">
+        <x:v>Local Mac Agent</x:v>
+      </x:c>
+      <x:c r="K169" s="66"/>
+      <x:c r="L169" s="66"/>
+      <x:c r="M169" s="66" t="str">
+        <x:v>Reduces cloud Mac cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="66" t="str">
-        <x:v>R-163</x:v>
-      </x:c>
-      <x:c r="B170" s="66" t="str">
+      <x:c r="A170" s="65" t="str">
+        <x:v>R-162</x:v>
+      </x:c>
+      <x:c r="B170" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C170" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D170" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="E170" s="66" t="str">
-        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
-      </x:c>
-      <x:c r="F170" s="66" t="str">
+      <x:c r="C170" s="65" t="str">
+        <x:v>Preview</x:v>
+      </x:c>
+      <x:c r="D170" s="65" t="str">
+        <x:v>Interactive cloud simulator metering</x:v>
+      </x:c>
+      <x:c r="E170" s="65" t="str">
+        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
+      </x:c>
+      <x:c r="F170" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G170" s="66"/>
-      <x:c r="H170" s="66" t="str">
+      <x:c r="G170" s="65"/>
+      <x:c r="H170" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I170" s="388" t="n">
+      <x:c r="I170" s="389" t="n">
         <x:f>IF(H170="Done",1,IF(H170="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J170" s="66" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K170" s="66"/>
-      <x:c r="L170" s="66"/>
-      <x:c r="M170" s="66" t="str">
-        <x:v>Measure before rewrite.</x:v>
+      <x:c r="J170" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K170" s="65"/>
+      <x:c r="L170" s="65"/>
+      <x:c r="M170" s="65" t="str">
+        <x:v>Separate verification build cost from interactive session cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="65" t="str">
-        <x:v>R-164</x:v>
-      </x:c>
-      <x:c r="B171" s="65" t="str">
+      <x:c r="A171" s="66" t="str">
+        <x:v>R-163</x:v>
+      </x:c>
+      <x:c r="B171" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C171" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D171" s="65" t="str">
-        <x:v>Template/repo health dashboard</x:v>
-      </x:c>
-      <x:c r="E171" s="65" t="str">
-        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
-      </x:c>
-      <x:c r="F171" s="65" t="str">
+      <x:c r="C171" s="66" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D171" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="E171" s="66" t="str">
+        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
+      </x:c>
+      <x:c r="F171" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G171" s="65"/>
-      <x:c r="H171" s="65" t="str">
+      <x:c r="G171" s="66"/>
+      <x:c r="H171" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I171" s="389" t="n">
+      <x:c r="I171" s="388" t="n">
         <x:f>IF(H171="Done",1,IF(H171="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J171" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="K171" s="65"/>
-      <x:c r="L171" s="65"/>
-      <x:c r="M171" s="65" t="str">
-        <x:v>Use data to trigger architecture review.</x:v>
+      <x:c r="J171" s="66" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K171" s="66"/>
+      <x:c r="L171" s="66"/>
+      <x:c r="M171" s="66" t="str">
+        <x:v>Measure before rewrite.</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="66" t="str">
-        <x:v>R-165</x:v>
-      </x:c>
-      <x:c r="B172" s="66" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C172" s="66" t="str">
-        <x:v>Migration</x:v>
-      </x:c>
-      <x:c r="D172" s="66" t="str">
-        <x:v>Cross-platform to native migration engine</x:v>
-      </x:c>
-      <x:c r="E172" s="66" t="str">
-        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
-      </x:c>
-      <x:c r="F172" s="66" t="str">
+      <x:c r="A172" s="65" t="str">
+        <x:v>R-164</x:v>
+      </x:c>
+      <x:c r="B172" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C172" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D172" s="65" t="str">
+        <x:v>Template/repo health dashboard</x:v>
+      </x:c>
+      <x:c r="E172" s="65" t="str">
+        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
+      </x:c>
+      <x:c r="F172" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G172" s="66"/>
-      <x:c r="H172" s="66" t="str">
+      <x:c r="G172" s="65"/>
+      <x:c r="H172" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I172" s="388" t="n">
+      <x:c r="I172" s="389" t="n">
         <x:f>IF(H172="Done",1,IF(H172="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J172" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="K172" s="66"/>
-      <x:c r="L172" s="66"/>
-      <x:c r="M172" s="66" t="str">
-        <x:v>Prevents framework lock-in.</x:v>
+      <x:c r="J172" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="K172" s="65"/>
+      <x:c r="L172" s="65"/>
+      <x:c r="M172" s="65" t="str">
+        <x:v>Use data to trigger architecture review.</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="65" t="str">
-        <x:v>R-166</x:v>
-      </x:c>
-      <x:c r="B173" s="65" t="str">
+      <x:c r="A173" s="66" t="str">
+        <x:v>R-165</x:v>
+      </x:c>
+      <x:c r="B173" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C173" s="65" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D173" s="65" t="str">
-        <x:v>Cross-repo task coordinator</x:v>
-      </x:c>
-      <x:c r="E173" s="65" t="str">
-        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
-      </x:c>
-      <x:c r="F173" s="65" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G173" s="65"/>
-      <x:c r="H173" s="65" t="str">
+      <x:c r="C173" s="66" t="str">
+        <x:v>Migration</x:v>
+      </x:c>
+      <x:c r="D173" s="66" t="str">
+        <x:v>Cross-platform to native migration engine</x:v>
+      </x:c>
+      <x:c r="E173" s="66" t="str">
+        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
+      </x:c>
+      <x:c r="F173" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G173" s="66"/>
+      <x:c r="H173" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I173" s="389" t="n">
+      <x:c r="I173" s="388" t="n">
         <x:f>IF(H173="Done",1,IF(H173="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J173" s="65" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="K173" s="65"/>
-      <x:c r="L173" s="65"/>
-      <x:c r="M173" s="65"/>
+      <x:c r="J173" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="K173" s="66"/>
+      <x:c r="L173" s="66"/>
+      <x:c r="M173" s="66" t="str">
+        <x:v>Prevents framework lock-in.</x:v>
+      </x:c>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="66" t="str">
-        <x:v>R-167</x:v>
-      </x:c>
-      <x:c r="B174" s="66" t="str">
+      <x:c r="A174" s="65" t="str">
+        <x:v>R-166</x:v>
+      </x:c>
+      <x:c r="B174" s="65" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C174" s="66" t="str">
-        <x:v>Infrastructure</x:v>
-      </x:c>
-      <x:c r="D174" s="66" t="str">
-        <x:v>BYOC / private runners</x:v>
-      </x:c>
-      <x:c r="E174" s="66" t="str">
-        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
-      </x:c>
-      <x:c r="F174" s="66" t="str">
+      <x:c r="C174" s="65" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D174" s="65" t="str">
+        <x:v>Cross-repo task coordinator</x:v>
+      </x:c>
+      <x:c r="E174" s="65" t="str">
+        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
+      </x:c>
+      <x:c r="F174" s="65" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G174" s="66"/>
-      <x:c r="H174" s="66" t="str">
+      <x:c r="G174" s="65"/>
+      <x:c r="H174" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I174" s="388" t="n">
+      <x:c r="I174" s="389" t="n">
         <x:f>IF(H174="Done",1,IF(H174="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J174" s="66" t="str">
-        <x:v>Enterprise workload isolation</x:v>
-      </x:c>
-      <x:c r="K174" s="66"/>
-      <x:c r="L174" s="66"/>
-      <x:c r="M174" s="66"/>
+      <x:c r="J174" s="65" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="K174" s="65"/>
+      <x:c r="L174" s="65"/>
+      <x:c r="M174" s="65"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="65" t="str">
-        <x:v>R-168</x:v>
-      </x:c>
-      <x:c r="B175" s="65" t="str">
+      <x:c r="A175" s="66" t="str">
+        <x:v>R-167</x:v>
+      </x:c>
+      <x:c r="B175" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C175" s="65" t="str">
-        <x:v>Testing</x:v>
-      </x:c>
-      <x:c r="D175" s="65" t="str">
-        <x:v>Physical device cloud integration</x:v>
-      </x:c>
-      <x:c r="E175" s="65" t="str">
-        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
-      </x:c>
-      <x:c r="F175" s="65" t="str">
+      <x:c r="C175" s="66" t="str">
+        <x:v>Infrastructure</x:v>
+      </x:c>
+      <x:c r="D175" s="66" t="str">
+        <x:v>BYOC / private runners</x:v>
+      </x:c>
+      <x:c r="E175" s="66" t="str">
+        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
+      </x:c>
+      <x:c r="F175" s="66" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G175" s="65"/>
-      <x:c r="H175" s="65" t="str">
+      <x:c r="G175" s="66"/>
+      <x:c r="H175" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I175" s="389" t="n">
+      <x:c r="I175" s="388" t="n">
         <x:f>IF(H175="Done",1,IF(H175="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J175" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K175" s="65"/>
-      <x:c r="L175" s="65"/>
-      <x:c r="M175" s="65"/>
+      <x:c r="J175" s="66" t="str">
+        <x:v>Enterprise workload isolation</x:v>
+      </x:c>
+      <x:c r="K175" s="66"/>
+      <x:c r="L175" s="66"/>
+      <x:c r="M175" s="66"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="127" t="str">
-        <x:v>R-169</x:v>
-      </x:c>
-      <x:c r="B176" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
-      </x:c>
-      <x:c r="C176" s="127" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D176" s="127" t="str">
-        <x:v>Template support lifecycle</x:v>
-      </x:c>
-      <x:c r="E176" s="127" t="str">
-        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
-      </x:c>
-      <x:c r="F176" s="127" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G176" s="127"/>
-      <x:c r="H176" s="127" t="str">
+      <x:c r="A176" s="65" t="str">
+        <x:v>R-168</x:v>
+      </x:c>
+      <x:c r="B176" s="65" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C176" s="65" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="D176" s="65" t="str">
+        <x:v>Physical device cloud integration</x:v>
+      </x:c>
+      <x:c r="E176" s="65" t="str">
+        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
+      </x:c>
+      <x:c r="F176" s="65" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G176" s="65"/>
+      <x:c r="H176" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I176" s="390" t="n">
+      <x:c r="I176" s="389" t="n">
         <x:f>IF(H176="Done",1,IF(H176="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J176" s="127" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="K176" s="127"/>
-      <x:c r="L176" s="127"/>
-      <x:c r="M176" s="127"/>
+      <x:c r="J176" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K176" s="65"/>
+      <x:c r="L176" s="65"/>
+      <x:c r="M176" s="65"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="127" t="str">
-        <x:v>R-170</x:v>
+        <x:v>R-169</x:v>
       </x:c>
       <x:c r="B177" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C177" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D177" s="127" t="str">
-        <x:v>Framework/toolchain production SLO</x:v>
+        <x:v>Template support lifecycle</x:v>
       </x:c>
       <x:c r="E177" s="127" t="str">
-        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
+        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
       </x:c>
       <x:c r="F177" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G177" s="127"/>
       <x:c r="H177" s="127" t="str">
@@ -16301,29 +16309,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="127" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="K177" s="127"/>
       <x:c r="L177" s="127"/>
-      <x:c r="M177" s="127" t="str">
-        <x:v>Production readiness is measured, not assumed.</x:v>
-      </x:c>
+      <x:c r="M177" s="127"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="127" t="str">
-        <x:v>R-171</x:v>
+        <x:v>R-170</x:v>
       </x:c>
       <x:c r="B178" s="127" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C178" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D178" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Framework/toolchain production SLO</x:v>
       </x:c>
       <x:c r="E178" s="127" t="str">
-        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
+        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
       </x:c>
       <x:c r="F178" s="127" t="str">
         <x:v>P0</x:v>
@@ -16337,17 +16343,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="127" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="K178" s="127"/>
       <x:c r="L178" s="127"/>
       <x:c r="M178" s="127" t="str">
-        <x:v>No agent-to-vendor SDK coupling.</x:v>
+        <x:v>Production readiness is measured, not assumed.</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="127" t="str">
-        <x:v>R-172</x:v>
+        <x:v>R-171</x:v>
       </x:c>
       <x:c r="B179" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16356,10 +16362,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D179" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="E179" s="127" t="str">
-        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
+        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
       </x:c>
       <x:c r="F179" s="127" t="str">
         <x:v>P0</x:v>
@@ -16373,17 +16379,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K179" s="127"/>
       <x:c r="L179" s="127"/>
       <x:c r="M179" s="127" t="str">
-        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
+        <x:v>No agent-to-vendor SDK coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="127" t="str">
-        <x:v>R-173</x:v>
+        <x:v>R-172</x:v>
       </x:c>
       <x:c r="B180" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16392,10 +16398,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D180" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="E180" s="127" t="str">
-        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
+        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
       </x:c>
       <x:c r="F180" s="127" t="str">
         <x:v>P0</x:v>
@@ -16414,12 +16420,12 @@
       <x:c r="K180" s="127"/>
       <x:c r="L180" s="127"/>
       <x:c r="M180" s="127" t="str">
-        <x:v>Cheapest safe runtime wins.</x:v>
+        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="127" t="str">
-        <x:v>R-174</x:v>
+        <x:v>R-173</x:v>
       </x:c>
       <x:c r="B181" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16428,13 +16434,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D181" s="127" t="str">
-        <x:v>Browser runtime PoC</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="E181" s="127" t="str">
-        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
+        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
       </x:c>
       <x:c r="F181" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G181" s="127"/>
       <x:c r="H181" s="127" t="str">
@@ -16445,17 +16451,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K181" s="127"/>
       <x:c r="L181" s="127"/>
       <x:c r="M181" s="127" t="str">
-        <x:v>Not universal sandbox.</x:v>
+        <x:v>Cheapest safe runtime wins.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="127" t="str">
-        <x:v>R-175</x:v>
+        <x:v>R-174</x:v>
       </x:c>
       <x:c r="B182" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16464,13 +16470,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D182" s="127" t="str">
-        <x:v>Runtime quotas and metering</x:v>
+        <x:v>Browser runtime PoC</x:v>
       </x:c>
       <x:c r="E182" s="127" t="str">
-        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
+        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
       </x:c>
       <x:c r="F182" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G182" s="127"/>
       <x:c r="H182" s="127" t="str">
@@ -16481,29 +16487,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="K182" s="127"/>
       <x:c r="L182" s="127"/>
       <x:c r="M182" s="127" t="str">
-        <x:v>Required for cost and abuse control.</x:v>
+        <x:v>Not universal sandbox.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="127" t="str">
-        <x:v>R-176</x:v>
+        <x:v>R-175</x:v>
       </x:c>
       <x:c r="B183" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C183" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D183" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Runtime quotas and metering</x:v>
       </x:c>
       <x:c r="E183" s="127" t="str">
-        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
+        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
       </x:c>
       <x:c r="F183" s="127" t="str">
         <x:v>P0</x:v>
@@ -16517,17 +16523,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="127" t="str">
-        <x:v>Supervisor / orchestrator</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K183" s="127"/>
       <x:c r="L183" s="127"/>
       <x:c r="M183" s="127" t="str">
-        <x:v>Platform-owned state schema.</x:v>
+        <x:v>Required for cost and abuse control.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="127" t="str">
-        <x:v>R-177</x:v>
+        <x:v>R-176</x:v>
       </x:c>
       <x:c r="B184" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16536,10 +16542,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D184" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="E184" s="127" t="str">
-        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
+        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
       </x:c>
       <x:c r="F184" s="127" t="str">
         <x:v>P0</x:v>
@@ -16553,17 +16559,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Supervisor / orchestrator</x:v>
       </x:c>
       <x:c r="K184" s="127"/>
       <x:c r="L184" s="127"/>
       <x:c r="M184" s="127" t="str">
-        <x:v>No full restart by default.</x:v>
+        <x:v>Platform-owned state schema.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="127" t="str">
-        <x:v>R-178</x:v>
+        <x:v>R-177</x:v>
       </x:c>
       <x:c r="B185" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16572,10 +16578,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D185" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="E185" s="127" t="str">
-        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
+        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
       </x:c>
       <x:c r="F185" s="127" t="str">
         <x:v>P0</x:v>
@@ -16589,29 +16595,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K185" s="127"/>
       <x:c r="L185" s="127"/>
       <x:c r="M185" s="127" t="str">
-        <x:v>Prevent duplicate side effects.</x:v>
+        <x:v>No full restart by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="127" t="str">
-        <x:v>R-179</x:v>
+        <x:v>R-178</x:v>
       </x:c>
       <x:c r="B186" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C186" s="127" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D186" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="E186" s="127" t="str">
-        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
+        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
       </x:c>
       <x:c r="F186" s="127" t="str">
         <x:v>P0</x:v>
@@ -16625,29 +16631,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K186" s="127"/>
       <x:c r="L186" s="127"/>
       <x:c r="M186" s="127" t="str">
-        <x:v>Supports replay, audit and debugging.</x:v>
+        <x:v>Prevent duplicate side effects.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="127" t="str">
-        <x:v>R-180</x:v>
+        <x:v>R-179</x:v>
       </x:c>
       <x:c r="B187" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C187" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D187" s="127" t="str">
-        <x:v>Orchestrator Adapter</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="E187" s="127" t="str">
-        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
+        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
       </x:c>
       <x:c r="F187" s="127" t="str">
         <x:v>P0</x:v>
@@ -16666,24 +16672,24 @@
       <x:c r="K187" s="127"/>
       <x:c r="L187" s="127"/>
       <x:c r="M187" s="127" t="str">
-        <x:v>LangGraph may be first implementation.</x:v>
+        <x:v>Supports replay, audit and debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="127" t="str">
-        <x:v>R-181</x:v>
+        <x:v>R-180</x:v>
       </x:c>
       <x:c r="B188" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C188" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D188" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Orchestrator Adapter</x:v>
       </x:c>
       <x:c r="E188" s="127" t="str">
-        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
+        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
       </x:c>
       <x:c r="F188" s="127" t="str">
         <x:v>P0</x:v>
@@ -16697,17 +16703,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K188" s="127"/>
       <x:c r="L188" s="127"/>
       <x:c r="M188" s="127" t="str">
-        <x:v>Frontend never parses provider-specific streams.</x:v>
+        <x:v>LangGraph may be first implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="127" t="str">
-        <x:v>R-182</x:v>
+        <x:v>R-181</x:v>
       </x:c>
       <x:c r="B189" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16716,10 +16722,10 @@
         <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D189" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="E189" s="127" t="str">
-        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
+        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
       </x:c>
       <x:c r="F189" s="127" t="str">
         <x:v>P0</x:v>
@@ -16733,29 +16739,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K189" s="127"/>
       <x:c r="L189" s="127"/>
       <x:c r="M189" s="127" t="str">
-        <x:v>SSE allowed for simple one-way streams.</x:v>
+        <x:v>Frontend never parses provider-specific streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="127" t="str">
-        <x:v>R-183</x:v>
+        <x:v>R-182</x:v>
       </x:c>
       <x:c r="B190" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C190" s="127" t="str">
-        <x:v>Approvals</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D190" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="E190" s="127" t="str">
-        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
+        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
       </x:c>
       <x:c r="F190" s="127" t="str">
         <x:v>P0</x:v>
@@ -16769,17 +16775,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="K190" s="127"/>
       <x:c r="L190" s="127"/>
       <x:c r="M190" s="127" t="str">
-        <x:v>Approval based on risk.</x:v>
+        <x:v>SSE allowed for simple one-way streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="127" t="str">
-        <x:v>R-184</x:v>
+        <x:v>R-183</x:v>
       </x:c>
       <x:c r="B191" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16788,10 +16794,10 @@
         <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D191" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="E191" s="127" t="str">
-        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
+        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
       </x:c>
       <x:c r="F191" s="127" t="str">
         <x:v>P0</x:v>
@@ -16805,29 +16811,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K191" s="127"/>
       <x:c r="L191" s="127"/>
       <x:c r="M191" s="127" t="str">
-        <x:v>Production/destructive actions auditable.</x:v>
+        <x:v>Approval based on risk.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="127" t="str">
-        <x:v>R-185</x:v>
+        <x:v>R-184</x:v>
       </x:c>
       <x:c r="B192" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C192" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D192" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="E192" s="127" t="str">
-        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
+        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
       </x:c>
       <x:c r="F192" s="127" t="str">
         <x:v>P0</x:v>
@@ -16841,17 +16847,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="K192" s="127"/>
       <x:c r="L192" s="127"/>
       <x:c r="M192" s="127" t="str">
-        <x:v>Deny by default.</x:v>
+        <x:v>Production/destructive actions auditable.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="127" t="str">
-        <x:v>R-186</x:v>
+        <x:v>R-185</x:v>
       </x:c>
       <x:c r="B193" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16860,13 +16866,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D193" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="E193" s="127" t="str">
-        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
+        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
       </x:c>
       <x:c r="F193" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G193" s="127"/>
       <x:c r="H193" s="127" t="str">
@@ -16877,17 +16883,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K193" s="127"/>
       <x:c r="L193" s="127"/>
       <x:c r="M193" s="127" t="str">
-        <x:v>No arbitrary agent-to-MCP connections.</x:v>
+        <x:v>Deny by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="127" t="str">
-        <x:v>R-187</x:v>
+        <x:v>R-186</x:v>
       </x:c>
       <x:c r="B194" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16896,13 +16902,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D194" s="127" t="str">
-        <x:v>Tool secret broker</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="E194" s="127" t="str">
-        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
+        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
       </x:c>
       <x:c r="F194" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G194" s="127"/>
       <x:c r="H194" s="127" t="str">
@@ -16918,27 +16924,27 @@
       <x:c r="K194" s="127"/>
       <x:c r="L194" s="127"/>
       <x:c r="M194" s="127" t="str">
-        <x:v>Audit every secret grant.</x:v>
+        <x:v>No arbitrary agent-to-MCP connections.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="127" t="str">
-        <x:v>R-188</x:v>
+        <x:v>R-187</x:v>
       </x:c>
       <x:c r="B195" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C195" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D195" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Tool secret broker</x:v>
       </x:c>
       <x:c r="E195" s="127" t="str">
-        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
+        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
       </x:c>
       <x:c r="F195" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G195" s="127"/>
       <x:c r="H195" s="127" t="str">
@@ -16949,32 +16955,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J195" s="127" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="K195" s="127"/>
       <x:c r="L195" s="127"/>
       <x:c r="M195" s="127" t="str">
-        <x:v>Not platform core.</x:v>
+        <x:v>Audit every secret grant.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="127" t="str">
-        <x:v>R-189</x:v>
+        <x:v>R-188</x:v>
       </x:c>
       <x:c r="B196" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C196" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D196" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="E196" s="127" t="str">
-        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
+        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
       </x:c>
       <x:c r="F196" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G196" s="127"/>
       <x:c r="H196" s="127" t="str">
@@ -16985,29 +16991,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J196" s="127" t="str">
-        <x:v>Architecture decision records</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K196" s="127"/>
       <x:c r="L196" s="127"/>
       <x:c r="M196" s="127" t="str">
-        <x:v>References inform; benchmarks decide.</x:v>
+        <x:v>Not platform core.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="127" t="str">
-        <x:v>R-190</x:v>
+        <x:v>R-189</x:v>
       </x:c>
       <x:c r="B197" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C197" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D197" s="127" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="E197" s="127" t="str">
-        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
+        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
       </x:c>
       <x:c r="F197" s="127" t="str">
         <x:v>P0</x:v>
@@ -17021,32 +17027,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J197" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Architecture decision records</x:v>
       </x:c>
       <x:c r="K197" s="127"/>
       <x:c r="L197" s="127"/>
       <x:c r="M197" s="127" t="str">
-        <x:v>Architectural learning != code copying.</x:v>
+        <x:v>References inform; benchmarks decide.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="127" t="str">
-        <x:v>R-191</x:v>
+        <x:v>R-190</x:v>
       </x:c>
       <x:c r="B198" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C198" s="127" t="str">
-        <x:v>Team</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D198" s="127" t="str">
-        <x:v>Shared engineering glossary</x:v>
+        <x:v>Open-source license review</x:v>
       </x:c>
       <x:c r="E198" s="127" t="str">
-        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
+        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
       </x:c>
       <x:c r="F198" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G198" s="127"/>
       <x:c r="H198" s="127" t="str">
@@ -17056,31 +17062,33 @@
         <x:f>IF(H198="Done",1,IF(H198="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J198" s="127"/>
+      <x:c r="J198" s="127" t="str">
+        <x:v>Build-vs-Buy benchmark process</x:v>
+      </x:c>
       <x:c r="K198" s="127"/>
       <x:c r="L198" s="127"/>
       <x:c r="M198" s="127" t="str">
-        <x:v>Use in docs and AI prompts.</x:v>
+        <x:v>Architectural learning != code copying.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="127" t="str">
-        <x:v>R-192</x:v>
+        <x:v>R-191</x:v>
       </x:c>
       <x:c r="B199" s="127" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C199" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Team</x:v>
       </x:c>
       <x:c r="D199" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Shared engineering glossary</x:v>
       </x:c>
       <x:c r="E199" s="127" t="str">
-        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
+        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
       </x:c>
       <x:c r="F199" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G199" s="127"/>
       <x:c r="H199" s="127" t="str">
@@ -17090,30 +17098,28 @@
         <x:f>IF(H199="Done",1,IF(H199="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J199" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
-      </x:c>
+      <x:c r="J199" s="127"/>
       <x:c r="K199" s="127"/>
       <x:c r="L199" s="127"/>
       <x:c r="M199" s="127" t="str">
-        <x:v>Marketplace later.</x:v>
+        <x:v>Use in docs and AI prompts.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="127" t="str">
-        <x:v>R-193</x:v>
+        <x:v>R-192</x:v>
       </x:c>
       <x:c r="B200" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C200" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D200" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="E200" s="127" t="str">
-        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
+        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
       </x:c>
       <x:c r="F200" s="127" t="str">
         <x:v>P1</x:v>
@@ -17127,17 +17133,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="127" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K200" s="127"/>
       <x:c r="L200" s="127"/>
       <x:c r="M200" s="127" t="str">
-        <x:v>Extends local mode beyond Mac.</x:v>
+        <x:v>Marketplace later.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="127" t="str">
-        <x:v>R-194</x:v>
+        <x:v>R-193</x:v>
       </x:c>
       <x:c r="B201" s="127" t="str">
         <x:v>MID</x:v>
@@ -17146,10 +17152,10 @@
         <x:v>Execution</x:v>
       </x:c>
       <x:c r="D201" s="127" t="str">
-        <x:v>Hybrid BYOK/local mode</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="E201" s="127" t="str">
-        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
+        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
       </x:c>
       <x:c r="F201" s="127" t="str">
         <x:v>P1</x:v>
@@ -17163,29 +17169,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="K201" s="127"/>
       <x:c r="L201" s="127"/>
       <x:c r="M201" s="127" t="str">
-        <x:v>Privacy + cost option.</x:v>
+        <x:v>Extends local mode beyond Mac.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="127" t="str">
-        <x:v>R-195</x:v>
+        <x:v>R-194</x:v>
       </x:c>
       <x:c r="B202" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C202" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D202" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Hybrid BYOK/local mode</x:v>
       </x:c>
       <x:c r="E202" s="127" t="str">
-        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
+        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
       </x:c>
       <x:c r="F202" s="127" t="str">
         <x:v>P1</x:v>
@@ -17199,17 +17205,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K202" s="127"/>
       <x:c r="L202" s="127"/>
       <x:c r="M202" s="127" t="str">
-        <x:v>Validate portability/failover.</x:v>
+        <x:v>Privacy + cost option.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="127" t="str">
-        <x:v>R-196</x:v>
+        <x:v>R-195</x:v>
       </x:c>
       <x:c r="B203" s="127" t="str">
         <x:v>MID</x:v>
@@ -17218,13 +17224,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D203" s="127" t="str">
-        <x:v>Sandbox snapshots and warm pools</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="E203" s="127" t="str">
-        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
+        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
       </x:c>
       <x:c r="F203" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G203" s="127"/>
       <x:c r="H203" s="127" t="str">
@@ -17235,32 +17241,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K203" s="127"/>
       <x:c r="L203" s="127"/>
       <x:c r="M203" s="127" t="str">
-        <x:v>Do not optimize blindly.</x:v>
+        <x:v>Validate portability/failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="127" t="str">
-        <x:v>R-197</x:v>
+        <x:v>R-196</x:v>
       </x:c>
       <x:c r="B204" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C204" s="127" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D204" s="127" t="str">
-        <x:v>Agent time-travel debugging</x:v>
+        <x:v>Sandbox snapshots and warm pools</x:v>
       </x:c>
       <x:c r="E204" s="127" t="str">
-        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
+        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
       </x:c>
       <x:c r="F204" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G204" s="127"/>
       <x:c r="H204" s="127" t="str">
@@ -17271,32 +17277,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K204" s="127"/>
       <x:c r="L204" s="127"/>
       <x:c r="M204" s="127" t="str">
-        <x:v>Operator and developer debugging.</x:v>
+        <x:v>Do not optimize blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="127" t="str">
-        <x:v>R-198</x:v>
+        <x:v>R-197</x:v>
       </x:c>
       <x:c r="B205" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C205" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D205" s="127" t="str">
-        <x:v>Tool marketplace verification</x:v>
+        <x:v>Agent time-travel debugging</x:v>
       </x:c>
       <x:c r="E205" s="127" t="str">
-        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
+        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
       </x:c>
       <x:c r="F205" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G205" s="127"/>
       <x:c r="H205" s="127" t="str">
@@ -17307,32 +17313,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K205" s="127"/>
       <x:c r="L205" s="127"/>
       <x:c r="M205" s="127" t="str">
-        <x:v>Verified badge is evidence-based.</x:v>
+        <x:v>Operator and developer debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="127" t="str">
-        <x:v>R-199</x:v>
+        <x:v>R-198</x:v>
       </x:c>
       <x:c r="B206" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C206" s="127" t="str">
-        <x:v>Routing</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D206" s="127" t="str">
-        <x:v>Runtime provider cost-latency routing</x:v>
+        <x:v>Tool marketplace verification</x:v>
       </x:c>
       <x:c r="E206" s="127" t="str">
-        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
+        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
       </x:c>
       <x:c r="F206" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G206" s="127"/>
       <x:c r="H206" s="127" t="str">
@@ -17343,32 +17349,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K206" s="127"/>
       <x:c r="L206" s="127"/>
       <x:c r="M206" s="127" t="str">
-        <x:v>Policy can override cheapest route.</x:v>
+        <x:v>Verified badge is evidence-based.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="127" t="str">
-        <x:v>R-200</x:v>
+        <x:v>R-199</x:v>
       </x:c>
       <x:c r="B207" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C207" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="D207" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Runtime provider cost-latency routing</x:v>
       </x:c>
       <x:c r="E207" s="127" t="str">
-        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
+        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
       </x:c>
       <x:c r="F207" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G207" s="127"/>
       <x:c r="H207" s="127" t="str">
@@ -17379,29 +17385,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K207" s="127"/>
       <x:c r="L207" s="127"/>
       <x:c r="M207" s="127" t="str">
-        <x:v>Keep portability via IR/contracts.</x:v>
+        <x:v>Policy can override cheapest route.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="127" t="str">
-        <x:v>R-201</x:v>
+        <x:v>R-200</x:v>
       </x:c>
       <x:c r="B208" s="127" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C208" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D208" s="127" t="str">
-        <x:v>Customer private MCP servers</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="E208" s="127" t="str">
-        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
+        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
       </x:c>
       <x:c r="F208" s="127" t="str">
         <x:v>P2</x:v>
@@ -17415,32 +17421,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="K208" s="127"/>
       <x:c r="L208" s="127"/>
       <x:c r="M208" s="127" t="str">
-        <x:v>Enterprise feature.</x:v>
+        <x:v>Keep portability via IR/contracts.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="127" t="str">
-        <x:v>R-202</x:v>
+        <x:v>R-201</x:v>
       </x:c>
       <x:c r="B209" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C209" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D209" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>Customer private MCP servers</x:v>
       </x:c>
       <x:c r="E209" s="127" t="str">
-        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
+        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
       </x:c>
       <x:c r="F209" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G209" s="127"/>
       <x:c r="H209" s="127" t="str">
@@ -17451,32 +17457,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="127" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K209" s="127"/>
       <x:c r="L209" s="127"/>
       <x:c r="M209" s="127" t="str">
-        <x:v>Central policy + audit remain.</x:v>
+        <x:v>Enterprise feature.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="127" t="str">
-        <x:v>R-203</x:v>
+        <x:v>R-202</x:v>
       </x:c>
       <x:c r="B210" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C210" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D210" s="127" t="str">
-        <x:v>Cross-region runtime scheduler</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="E210" s="127" t="str">
-        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
+        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
       </x:c>
       <x:c r="F210" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G210" s="127"/>
       <x:c r="H210" s="127" t="str">
@@ -17487,17 +17493,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="K210" s="127"/>
       <x:c r="L210" s="127"/>
       <x:c r="M210" s="127" t="str">
-        <x:v>Enterprise scale.</x:v>
+        <x:v>Central policy + audit remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="127" t="str">
-        <x:v>R-204</x:v>
+        <x:v>R-203</x:v>
       </x:c>
       <x:c r="B211" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17506,10 +17512,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D211" s="127" t="str">
-        <x:v>Hardened microVM runner fleet</x:v>
+        <x:v>Cross-region runtime scheduler</x:v>
       </x:c>
       <x:c r="E211" s="127" t="str">
-        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
+        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
       </x:c>
       <x:c r="F211" s="127" t="str">
         <x:v>P2</x:v>
@@ -17523,32 +17529,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="127" t="str">
-        <x:v>Provider cost-latency routing</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="K211" s="127"/>
       <x:c r="L211" s="127"/>
       <x:c r="M211" s="127" t="str">
-        <x:v>Do not build before benchmark.</x:v>
+        <x:v>Enterprise scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="127" t="str">
-        <x:v>R-205</x:v>
+        <x:v>R-204</x:v>
       </x:c>
       <x:c r="B212" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C212" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D212" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>Hardened microVM runner fleet</x:v>
       </x:c>
       <x:c r="E212" s="127" t="str">
-        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
+        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
       </x:c>
       <x:c r="F212" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G212" s="127"/>
       <x:c r="H212" s="127" t="str">
@@ -17559,29 +17565,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Provider cost-latency routing</x:v>
       </x:c>
       <x:c r="K212" s="127"/>
       <x:c r="L212" s="127"/>
       <x:c r="M212" s="127" t="str">
-        <x:v>Checkpoint-aware failover.</x:v>
+        <x:v>Do not build before benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="127" t="str">
-        <x:v>R-206</x:v>
+        <x:v>R-205</x:v>
       </x:c>
       <x:c r="B213" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C213" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D213" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="E213" s="127" t="str">
-        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
+        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
       </x:c>
       <x:c r="F213" s="127" t="str">
         <x:v>P1</x:v>
@@ -17595,17 +17601,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K213" s="127"/>
       <x:c r="L213" s="127"/>
       <x:c r="M213" s="127" t="str">
-        <x:v>Enterprise override support.</x:v>
+        <x:v>Checkpoint-aware failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="127" t="str">
-        <x:v>R-207</x:v>
+        <x:v>R-206</x:v>
       </x:c>
       <x:c r="B214" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17614,13 +17620,13 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D214" s="127" t="str">
-        <x:v>Two-person critical approval</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="E214" s="127" t="str">
-        <x:v>Optional dual approval for L4 actions.</x:v>
+        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
       </x:c>
       <x:c r="F214" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G214" s="127"/>
       <x:c r="H214" s="127" t="str">
@@ -17631,29 +17637,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K214" s="127"/>
       <x:c r="L214" s="127"/>
       <x:c r="M214" s="127" t="str">
-        <x:v>High-risk enterprise.</x:v>
+        <x:v>Enterprise override support.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="127" t="str">
-        <x:v>R-208</x:v>
+        <x:v>R-207</x:v>
       </x:c>
       <x:c r="B215" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C215" s="127" t="str">
-        <x:v>Models</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D215" s="127" t="str">
-        <x:v>Customer private model endpoints</x:v>
+        <x:v>Two-person critical approval</x:v>
       </x:c>
       <x:c r="E215" s="127" t="str">
-        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
+        <x:v>Optional dual approval for L4 actions.</x:v>
       </x:c>
       <x:c r="F215" s="127" t="str">
         <x:v>P2</x:v>
@@ -17667,29 +17673,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="127" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="K215" s="127"/>
       <x:c r="L215" s="127"/>
       <x:c r="M215" s="127" t="str">
-        <x:v>No direct client-to-model coupling.</x:v>
+        <x:v>High-risk enterprise.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="127" t="str">
-        <x:v>R-209</x:v>
+        <x:v>R-208</x:v>
       </x:c>
       <x:c r="B216" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C216" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D216" s="127" t="str">
-        <x:v>Automated provider benchmark suite</x:v>
+        <x:v>Customer private model endpoints</x:v>
       </x:c>
       <x:c r="E216" s="127" t="str">
-        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
+        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
       </x:c>
       <x:c r="F216" s="127" t="str">
         <x:v>P2</x:v>
@@ -17703,32 +17709,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="K216" s="127"/>
       <x:c r="L216" s="127"/>
       <x:c r="M216" s="127" t="str">
-        <x:v>Feeds routing/ADR reviews.</x:v>
+        <x:v>No direct client-to-model coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="127" t="str">
-        <x:v>R-210</x:v>
+        <x:v>R-209</x:v>
       </x:c>
       <x:c r="B217" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C217" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D217" s="127" t="str">
-        <x:v>Crash-resume production test</x:v>
+        <x:v>Automated provider benchmark suite</x:v>
       </x:c>
       <x:c r="E217" s="127" t="str">
-        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
+        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
       </x:c>
       <x:c r="F217" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G217" s="127"/>
       <x:c r="H217" s="127" t="str">
@@ -17739,17 +17745,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="K217" s="127"/>
       <x:c r="L217" s="127"/>
       <x:c r="M217" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Feeds routing/ADR reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="127" t="str">
-        <x:v>R-211</x:v>
+        <x:v>R-210</x:v>
       </x:c>
       <x:c r="B218" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17758,10 +17764,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D218" s="127" t="str">
-        <x:v>Duplicate side-effect prevention test</x:v>
+        <x:v>Crash-resume production test</x:v>
       </x:c>
       <x:c r="E218" s="127" t="str">
-        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
+        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
       </x:c>
       <x:c r="F218" s="127" t="str">
         <x:v>P0</x:v>
@@ -17775,7 +17781,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K218" s="127"/>
       <x:c r="L218" s="127"/>
@@ -17785,19 +17791,19 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="127" t="str">
-        <x:v>R-212</x:v>
+        <x:v>R-211</x:v>
       </x:c>
       <x:c r="B219" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C219" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D219" s="127" t="str">
-        <x:v>WebSocket replay correctness SLO</x:v>
+        <x:v>Duplicate side-effect prevention test</x:v>
       </x:c>
       <x:c r="E219" s="127" t="str">
-        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
+        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
       </x:c>
       <x:c r="F219" s="127" t="str">
         <x:v>P0</x:v>
@@ -17811,7 +17817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K219" s="127"/>
       <x:c r="L219" s="127"/>
@@ -17821,19 +17827,19 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="127" t="str">
-        <x:v>R-213</x:v>
+        <x:v>R-212</x:v>
       </x:c>
       <x:c r="B220" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C220" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D220" s="127" t="str">
-        <x:v>MCP isolation and prompt-injection test</x:v>
+        <x:v>WebSocket replay correctness SLO</x:v>
       </x:c>
       <x:c r="E220" s="127" t="str">
-        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
+        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
       </x:c>
       <x:c r="F220" s="127" t="str">
         <x:v>P0</x:v>
@@ -17847,7 +17853,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="K220" s="127"/>
       <x:c r="L220" s="127"/>
@@ -17857,7 +17863,7 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="127" t="str">
-        <x:v>R-214</x:v>
+        <x:v>R-213</x:v>
       </x:c>
       <x:c r="B221" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17866,10 +17872,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D221" s="127" t="str">
-        <x:v>Sandbox tenant isolation test</x:v>
+        <x:v>MCP isolation and prompt-injection test</x:v>
       </x:c>
       <x:c r="E221" s="127" t="str">
-        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
+        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
       </x:c>
       <x:c r="F221" s="127" t="str">
         <x:v>P0</x:v>
@@ -17883,7 +17889,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K221" s="127"/>
       <x:c r="L221" s="127"/>
@@ -17893,19 +17899,19 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="127" t="str">
-        <x:v>R-215</x:v>
+        <x:v>R-214</x:v>
       </x:c>
       <x:c r="B222" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C222" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D222" s="127" t="str">
-        <x:v>Runtime provider outage failover</x:v>
+        <x:v>Sandbox tenant isolation test</x:v>
       </x:c>
       <x:c r="E222" s="127" t="str">
-        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
+        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
       </x:c>
       <x:c r="F222" s="127" t="str">
         <x:v>P0</x:v>
@@ -17919,7 +17925,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K222" s="127"/>
       <x:c r="L222" s="127"/>
@@ -17929,19 +17935,19 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="127" t="str">
-        <x:v>R-216</x:v>
+        <x:v>R-215</x:v>
       </x:c>
       <x:c r="B223" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C223" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D223" s="127" t="str">
-        <x:v>Approval auditability test</x:v>
+        <x:v>Runtime provider outage failover</x:v>
       </x:c>
       <x:c r="E223" s="127" t="str">
-        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
+        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
       </x:c>
       <x:c r="F223" s="127" t="str">
         <x:v>P0</x:v>
@@ -17955,7 +17961,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="K223" s="127"/>
       <x:c r="L223" s="127"/>
@@ -17965,22 +17971,22 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="127" t="str">
-        <x:v>R-217</x:v>
+        <x:v>R-216</x:v>
       </x:c>
       <x:c r="B224" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C224" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D224" s="127" t="str">
-        <x:v>BaaS to custom migration test</x:v>
+        <x:v>Approval auditability test</x:v>
       </x:c>
       <x:c r="E224" s="127" t="str">
-        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
       </x:c>
       <x:c r="F224" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G224" s="127"/>
       <x:c r="H224" s="127" t="str">
@@ -17991,65 +17997,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K224" s="127"/>
       <x:c r="L224" s="127"/>
       <x:c r="M224" s="127" t="str">
-        <x:v>Avoid backend lock-in.</x:v>
+        <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" t="str">
-        <x:v>R-218</x:v>
-      </x:c>
-      <x:c r="B225" t="str">
+      <x:c r="A225" s="127" t="str">
+        <x:v>R-217</x:v>
+      </x:c>
+      <x:c r="B225" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C225" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="D225" t="str">
-        <x:v>Local Agent security lifecycle</x:v>
-      </x:c>
-      <x:c r="E225" t="str">
-        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
-      </x:c>
-      <x:c r="F225" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G225"/>
-      <x:c r="H225" t="str">
+      <x:c r="C225" s="127" t="str">
+        <x:v>Backend Strategy</x:v>
+      </x:c>
+      <x:c r="D225" s="127" t="str">
+        <x:v>BaaS to custom migration test</x:v>
+      </x:c>
+      <x:c r="E225" s="127" t="str">
+        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+      </x:c>
+      <x:c r="F225" s="127" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G225" s="127"/>
+      <x:c r="H225" s="127" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I225" t="n">
+      <x:c r="I225" s="390" t="n">
         <x:f>IF(H225="Done",1,IF(H225="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J225" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
-      </x:c>
-      <x:c r="K225"/>
-      <x:c r="L225"/>
-      <x:c r="M225" t="str">
-        <x:v>Production gate.</x:v>
+      <x:c r="J225" s="127" t="str">
+        <x:v>BaaS provider expansion</x:v>
+      </x:c>
+      <x:c r="K225" s="127"/>
+      <x:c r="L225" s="127"/>
+      <x:c r="M225" s="127" t="str">
+        <x:v>Avoid backend lock-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" t="str">
-        <x:v>R-219</x:v>
+        <x:v>R-218</x:v>
       </x:c>
       <x:c r="B226" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C226" t="str">
-        <x:v>Compliance</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D226" t="str">
-        <x:v>OSS license and SBOM gate</x:v>
+        <x:v>Local Agent security lifecycle</x:v>
       </x:c>
       <x:c r="E226" t="str">
-        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
       </x:c>
       <x:c r="F226" t="str">
         <x:v>P0</x:v>
@@ -18063,11 +18069,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J226" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K226"/>
       <x:c r="L226"/>
       <x:c r="M226" t="str">
+        <x:v>Production gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" t="str">
+        <x:v>R-219</x:v>
+      </x:c>
+      <x:c r="B227" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>Compliance</x:v>
+      </x:c>
+      <x:c r="D227" t="str">
+        <x:v>OSS license and SBOM gate</x:v>
+      </x:c>
+      <x:c r="E227" t="str">
+        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+      </x:c>
+      <x:c r="F227" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G227"/>
+      <x:c r="H227" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="I227" t="n">
+        <x:f>IF(H227="Done",1,IF(H227="In Progress",0.5,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J227" t="str">
+        <x:v>Open-source license review</x:v>
+      </x:c>
+      <x:c r="K227"/>
+      <x:c r="L227"/>
+      <x:c r="M227" t="str">
         <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
@@ -18076,7 +18118,7 @@
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H4:H115">
+  <x:conditionalFormatting sqref="H4:H116">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>H4="Done"</x:formula>
     </x:cfRule>
@@ -18091,34 +18133,34 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="10">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B115">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B116">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F115">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F116">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H115">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H116">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B116:B139">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B117:B140">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F116:F139">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F117:F140">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H116:H139">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H117:H140">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F140:F175">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F141:F176">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H140:H175">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H141:H176">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H224">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H225">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F224">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F225">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -10662,11 +10662,11 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-008</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation in progress on ai/R-009-usage-cost-accounting; usage/cost accounting records, price book, and ledger added; wired into the gateway; offline tests added; local_calls=0, cloud_calls=0.</x:v>
+        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2389,7 +2389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M116" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M117" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -2701,11 +2701,11 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"MVP")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"MVP")</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"MVP",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"MVP",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"MID",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"MID",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,7 +2746,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F6)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"ADVANCED",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"ADVANCED",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$227,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$227,"PRODUCTION",Phase_Roadmap!$H$4:$H$227,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"PRODUCTION",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F8)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$227,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -10641,7 +10641,7 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-009</x:v>
+        <x:v>R-220</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10650,10 +10650,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Usage and cost accounting</x:v>
+        <x:v>Cloud streaming (Server-Sent Events)</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
+        <x:v>Replace the single-event cloud stream wrapper with true incremental SSE streaming for OpenAI-compatible, Anthropic, and Gemini adapters; ordered delta events plus a final event with measured usage, reusing the HTTP-safety bounds.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
@@ -10662,28 +10662,28 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation in progress on ai/R-220-cloud-streaming; true SSE streaming added for OpenAI-compatible, Anthropic, and Gemini adapters; offline parser tests added; cloud_calls=0.</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 57, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10692,10 +10692,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>Cloud API-key provider adapters</x:v>
+        <x:v>Usage and cost accounting</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
+        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
@@ -10711,21 +10711,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10734,10 +10734,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>Balanced Model Gateway router</x:v>
+        <x:v>Cloud API-key provider adapters</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
+        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
@@ -10753,21 +10753,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
+        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10776,16 +10776,16 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>Loopback Ollama provider adapter</x:v>
+        <x:v>Balanced Model Gateway router</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
+        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G12" s="32" t="str">
-        <x:v>Codex</x:v>
+        <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H12" s="32" t="str">
         <x:v>Done</x:v>
@@ -10795,21 +10795,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10818,10 +10818,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
@@ -10837,33 +10837,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C14" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
@@ -10879,33 +10879,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K14" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L14" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M14" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C15" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
@@ -10921,33 +10921,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K15" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L15" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M15" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C16" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
@@ -10963,33 +10963,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J16" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K16" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L16" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M16" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C17" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
@@ -11005,53 +11005,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K17" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L17" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M17" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C18" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G18" s="32"/>
+      <x:c r="G18" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H18" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I18" s="376" t="n">
         <x:f>IF(H18="Done",1,IF(H18="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="32"/>
-      <x:c r="K18" s="32"/>
-      <x:c r="L18" s="32"/>
-      <x:c r="M18" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K18" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L18" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M18" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11060,10 +11070,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
@@ -11083,7 +11093,7 @@
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11092,10 +11102,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
@@ -11115,7 +11125,7 @@
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11124,10 +11134,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11147,7 +11157,7 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11156,10 +11166,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11179,7 +11189,7 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11188,10 +11198,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11211,19 +11221,19 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C24" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11243,7 +11253,7 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11252,10 +11262,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11275,19 +11285,19 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C26" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11307,7 +11317,7 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11316,10 +11326,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11339,19 +11349,19 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C28" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11371,19 +11381,19 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C29" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11403,7 +11413,7 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11412,10 +11422,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11435,19 +11445,19 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C31" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11467,7 +11477,7 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11476,10 +11486,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11499,7 +11509,7 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11508,10 +11518,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11531,19 +11541,19 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C34" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11563,7 +11573,7 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11572,10 +11582,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11595,7 +11605,7 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11604,10 +11614,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11627,7 +11637,7 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11636,10 +11646,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11659,7 +11669,7 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11668,10 +11678,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11691,19 +11701,19 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C39" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11723,7 +11733,7 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11732,10 +11742,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11755,19 +11765,19 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C41" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11787,7 +11797,7 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11796,10 +11806,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11819,19 +11829,19 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C43" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11851,19 +11861,19 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C44" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11883,19 +11893,19 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C45" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11915,7 +11925,7 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11924,10 +11934,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11947,7 +11957,7 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11956,10 +11966,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11979,7 +11989,7 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11988,10 +11998,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -12011,19 +12021,19 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C49" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12043,7 +12053,7 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12052,10 +12062,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12075,19 +12085,19 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C51" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12107,7 +12117,7 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12116,10 +12126,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12139,19 +12149,19 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C53" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12171,7 +12181,7 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12180,10 +12190,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12203,7 +12213,7 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12212,10 +12222,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12235,19 +12245,19 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C56" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
         <x:v>P0</x:v>
@@ -12267,7 +12277,7 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12276,10 +12286,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
         <x:v>P0</x:v>
@@ -12299,7 +12309,7 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12308,10 +12318,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
         <x:v>P0</x:v>
@@ -12331,19 +12341,19 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C59" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
         <x:v>P0</x:v>
@@ -12363,22 +12373,22 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C60" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G60" s="32"/>
       <x:c r="H60" s="32" t="str">
@@ -12395,7 +12405,7 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
         <x:v>MID</x:v>
@@ -12404,10 +12414,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
         <x:v>P1</x:v>
@@ -12427,19 +12437,19 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C62" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
         <x:v>P1</x:v>
@@ -12459,19 +12469,19 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C63" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12491,7 +12501,7 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
@@ -12500,10 +12510,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12523,19 +12533,19 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C65" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12555,19 +12565,19 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C66" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12587,19 +12597,19 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C67" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12619,7 +12629,7 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
@@ -12628,10 +12638,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12651,19 +12661,19 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C69" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12683,7 +12693,7 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
@@ -12692,10 +12702,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12715,7 +12725,7 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
@@ -12724,10 +12734,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12747,19 +12757,19 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C72" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12779,7 +12789,7 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
@@ -12788,10 +12798,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12811,19 +12821,19 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C74" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12843,19 +12853,19 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C75" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12875,19 +12885,19 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C76" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12907,19 +12917,19 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C77" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12939,7 +12949,7 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
@@ -12948,10 +12958,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12971,7 +12981,7 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
@@ -12980,10 +12990,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -13003,19 +13013,19 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C80" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -13035,7 +13045,7 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
         <x:v>MID</x:v>
@@ -13044,10 +13054,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
         <x:v>P1</x:v>
@@ -13067,19 +13077,19 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C82" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
         <x:v>P1</x:v>
@@ -13099,19 +13109,19 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C83" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
         <x:v>P1</x:v>
@@ -13131,19 +13141,19 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C84" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
         <x:v>P1</x:v>
@@ -13163,22 +13173,22 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C85" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G85" s="32"/>
       <x:c r="H85" s="32" t="str">
@@ -13195,7 +13205,7 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13204,13 +13214,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G86" s="32"/>
       <x:c r="H86" s="32" t="str">
@@ -13227,22 +13237,22 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C87" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G87" s="32"/>
       <x:c r="H87" s="32" t="str">
@@ -13259,7 +13269,7 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13268,10 +13278,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
         <x:v>P2</x:v>
@@ -13291,19 +13301,19 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C89" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
         <x:v>P2</x:v>
@@ -13323,19 +13333,19 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C90" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13355,19 +13365,19 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C91" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13387,7 +13397,7 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13396,10 +13406,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13419,19 +13429,19 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C93" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13451,7 +13461,7 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13460,10 +13470,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13483,7 +13493,7 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13492,10 +13502,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13515,19 +13525,19 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C96" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13547,7 +13557,7 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13556,10 +13566,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13579,19 +13589,19 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C98" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
         <x:v>P2</x:v>
@@ -13611,19 +13621,19 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C99" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
         <x:v>P2</x:v>
@@ -13643,7 +13653,7 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13652,10 +13662,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
         <x:v>P2</x:v>
@@ -13675,19 +13685,19 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-093</x:v>
+        <x:v>R-092</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C101" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>Quality trend analytics</x:v>
+        <x:v>Spot/preemptible optimization</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
+        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
         <x:v>P2</x:v>
@@ -13707,22 +13717,22 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-094</x:v>
+        <x:v>R-093</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C102" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>SLO/SLA framework</x:v>
+        <x:v>Quality trend analytics</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
+        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G102" s="32"/>
       <x:c r="H102" s="32" t="str">
@@ -13739,7 +13749,7 @@
     </x:row>
     <x:row r="103" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A103" s="32" t="str">
-        <x:v>R-095</x:v>
+        <x:v>R-094</x:v>
       </x:c>
       <x:c r="B103" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13748,10 +13758,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D103" s="32" t="str">
-        <x:v>HA control plane</x:v>
+        <x:v>SLO/SLA framework</x:v>
       </x:c>
       <x:c r="E103" s="32" t="str">
-        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
+        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
       </x:c>
       <x:c r="F103" s="32" t="str">
         <x:v>P0</x:v>
@@ -13771,7 +13781,7 @@
     </x:row>
     <x:row r="104" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A104" s="32" t="str">
-        <x:v>R-096</x:v>
+        <x:v>R-095</x:v>
       </x:c>
       <x:c r="B104" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13780,10 +13790,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D104" s="32" t="str">
-        <x:v>Backup + restore drills</x:v>
+        <x:v>HA control plane</x:v>
       </x:c>
       <x:c r="E104" s="32" t="str">
-        <x:v>Automated backups plus regularly tested restoration.</x:v>
+        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
       </x:c>
       <x:c r="F104" s="32" t="str">
         <x:v>P0</x:v>
@@ -13803,7 +13813,7 @@
     </x:row>
     <x:row r="105" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A105" s="32" t="str">
-        <x:v>R-097</x:v>
+        <x:v>R-096</x:v>
       </x:c>
       <x:c r="B105" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13812,10 +13822,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D105" s="32" t="str">
-        <x:v>Disaster recovery</x:v>
+        <x:v>Backup + restore drills</x:v>
       </x:c>
       <x:c r="E105" s="32" t="str">
-        <x:v>Document and exercise regional recovery procedures.</x:v>
+        <x:v>Automated backups plus regularly tested restoration.</x:v>
       </x:c>
       <x:c r="F105" s="32" t="str">
         <x:v>P0</x:v>
@@ -13835,19 +13845,19 @@
     </x:row>
     <x:row r="106" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A106" s="32" t="str">
-        <x:v>R-098</x:v>
+        <x:v>R-097</x:v>
       </x:c>
       <x:c r="B106" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C106" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D106" s="32" t="str">
-        <x:v>Independent penetration test</x:v>
+        <x:v>Disaster recovery</x:v>
       </x:c>
       <x:c r="E106" s="32" t="str">
-        <x:v>External security assessment before broad enterprise launch.</x:v>
+        <x:v>Document and exercise regional recovery procedures.</x:v>
       </x:c>
       <x:c r="F106" s="32" t="str">
         <x:v>P0</x:v>
@@ -13867,7 +13877,7 @@
     </x:row>
     <x:row r="107" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A107" s="32" t="str">
-        <x:v>R-099</x:v>
+        <x:v>R-098</x:v>
       </x:c>
       <x:c r="B107" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13876,10 +13886,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>SOC 2 readiness controls</x:v>
+        <x:v>Independent penetration test</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
-        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
+        <x:v>External security assessment before broad enterprise launch.</x:v>
       </x:c>
       <x:c r="F107" s="32" t="str">
         <x:v>P0</x:v>
@@ -13899,7 +13909,7 @@
     </x:row>
     <x:row r="108" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A108" s="32" t="str">
-        <x:v>R-100</x:v>
+        <x:v>R-099</x:v>
       </x:c>
       <x:c r="B108" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13908,10 +13918,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>Tenant isolation validation</x:v>
+        <x:v>SOC 2 readiness controls</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
-        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
+        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
       </x:c>
       <x:c r="F108" s="32" t="str">
         <x:v>P0</x:v>
@@ -13931,7 +13941,7 @@
     </x:row>
     <x:row r="109" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A109" s="32" t="str">
-        <x:v>R-101</x:v>
+        <x:v>R-100</x:v>
       </x:c>
       <x:c r="B109" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13940,10 +13950,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>Signing-key hardening</x:v>
+        <x:v>Tenant isolation validation</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
-        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
+        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
       </x:c>
       <x:c r="F109" s="32" t="str">
         <x:v>P0</x:v>
@@ -13963,19 +13973,19 @@
     </x:row>
     <x:row r="110" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A110" s="32" t="str">
-        <x:v>R-102</x:v>
+        <x:v>R-101</x:v>
       </x:c>
       <x:c r="B110" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C110" s="32" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>24x7 incident process</x:v>
+        <x:v>Signing-key hardening</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
-        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
+        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
       </x:c>
       <x:c r="F110" s="32" t="str">
         <x:v>P0</x:v>
@@ -13995,7 +14005,7 @@
     </x:row>
     <x:row r="111" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A111" s="32" t="str">
-        <x:v>R-103</x:v>
+        <x:v>R-102</x:v>
       </x:c>
       <x:c r="B111" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14004,10 +14014,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>Capacity/load tests</x:v>
+        <x:v>24x7 incident process</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
-        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
+        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
       </x:c>
       <x:c r="F111" s="32" t="str">
         <x:v>P0</x:v>
@@ -14027,7 +14037,7 @@
     </x:row>
     <x:row r="112" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A112" s="32" t="str">
-        <x:v>R-104</x:v>
+        <x:v>R-103</x:v>
       </x:c>
       <x:c r="B112" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14036,10 +14046,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Cost guardrails</x:v>
+        <x:v>Capacity/load tests</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
+        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
         <x:v>P0</x:v>
@@ -14059,19 +14069,19 @@
     </x:row>
     <x:row r="113" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A113" s="32" t="str">
-        <x:v>R-105</x:v>
+        <x:v>R-104</x:v>
       </x:c>
       <x:c r="B113" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C113" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Release qualification suite</x:v>
+        <x:v>Cost guardrails</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Full regression across supported stack versions before platform releases.</x:v>
+        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
         <x:v>P0</x:v>
@@ -14091,7 +14101,7 @@
     </x:row>
     <x:row r="114" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A114" s="32" t="str">
-        <x:v>R-106</x:v>
+        <x:v>R-105</x:v>
       </x:c>
       <x:c r="B114" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14100,10 +14110,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D114" s="32" t="str">
-        <x:v>Canary platform releases</x:v>
+        <x:v>Release qualification suite</x:v>
       </x:c>
       <x:c r="E114" s="32" t="str">
-        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
+        <x:v>Full regression across supported stack versions before platform releases.</x:v>
       </x:c>
       <x:c r="F114" s="32" t="str">
         <x:v>P0</x:v>
@@ -14123,19 +14133,19 @@
     </x:row>
     <x:row r="115" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A115" s="32" t="str">
-        <x:v>R-107</x:v>
+        <x:v>R-106</x:v>
       </x:c>
       <x:c r="B115" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C115" s="32" t="str">
-        <x:v>Support</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D115" s="32" t="str">
-        <x:v>Support tooling</x:v>
+        <x:v>Canary platform releases</x:v>
       </x:c>
       <x:c r="E115" s="32" t="str">
-        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
+        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
       </x:c>
       <x:c r="F115" s="32" t="str">
         <x:v>P0</x:v>
@@ -14155,19 +14165,19 @@
     </x:row>
     <x:row r="116" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A116" s="32" t="str">
-        <x:v>R-108</x:v>
+        <x:v>R-107</x:v>
       </x:c>
       <x:c r="B116" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C116" s="32" t="str">
-        <x:v>Legal/Privacy</x:v>
+        <x:v>Support</x:v>
       </x:c>
       <x:c r="D116" s="32" t="str">
-        <x:v>Privacy + retention controls</x:v>
+        <x:v>Support tooling</x:v>
       </x:c>
       <x:c r="E116" s="32" t="str">
-        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
       </x:c>
       <x:c r="F116" s="32" t="str">
         <x:v>P0</x:v>
@@ -14185,2154 +14195,2152 @@
       <x:c r="L116" s="32"/>
       <x:c r="M116" s="32"/>
     </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="43" t="str">
-        <x:v>R-109</x:v>
-      </x:c>
-      <x:c r="B117" s="43" t="str">
+    <x:row r="117" s="40" customFormat="1" ht="34" customHeight="1">
+      <x:c r="A117" s="32" t="str">
+        <x:v>R-108</x:v>
+      </x:c>
+      <x:c r="B117" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C117" s="43" t="str">
-        <x:v>Business</x:v>
-      </x:c>
-      <x:c r="D117" s="43" t="str">
-        <x:v>Plan entitlements</x:v>
-      </x:c>
-      <x:c r="E117" s="43" t="str">
-        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
-      </x:c>
-      <x:c r="F117" s="43" t="str">
+      <x:c r="C117" s="32" t="str">
+        <x:v>Legal/Privacy</x:v>
+      </x:c>
+      <x:c r="D117" s="32" t="str">
+        <x:v>Privacy + retention controls</x:v>
+      </x:c>
+      <x:c r="E117" s="32" t="str">
+        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+      </x:c>
+      <x:c r="F117" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G117" s="43"/>
-      <x:c r="H117" s="43" t="str">
+      <x:c r="G117" s="32"/>
+      <x:c r="H117" s="32" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I117" s="386" t="n">
+      <x:c r="I117" s="376" t="n">
         <x:f>IF(H117="Done",1,IF(H117="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J117" s="43"/>
-      <x:c r="K117" s="43"/>
-      <x:c r="L117" s="43"/>
-      <x:c r="M117" s="43"/>
+      <x:c r="J117" s="32"/>
+      <x:c r="K117" s="32"/>
+      <x:c r="L117" s="32"/>
+      <x:c r="M117" s="32"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="42" t="str">
-        <x:v>R-110</x:v>
-      </x:c>
-      <x:c r="B118" s="42" t="str">
+      <x:c r="A118" s="43" t="str">
+        <x:v>R-109</x:v>
+      </x:c>
+      <x:c r="B118" s="43" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C118" s="42" t="str">
+      <x:c r="C118" s="43" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="D118" s="42" t="str">
-        <x:v>Unit economics dashboard</x:v>
-      </x:c>
-      <x:c r="E118" s="42" t="str">
-        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
-      </x:c>
-      <x:c r="F118" s="42" t="str">
+      <x:c r="D118" s="43" t="str">
+        <x:v>Plan entitlements</x:v>
+      </x:c>
+      <x:c r="E118" s="43" t="str">
+        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
+      </x:c>
+      <x:c r="F118" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G118" s="42"/>
-      <x:c r="H118" s="42" t="str">
+      <x:c r="G118" s="43"/>
+      <x:c r="H118" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I118" s="387" t="n">
+      <x:c r="I118" s="386" t="n">
         <x:f>IF(H118="Done",1,IF(H118="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J118" s="42"/>
-      <x:c r="K118" s="42"/>
-      <x:c r="L118" s="42"/>
-      <x:c r="M118" s="42"/>
+      <x:c r="J118" s="43"/>
+      <x:c r="K118" s="43"/>
+      <x:c r="L118" s="43"/>
+      <x:c r="M118" s="43"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="43" t="str">
-        <x:v>R-111</x:v>
-      </x:c>
-      <x:c r="B119" s="43" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C119" s="43" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D119" s="43" t="str">
-        <x:v>Cross-platform Mobile Agent</x:v>
-      </x:c>
-      <x:c r="E119" s="43" t="str">
-        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
-      </x:c>
-      <x:c r="F119" s="43" t="str">
+      <x:c r="A119" s="42" t="str">
+        <x:v>R-110</x:v>
+      </x:c>
+      <x:c r="B119" s="42" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C119" s="42" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="D119" s="42" t="str">
+        <x:v>Unit economics dashboard</x:v>
+      </x:c>
+      <x:c r="E119" s="42" t="str">
+        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
+      </x:c>
+      <x:c r="F119" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G119" s="43"/>
-      <x:c r="H119" s="43" t="str">
+      <x:c r="G119" s="42"/>
+      <x:c r="H119" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I119" s="386" t="n">
+      <x:c r="I119" s="387" t="n">
         <x:f>IF(H119="Done",1,IF(H119="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J119" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K119" s="43"/>
-      <x:c r="L119" s="43"/>
-      <x:c r="M119" s="43"/>
+      <x:c r="J119" s="42"/>
+      <x:c r="K119" s="42"/>
+      <x:c r="L119" s="42"/>
+      <x:c r="M119" s="42"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="42" t="str">
-        <x:v>R-112</x:v>
-      </x:c>
-      <x:c r="B120" s="42" t="str">
+      <x:c r="A120" s="43" t="str">
+        <x:v>R-111</x:v>
+      </x:c>
+      <x:c r="B120" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C120" s="42" t="str">
+      <x:c r="C120" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D120" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="E120" s="42" t="str">
-        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
-      </x:c>
-      <x:c r="F120" s="42" t="str">
+      <x:c r="D120" s="43" t="str">
+        <x:v>Cross-platform Mobile Agent</x:v>
+      </x:c>
+      <x:c r="E120" s="43" t="str">
+        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
+      </x:c>
+      <x:c r="F120" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G120" s="42"/>
-      <x:c r="H120" s="42" t="str">
+      <x:c r="G120" s="43"/>
+      <x:c r="H120" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I120" s="387" t="n">
+      <x:c r="I120" s="386" t="n">
         <x:f>IF(H120="Done",1,IF(H120="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="42" t="str">
-        <x:v>Requirement specification step</x:v>
-      </x:c>
-      <x:c r="K120" s="42"/>
-      <x:c r="L120" s="42"/>
-      <x:c r="M120" s="42"/>
+      <x:c r="J120" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K120" s="43"/>
+      <x:c r="L120" s="43"/>
+      <x:c r="M120" s="43"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="43" t="str">
-        <x:v>R-113</x:v>
-      </x:c>
-      <x:c r="B121" s="43" t="str">
+      <x:c r="A121" s="42" t="str">
+        <x:v>R-112</x:v>
+      </x:c>
+      <x:c r="B121" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C121" s="43" t="str">
+      <x:c r="C121" s="42" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D121" s="43" t="str">
-        <x:v>Auto / Recommended project mode</x:v>
-      </x:c>
-      <x:c r="E121" s="43" t="str">
-        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
-      </x:c>
-      <x:c r="F121" s="43" t="str">
+      <x:c r="D121" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="E121" s="42" t="str">
+        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
+      </x:c>
+      <x:c r="F121" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G121" s="43"/>
-      <x:c r="H121" s="43" t="str">
+      <x:c r="G121" s="42"/>
+      <x:c r="H121" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I121" s="386" t="n">
+      <x:c r="I121" s="387" t="n">
         <x:f>IF(H121="Done",1,IF(H121="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K121" s="43"/>
-      <x:c r="L121" s="43"/>
-      <x:c r="M121" s="43"/>
+      <x:c r="J121" s="42" t="str">
+        <x:v>Requirement specification step</x:v>
+      </x:c>
+      <x:c r="K121" s="42"/>
+      <x:c r="L121" s="42"/>
+      <x:c r="M121" s="42"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="42" t="str">
-        <x:v>R-114</x:v>
-      </x:c>
-      <x:c r="B122" s="42" t="str">
+      <x:c r="A122" s="43" t="str">
+        <x:v>R-113</x:v>
+      </x:c>
+      <x:c r="B122" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C122" s="42" t="str">
+      <x:c r="C122" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D122" s="42" t="str">
-        <x:v>Manual framework override</x:v>
-      </x:c>
-      <x:c r="E122" s="42" t="str">
-        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
-      </x:c>
-      <x:c r="F122" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G122" s="42"/>
-      <x:c r="H122" s="42" t="str">
+      <x:c r="D122" s="43" t="str">
+        <x:v>Auto / Recommended project mode</x:v>
+      </x:c>
+      <x:c r="E122" s="43" t="str">
+        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
+      </x:c>
+      <x:c r="F122" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G122" s="43"/>
+      <x:c r="H122" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I122" s="387" t="n">
+      <x:c r="I122" s="386" t="n">
         <x:f>IF(H122="Done",1,IF(H122="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="42" t="str">
+      <x:c r="J122" s="43" t="str">
         <x:v>Framework recommendation engine</x:v>
       </x:c>
-      <x:c r="K122" s="42"/>
-      <x:c r="L122" s="42"/>
-      <x:c r="M122" s="42"/>
+      <x:c r="K122" s="43"/>
+      <x:c r="L122" s="43"/>
+      <x:c r="M122" s="43"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="43" t="str">
-        <x:v>R-115</x:v>
-      </x:c>
-      <x:c r="B123" s="43" t="str">
+      <x:c r="A123" s="42" t="str">
+        <x:v>R-114</x:v>
+      </x:c>
+      <x:c r="B123" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C123" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D123" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="E123" s="43" t="str">
-        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
-      </x:c>
-      <x:c r="F123" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G123" s="43"/>
-      <x:c r="H123" s="43" t="str">
+      <x:c r="C123" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D123" s="42" t="str">
+        <x:v>Manual framework override</x:v>
+      </x:c>
+      <x:c r="E123" s="42" t="str">
+        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
+      </x:c>
+      <x:c r="F123" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G123" s="42"/>
+      <x:c r="H123" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I123" s="386" t="n">
+      <x:c r="I123" s="387" t="n">
         <x:f>IF(H123="Done",1,IF(H123="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J123" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K123" s="43"/>
-      <x:c r="L123" s="43"/>
-      <x:c r="M123" s="43"/>
+      <x:c r="J123" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K123" s="42"/>
+      <x:c r="L123" s="42"/>
+      <x:c r="M123" s="42"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="42" t="str">
-        <x:v>R-116</x:v>
-      </x:c>
-      <x:c r="B124" s="42" t="str">
+      <x:c r="A124" s="43" t="str">
+        <x:v>R-115</x:v>
+      </x:c>
+      <x:c r="B124" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C124" s="42" t="str">
+      <x:c r="C124" s="43" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D124" s="42" t="str">
-        <x:v>Shared-code policy</x:v>
-      </x:c>
-      <x:c r="E124" s="42" t="str">
-        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
-      </x:c>
-      <x:c r="F124" s="42" t="str">
+      <x:c r="D124" s="43" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="E124" s="43" t="str">
+        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
+      </x:c>
+      <x:c r="F124" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G124" s="42"/>
-      <x:c r="H124" s="42" t="str">
+      <x:c r="G124" s="43"/>
+      <x:c r="H124" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I124" s="387" t="n">
+      <x:c r="I124" s="386" t="n">
         <x:f>IF(H124="Done",1,IF(H124="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K124" s="42"/>
-      <x:c r="L124" s="42"/>
-      <x:c r="M124" s="42"/>
+      <x:c r="J124" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K124" s="43"/>
+      <x:c r="L124" s="43"/>
+      <x:c r="M124" s="43"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="43" t="str">
-        <x:v>R-117</x:v>
-      </x:c>
-      <x:c r="B125" s="43" t="str">
+      <x:c r="A125" s="42" t="str">
+        <x:v>R-116</x:v>
+      </x:c>
+      <x:c r="B125" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C125" s="43" t="str">
-        <x:v>Web/Admin</x:v>
-      </x:c>
-      <x:c r="D125" s="43" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="E125" s="43" t="str">
-        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
-      </x:c>
-      <x:c r="F125" s="43" t="str">
+      <x:c r="C125" s="42" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D125" s="42" t="str">
+        <x:v>Shared-code policy</x:v>
+      </x:c>
+      <x:c r="E125" s="42" t="str">
+        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
+      </x:c>
+      <x:c r="F125" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G125" s="43"/>
-      <x:c r="H125" s="43" t="str">
+      <x:c r="G125" s="42"/>
+      <x:c r="H125" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I125" s="386" t="n">
+      <x:c r="I125" s="387" t="n">
         <x:f>IF(H125="Done",1,IF(H125="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J125" s="43" t="str">
-        <x:v>Web/Admin Agent</x:v>
-      </x:c>
-      <x:c r="K125" s="43"/>
-      <x:c r="L125" s="43"/>
-      <x:c r="M125" s="43"/>
+      <x:c r="J125" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K125" s="42"/>
+      <x:c r="L125" s="42"/>
+      <x:c r="M125" s="42"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="42" t="str">
-        <x:v>R-118</x:v>
-      </x:c>
-      <x:c r="B126" s="42" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C126" s="42" t="str">
+      <x:c r="A126" s="43" t="str">
+        <x:v>R-117</x:v>
+      </x:c>
+      <x:c r="B126" s="43" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C126" s="43" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D126" s="42" t="str">
-        <x:v>Flutter Web optional profile</x:v>
-      </x:c>
-      <x:c r="E126" s="42" t="str">
-        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
-      </x:c>
-      <x:c r="F126" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G126" s="42"/>
-      <x:c r="H126" s="42" t="str">
+      <x:c r="D126" s="43" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="E126" s="43" t="str">
+        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
+      </x:c>
+      <x:c r="F126" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G126" s="43"/>
+      <x:c r="H126" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I126" s="387" t="n">
+      <x:c r="I126" s="386" t="n">
         <x:f>IF(H126="Done",1,IF(H126="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="42" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
-      </x:c>
-      <x:c r="K126" s="42"/>
-      <x:c r="L126" s="42"/>
-      <x:c r="M126" s="42"/>
+      <x:c r="J126" s="43" t="str">
+        <x:v>Web/Admin Agent</x:v>
+      </x:c>
+      <x:c r="K126" s="43"/>
+      <x:c r="L126" s="43"/>
+      <x:c r="M126" s="43"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="43" t="str">
-        <x:v>R-119</x:v>
-      </x:c>
-      <x:c r="B127" s="43" t="str">
+      <x:c r="A127" s="42" t="str">
+        <x:v>R-118</x:v>
+      </x:c>
+      <x:c r="B127" s="42" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C127" s="43" t="str">
+      <x:c r="C127" s="42" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D127" s="43" t="str">
-        <x:v>React Native Web optional profile</x:v>
-      </x:c>
-      <x:c r="E127" s="43" t="str">
-        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
-      </x:c>
-      <x:c r="F127" s="43" t="str">
+      <x:c r="D127" s="42" t="str">
+        <x:v>Flutter Web optional profile</x:v>
+      </x:c>
+      <x:c r="E127" s="42" t="str">
+        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
+      </x:c>
+      <x:c r="F127" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G127" s="43"/>
-      <x:c r="H127" s="43" t="str">
+      <x:c r="G127" s="42"/>
+      <x:c r="H127" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I127" s="386" t="n">
+      <x:c r="I127" s="387" t="n">
         <x:f>IF(H127="Done",1,IF(H127="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J127" s="43" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
-      </x:c>
-      <x:c r="K127" s="43"/>
-      <x:c r="L127" s="43"/>
-      <x:c r="M127" s="43"/>
+      <x:c r="J127" s="42" t="str">
+        <x:v>Flutter target (GA baseline)</x:v>
+      </x:c>
+      <x:c r="K127" s="42"/>
+      <x:c r="L127" s="42"/>
+      <x:c r="M127" s="42"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="42" t="str">
-        <x:v>R-120</x:v>
-      </x:c>
-      <x:c r="B128" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C128" s="42" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D128" s="42" t="str">
-        <x:v>Native recommendation profile</x:v>
-      </x:c>
-      <x:c r="E128" s="42" t="str">
-        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
-      </x:c>
-      <x:c r="F128" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G128" s="42"/>
-      <x:c r="H128" s="42" t="str">
+      <x:c r="A128" s="43" t="str">
+        <x:v>R-119</x:v>
+      </x:c>
+      <x:c r="B128" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C128" s="43" t="str">
+        <x:v>Web/Admin</x:v>
+      </x:c>
+      <x:c r="D128" s="43" t="str">
+        <x:v>React Native Web optional profile</x:v>
+      </x:c>
+      <x:c r="E128" s="43" t="str">
+        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
+      </x:c>
+      <x:c r="F128" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G128" s="43"/>
+      <x:c r="H128" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I128" s="387" t="n">
+      <x:c r="I128" s="386" t="n">
         <x:f>IF(H128="Done",1,IF(H128="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K128" s="42"/>
-      <x:c r="L128" s="42"/>
-      <x:c r="M128" s="42"/>
+      <x:c r="J128" s="43" t="str">
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
+      </x:c>
+      <x:c r="K128" s="43"/>
+      <x:c r="L128" s="43"/>
+      <x:c r="M128" s="43"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="43" t="str">
-        <x:v>R-121</x:v>
-      </x:c>
-      <x:c r="B129" s="43" t="str">
+      <x:c r="A129" s="42" t="str">
+        <x:v>R-120</x:v>
+      </x:c>
+      <x:c r="B129" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C129" s="43" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D129" s="43" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="E129" s="43" t="str">
-        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
-      </x:c>
-      <x:c r="F129" s="43" t="str">
+      <x:c r="C129" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D129" s="42" t="str">
+        <x:v>Native recommendation profile</x:v>
+      </x:c>
+      <x:c r="E129" s="42" t="str">
+        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
+      </x:c>
+      <x:c r="F129" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G129" s="43"/>
-      <x:c r="H129" s="43" t="str">
+      <x:c r="G129" s="42"/>
+      <x:c r="H129" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I129" s="386" t="n">
+      <x:c r="I129" s="387" t="n">
         <x:f>IF(H129="Done",1,IF(H129="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J129" s="43" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K129" s="43"/>
-      <x:c r="L129" s="43"/>
-      <x:c r="M129" s="43"/>
+      <x:c r="J129" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K129" s="42"/>
+      <x:c r="L129" s="42"/>
+      <x:c r="M129" s="42"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="42" t="str">
-        <x:v>R-122</x:v>
-      </x:c>
-      <x:c r="B130" s="42" t="str">
+      <x:c r="A130" s="43" t="str">
+        <x:v>R-121</x:v>
+      </x:c>
+      <x:c r="B130" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C130" s="42" t="str">
+      <x:c r="C130" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D130" s="42" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="E130" s="42" t="str">
-        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
-      </x:c>
-      <x:c r="F130" s="42" t="str">
+      <x:c r="D130" s="43" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="E130" s="43" t="str">
+        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
+      </x:c>
+      <x:c r="F130" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G130" s="42"/>
-      <x:c r="H130" s="42" t="str">
+      <x:c r="G130" s="43"/>
+      <x:c r="H130" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I130" s="387" t="n">
+      <x:c r="I130" s="386" t="n">
         <x:f>IF(H130="Done",1,IF(H130="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J130" s="42" t="str">
+      <x:c r="J130" s="43" t="str">
         <x:v>Project + workspace model</x:v>
       </x:c>
-      <x:c r="K130" s="42"/>
-      <x:c r="L130" s="42"/>
-      <x:c r="M130" s="42"/>
+      <x:c r="K130" s="43"/>
+      <x:c r="L130" s="43"/>
+      <x:c r="M130" s="43"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="43" t="str">
-        <x:v>R-123</x:v>
-      </x:c>
-      <x:c r="B131" s="43" t="str">
+      <x:c r="A131" s="42" t="str">
+        <x:v>R-122</x:v>
+      </x:c>
+      <x:c r="B131" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C131" s="43" t="str">
+      <x:c r="C131" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D131" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="E131" s="43" t="str">
-        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
-      </x:c>
-      <x:c r="F131" s="43" t="str">
+      <x:c r="D131" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="E131" s="42" t="str">
+        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
+      </x:c>
+      <x:c r="F131" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G131" s="43"/>
-      <x:c r="H131" s="43" t="str">
+      <x:c r="G131" s="42"/>
+      <x:c r="H131" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I131" s="386" t="n">
+      <x:c r="I131" s="387" t="n">
         <x:f>IF(H131="Done",1,IF(H131="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J131" s="43" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="K131" s="43"/>
-      <x:c r="L131" s="43"/>
-      <x:c r="M131" s="43"/>
+      <x:c r="J131" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K131" s="42"/>
+      <x:c r="L131" s="42"/>
+      <x:c r="M131" s="42"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="42" t="str">
-        <x:v>R-124</x:v>
-      </x:c>
-      <x:c r="B132" s="42" t="str">
+      <x:c r="A132" s="43" t="str">
+        <x:v>R-123</x:v>
+      </x:c>
+      <x:c r="B132" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C132" s="42" t="str">
+      <x:c r="C132" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D132" s="42" t="str">
-        <x:v>Repository naming convention</x:v>
-      </x:c>
-      <x:c r="E132" s="42" t="str">
-        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
-      </x:c>
-      <x:c r="F132" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G132" s="42"/>
-      <x:c r="H132" s="42" t="str">
+      <x:c r="D132" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="E132" s="43" t="str">
+        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
+      </x:c>
+      <x:c r="F132" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G132" s="43"/>
+      <x:c r="H132" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I132" s="387" t="n">
+      <x:c r="I132" s="386" t="n">
         <x:f>IF(H132="Done",1,IF(H132="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J132" s="42" t="str">
+      <x:c r="J132" s="43" t="str">
         <x:v>One Git repo per customer project</x:v>
       </x:c>
-      <x:c r="K132" s="42"/>
-      <x:c r="L132" s="42"/>
-      <x:c r="M132" s="42"/>
+      <x:c r="K132" s="43"/>
+      <x:c r="L132" s="43"/>
+      <x:c r="M132" s="43"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="43" t="str">
-        <x:v>R-125</x:v>
-      </x:c>
-      <x:c r="B133" s="43" t="str">
+      <x:c r="A133" s="42" t="str">
+        <x:v>R-124</x:v>
+      </x:c>
+      <x:c r="B133" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C133" s="43" t="str">
+      <x:c r="C133" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D133" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="E133" s="43" t="str">
-        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
-      </x:c>
-      <x:c r="F133" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G133" s="43"/>
-      <x:c r="H133" s="43" t="str">
+      <x:c r="D133" s="42" t="str">
+        <x:v>Repository naming convention</x:v>
+      </x:c>
+      <x:c r="E133" s="42" t="str">
+        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
+      </x:c>
+      <x:c r="F133" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G133" s="42"/>
+      <x:c r="H133" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I133" s="386" t="n">
+      <x:c r="I133" s="387" t="n">
         <x:f>IF(H133="Done",1,IF(H133="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J133" s="43" t="str">
-        <x:v>Branch per task</x:v>
-      </x:c>
-      <x:c r="K133" s="43"/>
-      <x:c r="L133" s="43"/>
-      <x:c r="M133" s="43"/>
+      <x:c r="J133" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="K133" s="42"/>
+      <x:c r="L133" s="42"/>
+      <x:c r="M133" s="42"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="42" t="str">
-        <x:v>R-126</x:v>
-      </x:c>
-      <x:c r="B134" s="42" t="str">
+      <x:c r="A134" s="43" t="str">
+        <x:v>R-125</x:v>
+      </x:c>
+      <x:c r="B134" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C134" s="42" t="str">
-        <x:v>Product Foundation</x:v>
-      </x:c>
-      <x:c r="D134" s="42" t="str">
-        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
-      </x:c>
-      <x:c r="E134" s="42" t="str">
-        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
-      </x:c>
-      <x:c r="F134" s="42" t="str">
+      <x:c r="C134" s="43" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D134" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="E134" s="43" t="str">
+        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
+      </x:c>
+      <x:c r="F134" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G134" s="42"/>
-      <x:c r="H134" s="42" t="str">
+      <x:c r="G134" s="43"/>
+      <x:c r="H134" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I134" s="387" t="n">
+      <x:c r="I134" s="386" t="n">
         <x:f>IF(H134="Done",1,IF(H134="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J134" s="42" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K134" s="42"/>
-      <x:c r="L134" s="42"/>
-      <x:c r="M134" s="42"/>
+      <x:c r="J134" s="43" t="str">
+        <x:v>Branch per task</x:v>
+      </x:c>
+      <x:c r="K134" s="43"/>
+      <x:c r="L134" s="43"/>
+      <x:c r="M134" s="43"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="43" t="str">
-        <x:v>R-127</x:v>
-      </x:c>
-      <x:c r="B135" s="43" t="str">
+      <x:c r="A135" s="42" t="str">
+        <x:v>R-126</x:v>
+      </x:c>
+      <x:c r="B135" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C135" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D135" s="43" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="E135" s="43" t="str">
-        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
-      </x:c>
-      <x:c r="F135" s="43" t="str">
+      <x:c r="C135" s="42" t="str">
+        <x:v>Product Foundation</x:v>
+      </x:c>
+      <x:c r="D135" s="42" t="str">
+        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
+      </x:c>
+      <x:c r="E135" s="42" t="str">
+        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
+      </x:c>
+      <x:c r="F135" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G135" s="43"/>
-      <x:c r="H135" s="43" t="str">
+      <x:c r="G135" s="42"/>
+      <x:c r="H135" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I135" s="386" t="n">
+      <x:c r="I135" s="387" t="n">
         <x:f>IF(H135="Done",1,IF(H135="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J135" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K135" s="43"/>
-      <x:c r="L135" s="43"/>
-      <x:c r="M135" s="43"/>
+      <x:c r="J135" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K135" s="42"/>
+      <x:c r="L135" s="42"/>
+      <x:c r="M135" s="42"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="42" t="str">
-        <x:v>R-128</x:v>
-      </x:c>
-      <x:c r="B136" s="42" t="str">
+      <x:c r="A136" s="43" t="str">
+        <x:v>R-127</x:v>
+      </x:c>
+      <x:c r="B136" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C136" s="42" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D136" s="42" t="str">
-        <x:v>Cross-language monorepo orchestration</x:v>
-      </x:c>
-      <x:c r="E136" s="42" t="str">
-        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
-      </x:c>
-      <x:c r="F136" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G136" s="42"/>
-      <x:c r="H136" s="42" t="str">
+      <x:c r="C136" s="43" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D136" s="43" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="E136" s="43" t="str">
+        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
+      </x:c>
+      <x:c r="F136" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G136" s="43"/>
+      <x:c r="H136" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I136" s="387" t="n">
+      <x:c r="I136" s="386" t="n">
         <x:f>IF(H136="Done",1,IF(H136="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J136" s="42" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K136" s="42"/>
-      <x:c r="L136" s="42"/>
-      <x:c r="M136" s="42"/>
+      <x:c r="J136" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K136" s="43"/>
+      <x:c r="L136" s="43"/>
+      <x:c r="M136" s="43"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="43" t="str">
-        <x:v>R-129</x:v>
-      </x:c>
-      <x:c r="B137" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C137" s="43" t="str">
+      <x:c r="A137" s="42" t="str">
+        <x:v>R-128</x:v>
+      </x:c>
+      <x:c r="B137" s="42" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C137" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D137" s="43" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="E137" s="43" t="str">
-        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
-      </x:c>
-      <x:c r="F137" s="43" t="str">
+      <x:c r="D137" s="42" t="str">
+        <x:v>Cross-language monorepo orchestration</x:v>
+      </x:c>
+      <x:c r="E137" s="42" t="str">
+        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
+      </x:c>
+      <x:c r="F137" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G137" s="43"/>
-      <x:c r="H137" s="43" t="str">
+      <x:c r="G137" s="42"/>
+      <x:c r="H137" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I137" s="386" t="n">
+      <x:c r="I137" s="387" t="n">
         <x:f>IF(H137="Done",1,IF(H137="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J137" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K137" s="43"/>
-      <x:c r="L137" s="43"/>
-      <x:c r="M137" s="43"/>
+      <x:c r="J137" s="42" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K137" s="42"/>
+      <x:c r="L137" s="42"/>
+      <x:c r="M137" s="42"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="42" t="str">
-        <x:v>R-130</x:v>
-      </x:c>
-      <x:c r="B138" s="42" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C138" s="42" t="str">
+      <x:c r="A138" s="43" t="str">
+        <x:v>R-129</x:v>
+      </x:c>
+      <x:c r="B138" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C138" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D138" s="42" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="E138" s="42" t="str">
-        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
-      </x:c>
-      <x:c r="F138" s="42" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G138" s="42"/>
-      <x:c r="H138" s="42" t="str">
+      <x:c r="D138" s="43" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="E138" s="43" t="str">
+        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
+      </x:c>
+      <x:c r="F138" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G138" s="43"/>
+      <x:c r="H138" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I138" s="387" t="n">
+      <x:c r="I138" s="386" t="n">
         <x:f>IF(H138="Done",1,IF(H138="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J138" s="42" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="K138" s="42"/>
-      <x:c r="L138" s="42"/>
-      <x:c r="M138" s="42"/>
+      <x:c r="J138" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K138" s="43"/>
+      <x:c r="L138" s="43"/>
+      <x:c r="M138" s="43"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="43" t="str">
-        <x:v>R-131</x:v>
-      </x:c>
-      <x:c r="B139" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C139" s="43" t="str">
+      <x:c r="A139" s="42" t="str">
+        <x:v>R-130</x:v>
+      </x:c>
+      <x:c r="B139" s="42" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C139" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D139" s="43" t="str">
-        <x:v>CODEOWNERS + protected paths</x:v>
-      </x:c>
-      <x:c r="E139" s="43" t="str">
-        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
-      </x:c>
-      <x:c r="F139" s="43" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G139" s="43"/>
-      <x:c r="H139" s="43" t="str">
+      <x:c r="D139" s="42" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="E139" s="42" t="str">
+        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
+      </x:c>
+      <x:c r="F139" s="42" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G139" s="42"/>
+      <x:c r="H139" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I139" s="386" t="n">
+      <x:c r="I139" s="387" t="n">
         <x:f>IF(H139="Done",1,IF(H139="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J139" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="K139" s="43"/>
-      <x:c r="L139" s="43"/>
-      <x:c r="M139" s="43"/>
+      <x:c r="J139" s="42" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="K139" s="42"/>
+      <x:c r="L139" s="42"/>
+      <x:c r="M139" s="42"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="42" t="str">
-        <x:v>R-132</x:v>
-      </x:c>
-      <x:c r="B140" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C140" s="42" t="str">
+      <x:c r="A140" s="43" t="str">
+        <x:v>R-131</x:v>
+      </x:c>
+      <x:c r="B140" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C140" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D140" s="42" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="E140" s="42" t="str">
-        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
-      </x:c>
-      <x:c r="F140" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G140" s="42"/>
-      <x:c r="H140" s="42" t="str">
+      <x:c r="D140" s="43" t="str">
+        <x:v>CODEOWNERS + protected paths</x:v>
+      </x:c>
+      <x:c r="E140" s="43" t="str">
+        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
+      </x:c>
+      <x:c r="F140" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G140" s="43"/>
+      <x:c r="H140" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I140" s="387" t="n">
+      <x:c r="I140" s="386" t="n">
         <x:f>IF(H140="Done",1,IF(H140="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J140" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K140" s="42"/>
-      <x:c r="L140" s="42"/>
-      <x:c r="M140" s="42"/>
+      <x:c r="J140" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="K140" s="43"/>
+      <x:c r="L140" s="43"/>
+      <x:c r="M140" s="43"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="66" t="str">
-        <x:v>R-133</x:v>
-      </x:c>
-      <x:c r="B141" s="66" t="str">
+      <x:c r="A141" s="42" t="str">
+        <x:v>R-132</x:v>
+      </x:c>
+      <x:c r="B141" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C141" s="66" t="str">
-        <x:v>Change Safety</x:v>
-      </x:c>
-      <x:c r="D141" s="66" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="E141" s="66" t="str">
-        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
-      </x:c>
-      <x:c r="F141" s="66" t="str">
+      <x:c r="C141" s="42" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D141" s="42" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="E141" s="42" t="str">
+        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
+      </x:c>
+      <x:c r="F141" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G141" s="66"/>
-      <x:c r="H141" s="66" t="str">
+      <x:c r="G141" s="42"/>
+      <x:c r="H141" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I141" s="388" t="n">
+      <x:c r="I141" s="387" t="n">
         <x:f>IF(H141="Done",1,IF(H141="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J141" s="66" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K141" s="66"/>
-      <x:c r="L141" s="66"/>
-      <x:c r="M141" s="66"/>
+      <x:c r="J141" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K141" s="42"/>
+      <x:c r="L141" s="42"/>
+      <x:c r="M141" s="42"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="65" t="str">
-        <x:v>R-134</x:v>
-      </x:c>
-      <x:c r="B142" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C142" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D142" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="E142" s="65" t="str">
-        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
-      </x:c>
-      <x:c r="F142" s="65" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G142" s="65"/>
-      <x:c r="H142" s="65" t="str">
+      <x:c r="A142" s="66" t="str">
+        <x:v>R-133</x:v>
+      </x:c>
+      <x:c r="B142" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C142" s="66" t="str">
+        <x:v>Change Safety</x:v>
+      </x:c>
+      <x:c r="D142" s="66" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="E142" s="66" t="str">
+        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
+      </x:c>
+      <x:c r="F142" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G142" s="66"/>
+      <x:c r="H142" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I142" s="389" t="n">
+      <x:c r="I142" s="388" t="n">
         <x:f>IF(H142="Done",1,IF(H142="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J142" s="65" t="str">
-        <x:v>Build artifact caching</x:v>
-      </x:c>
-      <x:c r="K142" s="65"/>
-      <x:c r="L142" s="65"/>
-      <x:c r="M142" s="65"/>
+      <x:c r="J142" s="66" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K142" s="66"/>
+      <x:c r="L142" s="66"/>
+      <x:c r="M142" s="66"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="66" t="str">
-        <x:v>R-135</x:v>
-      </x:c>
-      <x:c r="B143" s="66" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C143" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D143" s="66" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="E143" s="66" t="str">
-        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
-      </x:c>
-      <x:c r="F143" s="66" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G143" s="66"/>
-      <x:c r="H143" s="66" t="str">
+      <x:c r="A143" s="65" t="str">
+        <x:v>R-134</x:v>
+      </x:c>
+      <x:c r="B143" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C143" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D143" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="E143" s="65" t="str">
+        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
+      </x:c>
+      <x:c r="F143" s="65" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G143" s="65"/>
+      <x:c r="H143" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I143" s="388" t="n">
+      <x:c r="I143" s="389" t="n">
         <x:f>IF(H143="Done",1,IF(H143="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J143" s="66" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K143" s="66"/>
-      <x:c r="L143" s="66"/>
-      <x:c r="M143" s="66" t="str">
-        <x:v>V3</x:v>
-      </x:c>
+      <x:c r="J143" s="65" t="str">
+        <x:v>Build artifact caching</x:v>
+      </x:c>
+      <x:c r="K143" s="65"/>
+      <x:c r="L143" s="65"/>
+      <x:c r="M143" s="65"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="65" t="str">
-        <x:v>R-136</x:v>
-      </x:c>
-      <x:c r="B144" s="65" t="str">
+      <x:c r="A144" s="66" t="str">
+        <x:v>R-135</x:v>
+      </x:c>
+      <x:c r="B144" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C144" s="65" t="str">
+      <x:c r="C144" s="66" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D144" s="65" t="str">
-        <x:v>Recommendation score model</x:v>
-      </x:c>
-      <x:c r="E144" s="65" t="str">
-        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
-      </x:c>
-      <x:c r="F144" s="65" t="str">
+      <x:c r="D144" s="66" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="E144" s="66" t="str">
+        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
+      </x:c>
+      <x:c r="F144" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G144" s="65"/>
-      <x:c r="H144" s="65" t="str">
+      <x:c r="G144" s="66"/>
+      <x:c r="H144" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I144" s="389" t="n">
+      <x:c r="I144" s="388" t="n">
         <x:f>IF(H144="Done",1,IF(H144="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J144" s="65" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="K144" s="65"/>
-      <x:c r="L144" s="65"/>
-      <x:c r="M144" s="65" t="str">
-        <x:v>Do not choose by industry label alone.</x:v>
+      <x:c r="J144" s="66" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K144" s="66"/>
+      <x:c r="L144" s="66"/>
+      <x:c r="M144" s="66" t="str">
+        <x:v>V3</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="66" t="str">
-        <x:v>R-137</x:v>
-      </x:c>
-      <x:c r="B145" s="66" t="str">
+      <x:c r="A145" s="65" t="str">
+        <x:v>R-136</x:v>
+      </x:c>
+      <x:c r="B145" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C145" s="66" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D145" s="66" t="str">
-        <x:v>Code sharing policy</x:v>
-      </x:c>
-      <x:c r="E145" s="66" t="str">
-        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
-      </x:c>
-      <x:c r="F145" s="66" t="str">
+      <x:c r="C145" s="65" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D145" s="65" t="str">
+        <x:v>Recommendation score model</x:v>
+      </x:c>
+      <x:c r="E145" s="65" t="str">
+        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
+      </x:c>
+      <x:c r="F145" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G145" s="66"/>
-      <x:c r="H145" s="66" t="str">
+      <x:c r="G145" s="65"/>
+      <x:c r="H145" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I145" s="388" t="n">
+      <x:c r="I145" s="389" t="n">
         <x:f>IF(H145="Done",1,IF(H145="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="66" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K145" s="66"/>
-      <x:c r="L145" s="66"/>
-      <x:c r="M145" s="66" t="str">
-        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
+      <x:c r="J145" s="65" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="K145" s="65"/>
+      <x:c r="L145" s="65"/>
+      <x:c r="M145" s="65" t="str">
+        <x:v>Do not choose by industry label alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="65" t="str">
-        <x:v>R-138</x:v>
-      </x:c>
-      <x:c r="B146" s="65" t="str">
+      <x:c r="A146" s="66" t="str">
+        <x:v>R-137</x:v>
+      </x:c>
+      <x:c r="B146" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C146" s="65" t="str">
+      <x:c r="C146" s="66" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D146" s="65" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="E146" s="65" t="str">
-        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
-      </x:c>
-      <x:c r="F146" s="65" t="str">
+      <x:c r="D146" s="66" t="str">
+        <x:v>Code sharing policy</x:v>
+      </x:c>
+      <x:c r="E146" s="66" t="str">
+        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
+      </x:c>
+      <x:c r="F146" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G146" s="65"/>
-      <x:c r="H146" s="65" t="str">
+      <x:c r="G146" s="66"/>
+      <x:c r="H146" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I146" s="389" t="n">
+      <x:c r="I146" s="388" t="n">
         <x:f>IF(H146="Done",1,IF(H146="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="65" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K146" s="65"/>
-      <x:c r="L146" s="65"/>
-      <x:c r="M146" s="65" t="str">
-        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
+      <x:c r="J146" s="66" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K146" s="66"/>
+      <x:c r="L146" s="66"/>
+      <x:c r="M146" s="66" t="str">
+        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="66" t="str">
-        <x:v>R-139</x:v>
-      </x:c>
-      <x:c r="B147" s="66" t="str">
+      <x:c r="A147" s="65" t="str">
+        <x:v>R-138</x:v>
+      </x:c>
+      <x:c r="B147" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C147" s="66" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D147" s="66" t="str">
-        <x:v>Root task commands</x:v>
-      </x:c>
-      <x:c r="E147" s="66" t="str">
-        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
-      </x:c>
-      <x:c r="F147" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G147" s="66"/>
-      <x:c r="H147" s="66" t="str">
+      <x:c r="C147" s="65" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D147" s="65" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="E147" s="65" t="str">
+        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
+      </x:c>
+      <x:c r="F147" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G147" s="65"/>
+      <x:c r="H147" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I147" s="388" t="n">
+      <x:c r="I147" s="389" t="n">
         <x:f>IF(H147="Done",1,IF(H147="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="66" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="K147" s="66"/>
-      <x:c r="L147" s="66"/>
-      <x:c r="M147" s="66" t="str">
-        <x:v>Framework-independent agent commands.</x:v>
+      <x:c r="J147" s="65" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K147" s="65"/>
+      <x:c r="L147" s="65"/>
+      <x:c r="M147" s="65" t="str">
+        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="65" t="str">
-        <x:v>R-140</x:v>
-      </x:c>
-      <x:c r="B148" s="65" t="str">
+      <x:c r="A148" s="66" t="str">
+        <x:v>R-139</x:v>
+      </x:c>
+      <x:c r="B148" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C148" s="65" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D148" s="65" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="E148" s="65" t="str">
-        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
-      </x:c>
-      <x:c r="F148" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G148" s="65"/>
-      <x:c r="H148" s="65" t="str">
+      <x:c r="C148" s="66" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D148" s="66" t="str">
+        <x:v>Root task commands</x:v>
+      </x:c>
+      <x:c r="E148" s="66" t="str">
+        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
+      </x:c>
+      <x:c r="F148" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G148" s="66"/>
+      <x:c r="H148" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I148" s="389" t="n">
+      <x:c r="I148" s="388" t="n">
         <x:f>IF(H148="Done",1,IF(H148="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J148" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K148" s="65"/>
-      <x:c r="L148" s="65"/>
-      <x:c r="M148" s="65" t="str">
-        <x:v>Stable target.</x:v>
+      <x:c r="J148" s="66" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="K148" s="66"/>
+      <x:c r="L148" s="66"/>
+      <x:c r="M148" s="66" t="str">
+        <x:v>Framework-independent agent commands.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="66" t="str">
-        <x:v>R-141</x:v>
-      </x:c>
-      <x:c r="B149" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C149" s="66" t="str">
+      <x:c r="A149" s="65" t="str">
+        <x:v>R-140</x:v>
+      </x:c>
+      <x:c r="B149" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C149" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D149" s="66" t="str">
-        <x:v>Flutter scaled template</x:v>
-      </x:c>
-      <x:c r="E149" s="66" t="str">
-        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
-      </x:c>
-      <x:c r="F149" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G149" s="66"/>
-      <x:c r="H149" s="66" t="str">
+      <x:c r="D149" s="65" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="E149" s="65" t="str">
+        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
+      </x:c>
+      <x:c r="F149" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G149" s="65"/>
+      <x:c r="H149" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I149" s="388" t="n">
+      <x:c r="I149" s="389" t="n">
         <x:f>IF(H149="Done",1,IF(H149="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J149" s="66" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="K149" s="66"/>
-      <x:c r="L149" s="66"/>
-      <x:c r="M149" s="66" t="str">
-        <x:v>Use only when complexity warrants.</x:v>
+      <x:c r="J149" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K149" s="65"/>
+      <x:c r="L149" s="65"/>
+      <x:c r="M149" s="65" t="str">
+        <x:v>Stable target.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="65" t="str">
-        <x:v>R-142</x:v>
-      </x:c>
-      <x:c r="B150" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C150" s="65" t="str">
+      <x:c r="A150" s="66" t="str">
+        <x:v>R-141</x:v>
+      </x:c>
+      <x:c r="B150" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C150" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D150" s="65" t="str">
-        <x:v>React Native TypeScript template</x:v>
-      </x:c>
-      <x:c r="E150" s="65" t="str">
-        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
-      </x:c>
-      <x:c r="F150" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G150" s="65"/>
-      <x:c r="H150" s="65" t="str">
+      <x:c r="D150" s="66" t="str">
+        <x:v>Flutter scaled template</x:v>
+      </x:c>
+      <x:c r="E150" s="66" t="str">
+        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
+      </x:c>
+      <x:c r="F150" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G150" s="66"/>
+      <x:c r="H150" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I150" s="389" t="n">
+      <x:c r="I150" s="388" t="n">
         <x:f>IF(H150="Done",1,IF(H150="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K150" s="65"/>
-      <x:c r="L150" s="65"/>
-      <x:c r="M150" s="65" t="str">
-        <x:v>Expo profile when capabilities fit.</x:v>
+      <x:c r="J150" s="66" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="K150" s="66"/>
+      <x:c r="L150" s="66"/>
+      <x:c r="M150" s="66" t="str">
+        <x:v>Use only when complexity warrants.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="66" t="str">
-        <x:v>R-143</x:v>
-      </x:c>
-      <x:c r="B151" s="66" t="str">
+      <x:c r="A151" s="65" t="str">
+        <x:v>R-142</x:v>
+      </x:c>
+      <x:c r="B151" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C151" s="66" t="str">
+      <x:c r="C151" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D151" s="66" t="str">
-        <x:v>React Native shared TS packages</x:v>
-      </x:c>
-      <x:c r="E151" s="66" t="str">
-        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
-      </x:c>
-      <x:c r="F151" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G151" s="66"/>
-      <x:c r="H151" s="66" t="str">
+      <x:c r="D151" s="65" t="str">
+        <x:v>React Native TypeScript template</x:v>
+      </x:c>
+      <x:c r="E151" s="65" t="str">
+        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
+      </x:c>
+      <x:c r="F151" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G151" s="65"/>
+      <x:c r="H151" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I151" s="388" t="n">
+      <x:c r="I151" s="389" t="n">
         <x:f>IF(H151="Done",1,IF(H151="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J151" s="66" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K151" s="66"/>
-      <x:c r="L151" s="66"/>
-      <x:c r="M151" s="66" t="str">
-        <x:v>Do not share UI blindly.</x:v>
+      <x:c r="J151" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K151" s="65"/>
+      <x:c r="L151" s="65"/>
+      <x:c r="M151" s="65" t="str">
+        <x:v>Expo profile when capabilities fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="65" t="str">
-        <x:v>R-144</x:v>
-      </x:c>
-      <x:c r="B152" s="65" t="str">
+      <x:c r="A152" s="66" t="str">
+        <x:v>R-143</x:v>
+      </x:c>
+      <x:c r="B152" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C152" s="65" t="str">
+      <x:c r="C152" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D152" s="65" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="E152" s="65" t="str">
-        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
-      </x:c>
-      <x:c r="F152" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G152" s="65"/>
-      <x:c r="H152" s="65" t="str">
+      <x:c r="D152" s="66" t="str">
+        <x:v>React Native shared TS packages</x:v>
+      </x:c>
+      <x:c r="E152" s="66" t="str">
+        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
+      </x:c>
+      <x:c r="F152" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G152" s="66"/>
+      <x:c r="H152" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I152" s="389" t="n">
+      <x:c r="I152" s="388" t="n">
         <x:f>IF(H152="Done",1,IF(H152="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J152" s="65" t="str">
-        <x:v>Native Android Agent</x:v>
-      </x:c>
-      <x:c r="K152" s="65"/>
-      <x:c r="L152" s="65"/>
-      <x:c r="M152" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J152" s="66" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K152" s="66"/>
+      <x:c r="L152" s="66"/>
+      <x:c r="M152" s="66" t="str">
+        <x:v>Do not share UI blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="66" t="str">
-        <x:v>R-145</x:v>
-      </x:c>
-      <x:c r="B153" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C153" s="66" t="str">
+      <x:c r="A153" s="65" t="str">
+        <x:v>R-144</x:v>
+      </x:c>
+      <x:c r="B153" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C153" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D153" s="66" t="str">
-        <x:v>Native Android scaled modules</x:v>
-      </x:c>
-      <x:c r="E153" s="66" t="str">
-        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
-      </x:c>
-      <x:c r="F153" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G153" s="66"/>
-      <x:c r="H153" s="66" t="str">
+      <x:c r="D153" s="65" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="E153" s="65" t="str">
+        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
+      </x:c>
+      <x:c r="F153" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G153" s="65"/>
+      <x:c r="H153" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I153" s="388" t="n">
+      <x:c r="I153" s="389" t="n">
         <x:f>IF(H153="Done",1,IF(H153="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J153" s="66" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="K153" s="66"/>
-      <x:c r="L153" s="66"/>
-      <x:c r="M153" s="66" t="str">
-        <x:v>Experienced team structure.</x:v>
+      <x:c r="J153" s="65" t="str">
+        <x:v>Native Android Agent</x:v>
+      </x:c>
+      <x:c r="K153" s="65"/>
+      <x:c r="L153" s="65"/>
+      <x:c r="M153" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="65" t="str">
-        <x:v>R-146</x:v>
-      </x:c>
-      <x:c r="B154" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C154" s="65" t="str">
+      <x:c r="A154" s="66" t="str">
+        <x:v>R-145</x:v>
+      </x:c>
+      <x:c r="B154" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C154" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D154" s="65" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="E154" s="65" t="str">
-        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
-      </x:c>
-      <x:c r="F154" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G154" s="65"/>
-      <x:c r="H154" s="65" t="str">
+      <x:c r="D154" s="66" t="str">
+        <x:v>Native Android scaled modules</x:v>
+      </x:c>
+      <x:c r="E154" s="66" t="str">
+        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
+      </x:c>
+      <x:c r="F154" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G154" s="66"/>
+      <x:c r="H154" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I154" s="389" t="n">
+      <x:c r="I154" s="388" t="n">
         <x:f>IF(H154="Done",1,IF(H154="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="65" t="str">
-        <x:v>Native iOS Agent</x:v>
-      </x:c>
-      <x:c r="K154" s="65"/>
-      <x:c r="L154" s="65"/>
-      <x:c r="M154" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J154" s="66" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="K154" s="66"/>
+      <x:c r="L154" s="66"/>
+      <x:c r="M154" s="66" t="str">
+        <x:v>Experienced team structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="66" t="str">
-        <x:v>R-147</x:v>
-      </x:c>
-      <x:c r="B155" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C155" s="66" t="str">
+      <x:c r="A155" s="65" t="str">
+        <x:v>R-146</x:v>
+      </x:c>
+      <x:c r="B155" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C155" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D155" s="66" t="str">
-        <x:v>Native iOS scaled Swift Packages</x:v>
-      </x:c>
-      <x:c r="E155" s="66" t="str">
-        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
-      </x:c>
-      <x:c r="F155" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G155" s="66"/>
-      <x:c r="H155" s="66" t="str">
+      <x:c r="D155" s="65" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="E155" s="65" t="str">
+        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
+      </x:c>
+      <x:c r="F155" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G155" s="65"/>
+      <x:c r="H155" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I155" s="388" t="n">
+      <x:c r="I155" s="389" t="n">
         <x:f>IF(H155="Done",1,IF(H155="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J155" s="66" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="K155" s="66"/>
-      <x:c r="L155" s="66"/>
-      <x:c r="M155" s="66" t="str">
-        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
+      <x:c r="J155" s="65" t="str">
+        <x:v>Native iOS Agent</x:v>
+      </x:c>
+      <x:c r="K155" s="65"/>
+      <x:c r="L155" s="65"/>
+      <x:c r="M155" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="65" t="str">
-        <x:v>R-148</x:v>
-      </x:c>
-      <x:c r="B156" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C156" s="65" t="str">
+      <x:c r="A156" s="66" t="str">
+        <x:v>R-147</x:v>
+      </x:c>
+      <x:c r="B156" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C156" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D156" s="65" t="str">
-        <x:v>Next.js public web template</x:v>
-      </x:c>
-      <x:c r="E156" s="65" t="str">
-        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
-      </x:c>
-      <x:c r="F156" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G156" s="65"/>
-      <x:c r="H156" s="65" t="str">
+      <x:c r="D156" s="66" t="str">
+        <x:v>Native iOS scaled Swift Packages</x:v>
+      </x:c>
+      <x:c r="E156" s="66" t="str">
+        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
+      </x:c>
+      <x:c r="F156" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G156" s="66"/>
+      <x:c r="H156" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I156" s="389" t="n">
+      <x:c r="I156" s="388" t="n">
         <x:f>IF(H156="Done",1,IF(H156="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J156" s="65" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="K156" s="65"/>
-      <x:c r="L156" s="65"/>
-      <x:c r="M156" s="65" t="str">
-        <x:v>Web optimized independently.</x:v>
+      <x:c r="J156" s="66" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="K156" s="66"/>
+      <x:c r="L156" s="66"/>
+      <x:c r="M156" s="66" t="str">
+        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="66" t="str">
-        <x:v>R-149</x:v>
-      </x:c>
-      <x:c r="B157" s="66" t="str">
+      <x:c r="A157" s="65" t="str">
+        <x:v>R-148</x:v>
+      </x:c>
+      <x:c r="B157" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C157" s="66" t="str">
+      <x:c r="C157" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D157" s="66" t="str">
-        <x:v>Next.js admin template</x:v>
-      </x:c>
-      <x:c r="E157" s="66" t="str">
-        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
-      </x:c>
-      <x:c r="F157" s="66" t="str">
+      <x:c r="D157" s="65" t="str">
+        <x:v>Next.js public web template</x:v>
+      </x:c>
+      <x:c r="E157" s="65" t="str">
+        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
+      </x:c>
+      <x:c r="F157" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G157" s="66"/>
-      <x:c r="H157" s="66" t="str">
+      <x:c r="G157" s="65"/>
+      <x:c r="H157" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I157" s="388" t="n">
+      <x:c r="I157" s="389" t="n">
         <x:f>IF(H157="Done",1,IF(H157="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J157" s="66" t="str">
+      <x:c r="J157" s="65" t="str">
         <x:v>Next.js web + admin default</x:v>
       </x:c>
-      <x:c r="K157" s="66"/>
-      <x:c r="L157" s="66"/>
-      <x:c r="M157" s="66" t="str">
-        <x:v>Never force admin onto Flutter/RN Web.</x:v>
+      <x:c r="K157" s="65"/>
+      <x:c r="L157" s="65"/>
+      <x:c r="M157" s="65" t="str">
+        <x:v>Web optimized independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="65" t="str">
-        <x:v>R-150</x:v>
-      </x:c>
-      <x:c r="B158" s="65" t="str">
+      <x:c r="A158" s="66" t="str">
+        <x:v>R-149</x:v>
+      </x:c>
+      <x:c r="B158" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C158" s="65" t="str">
+      <x:c r="C158" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D158" s="65" t="str">
-        <x:v>Go backend standard template</x:v>
-      </x:c>
-      <x:c r="E158" s="65" t="str">
-        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
-      </x:c>
-      <x:c r="F158" s="65" t="str">
+      <x:c r="D158" s="66" t="str">
+        <x:v>Next.js admin template</x:v>
+      </x:c>
+      <x:c r="E158" s="66" t="str">
+        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
+      </x:c>
+      <x:c r="F158" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G158" s="65"/>
-      <x:c r="H158" s="65" t="str">
+      <x:c r="G158" s="66"/>
+      <x:c r="H158" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I158" s="389" t="n">
+      <x:c r="I158" s="388" t="n">
         <x:f>IF(H158="Done",1,IF(H158="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="65" t="str">
-        <x:v>Backend Agent</x:v>
-      </x:c>
-      <x:c r="K158" s="65"/>
-      <x:c r="L158" s="65"/>
-      <x:c r="M158" s="65" t="str">
-        <x:v>Default backend profile.</x:v>
+      <x:c r="J158" s="66" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="K158" s="66"/>
+      <x:c r="L158" s="66"/>
+      <x:c r="M158" s="66" t="str">
+        <x:v>Never force admin onto Flutter/RN Web.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="66" t="str">
-        <x:v>R-151</x:v>
-      </x:c>
-      <x:c r="B159" s="66" t="str">
+      <x:c r="A159" s="65" t="str">
+        <x:v>R-150</x:v>
+      </x:c>
+      <x:c r="B159" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C159" s="66" t="str">
+      <x:c r="C159" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D159" s="66" t="str">
-        <x:v>Python backend standard template</x:v>
-      </x:c>
-      <x:c r="E159" s="66" t="str">
-        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
-      </x:c>
-      <x:c r="F159" s="66" t="str">
+      <x:c r="D159" s="65" t="str">
+        <x:v>Go backend standard template</x:v>
+      </x:c>
+      <x:c r="E159" s="65" t="str">
+        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
+      </x:c>
+      <x:c r="F159" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G159" s="66"/>
-      <x:c r="H159" s="66" t="str">
+      <x:c r="G159" s="65"/>
+      <x:c r="H159" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I159" s="388" t="n">
+      <x:c r="I159" s="389" t="n">
         <x:f>IF(H159="Done",1,IF(H159="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="66" t="str">
+      <x:c r="J159" s="65" t="str">
         <x:v>Backend Agent</x:v>
       </x:c>
-      <x:c r="K159" s="66"/>
-      <x:c r="L159" s="66"/>
-      <x:c r="M159" s="66" t="str">
-        <x:v>Alternative default backend profile.</x:v>
+      <x:c r="K159" s="65"/>
+      <x:c r="L159" s="65"/>
+      <x:c r="M159" s="65" t="str">
+        <x:v>Default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="65" t="str">
-        <x:v>R-152</x:v>
-      </x:c>
-      <x:c r="B160" s="65" t="str">
+      <x:c r="A160" s="66" t="str">
+        <x:v>R-151</x:v>
+      </x:c>
+      <x:c r="B160" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C160" s="65" t="str">
-        <x:v>Contracts</x:v>
-      </x:c>
-      <x:c r="D160" s="65" t="str">
-        <x:v>Generated client matrix</x:v>
-      </x:c>
-      <x:c r="E160" s="65" t="str">
-        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
-      </x:c>
-      <x:c r="F160" s="65" t="str">
+      <x:c r="C160" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D160" s="66" t="str">
+        <x:v>Python backend standard template</x:v>
+      </x:c>
+      <x:c r="E160" s="66" t="str">
+        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
+      </x:c>
+      <x:c r="F160" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G160" s="65"/>
-      <x:c r="H160" s="65" t="str">
+      <x:c r="G160" s="66"/>
+      <x:c r="H160" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I160" s="389" t="n">
+      <x:c r="I160" s="388" t="n">
         <x:f>IF(H160="Done",1,IF(H160="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="65" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K160" s="65"/>
-      <x:c r="L160" s="65"/>
-      <x:c r="M160" s="65" t="str">
-        <x:v>Contract-first consistency.</x:v>
+      <x:c r="J160" s="66" t="str">
+        <x:v>Backend Agent</x:v>
+      </x:c>
+      <x:c r="K160" s="66"/>
+      <x:c r="L160" s="66"/>
+      <x:c r="M160" s="66" t="str">
+        <x:v>Alternative default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="66" t="str">
-        <x:v>R-153</x:v>
-      </x:c>
-      <x:c r="B161" s="66" t="str">
+      <x:c r="A161" s="65" t="str">
+        <x:v>R-152</x:v>
+      </x:c>
+      <x:c r="B161" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C161" s="66" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D161" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="E161" s="66" t="str">
-        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
-      </x:c>
-      <x:c r="F161" s="66" t="str">
+      <x:c r="C161" s="65" t="str">
+        <x:v>Contracts</x:v>
+      </x:c>
+      <x:c r="D161" s="65" t="str">
+        <x:v>Generated client matrix</x:v>
+      </x:c>
+      <x:c r="E161" s="65" t="str">
+        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
+      </x:c>
+      <x:c r="F161" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G161" s="66"/>
-      <x:c r="H161" s="66" t="str">
+      <x:c r="G161" s="65"/>
+      <x:c r="H161" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I161" s="388" t="n">
+      <x:c r="I161" s="389" t="n">
         <x:f>IF(H161="Done",1,IF(H161="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J161" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K161" s="66"/>
-      <x:c r="L161" s="66"/>
-      <x:c r="M161" s="66" t="str">
-        <x:v>Stable/Beta/Experimental visible to user.</x:v>
+      <x:c r="J161" s="65" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K161" s="65"/>
+      <x:c r="L161" s="65"/>
+      <x:c r="M161" s="65" t="str">
+        <x:v>Contract-first consistency.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="65" t="str">
-        <x:v>R-154</x:v>
-      </x:c>
-      <x:c r="B162" s="65" t="str">
+      <x:c r="A162" s="66" t="str">
+        <x:v>R-153</x:v>
+      </x:c>
+      <x:c r="B162" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C162" s="65" t="str">
-        <x:v>Dependencies</x:v>
-      </x:c>
-      <x:c r="D162" s="65" t="str">
-        <x:v>Approved dependency catalog</x:v>
-      </x:c>
-      <x:c r="E162" s="65" t="str">
-        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
-      </x:c>
-      <x:c r="F162" s="65" t="str">
+      <x:c r="C162" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D162" s="66" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="E162" s="66" t="str">
+        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
+      </x:c>
+      <x:c r="F162" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G162" s="65"/>
-      <x:c r="H162" s="65" t="str">
+      <x:c r="G162" s="66"/>
+      <x:c r="H162" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I162" s="389" t="n">
+      <x:c r="I162" s="388" t="n">
         <x:f>IF(H162="Done",1,IF(H162="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J162" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K162" s="65"/>
-      <x:c r="L162" s="65"/>
-      <x:c r="M162" s="65" t="str">
-        <x:v>Prevents dependency explosion.</x:v>
+      <x:c r="J162" s="66" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K162" s="66"/>
+      <x:c r="L162" s="66"/>
+      <x:c r="M162" s="66" t="str">
+        <x:v>Stable/Beta/Experimental visible to user.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="66" t="str">
-        <x:v>R-155</x:v>
-      </x:c>
-      <x:c r="B163" s="66" t="str">
+      <x:c r="A163" s="65" t="str">
+        <x:v>R-154</x:v>
+      </x:c>
+      <x:c r="B163" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C163" s="66" t="str">
-        <x:v>Platform Architecture</x:v>
-      </x:c>
-      <x:c r="D163" s="66" t="str">
-        <x:v>Go control plane modular monolith</x:v>
-      </x:c>
-      <x:c r="E163" s="66" t="str">
-        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
-      </x:c>
-      <x:c r="F163" s="66" t="str">
+      <x:c r="C163" s="65" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D163" s="65" t="str">
+        <x:v>Approved dependency catalog</x:v>
+      </x:c>
+      <x:c r="E163" s="65" t="str">
+        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
+      </x:c>
+      <x:c r="F163" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G163" s="66"/>
-      <x:c r="H163" s="66" t="str">
+      <x:c r="G163" s="65"/>
+      <x:c r="H163" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I163" s="388" t="n">
+      <x:c r="I163" s="389" t="n">
         <x:f>IF(H163="Done",1,IF(H163="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J163" s="66" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K163" s="66"/>
-      <x:c r="L163" s="66"/>
-      <x:c r="M163" s="66" t="str">
-        <x:v>Avoid premature microservices.</x:v>
+      <x:c r="J163" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K163" s="65"/>
+      <x:c r="L163" s="65"/>
+      <x:c r="M163" s="65" t="str">
+        <x:v>Prevents dependency explosion.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="65" t="str">
-        <x:v>R-156</x:v>
-      </x:c>
-      <x:c r="B164" s="65" t="str">
+      <x:c r="A164" s="66" t="str">
+        <x:v>R-155</x:v>
+      </x:c>
+      <x:c r="B164" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C164" s="65" t="str">
+      <x:c r="C164" s="66" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D164" s="65" t="str">
-        <x:v>Python agent engine boundary</x:v>
-      </x:c>
-      <x:c r="E164" s="65" t="str">
-        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
-      </x:c>
-      <x:c r="F164" s="65" t="str">
+      <x:c r="D164" s="66" t="str">
+        <x:v>Go control plane modular monolith</x:v>
+      </x:c>
+      <x:c r="E164" s="66" t="str">
+        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
+      </x:c>
+      <x:c r="F164" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G164" s="65"/>
-      <x:c r="H164" s="65" t="str">
+      <x:c r="G164" s="66"/>
+      <x:c r="H164" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I164" s="389" t="n">
+      <x:c r="I164" s="388" t="n">
         <x:f>IF(H164="Done",1,IF(H164="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J164" s="65" t="str">
-        <x:v>Model gateway</x:v>
-      </x:c>
-      <x:c r="K164" s="65"/>
-      <x:c r="L164" s="65"/>
-      <x:c r="M164" s="65" t="str">
-        <x:v>Different ecosystem/iteration cadence.</x:v>
+      <x:c r="J164" s="66" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K164" s="66"/>
+      <x:c r="L164" s="66"/>
+      <x:c r="M164" s="66" t="str">
+        <x:v>Avoid premature microservices.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="66" t="str">
-        <x:v>R-157</x:v>
-      </x:c>
-      <x:c r="B165" s="66" t="str">
+      <x:c r="A165" s="65" t="str">
+        <x:v>R-156</x:v>
+      </x:c>
+      <x:c r="B165" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C165" s="66" t="str">
+      <x:c r="C165" s="65" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D165" s="66" t="str">
-        <x:v>Runner manager boundary</x:v>
-      </x:c>
-      <x:c r="E165" s="66" t="str">
-        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
-      </x:c>
-      <x:c r="F165" s="66" t="str">
+      <x:c r="D165" s="65" t="str">
+        <x:v>Python agent engine boundary</x:v>
+      </x:c>
+      <x:c r="E165" s="65" t="str">
+        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
+      </x:c>
+      <x:c r="F165" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G165" s="66"/>
-      <x:c r="H165" s="66" t="str">
+      <x:c r="G165" s="65"/>
+      <x:c r="H165" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I165" s="388" t="n">
+      <x:c r="I165" s="389" t="n">
         <x:f>IF(H165="Done",1,IF(H165="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J165" s="66" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
-      </x:c>
-      <x:c r="K165" s="66"/>
-      <x:c r="L165" s="66"/>
-      <x:c r="M165" s="66" t="str">
-        <x:v>Central execution control.</x:v>
+      <x:c r="J165" s="65" t="str">
+        <x:v>Model gateway</x:v>
+      </x:c>
+      <x:c r="K165" s="65"/>
+      <x:c r="L165" s="65"/>
+      <x:c r="M165" s="65" t="str">
+        <x:v>Different ecosystem/iteration cadence.</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="65" t="str">
-        <x:v>R-158</x:v>
-      </x:c>
-      <x:c r="B166" s="65" t="str">
+      <x:c r="A166" s="66" t="str">
+        <x:v>R-157</x:v>
+      </x:c>
+      <x:c r="B166" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C166" s="65" t="str">
-        <x:v>CI/CD</x:v>
-      </x:c>
-      <x:c r="D166" s="65" t="str">
-        <x:v>Unified PR pipeline</x:v>
-      </x:c>
-      <x:c r="E166" s="65" t="str">
-        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
-      </x:c>
-      <x:c r="F166" s="65" t="str">
+      <x:c r="C166" s="66" t="str">
+        <x:v>Platform Architecture</x:v>
+      </x:c>
+      <x:c r="D166" s="66" t="str">
+        <x:v>Runner manager boundary</x:v>
+      </x:c>
+      <x:c r="E166" s="66" t="str">
+        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
+      </x:c>
+      <x:c r="F166" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G166" s="65"/>
-      <x:c r="H166" s="65" t="str">
+      <x:c r="G166" s="66"/>
+      <x:c r="H166" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I166" s="389" t="n">
+      <x:c r="I166" s="388" t="n">
         <x:f>IF(H166="Done",1,IF(H166="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J166" s="65" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="K166" s="65"/>
-      <x:c r="L166" s="65"/>
-      <x:c r="M166" s="65" t="str">
-        <x:v>Real iOS compile uses macOS.</x:v>
+      <x:c r="J166" s="66" t="str">
+        <x:v>Ephemeral Linux sandbox</x:v>
+      </x:c>
+      <x:c r="K166" s="66"/>
+      <x:c r="L166" s="66"/>
+      <x:c r="M166" s="66" t="str">
+        <x:v>Central execution control.</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="66" t="str">
-        <x:v>R-159</x:v>
-      </x:c>
-      <x:c r="B167" s="66" t="str">
+      <x:c r="A167" s="65" t="str">
+        <x:v>R-158</x:v>
+      </x:c>
+      <x:c r="B167" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C167" s="66" t="str">
+      <x:c r="C167" s="65" t="str">
         <x:v>CI/CD</x:v>
       </x:c>
-      <x:c r="D167" s="66" t="str">
-        <x:v>Immutable build promotion</x:v>
-      </x:c>
-      <x:c r="E167" s="66" t="str">
-        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
-      </x:c>
-      <x:c r="F167" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G167" s="66"/>
-      <x:c r="H167" s="66" t="str">
+      <x:c r="D167" s="65" t="str">
+        <x:v>Unified PR pipeline</x:v>
+      </x:c>
+      <x:c r="E167" s="65" t="str">
+        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
+      </x:c>
+      <x:c r="F167" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G167" s="65"/>
+      <x:c r="H167" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I167" s="388" t="n">
+      <x:c r="I167" s="389" t="n">
         <x:f>IF(H167="Done",1,IF(H167="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J167" s="66" t="str">
-        <x:v>Deployment Agent</x:v>
-      </x:c>
-      <x:c r="K167" s="66"/>
-      <x:c r="L167" s="66"/>
-      <x:c r="M167" s="66" t="str">
-        <x:v>Reduces preview/production mismatch.</x:v>
+      <x:c r="J167" s="65" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="K167" s="65"/>
+      <x:c r="L167" s="65"/>
+      <x:c r="M167" s="65" t="str">
+        <x:v>Real iOS compile uses macOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="65" t="str">
-        <x:v>R-160</x:v>
-      </x:c>
-      <x:c r="B168" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C168" s="65" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D168" s="65" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="E168" s="65" t="str">
-        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
-      </x:c>
-      <x:c r="F168" s="65" t="str">
+      <x:c r="A168" s="66" t="str">
+        <x:v>R-159</x:v>
+      </x:c>
+      <x:c r="B168" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C168" s="66" t="str">
+        <x:v>CI/CD</x:v>
+      </x:c>
+      <x:c r="D168" s="66" t="str">
+        <x:v>Immutable build promotion</x:v>
+      </x:c>
+      <x:c r="E168" s="66" t="str">
+        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
+      </x:c>
+      <x:c r="F168" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G168" s="65"/>
-      <x:c r="H168" s="65" t="str">
+      <x:c r="G168" s="66"/>
+      <x:c r="H168" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I168" s="389" t="n">
+      <x:c r="I168" s="388" t="n">
         <x:f>IF(H168="Done",1,IF(H168="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J168" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K168" s="65"/>
-      <x:c r="L168" s="65"/>
-      <x:c r="M168" s="65"/>
+      <x:c r="J168" s="66" t="str">
+        <x:v>Deployment Agent</x:v>
+      </x:c>
+      <x:c r="K168" s="66"/>
+      <x:c r="L168" s="66"/>
+      <x:c r="M168" s="66" t="str">
+        <x:v>Reduces preview/production mismatch.</x:v>
+      </x:c>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="66" t="str">
-        <x:v>R-161</x:v>
-      </x:c>
-      <x:c r="B169" s="66" t="str">
+      <x:c r="A169" s="65" t="str">
+        <x:v>R-160</x:v>
+      </x:c>
+      <x:c r="B169" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C169" s="66" t="str">
-        <x:v>Preview</x:v>
-      </x:c>
-      <x:c r="D169" s="66" t="str">
-        <x:v>Local Mac Agent productized</x:v>
-      </x:c>
-      <x:c r="E169" s="66" t="str">
-        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
-      </x:c>
-      <x:c r="F169" s="66" t="str">
+      <x:c r="C169" s="65" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D169" s="65" t="str">
+        <x:v>Framework upgrade workflow</x:v>
+      </x:c>
+      <x:c r="E169" s="65" t="str">
+        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
+      </x:c>
+      <x:c r="F169" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G169" s="66"/>
-      <x:c r="H169" s="66" t="str">
+      <x:c r="G169" s="65"/>
+      <x:c r="H169" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I169" s="388" t="n">
+      <x:c r="I169" s="389" t="n">
         <x:f>IF(H169="Done",1,IF(H169="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J169" s="66" t="str">
-        <x:v>Local Mac Agent</x:v>
-      </x:c>
-      <x:c r="K169" s="66"/>
-      <x:c r="L169" s="66"/>
-      <x:c r="M169" s="66" t="str">
-        <x:v>Reduces cloud Mac cost.</x:v>
-      </x:c>
+      <x:c r="J169" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K169" s="65"/>
+      <x:c r="L169" s="65"/>
+      <x:c r="M169" s="65"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="65" t="str">
-        <x:v>R-162</x:v>
-      </x:c>
-      <x:c r="B170" s="65" t="str">
+      <x:c r="A170" s="66" t="str">
+        <x:v>R-161</x:v>
+      </x:c>
+      <x:c r="B170" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C170" s="65" t="str">
+      <x:c r="C170" s="66" t="str">
         <x:v>Preview</x:v>
       </x:c>
-      <x:c r="D170" s="65" t="str">
-        <x:v>Interactive cloud simulator metering</x:v>
-      </x:c>
-      <x:c r="E170" s="65" t="str">
-        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
-      </x:c>
-      <x:c r="F170" s="65" t="str">
+      <x:c r="D170" s="66" t="str">
+        <x:v>Local Mac Agent productized</x:v>
+      </x:c>
+      <x:c r="E170" s="66" t="str">
+        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
+      </x:c>
+      <x:c r="F170" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G170" s="65"/>
-      <x:c r="H170" s="65" t="str">
+      <x:c r="G170" s="66"/>
+      <x:c r="H170" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I170" s="389" t="n">
+      <x:c r="I170" s="388" t="n">
         <x:f>IF(H170="Done",1,IF(H170="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J170" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K170" s="65"/>
-      <x:c r="L170" s="65"/>
-      <x:c r="M170" s="65" t="str">
-        <x:v>Separate verification build cost from interactive session cost.</x:v>
+      <x:c r="J170" s="66" t="str">
+        <x:v>Local Mac Agent</x:v>
+      </x:c>
+      <x:c r="K170" s="66"/>
+      <x:c r="L170" s="66"/>
+      <x:c r="M170" s="66" t="str">
+        <x:v>Reduces cloud Mac cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="66" t="str">
-        <x:v>R-163</x:v>
-      </x:c>
-      <x:c r="B171" s="66" t="str">
+      <x:c r="A171" s="65" t="str">
+        <x:v>R-162</x:v>
+      </x:c>
+      <x:c r="B171" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C171" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D171" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="E171" s="66" t="str">
-        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
-      </x:c>
-      <x:c r="F171" s="66" t="str">
+      <x:c r="C171" s="65" t="str">
+        <x:v>Preview</x:v>
+      </x:c>
+      <x:c r="D171" s="65" t="str">
+        <x:v>Interactive cloud simulator metering</x:v>
+      </x:c>
+      <x:c r="E171" s="65" t="str">
+        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
+      </x:c>
+      <x:c r="F171" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G171" s="66"/>
-      <x:c r="H171" s="66" t="str">
+      <x:c r="G171" s="65"/>
+      <x:c r="H171" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I171" s="388" t="n">
+      <x:c r="I171" s="389" t="n">
         <x:f>IF(H171="Done",1,IF(H171="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J171" s="66" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K171" s="66"/>
-      <x:c r="L171" s="66"/>
-      <x:c r="M171" s="66" t="str">
-        <x:v>Measure before rewrite.</x:v>
+      <x:c r="J171" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K171" s="65"/>
+      <x:c r="L171" s="65"/>
+      <x:c r="M171" s="65" t="str">
+        <x:v>Separate verification build cost from interactive session cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="65" t="str">
-        <x:v>R-164</x:v>
-      </x:c>
-      <x:c r="B172" s="65" t="str">
+      <x:c r="A172" s="66" t="str">
+        <x:v>R-163</x:v>
+      </x:c>
+      <x:c r="B172" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C172" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D172" s="65" t="str">
-        <x:v>Template/repo health dashboard</x:v>
-      </x:c>
-      <x:c r="E172" s="65" t="str">
-        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
-      </x:c>
-      <x:c r="F172" s="65" t="str">
+      <x:c r="C172" s="66" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D172" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="E172" s="66" t="str">
+        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
+      </x:c>
+      <x:c r="F172" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G172" s="65"/>
-      <x:c r="H172" s="65" t="str">
+      <x:c r="G172" s="66"/>
+      <x:c r="H172" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I172" s="389" t="n">
+      <x:c r="I172" s="388" t="n">
         <x:f>IF(H172="Done",1,IF(H172="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J172" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="K172" s="65"/>
-      <x:c r="L172" s="65"/>
-      <x:c r="M172" s="65" t="str">
-        <x:v>Use data to trigger architecture review.</x:v>
+      <x:c r="J172" s="66" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K172" s="66"/>
+      <x:c r="L172" s="66"/>
+      <x:c r="M172" s="66" t="str">
+        <x:v>Measure before rewrite.</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="66" t="str">
-        <x:v>R-165</x:v>
-      </x:c>
-      <x:c r="B173" s="66" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C173" s="66" t="str">
-        <x:v>Migration</x:v>
-      </x:c>
-      <x:c r="D173" s="66" t="str">
-        <x:v>Cross-platform to native migration engine</x:v>
-      </x:c>
-      <x:c r="E173" s="66" t="str">
-        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
-      </x:c>
-      <x:c r="F173" s="66" t="str">
+      <x:c r="A173" s="65" t="str">
+        <x:v>R-164</x:v>
+      </x:c>
+      <x:c r="B173" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C173" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D173" s="65" t="str">
+        <x:v>Template/repo health dashboard</x:v>
+      </x:c>
+      <x:c r="E173" s="65" t="str">
+        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
+      </x:c>
+      <x:c r="F173" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G173" s="66"/>
-      <x:c r="H173" s="66" t="str">
+      <x:c r="G173" s="65"/>
+      <x:c r="H173" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I173" s="388" t="n">
+      <x:c r="I173" s="389" t="n">
         <x:f>IF(H173="Done",1,IF(H173="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J173" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="K173" s="66"/>
-      <x:c r="L173" s="66"/>
-      <x:c r="M173" s="66" t="str">
-        <x:v>Prevents framework lock-in.</x:v>
+      <x:c r="J173" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="K173" s="65"/>
+      <x:c r="L173" s="65"/>
+      <x:c r="M173" s="65" t="str">
+        <x:v>Use data to trigger architecture review.</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="65" t="str">
-        <x:v>R-166</x:v>
-      </x:c>
-      <x:c r="B174" s="65" t="str">
+      <x:c r="A174" s="66" t="str">
+        <x:v>R-165</x:v>
+      </x:c>
+      <x:c r="B174" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C174" s="65" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D174" s="65" t="str">
-        <x:v>Cross-repo task coordinator</x:v>
-      </x:c>
-      <x:c r="E174" s="65" t="str">
-        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
-      </x:c>
-      <x:c r="F174" s="65" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G174" s="65"/>
-      <x:c r="H174" s="65" t="str">
+      <x:c r="C174" s="66" t="str">
+        <x:v>Migration</x:v>
+      </x:c>
+      <x:c r="D174" s="66" t="str">
+        <x:v>Cross-platform to native migration engine</x:v>
+      </x:c>
+      <x:c r="E174" s="66" t="str">
+        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
+      </x:c>
+      <x:c r="F174" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G174" s="66"/>
+      <x:c r="H174" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I174" s="389" t="n">
+      <x:c r="I174" s="388" t="n">
         <x:f>IF(H174="Done",1,IF(H174="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J174" s="65" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="K174" s="65"/>
-      <x:c r="L174" s="65"/>
-      <x:c r="M174" s="65"/>
+      <x:c r="J174" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="K174" s="66"/>
+      <x:c r="L174" s="66"/>
+      <x:c r="M174" s="66" t="str">
+        <x:v>Prevents framework lock-in.</x:v>
+      </x:c>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="66" t="str">
-        <x:v>R-167</x:v>
-      </x:c>
-      <x:c r="B175" s="66" t="str">
+      <x:c r="A175" s="65" t="str">
+        <x:v>R-166</x:v>
+      </x:c>
+      <x:c r="B175" s="65" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C175" s="66" t="str">
-        <x:v>Infrastructure</x:v>
-      </x:c>
-      <x:c r="D175" s="66" t="str">
-        <x:v>BYOC / private runners</x:v>
-      </x:c>
-      <x:c r="E175" s="66" t="str">
-        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
-      </x:c>
-      <x:c r="F175" s="66" t="str">
+      <x:c r="C175" s="65" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D175" s="65" t="str">
+        <x:v>Cross-repo task coordinator</x:v>
+      </x:c>
+      <x:c r="E175" s="65" t="str">
+        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
+      </x:c>
+      <x:c r="F175" s="65" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G175" s="66"/>
-      <x:c r="H175" s="66" t="str">
+      <x:c r="G175" s="65"/>
+      <x:c r="H175" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I175" s="388" t="n">
+      <x:c r="I175" s="389" t="n">
         <x:f>IF(H175="Done",1,IF(H175="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J175" s="66" t="str">
-        <x:v>Enterprise workload isolation</x:v>
-      </x:c>
-      <x:c r="K175" s="66"/>
-      <x:c r="L175" s="66"/>
-      <x:c r="M175" s="66"/>
+      <x:c r="J175" s="65" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="K175" s="65"/>
+      <x:c r="L175" s="65"/>
+      <x:c r="M175" s="65"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="65" t="str">
-        <x:v>R-168</x:v>
-      </x:c>
-      <x:c r="B176" s="65" t="str">
+      <x:c r="A176" s="66" t="str">
+        <x:v>R-167</x:v>
+      </x:c>
+      <x:c r="B176" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C176" s="65" t="str">
-        <x:v>Testing</x:v>
-      </x:c>
-      <x:c r="D176" s="65" t="str">
-        <x:v>Physical device cloud integration</x:v>
-      </x:c>
-      <x:c r="E176" s="65" t="str">
-        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
-      </x:c>
-      <x:c r="F176" s="65" t="str">
+      <x:c r="C176" s="66" t="str">
+        <x:v>Infrastructure</x:v>
+      </x:c>
+      <x:c r="D176" s="66" t="str">
+        <x:v>BYOC / private runners</x:v>
+      </x:c>
+      <x:c r="E176" s="66" t="str">
+        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
+      </x:c>
+      <x:c r="F176" s="66" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G176" s="65"/>
-      <x:c r="H176" s="65" t="str">
+      <x:c r="G176" s="66"/>
+      <x:c r="H176" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I176" s="389" t="n">
+      <x:c r="I176" s="388" t="n">
         <x:f>IF(H176="Done",1,IF(H176="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J176" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K176" s="65"/>
-      <x:c r="L176" s="65"/>
-      <x:c r="M176" s="65"/>
+      <x:c r="J176" s="66" t="str">
+        <x:v>Enterprise workload isolation</x:v>
+      </x:c>
+      <x:c r="K176" s="66"/>
+      <x:c r="L176" s="66"/>
+      <x:c r="M176" s="66"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="127" t="str">
-        <x:v>R-169</x:v>
-      </x:c>
-      <x:c r="B177" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
-      </x:c>
-      <x:c r="C177" s="127" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D177" s="127" t="str">
-        <x:v>Template support lifecycle</x:v>
-      </x:c>
-      <x:c r="E177" s="127" t="str">
-        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
-      </x:c>
-      <x:c r="F177" s="127" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G177" s="127"/>
-      <x:c r="H177" s="127" t="str">
+      <x:c r="A177" s="65" t="str">
+        <x:v>R-168</x:v>
+      </x:c>
+      <x:c r="B177" s="65" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C177" s="65" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="D177" s="65" t="str">
+        <x:v>Physical device cloud integration</x:v>
+      </x:c>
+      <x:c r="E177" s="65" t="str">
+        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
+      </x:c>
+      <x:c r="F177" s="65" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G177" s="65"/>
+      <x:c r="H177" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I177" s="390" t="n">
+      <x:c r="I177" s="389" t="n">
         <x:f>IF(H177="Done",1,IF(H177="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J177" s="127" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="K177" s="127"/>
-      <x:c r="L177" s="127"/>
-      <x:c r="M177" s="127"/>
+      <x:c r="J177" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K177" s="65"/>
+      <x:c r="L177" s="65"/>
+      <x:c r="M177" s="65"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="127" t="str">
-        <x:v>R-170</x:v>
+        <x:v>R-169</x:v>
       </x:c>
       <x:c r="B178" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C178" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D178" s="127" t="str">
-        <x:v>Framework/toolchain production SLO</x:v>
+        <x:v>Template support lifecycle</x:v>
       </x:c>
       <x:c r="E178" s="127" t="str">
-        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
+        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
       </x:c>
       <x:c r="F178" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G178" s="127"/>
       <x:c r="H178" s="127" t="str">
@@ -16343,29 +16351,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="127" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="K178" s="127"/>
       <x:c r="L178" s="127"/>
-      <x:c r="M178" s="127" t="str">
-        <x:v>Production readiness is measured, not assumed.</x:v>
-      </x:c>
+      <x:c r="M178" s="127"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="127" t="str">
-        <x:v>R-171</x:v>
+        <x:v>R-170</x:v>
       </x:c>
       <x:c r="B179" s="127" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C179" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D179" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Framework/toolchain production SLO</x:v>
       </x:c>
       <x:c r="E179" s="127" t="str">
-        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
+        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
       </x:c>
       <x:c r="F179" s="127" t="str">
         <x:v>P0</x:v>
@@ -16379,17 +16385,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="127" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="K179" s="127"/>
       <x:c r="L179" s="127"/>
       <x:c r="M179" s="127" t="str">
-        <x:v>No agent-to-vendor SDK coupling.</x:v>
+        <x:v>Production readiness is measured, not assumed.</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="127" t="str">
-        <x:v>R-172</x:v>
+        <x:v>R-171</x:v>
       </x:c>
       <x:c r="B180" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16398,10 +16404,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D180" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="E180" s="127" t="str">
-        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
+        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
       </x:c>
       <x:c r="F180" s="127" t="str">
         <x:v>P0</x:v>
@@ -16415,17 +16421,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K180" s="127"/>
       <x:c r="L180" s="127"/>
       <x:c r="M180" s="127" t="str">
-        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
+        <x:v>No agent-to-vendor SDK coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="127" t="str">
-        <x:v>R-173</x:v>
+        <x:v>R-172</x:v>
       </x:c>
       <x:c r="B181" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16434,10 +16440,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D181" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="E181" s="127" t="str">
-        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
+        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
       </x:c>
       <x:c r="F181" s="127" t="str">
         <x:v>P0</x:v>
@@ -16456,12 +16462,12 @@
       <x:c r="K181" s="127"/>
       <x:c r="L181" s="127"/>
       <x:c r="M181" s="127" t="str">
-        <x:v>Cheapest safe runtime wins.</x:v>
+        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="127" t="str">
-        <x:v>R-174</x:v>
+        <x:v>R-173</x:v>
       </x:c>
       <x:c r="B182" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16470,13 +16476,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D182" s="127" t="str">
-        <x:v>Browser runtime PoC</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="E182" s="127" t="str">
-        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
+        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
       </x:c>
       <x:c r="F182" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G182" s="127"/>
       <x:c r="H182" s="127" t="str">
@@ -16487,17 +16493,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K182" s="127"/>
       <x:c r="L182" s="127"/>
       <x:c r="M182" s="127" t="str">
-        <x:v>Not universal sandbox.</x:v>
+        <x:v>Cheapest safe runtime wins.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="127" t="str">
-        <x:v>R-175</x:v>
+        <x:v>R-174</x:v>
       </x:c>
       <x:c r="B183" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16506,13 +16512,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D183" s="127" t="str">
-        <x:v>Runtime quotas and metering</x:v>
+        <x:v>Browser runtime PoC</x:v>
       </x:c>
       <x:c r="E183" s="127" t="str">
-        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
+        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
       </x:c>
       <x:c r="F183" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G183" s="127"/>
       <x:c r="H183" s="127" t="str">
@@ -16523,29 +16529,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="K183" s="127"/>
       <x:c r="L183" s="127"/>
       <x:c r="M183" s="127" t="str">
-        <x:v>Required for cost and abuse control.</x:v>
+        <x:v>Not universal sandbox.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="127" t="str">
-        <x:v>R-176</x:v>
+        <x:v>R-175</x:v>
       </x:c>
       <x:c r="B184" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C184" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D184" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Runtime quotas and metering</x:v>
       </x:c>
       <x:c r="E184" s="127" t="str">
-        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
+        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
       </x:c>
       <x:c r="F184" s="127" t="str">
         <x:v>P0</x:v>
@@ -16559,17 +16565,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="127" t="str">
-        <x:v>Supervisor / orchestrator</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K184" s="127"/>
       <x:c r="L184" s="127"/>
       <x:c r="M184" s="127" t="str">
-        <x:v>Platform-owned state schema.</x:v>
+        <x:v>Required for cost and abuse control.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="127" t="str">
-        <x:v>R-177</x:v>
+        <x:v>R-176</x:v>
       </x:c>
       <x:c r="B185" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16578,10 +16584,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D185" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="E185" s="127" t="str">
-        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
+        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
       </x:c>
       <x:c r="F185" s="127" t="str">
         <x:v>P0</x:v>
@@ -16595,17 +16601,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Supervisor / orchestrator</x:v>
       </x:c>
       <x:c r="K185" s="127"/>
       <x:c r="L185" s="127"/>
       <x:c r="M185" s="127" t="str">
-        <x:v>No full restart by default.</x:v>
+        <x:v>Platform-owned state schema.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="127" t="str">
-        <x:v>R-178</x:v>
+        <x:v>R-177</x:v>
       </x:c>
       <x:c r="B186" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16614,10 +16620,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D186" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="E186" s="127" t="str">
-        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
+        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
       </x:c>
       <x:c r="F186" s="127" t="str">
         <x:v>P0</x:v>
@@ -16631,29 +16637,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K186" s="127"/>
       <x:c r="L186" s="127"/>
       <x:c r="M186" s="127" t="str">
-        <x:v>Prevent duplicate side effects.</x:v>
+        <x:v>No full restart by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="127" t="str">
-        <x:v>R-179</x:v>
+        <x:v>R-178</x:v>
       </x:c>
       <x:c r="B187" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C187" s="127" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D187" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="E187" s="127" t="str">
-        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
+        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
       </x:c>
       <x:c r="F187" s="127" t="str">
         <x:v>P0</x:v>
@@ -16667,29 +16673,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K187" s="127"/>
       <x:c r="L187" s="127"/>
       <x:c r="M187" s="127" t="str">
-        <x:v>Supports replay, audit and debugging.</x:v>
+        <x:v>Prevent duplicate side effects.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="127" t="str">
-        <x:v>R-180</x:v>
+        <x:v>R-179</x:v>
       </x:c>
       <x:c r="B188" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C188" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D188" s="127" t="str">
-        <x:v>Orchestrator Adapter</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="E188" s="127" t="str">
-        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
+        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
       </x:c>
       <x:c r="F188" s="127" t="str">
         <x:v>P0</x:v>
@@ -16708,24 +16714,24 @@
       <x:c r="K188" s="127"/>
       <x:c r="L188" s="127"/>
       <x:c r="M188" s="127" t="str">
-        <x:v>LangGraph may be first implementation.</x:v>
+        <x:v>Supports replay, audit and debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="127" t="str">
-        <x:v>R-181</x:v>
+        <x:v>R-180</x:v>
       </x:c>
       <x:c r="B189" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C189" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D189" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Orchestrator Adapter</x:v>
       </x:c>
       <x:c r="E189" s="127" t="str">
-        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
+        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
       </x:c>
       <x:c r="F189" s="127" t="str">
         <x:v>P0</x:v>
@@ -16739,17 +16745,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K189" s="127"/>
       <x:c r="L189" s="127"/>
       <x:c r="M189" s="127" t="str">
-        <x:v>Frontend never parses provider-specific streams.</x:v>
+        <x:v>LangGraph may be first implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="127" t="str">
-        <x:v>R-182</x:v>
+        <x:v>R-181</x:v>
       </x:c>
       <x:c r="B190" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16758,10 +16764,10 @@
         <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D190" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="E190" s="127" t="str">
-        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
+        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
       </x:c>
       <x:c r="F190" s="127" t="str">
         <x:v>P0</x:v>
@@ -16775,29 +16781,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K190" s="127"/>
       <x:c r="L190" s="127"/>
       <x:c r="M190" s="127" t="str">
-        <x:v>SSE allowed for simple one-way streams.</x:v>
+        <x:v>Frontend never parses provider-specific streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="127" t="str">
-        <x:v>R-183</x:v>
+        <x:v>R-182</x:v>
       </x:c>
       <x:c r="B191" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C191" s="127" t="str">
-        <x:v>Approvals</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D191" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="E191" s="127" t="str">
-        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
+        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
       </x:c>
       <x:c r="F191" s="127" t="str">
         <x:v>P0</x:v>
@@ -16811,17 +16817,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="K191" s="127"/>
       <x:c r="L191" s="127"/>
       <x:c r="M191" s="127" t="str">
-        <x:v>Approval based on risk.</x:v>
+        <x:v>SSE allowed for simple one-way streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="127" t="str">
-        <x:v>R-184</x:v>
+        <x:v>R-183</x:v>
       </x:c>
       <x:c r="B192" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16830,10 +16836,10 @@
         <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D192" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="E192" s="127" t="str">
-        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
+        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
       </x:c>
       <x:c r="F192" s="127" t="str">
         <x:v>P0</x:v>
@@ -16847,29 +16853,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K192" s="127"/>
       <x:c r="L192" s="127"/>
       <x:c r="M192" s="127" t="str">
-        <x:v>Production/destructive actions auditable.</x:v>
+        <x:v>Approval based on risk.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="127" t="str">
-        <x:v>R-185</x:v>
+        <x:v>R-184</x:v>
       </x:c>
       <x:c r="B193" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C193" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D193" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="E193" s="127" t="str">
-        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
+        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
       </x:c>
       <x:c r="F193" s="127" t="str">
         <x:v>P0</x:v>
@@ -16883,17 +16889,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="K193" s="127"/>
       <x:c r="L193" s="127"/>
       <x:c r="M193" s="127" t="str">
-        <x:v>Deny by default.</x:v>
+        <x:v>Production/destructive actions auditable.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="127" t="str">
-        <x:v>R-186</x:v>
+        <x:v>R-185</x:v>
       </x:c>
       <x:c r="B194" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16902,13 +16908,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D194" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="E194" s="127" t="str">
-        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
+        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
       </x:c>
       <x:c r="F194" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G194" s="127"/>
       <x:c r="H194" s="127" t="str">
@@ -16919,17 +16925,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K194" s="127"/>
       <x:c r="L194" s="127"/>
       <x:c r="M194" s="127" t="str">
-        <x:v>No arbitrary agent-to-MCP connections.</x:v>
+        <x:v>Deny by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="127" t="str">
-        <x:v>R-187</x:v>
+        <x:v>R-186</x:v>
       </x:c>
       <x:c r="B195" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16938,13 +16944,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D195" s="127" t="str">
-        <x:v>Tool secret broker</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="E195" s="127" t="str">
-        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
+        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
       </x:c>
       <x:c r="F195" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G195" s="127"/>
       <x:c r="H195" s="127" t="str">
@@ -16960,27 +16966,27 @@
       <x:c r="K195" s="127"/>
       <x:c r="L195" s="127"/>
       <x:c r="M195" s="127" t="str">
-        <x:v>Audit every secret grant.</x:v>
+        <x:v>No arbitrary agent-to-MCP connections.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="127" t="str">
-        <x:v>R-188</x:v>
+        <x:v>R-187</x:v>
       </x:c>
       <x:c r="B196" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C196" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D196" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Tool secret broker</x:v>
       </x:c>
       <x:c r="E196" s="127" t="str">
-        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
+        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
       </x:c>
       <x:c r="F196" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G196" s="127"/>
       <x:c r="H196" s="127" t="str">
@@ -16991,32 +16997,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J196" s="127" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="K196" s="127"/>
       <x:c r="L196" s="127"/>
       <x:c r="M196" s="127" t="str">
-        <x:v>Not platform core.</x:v>
+        <x:v>Audit every secret grant.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="127" t="str">
-        <x:v>R-189</x:v>
+        <x:v>R-188</x:v>
       </x:c>
       <x:c r="B197" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C197" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D197" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="E197" s="127" t="str">
-        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
+        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
       </x:c>
       <x:c r="F197" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G197" s="127"/>
       <x:c r="H197" s="127" t="str">
@@ -17027,29 +17033,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J197" s="127" t="str">
-        <x:v>Architecture decision records</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K197" s="127"/>
       <x:c r="L197" s="127"/>
       <x:c r="M197" s="127" t="str">
-        <x:v>References inform; benchmarks decide.</x:v>
+        <x:v>Not platform core.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="127" t="str">
-        <x:v>R-190</x:v>
+        <x:v>R-189</x:v>
       </x:c>
       <x:c r="B198" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C198" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D198" s="127" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="E198" s="127" t="str">
-        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
+        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
       </x:c>
       <x:c r="F198" s="127" t="str">
         <x:v>P0</x:v>
@@ -17063,32 +17069,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J198" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Architecture decision records</x:v>
       </x:c>
       <x:c r="K198" s="127"/>
       <x:c r="L198" s="127"/>
       <x:c r="M198" s="127" t="str">
-        <x:v>Architectural learning != code copying.</x:v>
+        <x:v>References inform; benchmarks decide.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="127" t="str">
-        <x:v>R-191</x:v>
+        <x:v>R-190</x:v>
       </x:c>
       <x:c r="B199" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C199" s="127" t="str">
-        <x:v>Team</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D199" s="127" t="str">
-        <x:v>Shared engineering glossary</x:v>
+        <x:v>Open-source license review</x:v>
       </x:c>
       <x:c r="E199" s="127" t="str">
-        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
+        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
       </x:c>
       <x:c r="F199" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G199" s="127"/>
       <x:c r="H199" s="127" t="str">
@@ -17098,31 +17104,33 @@
         <x:f>IF(H199="Done",1,IF(H199="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J199" s="127"/>
+      <x:c r="J199" s="127" t="str">
+        <x:v>Build-vs-Buy benchmark process</x:v>
+      </x:c>
       <x:c r="K199" s="127"/>
       <x:c r="L199" s="127"/>
       <x:c r="M199" s="127" t="str">
-        <x:v>Use in docs and AI prompts.</x:v>
+        <x:v>Architectural learning != code copying.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="127" t="str">
-        <x:v>R-192</x:v>
+        <x:v>R-191</x:v>
       </x:c>
       <x:c r="B200" s="127" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C200" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Team</x:v>
       </x:c>
       <x:c r="D200" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Shared engineering glossary</x:v>
       </x:c>
       <x:c r="E200" s="127" t="str">
-        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
+        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
       </x:c>
       <x:c r="F200" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G200" s="127"/>
       <x:c r="H200" s="127" t="str">
@@ -17132,30 +17140,28 @@
         <x:f>IF(H200="Done",1,IF(H200="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J200" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
-      </x:c>
+      <x:c r="J200" s="127"/>
       <x:c r="K200" s="127"/>
       <x:c r="L200" s="127"/>
       <x:c r="M200" s="127" t="str">
-        <x:v>Marketplace later.</x:v>
+        <x:v>Use in docs and AI prompts.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="127" t="str">
-        <x:v>R-193</x:v>
+        <x:v>R-192</x:v>
       </x:c>
       <x:c r="B201" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C201" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D201" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="E201" s="127" t="str">
-        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
+        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
       </x:c>
       <x:c r="F201" s="127" t="str">
         <x:v>P1</x:v>
@@ -17169,17 +17175,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="127" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K201" s="127"/>
       <x:c r="L201" s="127"/>
       <x:c r="M201" s="127" t="str">
-        <x:v>Extends local mode beyond Mac.</x:v>
+        <x:v>Marketplace later.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="127" t="str">
-        <x:v>R-194</x:v>
+        <x:v>R-193</x:v>
       </x:c>
       <x:c r="B202" s="127" t="str">
         <x:v>MID</x:v>
@@ -17188,10 +17194,10 @@
         <x:v>Execution</x:v>
       </x:c>
       <x:c r="D202" s="127" t="str">
-        <x:v>Hybrid BYOK/local mode</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="E202" s="127" t="str">
-        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
+        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
       </x:c>
       <x:c r="F202" s="127" t="str">
         <x:v>P1</x:v>
@@ -17205,29 +17211,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="K202" s="127"/>
       <x:c r="L202" s="127"/>
       <x:c r="M202" s="127" t="str">
-        <x:v>Privacy + cost option.</x:v>
+        <x:v>Extends local mode beyond Mac.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="127" t="str">
-        <x:v>R-195</x:v>
+        <x:v>R-194</x:v>
       </x:c>
       <x:c r="B203" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C203" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D203" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Hybrid BYOK/local mode</x:v>
       </x:c>
       <x:c r="E203" s="127" t="str">
-        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
+        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
       </x:c>
       <x:c r="F203" s="127" t="str">
         <x:v>P1</x:v>
@@ -17241,17 +17247,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K203" s="127"/>
       <x:c r="L203" s="127"/>
       <x:c r="M203" s="127" t="str">
-        <x:v>Validate portability/failover.</x:v>
+        <x:v>Privacy + cost option.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="127" t="str">
-        <x:v>R-196</x:v>
+        <x:v>R-195</x:v>
       </x:c>
       <x:c r="B204" s="127" t="str">
         <x:v>MID</x:v>
@@ -17260,13 +17266,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D204" s="127" t="str">
-        <x:v>Sandbox snapshots and warm pools</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="E204" s="127" t="str">
-        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
+        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
       </x:c>
       <x:c r="F204" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G204" s="127"/>
       <x:c r="H204" s="127" t="str">
@@ -17277,32 +17283,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K204" s="127"/>
       <x:c r="L204" s="127"/>
       <x:c r="M204" s="127" t="str">
-        <x:v>Do not optimize blindly.</x:v>
+        <x:v>Validate portability/failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="127" t="str">
-        <x:v>R-197</x:v>
+        <x:v>R-196</x:v>
       </x:c>
       <x:c r="B205" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C205" s="127" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D205" s="127" t="str">
-        <x:v>Agent time-travel debugging</x:v>
+        <x:v>Sandbox snapshots and warm pools</x:v>
       </x:c>
       <x:c r="E205" s="127" t="str">
-        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
+        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
       </x:c>
       <x:c r="F205" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G205" s="127"/>
       <x:c r="H205" s="127" t="str">
@@ -17313,32 +17319,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K205" s="127"/>
       <x:c r="L205" s="127"/>
       <x:c r="M205" s="127" t="str">
-        <x:v>Operator and developer debugging.</x:v>
+        <x:v>Do not optimize blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="127" t="str">
-        <x:v>R-198</x:v>
+        <x:v>R-197</x:v>
       </x:c>
       <x:c r="B206" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C206" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D206" s="127" t="str">
-        <x:v>Tool marketplace verification</x:v>
+        <x:v>Agent time-travel debugging</x:v>
       </x:c>
       <x:c r="E206" s="127" t="str">
-        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
+        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
       </x:c>
       <x:c r="F206" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G206" s="127"/>
       <x:c r="H206" s="127" t="str">
@@ -17349,32 +17355,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K206" s="127"/>
       <x:c r="L206" s="127"/>
       <x:c r="M206" s="127" t="str">
-        <x:v>Verified badge is evidence-based.</x:v>
+        <x:v>Operator and developer debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="127" t="str">
-        <x:v>R-199</x:v>
+        <x:v>R-198</x:v>
       </x:c>
       <x:c r="B207" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C207" s="127" t="str">
-        <x:v>Routing</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D207" s="127" t="str">
-        <x:v>Runtime provider cost-latency routing</x:v>
+        <x:v>Tool marketplace verification</x:v>
       </x:c>
       <x:c r="E207" s="127" t="str">
-        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
+        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
       </x:c>
       <x:c r="F207" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G207" s="127"/>
       <x:c r="H207" s="127" t="str">
@@ -17385,32 +17391,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K207" s="127"/>
       <x:c r="L207" s="127"/>
       <x:c r="M207" s="127" t="str">
-        <x:v>Policy can override cheapest route.</x:v>
+        <x:v>Verified badge is evidence-based.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="127" t="str">
-        <x:v>R-200</x:v>
+        <x:v>R-199</x:v>
       </x:c>
       <x:c r="B208" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C208" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="D208" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Runtime provider cost-latency routing</x:v>
       </x:c>
       <x:c r="E208" s="127" t="str">
-        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
+        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
       </x:c>
       <x:c r="F208" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G208" s="127"/>
       <x:c r="H208" s="127" t="str">
@@ -17421,29 +17427,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K208" s="127"/>
       <x:c r="L208" s="127"/>
       <x:c r="M208" s="127" t="str">
-        <x:v>Keep portability via IR/contracts.</x:v>
+        <x:v>Policy can override cheapest route.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="127" t="str">
-        <x:v>R-201</x:v>
+        <x:v>R-200</x:v>
       </x:c>
       <x:c r="B209" s="127" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C209" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D209" s="127" t="str">
-        <x:v>Customer private MCP servers</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="E209" s="127" t="str">
-        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
+        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
       </x:c>
       <x:c r="F209" s="127" t="str">
         <x:v>P2</x:v>
@@ -17457,32 +17463,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="K209" s="127"/>
       <x:c r="L209" s="127"/>
       <x:c r="M209" s="127" t="str">
-        <x:v>Enterprise feature.</x:v>
+        <x:v>Keep portability via IR/contracts.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="127" t="str">
-        <x:v>R-202</x:v>
+        <x:v>R-201</x:v>
       </x:c>
       <x:c r="B210" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C210" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D210" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>Customer private MCP servers</x:v>
       </x:c>
       <x:c r="E210" s="127" t="str">
-        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
+        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
       </x:c>
       <x:c r="F210" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G210" s="127"/>
       <x:c r="H210" s="127" t="str">
@@ -17493,32 +17499,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="127" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K210" s="127"/>
       <x:c r="L210" s="127"/>
       <x:c r="M210" s="127" t="str">
-        <x:v>Central policy + audit remain.</x:v>
+        <x:v>Enterprise feature.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="127" t="str">
-        <x:v>R-203</x:v>
+        <x:v>R-202</x:v>
       </x:c>
       <x:c r="B211" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C211" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D211" s="127" t="str">
-        <x:v>Cross-region runtime scheduler</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="E211" s="127" t="str">
-        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
+        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
       </x:c>
       <x:c r="F211" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G211" s="127"/>
       <x:c r="H211" s="127" t="str">
@@ -17529,17 +17535,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="K211" s="127"/>
       <x:c r="L211" s="127"/>
       <x:c r="M211" s="127" t="str">
-        <x:v>Enterprise scale.</x:v>
+        <x:v>Central policy + audit remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="127" t="str">
-        <x:v>R-204</x:v>
+        <x:v>R-203</x:v>
       </x:c>
       <x:c r="B212" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17548,10 +17554,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D212" s="127" t="str">
-        <x:v>Hardened microVM runner fleet</x:v>
+        <x:v>Cross-region runtime scheduler</x:v>
       </x:c>
       <x:c r="E212" s="127" t="str">
-        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
+        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
       </x:c>
       <x:c r="F212" s="127" t="str">
         <x:v>P2</x:v>
@@ -17565,32 +17571,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="127" t="str">
-        <x:v>Provider cost-latency routing</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="K212" s="127"/>
       <x:c r="L212" s="127"/>
       <x:c r="M212" s="127" t="str">
-        <x:v>Do not build before benchmark.</x:v>
+        <x:v>Enterprise scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="127" t="str">
-        <x:v>R-205</x:v>
+        <x:v>R-204</x:v>
       </x:c>
       <x:c r="B213" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C213" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D213" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>Hardened microVM runner fleet</x:v>
       </x:c>
       <x:c r="E213" s="127" t="str">
-        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
+        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
       </x:c>
       <x:c r="F213" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G213" s="127"/>
       <x:c r="H213" s="127" t="str">
@@ -17601,29 +17607,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Provider cost-latency routing</x:v>
       </x:c>
       <x:c r="K213" s="127"/>
       <x:c r="L213" s="127"/>
       <x:c r="M213" s="127" t="str">
-        <x:v>Checkpoint-aware failover.</x:v>
+        <x:v>Do not build before benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="127" t="str">
-        <x:v>R-206</x:v>
+        <x:v>R-205</x:v>
       </x:c>
       <x:c r="B214" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C214" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D214" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="E214" s="127" t="str">
-        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
+        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
       </x:c>
       <x:c r="F214" s="127" t="str">
         <x:v>P1</x:v>
@@ -17637,17 +17643,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K214" s="127"/>
       <x:c r="L214" s="127"/>
       <x:c r="M214" s="127" t="str">
-        <x:v>Enterprise override support.</x:v>
+        <x:v>Checkpoint-aware failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="127" t="str">
-        <x:v>R-207</x:v>
+        <x:v>R-206</x:v>
       </x:c>
       <x:c r="B215" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17656,13 +17662,13 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D215" s="127" t="str">
-        <x:v>Two-person critical approval</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="E215" s="127" t="str">
-        <x:v>Optional dual approval for L4 actions.</x:v>
+        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
       </x:c>
       <x:c r="F215" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G215" s="127"/>
       <x:c r="H215" s="127" t="str">
@@ -17673,29 +17679,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K215" s="127"/>
       <x:c r="L215" s="127"/>
       <x:c r="M215" s="127" t="str">
-        <x:v>High-risk enterprise.</x:v>
+        <x:v>Enterprise override support.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="127" t="str">
-        <x:v>R-208</x:v>
+        <x:v>R-207</x:v>
       </x:c>
       <x:c r="B216" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C216" s="127" t="str">
-        <x:v>Models</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D216" s="127" t="str">
-        <x:v>Customer private model endpoints</x:v>
+        <x:v>Two-person critical approval</x:v>
       </x:c>
       <x:c r="E216" s="127" t="str">
-        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
+        <x:v>Optional dual approval for L4 actions.</x:v>
       </x:c>
       <x:c r="F216" s="127" t="str">
         <x:v>P2</x:v>
@@ -17709,29 +17715,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="127" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="K216" s="127"/>
       <x:c r="L216" s="127"/>
       <x:c r="M216" s="127" t="str">
-        <x:v>No direct client-to-model coupling.</x:v>
+        <x:v>High-risk enterprise.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="127" t="str">
-        <x:v>R-209</x:v>
+        <x:v>R-208</x:v>
       </x:c>
       <x:c r="B217" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C217" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D217" s="127" t="str">
-        <x:v>Automated provider benchmark suite</x:v>
+        <x:v>Customer private model endpoints</x:v>
       </x:c>
       <x:c r="E217" s="127" t="str">
-        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
+        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
       </x:c>
       <x:c r="F217" s="127" t="str">
         <x:v>P2</x:v>
@@ -17745,32 +17751,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="K217" s="127"/>
       <x:c r="L217" s="127"/>
       <x:c r="M217" s="127" t="str">
-        <x:v>Feeds routing/ADR reviews.</x:v>
+        <x:v>No direct client-to-model coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="127" t="str">
-        <x:v>R-210</x:v>
+        <x:v>R-209</x:v>
       </x:c>
       <x:c r="B218" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C218" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D218" s="127" t="str">
-        <x:v>Crash-resume production test</x:v>
+        <x:v>Automated provider benchmark suite</x:v>
       </x:c>
       <x:c r="E218" s="127" t="str">
-        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
+        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
       </x:c>
       <x:c r="F218" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G218" s="127"/>
       <x:c r="H218" s="127" t="str">
@@ -17781,17 +17787,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="K218" s="127"/>
       <x:c r="L218" s="127"/>
       <x:c r="M218" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Feeds routing/ADR reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="127" t="str">
-        <x:v>R-211</x:v>
+        <x:v>R-210</x:v>
       </x:c>
       <x:c r="B219" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17800,10 +17806,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D219" s="127" t="str">
-        <x:v>Duplicate side-effect prevention test</x:v>
+        <x:v>Crash-resume production test</x:v>
       </x:c>
       <x:c r="E219" s="127" t="str">
-        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
+        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
       </x:c>
       <x:c r="F219" s="127" t="str">
         <x:v>P0</x:v>
@@ -17817,7 +17823,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K219" s="127"/>
       <x:c r="L219" s="127"/>
@@ -17827,19 +17833,19 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="127" t="str">
-        <x:v>R-212</x:v>
+        <x:v>R-211</x:v>
       </x:c>
       <x:c r="B220" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C220" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D220" s="127" t="str">
-        <x:v>WebSocket replay correctness SLO</x:v>
+        <x:v>Duplicate side-effect prevention test</x:v>
       </x:c>
       <x:c r="E220" s="127" t="str">
-        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
+        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
       </x:c>
       <x:c r="F220" s="127" t="str">
         <x:v>P0</x:v>
@@ -17853,7 +17859,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K220" s="127"/>
       <x:c r="L220" s="127"/>
@@ -17863,19 +17869,19 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="127" t="str">
-        <x:v>R-213</x:v>
+        <x:v>R-212</x:v>
       </x:c>
       <x:c r="B221" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C221" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D221" s="127" t="str">
-        <x:v>MCP isolation and prompt-injection test</x:v>
+        <x:v>WebSocket replay correctness SLO</x:v>
       </x:c>
       <x:c r="E221" s="127" t="str">
-        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
+        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
       </x:c>
       <x:c r="F221" s="127" t="str">
         <x:v>P0</x:v>
@@ -17889,7 +17895,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="K221" s="127"/>
       <x:c r="L221" s="127"/>
@@ -17899,7 +17905,7 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="127" t="str">
-        <x:v>R-214</x:v>
+        <x:v>R-213</x:v>
       </x:c>
       <x:c r="B222" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17908,10 +17914,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D222" s="127" t="str">
-        <x:v>Sandbox tenant isolation test</x:v>
+        <x:v>MCP isolation and prompt-injection test</x:v>
       </x:c>
       <x:c r="E222" s="127" t="str">
-        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
+        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
       </x:c>
       <x:c r="F222" s="127" t="str">
         <x:v>P0</x:v>
@@ -17925,7 +17931,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K222" s="127"/>
       <x:c r="L222" s="127"/>
@@ -17935,19 +17941,19 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="127" t="str">
-        <x:v>R-215</x:v>
+        <x:v>R-214</x:v>
       </x:c>
       <x:c r="B223" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C223" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D223" s="127" t="str">
-        <x:v>Runtime provider outage failover</x:v>
+        <x:v>Sandbox tenant isolation test</x:v>
       </x:c>
       <x:c r="E223" s="127" t="str">
-        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
+        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
       </x:c>
       <x:c r="F223" s="127" t="str">
         <x:v>P0</x:v>
@@ -17961,7 +17967,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K223" s="127"/>
       <x:c r="L223" s="127"/>
@@ -17971,19 +17977,19 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="127" t="str">
-        <x:v>R-216</x:v>
+        <x:v>R-215</x:v>
       </x:c>
       <x:c r="B224" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C224" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D224" s="127" t="str">
-        <x:v>Approval auditability test</x:v>
+        <x:v>Runtime provider outage failover</x:v>
       </x:c>
       <x:c r="E224" s="127" t="str">
-        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
+        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
       </x:c>
       <x:c r="F224" s="127" t="str">
         <x:v>P0</x:v>
@@ -17997,7 +18003,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="K224" s="127"/>
       <x:c r="L224" s="127"/>
@@ -18007,22 +18013,22 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="127" t="str">
-        <x:v>R-217</x:v>
+        <x:v>R-216</x:v>
       </x:c>
       <x:c r="B225" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C225" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D225" s="127" t="str">
-        <x:v>BaaS to custom migration test</x:v>
+        <x:v>Approval auditability test</x:v>
       </x:c>
       <x:c r="E225" s="127" t="str">
-        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
       </x:c>
       <x:c r="F225" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G225" s="127"/>
       <x:c r="H225" s="127" t="str">
@@ -18033,65 +18039,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K225" s="127"/>
       <x:c r="L225" s="127"/>
       <x:c r="M225" s="127" t="str">
-        <x:v>Avoid backend lock-in.</x:v>
+        <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
-      <x:c r="A226" t="str">
-        <x:v>R-218</x:v>
-      </x:c>
-      <x:c r="B226" t="str">
+      <x:c r="A226" s="127" t="str">
+        <x:v>R-217</x:v>
+      </x:c>
+      <x:c r="B226" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C226" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="D226" t="str">
-        <x:v>Local Agent security lifecycle</x:v>
-      </x:c>
-      <x:c r="E226" t="str">
-        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
-      </x:c>
-      <x:c r="F226" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G226"/>
-      <x:c r="H226" t="str">
+      <x:c r="C226" s="127" t="str">
+        <x:v>Backend Strategy</x:v>
+      </x:c>
+      <x:c r="D226" s="127" t="str">
+        <x:v>BaaS to custom migration test</x:v>
+      </x:c>
+      <x:c r="E226" s="127" t="str">
+        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+      </x:c>
+      <x:c r="F226" s="127" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G226" s="127"/>
+      <x:c r="H226" s="127" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I226" t="n">
+      <x:c r="I226" s="390" t="n">
         <x:f>IF(H226="Done",1,IF(H226="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J226" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
-      </x:c>
-      <x:c r="K226"/>
-      <x:c r="L226"/>
-      <x:c r="M226" t="str">
-        <x:v>Production gate.</x:v>
+      <x:c r="J226" s="127" t="str">
+        <x:v>BaaS provider expansion</x:v>
+      </x:c>
+      <x:c r="K226" s="127"/>
+      <x:c r="L226" s="127"/>
+      <x:c r="M226" s="127" t="str">
+        <x:v>Avoid backend lock-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" t="str">
-        <x:v>R-219</x:v>
+        <x:v>R-218</x:v>
       </x:c>
       <x:c r="B227" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C227" t="str">
-        <x:v>Compliance</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D227" t="str">
-        <x:v>OSS license and SBOM gate</x:v>
+        <x:v>Local Agent security lifecycle</x:v>
       </x:c>
       <x:c r="E227" t="str">
-        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
       </x:c>
       <x:c r="F227" t="str">
         <x:v>P0</x:v>
@@ -18105,11 +18111,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J227" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K227"/>
       <x:c r="L227"/>
       <x:c r="M227" t="str">
+        <x:v>Production gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="str">
+        <x:v>R-219</x:v>
+      </x:c>
+      <x:c r="B228" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>Compliance</x:v>
+      </x:c>
+      <x:c r="D228" t="str">
+        <x:v>OSS license and SBOM gate</x:v>
+      </x:c>
+      <x:c r="E228" t="str">
+        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+      </x:c>
+      <x:c r="F228" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G228"/>
+      <x:c r="H228" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="I228" t="n">
+        <x:f>IF(H228="Done",1,IF(H228="In Progress",0.5,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J228" t="str">
+        <x:v>Open-source license review</x:v>
+      </x:c>
+      <x:c r="K228"/>
+      <x:c r="L228"/>
+      <x:c r="M228" t="str">
         <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
@@ -18118,7 +18160,7 @@
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H4:H116">
+  <x:conditionalFormatting sqref="H4:H117">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>H4="Done"</x:formula>
     </x:cfRule>
@@ -18133,34 +18175,34 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="10">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B116">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B117">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F116">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F117">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H116">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H117">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B117:B140">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B118:B141">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F117:F140">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F118:F141">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H117:H140">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H118:H141">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F141:F176">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F142:F177">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H141:H176">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H142:H177">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H225">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H226">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F225">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F226">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -10662,11 +10662,11 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-009</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation in progress on ai/R-220-cloud-streaming; true SSE streaming added for OpenAI-compatible, Anthropic, and Gemini adapters; offline parser tests added; cloud_calls=0.</x:v>
+        <x:v>Implementation 4e31841e730a6466da55843ff352f7144dd763e9; task verify passed with 78 agent-engine tests (5 new SSE streaming tests); true incremental streaming for OpenAI/Anthropic/Gemini; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 57, 84, 85, 90, 91, and 92.</x:v>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2389,7 +2389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M117" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M118" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -2701,11 +2701,11 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"MVP")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"MVP")</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"MVP",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"MVP",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"MID",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"MID",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,7 +2746,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F6)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"ADVANCED",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"ADVANCED",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$228,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$228,"PRODUCTION",Phase_Roadmap!$H$4:$H$228,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"PRODUCTION",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F8)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$228,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -10641,7 +10641,7 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-220</x:v>
+        <x:v>R-221</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10650,10 +10650,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Cloud streaming (Server-Sent Events)</x:v>
+        <x:v>Cross-provider fallback and circuit breaking</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Replace the single-event cloud stream wrapper with true incremental SSE streaming for OpenAI-compatible, Anthropic, and Gemini adapters; ordered delta events plus a final event with measured usage, reusing the HTTP-safety bounds.</x:v>
+        <x:v>Add explicit allowlist-driven cross-provider fallback and per-provider circuit breaking to the gateway: on a retriable failure advance to the next allowed, registered, circuit-closed candidate; a per-provider breaker opens after repeated failures and recovers after a cooldown.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
@@ -10662,28 +10662,28 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-009</x:v>
+        <x:v>R-220</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation 4e31841e730a6466da55843ff352f7144dd763e9; task verify passed with 78 agent-engine tests (5 new SSE streaming tests); true incremental streaming for OpenAI/Anthropic/Gemini; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation in progress on ai/R-221-cross-provider-fallback; explicit fallback chain + per-provider circuit breaker added to the gateway; offline tests added; cloud_calls=0.</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 57, 84, 85, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 18.3, 84, 89, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-009</x:v>
+        <x:v>R-220</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10692,10 +10692,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>Usage and cost accounting</x:v>
+        <x:v>Cloud streaming (Server-Sent Events)</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
+        <x:v>Replace the single-event cloud stream wrapper with true incremental SSE streaming for OpenAI-compatible, Anthropic, and Gemini adapters; ordered delta events plus a final event with measured usage, reusing the HTTP-safety bounds.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
@@ -10711,21 +10711,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation 4e31841e730a6466da55843ff352f7144dd763e9; task verify passed with 78 agent-engine tests (5 new SSE streaming tests); true incremental streaming for OpenAI/Anthropic/Gemini; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 57, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10734,10 +10734,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>Cloud API-key provider adapters</x:v>
+        <x:v>Usage and cost accounting</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
+        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
@@ -10753,21 +10753,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10776,10 +10776,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>Balanced Model Gateway router</x:v>
+        <x:v>Cloud API-key provider adapters</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
+        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
@@ -10795,21 +10795,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
+        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10818,16 +10818,16 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>Loopback Ollama provider adapter</x:v>
+        <x:v>Balanced Model Gateway router</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
+        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G13" s="32" t="str">
-        <x:v>Codex</x:v>
+        <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H13" s="32" t="str">
         <x:v>Done</x:v>
@@ -10837,21 +10837,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10860,10 +10860,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
@@ -10879,33 +10879,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K14" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L14" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M14" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C15" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
@@ -10921,33 +10921,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K15" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L15" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M15" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C16" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
@@ -10963,33 +10963,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J16" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K16" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L16" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M16" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C17" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
@@ -11005,33 +11005,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K17" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L17" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M17" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C18" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
@@ -11047,53 +11047,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K18" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L18" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M18" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C19" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G19" s="32"/>
+      <x:c r="G19" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H19" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I19" s="376" t="n">
         <x:f>IF(H19="Done",1,IF(H19="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="32"/>
-      <x:c r="K19" s="32"/>
-      <x:c r="L19" s="32"/>
-      <x:c r="M19" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K19" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L19" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M19" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11102,10 +11112,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
@@ -11125,7 +11135,7 @@
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11134,10 +11144,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11157,7 +11167,7 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11166,10 +11176,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11189,7 +11199,7 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11198,10 +11208,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11221,7 +11231,7 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11230,10 +11240,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11253,19 +11263,19 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C25" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11285,7 +11295,7 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11294,10 +11304,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11317,19 +11327,19 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C27" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11349,7 +11359,7 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11358,10 +11368,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11381,19 +11391,19 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C29" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11413,19 +11423,19 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C30" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11445,7 +11455,7 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11454,10 +11464,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11477,19 +11487,19 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C32" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11509,7 +11519,7 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11518,10 +11528,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11541,7 +11551,7 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11550,10 +11560,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11573,19 +11583,19 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C35" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11605,7 +11615,7 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11614,10 +11624,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11637,7 +11647,7 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11646,10 +11656,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11669,7 +11679,7 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11678,10 +11688,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11701,7 +11711,7 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11710,10 +11720,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11733,19 +11743,19 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C40" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11765,7 +11775,7 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11774,10 +11784,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11797,19 +11807,19 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C42" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11829,7 +11839,7 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11838,10 +11848,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11861,19 +11871,19 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C44" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11893,19 +11903,19 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C45" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11925,19 +11935,19 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C46" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11957,7 +11967,7 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11966,10 +11976,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11989,7 +11999,7 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11998,10 +12008,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -12021,7 +12031,7 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12030,10 +12040,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12053,19 +12063,19 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C50" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12085,7 +12095,7 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12094,10 +12104,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12117,19 +12127,19 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C52" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12149,7 +12159,7 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12158,10 +12168,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12181,19 +12191,19 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C54" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12213,7 +12223,7 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12222,10 +12232,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12245,7 +12255,7 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12254,10 +12264,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
         <x:v>P0</x:v>
@@ -12277,19 +12287,19 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C57" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
         <x:v>P0</x:v>
@@ -12309,7 +12319,7 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12318,10 +12328,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
         <x:v>P0</x:v>
@@ -12341,7 +12351,7 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12350,10 +12360,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
         <x:v>P0</x:v>
@@ -12373,19 +12383,19 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C60" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
         <x:v>P0</x:v>
@@ -12405,22 +12415,22 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C61" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G61" s="32"/>
       <x:c r="H61" s="32" t="str">
@@ -12437,7 +12447,7 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
         <x:v>MID</x:v>
@@ -12446,10 +12456,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
         <x:v>P1</x:v>
@@ -12469,19 +12479,19 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C63" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12501,19 +12511,19 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C64" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12533,7 +12543,7 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
@@ -12542,10 +12552,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12565,19 +12575,19 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C66" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12597,19 +12607,19 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C67" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12629,19 +12639,19 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C68" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12661,7 +12671,7 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
@@ -12670,10 +12680,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12693,19 +12703,19 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C70" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12725,7 +12735,7 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
@@ -12734,10 +12744,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12757,7 +12767,7 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
@@ -12766,10 +12776,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12789,19 +12799,19 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C73" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12821,7 +12831,7 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
@@ -12830,10 +12840,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12853,19 +12863,19 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C75" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12885,19 +12895,19 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C76" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12917,19 +12927,19 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C77" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12949,19 +12959,19 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C78" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12981,7 +12991,7 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
@@ -12990,10 +13000,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -13013,7 +13023,7 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
@@ -13022,10 +13032,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -13045,19 +13055,19 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C81" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
         <x:v>P1</x:v>
@@ -13077,7 +13087,7 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
         <x:v>MID</x:v>
@@ -13086,10 +13096,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
         <x:v>P1</x:v>
@@ -13109,19 +13119,19 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C83" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
         <x:v>P1</x:v>
@@ -13141,19 +13151,19 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C84" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
         <x:v>P1</x:v>
@@ -13173,19 +13183,19 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C85" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
         <x:v>P1</x:v>
@@ -13205,22 +13215,22 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C86" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G86" s="32"/>
       <x:c r="H86" s="32" t="str">
@@ -13237,7 +13247,7 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13246,13 +13256,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G87" s="32"/>
       <x:c r="H87" s="32" t="str">
@@ -13269,22 +13279,22 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C88" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G88" s="32"/>
       <x:c r="H88" s="32" t="str">
@@ -13301,7 +13311,7 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13310,10 +13320,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
         <x:v>P2</x:v>
@@ -13333,19 +13343,19 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C90" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13365,19 +13375,19 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C91" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13397,19 +13407,19 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C92" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13429,7 +13439,7 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13438,10 +13448,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13461,19 +13471,19 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C94" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13493,7 +13503,7 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13502,10 +13512,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13525,7 +13535,7 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13534,10 +13544,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13557,19 +13567,19 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C97" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13589,7 +13599,7 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13598,10 +13608,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
         <x:v>P2</x:v>
@@ -13621,19 +13631,19 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C99" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
         <x:v>P2</x:v>
@@ -13653,19 +13663,19 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C100" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
         <x:v>P2</x:v>
@@ -13685,7 +13695,7 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13694,10 +13704,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
         <x:v>P2</x:v>
@@ -13717,19 +13727,19 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-093</x:v>
+        <x:v>R-092</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C102" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>Quality trend analytics</x:v>
+        <x:v>Spot/preemptible optimization</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
+        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
         <x:v>P2</x:v>
@@ -13749,22 +13759,22 @@
     </x:row>
     <x:row r="103" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A103" s="32" t="str">
-        <x:v>R-094</x:v>
+        <x:v>R-093</x:v>
       </x:c>
       <x:c r="B103" s="32" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C103" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D103" s="32" t="str">
-        <x:v>SLO/SLA framework</x:v>
+        <x:v>Quality trend analytics</x:v>
       </x:c>
       <x:c r="E103" s="32" t="str">
-        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
+        <x:v>Track regression, debt and agent success by model/version/framework.</x:v>
       </x:c>
       <x:c r="F103" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G103" s="32"/>
       <x:c r="H103" s="32" t="str">
@@ -13781,7 +13791,7 @@
     </x:row>
     <x:row r="104" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A104" s="32" t="str">
-        <x:v>R-095</x:v>
+        <x:v>R-094</x:v>
       </x:c>
       <x:c r="B104" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13790,10 +13800,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D104" s="32" t="str">
-        <x:v>HA control plane</x:v>
+        <x:v>SLO/SLA framework</x:v>
       </x:c>
       <x:c r="E104" s="32" t="str">
-        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
+        <x:v>Define availability, task success, build latency and recovery objectives.</x:v>
       </x:c>
       <x:c r="F104" s="32" t="str">
         <x:v>P0</x:v>
@@ -13813,7 +13823,7 @@
     </x:row>
     <x:row r="105" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A105" s="32" t="str">
-        <x:v>R-096</x:v>
+        <x:v>R-095</x:v>
       </x:c>
       <x:c r="B105" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13822,10 +13832,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D105" s="32" t="str">
-        <x:v>Backup + restore drills</x:v>
+        <x:v>HA control plane</x:v>
       </x:c>
       <x:c r="E105" s="32" t="str">
-        <x:v>Automated backups plus regularly tested restoration.</x:v>
+        <x:v>Remove single points of failure across API, queue, DB and model gateway.</x:v>
       </x:c>
       <x:c r="F105" s="32" t="str">
         <x:v>P0</x:v>
@@ -13845,7 +13855,7 @@
     </x:row>
     <x:row r="106" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A106" s="32" t="str">
-        <x:v>R-097</x:v>
+        <x:v>R-096</x:v>
       </x:c>
       <x:c r="B106" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13854,10 +13864,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D106" s="32" t="str">
-        <x:v>Disaster recovery</x:v>
+        <x:v>Backup + restore drills</x:v>
       </x:c>
       <x:c r="E106" s="32" t="str">
-        <x:v>Document and exercise regional recovery procedures.</x:v>
+        <x:v>Automated backups plus regularly tested restoration.</x:v>
       </x:c>
       <x:c r="F106" s="32" t="str">
         <x:v>P0</x:v>
@@ -13877,19 +13887,19 @@
     </x:row>
     <x:row r="107" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A107" s="32" t="str">
-        <x:v>R-098</x:v>
+        <x:v>R-097</x:v>
       </x:c>
       <x:c r="B107" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C107" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>Independent penetration test</x:v>
+        <x:v>Disaster recovery</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
-        <x:v>External security assessment before broad enterprise launch.</x:v>
+        <x:v>Document and exercise regional recovery procedures.</x:v>
       </x:c>
       <x:c r="F107" s="32" t="str">
         <x:v>P0</x:v>
@@ -13909,7 +13919,7 @@
     </x:row>
     <x:row r="108" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A108" s="32" t="str">
-        <x:v>R-099</x:v>
+        <x:v>R-098</x:v>
       </x:c>
       <x:c r="B108" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13918,10 +13928,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>SOC 2 readiness controls</x:v>
+        <x:v>Independent penetration test</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
-        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
+        <x:v>External security assessment before broad enterprise launch.</x:v>
       </x:c>
       <x:c r="F108" s="32" t="str">
         <x:v>P0</x:v>
@@ -13941,7 +13951,7 @@
     </x:row>
     <x:row r="109" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A109" s="32" t="str">
-        <x:v>R-100</x:v>
+        <x:v>R-099</x:v>
       </x:c>
       <x:c r="B109" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13950,10 +13960,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>Tenant isolation validation</x:v>
+        <x:v>SOC 2 readiness controls</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
-        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
+        <x:v>Audit logging, access reviews, change management, incident response and evidence.</x:v>
       </x:c>
       <x:c r="F109" s="32" t="str">
         <x:v>P0</x:v>
@@ -13973,7 +13983,7 @@
     </x:row>
     <x:row r="110" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A110" s="32" t="str">
-        <x:v>R-101</x:v>
+        <x:v>R-100</x:v>
       </x:c>
       <x:c r="B110" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -13982,10 +13992,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>Signing-key hardening</x:v>
+        <x:v>Tenant isolation validation</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
-        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
+        <x:v>Automated tests prove data/secret/build isolation between tenants.</x:v>
       </x:c>
       <x:c r="F110" s="32" t="str">
         <x:v>P0</x:v>
@@ -14005,19 +14015,19 @@
     </x:row>
     <x:row r="111" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A111" s="32" t="str">
-        <x:v>R-102</x:v>
+        <x:v>R-101</x:v>
       </x:c>
       <x:c r="B111" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C111" s="32" t="str">
-        <x:v>Operations</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>24x7 incident process</x:v>
+        <x:v>Signing-key hardening</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
-        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
+        <x:v>KMS/HSM-backed signing workflows and strict operator access.</x:v>
       </x:c>
       <x:c r="F111" s="32" t="str">
         <x:v>P0</x:v>
@@ -14037,7 +14047,7 @@
     </x:row>
     <x:row r="112" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A112" s="32" t="str">
-        <x:v>R-103</x:v>
+        <x:v>R-102</x:v>
       </x:c>
       <x:c r="B112" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14046,10 +14056,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Capacity/load tests</x:v>
+        <x:v>24x7 incident process</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
+        <x:v>On-call, severity levels, runbooks, status page and postmortems.</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
         <x:v>P0</x:v>
@@ -14069,7 +14079,7 @@
     </x:row>
     <x:row r="113" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A113" s="32" t="str">
-        <x:v>R-104</x:v>
+        <x:v>R-103</x:v>
       </x:c>
       <x:c r="B113" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14078,10 +14088,10 @@
         <x:v>Operations</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Cost guardrails</x:v>
+        <x:v>Capacity/load tests</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
+        <x:v>Prove planned concurrency for AI, sandboxes, builds and previews.</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
         <x:v>P0</x:v>
@@ -14101,19 +14111,19 @@
     </x:row>
     <x:row r="114" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A114" s="32" t="str">
-        <x:v>R-105</x:v>
+        <x:v>R-104</x:v>
       </x:c>
       <x:c r="B114" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C114" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="D114" s="32" t="str">
-        <x:v>Release qualification suite</x:v>
+        <x:v>Cost guardrails</x:v>
       </x:c>
       <x:c r="E114" s="32" t="str">
-        <x:v>Full regression across supported stack versions before platform releases.</x:v>
+        <x:v>Project/account spending caps, anomaly detection and kill switches.</x:v>
       </x:c>
       <x:c r="F114" s="32" t="str">
         <x:v>P0</x:v>
@@ -14133,7 +14143,7 @@
     </x:row>
     <x:row r="115" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A115" s="32" t="str">
-        <x:v>R-106</x:v>
+        <x:v>R-105</x:v>
       </x:c>
       <x:c r="B115" s="32" t="str">
         <x:v>PRODUCTION</x:v>
@@ -14142,10 +14152,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D115" s="32" t="str">
-        <x:v>Canary platform releases</x:v>
+        <x:v>Release qualification suite</x:v>
       </x:c>
       <x:c r="E115" s="32" t="str">
-        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
+        <x:v>Full regression across supported stack versions before platform releases.</x:v>
       </x:c>
       <x:c r="F115" s="32" t="str">
         <x:v>P0</x:v>
@@ -14165,19 +14175,19 @@
     </x:row>
     <x:row r="116" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A116" s="32" t="str">
-        <x:v>R-107</x:v>
+        <x:v>R-106</x:v>
       </x:c>
       <x:c r="B116" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C116" s="32" t="str">
-        <x:v>Support</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D116" s="32" t="str">
-        <x:v>Support tooling</x:v>
+        <x:v>Canary platform releases</x:v>
       </x:c>
       <x:c r="E116" s="32" t="str">
-        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
+        <x:v>Gradual rollout with automatic rollback on health regression.</x:v>
       </x:c>
       <x:c r="F116" s="32" t="str">
         <x:v>P0</x:v>
@@ -14197,19 +14207,19 @@
     </x:row>
     <x:row r="117" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A117" s="32" t="str">
-        <x:v>R-108</x:v>
+        <x:v>R-107</x:v>
       </x:c>
       <x:c r="B117" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C117" s="32" t="str">
-        <x:v>Legal/Privacy</x:v>
+        <x:v>Support</x:v>
       </x:c>
       <x:c r="D117" s="32" t="str">
-        <x:v>Privacy + retention controls</x:v>
+        <x:v>Support tooling</x:v>
       </x:c>
       <x:c r="E117" s="32" t="str">
-        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+        <x:v>Project-safe diagnostic bundles with secrets redacted.</x:v>
       </x:c>
       <x:c r="F117" s="32" t="str">
         <x:v>P0</x:v>
@@ -14227,2154 +14237,2152 @@
       <x:c r="L117" s="32"/>
       <x:c r="M117" s="32"/>
     </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="43" t="str">
-        <x:v>R-109</x:v>
-      </x:c>
-      <x:c r="B118" s="43" t="str">
+    <x:row r="118" s="40" customFormat="1" ht="34" customHeight="1">
+      <x:c r="A118" s="32" t="str">
+        <x:v>R-108</x:v>
+      </x:c>
+      <x:c r="B118" s="32" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C118" s="43" t="str">
-        <x:v>Business</x:v>
-      </x:c>
-      <x:c r="D118" s="43" t="str">
-        <x:v>Plan entitlements</x:v>
-      </x:c>
-      <x:c r="E118" s="43" t="str">
-        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
-      </x:c>
-      <x:c r="F118" s="43" t="str">
+      <x:c r="C118" s="32" t="str">
+        <x:v>Legal/Privacy</x:v>
+      </x:c>
+      <x:c r="D118" s="32" t="str">
+        <x:v>Privacy + retention controls</x:v>
+      </x:c>
+      <x:c r="E118" s="32" t="str">
+        <x:v>Deletion, export, retention, DPA and subprocessors documented.</x:v>
+      </x:c>
+      <x:c r="F118" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G118" s="43"/>
-      <x:c r="H118" s="43" t="str">
+      <x:c r="G118" s="32"/>
+      <x:c r="H118" s="32" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I118" s="386" t="n">
+      <x:c r="I118" s="376" t="n">
         <x:f>IF(H118="Done",1,IF(H118="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J118" s="43"/>
-      <x:c r="K118" s="43"/>
-      <x:c r="L118" s="43"/>
-      <x:c r="M118" s="43"/>
+      <x:c r="J118" s="32"/>
+      <x:c r="K118" s="32"/>
+      <x:c r="L118" s="32"/>
+      <x:c r="M118" s="32"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="42" t="str">
-        <x:v>R-110</x:v>
-      </x:c>
-      <x:c r="B119" s="42" t="str">
+      <x:c r="A119" s="43" t="str">
+        <x:v>R-109</x:v>
+      </x:c>
+      <x:c r="B119" s="43" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C119" s="42" t="str">
+      <x:c r="C119" s="43" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="D119" s="42" t="str">
-        <x:v>Unit economics dashboard</x:v>
-      </x:c>
-      <x:c r="E119" s="42" t="str">
-        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
-      </x:c>
-      <x:c r="F119" s="42" t="str">
+      <x:c r="D119" s="43" t="str">
+        <x:v>Plan entitlements</x:v>
+      </x:c>
+      <x:c r="E119" s="43" t="str">
+        <x:v>Feature/compute/model limits enforced consistently across plans.</x:v>
+      </x:c>
+      <x:c r="F119" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G119" s="42"/>
-      <x:c r="H119" s="42" t="str">
+      <x:c r="G119" s="43"/>
+      <x:c r="H119" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I119" s="387" t="n">
+      <x:c r="I119" s="386" t="n">
         <x:f>IF(H119="Done",1,IF(H119="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J119" s="42"/>
-      <x:c r="K119" s="42"/>
-      <x:c r="L119" s="42"/>
-      <x:c r="M119" s="42"/>
+      <x:c r="J119" s="43"/>
+      <x:c r="K119" s="43"/>
+      <x:c r="L119" s="43"/>
+      <x:c r="M119" s="43"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="43" t="str">
-        <x:v>R-111</x:v>
-      </x:c>
-      <x:c r="B120" s="43" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C120" s="43" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D120" s="43" t="str">
-        <x:v>Cross-platform Mobile Agent</x:v>
-      </x:c>
-      <x:c r="E120" s="43" t="str">
-        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
-      </x:c>
-      <x:c r="F120" s="43" t="str">
+      <x:c r="A120" s="42" t="str">
+        <x:v>R-110</x:v>
+      </x:c>
+      <x:c r="B120" s="42" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C120" s="42" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="D120" s="42" t="str">
+        <x:v>Unit economics dashboard</x:v>
+      </x:c>
+      <x:c r="E120" s="42" t="str">
+        <x:v>Gross margin by plan, task type, model and compute class.</x:v>
+      </x:c>
+      <x:c r="F120" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G120" s="43"/>
-      <x:c r="H120" s="43" t="str">
+      <x:c r="G120" s="42"/>
+      <x:c r="H120" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I120" s="386" t="n">
+      <x:c r="I120" s="387" t="n">
         <x:f>IF(H120="Done",1,IF(H120="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K120" s="43"/>
-      <x:c r="L120" s="43"/>
-      <x:c r="M120" s="43"/>
+      <x:c r="J120" s="42"/>
+      <x:c r="K120" s="42"/>
+      <x:c r="L120" s="42"/>
+      <x:c r="M120" s="42"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="42" t="str">
-        <x:v>R-112</x:v>
-      </x:c>
-      <x:c r="B121" s="42" t="str">
+      <x:c r="A121" s="43" t="str">
+        <x:v>R-111</x:v>
+      </x:c>
+      <x:c r="B121" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C121" s="42" t="str">
+      <x:c r="C121" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D121" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="E121" s="42" t="str">
-        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
-      </x:c>
-      <x:c r="F121" s="42" t="str">
+      <x:c r="D121" s="43" t="str">
+        <x:v>Cross-platform Mobile Agent</x:v>
+      </x:c>
+      <x:c r="E121" s="43" t="str">
+        <x:v>Generate/modify Flutter or React Native based on selected target adapter; activate only the chosen framework.</x:v>
+      </x:c>
+      <x:c r="F121" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G121" s="42"/>
-      <x:c r="H121" s="42" t="str">
+      <x:c r="G121" s="43"/>
+      <x:c r="H121" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I121" s="387" t="n">
+      <x:c r="I121" s="386" t="n">
         <x:f>IF(H121="Done",1,IF(H121="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="42" t="str">
-        <x:v>Requirement specification step</x:v>
-      </x:c>
-      <x:c r="K121" s="42"/>
-      <x:c r="L121" s="42"/>
-      <x:c r="M121" s="42"/>
+      <x:c r="J121" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K121" s="43"/>
+      <x:c r="L121" s="43"/>
+      <x:c r="M121" s="43"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="43" t="str">
-        <x:v>R-113</x:v>
-      </x:c>
-      <x:c r="B122" s="43" t="str">
+      <x:c r="A122" s="42" t="str">
+        <x:v>R-112</x:v>
+      </x:c>
+      <x:c r="B122" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C122" s="43" t="str">
+      <x:c r="C122" s="42" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D122" s="43" t="str">
-        <x:v>Auto / Recommended project mode</x:v>
-      </x:c>
-      <x:c r="E122" s="43" t="str">
-        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
-      </x:c>
-      <x:c r="F122" s="43" t="str">
+      <x:c r="D122" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="E122" s="42" t="str">
+        <x:v>Score project requirements and recommend Flutter, React Native, Native, or Web/PWA; do not decide only by industry label.</x:v>
+      </x:c>
+      <x:c r="F122" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G122" s="43"/>
-      <x:c r="H122" s="43" t="str">
+      <x:c r="G122" s="42"/>
+      <x:c r="H122" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I122" s="386" t="n">
+      <x:c r="I122" s="387" t="n">
         <x:f>IF(H122="Done",1,IF(H122="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="43" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K122" s="43"/>
-      <x:c r="L122" s="43"/>
-      <x:c r="M122" s="43"/>
+      <x:c r="J122" s="42" t="str">
+        <x:v>Requirement specification step</x:v>
+      </x:c>
+      <x:c r="K122" s="42"/>
+      <x:c r="L122" s="42"/>
+      <x:c r="M122" s="42"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="42" t="str">
-        <x:v>R-114</x:v>
-      </x:c>
-      <x:c r="B123" s="42" t="str">
+      <x:c r="A123" s="43" t="str">
+        <x:v>R-113</x:v>
+      </x:c>
+      <x:c r="B123" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C123" s="42" t="str">
+      <x:c r="C123" s="43" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D123" s="42" t="str">
-        <x:v>Manual framework override</x:v>
-      </x:c>
-      <x:c r="E123" s="42" t="str">
-        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
-      </x:c>
-      <x:c r="F123" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G123" s="42"/>
-      <x:c r="H123" s="42" t="str">
+      <x:c r="D123" s="43" t="str">
+        <x:v>Auto / Recommended project mode</x:v>
+      </x:c>
+      <x:c r="E123" s="43" t="str">
+        <x:v>Default create-project option selects the cheapest safe architecture and explains why.</x:v>
+      </x:c>
+      <x:c r="F123" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G123" s="43"/>
+      <x:c r="H123" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I123" s="387" t="n">
+      <x:c r="I123" s="386" t="n">
         <x:f>IF(H123="Done",1,IF(H123="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J123" s="42" t="str">
+      <x:c r="J123" s="43" t="str">
         <x:v>Framework recommendation engine</x:v>
       </x:c>
-      <x:c r="K123" s="42"/>
-      <x:c r="L123" s="42"/>
-      <x:c r="M123" s="42"/>
+      <x:c r="K123" s="43"/>
+      <x:c r="L123" s="43"/>
+      <x:c r="M123" s="43"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="43" t="str">
-        <x:v>R-115</x:v>
-      </x:c>
-      <x:c r="B124" s="43" t="str">
+      <x:c r="A124" s="42" t="str">
+        <x:v>R-114</x:v>
+      </x:c>
+      <x:c r="B124" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C124" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D124" s="43" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="E124" s="43" t="str">
-        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
-      </x:c>
-      <x:c r="F124" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G124" s="43"/>
-      <x:c r="H124" s="43" t="str">
+      <x:c r="C124" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D124" s="42" t="str">
+        <x:v>Manual framework override</x:v>
+      </x:c>
+      <x:c r="E124" s="42" t="str">
+        <x:v>User can choose Flutter, React Native or Native even when recommendation differs; show cost/risk warning.</x:v>
+      </x:c>
+      <x:c r="F124" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G124" s="42"/>
+      <x:c r="H124" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I124" s="386" t="n">
+      <x:c r="I124" s="387" t="n">
         <x:f>IF(H124="Done",1,IF(H124="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K124" s="43"/>
-      <x:c r="L124" s="43"/>
-      <x:c r="M124" s="43"/>
+      <x:c r="J124" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K124" s="42"/>
+      <x:c r="L124" s="42"/>
+      <x:c r="M124" s="42"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="42" t="str">
-        <x:v>R-116</x:v>
-      </x:c>
-      <x:c r="B125" s="42" t="str">
+      <x:c r="A125" s="43" t="str">
+        <x:v>R-115</x:v>
+      </x:c>
+      <x:c r="B125" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C125" s="42" t="str">
+      <x:c r="C125" s="43" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D125" s="42" t="str">
-        <x:v>Shared-code policy</x:v>
-      </x:c>
-      <x:c r="E125" s="42" t="str">
-        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
-      </x:c>
-      <x:c r="F125" s="42" t="str">
+      <x:c r="D125" s="43" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="E125" s="43" t="str">
+        <x:v>Application IR feeds framework-specific generators through a stable adapter interface so new targets do not change product intent.</x:v>
+      </x:c>
+      <x:c r="F125" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G125" s="42"/>
-      <x:c r="H125" s="42" t="str">
+      <x:c r="G125" s="43"/>
+      <x:c r="H125" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I125" s="387" t="n">
+      <x:c r="I125" s="386" t="n">
         <x:f>IF(H125="Done",1,IF(H125="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J125" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K125" s="42"/>
-      <x:c r="L125" s="42"/>
-      <x:c r="M125" s="42"/>
+      <x:c r="J125" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K125" s="43"/>
+      <x:c r="L125" s="43"/>
+      <x:c r="M125" s="43"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="43" t="str">
-        <x:v>R-117</x:v>
-      </x:c>
-      <x:c r="B126" s="43" t="str">
+      <x:c r="A126" s="42" t="str">
+        <x:v>R-116</x:v>
+      </x:c>
+      <x:c r="B126" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C126" s="43" t="str">
-        <x:v>Web/Admin</x:v>
-      </x:c>
-      <x:c r="D126" s="43" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="E126" s="43" t="str">
-        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
-      </x:c>
-      <x:c r="F126" s="43" t="str">
+      <x:c r="C126" s="42" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D126" s="42" t="str">
+        <x:v>Shared-code policy</x:v>
+      </x:c>
+      <x:c r="E126" s="42" t="str">
+        <x:v>Share contracts, schemas, design tokens, validation and business rules first; share UI/runtime code only when framework safely supports it.</x:v>
+      </x:c>
+      <x:c r="F126" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G126" s="43"/>
-      <x:c r="H126" s="43" t="str">
+      <x:c r="G126" s="42"/>
+      <x:c r="H126" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I126" s="386" t="n">
+      <x:c r="I126" s="387" t="n">
         <x:f>IF(H126="Done",1,IF(H126="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="43" t="str">
-        <x:v>Web/Admin Agent</x:v>
-      </x:c>
-      <x:c r="K126" s="43"/>
-      <x:c r="L126" s="43"/>
-      <x:c r="M126" s="43"/>
+      <x:c r="J126" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K126" s="42"/>
+      <x:c r="L126" s="42"/>
+      <x:c r="M126" s="42"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="42" t="str">
-        <x:v>R-118</x:v>
-      </x:c>
-      <x:c r="B127" s="42" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C127" s="42" t="str">
+      <x:c r="A127" s="43" t="str">
+        <x:v>R-117</x:v>
+      </x:c>
+      <x:c r="B127" s="43" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C127" s="43" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D127" s="42" t="str">
-        <x:v>Flutter Web optional profile</x:v>
-      </x:c>
-      <x:c r="E127" s="42" t="str">
-        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
-      </x:c>
-      <x:c r="F127" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G127" s="42"/>
-      <x:c r="H127" s="42" t="str">
+      <x:c r="D127" s="43" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="E127" s="43" t="str">
+        <x:v>Use Next.js/TypeScript for customer web and admin by default for SEO, desktop UX, accessibility and maintainability.</x:v>
+      </x:c>
+      <x:c r="F127" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G127" s="43"/>
+      <x:c r="H127" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I127" s="387" t="n">
+      <x:c r="I127" s="386" t="n">
         <x:f>IF(H127="Done",1,IF(H127="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J127" s="42" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
-      </x:c>
-      <x:c r="K127" s="42"/>
-      <x:c r="L127" s="42"/>
-      <x:c r="M127" s="42"/>
+      <x:c r="J127" s="43" t="str">
+        <x:v>Web/Admin Agent</x:v>
+      </x:c>
+      <x:c r="K127" s="43"/>
+      <x:c r="L127" s="43"/>
+      <x:c r="M127" s="43"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="43" t="str">
-        <x:v>R-119</x:v>
-      </x:c>
-      <x:c r="B128" s="43" t="str">
+      <x:c r="A128" s="42" t="str">
+        <x:v>R-118</x:v>
+      </x:c>
+      <x:c r="B128" s="42" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C128" s="43" t="str">
+      <x:c r="C128" s="42" t="str">
         <x:v>Web/Admin</x:v>
       </x:c>
-      <x:c r="D128" s="43" t="str">
-        <x:v>React Native Web optional profile</x:v>
-      </x:c>
-      <x:c r="E128" s="43" t="str">
-        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
-      </x:c>
-      <x:c r="F128" s="43" t="str">
+      <x:c r="D128" s="42" t="str">
+        <x:v>Flutter Web optional profile</x:v>
+      </x:c>
+      <x:c r="E128" s="42" t="str">
+        <x:v>Allow Flutter Web for app-like browser experiences when SEO/desktop constraints are acceptable; never force admin panel onto Flutter.</x:v>
+      </x:c>
+      <x:c r="F128" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G128" s="43"/>
-      <x:c r="H128" s="43" t="str">
+      <x:c r="G128" s="42"/>
+      <x:c r="H128" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I128" s="386" t="n">
+      <x:c r="I128" s="387" t="n">
         <x:f>IF(H128="Done",1,IF(H128="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="43" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
-      </x:c>
-      <x:c r="K128" s="43"/>
-      <x:c r="L128" s="43"/>
-      <x:c r="M128" s="43"/>
+      <x:c r="J128" s="42" t="str">
+        <x:v>Flutter target (GA baseline)</x:v>
+      </x:c>
+      <x:c r="K128" s="42"/>
+      <x:c r="L128" s="42"/>
+      <x:c r="M128" s="42"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="42" t="str">
-        <x:v>R-120</x:v>
-      </x:c>
-      <x:c r="B129" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C129" s="42" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D129" s="42" t="str">
-        <x:v>Native recommendation profile</x:v>
-      </x:c>
-      <x:c r="E129" s="42" t="str">
-        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
-      </x:c>
-      <x:c r="F129" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G129" s="42"/>
-      <x:c r="H129" s="42" t="str">
+      <x:c r="A129" s="43" t="str">
+        <x:v>R-119</x:v>
+      </x:c>
+      <x:c r="B129" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C129" s="43" t="str">
+        <x:v>Web/Admin</x:v>
+      </x:c>
+      <x:c r="D129" s="43" t="str">
+        <x:v>React Native Web optional profile</x:v>
+      </x:c>
+      <x:c r="E129" s="43" t="str">
+        <x:v>Allow Expo Web/React Native Web for high code-sharing projects; Next.js remains preferred for SEO-heavy public web and complex admin.</x:v>
+      </x:c>
+      <x:c r="F129" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G129" s="43"/>
+      <x:c r="H129" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I129" s="387" t="n">
+      <x:c r="I129" s="386" t="n">
         <x:f>IF(H129="Done",1,IF(H129="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J129" s="42" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K129" s="42"/>
-      <x:c r="L129" s="42"/>
-      <x:c r="M129" s="42"/>
+      <x:c r="J129" s="43" t="str">
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
+      </x:c>
+      <x:c r="K129" s="43"/>
+      <x:c r="L129" s="43"/>
+      <x:c r="M129" s="43"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="43" t="str">
-        <x:v>R-121</x:v>
-      </x:c>
-      <x:c r="B130" s="43" t="str">
+      <x:c r="A130" s="42" t="str">
+        <x:v>R-120</x:v>
+      </x:c>
+      <x:c r="B130" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C130" s="43" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D130" s="43" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="E130" s="43" t="str">
-        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
-      </x:c>
-      <x:c r="F130" s="43" t="str">
+      <x:c r="C130" s="42" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D130" s="42" t="str">
+        <x:v>Native recommendation profile</x:v>
+      </x:c>
+      <x:c r="E130" s="42" t="str">
+        <x:v>Recommend Kotlin + Swift when deep platform APIs, hardware, background execution, performance, platform UX or compliance needs justify extra cost.</x:v>
+      </x:c>
+      <x:c r="F130" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G130" s="43"/>
-      <x:c r="H130" s="43" t="str">
+      <x:c r="G130" s="42"/>
+      <x:c r="H130" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I130" s="386" t="n">
+      <x:c r="I130" s="387" t="n">
         <x:f>IF(H130="Done",1,IF(H130="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J130" s="43" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K130" s="43"/>
-      <x:c r="L130" s="43"/>
-      <x:c r="M130" s="43"/>
+      <x:c r="J130" s="42" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K130" s="42"/>
+      <x:c r="L130" s="42"/>
+      <x:c r="M130" s="42"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="42" t="str">
-        <x:v>R-122</x:v>
-      </x:c>
-      <x:c r="B131" s="42" t="str">
+      <x:c r="A131" s="43" t="str">
+        <x:v>R-121</x:v>
+      </x:c>
+      <x:c r="B131" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C131" s="42" t="str">
+      <x:c r="C131" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D131" s="42" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="E131" s="42" t="str">
-        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
-      </x:c>
-      <x:c r="F131" s="42" t="str">
+      <x:c r="D131" s="43" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="E131" s="43" t="str">
+        <x:v>Start our own platform in one modular Git monorepo: console, Go services, Python AI services, workers, contracts, infra and docs.</x:v>
+      </x:c>
+      <x:c r="F131" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G131" s="42"/>
-      <x:c r="H131" s="42" t="str">
+      <x:c r="G131" s="43"/>
+      <x:c r="H131" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I131" s="387" t="n">
+      <x:c r="I131" s="386" t="n">
         <x:f>IF(H131="Done",1,IF(H131="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J131" s="42" t="str">
+      <x:c r="J131" s="43" t="str">
         <x:v>Project + workspace model</x:v>
       </x:c>
-      <x:c r="K131" s="42"/>
-      <x:c r="L131" s="42"/>
-      <x:c r="M131" s="42"/>
+      <x:c r="K131" s="43"/>
+      <x:c r="L131" s="43"/>
+      <x:c r="M131" s="43"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="43" t="str">
-        <x:v>R-123</x:v>
-      </x:c>
-      <x:c r="B132" s="43" t="str">
+      <x:c r="A132" s="42" t="str">
+        <x:v>R-122</x:v>
+      </x:c>
+      <x:c r="B132" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C132" s="43" t="str">
+      <x:c r="C132" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D132" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="E132" s="43" t="str">
-        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
-      </x:c>
-      <x:c r="F132" s="43" t="str">
+      <x:c r="D132" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="E132" s="42" t="str">
+        <x:v>Never mix multiple customer apps in one source repo. Each generated project receives its own repository and access boundary.</x:v>
+      </x:c>
+      <x:c r="F132" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G132" s="43"/>
-      <x:c r="H132" s="43" t="str">
+      <x:c r="G132" s="42"/>
+      <x:c r="H132" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I132" s="386" t="n">
+      <x:c r="I132" s="387" t="n">
         <x:f>IF(H132="Done",1,IF(H132="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J132" s="43" t="str">
-        <x:v>One Git repo per customer project</x:v>
-      </x:c>
-      <x:c r="K132" s="43"/>
-      <x:c r="L132" s="43"/>
-      <x:c r="M132" s="43"/>
+      <x:c r="J132" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K132" s="42"/>
+      <x:c r="L132" s="42"/>
+      <x:c r="M132" s="42"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="42" t="str">
-        <x:v>R-124</x:v>
-      </x:c>
-      <x:c r="B133" s="42" t="str">
+      <x:c r="A133" s="43" t="str">
+        <x:v>R-123</x:v>
+      </x:c>
+      <x:c r="B133" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C133" s="42" t="str">
+      <x:c r="C133" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D133" s="42" t="str">
-        <x:v>Repository naming convention</x:v>
-      </x:c>
-      <x:c r="E133" s="42" t="str">
-        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
-      </x:c>
-      <x:c r="F133" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G133" s="42"/>
-      <x:c r="H133" s="42" t="str">
+      <x:c r="D133" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="E133" s="43" t="str">
+        <x:v>Keep mobile, web, admin, backend, database, contracts, infra and tests together so AI changes can be atomic across the product.</x:v>
+      </x:c>
+      <x:c r="F133" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G133" s="43"/>
+      <x:c r="H133" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I133" s="387" t="n">
+      <x:c r="I133" s="386" t="n">
         <x:f>IF(H133="Done",1,IF(H133="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J133" s="42" t="str">
+      <x:c r="J133" s="43" t="str">
         <x:v>One Git repo per customer project</x:v>
       </x:c>
-      <x:c r="K133" s="42"/>
-      <x:c r="L133" s="42"/>
-      <x:c r="M133" s="42"/>
+      <x:c r="K133" s="43"/>
+      <x:c r="L133" s="43"/>
+      <x:c r="M133" s="43"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="43" t="str">
-        <x:v>R-125</x:v>
-      </x:c>
-      <x:c r="B134" s="43" t="str">
+      <x:c r="A134" s="42" t="str">
+        <x:v>R-124</x:v>
+      </x:c>
+      <x:c r="B134" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C134" s="43" t="str">
+      <x:c r="C134" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D134" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="E134" s="43" t="str">
-        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
-      </x:c>
-      <x:c r="F134" s="43" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G134" s="43"/>
-      <x:c r="H134" s="43" t="str">
+      <x:c r="D134" s="42" t="str">
+        <x:v>Repository naming convention</x:v>
+      </x:c>
+      <x:c r="E134" s="42" t="str">
+        <x:v>Default repo name: project-&lt;project-slug&gt;; allow workspace prefix and customer-owned Git organization.</x:v>
+      </x:c>
+      <x:c r="F134" s="42" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G134" s="42"/>
+      <x:c r="H134" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I134" s="386" t="n">
+      <x:c r="I134" s="387" t="n">
         <x:f>IF(H134="Done",1,IF(H134="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J134" s="43" t="str">
-        <x:v>Branch per task</x:v>
-      </x:c>
-      <x:c r="K134" s="43"/>
-      <x:c r="L134" s="43"/>
-      <x:c r="M134" s="43"/>
+      <x:c r="J134" s="42" t="str">
+        <x:v>One Git repo per customer project</x:v>
+      </x:c>
+      <x:c r="K134" s="42"/>
+      <x:c r="L134" s="42"/>
+      <x:c r="M134" s="42"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="42" t="str">
-        <x:v>R-126</x:v>
-      </x:c>
-      <x:c r="B135" s="42" t="str">
+      <x:c r="A135" s="43" t="str">
+        <x:v>R-125</x:v>
+      </x:c>
+      <x:c r="B135" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C135" s="42" t="str">
-        <x:v>Product Foundation</x:v>
-      </x:c>
-      <x:c r="D135" s="42" t="str">
-        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
-      </x:c>
-      <x:c r="E135" s="42" t="str">
-        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
-      </x:c>
-      <x:c r="F135" s="42" t="str">
+      <x:c r="C135" s="43" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D135" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="E135" s="43" t="str">
+        <x:v>Use short-lived ai/&lt;task-id&gt;-&lt;slug&gt; branches, protected main, task-linked commits and one reviewable PR/change set per AI task.</x:v>
+      </x:c>
+      <x:c r="F135" s="43" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G135" s="42"/>
-      <x:c r="H135" s="42" t="str">
+      <x:c r="G135" s="43"/>
+      <x:c r="H135" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I135" s="387" t="n">
+      <x:c r="I135" s="386" t="n">
         <x:f>IF(H135="Done",1,IF(H135="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J135" s="42" t="str">
-        <x:v>Project + workspace model</x:v>
-      </x:c>
-      <x:c r="K135" s="42"/>
-      <x:c r="L135" s="42"/>
-      <x:c r="M135" s="42"/>
+      <x:c r="J135" s="43" t="str">
+        <x:v>Branch per task</x:v>
+      </x:c>
+      <x:c r="K135" s="43"/>
+      <x:c r="L135" s="43"/>
+      <x:c r="M135" s="43"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="43" t="str">
-        <x:v>R-127</x:v>
-      </x:c>
-      <x:c r="B136" s="43" t="str">
+      <x:c r="A136" s="42" t="str">
+        <x:v>R-126</x:v>
+      </x:c>
+      <x:c r="B136" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C136" s="43" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D136" s="43" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="E136" s="43" t="str">
-        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
-      </x:c>
-      <x:c r="F136" s="43" t="str">
+      <x:c r="C136" s="42" t="str">
+        <x:v>Product Foundation</x:v>
+      </x:c>
+      <x:c r="D136" s="42" t="str">
+        <x:v>Organization &gt; Workspace &gt; Project &gt; Environment model</x:v>
+      </x:c>
+      <x:c r="E136" s="42" t="str">
+        <x:v>Canonical hierarchy for tenancy, billing, permissions, repositories, targets and deployments.</x:v>
+      </x:c>
+      <x:c r="F136" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G136" s="43"/>
-      <x:c r="H136" s="43" t="str">
+      <x:c r="G136" s="42"/>
+      <x:c r="H136" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I136" s="386" t="n">
+      <x:c r="I136" s="387" t="n">
         <x:f>IF(H136="Done",1,IF(H136="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J136" s="43" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K136" s="43"/>
-      <x:c r="L136" s="43"/>
-      <x:c r="M136" s="43"/>
+      <x:c r="J136" s="42" t="str">
+        <x:v>Project + workspace model</x:v>
+      </x:c>
+      <x:c r="K136" s="42"/>
+      <x:c r="L136" s="42"/>
+      <x:c r="M136" s="42"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="42" t="str">
-        <x:v>R-128</x:v>
-      </x:c>
-      <x:c r="B137" s="42" t="str">
+      <x:c r="A137" s="43" t="str">
+        <x:v>R-127</x:v>
+      </x:c>
+      <x:c r="B137" s="43" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C137" s="42" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D137" s="42" t="str">
-        <x:v>Cross-language monorepo orchestration</x:v>
-      </x:c>
-      <x:c r="E137" s="42" t="str">
-        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
-      </x:c>
-      <x:c r="F137" s="42" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G137" s="42"/>
-      <x:c r="H137" s="42" t="str">
+      <x:c r="C137" s="43" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D137" s="43" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="E137" s="43" t="str">
+        <x:v>Generate OpenAPI/AsyncAPI/schema contracts and typed clients for Flutter/Dart, TypeScript, Kotlin and Swift as needed.</x:v>
+      </x:c>
+      <x:c r="F137" s="43" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G137" s="43"/>
+      <x:c r="H137" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I137" s="387" t="n">
+      <x:c r="I137" s="386" t="n">
         <x:f>IF(H137="Done",1,IF(H137="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J137" s="42" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K137" s="42"/>
-      <x:c r="L137" s="42"/>
-      <x:c r="M137" s="42"/>
+      <x:c r="J137" s="43" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K137" s="43"/>
+      <x:c r="L137" s="43"/>
+      <x:c r="M137" s="43"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="43" t="str">
-        <x:v>R-129</x:v>
-      </x:c>
-      <x:c r="B138" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C138" s="43" t="str">
+      <x:c r="A138" s="42" t="str">
+        <x:v>R-128</x:v>
+      </x:c>
+      <x:c r="B138" s="42" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C138" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D138" s="43" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="E138" s="43" t="str">
-        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
-      </x:c>
-      <x:c r="F138" s="43" t="str">
+      <x:c r="D138" s="42" t="str">
+        <x:v>Cross-language monorepo orchestration</x:v>
+      </x:c>
+      <x:c r="E138" s="42" t="str">
+        <x:v>Use root Taskfile/Make; pnpm/Turborepo for TypeScript, Go workspaces for Go and uv/Poetry for Python; avoid Bazel until scale demands it.</x:v>
+      </x:c>
+      <x:c r="F138" s="42" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G138" s="43"/>
-      <x:c r="H138" s="43" t="str">
+      <x:c r="G138" s="42"/>
+      <x:c r="H138" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I138" s="386" t="n">
+      <x:c r="I138" s="387" t="n">
         <x:f>IF(H138="Done",1,IF(H138="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J138" s="43" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K138" s="43"/>
-      <x:c r="L138" s="43"/>
-      <x:c r="M138" s="43"/>
+      <x:c r="J138" s="42" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K138" s="42"/>
+      <x:c r="L138" s="42"/>
+      <x:c r="M138" s="42"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="42" t="str">
-        <x:v>R-130</x:v>
-      </x:c>
-      <x:c r="B139" s="42" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C139" s="42" t="str">
+      <x:c r="A139" s="43" t="str">
+        <x:v>R-129</x:v>
+      </x:c>
+      <x:c r="B139" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C139" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D139" s="42" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="E139" s="42" t="str">
-        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
-      </x:c>
-      <x:c r="F139" s="42" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G139" s="42"/>
-      <x:c r="H139" s="42" t="str">
+      <x:c r="D139" s="43" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="E139" s="43" t="str">
+        <x:v>Split a customer monorepo only for independent teams, compliance boundaries, release cadence, access control or measured build/repo scale.</x:v>
+      </x:c>
+      <x:c r="F139" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G139" s="43"/>
+      <x:c r="H139" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I139" s="387" t="n">
+      <x:c r="I139" s="386" t="n">
         <x:f>IF(H139="Done",1,IF(H139="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J139" s="42" t="str">
-        <x:v>Repository split decision policy</x:v>
-      </x:c>
-      <x:c r="K139" s="42"/>
-      <x:c r="L139" s="42"/>
-      <x:c r="M139" s="42"/>
+      <x:c r="J139" s="43" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K139" s="43"/>
+      <x:c r="L139" s="43"/>
+      <x:c r="M139" s="43"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="43" t="str">
-        <x:v>R-131</x:v>
-      </x:c>
-      <x:c r="B140" s="43" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C140" s="43" t="str">
+      <x:c r="A140" s="42" t="str">
+        <x:v>R-130</x:v>
+      </x:c>
+      <x:c r="B140" s="42" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C140" s="42" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D140" s="43" t="str">
-        <x:v>CODEOWNERS + protected paths</x:v>
-      </x:c>
-      <x:c r="E140" s="43" t="str">
-        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
-      </x:c>
-      <x:c r="F140" s="43" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G140" s="43"/>
-      <x:c r="H140" s="43" t="str">
+      <x:c r="D140" s="42" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="E140" s="42" t="str">
+        <x:v>Support service-per-repo or domain repos while preserving IR, contracts and cross-repo change orchestration.</x:v>
+      </x:c>
+      <x:c r="F140" s="42" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G140" s="42"/>
+      <x:c r="H140" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I140" s="386" t="n">
+      <x:c r="I140" s="387" t="n">
         <x:f>IF(H140="Done",1,IF(H140="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J140" s="43" t="str">
-        <x:v>Branch + PR naming convention</x:v>
-      </x:c>
-      <x:c r="K140" s="43"/>
-      <x:c r="L140" s="43"/>
-      <x:c r="M140" s="43"/>
+      <x:c r="J140" s="42" t="str">
+        <x:v>Repository split decision policy</x:v>
+      </x:c>
+      <x:c r="K140" s="42"/>
+      <x:c r="L140" s="42"/>
+      <x:c r="M140" s="42"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="42" t="str">
-        <x:v>R-132</x:v>
-      </x:c>
-      <x:c r="B141" s="42" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C141" s="42" t="str">
+      <x:c r="A141" s="43" t="str">
+        <x:v>R-131</x:v>
+      </x:c>
+      <x:c r="B141" s="43" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C141" s="43" t="str">
         <x:v>Git/Repository</x:v>
       </x:c>
-      <x:c r="D141" s="42" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="E141" s="42" t="str">
-        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
-      </x:c>
-      <x:c r="F141" s="42" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G141" s="42"/>
-      <x:c r="H141" s="42" t="str">
+      <x:c r="D141" s="43" t="str">
+        <x:v>CODEOWNERS + protected paths</x:v>
+      </x:c>
+      <x:c r="E141" s="43" t="str">
+        <x:v>Require human/security ownership for sensitive modules, production infra, auth, billing and signing workflows.</x:v>
+      </x:c>
+      <x:c r="F141" s="43" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G141" s="43"/>
+      <x:c r="H141" s="43" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I141" s="387" t="n">
+      <x:c r="I141" s="386" t="n">
         <x:f>IF(H141="Done",1,IF(H141="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J141" s="42" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K141" s="42"/>
-      <x:c r="L141" s="42"/>
-      <x:c r="M141" s="42"/>
+      <x:c r="J141" s="43" t="str">
+        <x:v>Branch + PR naming convention</x:v>
+      </x:c>
+      <x:c r="K141" s="43"/>
+      <x:c r="L141" s="43"/>
+      <x:c r="M141" s="43"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="66" t="str">
-        <x:v>R-133</x:v>
-      </x:c>
-      <x:c r="B142" s="66" t="str">
+      <x:c r="A142" s="42" t="str">
+        <x:v>R-132</x:v>
+      </x:c>
+      <x:c r="B142" s="42" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C142" s="66" t="str">
-        <x:v>Change Safety</x:v>
-      </x:c>
-      <x:c r="D142" s="66" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="E142" s="66" t="str">
-        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
-      </x:c>
-      <x:c r="F142" s="66" t="str">
+      <x:c r="C142" s="42" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D142" s="42" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="E142" s="42" t="str">
+        <x:v>Provide Flutter, React Native and Native directory templates behind the same canonical project structure.</x:v>
+      </x:c>
+      <x:c r="F142" s="42" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G142" s="66"/>
-      <x:c r="H142" s="66" t="str">
+      <x:c r="G142" s="42"/>
+      <x:c r="H142" s="42" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I142" s="388" t="n">
+      <x:c r="I142" s="387" t="n">
         <x:f>IF(H142="Done",1,IF(H142="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J142" s="66" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K142" s="66"/>
-      <x:c r="L142" s="66"/>
-      <x:c r="M142" s="66"/>
+      <x:c r="J142" s="42" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K142" s="42"/>
+      <x:c r="L142" s="42"/>
+      <x:c r="M142" s="42"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="65" t="str">
-        <x:v>R-134</x:v>
-      </x:c>
-      <x:c r="B143" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C143" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D143" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="E143" s="65" t="str">
-        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
-      </x:c>
-      <x:c r="F143" s="65" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G143" s="65"/>
-      <x:c r="H143" s="65" t="str">
+      <x:c r="A143" s="66" t="str">
+        <x:v>R-133</x:v>
+      </x:c>
+      <x:c r="B143" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C143" s="66" t="str">
+        <x:v>Change Safety</x:v>
+      </x:c>
+      <x:c r="D143" s="66" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="E143" s="66" t="str">
+        <x:v>One task can update mobile + web + backend + schema + tests in one branch; merge only if all required target gates pass.</x:v>
+      </x:c>
+      <x:c r="F143" s="66" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G143" s="66"/>
+      <x:c r="H143" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I143" s="389" t="n">
+      <x:c r="I143" s="388" t="n">
         <x:f>IF(H143="Done",1,IF(H143="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J143" s="65" t="str">
-        <x:v>Build artifact caching</x:v>
-      </x:c>
-      <x:c r="K143" s="65"/>
-      <x:c r="L143" s="65"/>
-      <x:c r="M143" s="65"/>
+      <x:c r="J143" s="66" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K143" s="66"/>
+      <x:c r="L143" s="66"/>
+      <x:c r="M143" s="66"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="66" t="str">
-        <x:v>R-135</x:v>
-      </x:c>
-      <x:c r="B144" s="66" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C144" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D144" s="66" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="E144" s="66" t="str">
-        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
-      </x:c>
-      <x:c r="F144" s="66" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G144" s="66"/>
-      <x:c r="H144" s="66" t="str">
+      <x:c r="A144" s="65" t="str">
+        <x:v>R-134</x:v>
+      </x:c>
+      <x:c r="B144" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C144" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D144" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="E144" s="65" t="str">
+        <x:v>Track repo size, dependency graph growth, build duration, cache hit rate and split-repo trigger thresholds.</x:v>
+      </x:c>
+      <x:c r="F144" s="65" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G144" s="65"/>
+      <x:c r="H144" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I144" s="388" t="n">
+      <x:c r="I144" s="389" t="n">
         <x:f>IF(H144="Done",1,IF(H144="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J144" s="66" t="str">
-        <x:v>Framework recommendation engine</x:v>
-      </x:c>
-      <x:c r="K144" s="66"/>
-      <x:c r="L144" s="66"/>
-      <x:c r="M144" s="66" t="str">
-        <x:v>V3</x:v>
-      </x:c>
+      <x:c r="J144" s="65" t="str">
+        <x:v>Build artifact caching</x:v>
+      </x:c>
+      <x:c r="K144" s="65"/>
+      <x:c r="L144" s="65"/>
+      <x:c r="M144" s="65"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="65" t="str">
-        <x:v>R-136</x:v>
-      </x:c>
-      <x:c r="B145" s="65" t="str">
+      <x:c r="A145" s="66" t="str">
+        <x:v>R-135</x:v>
+      </x:c>
+      <x:c r="B145" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C145" s="65" t="str">
+      <x:c r="C145" s="66" t="str">
         <x:v>Framework Strategy</x:v>
       </x:c>
-      <x:c r="D145" s="65" t="str">
-        <x:v>Recommendation score model</x:v>
-      </x:c>
-      <x:c r="E145" s="65" t="str">
-        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
-      </x:c>
-      <x:c r="F145" s="65" t="str">
+      <x:c r="D145" s="66" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="E145" s="66" t="str">
+        <x:v>Before generation, show Auto / Flutter / React Native / Native / Web-only options with simple reasons, cost class and limitations.</x:v>
+      </x:c>
+      <x:c r="F145" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G145" s="65"/>
-      <x:c r="H145" s="65" t="str">
+      <x:c r="G145" s="66"/>
+      <x:c r="H145" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I145" s="389" t="n">
+      <x:c r="I145" s="388" t="n">
         <x:f>IF(H145="Done",1,IF(H145="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J145" s="65" t="str">
-        <x:v>Stack selection wizard</x:v>
-      </x:c>
-      <x:c r="K145" s="65"/>
-      <x:c r="L145" s="65"/>
-      <x:c r="M145" s="65" t="str">
-        <x:v>Do not choose by industry label alone.</x:v>
+      <x:c r="J145" s="66" t="str">
+        <x:v>Framework recommendation engine</x:v>
+      </x:c>
+      <x:c r="K145" s="66"/>
+      <x:c r="L145" s="66"/>
+      <x:c r="M145" s="66" t="str">
+        <x:v>V3</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="66" t="str">
-        <x:v>R-137</x:v>
-      </x:c>
-      <x:c r="B146" s="66" t="str">
+      <x:c r="A146" s="65" t="str">
+        <x:v>R-136</x:v>
+      </x:c>
+      <x:c r="B146" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C146" s="66" t="str">
-        <x:v>Architecture</x:v>
-      </x:c>
-      <x:c r="D146" s="66" t="str">
-        <x:v>Code sharing policy</x:v>
-      </x:c>
-      <x:c r="E146" s="66" t="str">
-        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
-      </x:c>
-      <x:c r="F146" s="66" t="str">
+      <x:c r="C146" s="65" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D146" s="65" t="str">
+        <x:v>Recommendation score model</x:v>
+      </x:c>
+      <x:c r="E146" s="65" t="str">
+        <x:v>Score budget, team skills, web reuse, native APIs, background work, performance, hardware and platform UX. Store score/reasons in IR.</x:v>
+      </x:c>
+      <x:c r="F146" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G146" s="66"/>
-      <x:c r="H146" s="66" t="str">
+      <x:c r="G146" s="65"/>
+      <x:c r="H146" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I146" s="388" t="n">
+      <x:c r="I146" s="389" t="n">
         <x:f>IF(H146="Done",1,IF(H146="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J146" s="66" t="str">
-        <x:v>Application IR v1</x:v>
-      </x:c>
-      <x:c r="K146" s="66"/>
-      <x:c r="L146" s="66"/>
-      <x:c r="M146" s="66" t="str">
-        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
+      <x:c r="J146" s="65" t="str">
+        <x:v>Stack selection wizard</x:v>
+      </x:c>
+      <x:c r="K146" s="65"/>
+      <x:c r="L146" s="65"/>
+      <x:c r="M146" s="65" t="str">
+        <x:v>Do not choose by industry label alone.</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="65" t="str">
-        <x:v>R-138</x:v>
-      </x:c>
-      <x:c r="B147" s="65" t="str">
+      <x:c r="A147" s="66" t="str">
+        <x:v>R-137</x:v>
+      </x:c>
+      <x:c r="B147" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C147" s="65" t="str">
+      <x:c r="C147" s="66" t="str">
         <x:v>Architecture</x:v>
       </x:c>
-      <x:c r="D147" s="65" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="E147" s="65" t="str">
-        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
-      </x:c>
-      <x:c r="F147" s="65" t="str">
+      <x:c r="D147" s="66" t="str">
+        <x:v>Code sharing policy</x:v>
+      </x:c>
+      <x:c r="E147" s="66" t="str">
+        <x:v>Share IR, contracts, tokens, localization, analytics and compatible domain packages; never force 100% runtime sharing.</x:v>
+      </x:c>
+      <x:c r="F147" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G147" s="65"/>
-      <x:c r="H147" s="65" t="str">
+      <x:c r="G147" s="66"/>
+      <x:c r="H147" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I147" s="389" t="n">
+      <x:c r="I147" s="388" t="n">
         <x:f>IF(H147="Done",1,IF(H147="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J147" s="65" t="str">
-        <x:v>Customer project monorepo default</x:v>
-      </x:c>
-      <x:c r="K147" s="65"/>
-      <x:c r="L147" s="65"/>
-      <x:c r="M147" s="65" t="str">
-        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
+      <x:c r="J147" s="66" t="str">
+        <x:v>Application IR v1</x:v>
+      </x:c>
+      <x:c r="K147" s="66"/>
+      <x:c r="L147" s="66"/>
+      <x:c r="M147" s="66" t="str">
+        <x:v>Prevents bad Flutter/RN Web/admin decisions.</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="66" t="str">
-        <x:v>R-139</x:v>
-      </x:c>
-      <x:c r="B148" s="66" t="str">
+      <x:c r="A148" s="65" t="str">
+        <x:v>R-138</x:v>
+      </x:c>
+      <x:c r="B148" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C148" s="66" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D148" s="66" t="str">
-        <x:v>Root task commands</x:v>
-      </x:c>
-      <x:c r="E148" s="66" t="str">
-        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
-      </x:c>
-      <x:c r="F148" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G148" s="66"/>
-      <x:c r="H148" s="66" t="str">
+      <x:c r="C148" s="65" t="str">
+        <x:v>Architecture</x:v>
+      </x:c>
+      <x:c r="D148" s="65" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="E148" s="65" t="str">
+        <x:v>Standard root: .ai/, apps/, services/, packages/, database/, infra/, tests/, docs/, scripts/.</x:v>
+      </x:c>
+      <x:c r="F148" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G148" s="65"/>
+      <x:c r="H148" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I148" s="388" t="n">
+      <x:c r="I148" s="389" t="n">
         <x:f>IF(H148="Done",1,IF(H148="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J148" s="66" t="str">
-        <x:v>Canonical generated project root</x:v>
-      </x:c>
-      <x:c r="K148" s="66"/>
-      <x:c r="L148" s="66"/>
-      <x:c r="M148" s="66" t="str">
-        <x:v>Framework-independent agent commands.</x:v>
+      <x:c r="J148" s="65" t="str">
+        <x:v>Customer project monorepo default</x:v>
+      </x:c>
+      <x:c r="K148" s="65"/>
+      <x:c r="L148" s="65"/>
+      <x:c r="M148" s="65" t="str">
+        <x:v>Stable paths improve AI context and developer onboarding.</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="65" t="str">
-        <x:v>R-140</x:v>
-      </x:c>
-      <x:c r="B149" s="65" t="str">
+      <x:c r="A149" s="66" t="str">
+        <x:v>R-139</x:v>
+      </x:c>
+      <x:c r="B149" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C149" s="65" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D149" s="65" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="E149" s="65" t="str">
-        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
-      </x:c>
-      <x:c r="F149" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G149" s="65"/>
-      <x:c r="H149" s="65" t="str">
+      <x:c r="C149" s="66" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D149" s="66" t="str">
+        <x:v>Root task commands</x:v>
+      </x:c>
+      <x:c r="E149" s="66" t="str">
+        <x:v>Every project exposes bootstrap, lint, test, build, check, preview and ci through Taskfile/Make.</x:v>
+      </x:c>
+      <x:c r="F149" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G149" s="66"/>
+      <x:c r="H149" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I149" s="389" t="n">
+      <x:c r="I149" s="388" t="n">
         <x:f>IF(H149="Done",1,IF(H149="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J149" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K149" s="65"/>
-      <x:c r="L149" s="65"/>
-      <x:c r="M149" s="65" t="str">
-        <x:v>Stable target.</x:v>
+      <x:c r="J149" s="66" t="str">
+        <x:v>Canonical generated project root</x:v>
+      </x:c>
+      <x:c r="K149" s="66"/>
+      <x:c r="L149" s="66"/>
+      <x:c r="M149" s="66" t="str">
+        <x:v>Framework-independent agent commands.</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="66" t="str">
-        <x:v>R-141</x:v>
-      </x:c>
-      <x:c r="B150" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C150" s="66" t="str">
+      <x:c r="A150" s="65" t="str">
+        <x:v>R-140</x:v>
+      </x:c>
+      <x:c r="B150" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C150" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D150" s="66" t="str">
-        <x:v>Flutter scaled template</x:v>
-      </x:c>
-      <x:c r="E150" s="66" t="str">
-        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
-      </x:c>
-      <x:c r="F150" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G150" s="66"/>
-      <x:c r="H150" s="66" t="str">
+      <x:c r="D150" s="65" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="E150" s="65" t="str">
+        <x:v>Feature-first Flutter template with app/core/design_system/features/test; avoid unnecessary domain layers in simple apps.</x:v>
+      </x:c>
+      <x:c r="F150" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G150" s="65"/>
+      <x:c r="H150" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I150" s="388" t="n">
+      <x:c r="I150" s="389" t="n">
         <x:f>IF(H150="Done",1,IF(H150="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J150" s="66" t="str">
-        <x:v>Flutter lean template</x:v>
-      </x:c>
-      <x:c r="K150" s="66"/>
-      <x:c r="L150" s="66"/>
-      <x:c r="M150" s="66" t="str">
-        <x:v>Use only when complexity warrants.</x:v>
+      <x:c r="J150" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K150" s="65"/>
+      <x:c r="L150" s="65"/>
+      <x:c r="M150" s="65" t="str">
+        <x:v>Stable target.</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="65" t="str">
-        <x:v>R-142</x:v>
-      </x:c>
-      <x:c r="B151" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C151" s="65" t="str">
+      <x:c r="A151" s="66" t="str">
+        <x:v>R-141</x:v>
+      </x:c>
+      <x:c r="B151" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C151" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D151" s="65" t="str">
-        <x:v>React Native TypeScript template</x:v>
-      </x:c>
-      <x:c r="E151" s="65" t="str">
-        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
-      </x:c>
-      <x:c r="F151" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G151" s="65"/>
-      <x:c r="H151" s="65" t="str">
+      <x:c r="D151" s="66" t="str">
+        <x:v>Flutter scaled template</x:v>
+      </x:c>
+      <x:c r="E151" s="66" t="str">
+        <x:v>Scaled Flutter structure with stronger feature/domain boundaries and approved native adapters.</x:v>
+      </x:c>
+      <x:c r="F151" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G151" s="66"/>
+      <x:c r="H151" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I151" s="389" t="n">
+      <x:c r="I151" s="388" t="n">
         <x:f>IF(H151="Done",1,IF(H151="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J151" s="65" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K151" s="65"/>
-      <x:c r="L151" s="65"/>
-      <x:c r="M151" s="65" t="str">
-        <x:v>Expo profile when capabilities fit.</x:v>
+      <x:c r="J151" s="66" t="str">
+        <x:v>Flutter lean template</x:v>
+      </x:c>
+      <x:c r="K151" s="66"/>
+      <x:c r="L151" s="66"/>
+      <x:c r="M151" s="66" t="str">
+        <x:v>Use only when complexity warrants.</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="66" t="str">
-        <x:v>R-143</x:v>
-      </x:c>
-      <x:c r="B152" s="66" t="str">
+      <x:c r="A152" s="65" t="str">
+        <x:v>R-142</x:v>
+      </x:c>
+      <x:c r="B152" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C152" s="66" t="str">
+      <x:c r="C152" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D152" s="66" t="str">
-        <x:v>React Native shared TS packages</x:v>
-      </x:c>
-      <x:c r="E152" s="66" t="str">
-        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
-      </x:c>
-      <x:c r="F152" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G152" s="66"/>
-      <x:c r="H152" s="66" t="str">
+      <x:c r="D152" s="65" t="str">
+        <x:v>React Native TypeScript template</x:v>
+      </x:c>
+      <x:c r="E152" s="65" t="str">
+        <x:v>Feature-first RN template with app/features/shared/design-system and explicit native module boundaries.</x:v>
+      </x:c>
+      <x:c r="F152" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G152" s="65"/>
+      <x:c r="H152" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I152" s="388" t="n">
+      <x:c r="I152" s="389" t="n">
         <x:f>IF(H152="Done",1,IF(H152="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J152" s="66" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K152" s="66"/>
-      <x:c r="L152" s="66"/>
-      <x:c r="M152" s="66" t="str">
-        <x:v>Do not share UI blindly.</x:v>
+      <x:c r="J152" s="65" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K152" s="65"/>
+      <x:c r="L152" s="65"/>
+      <x:c r="M152" s="65" t="str">
+        <x:v>Expo profile when capabilities fit.</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="65" t="str">
-        <x:v>R-144</x:v>
-      </x:c>
-      <x:c r="B153" s="65" t="str">
+      <x:c r="A153" s="66" t="str">
+        <x:v>R-143</x:v>
+      </x:c>
+      <x:c r="B153" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C153" s="65" t="str">
+      <x:c r="C153" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D153" s="65" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="E153" s="65" t="str">
-        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
-      </x:c>
-      <x:c r="F153" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G153" s="65"/>
-      <x:c r="H153" s="65" t="str">
+      <x:c r="D153" s="66" t="str">
+        <x:v>React Native shared TS packages</x:v>
+      </x:c>
+      <x:c r="E153" s="66" t="str">
+        <x:v>Root contracts/validation/api-client packages reusable by RN and Next.js where runtime compatibility is safe.</x:v>
+      </x:c>
+      <x:c r="F153" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G153" s="66"/>
+      <x:c r="H153" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I153" s="389" t="n">
+      <x:c r="I153" s="388" t="n">
         <x:f>IF(H153="Done",1,IF(H153="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J153" s="65" t="str">
-        <x:v>Native Android Agent</x:v>
-      </x:c>
-      <x:c r="K153" s="65"/>
-      <x:c r="L153" s="65"/>
-      <x:c r="M153" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J153" s="66" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K153" s="66"/>
+      <x:c r="L153" s="66"/>
+      <x:c r="M153" s="66" t="str">
+        <x:v>Do not share UI blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="66" t="str">
-        <x:v>R-145</x:v>
-      </x:c>
-      <x:c r="B154" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C154" s="66" t="str">
+      <x:c r="A154" s="65" t="str">
+        <x:v>R-144</x:v>
+      </x:c>
+      <x:c r="B154" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C154" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D154" s="66" t="str">
-        <x:v>Native Android scaled modules</x:v>
-      </x:c>
-      <x:c r="E154" s="66" t="str">
-        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
-      </x:c>
-      <x:c r="F154" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G154" s="66"/>
-      <x:c r="H154" s="66" t="str">
+      <x:c r="D154" s="65" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="E154" s="65" t="str">
+        <x:v>Kotlin/Compose template with thin app + core infrastructure and feature-first structure; avoid over-modularization.</x:v>
+      </x:c>
+      <x:c r="F154" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G154" s="65"/>
+      <x:c r="H154" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I154" s="388" t="n">
+      <x:c r="I154" s="389" t="n">
         <x:f>IF(H154="Done",1,IF(H154="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J154" s="66" t="str">
-        <x:v>Native Android lean template</x:v>
-      </x:c>
-      <x:c r="K154" s="66"/>
-      <x:c r="L154" s="66"/>
-      <x:c r="M154" s="66" t="str">
-        <x:v>Experienced team structure.</x:v>
+      <x:c r="J154" s="65" t="str">
+        <x:v>Native Android Agent</x:v>
+      </x:c>
+      <x:c r="K154" s="65"/>
+      <x:c r="L154" s="65"/>
+      <x:c r="M154" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="65" t="str">
-        <x:v>R-146</x:v>
-      </x:c>
-      <x:c r="B155" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C155" s="65" t="str">
+      <x:c r="A155" s="66" t="str">
+        <x:v>R-145</x:v>
+      </x:c>
+      <x:c r="B155" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C155" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D155" s="65" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="E155" s="65" t="str">
-        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
-      </x:c>
-      <x:c r="F155" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G155" s="65"/>
-      <x:c r="H155" s="65" t="str">
+      <x:c r="D155" s="66" t="str">
+        <x:v>Native Android scaled modules</x:v>
+      </x:c>
+      <x:c r="E155" s="66" t="str">
+        <x:v>Add core/designsystem/network/database/testing + feature modules + Gradle convention plugins/version catalog when scale justifies.</x:v>
+      </x:c>
+      <x:c r="F155" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G155" s="66"/>
+      <x:c r="H155" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I155" s="389" t="n">
+      <x:c r="I155" s="388" t="n">
         <x:f>IF(H155="Done",1,IF(H155="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J155" s="65" t="str">
-        <x:v>Native iOS Agent</x:v>
-      </x:c>
-      <x:c r="K155" s="65"/>
-      <x:c r="L155" s="65"/>
-      <x:c r="M155" s="65" t="str">
-        <x:v>Native selectable beta.</x:v>
+      <x:c r="J155" s="66" t="str">
+        <x:v>Native Android lean template</x:v>
+      </x:c>
+      <x:c r="K155" s="66"/>
+      <x:c r="L155" s="66"/>
+      <x:c r="M155" s="66" t="str">
+        <x:v>Experienced team structure.</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="66" t="str">
-        <x:v>R-147</x:v>
-      </x:c>
-      <x:c r="B156" s="66" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C156" s="66" t="str">
+      <x:c r="A156" s="65" t="str">
+        <x:v>R-146</x:v>
+      </x:c>
+      <x:c r="B156" s="65" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C156" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D156" s="66" t="str">
-        <x:v>Native iOS scaled Swift Packages</x:v>
-      </x:c>
-      <x:c r="E156" s="66" t="str">
-        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
-      </x:c>
-      <x:c r="F156" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G156" s="66"/>
-      <x:c r="H156" s="66" t="str">
+      <x:c r="D156" s="65" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="E156" s="65" t="str">
+        <x:v>SwiftUI template with App/Core/Features/Tests, async-await, Keychain, DI composition roots.</x:v>
+      </x:c>
+      <x:c r="F156" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G156" s="65"/>
+      <x:c r="H156" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I156" s="388" t="n">
+      <x:c r="I156" s="389" t="n">
         <x:f>IF(H156="Done",1,IF(H156="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J156" s="66" t="str">
-        <x:v>Native iOS lean template</x:v>
-      </x:c>
-      <x:c r="K156" s="66"/>
-      <x:c r="L156" s="66"/>
-      <x:c r="M156" s="66" t="str">
-        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
+      <x:c r="J156" s="65" t="str">
+        <x:v>Native iOS Agent</x:v>
+      </x:c>
+      <x:c r="K156" s="65"/>
+      <x:c r="L156" s="65"/>
+      <x:c r="M156" s="65" t="str">
+        <x:v>Native selectable beta.</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="65" t="str">
-        <x:v>R-148</x:v>
-      </x:c>
-      <x:c r="B157" s="65" t="str">
-        <x:v>MVP</x:v>
-      </x:c>
-      <x:c r="C157" s="65" t="str">
+      <x:c r="A157" s="66" t="str">
+        <x:v>R-147</x:v>
+      </x:c>
+      <x:c r="B157" s="66" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C157" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D157" s="65" t="str">
-        <x:v>Next.js public web template</x:v>
-      </x:c>
-      <x:c r="E157" s="65" t="str">
-        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
-      </x:c>
-      <x:c r="F157" s="65" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G157" s="65"/>
-      <x:c r="H157" s="65" t="str">
+      <x:c r="D157" s="66" t="str">
+        <x:v>Native iOS scaled Swift Packages</x:v>
+      </x:c>
+      <x:c r="E157" s="66" t="str">
+        <x:v>Move stable cores/features to local Swift Packages when build/team size benefits.</x:v>
+      </x:c>
+      <x:c r="F157" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G157" s="66"/>
+      <x:c r="H157" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I157" s="389" t="n">
+      <x:c r="I157" s="388" t="n">
         <x:f>IF(H157="Done",1,IF(H157="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J157" s="65" t="str">
-        <x:v>Next.js web + admin default</x:v>
-      </x:c>
-      <x:c r="K157" s="65"/>
-      <x:c r="L157" s="65"/>
-      <x:c r="M157" s="65" t="str">
-        <x:v>Web optimized independently.</x:v>
+      <x:c r="J157" s="66" t="str">
+        <x:v>Native iOS lean template</x:v>
+      </x:c>
+      <x:c r="K157" s="66"/>
+      <x:c r="L157" s="66"/>
+      <x:c r="M157" s="66" t="str">
+        <x:v>Do not force Tuist/XcodeGen in earliest template.</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="66" t="str">
-        <x:v>R-149</x:v>
-      </x:c>
-      <x:c r="B158" s="66" t="str">
+      <x:c r="A158" s="65" t="str">
+        <x:v>R-148</x:v>
+      </x:c>
+      <x:c r="B158" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C158" s="66" t="str">
+      <x:c r="C158" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D158" s="66" t="str">
-        <x:v>Next.js admin template</x:v>
-      </x:c>
-      <x:c r="E158" s="66" t="str">
-        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
-      </x:c>
-      <x:c r="F158" s="66" t="str">
+      <x:c r="D158" s="65" t="str">
+        <x:v>Next.js public web template</x:v>
+      </x:c>
+      <x:c r="E158" s="65" t="str">
+        <x:v>App Router, feature-first, server/client boundaries, SEO/accessibility/performance gates.</x:v>
+      </x:c>
+      <x:c r="F158" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G158" s="66"/>
-      <x:c r="H158" s="66" t="str">
+      <x:c r="G158" s="65"/>
+      <x:c r="H158" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I158" s="388" t="n">
+      <x:c r="I158" s="389" t="n">
         <x:f>IF(H158="Done",1,IF(H158="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J158" s="66" t="str">
+      <x:c r="J158" s="65" t="str">
         <x:v>Next.js web + admin default</x:v>
       </x:c>
-      <x:c r="K158" s="66"/>
-      <x:c r="L158" s="66"/>
-      <x:c r="M158" s="66" t="str">
-        <x:v>Never force admin onto Flutter/RN Web.</x:v>
+      <x:c r="K158" s="65"/>
+      <x:c r="L158" s="65"/>
+      <x:c r="M158" s="65" t="str">
+        <x:v>Web optimized independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="65" t="str">
-        <x:v>R-150</x:v>
-      </x:c>
-      <x:c r="B159" s="65" t="str">
+      <x:c r="A159" s="66" t="str">
+        <x:v>R-149</x:v>
+      </x:c>
+      <x:c r="B159" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C159" s="65" t="str">
+      <x:c r="C159" s="66" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D159" s="65" t="str">
-        <x:v>Go backend standard template</x:v>
-      </x:c>
-      <x:c r="E159" s="65" t="str">
-        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
-      </x:c>
-      <x:c r="F159" s="65" t="str">
+      <x:c r="D159" s="66" t="str">
+        <x:v>Next.js admin template</x:v>
+      </x:c>
+      <x:c r="E159" s="66" t="str">
+        <x:v>Desktop-first modules, RBAC/ABAC, audit trail, data grids, filters, confirmations and async exports.</x:v>
+      </x:c>
+      <x:c r="F159" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G159" s="65"/>
-      <x:c r="H159" s="65" t="str">
+      <x:c r="G159" s="66"/>
+      <x:c r="H159" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I159" s="389" t="n">
+      <x:c r="I159" s="388" t="n">
         <x:f>IF(H159="Done",1,IF(H159="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J159" s="65" t="str">
-        <x:v>Backend Agent</x:v>
-      </x:c>
-      <x:c r="K159" s="65"/>
-      <x:c r="L159" s="65"/>
-      <x:c r="M159" s="65" t="str">
-        <x:v>Default backend profile.</x:v>
+      <x:c r="J159" s="66" t="str">
+        <x:v>Next.js web + admin default</x:v>
+      </x:c>
+      <x:c r="K159" s="66"/>
+      <x:c r="L159" s="66"/>
+      <x:c r="M159" s="66" t="str">
+        <x:v>Never force admin onto Flutter/RN Web.</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="66" t="str">
-        <x:v>R-151</x:v>
-      </x:c>
-      <x:c r="B160" s="66" t="str">
+      <x:c r="A160" s="65" t="str">
+        <x:v>R-150</x:v>
+      </x:c>
+      <x:c r="B160" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C160" s="66" t="str">
+      <x:c r="C160" s="65" t="str">
         <x:v>Templates</x:v>
       </x:c>
-      <x:c r="D160" s="66" t="str">
-        <x:v>Python backend standard template</x:v>
-      </x:c>
-      <x:c r="E160" s="66" t="str">
-        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
-      </x:c>
-      <x:c r="F160" s="66" t="str">
+      <x:c r="D160" s="65" t="str">
+        <x:v>Go backend standard template</x:v>
+      </x:c>
+      <x:c r="E160" s="65" t="str">
+        <x:v>Domain/application/adapters structure, explicit transactions, idempotency, timeouts and observability.</x:v>
+      </x:c>
+      <x:c r="F160" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G160" s="66"/>
-      <x:c r="H160" s="66" t="str">
+      <x:c r="G160" s="65"/>
+      <x:c r="H160" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I160" s="388" t="n">
+      <x:c r="I160" s="389" t="n">
         <x:f>IF(H160="Done",1,IF(H160="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J160" s="66" t="str">
+      <x:c r="J160" s="65" t="str">
         <x:v>Backend Agent</x:v>
       </x:c>
-      <x:c r="K160" s="66"/>
-      <x:c r="L160" s="66"/>
-      <x:c r="M160" s="66" t="str">
-        <x:v>Alternative default backend profile.</x:v>
+      <x:c r="K160" s="65"/>
+      <x:c r="L160" s="65"/>
+      <x:c r="M160" s="65" t="str">
+        <x:v>Default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="65" t="str">
-        <x:v>R-152</x:v>
-      </x:c>
-      <x:c r="B161" s="65" t="str">
+      <x:c r="A161" s="66" t="str">
+        <x:v>R-151</x:v>
+      </x:c>
+      <x:c r="B161" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C161" s="65" t="str">
-        <x:v>Contracts</x:v>
-      </x:c>
-      <x:c r="D161" s="65" t="str">
-        <x:v>Generated client matrix</x:v>
-      </x:c>
-      <x:c r="E161" s="65" t="str">
-        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
-      </x:c>
-      <x:c r="F161" s="65" t="str">
+      <x:c r="C161" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D161" s="66" t="str">
+        <x:v>Python backend standard template</x:v>
+      </x:c>
+      <x:c r="E161" s="66" t="str">
+        <x:v>Typed domain/application/infrastructure structure; thin routes; migration and async discipline.</x:v>
+      </x:c>
+      <x:c r="F161" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G161" s="65"/>
-      <x:c r="H161" s="65" t="str">
+      <x:c r="G161" s="66"/>
+      <x:c r="H161" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I161" s="389" t="n">
+      <x:c r="I161" s="388" t="n">
         <x:f>IF(H161="Done",1,IF(H161="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J161" s="65" t="str">
-        <x:v>Shared contracts package</x:v>
-      </x:c>
-      <x:c r="K161" s="65"/>
-      <x:c r="L161" s="65"/>
-      <x:c r="M161" s="65" t="str">
-        <x:v>Contract-first consistency.</x:v>
+      <x:c r="J161" s="66" t="str">
+        <x:v>Backend Agent</x:v>
+      </x:c>
+      <x:c r="K161" s="66"/>
+      <x:c r="L161" s="66"/>
+      <x:c r="M161" s="66" t="str">
+        <x:v>Alternative default backend profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="66" t="str">
-        <x:v>R-153</x:v>
-      </x:c>
-      <x:c r="B162" s="66" t="str">
+      <x:c r="A162" s="65" t="str">
+        <x:v>R-152</x:v>
+      </x:c>
+      <x:c r="B162" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C162" s="66" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D162" s="66" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="E162" s="66" t="str">
-        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
-      </x:c>
-      <x:c r="F162" s="66" t="str">
+      <x:c r="C162" s="65" t="str">
+        <x:v>Contracts</x:v>
+      </x:c>
+      <x:c r="D162" s="65" t="str">
+        <x:v>Generated client matrix</x:v>
+      </x:c>
+      <x:c r="E162" s="65" t="str">
+        <x:v>Generate Dart, TypeScript, Kotlin and Swift API clients only for selected targets; generated code is deterministic and not hand-edited.</x:v>
+      </x:c>
+      <x:c r="F162" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G162" s="66"/>
-      <x:c r="H162" s="66" t="str">
+      <x:c r="G162" s="65"/>
+      <x:c r="H162" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I162" s="388" t="n">
+      <x:c r="I162" s="389" t="n">
         <x:f>IF(H162="Done",1,IF(H162="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J162" s="66" t="str">
-        <x:v>Framework-specific repo templates</x:v>
-      </x:c>
-      <x:c r="K162" s="66"/>
-      <x:c r="L162" s="66"/>
-      <x:c r="M162" s="66" t="str">
-        <x:v>Stable/Beta/Experimental visible to user.</x:v>
+      <x:c r="J162" s="65" t="str">
+        <x:v>Shared contracts package</x:v>
+      </x:c>
+      <x:c r="K162" s="65"/>
+      <x:c r="L162" s="65"/>
+      <x:c r="M162" s="65" t="str">
+        <x:v>Contract-first consistency.</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="65" t="str">
-        <x:v>R-154</x:v>
-      </x:c>
-      <x:c r="B163" s="65" t="str">
+      <x:c r="A163" s="66" t="str">
+        <x:v>R-153</x:v>
+      </x:c>
+      <x:c r="B163" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C163" s="65" t="str">
-        <x:v>Dependencies</x:v>
-      </x:c>
-      <x:c r="D163" s="65" t="str">
-        <x:v>Approved dependency catalog</x:v>
-      </x:c>
-      <x:c r="E163" s="65" t="str">
-        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
-      </x:c>
-      <x:c r="F163" s="65" t="str">
+      <x:c r="C163" s="66" t="str">
+        <x:v>Templates</x:v>
+      </x:c>
+      <x:c r="D163" s="66" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="E163" s="66" t="str">
+        <x:v>Every template has ID, version, maturity, supported platforms and mandatory checks.</x:v>
+      </x:c>
+      <x:c r="F163" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G163" s="65"/>
-      <x:c r="H163" s="65" t="str">
+      <x:c r="G163" s="66"/>
+      <x:c r="H163" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I163" s="389" t="n">
+      <x:c r="I163" s="388" t="n">
         <x:f>IF(H163="Done",1,IF(H163="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J163" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K163" s="65"/>
-      <x:c r="L163" s="65"/>
-      <x:c r="M163" s="65" t="str">
-        <x:v>Prevents dependency explosion.</x:v>
+      <x:c r="J163" s="66" t="str">
+        <x:v>Framework-specific repo templates</x:v>
+      </x:c>
+      <x:c r="K163" s="66"/>
+      <x:c r="L163" s="66"/>
+      <x:c r="M163" s="66" t="str">
+        <x:v>Stable/Beta/Experimental visible to user.</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="66" t="str">
-        <x:v>R-155</x:v>
-      </x:c>
-      <x:c r="B164" s="66" t="str">
+      <x:c r="A164" s="65" t="str">
+        <x:v>R-154</x:v>
+      </x:c>
+      <x:c r="B164" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C164" s="66" t="str">
-        <x:v>Platform Architecture</x:v>
-      </x:c>
-      <x:c r="D164" s="66" t="str">
-        <x:v>Go control plane modular monolith</x:v>
-      </x:c>
-      <x:c r="E164" s="66" t="str">
-        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
-      </x:c>
-      <x:c r="F164" s="66" t="str">
+      <x:c r="C164" s="65" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D164" s="65" t="str">
+        <x:v>Approved dependency catalog</x:v>
+      </x:c>
+      <x:c r="E164" s="65" t="str">
+        <x:v>Dependency additions pass license/security/maintenance policy; lockfiles committed.</x:v>
+      </x:c>
+      <x:c r="F164" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G164" s="66"/>
-      <x:c r="H164" s="66" t="str">
+      <x:c r="G164" s="65"/>
+      <x:c r="H164" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I164" s="388" t="n">
+      <x:c r="I164" s="389" t="n">
         <x:f>IF(H164="Done",1,IF(H164="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J164" s="66" t="str">
-        <x:v>Platform modular monorepo</x:v>
-      </x:c>
-      <x:c r="K164" s="66"/>
-      <x:c r="L164" s="66"/>
-      <x:c r="M164" s="66" t="str">
-        <x:v>Avoid premature microservices.</x:v>
+      <x:c r="J164" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K164" s="65"/>
+      <x:c r="L164" s="65"/>
+      <x:c r="M164" s="65" t="str">
+        <x:v>Prevents dependency explosion.</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="65" t="str">
-        <x:v>R-156</x:v>
-      </x:c>
-      <x:c r="B165" s="65" t="str">
+      <x:c r="A165" s="66" t="str">
+        <x:v>R-155</x:v>
+      </x:c>
+      <x:c r="B165" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C165" s="65" t="str">
+      <x:c r="C165" s="66" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D165" s="65" t="str">
-        <x:v>Python agent engine boundary</x:v>
-      </x:c>
-      <x:c r="E165" s="65" t="str">
-        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
-      </x:c>
-      <x:c r="F165" s="65" t="str">
+      <x:c r="D165" s="66" t="str">
+        <x:v>Go control plane modular monolith</x:v>
+      </x:c>
+      <x:c r="E165" s="66" t="str">
+        <x:v>Keep auth/org/workspace/project/jobs/Git/usage/audit/basic billing in one Go service initially.</x:v>
+      </x:c>
+      <x:c r="F165" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G165" s="65"/>
-      <x:c r="H165" s="65" t="str">
+      <x:c r="G165" s="66"/>
+      <x:c r="H165" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I165" s="389" t="n">
+      <x:c r="I165" s="388" t="n">
         <x:f>IF(H165="Done",1,IF(H165="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J165" s="65" t="str">
-        <x:v>Model gateway</x:v>
-      </x:c>
-      <x:c r="K165" s="65"/>
-      <x:c r="L165" s="65"/>
-      <x:c r="M165" s="65" t="str">
-        <x:v>Different ecosystem/iteration cadence.</x:v>
+      <x:c r="J165" s="66" t="str">
+        <x:v>Platform modular monorepo</x:v>
+      </x:c>
+      <x:c r="K165" s="66"/>
+      <x:c r="L165" s="66"/>
+      <x:c r="M165" s="66" t="str">
+        <x:v>Avoid premature microservices.</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="66" t="str">
-        <x:v>R-157</x:v>
-      </x:c>
-      <x:c r="B166" s="66" t="str">
+      <x:c r="A166" s="65" t="str">
+        <x:v>R-156</x:v>
+      </x:c>
+      <x:c r="B166" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C166" s="66" t="str">
+      <x:c r="C166" s="65" t="str">
         <x:v>Platform Architecture</x:v>
       </x:c>
-      <x:c r="D166" s="66" t="str">
-        <x:v>Runner manager boundary</x:v>
-      </x:c>
-      <x:c r="E166" s="66" t="str">
-        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
-      </x:c>
-      <x:c r="F166" s="66" t="str">
+      <x:c r="D166" s="65" t="str">
+        <x:v>Python agent engine boundary</x:v>
+      </x:c>
+      <x:c r="E166" s="65" t="str">
+        <x:v>Planning, model gateway, context/RAG, tools and evals live in a separate Python service.</x:v>
+      </x:c>
+      <x:c r="F166" s="65" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G166" s="66"/>
-      <x:c r="H166" s="66" t="str">
+      <x:c r="G166" s="65"/>
+      <x:c r="H166" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I166" s="388" t="n">
+      <x:c r="I166" s="389" t="n">
         <x:f>IF(H166="Done",1,IF(H166="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J166" s="66" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
-      </x:c>
-      <x:c r="K166" s="66"/>
-      <x:c r="L166" s="66"/>
-      <x:c r="M166" s="66" t="str">
-        <x:v>Central execution control.</x:v>
+      <x:c r="J166" s="65" t="str">
+        <x:v>Model gateway</x:v>
+      </x:c>
+      <x:c r="K166" s="65"/>
+      <x:c r="L166" s="65"/>
+      <x:c r="M166" s="65" t="str">
+        <x:v>Different ecosystem/iteration cadence.</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="65" t="str">
-        <x:v>R-158</x:v>
-      </x:c>
-      <x:c r="B167" s="65" t="str">
+      <x:c r="A167" s="66" t="str">
+        <x:v>R-157</x:v>
+      </x:c>
+      <x:c r="B167" s="66" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C167" s="65" t="str">
-        <x:v>CI/CD</x:v>
-      </x:c>
-      <x:c r="D167" s="65" t="str">
-        <x:v>Unified PR pipeline</x:v>
-      </x:c>
-      <x:c r="E167" s="65" t="str">
-        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
-      </x:c>
-      <x:c r="F167" s="65" t="str">
+      <x:c r="C167" s="66" t="str">
+        <x:v>Platform Architecture</x:v>
+      </x:c>
+      <x:c r="D167" s="66" t="str">
+        <x:v>Runner manager boundary</x:v>
+      </x:c>
+      <x:c r="E167" s="66" t="str">
+        <x:v>Go service schedules Linux/Android/Web/macOS jobs with quotas, timeouts and isolation.</x:v>
+      </x:c>
+      <x:c r="F167" s="66" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G167" s="65"/>
-      <x:c r="H167" s="65" t="str">
+      <x:c r="G167" s="66"/>
+      <x:c r="H167" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I167" s="389" t="n">
+      <x:c r="I167" s="388" t="n">
         <x:f>IF(H167="Done",1,IF(H167="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J167" s="65" t="str">
-        <x:v>Atomic cross-platform change set</x:v>
-      </x:c>
-      <x:c r="K167" s="65"/>
-      <x:c r="L167" s="65"/>
-      <x:c r="M167" s="65" t="str">
-        <x:v>Real iOS compile uses macOS.</x:v>
+      <x:c r="J167" s="66" t="str">
+        <x:v>Ephemeral Linux sandbox</x:v>
+      </x:c>
+      <x:c r="K167" s="66"/>
+      <x:c r="L167" s="66"/>
+      <x:c r="M167" s="66" t="str">
+        <x:v>Central execution control.</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="66" t="str">
-        <x:v>R-159</x:v>
-      </x:c>
-      <x:c r="B168" s="66" t="str">
+      <x:c r="A168" s="65" t="str">
+        <x:v>R-158</x:v>
+      </x:c>
+      <x:c r="B168" s="65" t="str">
         <x:v>MVP</x:v>
       </x:c>
-      <x:c r="C168" s="66" t="str">
+      <x:c r="C168" s="65" t="str">
         <x:v>CI/CD</x:v>
       </x:c>
-      <x:c r="D168" s="66" t="str">
-        <x:v>Immutable build promotion</x:v>
-      </x:c>
-      <x:c r="E168" s="66" t="str">
-        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
-      </x:c>
-      <x:c r="F168" s="66" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G168" s="66"/>
-      <x:c r="H168" s="66" t="str">
+      <x:c r="D168" s="65" t="str">
+        <x:v>Unified PR pipeline</x:v>
+      </x:c>
+      <x:c r="E168" s="65" t="str">
+        <x:v>IR/policy -&gt; lint -&gt; static -&gt; tests -&gt; contract -&gt; affected builds -&gt; security -&gt; E2E/visual -&gt; AI review.</x:v>
+      </x:c>
+      <x:c r="F168" s="65" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G168" s="65"/>
+      <x:c r="H168" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I168" s="388" t="n">
+      <x:c r="I168" s="389" t="n">
         <x:f>IF(H168="Done",1,IF(H168="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J168" s="66" t="str">
-        <x:v>Deployment Agent</x:v>
-      </x:c>
-      <x:c r="K168" s="66"/>
-      <x:c r="L168" s="66"/>
-      <x:c r="M168" s="66" t="str">
-        <x:v>Reduces preview/production mismatch.</x:v>
+      <x:c r="J168" s="65" t="str">
+        <x:v>Atomic cross-platform change set</x:v>
+      </x:c>
+      <x:c r="K168" s="65"/>
+      <x:c r="L168" s="65"/>
+      <x:c r="M168" s="65" t="str">
+        <x:v>Real iOS compile uses macOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="65" t="str">
-        <x:v>R-160</x:v>
-      </x:c>
-      <x:c r="B169" s="65" t="str">
-        <x:v>MID</x:v>
-      </x:c>
-      <x:c r="C169" s="65" t="str">
-        <x:v>Developer Experience</x:v>
-      </x:c>
-      <x:c r="D169" s="65" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="E169" s="65" t="str">
-        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
-      </x:c>
-      <x:c r="F169" s="65" t="str">
+      <x:c r="A169" s="66" t="str">
+        <x:v>R-159</x:v>
+      </x:c>
+      <x:c r="B169" s="66" t="str">
+        <x:v>MVP</x:v>
+      </x:c>
+      <x:c r="C169" s="66" t="str">
+        <x:v>CI/CD</x:v>
+      </x:c>
+      <x:c r="D169" s="66" t="str">
+        <x:v>Immutable build promotion</x:v>
+      </x:c>
+      <x:c r="E169" s="66" t="str">
+        <x:v>Build artifact once after merge and promote through preview/staging/production instead of rebuilding per environment.</x:v>
+      </x:c>
+      <x:c r="F169" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G169" s="65"/>
-      <x:c r="H169" s="65" t="str">
+      <x:c r="G169" s="66"/>
+      <x:c r="H169" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I169" s="389" t="n">
+      <x:c r="I169" s="388" t="n">
         <x:f>IF(H169="Done",1,IF(H169="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J169" s="65" t="str">
-        <x:v>Template manifest + maturity</x:v>
-      </x:c>
-      <x:c r="K169" s="65"/>
-      <x:c r="L169" s="65"/>
-      <x:c r="M169" s="65"/>
+      <x:c r="J169" s="66" t="str">
+        <x:v>Deployment Agent</x:v>
+      </x:c>
+      <x:c r="K169" s="66"/>
+      <x:c r="L169" s="66"/>
+      <x:c r="M169" s="66" t="str">
+        <x:v>Reduces preview/production mismatch.</x:v>
+      </x:c>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="66" t="str">
-        <x:v>R-161</x:v>
-      </x:c>
-      <x:c r="B170" s="66" t="str">
+      <x:c r="A170" s="65" t="str">
+        <x:v>R-160</x:v>
+      </x:c>
+      <x:c r="B170" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C170" s="66" t="str">
-        <x:v>Preview</x:v>
-      </x:c>
-      <x:c r="D170" s="66" t="str">
-        <x:v>Local Mac Agent productized</x:v>
-      </x:c>
-      <x:c r="E170" s="66" t="str">
-        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
-      </x:c>
-      <x:c r="F170" s="66" t="str">
+      <x:c r="C170" s="65" t="str">
+        <x:v>Developer Experience</x:v>
+      </x:c>
+      <x:c r="D170" s="65" t="str">
+        <x:v>Framework upgrade workflow</x:v>
+      </x:c>
+      <x:c r="E170" s="65" t="str">
+        <x:v>Controlled template upgrade task with compatibility tests and ADR; agents cannot randomly switch state/DI/navigation/networking frameworks.</x:v>
+      </x:c>
+      <x:c r="F170" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G170" s="66"/>
-      <x:c r="H170" s="66" t="str">
+      <x:c r="G170" s="65"/>
+      <x:c r="H170" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I170" s="388" t="n">
+      <x:c r="I170" s="389" t="n">
         <x:f>IF(H170="Done",1,IF(H170="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J170" s="66" t="str">
-        <x:v>Local Mac Agent</x:v>
-      </x:c>
-      <x:c r="K170" s="66"/>
-      <x:c r="L170" s="66"/>
-      <x:c r="M170" s="66" t="str">
-        <x:v>Reduces cloud Mac cost.</x:v>
-      </x:c>
+      <x:c r="J170" s="65" t="str">
+        <x:v>Template manifest + maturity</x:v>
+      </x:c>
+      <x:c r="K170" s="65"/>
+      <x:c r="L170" s="65"/>
+      <x:c r="M170" s="65"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="65" t="str">
-        <x:v>R-162</x:v>
-      </x:c>
-      <x:c r="B171" s="65" t="str">
+      <x:c r="A171" s="66" t="str">
+        <x:v>R-161</x:v>
+      </x:c>
+      <x:c r="B171" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C171" s="65" t="str">
+      <x:c r="C171" s="66" t="str">
         <x:v>Preview</x:v>
       </x:c>
-      <x:c r="D171" s="65" t="str">
-        <x:v>Interactive cloud simulator metering</x:v>
-      </x:c>
-      <x:c r="E171" s="65" t="str">
-        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
-      </x:c>
-      <x:c r="F171" s="65" t="str">
+      <x:c r="D171" s="66" t="str">
+        <x:v>Local Mac Agent productized</x:v>
+      </x:c>
+      <x:c r="E171" s="66" t="str">
+        <x:v>Optional signed Mac helper runs Xcode/simulator locally after explicit user permission; cloud Mac remains available.</x:v>
+      </x:c>
+      <x:c r="F171" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G171" s="65"/>
-      <x:c r="H171" s="65" t="str">
+      <x:c r="G171" s="66"/>
+      <x:c r="H171" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I171" s="389" t="n">
+      <x:c r="I171" s="388" t="n">
         <x:f>IF(H171="Done",1,IF(H171="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J171" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K171" s="65"/>
-      <x:c r="L171" s="65"/>
-      <x:c r="M171" s="65" t="str">
-        <x:v>Separate verification build cost from interactive session cost.</x:v>
+      <x:c r="J171" s="66" t="str">
+        <x:v>Local Mac Agent</x:v>
+      </x:c>
+      <x:c r="K171" s="66"/>
+      <x:c r="L171" s="66"/>
+      <x:c r="M171" s="66" t="str">
+        <x:v>Reduces cloud Mac cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="66" t="str">
-        <x:v>R-163</x:v>
-      </x:c>
-      <x:c r="B172" s="66" t="str">
+      <x:c r="A172" s="65" t="str">
+        <x:v>R-162</x:v>
+      </x:c>
+      <x:c r="B172" s="65" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C172" s="66" t="str">
-        <x:v>Framework Strategy</x:v>
-      </x:c>
-      <x:c r="D172" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="E172" s="66" t="str">
-        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
-      </x:c>
-      <x:c r="F172" s="66" t="str">
+      <x:c r="C172" s="65" t="str">
+        <x:v>Preview</x:v>
+      </x:c>
+      <x:c r="D172" s="65" t="str">
+        <x:v>Interactive cloud simulator metering</x:v>
+      </x:c>
+      <x:c r="E172" s="65" t="str">
+        <x:v>Cloud native iOS simulator sessions are explicit premium compute; browser preview stays included.</x:v>
+      </x:c>
+      <x:c r="F172" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G172" s="66"/>
-      <x:c r="H172" s="66" t="str">
+      <x:c r="G172" s="65"/>
+      <x:c r="H172" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I172" s="388" t="n">
+      <x:c r="I172" s="389" t="n">
         <x:f>IF(H172="Done",1,IF(H172="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J172" s="66" t="str">
-        <x:v>Framework adapter contract</x:v>
-      </x:c>
-      <x:c r="K172" s="66"/>
-      <x:c r="L172" s="66"/>
-      <x:c r="M172" s="66" t="str">
-        <x:v>Measure before rewrite.</x:v>
+      <x:c r="J172" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K172" s="65"/>
+      <x:c r="L172" s="65"/>
+      <x:c r="M172" s="65" t="str">
+        <x:v>Separate verification build cost from interactive session cost.</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="65" t="str">
-        <x:v>R-164</x:v>
-      </x:c>
-      <x:c r="B173" s="65" t="str">
+      <x:c r="A173" s="66" t="str">
+        <x:v>R-163</x:v>
+      </x:c>
+      <x:c r="B173" s="66" t="str">
         <x:v>MID</x:v>
       </x:c>
-      <x:c r="C173" s="65" t="str">
-        <x:v>Analytics</x:v>
-      </x:c>
-      <x:c r="D173" s="65" t="str">
-        <x:v>Template/repo health dashboard</x:v>
-      </x:c>
-      <x:c r="E173" s="65" t="str">
-        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
-      </x:c>
-      <x:c r="F173" s="65" t="str">
+      <x:c r="C173" s="66" t="str">
+        <x:v>Framework Strategy</x:v>
+      </x:c>
+      <x:c r="D173" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="E173" s="66" t="str">
+        <x:v>Before full migration, allow an approved small native module/plugin when one capability exceeds Flutter/RN limits.</x:v>
+      </x:c>
+      <x:c r="F173" s="66" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G173" s="65"/>
-      <x:c r="H173" s="65" t="str">
+      <x:c r="G173" s="66"/>
+      <x:c r="H173" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I173" s="389" t="n">
+      <x:c r="I173" s="388" t="n">
         <x:f>IF(H173="Done",1,IF(H173="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J173" s="65" t="str">
-        <x:v>Repository/build health metrics</x:v>
-      </x:c>
-      <x:c r="K173" s="65"/>
-      <x:c r="L173" s="65"/>
-      <x:c r="M173" s="65" t="str">
-        <x:v>Use data to trigger architecture review.</x:v>
+      <x:c r="J173" s="66" t="str">
+        <x:v>Framework adapter contract</x:v>
+      </x:c>
+      <x:c r="K173" s="66"/>
+      <x:c r="L173" s="66"/>
+      <x:c r="M173" s="66" t="str">
+        <x:v>Measure before rewrite.</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="66" t="str">
-        <x:v>R-165</x:v>
-      </x:c>
-      <x:c r="B174" s="66" t="str">
-        <x:v>ADVANCED</x:v>
-      </x:c>
-      <x:c r="C174" s="66" t="str">
-        <x:v>Migration</x:v>
-      </x:c>
-      <x:c r="D174" s="66" t="str">
-        <x:v>Cross-platform to native migration engine</x:v>
-      </x:c>
-      <x:c r="E174" s="66" t="str">
-        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
-      </x:c>
-      <x:c r="F174" s="66" t="str">
+      <x:c r="A174" s="65" t="str">
+        <x:v>R-164</x:v>
+      </x:c>
+      <x:c r="B174" s="65" t="str">
+        <x:v>MID</x:v>
+      </x:c>
+      <x:c r="C174" s="65" t="str">
+        <x:v>Analytics</x:v>
+      </x:c>
+      <x:c r="D174" s="65" t="str">
+        <x:v>Template/repo health dashboard</x:v>
+      </x:c>
+      <x:c r="E174" s="65" t="str">
+        <x:v>Track template version, dependency drift, build duration, cache hit, repo size, module growth and native bridge count.</x:v>
+      </x:c>
+      <x:c r="F174" s="65" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="G174" s="66"/>
-      <x:c r="H174" s="66" t="str">
+      <x:c r="G174" s="65"/>
+      <x:c r="H174" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I174" s="388" t="n">
+      <x:c r="I174" s="389" t="n">
         <x:f>IF(H174="Done",1,IF(H174="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J174" s="66" t="str">
-        <x:v>Native module adapter path</x:v>
-      </x:c>
-      <x:c r="K174" s="66"/>
-      <x:c r="L174" s="66"/>
-      <x:c r="M174" s="66" t="str">
-        <x:v>Prevents framework lock-in.</x:v>
+      <x:c r="J174" s="65" t="str">
+        <x:v>Repository/build health metrics</x:v>
+      </x:c>
+      <x:c r="K174" s="65"/>
+      <x:c r="L174" s="65"/>
+      <x:c r="M174" s="65" t="str">
+        <x:v>Use data to trigger architecture review.</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="65" t="str">
-        <x:v>R-166</x:v>
-      </x:c>
-      <x:c r="B175" s="65" t="str">
+      <x:c r="A175" s="66" t="str">
+        <x:v>R-165</x:v>
+      </x:c>
+      <x:c r="B175" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C175" s="65" t="str">
-        <x:v>Git/Repository</x:v>
-      </x:c>
-      <x:c r="D175" s="65" t="str">
-        <x:v>Cross-repo task coordinator</x:v>
-      </x:c>
-      <x:c r="E175" s="65" t="str">
-        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
-      </x:c>
-      <x:c r="F175" s="65" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="G175" s="65"/>
-      <x:c r="H175" s="65" t="str">
+      <x:c r="C175" s="66" t="str">
+        <x:v>Migration</x:v>
+      </x:c>
+      <x:c r="D175" s="66" t="str">
+        <x:v>Cross-platform to native migration engine</x:v>
+      </x:c>
+      <x:c r="E175" s="66" t="str">
+        <x:v>Generate parallel native target from IR/contracts, parity-test it and migrate gradually when measured constraints justify.</x:v>
+      </x:c>
+      <x:c r="F175" s="66" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G175" s="66"/>
+      <x:c r="H175" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I175" s="389" t="n">
+      <x:c r="I175" s="388" t="n">
         <x:f>IF(H175="Done",1,IF(H175="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J175" s="65" t="str">
-        <x:v>Enterprise multi-repo support</x:v>
-      </x:c>
-      <x:c r="K175" s="65"/>
-      <x:c r="L175" s="65"/>
-      <x:c r="M175" s="65"/>
+      <x:c r="J175" s="66" t="str">
+        <x:v>Native module adapter path</x:v>
+      </x:c>
+      <x:c r="K175" s="66"/>
+      <x:c r="L175" s="66"/>
+      <x:c r="M175" s="66" t="str">
+        <x:v>Prevents framework lock-in.</x:v>
+      </x:c>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="66" t="str">
-        <x:v>R-167</x:v>
-      </x:c>
-      <x:c r="B176" s="66" t="str">
+      <x:c r="A176" s="65" t="str">
+        <x:v>R-166</x:v>
+      </x:c>
+      <x:c r="B176" s="65" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C176" s="66" t="str">
-        <x:v>Infrastructure</x:v>
-      </x:c>
-      <x:c r="D176" s="66" t="str">
-        <x:v>BYOC / private runners</x:v>
-      </x:c>
-      <x:c r="E176" s="66" t="str">
-        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
-      </x:c>
-      <x:c r="F176" s="66" t="str">
+      <x:c r="C176" s="65" t="str">
+        <x:v>Git/Repository</x:v>
+      </x:c>
+      <x:c r="D176" s="65" t="str">
+        <x:v>Cross-repo task coordinator</x:v>
+      </x:c>
+      <x:c r="E176" s="65" t="str">
+        <x:v>For enterprise multi-repo, produce linked branches/PRs with shared task ID, contract version and merge ordering.</x:v>
+      </x:c>
+      <x:c r="F176" s="65" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G176" s="66"/>
-      <x:c r="H176" s="66" t="str">
+      <x:c r="G176" s="65"/>
+      <x:c r="H176" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I176" s="388" t="n">
+      <x:c r="I176" s="389" t="n">
         <x:f>IF(H176="Done",1,IF(H176="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J176" s="66" t="str">
-        <x:v>Enterprise workload isolation</x:v>
-      </x:c>
-      <x:c r="K176" s="66"/>
-      <x:c r="L176" s="66"/>
-      <x:c r="M176" s="66"/>
+      <x:c r="J176" s="65" t="str">
+        <x:v>Enterprise multi-repo support</x:v>
+      </x:c>
+      <x:c r="K176" s="65"/>
+      <x:c r="L176" s="65"/>
+      <x:c r="M176" s="65"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="65" t="str">
-        <x:v>R-168</x:v>
-      </x:c>
-      <x:c r="B177" s="65" t="str">
+      <x:c r="A177" s="66" t="str">
+        <x:v>R-167</x:v>
+      </x:c>
+      <x:c r="B177" s="66" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
-      <x:c r="C177" s="65" t="str">
-        <x:v>Testing</x:v>
-      </x:c>
-      <x:c r="D177" s="65" t="str">
-        <x:v>Physical device cloud integration</x:v>
-      </x:c>
-      <x:c r="E177" s="65" t="str">
-        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
-      </x:c>
-      <x:c r="F177" s="65" t="str">
+      <x:c r="C177" s="66" t="str">
+        <x:v>Infrastructure</x:v>
+      </x:c>
+      <x:c r="D177" s="66" t="str">
+        <x:v>BYOC / private runners</x:v>
+      </x:c>
+      <x:c r="E177" s="66" t="str">
+        <x:v>Allow enterprise customers to execute builds/agents in approved customer cloud/VPC while platform keeps orchestration.</x:v>
+      </x:c>
+      <x:c r="F177" s="66" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="G177" s="65"/>
-      <x:c r="H177" s="65" t="str">
+      <x:c r="G177" s="66"/>
+      <x:c r="H177" s="66" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I177" s="389" t="n">
+      <x:c r="I177" s="388" t="n">
         <x:f>IF(H177="Done",1,IF(H177="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J177" s="65" t="str">
-        <x:v>Real iOS Simulator</x:v>
-      </x:c>
-      <x:c r="K177" s="65"/>
-      <x:c r="L177" s="65"/>
-      <x:c r="M177" s="65"/>
+      <x:c r="J177" s="66" t="str">
+        <x:v>Enterprise workload isolation</x:v>
+      </x:c>
+      <x:c r="K177" s="66"/>
+      <x:c r="L177" s="66"/>
+      <x:c r="M177" s="66"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="127" t="str">
-        <x:v>R-169</x:v>
-      </x:c>
-      <x:c r="B178" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
-      </x:c>
-      <x:c r="C178" s="127" t="str">
-        <x:v>Templates</x:v>
-      </x:c>
-      <x:c r="D178" s="127" t="str">
-        <x:v>Template support lifecycle</x:v>
-      </x:c>
-      <x:c r="E178" s="127" t="str">
-        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
-      </x:c>
-      <x:c r="F178" s="127" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="G178" s="127"/>
-      <x:c r="H178" s="127" t="str">
+      <x:c r="A178" s="65" t="str">
+        <x:v>R-168</x:v>
+      </x:c>
+      <x:c r="B178" s="65" t="str">
+        <x:v>ADVANCED</x:v>
+      </x:c>
+      <x:c r="C178" s="65" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="D178" s="65" t="str">
+        <x:v>Physical device cloud integration</x:v>
+      </x:c>
+      <x:c r="E178" s="65" t="str">
+        <x:v>Run selected releases/tests on real iPhone/Android devices after emulator/simulator gates.</x:v>
+      </x:c>
+      <x:c r="F178" s="65" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="G178" s="65"/>
+      <x:c r="H178" s="65" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I178" s="390" t="n">
+      <x:c r="I178" s="389" t="n">
         <x:f>IF(H178="Done",1,IF(H178="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J178" s="127" t="str">
-        <x:v>Framework upgrade workflow</x:v>
-      </x:c>
-      <x:c r="K178" s="127"/>
-      <x:c r="L178" s="127"/>
-      <x:c r="M178" s="127"/>
+      <x:c r="J178" s="65" t="str">
+        <x:v>Real iOS Simulator</x:v>
+      </x:c>
+      <x:c r="K178" s="65"/>
+      <x:c r="L178" s="65"/>
+      <x:c r="M178" s="65"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="127" t="str">
-        <x:v>R-170</x:v>
+        <x:v>R-169</x:v>
       </x:c>
       <x:c r="B179" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C179" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Templates</x:v>
       </x:c>
       <x:c r="D179" s="127" t="str">
-        <x:v>Framework/toolchain production SLO</x:v>
+        <x:v>Template support lifecycle</x:v>
       </x:c>
       <x:c r="E179" s="127" t="str">
-        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
+        <x:v>Publish supported template versions, security patch policy, upgrade windows and deprecation/migration rules.</x:v>
       </x:c>
       <x:c r="F179" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G179" s="127"/>
       <x:c r="H179" s="127" t="str">
@@ -16385,29 +16393,27 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="127" t="str">
-        <x:v>Template/repo health dashboard</x:v>
+        <x:v>Framework upgrade workflow</x:v>
       </x:c>
       <x:c r="K179" s="127"/>
       <x:c r="L179" s="127"/>
-      <x:c r="M179" s="127" t="str">
-        <x:v>Production readiness is measured, not assumed.</x:v>
-      </x:c>
+      <x:c r="M179" s="127"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="127" t="str">
-        <x:v>R-171</x:v>
+        <x:v>R-170</x:v>
       </x:c>
       <x:c r="B180" s="127" t="str">
-        <x:v>MVP</x:v>
+        <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C180" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D180" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Framework/toolchain production SLO</x:v>
       </x:c>
       <x:c r="E180" s="127" t="str">
-        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
+        <x:v>Track build success and regression by Flutter/RN/Android/iOS/Web/backend template and block bad template releases.</x:v>
       </x:c>
       <x:c r="F180" s="127" t="str">
         <x:v>P0</x:v>
@@ -16421,17 +16427,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="127" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>Template/repo health dashboard</x:v>
       </x:c>
       <x:c r="K180" s="127"/>
       <x:c r="L180" s="127"/>
       <x:c r="M180" s="127" t="str">
-        <x:v>No agent-to-vendor SDK coupling.</x:v>
+        <x:v>Production readiness is measured, not assumed.</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="127" t="str">
-        <x:v>R-172</x:v>
+        <x:v>R-171</x:v>
       </x:c>
       <x:c r="B181" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16440,10 +16446,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D181" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="E181" s="127" t="str">
-        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
+        <x:v>Define platform-owned execution interface for create/exec/files/ports/snapshot/artifacts/terminate.</x:v>
       </x:c>
       <x:c r="F181" s="127" t="str">
         <x:v>P0</x:v>
@@ -16457,17 +16463,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="K181" s="127"/>
       <x:c r="L181" s="127"/>
       <x:c r="M181" s="127" t="str">
-        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
+        <x:v>No agent-to-vendor SDK coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="127" t="str">
-        <x:v>R-173</x:v>
+        <x:v>R-172</x:v>
       </x:c>
       <x:c r="B182" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16476,10 +16482,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D182" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="E182" s="127" t="str">
-        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
+        <x:v>Implement first real Linux sandbox provider behind SandboxProvider.</x:v>
       </x:c>
       <x:c r="F182" s="127" t="str">
         <x:v>P0</x:v>
@@ -16498,12 +16504,12 @@
       <x:c r="K182" s="127"/>
       <x:c r="L182" s="127"/>
       <x:c r="M182" s="127" t="str">
-        <x:v>Cheapest safe runtime wins.</x:v>
+        <x:v>Benchmark E2B/Daytona/equivalent.</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="127" t="str">
-        <x:v>R-174</x:v>
+        <x:v>R-173</x:v>
       </x:c>
       <x:c r="B183" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16512,13 +16518,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D183" s="127" t="str">
-        <x:v>Browser runtime PoC</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="E183" s="127" t="str">
-        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
+        <x:v>Choose Browser/Linux/macOS/local runtime from task capability, trust and cost.</x:v>
       </x:c>
       <x:c r="F183" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G183" s="127"/>
       <x:c r="H183" s="127" t="str">
@@ -16529,17 +16535,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="127" t="str">
-        <x:v>Capability resolver</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K183" s="127"/>
       <x:c r="L183" s="127"/>
       <x:c r="M183" s="127" t="str">
-        <x:v>Not universal sandbox.</x:v>
+        <x:v>Cheapest safe runtime wins.</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="127" t="str">
-        <x:v>R-175</x:v>
+        <x:v>R-174</x:v>
       </x:c>
       <x:c r="B184" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16548,13 +16554,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D184" s="127" t="str">
-        <x:v>Runtime quotas and metering</x:v>
+        <x:v>Browser runtime PoC</x:v>
       </x:c>
       <x:c r="E184" s="127" t="str">
-        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
+        <x:v>Use WebContainer/WASM-style runtime only for eligible JS/TS/Node preview/tasks.</x:v>
       </x:c>
       <x:c r="F184" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G184" s="127"/>
       <x:c r="H184" s="127" t="str">
@@ -16565,29 +16571,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Capability resolver</x:v>
       </x:c>
       <x:c r="K184" s="127"/>
       <x:c r="L184" s="127"/>
       <x:c r="M184" s="127" t="str">
-        <x:v>Required for cost and abuse control.</x:v>
+        <x:v>Not universal sandbox.</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="127" t="str">
-        <x:v>R-176</x:v>
+        <x:v>R-175</x:v>
       </x:c>
       <x:c r="B185" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C185" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D185" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Runtime quotas and metering</x:v>
       </x:c>
       <x:c r="E185" s="127" t="str">
-        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
+        <x:v>CPU/RAM/disk/network/time/cost limits per workspace and task.</x:v>
       </x:c>
       <x:c r="F185" s="127" t="str">
         <x:v>P0</x:v>
@@ -16601,17 +16607,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="127" t="str">
-        <x:v>Supervisor / orchestrator</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K185" s="127"/>
       <x:c r="L185" s="127"/>
       <x:c r="M185" s="127" t="str">
-        <x:v>Platform-owned state schema.</x:v>
+        <x:v>Required for cost and abuse control.</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="127" t="str">
-        <x:v>R-177</x:v>
+        <x:v>R-176</x:v>
       </x:c>
       <x:c r="B186" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16620,10 +16626,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D186" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="E186" s="127" t="str">
-        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
+        <x:v>Persist task lifecycle from CREATED through planning/execution/verification/merge/deploy.</x:v>
       </x:c>
       <x:c r="F186" s="127" t="str">
         <x:v>P0</x:v>
@@ -16637,17 +16643,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Supervisor / orchestrator</x:v>
       </x:c>
       <x:c r="K186" s="127"/>
       <x:c r="L186" s="127"/>
       <x:c r="M186" s="127" t="str">
-        <x:v>No full restart by default.</x:v>
+        <x:v>Platform-owned state schema.</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="127" t="str">
-        <x:v>R-178</x:v>
+        <x:v>R-177</x:v>
       </x:c>
       <x:c r="B187" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16656,10 +16662,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D187" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="E187" s="127" t="str">
-        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
+        <x:v>Resume long tasks from last verified checkpoint after refresh/crash/provider failure.</x:v>
       </x:c>
       <x:c r="F187" s="127" t="str">
         <x:v>P0</x:v>
@@ -16673,29 +16679,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K187" s="127"/>
       <x:c r="L187" s="127"/>
       <x:c r="M187" s="127" t="str">
-        <x:v>Prevent duplicate side effects.</x:v>
+        <x:v>No full restart by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="127" t="str">
-        <x:v>R-179</x:v>
+        <x:v>R-178</x:v>
       </x:c>
       <x:c r="B188" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C188" s="127" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D188" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="E188" s="127" t="str">
-        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
+        <x:v>Every side-effecting tool step carries run/task/step IDs and idempotency key.</x:v>
       </x:c>
       <x:c r="F188" s="127" t="str">
         <x:v>P0</x:v>
@@ -16709,29 +16715,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="127" t="str">
-        <x:v>Durable run state machine</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K188" s="127"/>
       <x:c r="L188" s="127"/>
       <x:c r="M188" s="127" t="str">
-        <x:v>Supports replay, audit and debugging.</x:v>
+        <x:v>Prevent duplicate side effects.</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="127" t="str">
-        <x:v>R-180</x:v>
+        <x:v>R-179</x:v>
       </x:c>
       <x:c r="B189" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C189" s="127" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D189" s="127" t="str">
-        <x:v>Orchestrator Adapter</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="E189" s="127" t="str">
-        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
+        <x:v>Persist ordered agent/tool/build/test/approval events; large artifacts in object storage.</x:v>
       </x:c>
       <x:c r="F189" s="127" t="str">
         <x:v>P0</x:v>
@@ -16750,24 +16756,24 @@
       <x:c r="K189" s="127"/>
       <x:c r="L189" s="127"/>
       <x:c r="M189" s="127" t="str">
-        <x:v>LangGraph may be first implementation.</x:v>
+        <x:v>Supports replay, audit and debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="127" t="str">
-        <x:v>R-181</x:v>
+        <x:v>R-180</x:v>
       </x:c>
       <x:c r="B190" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C190" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D190" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Orchestrator Adapter</x:v>
       </x:c>
       <x:c r="E190" s="127" t="str">
-        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
+        <x:v>Hide LangGraph/CrewAI/other orchestration frameworks behind platform-owned interface.</x:v>
       </x:c>
       <x:c r="F190" s="127" t="str">
         <x:v>P0</x:v>
@@ -16781,17 +16787,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Durable run state machine</x:v>
       </x:c>
       <x:c r="K190" s="127"/>
       <x:c r="L190" s="127"/>
       <x:c r="M190" s="127" t="str">
-        <x:v>Frontend never parses provider-specific streams.</x:v>
+        <x:v>LangGraph may be first implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="127" t="str">
-        <x:v>R-182</x:v>
+        <x:v>R-181</x:v>
       </x:c>
       <x:c r="B191" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16800,10 +16806,10 @@
         <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D191" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="E191" s="127" t="str">
-        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
+        <x:v>Normalize agent/model/tool progress into a stable event envelope.</x:v>
       </x:c>
       <x:c r="F191" s="127" t="str">
         <x:v>P0</x:v>
@@ -16817,29 +16823,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="127" t="str">
-        <x:v>Platform event protocol</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K191" s="127"/>
       <x:c r="L191" s="127"/>
       <x:c r="M191" s="127" t="str">
-        <x:v>SSE allowed for simple one-way streams.</x:v>
+        <x:v>Frontend never parses provider-specific streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="127" t="str">
-        <x:v>R-183</x:v>
+        <x:v>R-182</x:v>
       </x:c>
       <x:c r="B192" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C192" s="127" t="str">
-        <x:v>Approvals</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D192" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="E192" s="127" t="str">
-        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
+        <x:v>Bidirectional agent sessions with sequence replay after reconnect.</x:v>
       </x:c>
       <x:c r="F192" s="127" t="str">
         <x:v>P0</x:v>
@@ -16853,17 +16859,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Platform event protocol</x:v>
       </x:c>
       <x:c r="K192" s="127"/>
       <x:c r="L192" s="127"/>
       <x:c r="M192" s="127" t="str">
-        <x:v>Approval based on risk.</x:v>
+        <x:v>SSE allowed for simple one-way streams.</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="127" t="str">
-        <x:v>R-184</x:v>
+        <x:v>R-183</x:v>
       </x:c>
       <x:c r="B193" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16872,10 +16878,10 @@
         <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D193" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="E193" s="127" t="str">
-        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
+        <x:v>Classify actions from read-only to critical enterprise side effects.</x:v>
       </x:c>
       <x:c r="F193" s="127" t="str">
         <x:v>P0</x:v>
@@ -16889,29 +16895,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="127" t="str">
-        <x:v>Risk classification L0-L4</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K193" s="127"/>
       <x:c r="L193" s="127"/>
       <x:c r="M193" s="127" t="str">
-        <x:v>Production/destructive actions auditable.</x:v>
+        <x:v>Approval based on risk.</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="127" t="str">
-        <x:v>R-185</x:v>
+        <x:v>R-184</x:v>
       </x:c>
       <x:c r="B194" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C194" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Approvals</x:v>
       </x:c>
       <x:c r="D194" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="E194" s="127" t="str">
-        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
+        <x:v>Store action, risk, environment, scope, cost, rollback, approver and expiry.</x:v>
       </x:c>
       <x:c r="F194" s="127" t="str">
         <x:v>P0</x:v>
@@ -16925,17 +16931,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="127" t="str">
-        <x:v>Agent permission model</x:v>
+        <x:v>Risk classification L0-L4</x:v>
       </x:c>
       <x:c r="K194" s="127"/>
       <x:c r="L194" s="127"/>
       <x:c r="M194" s="127" t="str">
-        <x:v>Deny by default.</x:v>
+        <x:v>Production/destructive actions auditable.</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="127" t="str">
-        <x:v>R-186</x:v>
+        <x:v>R-185</x:v>
       </x:c>
       <x:c r="B195" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16944,13 +16950,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D195" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="E195" s="127" t="str">
-        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
+        <x:v>Central registry for tool identity, schema, permissions, risk, secrets, limits and audit.</x:v>
       </x:c>
       <x:c r="F195" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G195" s="127"/>
       <x:c r="H195" s="127" t="str">
@@ -16961,17 +16967,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J195" s="127" t="str">
-        <x:v>First-party Tool Registry</x:v>
+        <x:v>Agent permission model</x:v>
       </x:c>
       <x:c r="K195" s="127"/>
       <x:c r="L195" s="127"/>
       <x:c r="M195" s="127" t="str">
-        <x:v>No arbitrary agent-to-MCP connections.</x:v>
+        <x:v>Deny by default.</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="127" t="str">
-        <x:v>R-187</x:v>
+        <x:v>R-186</x:v>
       </x:c>
       <x:c r="B196" s="127" t="str">
         <x:v>MVP</x:v>
@@ -16980,13 +16986,13 @@
         <x:v>Tools</x:v>
       </x:c>
       <x:c r="D196" s="127" t="str">
-        <x:v>Tool secret broker</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="E196" s="127" t="str">
-        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
+        <x:v>All MCP traffic passes through Tool Registry/policy; unverified servers disabled by default.</x:v>
       </x:c>
       <x:c r="F196" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G196" s="127"/>
       <x:c r="H196" s="127" t="str">
@@ -17002,27 +17008,27 @@
       <x:c r="K196" s="127"/>
       <x:c r="L196" s="127"/>
       <x:c r="M196" s="127" t="str">
-        <x:v>Audit every secret grant.</x:v>
+        <x:v>No arbitrary agent-to-MCP connections.</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="127" t="str">
-        <x:v>R-188</x:v>
+        <x:v>R-187</x:v>
       </x:c>
       <x:c r="B197" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C197" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D197" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Tool secret broker</x:v>
       </x:c>
       <x:c r="E197" s="127" t="str">
-        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
+        <x:v>Provide short-lived scoped credentials to tools without placing raw secrets in prompts.</x:v>
       </x:c>
       <x:c r="F197" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G197" s="127"/>
       <x:c r="H197" s="127" t="str">
@@ -17033,32 +17039,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J197" s="127" t="str">
-        <x:v>Application IR v1</x:v>
+        <x:v>First-party Tool Registry</x:v>
       </x:c>
       <x:c r="K197" s="127"/>
       <x:c r="L197" s="127"/>
       <x:c r="M197" s="127" t="str">
-        <x:v>Not platform core.</x:v>
+        <x:v>Audit every secret grant.</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="127" t="str">
-        <x:v>R-189</x:v>
+        <x:v>R-188</x:v>
       </x:c>
       <x:c r="B198" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C198" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D198" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="E198" s="127" t="str">
-        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
+        <x:v>Define optional Supabase/Firebase-style generated backend for suitable small/medium apps.</x:v>
       </x:c>
       <x:c r="F198" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G198" s="127"/>
       <x:c r="H198" s="127" t="str">
@@ -17069,29 +17075,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J198" s="127" t="str">
-        <x:v>Architecture decision records</x:v>
+        <x:v>Application IR v1</x:v>
       </x:c>
       <x:c r="K198" s="127"/>
       <x:c r="L198" s="127"/>
       <x:c r="M198" s="127" t="str">
-        <x:v>References inform; benchmarks decide.</x:v>
+        <x:v>Not platform core.</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="127" t="str">
-        <x:v>R-190</x:v>
+        <x:v>R-189</x:v>
       </x:c>
       <x:c r="B199" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C199" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D199" s="127" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="E199" s="127" t="str">
-        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
+        <x:v>Benchmark major providers/frameworks before adoption and record evidence in ADR.</x:v>
       </x:c>
       <x:c r="F199" s="127" t="str">
         <x:v>P0</x:v>
@@ -17105,32 +17111,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J199" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>Architecture decision records</x:v>
       </x:c>
       <x:c r="K199" s="127"/>
       <x:c r="L199" s="127"/>
       <x:c r="M199" s="127" t="str">
-        <x:v>Architectural learning != code copying.</x:v>
+        <x:v>References inform; benchmarks decide.</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="127" t="str">
-        <x:v>R-191</x:v>
+        <x:v>R-190</x:v>
       </x:c>
       <x:c r="B200" s="127" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C200" s="127" t="str">
-        <x:v>Team</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D200" s="127" t="str">
-        <x:v>Shared engineering glossary</x:v>
+        <x:v>Open-source license review</x:v>
       </x:c>
       <x:c r="E200" s="127" t="str">
-        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
+        <x:v>Track repo/commit/license before reuse; require legal approval for source reuse.</x:v>
       </x:c>
       <x:c r="F200" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G200" s="127"/>
       <x:c r="H200" s="127" t="str">
@@ -17140,31 +17146,33 @@
         <x:f>IF(H200="Done",1,IF(H200="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J200" s="127"/>
+      <x:c r="J200" s="127" t="str">
+        <x:v>Build-vs-Buy benchmark process</x:v>
+      </x:c>
       <x:c r="K200" s="127"/>
       <x:c r="L200" s="127"/>
       <x:c r="M200" s="127" t="str">
-        <x:v>Use in docs and AI prompts.</x:v>
+        <x:v>Architectural learning != code copying.</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="127" t="str">
-        <x:v>R-192</x:v>
+        <x:v>R-191</x:v>
       </x:c>
       <x:c r="B201" s="127" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C201" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Team</x:v>
       </x:c>
       <x:c r="D201" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Shared engineering glossary</x:v>
       </x:c>
       <x:c r="E201" s="127" t="str">
-        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
+        <x:v>Publish common definitions for agent/tool/sandbox/MCP/HITL/checkpoint/BYOC/BaaS/ADR.</x:v>
       </x:c>
       <x:c r="F201" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G201" s="127"/>
       <x:c r="H201" s="127" t="str">
@@ -17174,30 +17182,28 @@
         <x:f>IF(H201="Done",1,IF(H201="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J201" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
-      </x:c>
+      <x:c r="J201" s="127"/>
       <x:c r="K201" s="127"/>
       <x:c r="L201" s="127"/>
       <x:c r="M201" s="127" t="str">
-        <x:v>Marketplace later.</x:v>
+        <x:v>Use in docs and AI prompts.</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="127" t="str">
-        <x:v>R-193</x:v>
+        <x:v>R-192</x:v>
       </x:c>
       <x:c r="B202" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C202" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D202" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="E202" s="127" t="str">
-        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
+        <x:v>Install verified third-party MCP servers with consent, version identity and scopes.</x:v>
       </x:c>
       <x:c r="F202" s="127" t="str">
         <x:v>P1</x:v>
@@ -17211,17 +17217,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="127" t="str">
-        <x:v>Local Mac Agent productized</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K202" s="127"/>
       <x:c r="L202" s="127"/>
       <x:c r="M202" s="127" t="str">
-        <x:v>Extends local mode beyond Mac.</x:v>
+        <x:v>Marketplace later.</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="127" t="str">
-        <x:v>R-194</x:v>
+        <x:v>R-193</x:v>
       </x:c>
       <x:c r="B203" s="127" t="str">
         <x:v>MID</x:v>
@@ -17230,10 +17236,10 @@
         <x:v>Execution</x:v>
       </x:c>
       <x:c r="D203" s="127" t="str">
-        <x:v>Hybrid BYOK/local mode</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="E203" s="127" t="str">
-        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
+        <x:v>Signed local agent for Mac/Windows/Linux with explicit workspace grants.</x:v>
       </x:c>
       <x:c r="F203" s="127" t="str">
         <x:v>P1</x:v>
@@ -17247,29 +17253,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="127" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
+        <x:v>Local Mac Agent productized</x:v>
       </x:c>
       <x:c r="K203" s="127"/>
       <x:c r="L203" s="127"/>
       <x:c r="M203" s="127" t="str">
-        <x:v>Privacy + cost option.</x:v>
+        <x:v>Extends local mode beyond Mac.</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="127" t="str">
-        <x:v>R-195</x:v>
+        <x:v>R-194</x:v>
       </x:c>
       <x:c r="B204" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C204" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D204" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Hybrid BYOK/local mode</x:v>
       </x:c>
       <x:c r="E204" s="127" t="str">
-        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
+        <x:v>Allow customer model key and selected local execution while preserving central policy.</x:v>
       </x:c>
       <x:c r="F204" s="127" t="str">
         <x:v>P1</x:v>
@@ -17283,17 +17289,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="127" t="str">
-        <x:v>Managed Linux sandbox adapter</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K204" s="127"/>
       <x:c r="L204" s="127"/>
       <x:c r="M204" s="127" t="str">
-        <x:v>Validate portability/failover.</x:v>
+        <x:v>Privacy + cost option.</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="127" t="str">
-        <x:v>R-196</x:v>
+        <x:v>R-195</x:v>
       </x:c>
       <x:c r="B205" s="127" t="str">
         <x:v>MID</x:v>
@@ -17302,13 +17308,13 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D205" s="127" t="str">
-        <x:v>Sandbox snapshots and warm pools</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="E205" s="127" t="str">
-        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
+        <x:v>Add alternate managed sandbox and provider health abstraction.</x:v>
       </x:c>
       <x:c r="F205" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G205" s="127"/>
       <x:c r="H205" s="127" t="str">
@@ -17319,32 +17325,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Managed Linux sandbox adapter</x:v>
       </x:c>
       <x:c r="K205" s="127"/>
       <x:c r="L205" s="127"/>
       <x:c r="M205" s="127" t="str">
-        <x:v>Do not optimize blindly.</x:v>
+        <x:v>Validate portability/failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="127" t="str">
-        <x:v>R-197</x:v>
+        <x:v>R-196</x:v>
       </x:c>
       <x:c r="B206" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C206" s="127" t="str">
-        <x:v>Developer Experience</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D206" s="127" t="str">
-        <x:v>Agent time-travel debugging</x:v>
+        <x:v>Sandbox snapshots and warm pools</x:v>
       </x:c>
       <x:c r="E206" s="127" t="str">
-        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
+        <x:v>Use snapshots/prewarming where metrics prove latency/cost benefit.</x:v>
       </x:c>
       <x:c r="F206" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G206" s="127"/>
       <x:c r="H206" s="127" t="str">
@@ -17355,32 +17361,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="127" t="str">
-        <x:v>Agent event ledger</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K206" s="127"/>
       <x:c r="L206" s="127"/>
       <x:c r="M206" s="127" t="str">
-        <x:v>Operator and developer debugging.</x:v>
+        <x:v>Do not optimize blindly.</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="127" t="str">
-        <x:v>R-198</x:v>
+        <x:v>R-197</x:v>
       </x:c>
       <x:c r="B207" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C207" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Developer Experience</x:v>
       </x:c>
       <x:c r="D207" s="127" t="str">
-        <x:v>Tool marketplace verification</x:v>
+        <x:v>Agent time-travel debugging</x:v>
       </x:c>
       <x:c r="E207" s="127" t="str">
-        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
+        <x:v>Inspect checkpoints, event ledger, tool calls and recovery path for a run.</x:v>
       </x:c>
       <x:c r="F207" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G207" s="127"/>
       <x:c r="H207" s="127" t="str">
@@ -17391,32 +17397,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Agent event ledger</x:v>
       </x:c>
       <x:c r="K207" s="127"/>
       <x:c r="L207" s="127"/>
       <x:c r="M207" s="127" t="str">
-        <x:v>Verified badge is evidence-based.</x:v>
+        <x:v>Operator and developer debugging.</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="127" t="str">
-        <x:v>R-199</x:v>
+        <x:v>R-198</x:v>
       </x:c>
       <x:c r="B208" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C208" s="127" t="str">
-        <x:v>Routing</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D208" s="127" t="str">
-        <x:v>Runtime provider cost-latency routing</x:v>
+        <x:v>Tool marketplace verification</x:v>
       </x:c>
       <x:c r="E208" s="127" t="str">
-        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
+        <x:v>Security/license/schema/reliability review before external tool publication.</x:v>
       </x:c>
       <x:c r="F208" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G208" s="127"/>
       <x:c r="H208" s="127" t="str">
@@ -17427,32 +17433,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="127" t="str">
-        <x:v>Second sandbox provider adapter</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K208" s="127"/>
       <x:c r="L208" s="127"/>
       <x:c r="M208" s="127" t="str">
-        <x:v>Policy can override cheapest route.</x:v>
+        <x:v>Verified badge is evidence-based.</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="127" t="str">
-        <x:v>R-200</x:v>
+        <x:v>R-199</x:v>
       </x:c>
       <x:c r="B209" s="127" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C209" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="D209" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Runtime provider cost-latency routing</x:v>
       </x:c>
       <x:c r="E209" s="127" t="str">
-        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
+        <x:v>Route among eligible providers using health, latency, region and cost.</x:v>
       </x:c>
       <x:c r="F209" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G209" s="127"/>
       <x:c r="H209" s="127" t="str">
@@ -17463,29 +17469,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="127" t="str">
-        <x:v>Rapid BaaS profile design</x:v>
+        <x:v>Second sandbox provider adapter</x:v>
       </x:c>
       <x:c r="K209" s="127"/>
       <x:c r="L209" s="127"/>
       <x:c r="M209" s="127" t="str">
-        <x:v>Keep portability via IR/contracts.</x:v>
+        <x:v>Policy can override cheapest route.</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="127" t="str">
-        <x:v>R-201</x:v>
+        <x:v>R-200</x:v>
       </x:c>
       <x:c r="B210" s="127" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C210" s="127" t="str">
-        <x:v>Tools</x:v>
+        <x:v>Backend Strategy</x:v>
       </x:c>
       <x:c r="D210" s="127" t="str">
-        <x:v>Customer private MCP servers</x:v>
+        <x:v>BaaS provider expansion</x:v>
       </x:c>
       <x:c r="E210" s="127" t="str">
-        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
+        <x:v>Support second Rapid BaaS provider behind backend profile contract.</x:v>
       </x:c>
       <x:c r="F210" s="127" t="str">
         <x:v>P2</x:v>
@@ -17499,32 +17505,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="127" t="str">
-        <x:v>Verified MCP install flow</x:v>
+        <x:v>Rapid BaaS profile design</x:v>
       </x:c>
       <x:c r="K210" s="127"/>
       <x:c r="L210" s="127"/>
       <x:c r="M210" s="127" t="str">
-        <x:v>Enterprise feature.</x:v>
+        <x:v>Keep portability via IR/contracts.</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="127" t="str">
-        <x:v>R-202</x:v>
+        <x:v>R-201</x:v>
       </x:c>
       <x:c r="B211" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C211" s="127" t="str">
-        <x:v>Execution</x:v>
+        <x:v>Tools</x:v>
       </x:c>
       <x:c r="D211" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>Customer private MCP servers</x:v>
       </x:c>
       <x:c r="E211" s="127" t="str">
-        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
+        <x:v>Allow customer-owned MCP endpoints with private scopes and network policy.</x:v>
       </x:c>
       <x:c r="F211" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G211" s="127"/>
       <x:c r="H211" s="127" t="str">
@@ -17535,32 +17541,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="127" t="str">
-        <x:v>BYOC / private runners</x:v>
+        <x:v>Verified MCP install flow</x:v>
       </x:c>
       <x:c r="K211" s="127"/>
       <x:c r="L211" s="127"/>
       <x:c r="M211" s="127" t="str">
-        <x:v>Central policy + audit remain.</x:v>
+        <x:v>Enterprise feature.</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="127" t="str">
-        <x:v>R-203</x:v>
+        <x:v>R-202</x:v>
       </x:c>
       <x:c r="B212" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C212" s="127" t="str">
-        <x:v>Runtime</x:v>
+        <x:v>Execution</x:v>
       </x:c>
       <x:c r="D212" s="127" t="str">
-        <x:v>Cross-region runtime scheduler</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="E212" s="127" t="str">
-        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
+        <x:v>Run sandboxes/builds in customer VPC/private infrastructure.</x:v>
       </x:c>
       <x:c r="F212" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G212" s="127"/>
       <x:c r="H212" s="127" t="str">
@@ -17571,17 +17577,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="127" t="str">
-        <x:v>Private BYOC runners</x:v>
+        <x:v>BYOC / private runners</x:v>
       </x:c>
       <x:c r="K212" s="127"/>
       <x:c r="L212" s="127"/>
       <x:c r="M212" s="127" t="str">
-        <x:v>Enterprise scale.</x:v>
+        <x:v>Central policy + audit remain.</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="127" t="str">
-        <x:v>R-204</x:v>
+        <x:v>R-203</x:v>
       </x:c>
       <x:c r="B213" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17590,10 +17596,10 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D213" s="127" t="str">
-        <x:v>Hardened microVM runner fleet</x:v>
+        <x:v>Cross-region runtime scheduler</x:v>
       </x:c>
       <x:c r="E213" s="127" t="str">
-        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
+        <x:v>Select execution region by policy, residency, availability and latency.</x:v>
       </x:c>
       <x:c r="F213" s="127" t="str">
         <x:v>P2</x:v>
@@ -17607,32 +17613,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="127" t="str">
-        <x:v>Provider cost-latency routing</x:v>
+        <x:v>Private BYOC runners</x:v>
       </x:c>
       <x:c r="K213" s="127"/>
       <x:c r="L213" s="127"/>
       <x:c r="M213" s="127" t="str">
-        <x:v>Do not build before benchmark.</x:v>
+        <x:v>Enterprise scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="127" t="str">
-        <x:v>R-205</x:v>
+        <x:v>R-204</x:v>
       </x:c>
       <x:c r="B214" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C214" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Runtime</x:v>
       </x:c>
       <x:c r="D214" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>Hardened microVM runner fleet</x:v>
       </x:c>
       <x:c r="E214" s="127" t="str">
-        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
+        <x:v>Own isolated runner fleet only when security/economics justify operational burden.</x:v>
       </x:c>
       <x:c r="F214" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G214" s="127"/>
       <x:c r="H214" s="127" t="str">
@@ -17643,29 +17649,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Provider cost-latency routing</x:v>
       </x:c>
       <x:c r="K214" s="127"/>
       <x:c r="L214" s="127"/>
       <x:c r="M214" s="127" t="str">
-        <x:v>Checkpoint-aware failover.</x:v>
+        <x:v>Do not build before benchmark.</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="127" t="str">
-        <x:v>R-206</x:v>
+        <x:v>R-205</x:v>
       </x:c>
       <x:c r="B215" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C215" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D215" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="E215" s="127" t="str">
-        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
+        <x:v>Retry eligible tasks on alternate provider without duplicating side effects.</x:v>
       </x:c>
       <x:c r="F215" s="127" t="str">
         <x:v>P1</x:v>
@@ -17679,17 +17685,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K215" s="127"/>
       <x:c r="L215" s="127"/>
       <x:c r="M215" s="127" t="str">
-        <x:v>Enterprise override support.</x:v>
+        <x:v>Checkpoint-aware failover.</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="127" t="str">
-        <x:v>R-207</x:v>
+        <x:v>R-206</x:v>
       </x:c>
       <x:c r="B216" s="127" t="str">
         <x:v>ADVANCED</x:v>
@@ -17698,13 +17704,13 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D216" s="127" t="str">
-        <x:v>Two-person critical approval</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="E216" s="127" t="str">
-        <x:v>Optional dual approval for L4 actions.</x:v>
+        <x:v>Version risk/action/approval policies as tested configuration.</x:v>
       </x:c>
       <x:c r="F216" s="127" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G216" s="127"/>
       <x:c r="H216" s="127" t="str">
@@ -17715,29 +17721,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="127" t="str">
-        <x:v>Policy-as-code approvals</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K216" s="127"/>
       <x:c r="L216" s="127"/>
       <x:c r="M216" s="127" t="str">
-        <x:v>High-risk enterprise.</x:v>
+        <x:v>Enterprise override support.</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="127" t="str">
-        <x:v>R-208</x:v>
+        <x:v>R-207</x:v>
       </x:c>
       <x:c r="B217" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C217" s="127" t="str">
-        <x:v>Models</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D217" s="127" t="str">
-        <x:v>Customer private model endpoints</x:v>
+        <x:v>Two-person critical approval</x:v>
       </x:c>
       <x:c r="E217" s="127" t="str">
-        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
+        <x:v>Optional dual approval for L4 actions.</x:v>
       </x:c>
       <x:c r="F217" s="127" t="str">
         <x:v>P2</x:v>
@@ -17751,29 +17757,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="127" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Policy-as-code approvals</x:v>
       </x:c>
       <x:c r="K217" s="127"/>
       <x:c r="L217" s="127"/>
       <x:c r="M217" s="127" t="str">
-        <x:v>No direct client-to-model coupling.</x:v>
+        <x:v>High-risk enterprise.</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="127" t="str">
-        <x:v>R-209</x:v>
+        <x:v>R-208</x:v>
       </x:c>
       <x:c r="B218" s="127" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C218" s="127" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D218" s="127" t="str">
-        <x:v>Automated provider benchmark suite</x:v>
+        <x:v>Customer private model endpoints</x:v>
       </x:c>
       <x:c r="E218" s="127" t="str">
-        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
+        <x:v>Support approved VPC/private model endpoints behind Model Gateway.</x:v>
       </x:c>
       <x:c r="F218" s="127" t="str">
         <x:v>P2</x:v>
@@ -17787,32 +17793,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="127" t="str">
-        <x:v>Build-vs-Buy benchmark process</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="K218" s="127"/>
       <x:c r="L218" s="127"/>
       <x:c r="M218" s="127" t="str">
-        <x:v>Feeds routing/ADR reviews.</x:v>
+        <x:v>No direct client-to-model coupling.</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="127" t="str">
-        <x:v>R-210</x:v>
+        <x:v>R-209</x:v>
       </x:c>
       <x:c r="B219" s="127" t="str">
-        <x:v>PRODUCTION</x:v>
+        <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C219" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D219" s="127" t="str">
-        <x:v>Crash-resume production test</x:v>
+        <x:v>Automated provider benchmark suite</x:v>
       </x:c>
       <x:c r="E219" s="127" t="str">
-        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
+        <x:v>Continuously measure model/runtime/tool providers for cost, latency and reliability.</x:v>
       </x:c>
       <x:c r="F219" s="127" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="G219" s="127"/>
       <x:c r="H219" s="127" t="str">
@@ -17823,17 +17829,17 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="127" t="str">
-        <x:v>Checkpoint and resume</x:v>
+        <x:v>Build-vs-Buy benchmark process</x:v>
       </x:c>
       <x:c r="K219" s="127"/>
       <x:c r="L219" s="127"/>
       <x:c r="M219" s="127" t="str">
-        <x:v>Production gate.</x:v>
+        <x:v>Feeds routing/ADR reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="127" t="str">
-        <x:v>R-211</x:v>
+        <x:v>R-210</x:v>
       </x:c>
       <x:c r="B220" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17842,10 +17848,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D220" s="127" t="str">
-        <x:v>Duplicate side-effect prevention test</x:v>
+        <x:v>Crash-resume production test</x:v>
       </x:c>
       <x:c r="E220" s="127" t="str">
-        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
+        <x:v>Prove tasks resume after worker/provider failure from last verified checkpoint.</x:v>
       </x:c>
       <x:c r="F220" s="127" t="str">
         <x:v>P0</x:v>
@@ -17859,7 +17865,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="127" t="str">
-        <x:v>Tool idempotency keys</x:v>
+        <x:v>Checkpoint and resume</x:v>
       </x:c>
       <x:c r="K220" s="127"/>
       <x:c r="L220" s="127"/>
@@ -17869,19 +17875,19 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="127" t="str">
-        <x:v>R-212</x:v>
+        <x:v>R-211</x:v>
       </x:c>
       <x:c r="B221" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C221" s="127" t="str">
-        <x:v>Realtime</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D221" s="127" t="str">
-        <x:v>WebSocket replay correctness SLO</x:v>
+        <x:v>Duplicate side-effect prevention test</x:v>
       </x:c>
       <x:c r="E221" s="127" t="str">
-        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
+        <x:v>Prove retry/resume/failover cannot duplicate external mutations.</x:v>
       </x:c>
       <x:c r="F221" s="127" t="str">
         <x:v>P0</x:v>
@@ -17895,7 +17901,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="127" t="str">
-        <x:v>WebSocket reconnect and replay</x:v>
+        <x:v>Tool idempotency keys</x:v>
       </x:c>
       <x:c r="K221" s="127"/>
       <x:c r="L221" s="127"/>
@@ -17905,19 +17911,19 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="127" t="str">
-        <x:v>R-213</x:v>
+        <x:v>R-212</x:v>
       </x:c>
       <x:c r="B222" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C222" s="127" t="str">
-        <x:v>Security</x:v>
+        <x:v>Realtime</x:v>
       </x:c>
       <x:c r="D222" s="127" t="str">
-        <x:v>MCP isolation and prompt-injection test</x:v>
+        <x:v>WebSocket replay correctness SLO</x:v>
       </x:c>
       <x:c r="E222" s="127" t="str">
-        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
+        <x:v>Prove ordered reconnect/replay with no missing or duplicated critical events.</x:v>
       </x:c>
       <x:c r="F222" s="127" t="str">
         <x:v>P0</x:v>
@@ -17931,7 +17937,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="127" t="str">
-        <x:v>MCP Gateway foundation</x:v>
+        <x:v>WebSocket reconnect and replay</x:v>
       </x:c>
       <x:c r="K222" s="127"/>
       <x:c r="L222" s="127"/>
@@ -17941,7 +17947,7 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="127" t="str">
-        <x:v>R-214</x:v>
+        <x:v>R-213</x:v>
       </x:c>
       <x:c r="B223" s="127" t="str">
         <x:v>PRODUCTION</x:v>
@@ -17950,10 +17956,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D223" s="127" t="str">
-        <x:v>Sandbox tenant isolation test</x:v>
+        <x:v>MCP isolation and prompt-injection test</x:v>
       </x:c>
       <x:c r="E223" s="127" t="str">
-        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
+        <x:v>Prove tool output cannot override policy and workspace/tool scopes are isolated.</x:v>
       </x:c>
       <x:c r="F223" s="127" t="str">
         <x:v>P0</x:v>
@@ -17967,7 +17973,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="127" t="str">
-        <x:v>SandboxProvider abstraction</x:v>
+        <x:v>MCP Gateway foundation</x:v>
       </x:c>
       <x:c r="K223" s="127"/>
       <x:c r="L223" s="127"/>
@@ -17977,19 +17983,19 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="127" t="str">
-        <x:v>R-215</x:v>
+        <x:v>R-214</x:v>
       </x:c>
       <x:c r="B224" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C224" s="127" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D224" s="127" t="str">
-        <x:v>Runtime provider outage failover</x:v>
+        <x:v>Sandbox tenant isolation test</x:v>
       </x:c>
       <x:c r="E224" s="127" t="str">
-        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
+        <x:v>Prove no cross-tenant filesystem/process/network/secret access.</x:v>
       </x:c>
       <x:c r="F224" s="127" t="str">
         <x:v>P0</x:v>
@@ -18003,7 +18009,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="127" t="str">
-        <x:v>Multi-provider sandbox failover</x:v>
+        <x:v>SandboxProvider abstraction</x:v>
       </x:c>
       <x:c r="K224" s="127"/>
       <x:c r="L224" s="127"/>
@@ -18013,19 +18019,19 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="127" t="str">
-        <x:v>R-216</x:v>
+        <x:v>R-215</x:v>
       </x:c>
       <x:c r="B225" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C225" s="127" t="str">
-        <x:v>Governance</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D225" s="127" t="str">
-        <x:v>Approval auditability test</x:v>
+        <x:v>Runtime provider outage failover</x:v>
       </x:c>
       <x:c r="E225" s="127" t="str">
-        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
+        <x:v>Prove eligible jobs fail over safely during provider outage.</x:v>
       </x:c>
       <x:c r="F225" s="127" t="str">
         <x:v>P0</x:v>
@@ -18039,7 +18045,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="127" t="str">
-        <x:v>Approval object and immutable audit</x:v>
+        <x:v>Multi-provider sandbox failover</x:v>
       </x:c>
       <x:c r="K225" s="127"/>
       <x:c r="L225" s="127"/>
@@ -18049,22 +18055,22 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="127" t="str">
-        <x:v>R-217</x:v>
+        <x:v>R-216</x:v>
       </x:c>
       <x:c r="B226" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C226" s="127" t="str">
-        <x:v>Backend Strategy</x:v>
+        <x:v>Governance</x:v>
       </x:c>
       <x:c r="D226" s="127" t="str">
-        <x:v>BaaS to custom migration test</x:v>
+        <x:v>Approval auditability test</x:v>
       </x:c>
       <x:c r="E226" s="127" t="str">
-        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+        <x:v>Prove who approved what, when, scope, risk, environment and expiration.</x:v>
       </x:c>
       <x:c r="F226" s="127" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G226" s="127"/>
       <x:c r="H226" s="127" t="str">
@@ -18075,65 +18081,65 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J226" s="127" t="str">
-        <x:v>BaaS provider expansion</x:v>
+        <x:v>Approval object and immutable audit</x:v>
       </x:c>
       <x:c r="K226" s="127"/>
       <x:c r="L226" s="127"/>
       <x:c r="M226" s="127" t="str">
-        <x:v>Avoid backend lock-in.</x:v>
+        <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
-      <x:c r="A227" t="str">
-        <x:v>R-218</x:v>
-      </x:c>
-      <x:c r="B227" t="str">
+      <x:c r="A227" s="127" t="str">
+        <x:v>R-217</x:v>
+      </x:c>
+      <x:c r="B227" s="127" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
-      <x:c r="C227" t="str">
-        <x:v>Security</x:v>
-      </x:c>
-      <x:c r="D227" t="str">
-        <x:v>Local Agent security lifecycle</x:v>
-      </x:c>
-      <x:c r="E227" t="str">
-        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
-      </x:c>
-      <x:c r="F227" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="G227"/>
-      <x:c r="H227" t="str">
+      <x:c r="C227" s="127" t="str">
+        <x:v>Backend Strategy</x:v>
+      </x:c>
+      <x:c r="D227" s="127" t="str">
+        <x:v>BaaS to custom migration test</x:v>
+      </x:c>
+      <x:c r="E227" s="127" t="str">
+        <x:v>Prove project can migrate backend profile using IR/contracts without rediscovering product behavior.</x:v>
+      </x:c>
+      <x:c r="F227" s="127" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="G227" s="127"/>
+      <x:c r="H227" s="127" t="str">
         <x:v>Not Started</x:v>
       </x:c>
-      <x:c r="I227" t="n">
+      <x:c r="I227" s="390" t="n">
         <x:f>IF(H227="Done",1,IF(H227="In Progress",0.5,0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J227" t="str">
-        <x:v>Cross-platform Local Agent</x:v>
-      </x:c>
-      <x:c r="K227"/>
-      <x:c r="L227"/>
-      <x:c r="M227" t="str">
-        <x:v>Production gate.</x:v>
+      <x:c r="J227" s="127" t="str">
+        <x:v>BaaS provider expansion</x:v>
+      </x:c>
+      <x:c r="K227" s="127"/>
+      <x:c r="L227" s="127"/>
+      <x:c r="M227" s="127" t="str">
+        <x:v>Avoid backend lock-in.</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" t="str">
-        <x:v>R-219</x:v>
+        <x:v>R-218</x:v>
       </x:c>
       <x:c r="B228" t="str">
         <x:v>PRODUCTION</x:v>
       </x:c>
       <x:c r="C228" t="str">
-        <x:v>Compliance</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D228" t="str">
-        <x:v>OSS license and SBOM gate</x:v>
+        <x:v>Local Agent security lifecycle</x:v>
       </x:c>
       <x:c r="E228" t="str">
-        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+        <x:v>Signed install/update, folder grant, revoke/uninstall and local log controls verified.</x:v>
       </x:c>
       <x:c r="F228" t="str">
         <x:v>P0</x:v>
@@ -18147,11 +18153,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J228" t="str">
-        <x:v>Open-source license review</x:v>
+        <x:v>Cross-platform Local Agent</x:v>
       </x:c>
       <x:c r="K228"/>
       <x:c r="L228"/>
       <x:c r="M228" t="str">
+        <x:v>Production gate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" t="str">
+        <x:v>R-219</x:v>
+      </x:c>
+      <x:c r="B229" t="str">
+        <x:v>PRODUCTION</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>Compliance</x:v>
+      </x:c>
+      <x:c r="D229" t="str">
+        <x:v>OSS license and SBOM gate</x:v>
+      </x:c>
+      <x:c r="E229" t="str">
+        <x:v>Block release when third-party license/SBOM obligations are unresolved.</x:v>
+      </x:c>
+      <x:c r="F229" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="G229"/>
+      <x:c r="H229" t="str">
+        <x:v>Not Started</x:v>
+      </x:c>
+      <x:c r="I229" t="n">
+        <x:f>IF(H229="Done",1,IF(H229="In Progress",0.5,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J229" t="str">
+        <x:v>Open-source license review</x:v>
+      </x:c>
+      <x:c r="K229"/>
+      <x:c r="L229"/>
+      <x:c r="M229" t="str">
         <x:v>Production gate.</x:v>
       </x:c>
     </x:row>
@@ -18160,7 +18202,7 @@
     <x:mergeCell ref="A2:M2"/>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H4:H117">
+  <x:conditionalFormatting sqref="H4:H118">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>H4="Done"</x:formula>
     </x:cfRule>
@@ -18175,34 +18217,34 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="10">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B117">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B4:B118">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F117">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F118">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H117">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H118">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B118:B141">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B119:B142">
       <x:formula1>"MVP,MID,ADVANCED,PRODUCTION"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F118:F141">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F119:F142">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H118:H141">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H119:H142">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F142:F177">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F143:F178">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H142:H177">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H143:H178">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H226">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H4:H227">
       <x:formula1>"Not Started,In Progress,Blocked,Done,Deferred"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F226">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="F4:F227">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -10662,11 +10662,11 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
         <x:v>R-220</x:v>
@@ -10675,7 +10675,7 @@
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation in progress on ai/R-221-cross-provider-fallback; explicit fallback chain + per-provider circuit breaker added to the gateway; offline tests added; cloud_calls=0.</x:v>
+        <x:v>Implementation d0ee9f75b0d124fe60f1121b7f2a70d3b73040de; task verify passed with 86 agent-engine tests (8 new fallback/circuit-breaker tests); explicit allowlist fail-over + per-provider breaker; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
         <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 18.3, 84, 89, 90, 91, and 92.</x:v>

--- a/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
+++ b/R_&_D/OmniStackAI_Execution_Tracker_v6.xlsx
@@ -2389,7 +2389,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M118" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RoadmapTable" displayName="RoadmapTable" ref="A3:M119" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Phase"/>
@@ -2701,11 +2701,11 @@
         </x:is>
       </x:c>
       <x:c r="B5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"MVP")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$230,"MVP")</x:f>
         <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"MVP",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$230,"MVP",Phase_Roadmap!$H$4:$H$230,"Done")</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="376" t="n">
@@ -2718,7 +2718,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F5)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$230,F5)</x:f>
         <x:v>210</x:v>
       </x:c>
     </x:row>
@@ -2729,11 +2729,11 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"MID")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$230,"MID")</x:f>
         <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"MID",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$230,"MID",Phase_Roadmap!$H$4:$H$230,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="376" t="n">
@@ -2746,7 +2746,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F6)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$230,F6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2757,11 +2757,11 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"ADVANCED")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$230,"ADVANCED")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"ADVANCED",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$230,"ADVANCED",Phase_Roadmap!$H$4:$H$230,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="376" t="n">
@@ -2774,7 +2774,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F7)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$230,F7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2785,11 +2785,11 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$229,"PRODUCTION")</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$B$4:$B$230,"PRODUCTION")</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="32" t="n">
-        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$229,"PRODUCTION",Phase_Roadmap!$H$4:$H$229,"Done")</x:f>
+        <x:f>COUNTIFS(Phase_Roadmap!$B$4:$B$230,"PRODUCTION",Phase_Roadmap!$H$4:$H$230,"Done")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="376" t="n">
@@ -2802,7 +2802,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F8)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$230,F8)</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2813,7 +2813,7 @@
         </x:is>
       </x:c>
       <x:c r="G9" s="32" t="n">
-        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$229,F9)</x:f>
+        <x:f>COUNTIF(Phase_Roadmap!$H$4:$H$230,F9)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -10641,19 +10641,19 @@
     </x:row>
     <x:row r="9" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A9" s="32" t="str">
-        <x:v>R-221</x:v>
+        <x:v>R-222</x:v>
       </x:c>
       <x:c r="B9" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C9" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Console</x:v>
       </x:c>
       <x:c r="D9" s="32" t="str">
-        <x:v>Cross-provider fallback and circuit breaking</x:v>
+        <x:v>Platform console slice (model &amp; cost overview)</x:v>
       </x:c>
       <x:c r="E9" s="32" t="str">
-        <x:v>Add explicit allowlist-driven cross-provider fallback and per-provider circuit breaking to the gateway: on a retriable failure advance to the next allowed, registered, circuit-closed candidate; a per-provider breaker opens after repeated failures and recovers after a cooldown.</x:v>
+        <x:v>First visual console under apps/console-web: renders providers (local + all supported cloud, with active key-state), the Balanced routing ladder, the price book, and the usage/cost dashboard from a metadata-only snapshot. Dependency-free static slice; Next.js upgrade deferred until the build environment can install the toolchain.</x:v>
       </x:c>
       <x:c r="F9" s="32" t="str">
         <x:v>P0</x:v>
@@ -10662,28 +10662,28 @@
         <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H9" s="32" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="I9" s="376" t="n">
         <x:f>IF(H9="Done",1,IF(H9="In Progress",0.5,0))</x:f>
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J9" s="32" t="str">
-        <x:v>R-220</x:v>
+        <x:v>R-221</x:v>
       </x:c>
       <x:c r="K9" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L9" s="32" t="str">
-        <x:v>Implementation d0ee9f75b0d124fe60f1121b7f2a70d3b73040de; task verify passed with 86 agent-engine tests (8 new fallback/circuit-breaker tests); explicit allowlist fail-over + per-provider breaker; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation in progress on ai/R-222-console-web; static platform console + Python overview exporter added; local_calls=0, cloud_calls=0.</x:v>
       </x:c>
       <x:c r="M9" s="32" t="str">
-        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 18.3, 84, 89, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (advanced, smooth, secure platform) from Brief Sections 8, 15.2, 40, 41, 77, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A10" s="32" t="str">
-        <x:v>R-220</x:v>
+        <x:v>R-221</x:v>
       </x:c>
       <x:c r="B10" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10692,10 +10692,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D10" s="32" t="str">
-        <x:v>Cloud streaming (Server-Sent Events)</x:v>
+        <x:v>Cross-provider fallback and circuit breaking</x:v>
       </x:c>
       <x:c r="E10" s="32" t="str">
-        <x:v>Replace the single-event cloud stream wrapper with true incremental SSE streaming for OpenAI-compatible, Anthropic, and Gemini adapters; ordered delta events plus a final event with measured usage, reusing the HTTP-safety bounds.</x:v>
+        <x:v>Add explicit allowlist-driven cross-provider fallback and per-provider circuit breaking to the gateway: on a retriable failure advance to the next allowed, registered, circuit-closed candidate; a per-provider breaker opens after repeated failures and recovers after a cooldown.</x:v>
       </x:c>
       <x:c r="F10" s="32" t="str">
         <x:v>P0</x:v>
@@ -10711,21 +10711,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="32" t="str">
-        <x:v>R-009</x:v>
+        <x:v>R-220</x:v>
       </x:c>
       <x:c r="K10" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L10" s="32" t="str">
-        <x:v>Implementation 4e31841e730a6466da55843ff352f7144dd763e9; task verify passed with 78 agent-engine tests (5 new SSE streaming tests); true incremental streaming for OpenAI/Anthropic/Gemini; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation d0ee9f75b0d124fe60f1121b7f2a70d3b73040de; task verify passed with 86 agent-engine tests (8 new fallback/circuit-breaker tests); explicit allowlist fail-over + per-provider breaker; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M10" s="32" t="str">
-        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 57, 84, 85, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 18.3, 84, 89, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A11" s="32" t="str">
-        <x:v>R-009</x:v>
+        <x:v>R-220</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10734,10 +10734,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D11" s="32" t="str">
-        <x:v>Usage and cost accounting</x:v>
+        <x:v>Cloud streaming (Server-Sent Events)</x:v>
       </x:c>
       <x:c r="E11" s="32" t="str">
-        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
+        <x:v>Replace the single-event cloud stream wrapper with true incremental SSE streaming for OpenAI-compatible, Anthropic, and Gemini adapters; ordered delta events plus a final event with measured usage, reusing the HTTP-safety bounds.</x:v>
       </x:c>
       <x:c r="F11" s="32" t="str">
         <x:v>P0</x:v>
@@ -10753,21 +10753,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="K11" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L11" s="32" t="str">
-        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation 4e31841e730a6466da55843ff352f7144dd763e9; task verify passed with 78 agent-engine tests (5 new SSE streaming tests); true incremental streaming for OpenAI/Anthropic/Gemini; cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M11" s="32" t="str">
-        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (complete both required items one by one) from Brief Sections 18, 57, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="32" t="str">
-        <x:v>R-008</x:v>
+        <x:v>R-009</x:v>
       </x:c>
       <x:c r="B12" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10776,10 +10776,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D12" s="32" t="str">
-        <x:v>Cloud API-key provider adapters</x:v>
+        <x:v>Usage and cost accounting</x:v>
       </x:c>
       <x:c r="E12" s="32" t="str">
-        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
+        <x:v>Record every gateway dispatch as an immutable metadata-only usage record and compute estimated cost from a configurable price book (local Ollama = zero); aggregate totals, per-provider/model breakdowns, latency percentiles, and cost per successful call. No prompt content or secret is stored.</x:v>
       </x:c>
       <x:c r="F12" s="32" t="str">
         <x:v>P0</x:v>
@@ -10795,21 +10795,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="K12" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L12" s="32" t="str">
-        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation f2fc8654c6a5717e292adcdc2abb5da2fd7409c2; task verify passed with 74 agent-engine tests (13 new accounting tests); deterministic accounting, metadata-only records, local_calls=0, cloud_calls=0; live gateway prints cost summary; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M12" s="32" t="str">
-        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval (best-in-class usage/cost accounting) from Brief Sections 18.4, 23, 68, 84, 85, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A13" s="32" t="str">
-        <x:v>R-007</x:v>
+        <x:v>R-008</x:v>
       </x:c>
       <x:c r="B13" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10818,10 +10818,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D13" s="32" t="str">
-        <x:v>Balanced Model Gateway router</x:v>
+        <x:v>Cloud API-key provider adapters</x:v>
       </x:c>
       <x:c r="E13" s="32" t="str">
-        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
+        <x:v>Add key-activated cloud ModelProvider adapters (Anthropic, OpenAI, Gemini, OpenRouter, Groq) behind the shared boundary with an env bootstrap; each works when its API key is set, with an overridable default model. Local Ollama stays default and no key means no cloud call.</x:v>
       </x:c>
       <x:c r="F13" s="32" t="str">
         <x:v>P0</x:v>
@@ -10837,21 +10837,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J13" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="K13" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L13" s="32" t="str">
-        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
+        <x:v>Implementation eeade72e84c7f1ebd71dfc8c0f7c2f4db0f79677; task verify passed with 61 agent-engine tests (19 new cloud/bootstrap tests); no cloud key configured so cloud_calls=0; local gateway run works on qwen2.5-coder:14b and qwen3.5:9b; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M13" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
+        <x:v>Reconstructed with founder approval (configure each provider; run locally on Ollama until keys are added) from Brief Sections 18, 18.3, 84, 85, 87, 90, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A14" s="32" t="str">
-        <x:v>R-006</x:v>
+        <x:v>R-007</x:v>
       </x:c>
       <x:c r="B14" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10860,16 +10860,16 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
-        <x:v>Loopback Ollama provider adapter</x:v>
+        <x:v>Balanced Model Gateway router</x:v>
       </x:c>
       <x:c r="E14" s="32" t="str">
-        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
+        <x:v>Route model work under Balanced policy: reject L0 deterministic work, send sub-L3 work to the local Ollama provider, escalate L3/L4 to a cloud provider only when one is registered, guard the context budget, and never silently fall back to cloud.</x:v>
       </x:c>
       <x:c r="F14" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G14" s="32" t="str">
-        <x:v>Codex</x:v>
+        <x:v>Claude (Opus 4.8)</x:v>
       </x:c>
       <x:c r="H14" s="32" t="str">
         <x:v>Done</x:v>
@@ -10879,21 +10879,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="K14" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L14" s="32" t="str">
-        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
+        <x:v>Implementation 9faacd23dc22c6773f9a51dc58087d557c0be391; task verify passed with 42 agent-engine tests (14 new gateway tests); task agent-engine:gateway:run passed live on qwen2.5-coder:14b and qwen3.5:9b (L1/L2 to ollama-local, L0/L3/L4 refused); local_calls=4, cloud_calls=0; Compose unchanged (postgres, control-plane).</x:v>
       </x:c>
       <x:c r="M14" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18, 18.1, 18.2, 18.3, 84, 85, 91, and 92; founder intent to support both cloud API-key and local providers one at a time.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A15" s="32" t="str">
-        <x:v>R-005</x:v>
+        <x:v>R-006</x:v>
       </x:c>
       <x:c r="B15" s="32" t="str">
         <x:v>MVP</x:v>
@@ -10902,10 +10902,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D15" s="32" t="str">
-        <x:v>ModelProvider contract and registry</x:v>
+        <x:v>Loopback Ollama provider adapter</x:v>
       </x:c>
       <x:c r="E15" s="32" t="str">
-        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
+        <x:v>Implement bounded health, discovery, chat generation, and NDJSON streaming against the accepted ModelProvider contract.</x:v>
       </x:c>
       <x:c r="F15" s="32" t="str">
         <x:v>P0</x:v>
@@ -10921,33 +10921,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="K15" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L15" s="32" t="str">
-        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
+        <x:v>Implementation 8061ca3b129539ada4b0838d7d70c8acd3df1ea3; task verify, adapter tests, and live loopback conformance passed; local_calls=3, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M15" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 84, 85, 91, and 92.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A16" s="32" t="str">
-        <x:v>R-004</x:v>
+        <x:v>R-005</x:v>
       </x:c>
       <x:c r="B16" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C16" s="32" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D16" s="32" t="str">
-        <x:v>Go control-plane foundation</x:v>
+        <x:v>ModelProvider contract and registry</x:v>
       </x:c>
       <x:c r="E16" s="32" t="str">
-        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
+        <x:v>Define the vendor-neutral Python provider protocol, typed model-call records, and deterministic registry before any adapter exists.</x:v>
       </x:c>
       <x:c r="F16" s="32" t="str">
         <x:v>P0</x:v>
@@ -10963,33 +10963,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J16" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="K16" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L16" s="32" t="str">
-        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
+        <x:v>Implementation afdc4ba9c14b231dece9533dbdd39e1e79e9ace3; task verify and 13 contract tests passed; local_calls=2 inconclusive, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M16" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 18.3, 75, 83, 84, and 91.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A17" s="32" t="str">
-        <x:v>R-003</x:v>
+        <x:v>R-004</x:v>
       </x:c>
       <x:c r="B17" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C17" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Backend</x:v>
       </x:c>
       <x:c r="D17" s="32" t="str">
-        <x:v>Local Ollama Stage 0 bootstrap</x:v>
+        <x:v>Go control-plane foundation</x:v>
       </x:c>
       <x:c r="E17" s="32" t="str">
-        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
+        <x:v>Add the minimal Go modular-monolith service with typed configuration, liveness, PostgreSQL readiness, and graceful shutdown.</x:v>
       </x:c>
       <x:c r="F17" s="32" t="str">
         <x:v>P0</x:v>
@@ -11005,33 +11005,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="K17" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L17" s="32" t="str">
-        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
+        <x:v>Implementation c44fd8d013e3ec1497ccb4ab55f1433df042aeb5; task verify, race tests, and live health/readiness passed; local_calls=1, cloud_calls=0</x:v>
       </x:c>
       <x:c r="M17" s="32" t="str">
-        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 33, 74, and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A18" s="32" t="str">
-        <x:v>R-002</x:v>
+        <x:v>R-003</x:v>
       </x:c>
       <x:c r="B18" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C18" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D18" s="32" t="str">
-        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
+        <x:v>Local Ollama Stage 0 bootstrap</x:v>
       </x:c>
       <x:c r="E18" s="32" t="str">
-        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
+        <x:v>Validate a loopback-only Ollama runtime, discover the configured local coder, and run a deterministic inference smoke test.</x:v>
       </x:c>
       <x:c r="F18" s="32" t="str">
         <x:v>P0</x:v>
@@ -11047,33 +11047,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="K18" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L18" s="32" t="str">
-        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
+        <x:v>task verify: PASS; task ollama:verify: qwen2.5-coder:14b generated 6 tokens, cloud calls 0; implementation commit 822db27aa9c9e6ab836c28abba10f41dc27918d7</x:v>
       </x:c>
       <x:c r="M18" s="32" t="str">
-        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
+        <x:v>Reconstructed with founder approval from Brief Sections 79 and 84.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A19" s="32" t="str">
-        <x:v>R-001</x:v>
+        <x:v>R-002</x:v>
       </x:c>
       <x:c r="B19" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C19" s="32" t="str">
-        <x:v>Foundation</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
-        <x:v>Platform monorepo bootstrap</x:v>
+        <x:v>PostgreSQL + pgvector local bootstrap</x:v>
       </x:c>
       <x:c r="E19" s="32" t="str">
-        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
+        <x:v>Add local Docker Compose PostgreSQL with pgvector and a versioned initial migration.</x:v>
       </x:c>
       <x:c r="F19" s="32" t="str">
         <x:v>P0</x:v>
@@ -11089,53 +11089,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J19" s="32" t="str">
-        <x:v>None</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="K19" s="32" t="str">
         <x:v>Founder Stage 0</x:v>
       </x:c>
       <x:c r="L19" s="32" t="str">
-        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+        <x:v>task verify: PASS; task db:verify: PostgreSQL healthy, pgvector 0.8.6, migration 1; implementation commit 56bf4b0dea5486f8d6dcde0c7b1054249ebbb064</x:v>
       </x:c>
       <x:c r="M19" s="32" t="str">
-        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+        <x:v>Reconstructed with founder approval from the kickoff kit's canonical R-002 example.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>R-010</x:v>
+        <x:v>R-001</x:v>
       </x:c>
       <x:c r="B20" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C20" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Foundation</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
-        <x:v>Native iOS Agent</x:v>
+        <x:v>Platform monorepo bootstrap</x:v>
       </x:c>
       <x:c r="E20" s="32" t="str">
-        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
+        <x:v>Bootstrap the Section 74 skeleton and Stage 0 portable onboarding, verification, state, and handoff contract without implementing services or infrastructure.</x:v>
       </x:c>
       <x:c r="F20" s="32" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="G20" s="32"/>
+      <x:c r="G20" s="32" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="H20" s="32" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I20" s="376" t="n">
         <x:f>IF(H20="Done",1,IF(H20="In Progress",0.5,0))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="32"/>
-      <x:c r="K20" s="32"/>
-      <x:c r="L20" s="32"/>
-      <x:c r="M20" s="32"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K20" s="32" t="str">
+        <x:v>Founder Stage 0</x:v>
+      </x:c>
+      <x:c r="L20" s="32" t="str">
+        <x:v>task verify: PASS; implementation commit 655f01fa0425e8df9022ce6bb1d2040f56b1cb73</x:v>
+      </x:c>
+      <x:c r="M20" s="32" t="str">
+        <x:v>Reconstructed with founder approval because R-001 through R-009 were absent from the supplied workbook.</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>R-011</x:v>
+        <x:v>R-010</x:v>
       </x:c>
       <x:c r="B21" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11144,10 +11154,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D21" s="32" t="str">
-        <x:v>Web/Admin Agent</x:v>
+        <x:v>Native iOS Agent</x:v>
       </x:c>
       <x:c r="E21" s="32" t="str">
-        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
+        <x:v>Activated only for native iOS targets or native modules; generates Swift + SwiftUI using project conventions.</x:v>
       </x:c>
       <x:c r="F21" s="32" t="str">
         <x:v>P0</x:v>
@@ -11167,7 +11177,7 @@
     </x:row>
     <x:row r="22" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A22" s="32" t="str">
-        <x:v>R-012</x:v>
+        <x:v>R-011</x:v>
       </x:c>
       <x:c r="B22" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11176,10 +11186,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
-        <x:v>Backend Agent</x:v>
+        <x:v>Web/Admin Agent</x:v>
       </x:c>
       <x:c r="E22" s="32" t="str">
-        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
+        <x:v>Generate/modify React/Next.js TypeScript.</x:v>
       </x:c>
       <x:c r="F22" s="32" t="str">
         <x:v>P0</x:v>
@@ -11199,7 +11209,7 @@
     </x:row>
     <x:row r="23" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A23" s="32" t="str">
-        <x:v>R-013</x:v>
+        <x:v>R-012</x:v>
       </x:c>
       <x:c r="B23" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11208,10 +11218,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D23" s="32" t="str">
-        <x:v>Database Agent</x:v>
+        <x:v>Backend Agent</x:v>
       </x:c>
       <x:c r="E23" s="32" t="str">
-        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
+        <x:v>Generate/modify backend services; platform default Go/Python, generated app backend selectable.</x:v>
       </x:c>
       <x:c r="F23" s="32" t="str">
         <x:v>P0</x:v>
@@ -11231,7 +11241,7 @@
     </x:row>
     <x:row r="24" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A24" s="32" t="str">
-        <x:v>R-014</x:v>
+        <x:v>R-013</x:v>
       </x:c>
       <x:c r="B24" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11240,10 +11250,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
-        <x:v>QA Agent</x:v>
+        <x:v>Database Agent</x:v>
       </x:c>
       <x:c r="E24" s="32" t="str">
-        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
+        <x:v>Schema, indexes, migrations, rollback strategy and query checks.</x:v>
       </x:c>
       <x:c r="F24" s="32" t="str">
         <x:v>P0</x:v>
@@ -11263,7 +11273,7 @@
     </x:row>
     <x:row r="25" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A25" s="32" t="str">
-        <x:v>R-015</x:v>
+        <x:v>R-014</x:v>
       </x:c>
       <x:c r="B25" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11272,10 +11282,10 @@
         <x:v>Agents</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
-        <x:v>Security Review Agent</x:v>
+        <x:v>QA Agent</x:v>
       </x:c>
       <x:c r="E25" s="32" t="str">
-        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
+        <x:v>Select tests from impact graph and add tests for new behavior.</x:v>
       </x:c>
       <x:c r="F25" s="32" t="str">
         <x:v>P0</x:v>
@@ -11295,19 +11305,19 @@
     </x:row>
     <x:row r="26" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A26" s="32" t="str">
-        <x:v>R-016</x:v>
+        <x:v>R-015</x:v>
       </x:c>
       <x:c r="B26" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C26" s="32" t="str">
-        <x:v>Change Safety</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>Change Impact Engine v1</x:v>
+        <x:v>Security Review Agent</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
-        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
+        <x:v>Scan change for auth, secrets, input validation and dependency risk.</x:v>
       </x:c>
       <x:c r="F26" s="32" t="str">
         <x:v>P0</x:v>
@@ -11327,7 +11337,7 @@
     </x:row>
     <x:row r="27" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>R-017</x:v>
+        <x:v>R-016</x:v>
       </x:c>
       <x:c r="B27" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11336,10 +11346,10 @@
         <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>Blast-radius policy</x:v>
+        <x:v>Change Impact Engine v1</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
-        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
+        <x:v>Identify affected modules/APIs/schema/tests before edits.</x:v>
       </x:c>
       <x:c r="F27" s="32" t="str">
         <x:v>P0</x:v>
@@ -11359,19 +11369,19 @@
     </x:row>
     <x:row r="28" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A28" s="32" t="str">
-        <x:v>R-018</x:v>
+        <x:v>R-017</x:v>
       </x:c>
       <x:c r="B28" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C28" s="32" t="str">
-        <x:v>Code Intelligence</x:v>
+        <x:v>Change Safety</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>Repository index</x:v>
+        <x:v>Blast-radius policy</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
-        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
+        <x:v>Reject or require review when changed files exceed expected scope.</x:v>
       </x:c>
       <x:c r="F28" s="32" t="str">
         <x:v>P0</x:v>
@@ -11391,7 +11401,7 @@
     </x:row>
     <x:row r="29" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A29" s="32" t="str">
-        <x:v>R-019</x:v>
+        <x:v>R-018</x:v>
       </x:c>
       <x:c r="B29" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11400,10 +11410,10 @@
         <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>Semantic context retrieval</x:v>
+        <x:v>Repository index</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
-        <x:v>Send only relevant code/context to models.</x:v>
+        <x:v>Symbols, imports, routes, schemas and dependencies indexed per commit.</x:v>
       </x:c>
       <x:c r="F29" s="32" t="str">
         <x:v>P0</x:v>
@@ -11423,19 +11433,19 @@
     </x:row>
     <x:row r="30" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A30" s="32" t="str">
-        <x:v>R-020</x:v>
+        <x:v>R-019</x:v>
       </x:c>
       <x:c r="B30" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C30" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Code Intelligence</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>Structured patch engine</x:v>
+        <x:v>Semantic context retrieval</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
-        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
+        <x:v>Send only relevant code/context to models.</x:v>
       </x:c>
       <x:c r="F30" s="32" t="str">
         <x:v>P0</x:v>
@@ -11455,19 +11465,19 @@
     </x:row>
     <x:row r="31" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A31" s="32" t="str">
-        <x:v>R-021</x:v>
+        <x:v>R-020</x:v>
       </x:c>
       <x:c r="B31" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C31" s="32" t="str">
-        <x:v>Git</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D31" s="32" t="str">
-        <x:v>Branch per task</x:v>
+        <x:v>Structured patch engine</x:v>
       </x:c>
       <x:c r="E31" s="32" t="str">
-        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
+        <x:v>Prefer symbol/AST-aware targeted patches over full-file rewrites.</x:v>
       </x:c>
       <x:c r="F31" s="32" t="str">
         <x:v>P0</x:v>
@@ -11487,7 +11497,7 @@
     </x:row>
     <x:row r="32" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A32" s="32" t="str">
-        <x:v>R-022</x:v>
+        <x:v>R-021</x:v>
       </x:c>
       <x:c r="B32" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11496,10 +11506,10 @@
         <x:v>Git</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>Non-destructive rollback</x:v>
+        <x:v>Branch per task</x:v>
       </x:c>
       <x:c r="E32" s="32" t="str">
-        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
+        <x:v>Every AI task runs on its own branch/checkpoint.</x:v>
       </x:c>
       <x:c r="F32" s="32" t="str">
         <x:v>P0</x:v>
@@ -11519,19 +11529,19 @@
     </x:row>
     <x:row r="33" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A33" s="32" t="str">
-        <x:v>R-023</x:v>
+        <x:v>R-022</x:v>
       </x:c>
       <x:c r="B33" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C33" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Git</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>Model gateway</x:v>
+        <x:v>Non-destructive rollback</x:v>
       </x:c>
       <x:c r="E33" s="32" t="str">
-        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
+        <x:v>Use Git revert/cherry-pick; never destroy later work as the only rollback method.</x:v>
       </x:c>
       <x:c r="F33" s="32" t="str">
         <x:v>P0</x:v>
@@ -11551,7 +11561,7 @@
     </x:row>
     <x:row r="34" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A34" s="32" t="str">
-        <x:v>R-024</x:v>
+        <x:v>R-023</x:v>
       </x:c>
       <x:c r="B34" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11560,10 +11570,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D34" s="32" t="str">
-        <x:v>Routing + fallback</x:v>
+        <x:v>Model gateway</x:v>
       </x:c>
       <x:c r="E34" s="32" t="str">
-        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
+        <x:v>One internal API for OpenAI/Anthropic/Gemini and future models.</x:v>
       </x:c>
       <x:c r="F34" s="32" t="str">
         <x:v>P0</x:v>
@@ -11583,7 +11593,7 @@
     </x:row>
     <x:row r="35" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A35" s="32" t="str">
-        <x:v>R-025</x:v>
+        <x:v>R-024</x:v>
       </x:c>
       <x:c r="B35" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11592,10 +11602,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D35" s="32" t="str">
-        <x:v>Per-task budgets</x:v>
+        <x:v>Routing + fallback</x:v>
       </x:c>
       <x:c r="E35" s="32" t="str">
-        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
+        <x:v>Route by task quality/cost/latency; retry on another approved model after provider failure.</x:v>
       </x:c>
       <x:c r="F35" s="32" t="str">
         <x:v>P0</x:v>
@@ -11615,19 +11625,19 @@
     </x:row>
     <x:row r="36" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A36" s="32" t="str">
-        <x:v>R-026</x:v>
+        <x:v>R-025</x:v>
       </x:c>
       <x:c r="B36" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C36" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D36" s="32" t="str">
-        <x:v>PostgreSQL</x:v>
+        <x:v>Per-task budgets</x:v>
       </x:c>
       <x:c r="E36" s="32" t="str">
-        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
+        <x:v>Token/tool/time/retry limits prevent runaway loops.</x:v>
       </x:c>
       <x:c r="F36" s="32" t="str">
         <x:v>P0</x:v>
@@ -11647,7 +11657,7 @@
     </x:row>
     <x:row r="37" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A37" s="32" t="str">
-        <x:v>R-027</x:v>
+        <x:v>R-026</x:v>
       </x:c>
       <x:c r="B37" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11656,10 +11666,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D37" s="32" t="str">
-        <x:v>pgvector initially</x:v>
+        <x:v>PostgreSQL</x:v>
       </x:c>
       <x:c r="E37" s="32" t="str">
-        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
+        <x:v>Platform metadata, users, projects, billing, IR and audit records.</x:v>
       </x:c>
       <x:c r="F37" s="32" t="str">
         <x:v>P0</x:v>
@@ -11679,7 +11689,7 @@
     </x:row>
     <x:row r="38" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A38" s="32" t="str">
-        <x:v>R-028</x:v>
+        <x:v>R-027</x:v>
       </x:c>
       <x:c r="B38" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11688,10 +11698,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D38" s="32" t="str">
-        <x:v>Redis</x:v>
+        <x:v>pgvector initially</x:v>
       </x:c>
       <x:c r="E38" s="32" t="str">
-        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
+        <x:v>Project/code embeddings in PostgreSQL to avoid operating a separate vector DB too early.</x:v>
       </x:c>
       <x:c r="F38" s="32" t="str">
         <x:v>P0</x:v>
@@ -11711,7 +11721,7 @@
     </x:row>
     <x:row r="39" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>R-029</x:v>
+        <x:v>R-028</x:v>
       </x:c>
       <x:c r="B39" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11720,10 +11730,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D39" s="32" t="str">
-        <x:v>NATS / managed queue</x:v>
+        <x:v>Redis</x:v>
       </x:c>
       <x:c r="E39" s="32" t="str">
-        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
+        <x:v>Cache, short-lived agent state, rate limits and queues where appropriate.</x:v>
       </x:c>
       <x:c r="F39" s="32" t="str">
         <x:v>P0</x:v>
@@ -11743,7 +11753,7 @@
     </x:row>
     <x:row r="40" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A40" s="32" t="str">
-        <x:v>R-030</x:v>
+        <x:v>R-029</x:v>
       </x:c>
       <x:c r="B40" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11752,10 +11762,10 @@
         <x:v>Data</x:v>
       </x:c>
       <x:c r="D40" s="32" t="str">
-        <x:v>S3-compatible object storage</x:v>
+        <x:v>NATS / managed queue</x:v>
       </x:c>
       <x:c r="E40" s="32" t="str">
-        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
+        <x:v>Agent/build events with simpler operations than Kafka for MVP.</x:v>
       </x:c>
       <x:c r="F40" s="32" t="str">
         <x:v>P0</x:v>
@@ -11775,19 +11785,19 @@
     </x:row>
     <x:row r="41" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A41" s="32" t="str">
-        <x:v>R-031</x:v>
+        <x:v>R-030</x:v>
       </x:c>
       <x:c r="B41" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C41" s="32" t="str">
-        <x:v>Sandbox</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D41" s="32" t="str">
-        <x:v>Ephemeral Linux sandbox</x:v>
+        <x:v>S3-compatible object storage</x:v>
       </x:c>
       <x:c r="E41" s="32" t="str">
-        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
+        <x:v>Builds, screenshots, archives, test artifacts and logs.</x:v>
       </x:c>
       <x:c r="F41" s="32" t="str">
         <x:v>P0</x:v>
@@ -11807,7 +11817,7 @@
     </x:row>
     <x:row r="42" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A42" s="32" t="str">
-        <x:v>R-032</x:v>
+        <x:v>R-031</x:v>
       </x:c>
       <x:c r="B42" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11816,10 +11826,10 @@
         <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D42" s="32" t="str">
-        <x:v>Secret broker</x:v>
+        <x:v>Ephemeral Linux sandbox</x:v>
       </x:c>
       <x:c r="E42" s="32" t="str">
-        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
+        <x:v>Isolated build/run environment with CPU/RAM/disk/network limits.</x:v>
       </x:c>
       <x:c r="F42" s="32" t="str">
         <x:v>P0</x:v>
@@ -11839,19 +11849,19 @@
     </x:row>
     <x:row r="43" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>R-033</x:v>
+        <x:v>R-032</x:v>
       </x:c>
       <x:c r="B43" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C43" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Sandbox</x:v>
       </x:c>
       <x:c r="D43" s="32" t="str">
-        <x:v>Application-IR browser preview</x:v>
+        <x:v>Secret broker</x:v>
       </x:c>
       <x:c r="E43" s="32" t="str">
-        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
+        <x:v>Give tasks short-lived scoped credentials, never raw master secrets.</x:v>
       </x:c>
       <x:c r="F43" s="32" t="str">
         <x:v>P0</x:v>
@@ -11871,7 +11881,7 @@
     </x:row>
     <x:row r="44" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A44" s="32" t="str">
-        <x:v>R-034</x:v>
+        <x:v>R-033</x:v>
       </x:c>
       <x:c r="B44" s="32" t="str">
         <x:v>MVP</x:v>
@@ -11880,10 +11890,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D44" s="32" t="str">
-        <x:v>Web/Admin live preview</x:v>
+        <x:v>Application-IR browser preview</x:v>
       </x:c>
       <x:c r="E44" s="32" t="str">
-        <x:v>Run generated web apps in isolated preview containers.</x:v>
+        <x:v>Fast Android/iOS-like UI preview from same canonical IR.</x:v>
       </x:c>
       <x:c r="F44" s="32" t="str">
         <x:v>P0</x:v>
@@ -11903,19 +11913,19 @@
     </x:row>
     <x:row r="45" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A45" s="32" t="str">
-        <x:v>R-035</x:v>
+        <x:v>R-034</x:v>
       </x:c>
       <x:c r="B45" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C45" s="32" t="str">
-        <x:v>Android</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D45" s="32" t="str">
-        <x:v>Android build verification</x:v>
+        <x:v>Web/Admin live preview</x:v>
       </x:c>
       <x:c r="E45" s="32" t="str">
-        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
+        <x:v>Run generated web apps in isolated preview containers.</x:v>
       </x:c>
       <x:c r="F45" s="32" t="str">
         <x:v>P0</x:v>
@@ -11935,19 +11945,19 @@
     </x:row>
     <x:row r="46" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A46" s="32" t="str">
-        <x:v>R-036</x:v>
+        <x:v>R-035</x:v>
       </x:c>
       <x:c r="B46" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C46" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Android</x:v>
       </x:c>
       <x:c r="D46" s="32" t="str">
-        <x:v>Cloud macOS compile verification</x:v>
+        <x:v>Android build verification</x:v>
       </x:c>
       <x:c r="E46" s="32" t="str">
-        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
+        <x:v>Compile generated Kotlin/Compose on Linux workers.</x:v>
       </x:c>
       <x:c r="F46" s="32" t="str">
         <x:v>P0</x:v>
@@ -11967,19 +11977,19 @@
     </x:row>
     <x:row r="47" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A47" s="32" t="str">
-        <x:v>R-037</x:v>
+        <x:v>R-036</x:v>
       </x:c>
       <x:c r="B47" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C47" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D47" s="32" t="str">
-        <x:v>Unit + integration baseline</x:v>
+        <x:v>Cloud macOS compile verification</x:v>
       </x:c>
       <x:c r="E47" s="32" t="str">
-        <x:v>Generated changes require relevant tests.</x:v>
+        <x:v>Compile Swift/SwiftUI on a Mac pool when needed; user OS irrelevant.</x:v>
       </x:c>
       <x:c r="F47" s="32" t="str">
         <x:v>P0</x:v>
@@ -11999,7 +12009,7 @@
     </x:row>
     <x:row r="48" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A48" s="32" t="str">
-        <x:v>R-038</x:v>
+        <x:v>R-037</x:v>
       </x:c>
       <x:c r="B48" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12008,10 +12018,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D48" s="32" t="str">
-        <x:v>Regression gate</x:v>
+        <x:v>Unit + integration baseline</x:v>
       </x:c>
       <x:c r="E48" s="32" t="str">
-        <x:v>Existing passing tests must stay passing before merge.</x:v>
+        <x:v>Generated changes require relevant tests.</x:v>
       </x:c>
       <x:c r="F48" s="32" t="str">
         <x:v>P0</x:v>
@@ -12031,7 +12041,7 @@
     </x:row>
     <x:row r="49" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A49" s="32" t="str">
-        <x:v>R-039</x:v>
+        <x:v>R-038</x:v>
       </x:c>
       <x:c r="B49" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12040,10 +12050,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D49" s="32" t="str">
-        <x:v>API contract tests</x:v>
+        <x:v>Regression gate</x:v>
       </x:c>
       <x:c r="E49" s="32" t="str">
-        <x:v>Catch backend/mobile/web contract drift.</x:v>
+        <x:v>Existing passing tests must stay passing before merge.</x:v>
       </x:c>
       <x:c r="F49" s="32" t="str">
         <x:v>P0</x:v>
@@ -12063,7 +12073,7 @@
     </x:row>
     <x:row r="50" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A50" s="32" t="str">
-        <x:v>R-040</x:v>
+        <x:v>R-039</x:v>
       </x:c>
       <x:c r="B50" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12072,10 +12082,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="D50" s="32" t="str">
-        <x:v>Migration safety checks</x:v>
+        <x:v>API contract tests</x:v>
       </x:c>
       <x:c r="E50" s="32" t="str">
-        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
+        <x:v>Catch backend/mobile/web contract drift.</x:v>
       </x:c>
       <x:c r="F50" s="32" t="str">
         <x:v>P0</x:v>
@@ -12095,19 +12105,19 @@
     </x:row>
     <x:row r="51" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A51" s="32" t="str">
-        <x:v>R-041</x:v>
+        <x:v>R-040</x:v>
       </x:c>
       <x:c r="B51" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C51" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D51" s="32" t="str">
-        <x:v>SAST + dependency scanning</x:v>
+        <x:v>Migration safety checks</x:v>
       </x:c>
       <x:c r="E51" s="32" t="str">
-        <x:v>Scan generated and modified code before deploy.</x:v>
+        <x:v>Detect destructive schema changes and require explicit migration plan.</x:v>
       </x:c>
       <x:c r="F51" s="32" t="str">
         <x:v>P0</x:v>
@@ -12127,7 +12137,7 @@
     </x:row>
     <x:row r="52" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A52" s="32" t="str">
-        <x:v>R-042</x:v>
+        <x:v>R-041</x:v>
       </x:c>
       <x:c r="B52" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12136,10 +12146,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D52" s="32" t="str">
-        <x:v>Prompt/tool policy</x:v>
+        <x:v>SAST + dependency scanning</x:v>
       </x:c>
       <x:c r="E52" s="32" t="str">
-        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
+        <x:v>Scan generated and modified code before deploy.</x:v>
       </x:c>
       <x:c r="F52" s="32" t="str">
         <x:v>P0</x:v>
@@ -12159,19 +12169,19 @@
     </x:row>
     <x:row r="53" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A53" s="32" t="str">
-        <x:v>R-043</x:v>
+        <x:v>R-042</x:v>
       </x:c>
       <x:c r="B53" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C53" s="32" t="str">
-        <x:v>Observability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D53" s="32" t="str">
-        <x:v>Task trace</x:v>
+        <x:v>Prompt/tool policy</x:v>
       </x:c>
       <x:c r="E53" s="32" t="str">
-        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
+        <x:v>Repo content cannot silently override system policy or exfiltrate secrets.</x:v>
       </x:c>
       <x:c r="F53" s="32" t="str">
         <x:v>P0</x:v>
@@ -12191,7 +12201,7 @@
     </x:row>
     <x:row r="54" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A54" s="32" t="str">
-        <x:v>R-044</x:v>
+        <x:v>R-043</x:v>
       </x:c>
       <x:c r="B54" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12200,10 +12210,10 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="D54" s="32" t="str">
-        <x:v>Platform logs/metrics</x:v>
+        <x:v>Task trace</x:v>
       </x:c>
       <x:c r="E54" s="32" t="str">
-        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
+        <x:v>Trace prompt -&gt; plan -&gt; tools -&gt; patches -&gt; tests -&gt; cost -&gt; result.</x:v>
       </x:c>
       <x:c r="F54" s="32" t="str">
         <x:v>P0</x:v>
@@ -12223,19 +12233,19 @@
     </x:row>
     <x:row r="55" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A55" s="32" t="str">
-        <x:v>R-045</x:v>
+        <x:v>R-044</x:v>
       </x:c>
       <x:c r="B55" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C55" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Observability</x:v>
       </x:c>
       <x:c r="D55" s="32" t="str">
-        <x:v>Usage ledger</x:v>
+        <x:v>Platform logs/metrics</x:v>
       </x:c>
       <x:c r="E55" s="32" t="str">
-        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
+        <x:v>OpenTelemetry plus central logs and core service metrics.</x:v>
       </x:c>
       <x:c r="F55" s="32" t="str">
         <x:v>P0</x:v>
@@ -12255,7 +12265,7 @@
     </x:row>
     <x:row r="56" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A56" s="32" t="str">
-        <x:v>R-046</x:v>
+        <x:v>R-045</x:v>
       </x:c>
       <x:c r="B56" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12264,10 +12274,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D56" s="32" t="str">
-        <x:v>Pre-task estimate</x:v>
+        <x:v>Usage ledger</x:v>
       </x:c>
       <x:c r="E56" s="32" t="str">
-        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
+        <x:v>Track model tokens, build minutes, storage and Mac minutes per task/project.</x:v>
       </x:c>
       <x:c r="F56" s="32" t="str">
         <x:v>P0</x:v>
@@ -12287,7 +12297,7 @@
     </x:row>
     <x:row r="57" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A57" s="32" t="str">
-        <x:v>R-047</x:v>
+        <x:v>R-046</x:v>
       </x:c>
       <x:c r="B57" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12296,10 +12306,10 @@
         <x:v>Billing</x:v>
       </x:c>
       <x:c r="D57" s="32" t="str">
-        <x:v>No charge for internal failed retries</x:v>
+        <x:v>Pre-task estimate</x:v>
       </x:c>
       <x:c r="E57" s="32" t="str">
-        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
+        <x:v>Show estimated credit range before expensive tasks/native sessions.</x:v>
       </x:c>
       <x:c r="F57" s="32" t="str">
         <x:v>P0</x:v>
@@ -12319,19 +12329,19 @@
     </x:row>
     <x:row r="58" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A58" s="32" t="str">
-        <x:v>R-048</x:v>
+        <x:v>R-047</x:v>
       </x:c>
       <x:c r="B58" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C58" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D58" s="32" t="str">
-        <x:v>Web/backend deployment</x:v>
+        <x:v>No charge for internal failed retries</x:v>
       </x:c>
       <x:c r="E58" s="32" t="str">
-        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
+        <x:v>Customer pays intended task budget, not repeated agent mistakes within policy.</x:v>
       </x:c>
       <x:c r="F58" s="32" t="str">
         <x:v>P0</x:v>
@@ -12351,7 +12361,7 @@
     </x:row>
     <x:row r="59" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A59" s="32" t="str">
-        <x:v>R-049</x:v>
+        <x:v>R-048</x:v>
       </x:c>
       <x:c r="B59" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12360,10 +12370,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D59" s="32" t="str">
-        <x:v>Android APK/AAB build</x:v>
+        <x:v>Web/backend deployment</x:v>
       </x:c>
       <x:c r="E59" s="32" t="str">
-        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
+        <x:v>Immutable versioned deployments with health checks and rollback.</x:v>
       </x:c>
       <x:c r="F59" s="32" t="str">
         <x:v>P0</x:v>
@@ -12383,7 +12393,7 @@
     </x:row>
     <x:row r="60" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A60" s="32" t="str">
-        <x:v>R-050</x:v>
+        <x:v>R-049</x:v>
       </x:c>
       <x:c r="B60" s="32" t="str">
         <x:v>MVP</x:v>
@@ -12392,10 +12402,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D60" s="32" t="str">
-        <x:v>iOS IPA build pipeline</x:v>
+        <x:v>Android APK/AAB build</x:v>
       </x:c>
       <x:c r="E60" s="32" t="str">
-        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
+        <x:v>Generate signed artifacts using customer-owned signing configuration.</x:v>
       </x:c>
       <x:c r="F60" s="32" t="str">
         <x:v>P0</x:v>
@@ -12415,19 +12425,19 @@
     </x:row>
     <x:row r="61" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A61" s="32" t="str">
-        <x:v>R-051</x:v>
+        <x:v>R-050</x:v>
       </x:c>
       <x:c r="B61" s="32" t="str">
         <x:v>MVP</x:v>
       </x:c>
       <x:c r="C61" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D61" s="32" t="str">
-        <x:v>Core product KPIs</x:v>
+        <x:v>iOS IPA build pipeline</x:v>
       </x:c>
       <x:c r="E61" s="32" t="str">
-        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
+        <x:v>Secure Mac signing worker; certificate/profile stored in vault.</x:v>
       </x:c>
       <x:c r="F61" s="32" t="str">
         <x:v>P0</x:v>
@@ -12447,22 +12457,22 @@
     </x:row>
     <x:row r="62" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A62" s="32" t="str">
-        <x:v>R-052</x:v>
+        <x:v>R-051</x:v>
       </x:c>
       <x:c r="B62" s="32" t="str">
-        <x:v>MID</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C62" s="32" t="str">
-        <x:v>Preview</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D62" s="32" t="str">
-        <x:v>Interactive Android emulator streaming</x:v>
+        <x:v>Core product KPIs</x:v>
       </x:c>
       <x:c r="E62" s="32" t="str">
-        <x:v>Real Android runtime streamed into browser.</x:v>
+        <x:v>Track build success, regression, deployment, cost/task and user success.</x:v>
       </x:c>
       <x:c r="F62" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G62" s="32"/>
       <x:c r="H62" s="32" t="str">
@@ -12479,7 +12489,7 @@
     </x:row>
     <x:row r="63" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A63" s="32" t="str">
-        <x:v>R-053</x:v>
+        <x:v>R-052</x:v>
       </x:c>
       <x:c r="B63" s="32" t="str">
         <x:v>MID</x:v>
@@ -12488,10 +12498,10 @@
         <x:v>Preview</x:v>
       </x:c>
       <x:c r="D63" s="32" t="str">
-        <x:v>Interactive iOS simulator streaming</x:v>
+        <x:v>Interactive Android emulator streaming</x:v>
       </x:c>
       <x:c r="E63" s="32" t="str">
-        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
+        <x:v>Real Android runtime streamed into browser.</x:v>
       </x:c>
       <x:c r="F63" s="32" t="str">
         <x:v>P1</x:v>
@@ -12511,19 +12521,19 @@
     </x:row>
     <x:row r="64" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A64" s="32" t="str">
-        <x:v>R-054</x:v>
+        <x:v>R-053</x:v>
       </x:c>
       <x:c r="B64" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C64" s="32" t="str">
-        <x:v>iOS</x:v>
+        <x:v>Preview</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Local Mac Agent</x:v>
+        <x:v>Interactive iOS simulator streaming</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str">
-        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
+        <x:v>Remote Mac+iOS Simulator streamed through browser; metered credits.</x:v>
       </x:c>
       <x:c r="F64" s="32" t="str">
         <x:v>P1</x:v>
@@ -12543,19 +12553,19 @@
     </x:row>
     <x:row r="65" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A65" s="32" t="str">
-        <x:v>R-055</x:v>
+        <x:v>R-054</x:v>
       </x:c>
       <x:c r="B65" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C65" s="32" t="str">
-        <x:v>Integrations</x:v>
+        <x:v>iOS</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Verified integration catalog</x:v>
+        <x:v>Local Mac Agent</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
-        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
+        <x:v>Opt-in desktop helper uses customer Mac/Xcode instead of cloud Mac.</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
         <x:v>P1</x:v>
@@ -12575,7 +12585,7 @@
     </x:row>
     <x:row r="66" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A66" s="32" t="str">
-        <x:v>R-056</x:v>
+        <x:v>R-055</x:v>
       </x:c>
       <x:c r="B66" s="32" t="str">
         <x:v>MID</x:v>
@@ -12584,10 +12594,10 @@
         <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Integration health tests</x:v>
+        <x:v>Verified integration catalog</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
-        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
+        <x:v>Tested templates for payments, maps, auth, messaging, analytics and storage.</x:v>
       </x:c>
       <x:c r="F66" s="32" t="str">
         <x:v>P1</x:v>
@@ -12607,19 +12617,19 @@
     </x:row>
     <x:row r="67" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A67" s="32" t="str">
-        <x:v>R-057</x:v>
+        <x:v>R-056</x:v>
       </x:c>
       <x:c r="B67" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C67" s="32" t="str">
-        <x:v>Context</x:v>
+        <x:v>Integrations</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Long-project memory compaction</x:v>
+        <x:v>Integration health tests</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
-        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
+        <x:v>Credentials/scopes/webhooks verified automatically.</x:v>
       </x:c>
       <x:c r="F67" s="32" t="str">
         <x:v>P1</x:v>
@@ -12639,19 +12649,19 @@
     </x:row>
     <x:row r="68" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A68" s="32" t="str">
-        <x:v>R-058</x:v>
+        <x:v>R-057</x:v>
       </x:c>
       <x:c r="B68" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C68" s="32" t="str">
-        <x:v>Code Editing</x:v>
+        <x:v>Context</x:v>
       </x:c>
       <x:c r="D68" s="32" t="str">
-        <x:v>Language-specific structured editors</x:v>
+        <x:v>Long-project memory compaction</x:v>
       </x:c>
       <x:c r="E68" s="32" t="str">
-        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
+        <x:v>Summaries + graph + ADRs replace dependence on raw chat history.</x:v>
       </x:c>
       <x:c r="F68" s="32" t="str">
         <x:v>P1</x:v>
@@ -12671,19 +12681,19 @@
     </x:row>
     <x:row r="69" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A69" s="32" t="str">
-        <x:v>R-059</x:v>
+        <x:v>R-058</x:v>
       </x:c>
       <x:c r="B69" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C69" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Code Editing</x:v>
       </x:c>
       <x:c r="D69" s="32" t="str">
-        <x:v>Visual regression</x:v>
+        <x:v>Language-specific structured editors</x:v>
       </x:c>
       <x:c r="E69" s="32" t="str">
-        <x:v>Screenshot comparison with approved baselines.</x:v>
+        <x:v>SwiftSyntax, Kotlin PSI/tree-sitter, TS compiler APIs, Python LibCST, Go AST.</x:v>
       </x:c>
       <x:c r="F69" s="32" t="str">
         <x:v>P1</x:v>
@@ -12703,7 +12713,7 @@
     </x:row>
     <x:row r="70" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A70" s="32" t="str">
-        <x:v>R-060</x:v>
+        <x:v>R-059</x:v>
       </x:c>
       <x:c r="B70" s="32" t="str">
         <x:v>MID</x:v>
@@ -12712,10 +12722,10 @@
         <x:v>Quality</x:v>
       </x:c>
       <x:c r="D70" s="32" t="str">
-        <x:v>Performance budgets</x:v>
+        <x:v>Visual regression</x:v>
       </x:c>
       <x:c r="E70" s="32" t="str">
-        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
+        <x:v>Screenshot comparison with approved baselines.</x:v>
       </x:c>
       <x:c r="F70" s="32" t="str">
         <x:v>P1</x:v>
@@ -12735,19 +12745,19 @@
     </x:row>
     <x:row r="71" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A71" s="32" t="str">
-        <x:v>R-061</x:v>
+        <x:v>R-060</x:v>
       </x:c>
       <x:c r="B71" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C71" s="32" t="str">
-        <x:v>Deployment</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D71" s="32" t="str">
-        <x:v>Environment parity</x:v>
+        <x:v>Performance budgets</x:v>
       </x:c>
       <x:c r="E71" s="32" t="str">
-        <x:v>Preview/staging/production share same container and config contract.</x:v>
+        <x:v>Build size, API latency, query, memory and frontend performance gates.</x:v>
       </x:c>
       <x:c r="F71" s="32" t="str">
         <x:v>P1</x:v>
@@ -12767,7 +12777,7 @@
     </x:row>
     <x:row r="72" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A72" s="32" t="str">
-        <x:v>R-062</x:v>
+        <x:v>R-061</x:v>
       </x:c>
       <x:c r="B72" s="32" t="str">
         <x:v>MID</x:v>
@@ -12776,10 +12786,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D72" s="32" t="str">
-        <x:v>App Store / TestFlight automation</x:v>
+        <x:v>Environment parity</x:v>
       </x:c>
       <x:c r="E72" s="32" t="str">
-        <x:v>Prepare/upload builds with explicit user approval.</x:v>
+        <x:v>Preview/staging/production share same container and config contract.</x:v>
       </x:c>
       <x:c r="F72" s="32" t="str">
         <x:v>P1</x:v>
@@ -12799,7 +12809,7 @@
     </x:row>
     <x:row r="73" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A73" s="32" t="str">
-        <x:v>R-063</x:v>
+        <x:v>R-062</x:v>
       </x:c>
       <x:c r="B73" s="32" t="str">
         <x:v>MID</x:v>
@@ -12808,10 +12818,10 @@
         <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D73" s="32" t="str">
-        <x:v>Play Store automation</x:v>
+        <x:v>App Store / TestFlight automation</x:v>
       </x:c>
       <x:c r="E73" s="32" t="str">
-        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
+        <x:v>Prepare/upload builds with explicit user approval.</x:v>
       </x:c>
       <x:c r="F73" s="32" t="str">
         <x:v>P1</x:v>
@@ -12831,19 +12841,19 @@
     </x:row>
     <x:row r="74" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A74" s="32" t="str">
-        <x:v>R-064</x:v>
+        <x:v>R-063</x:v>
       </x:c>
       <x:c r="B74" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C74" s="32" t="str">
-        <x:v>Collaboration</x:v>
+        <x:v>Deployment</x:v>
       </x:c>
       <x:c r="D74" s="32" t="str">
-        <x:v>RBAC + approvals</x:v>
+        <x:v>Play Store automation</x:v>
       </x:c>
       <x:c r="E74" s="32" t="str">
-        <x:v>Owners can require code/security/deploy approvals.</x:v>
+        <x:v>Prepare/upload AAB with explicit user approval.</x:v>
       </x:c>
       <x:c r="F74" s="32" t="str">
         <x:v>P1</x:v>
@@ -12863,7 +12873,7 @@
     </x:row>
     <x:row r="75" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A75" s="32" t="str">
-        <x:v>R-065</x:v>
+        <x:v>R-064</x:v>
       </x:c>
       <x:c r="B75" s="32" t="str">
         <x:v>MID</x:v>
@@ -12872,10 +12882,10 @@
         <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D75" s="32" t="str">
-        <x:v>Comments/review workflow</x:v>
+        <x:v>RBAC + approvals</x:v>
       </x:c>
       <x:c r="E75" s="32" t="str">
-        <x:v>Human review on AI plan and diff.</x:v>
+        <x:v>Owners can require code/security/deploy approvals.</x:v>
       </x:c>
       <x:c r="F75" s="32" t="str">
         <x:v>P1</x:v>
@@ -12895,19 +12905,19 @@
     </x:row>
     <x:row r="76" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A76" s="32" t="str">
-        <x:v>R-066</x:v>
+        <x:v>R-065</x:v>
       </x:c>
       <x:c r="B76" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C76" s="32" t="str">
-        <x:v>Billing</x:v>
+        <x:v>Collaboration</x:v>
       </x:c>
       <x:c r="D76" s="32" t="str">
-        <x:v>BYOK</x:v>
+        <x:v>Comments/review workflow</x:v>
       </x:c>
       <x:c r="E76" s="32" t="str">
-        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
+        <x:v>Human review on AI plan and diff.</x:v>
       </x:c>
       <x:c r="F76" s="32" t="str">
         <x:v>P1</x:v>
@@ -12927,19 +12937,19 @@
     </x:row>
     <x:row r="77" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A77" s="32" t="str">
-        <x:v>R-067</x:v>
+        <x:v>R-066</x:v>
       </x:c>
       <x:c r="B77" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C77" s="32" t="str">
-        <x:v>Recovery</x:v>
+        <x:v>Billing</x:v>
       </x:c>
       <x:c r="D77" s="32" t="str">
-        <x:v>Auto-recovery agent</x:v>
+        <x:v>BYOK</x:v>
       </x:c>
       <x:c r="E77" s="32" t="str">
-        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
+        <x:v>Customer can use approved provider API keys with clear cost ownership.</x:v>
       </x:c>
       <x:c r="F77" s="32" t="str">
         <x:v>P1</x:v>
@@ -12959,19 +12969,19 @@
     </x:row>
     <x:row r="78" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A78" s="32" t="str">
-        <x:v>R-068</x:v>
+        <x:v>R-067</x:v>
       </x:c>
       <x:c r="B78" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C78" s="32" t="str">
-        <x:v>Analytics</x:v>
+        <x:v>Recovery</x:v>
       </x:c>
       <x:c r="D78" s="32" t="str">
-        <x:v>Project health score</x:v>
+        <x:v>Auto-recovery agent</x:v>
       </x:c>
       <x:c r="E78" s="32" t="str">
-        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
+        <x:v>Diagnose failed build/test and retry within strict bounded policy.</x:v>
       </x:c>
       <x:c r="F78" s="32" t="str">
         <x:v>P1</x:v>
@@ -12991,19 +13001,19 @@
     </x:row>
     <x:row r="79" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A79" s="32" t="str">
-        <x:v>R-069</x:v>
+        <x:v>R-068</x:v>
       </x:c>
       <x:c r="B79" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C79" s="32" t="str">
-        <x:v>Security</x:v>
+        <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D79" s="32" t="str">
-        <x:v>DAST</x:v>
+        <x:v>Project health score</x:v>
       </x:c>
       <x:c r="E79" s="32" t="str">
-        <x:v>Run dynamic scans against staging/preview.</x:v>
+        <x:v>Derived from measurable checks, with drill-down evidence.</x:v>
       </x:c>
       <x:c r="F79" s="32" t="str">
         <x:v>P1</x:v>
@@ -13023,7 +13033,7 @@
     </x:row>
     <x:row r="80" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A80" s="32" t="str">
-        <x:v>R-070</x:v>
+        <x:v>R-069</x:v>
       </x:c>
       <x:c r="B80" s="32" t="str">
         <x:v>MID</x:v>
@@ -13032,10 +13042,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D80" s="32" t="str">
-        <x:v>SBOM + license policy</x:v>
+        <x:v>DAST</x:v>
       </x:c>
       <x:c r="E80" s="32" t="str">
-        <x:v>Software bill of materials and restricted-license checks.</x:v>
+        <x:v>Run dynamic scans against staging/preview.</x:v>
       </x:c>
       <x:c r="F80" s="32" t="str">
         <x:v>P1</x:v>
@@ -13055,7 +13065,7 @@
     </x:row>
     <x:row r="81" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A81" s="32" t="str">
-        <x:v>R-071</x:v>
+        <x:v>R-070</x:v>
       </x:c>
       <x:c r="B81" s="32" t="str">
         <x:v>MID</x:v>
@@ -13064,10 +13074,10 @@
         <x:v>Security</x:v>
       </x:c>
       <x:c r="D81" s="32" t="str">
-        <x:v>Egress policy</x:v>
+        <x:v>SBOM + license policy</x:v>
       </x:c>
       <x:c r="E81" s="32" t="str">
-        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
+        <x:v>Software bill of materials and restricted-license checks.</x:v>
       </x:c>
       <x:c r="F81" s="32" t="str">
         <x:v>P1</x:v>
@@ -13087,19 +13097,19 @@
     </x:row>
     <x:row r="82" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A82" s="32" t="str">
-        <x:v>R-072</x:v>
+        <x:v>R-071</x:v>
       </x:c>
       <x:c r="B82" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C82" s="32" t="str">
-        <x:v>Reliability</x:v>
+        <x:v>Security</x:v>
       </x:c>
       <x:c r="D82" s="32" t="str">
-        <x:v>Build artifact caching</x:v>
+        <x:v>Egress policy</x:v>
       </x:c>
       <x:c r="E82" s="32" t="str">
-        <x:v>Cache dependencies and unchanged build outputs.</x:v>
+        <x:v>Sandbox network allowlist/denylist and per-integration scopes.</x:v>
       </x:c>
       <x:c r="F82" s="32" t="str">
         <x:v>P1</x:v>
@@ -13119,7 +13129,7 @@
     </x:row>
     <x:row r="83" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A83" s="32" t="str">
-        <x:v>R-073</x:v>
+        <x:v>R-072</x:v>
       </x:c>
       <x:c r="B83" s="32" t="str">
         <x:v>MID</x:v>
@@ -13128,10 +13138,10 @@
         <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D83" s="32" t="str">
-        <x:v>Incremental test selection</x:v>
+        <x:v>Build artifact caching</x:v>
       </x:c>
       <x:c r="E83" s="32" t="str">
-        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
+        <x:v>Cache dependencies and unchanged build outputs.</x:v>
       </x:c>
       <x:c r="F83" s="32" t="str">
         <x:v>P1</x:v>
@@ -13151,19 +13161,19 @@
     </x:row>
     <x:row r="84" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A84" s="32" t="str">
-        <x:v>R-074</x:v>
+        <x:v>R-073</x:v>
       </x:c>
       <x:c r="B84" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C84" s="32" t="str">
-        <x:v>Multi-stack</x:v>
+        <x:v>Reliability</x:v>
       </x:c>
       <x:c r="D84" s="32" t="str">
-        <x:v>Backend stack profiles</x:v>
+        <x:v>Incremental test selection</x:v>
       </x:c>
       <x:c r="E84" s="32" t="str">
-        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
+        <x:v>Impact graph selects relevant tests, while periodic full regression remains mandatory.</x:v>
       </x:c>
       <x:c r="F84" s="32" t="str">
         <x:v>P1</x:v>
@@ -13183,19 +13193,19 @@
     </x:row>
     <x:row r="85" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A85" s="32" t="str">
-        <x:v>R-075</x:v>
+        <x:v>R-074</x:v>
       </x:c>
       <x:c r="B85" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C85" s="32" t="str">
-        <x:v>Data</x:v>
+        <x:v>Multi-stack</x:v>
       </x:c>
       <x:c r="D85" s="32" t="str">
-        <x:v>Database profiles</x:v>
+        <x:v>Backend stack profiles</x:v>
       </x:c>
       <x:c r="E85" s="32" t="str">
-        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
+        <x:v>Offer Go, Python/FastAPI and optional Node/NestJS project templates.</x:v>
       </x:c>
       <x:c r="F85" s="32" t="str">
         <x:v>P1</x:v>
@@ -13215,19 +13225,19 @@
     </x:row>
     <x:row r="86" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A86" s="32" t="str">
-        <x:v>R-076</x:v>
+        <x:v>R-075</x:v>
       </x:c>
       <x:c r="B86" s="32" t="str">
         <x:v>MID</x:v>
       </x:c>
       <x:c r="C86" s="32" t="str">
-        <x:v>Developer UX</x:v>
+        <x:v>Data</x:v>
       </x:c>
       <x:c r="D86" s="32" t="str">
-        <x:v>Existing repo import</x:v>
+        <x:v>Database profiles</x:v>
       </x:c>
       <x:c r="E86" s="32" t="str">
-        <x:v>Understand and modify non-generated projects safely.</x:v>
+        <x:v>PostgreSQL default; optional MySQL, MongoDB, Supabase/Firebase connectors.</x:v>
       </x:c>
       <x:c r="F86" s="32" t="str">
         <x:v>P1</x:v>
@@ -13247,22 +13257,22 @@
     </x:row>
     <x:row r="87" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A87" s="32" t="str">
-        <x:v>R-077</x:v>
+        <x:v>R-076</x:v>
       </x:c>
       <x:c r="B87" s="32" t="str">
-        <x:v>MVP</x:v>
+        <x:v>MID</x:v>
       </x:c>
       <x:c r="C87" s="32" t="str">
-        <x:v>Mobile</x:v>
+        <x:v>Developer UX</x:v>
       </x:c>
       <x:c r="D87" s="32" t="str">
-        <x:v>Flutter target (GA baseline)</x:v>
+        <x:v>Existing repo import</x:v>
       </x:c>
       <x:c r="E87" s="32" t="str">
-        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
+        <x:v>Understand and modify non-generated projects safely.</x:v>
       </x:c>
       <x:c r="F87" s="32" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G87" s="32"/>
       <x:c r="H87" s="32" t="str">
@@ -13279,7 +13289,7 @@
     </x:row>
     <x:row r="88" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A88" s="32" t="str">
-        <x:v>R-078</x:v>
+        <x:v>R-077</x:v>
       </x:c>
       <x:c r="B88" s="32" t="str">
         <x:v>MVP</x:v>
@@ -13288,13 +13298,13 @@
         <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D88" s="32" t="str">
-        <x:v>React Native target (GA/beta by team capacity)</x:v>
+        <x:v>Flutter target (GA baseline)</x:v>
       </x:c>
       <x:c r="E88" s="32" t="str">
-        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
+        <x:v>Generate one Dart codebase for Android/iOS; optional Flutter Web only when project profile fits.</x:v>
       </x:c>
       <x:c r="F88" s="32" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="G88" s="32"/>
       <x:c r="H88" s="32" t="str">
@@ -13311,22 +13321,22 @@
     </x:row>
     <x:row r="89" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A89" s="32" t="str">
-        <x:v>R-079</x:v>
+        <x:v>R-078</x:v>
       </x:c>
       <x:c r="B89" s="32" t="str">
-        <x:v>ADVANCED</x:v>
+        <x:v>MVP</x:v>
       </x:c>
       <x:c r="C89" s="32" t="str">
-        <x:v>Models</x:v>
+        <x:v>Mobile</x:v>
       </x:c>
       <x:c r="D89" s="32" t="str">
-        <x:v>Model benchmark service</x:v>
+        <x:v>React Native target (GA/beta by team capacity)</x:v>
       </x:c>
       <x:c r="E89" s="32" t="str">
-        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
+        <x:v>Generate one TypeScript/React Native codebase for Android/iOS; Expo optional; share TS logic/components with web where safe.</x:v>
       </x:c>
       <x:c r="F89" s="32" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="G89" s="32"/>
       <x:c r="H89" s="32" t="str">
@@ -13343,7 +13353,7 @@
     </x:row>
     <x:row r="90" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A90" s="32" t="str">
-        <x:v>R-080</x:v>
+        <x:v>R-079</x:v>
       </x:c>
       <x:c r="B90" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13352,10 +13362,10 @@
         <x:v>Models</x:v>
       </x:c>
       <x:c r="D90" s="32" t="str">
-        <x:v>Self-hosted/local models</x:v>
+        <x:v>Model benchmark service</x:v>
       </x:c>
       <x:c r="E90" s="32" t="str">
-        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
+        <x:v>Continuously score models on internal coding/repair/security tasks.</x:v>
       </x:c>
       <x:c r="F90" s="32" t="str">
         <x:v>P2</x:v>
@@ -13375,19 +13385,19 @@
     </x:row>
     <x:row r="91" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A91" s="32" t="str">
-        <x:v>R-081</x:v>
+        <x:v>R-080</x:v>
       </x:c>
       <x:c r="B91" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C91" s="32" t="str">
-        <x:v>Agents</x:v>
+        <x:v>Models</x:v>
       </x:c>
       <x:c r="D91" s="32" t="str">
-        <x:v>Specialist agent marketplace</x:v>
+        <x:v>Self-hosted/local models</x:v>
       </x:c>
       <x:c r="E91" s="32" t="str">
-        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
+        <x:v>Private model endpoints for enterprise or low-cost tasks.</x:v>
       </x:c>
       <x:c r="F91" s="32" t="str">
         <x:v>P2</x:v>
@@ -13407,19 +13417,19 @@
     </x:row>
     <x:row r="92" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A92" s="32" t="str">
-        <x:v>R-082</x:v>
+        <x:v>R-081</x:v>
       </x:c>
       <x:c r="B92" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C92" s="32" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Agents</x:v>
       </x:c>
       <x:c r="D92" s="32" t="str">
-        <x:v>Physical device cloud</x:v>
+        <x:v>Specialist agent marketplace</x:v>
       </x:c>
       <x:c r="E92" s="32" t="str">
-        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
+        <x:v>Versioned approved agents with capability and permission manifests.</x:v>
       </x:c>
       <x:c r="F92" s="32" t="str">
         <x:v>P2</x:v>
@@ -13439,19 +13449,19 @@
     </x:row>
     <x:row r="93" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A93" s="32" t="str">
-        <x:v>R-083</x:v>
+        <x:v>R-082</x:v>
       </x:c>
       <x:c r="B93" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C93" s="32" t="str">
-        <x:v>Infrastructure</x:v>
+        <x:v>Testing</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>MicroVM sandbox</x:v>
+        <x:v>Physical device cloud</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
-        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
+        <x:v>Run selected flows on real iPhones/Android devices.</x:v>
       </x:c>
       <x:c r="F93" s="32" t="str">
         <x:v>P2</x:v>
@@ -13471,7 +13481,7 @@
     </x:row>
     <x:row r="94" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A94" s="32" t="str">
-        <x:v>R-084</x:v>
+        <x:v>R-083</x:v>
       </x:c>
       <x:c r="B94" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13480,10 +13490,10 @@
         <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D94" s="32" t="str">
-        <x:v>Multi-region build/control plane</x:v>
+        <x:v>MicroVM sandbox</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
-        <x:v>Regional workload placement and disaster recovery.</x:v>
+        <x:v>Firecracker/Kata/gVisor isolation for higher-risk arbitrary code execution.</x:v>
       </x:c>
       <x:c r="F94" s="32" t="str">
         <x:v>P2</x:v>
@@ -13503,19 +13513,19 @@
     </x:row>
     <x:row r="95" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A95" s="32" t="str">
-        <x:v>R-085</x:v>
+        <x:v>R-084</x:v>
       </x:c>
       <x:c r="B95" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C95" s="32" t="str">
-        <x:v>Enterprise</x:v>
+        <x:v>Infrastructure</x:v>
       </x:c>
       <x:c r="D95" s="32" t="str">
-        <x:v>BYOC</x:v>
+        <x:v>Multi-region build/control plane</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
-        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
+        <x:v>Regional workload placement and disaster recovery.</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
         <x:v>P2</x:v>
@@ -13535,7 +13545,7 @@
     </x:row>
     <x:row r="96" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A96" s="32" t="str">
-        <x:v>R-086</x:v>
+        <x:v>R-085</x:v>
       </x:c>
       <x:c r="B96" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13544,10 +13554,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Data residency controls</x:v>
+        <x:v>BYOC</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
-        <x:v>Pin project data/logs/builds to approved regions.</x:v>
+        <x:v>Deploy sandboxes/build workers into customer cloud/VPC.</x:v>
       </x:c>
       <x:c r="F96" s="32" t="str">
         <x:v>P2</x:v>
@@ -13567,7 +13577,7 @@
     </x:row>
     <x:row r="97" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A97" s="32" t="str">
-        <x:v>R-087</x:v>
+        <x:v>R-086</x:v>
       </x:c>
       <x:c r="B97" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13576,10 +13586,10 @@
         <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Policy-as-code</x:v>
+        <x:v>Data residency controls</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
-        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
+        <x:v>Pin project data/logs/builds to approved regions.</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
         <x:v>P2</x:v>
@@ -13599,19 +13609,19 @@
     </x:row>
     <x:row r="98" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A98" s="32" t="str">
-        <x:v>R-088</x:v>
+        <x:v>R-087</x:v>
       </x:c>
       <x:c r="B98" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C98" s="32" t="str">
-        <x:v>Architecture</x:v>
+        <x:v>Enterprise</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Cross-platform consistency checker</x:v>
+        <x:v>Policy-as-code</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
-        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
+        <x:v>Organization rules for models, packages, deployment, approvals and secrets.</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
         <x:v>P2</x:v>
@@ -13631,7 +13641,7 @@
     </x:row>
     <x:row r="99" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A99" s="32" t="str">
-        <x:v>R-089</x:v>
+        <x:v>R-088</x:v>
       </x:c>
       <x:c r="B99" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13640,10 +13650,10 @@
         <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>Automated refactoring planner</x:v>
+        <x:v>Cross-platform consistency checker</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
-        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
+        <x:v>Ensure feature behavior/API semantics stay aligned across Android/iOS/web.</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
         <x:v>P2</x:v>
@@ -13663,19 +13673,19 @@
     </x:row>
     <x:row r="100" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A100" s="32" t="str">
-        <x:v>R-090</x:v>
+        <x:v>R-089</x:v>
       </x:c>
       <x:c r="B100" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C100" s="32" t="str">
-        <x:v>Quality</x:v>
+        <x:v>Architecture</x:v>
       </x:c>
       <x:c r="D100" s="32" t="str">
-        <x:v>Mutation/fuzz testing</x:v>
+        <x:v>Automated refactoring planner</x:v>
       </x:c>
       <x:c r="E100" s="32" t="str">
-        <x:v>Higher assurance for critical services and parsers.</x:v>
+        <x:v>Detect debt and create safe incremental refactor plans.</x:v>
       </x:c>
       <x:c r="F100" s="32" t="str">
         <x:v>P2</x:v>
@@ -13695,19 +13705,19 @@
     </x:row>
     <x:row r="101" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A101" s="32" t="str">
-        <x:v>R-091</x:v>
+        <x:v>R-090</x:v>
       </x:c>
       <x:c r="B101" s="32" t="str">
         <x:v>ADVANCED</x:v>
       </x:c>
       <x:c r="C101" s="32" t="str">
-        <x:v>Cost</x:v>
+        <x:v>Quality</x:v>
       </x:c>
       <x:c r="D101" s="32" t="str">
-        <x:v>Predictive capacity scheduler</x:v>
+        <x:v>Mutation/fuzz testing</x:v>
       </x:c>
       <x:c r="E101" s="32" t="str">
-        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
+        <x:v>Higher assurance for critical services and parsers.</x:v>
       </x:c>
       <x:c r="F101" s="32" t="str">
         <x:v>P2</x:v>
@@ -13727,7 +13737,7 @@
     </x:row>
     <x:row r="102" s="40" customFormat="1" ht="34" customHeight="1">
       <x:c r="A102" s="32" t="str">
-        <x:v>R-092</x:v>
+        <x:v>R-091</x:v>
       </x:c>
       <x:c r="B102" s="32" t="str">
         <x:v>ADVANCED</x:v>
@@ -13736,10 +13746,10 @@
         <x:v>Cost</x:v>
       </x:c>
       <x:c r="D102" s="32" t="str">
-        <x:v>Spot/preemptible optimization</x:v>
+        <x:v>Predictive capacity scheduler</x:v>
       </x:c>
       <x:c r="E102" s="32" t="str">
-        <x:v>Use interruptible compute for safe non-release workloads.</x:v>
+        <x:v>Prewarm Mac/Linux workers using demand forecasts.</x:v>
       </x:c>
       <x:c r="F102" s="32" t="str">
         <x:v>P2</x:v>
@@ -13759,19 +13769,19 @@
     </x:row>
     <x:row r="103" s="40" customForm